--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H218"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="E79" t="n">
-        <v>72.25</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>69.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G79" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E80" t="n">
-        <v>71.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F80" t="n">
-        <v>69.55</v>
+        <v>71.5</v>
       </c>
       <c r="G80" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,3854 +2693,3966 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>70.3</v>
+        <v>72.8</v>
       </c>
       <c r="E81" t="n">
-        <v>73.3</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>70.3</v>
+        <v>71.5</v>
       </c>
       <c r="G81" t="n">
-        <v>72.84999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H81" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-37.37</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D82" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>73.5</v>
+        <v>72.25</v>
       </c>
       <c r="F82" t="n">
-        <v>71.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.51</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D83" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>73.15000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="F83" t="n">
-        <v>70.5</v>
+        <v>69.55</v>
       </c>
       <c r="G83" t="n">
-        <v>71.84999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>0.14</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>39.15</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29772381</v>
+        <v>5.29754581</v>
       </c>
       <c r="D84" t="n">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="E84" t="n">
-        <v>71.8</v>
+        <v>73.3</v>
       </c>
       <c r="F84" t="n">
-        <v>68.55</v>
+        <v>70.3</v>
       </c>
       <c r="G84" t="n">
-        <v>68.65000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-4.45</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-32.03</v>
+        <v>-37.37</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29452081</v>
+        <v>5.29380881</v>
       </c>
       <c r="D85" t="n">
-        <v>69.5</v>
+        <v>71.8</v>
       </c>
       <c r="E85" t="n">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="F85" t="n">
-        <v>68.15000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G85" t="n">
-        <v>68.75</v>
+        <v>71.75</v>
       </c>
       <c r="H85" t="n">
-        <v>0.15</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-245.51</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>5.26996981</v>
+        <v>5.29380881</v>
       </c>
       <c r="D86" t="n">
-        <v>67.75</v>
+        <v>72.8</v>
       </c>
       <c r="E86" t="n">
-        <v>70.15000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>67</v>
+        <v>70.5</v>
       </c>
       <c r="G86" t="n">
-        <v>68</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.99</v>
+        <v>39.15</v>
       </c>
       <c r="C87" t="n">
-        <v>5.27246881</v>
+        <v>5.29772381</v>
       </c>
       <c r="D87" t="n">
-        <v>68.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>69</v>
+        <v>71.8</v>
       </c>
       <c r="F87" t="n">
-        <v>65.65000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="G87" t="n">
-        <v>66.55</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-2.13</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-70.5937</v>
+        <v>-32.03</v>
       </c>
       <c r="C88" t="n">
-        <v>5.26540944</v>
+        <v>5.29452081</v>
       </c>
       <c r="D88" t="n">
-        <v>65.84999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E88" t="n">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="F88" t="n">
-        <v>64.45</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>65.84999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-83.42</v>
+        <v>-245.51</v>
       </c>
       <c r="C89" t="n">
-        <v>5.25706744</v>
+        <v>5.26996981</v>
       </c>
       <c r="D89" t="n">
-        <v>66.90000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="E89" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>67</v>
+      </c>
+      <c r="G89" t="n">
         <v>68</v>
       </c>
-      <c r="F89" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="H89" t="n">
-        <v>-0.38</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>32.9872</v>
+        <v>24.99</v>
       </c>
       <c r="C90" t="n">
-        <v>5.26036616</v>
+        <v>5.27246881</v>
       </c>
       <c r="D90" t="n">
-        <v>65.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>67.65000000000001</v>
+        <v>69</v>
       </c>
       <c r="F90" t="n">
-        <v>65.34999999999999</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>67.45</v>
+        <v>66.55</v>
       </c>
       <c r="H90" t="n">
-        <v>2.82</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-168.98</v>
+        <v>-70.5937</v>
       </c>
       <c r="C91" t="n">
-        <v>5.24346816</v>
+        <v>5.26540944</v>
       </c>
       <c r="D91" t="n">
-        <v>64.84999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>69</v>
+        <v>66.8</v>
       </c>
       <c r="F91" t="n">
-        <v>64.7</v>
+        <v>64.45</v>
       </c>
       <c r="G91" t="n">
-        <v>68.90000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>2.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-195.54</v>
+        <v>-83.42</v>
       </c>
       <c r="C92" t="n">
-        <v>5.22391416</v>
+        <v>5.25706744</v>
       </c>
       <c r="D92" t="n">
-        <v>69.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>70.2</v>
+        <v>68</v>
       </c>
       <c r="F92" t="n">
-        <v>67.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>69.05</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>0.22</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>16.18</v>
+        <v>32.9872</v>
       </c>
       <c r="C93" t="n">
-        <v>5.22553216</v>
+        <v>5.26036616</v>
       </c>
       <c r="D93" t="n">
-        <v>69.25</v>
+        <v>65.5</v>
       </c>
       <c r="E93" t="n">
-        <v>70.8</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>69.05</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>69.84999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="H93" t="n">
-        <v>1.16</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.87</v>
+        <v>-168.98</v>
       </c>
       <c r="C94" t="n">
-        <v>5.22691916</v>
+        <v>5.24346816</v>
       </c>
       <c r="D94" t="n">
-        <v>70.95</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="F94" t="n">
-        <v>69.15000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G94" t="n">
-        <v>70.15000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-145.08</v>
+        <v>-195.54</v>
       </c>
       <c r="C95" t="n">
-        <v>5.21241116</v>
+        <v>5.22391416</v>
       </c>
       <c r="D95" t="n">
-        <v>68.95</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>69</v>
+        <v>70.2</v>
       </c>
       <c r="F95" t="n">
-        <v>67.3</v>
+        <v>67.95</v>
       </c>
       <c r="G95" t="n">
-        <v>67.90000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="H95" t="n">
-        <v>-3.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.02</v>
+        <v>16.18</v>
       </c>
       <c r="C96" t="n">
-        <v>5.21491316</v>
+        <v>5.22553216</v>
       </c>
       <c r="D96" t="n">
-        <v>67.5</v>
+        <v>69.25</v>
       </c>
       <c r="E96" t="n">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F96" t="n">
-        <v>66.3</v>
+        <v>69.05</v>
       </c>
       <c r="G96" t="n">
-        <v>69.90000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>2.95</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-6.25</v>
+        <v>13.87</v>
       </c>
       <c r="C97" t="n">
-        <v>5.21428816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D97" t="n">
-        <v>71.25</v>
+        <v>70.95</v>
       </c>
       <c r="E97" t="n">
-        <v>73.3</v>
+        <v>71.3</v>
       </c>
       <c r="F97" t="n">
-        <v>70.84999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>71.3</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-48.58</v>
+        <v>-145.08</v>
       </c>
       <c r="C98" t="n">
-        <v>5.20943016</v>
+        <v>5.21241116</v>
       </c>
       <c r="D98" t="n">
-        <v>70.65000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E98" t="n">
-        <v>71.25</v>
+        <v>69</v>
       </c>
       <c r="F98" t="n">
-        <v>66.34999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G98" t="n">
-        <v>66.84999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>-6.24</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-197.18</v>
+        <v>25.02</v>
       </c>
       <c r="C99" t="n">
-        <v>5.18971216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D99" t="n">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="E99" t="n">
-        <v>67.34999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="G99" t="n">
-        <v>66</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.27</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>426.64</v>
+        <v>-6.25</v>
       </c>
       <c r="C100" t="n">
-        <v>5.23237616</v>
+        <v>5.21428816</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>71.25</v>
       </c>
       <c r="E100" t="n">
-        <v>68.7</v>
+        <v>73.3</v>
       </c>
       <c r="F100" t="n">
-        <v>66.34999999999999</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>66.8</v>
+        <v>71.3</v>
       </c>
       <c r="H100" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>41.4993</v>
+        <v>-48.58</v>
       </c>
       <c r="C101" t="n">
-        <v>5.23652609</v>
+        <v>5.20943016</v>
       </c>
       <c r="D101" t="n">
-        <v>65.59999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>66.05</v>
+        <v>71.25</v>
       </c>
       <c r="F101" t="n">
-        <v>64.2</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>64.8</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.99</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-220.5688</v>
+        <v>-197.18</v>
       </c>
       <c r="C102" t="n">
-        <v>5.21446921</v>
+        <v>5.18971216</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.65000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>63.45</v>
+        <v>65.8</v>
       </c>
       <c r="G102" t="n">
-        <v>67.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="H102" t="n">
-        <v>4.32</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>215.27</v>
+        <v>426.64</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23599621</v>
+        <v>5.23237616</v>
       </c>
       <c r="D103" t="n">
-        <v>69.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="E103" t="n">
-        <v>71.34999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F103" t="n">
-        <v>69.45</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>70.45</v>
+        <v>66.8</v>
       </c>
       <c r="H103" t="n">
-        <v>4.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-160.53</v>
+        <v>41.4993</v>
       </c>
       <c r="C104" t="n">
-        <v>5.21994321</v>
+        <v>5.23652609</v>
       </c>
       <c r="D104" t="n">
-        <v>69.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>70.8</v>
+        <v>66.05</v>
       </c>
       <c r="F104" t="n">
-        <v>68.7</v>
+        <v>64.2</v>
       </c>
       <c r="G104" t="n">
-        <v>69</v>
+        <v>64.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.06</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-304.01</v>
+        <v>-220.5688</v>
       </c>
       <c r="C105" t="n">
-        <v>5.18954221</v>
+        <v>5.21446921</v>
       </c>
       <c r="D105" t="n">
-        <v>69</v>
+        <v>66.2</v>
       </c>
       <c r="E105" t="n">
-        <v>71.5</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>68.3</v>
+        <v>63.45</v>
       </c>
       <c r="G105" t="n">
-        <v>70.05</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>1.52</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-30.3</v>
+        <v>215.27</v>
       </c>
       <c r="C106" t="n">
-        <v>5.18651221</v>
+        <v>5.23599621</v>
       </c>
       <c r="D106" t="n">
-        <v>68.05</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>69.34999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>68</v>
+        <v>69.45</v>
       </c>
       <c r="G106" t="n">
-        <v>68.8</v>
+        <v>70.45</v>
       </c>
       <c r="H106" t="n">
-        <v>-1.78</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-92.3</v>
+        <v>-160.53</v>
       </c>
       <c r="C107" t="n">
-        <v>5.17728221</v>
+        <v>5.21994321</v>
       </c>
       <c r="D107" t="n">
-        <v>68.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>69.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F107" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="G107" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.6</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>25.43</v>
+        <v>-304.01</v>
       </c>
       <c r="C108" t="n">
-        <v>5.17982521</v>
+        <v>5.18954221</v>
       </c>
       <c r="D108" t="n">
-        <v>68.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="E108" t="n">
-        <v>71.45</v>
+        <v>71.5</v>
       </c>
       <c r="F108" t="n">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G108" t="n">
-        <v>71.2</v>
+        <v>70.05</v>
       </c>
       <c r="H108" t="n">
-        <v>5.17</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>136.53</v>
+        <v>-30.3</v>
       </c>
       <c r="C109" t="n">
-        <v>5.19347821</v>
+        <v>5.18651221</v>
       </c>
       <c r="D109" t="n">
-        <v>71.2</v>
+        <v>68.05</v>
       </c>
       <c r="E109" t="n">
-        <v>73.40000000000001</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G109" t="n">
-        <v>71.8</v>
+        <v>68.8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.84</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-224.29</v>
+        <v>-92.3</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17104921</v>
+        <v>5.17728221</v>
       </c>
       <c r="D110" t="n">
-        <v>73.45</v>
+        <v>68.8</v>
       </c>
       <c r="E110" t="n">
-        <v>74</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>71.65000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="G110" t="n">
-        <v>73.3</v>
+        <v>67.7</v>
       </c>
       <c r="H110" t="n">
-        <v>2.09</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>97.7422</v>
+        <v>25.43</v>
       </c>
       <c r="C111" t="n">
-        <v>5.18082343</v>
+        <v>5.17982521</v>
       </c>
       <c r="D111" t="n">
-        <v>71.95</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>73.5</v>
+        <v>71.45</v>
       </c>
       <c r="F111" t="n">
-        <v>71.75</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G111" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.91</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-116.85</v>
+        <v>136.53</v>
       </c>
       <c r="C112" t="n">
-        <v>5.16913843</v>
+        <v>5.19347821</v>
       </c>
       <c r="D112" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E112" t="n">
-        <v>76.45</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>71.55</v>
+        <v>70</v>
       </c>
       <c r="G112" t="n">
-        <v>74.2</v>
+        <v>71.8</v>
       </c>
       <c r="H112" t="n">
-        <v>3.2</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>32.76</v>
+        <v>-224.29</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17241443</v>
+        <v>5.17104921</v>
       </c>
       <c r="D113" t="n">
-        <v>74.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E113" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F113" t="n">
-        <v>73.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>73.7</v>
+        <v>73.3</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.67</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-19.6</v>
+        <v>97.7422</v>
       </c>
       <c r="C114" t="n">
-        <v>5.17045443</v>
+        <v>5.18082343</v>
       </c>
       <c r="D114" t="n">
-        <v>73.7</v>
+        <v>71.95</v>
       </c>
       <c r="E114" t="n">
-        <v>73.95</v>
+        <v>73.5</v>
       </c>
       <c r="F114" t="n">
-        <v>71.65000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="G114" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.95</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>74.23999999999999</v>
+        <v>-116.85</v>
       </c>
       <c r="C115" t="n">
-        <v>5.17787843</v>
+        <v>5.16913843</v>
       </c>
       <c r="D115" t="n">
-        <v>73.75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>73.75</v>
+        <v>76.45</v>
       </c>
       <c r="F115" t="n">
-        <v>70.5</v>
+        <v>71.55</v>
       </c>
       <c r="G115" t="n">
-        <v>70.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>15.04</v>
+        <v>32.76</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17938243</v>
+        <v>5.17241443</v>
       </c>
       <c r="D116" t="n">
-        <v>70.95</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>72.15000000000001</v>
+        <v>75</v>
       </c>
       <c r="F116" t="n">
-        <v>70.95</v>
+        <v>73.25</v>
       </c>
       <c r="G116" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H116" t="n">
-        <v>0.99</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>213.47</v>
+        <v>-19.6</v>
       </c>
       <c r="C117" t="n">
-        <v>5.20072943</v>
+        <v>5.17045443</v>
       </c>
       <c r="D117" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E117" t="n">
-        <v>71.90000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="F117" t="n">
-        <v>70.40000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>71.45</v>
+        <v>73</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.21</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-167.67</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>5.18396243</v>
+        <v>5.17787843</v>
       </c>
       <c r="D118" t="n">
-        <v>72</v>
+        <v>73.75</v>
       </c>
       <c r="E118" t="n">
-        <v>73.45</v>
+        <v>73.75</v>
       </c>
       <c r="F118" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G118" t="n">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>2.59</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-78.5919</v>
+        <v>15.04</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17610324</v>
+        <v>5.17938243</v>
       </c>
       <c r="D119" t="n">
-        <v>73.3</v>
+        <v>70.95</v>
       </c>
       <c r="E119" t="n">
-        <v>73.3</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>71.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="G119" t="n">
-        <v>73.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.14</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-54.57</v>
+        <v>213.47</v>
       </c>
       <c r="C120" t="n">
-        <v>5.17064624</v>
+        <v>5.20072943</v>
       </c>
       <c r="D120" t="n">
-        <v>72.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>73.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>71.95</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>73.45</v>
+        <v>71.45</v>
       </c>
       <c r="H120" t="n">
-        <v>0.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>32.9</v>
+        <v>-167.67</v>
       </c>
       <c r="C121" t="n">
-        <v>5.17393624</v>
+        <v>5.18396243</v>
       </c>
       <c r="D121" t="n">
+        <v>72</v>
+      </c>
+      <c r="E121" t="n">
         <v>73.45</v>
       </c>
-      <c r="E121" t="n">
-        <v>74.40000000000001</v>
-      </c>
       <c r="F121" t="n">
-        <v>71.75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>73.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.41</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>41.93</v>
+        <v>-78.5919</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17812924</v>
+        <v>5.17610324</v>
       </c>
       <c r="D122" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="E122" t="n">
-        <v>73.65000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F122" t="n">
-        <v>68.7</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>69.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.44</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>52.87</v>
+        <v>-54.57</v>
       </c>
       <c r="C123" t="n">
-        <v>5.18341624</v>
+        <v>5.17064624</v>
       </c>
       <c r="D123" t="n">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E123" t="n">
-        <v>70.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>68.90000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G123" t="n">
-        <v>69.7</v>
+        <v>73.45</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>291.58</v>
+        <v>32.9</v>
       </c>
       <c r="C124" t="n">
-        <v>5.21257424</v>
+        <v>5.17393624</v>
       </c>
       <c r="D124" t="n">
-        <v>69.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E124" t="n">
-        <v>69.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>66.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G124" t="n">
-        <v>67</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>-3.87</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-60.7601</v>
+        <v>41.93</v>
       </c>
       <c r="C125" t="n">
-        <v>5.20649823</v>
+        <v>5.17812924</v>
       </c>
       <c r="D125" t="n">
-        <v>69.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E125" t="n">
-        <v>70.25</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>68.45</v>
+        <v>68.7</v>
       </c>
       <c r="G125" t="n">
-        <v>69.25</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>3.36</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>264.89</v>
+        <v>52.87</v>
       </c>
       <c r="C126" t="n">
-        <v>5.23298723</v>
+        <v>5.18341624</v>
       </c>
       <c r="D126" t="n">
-        <v>68.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>69.75</v>
+        <v>70.5</v>
       </c>
       <c r="F126" t="n">
-        <v>67.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>67.55</v>
+        <v>69.7</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.45</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>291.58</v>
       </c>
       <c r="C127" t="n">
-        <v>5.23298723</v>
+        <v>5.21257424</v>
       </c>
       <c r="D127" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>71.15000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F127" t="n">
-        <v>68.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G127" t="n">
-        <v>70.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H127" t="n">
-        <v>3.85</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-60.7601</v>
       </c>
       <c r="C128" t="n">
-        <v>5.23298723</v>
+        <v>5.20649823</v>
       </c>
       <c r="D128" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="F128" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="G128" t="n">
         <v>69.25</v>
       </c>
-      <c r="E128" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F128" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="G128" t="n">
-        <v>69.65000000000001</v>
-      </c>
       <c r="H128" t="n">
-        <v>-0.71</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-369.37</v>
+        <v>264.89</v>
       </c>
       <c r="C129" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D129" t="n">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E129" t="n">
-        <v>69.5</v>
+        <v>69.75</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.84999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.58</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D130" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E130" t="n">
-        <v>70.34999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="F130" t="n">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="G130" t="n">
-        <v>69.95</v>
+        <v>67.55</v>
       </c>
       <c r="H130" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>68.9663</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>5.20294686</v>
+        <v>5.23298723</v>
       </c>
       <c r="D131" t="n">
-        <v>68.34999999999999</v>
+        <v>69</v>
       </c>
       <c r="E131" t="n">
-        <v>70.3</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>68.34999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G131" t="n">
-        <v>70.05</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>0.14</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-247.41</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>5.17820586</v>
+        <v>5.23298723</v>
       </c>
       <c r="D132" t="n">
-        <v>69.5</v>
+        <v>69.25</v>
       </c>
       <c r="E132" t="n">
-        <v>74.15000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>69.45</v>
+        <v>68.2</v>
       </c>
       <c r="G132" t="n">
-        <v>73.84999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>5.42</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>27.55</v>
+        <v>-369.37</v>
       </c>
       <c r="C133" t="n">
-        <v>5.18096086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D133" t="n">
-        <v>73.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E133" t="n">
-        <v>75.15000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F133" t="n">
-        <v>73.05</v>
+        <v>67.3</v>
       </c>
       <c r="G133" t="n">
-        <v>73.40000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.61</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-286.2</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5.15234086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D134" t="n">
-        <v>73.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="E134" t="n">
-        <v>74.40000000000001</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>73.05</v>
+        <v>68.5</v>
       </c>
       <c r="G134" t="n">
-        <v>73.65000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="H134" t="n">
-        <v>0.34</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>48.88</v>
+        <v>68.9663</v>
       </c>
       <c r="C135" t="n">
-        <v>5.15722886</v>
+        <v>5.20294686</v>
       </c>
       <c r="D135" t="n">
-        <v>76.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>78.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F135" t="n">
-        <v>75.40000000000001</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>76.84999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H135" t="n">
-        <v>4.34</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-55.96</v>
+        <v>-247.41</v>
       </c>
       <c r="C136" t="n">
-        <v>5.15163286</v>
+        <v>5.17820586</v>
       </c>
       <c r="D136" t="n">
-        <v>75.05</v>
+        <v>69.5</v>
       </c>
       <c r="E136" t="n">
-        <v>75.90000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>74.25</v>
+        <v>69.45</v>
       </c>
       <c r="G136" t="n">
-        <v>75.59999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.63</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-385.85</v>
+        <v>27.55</v>
       </c>
       <c r="C137" t="n">
-        <v>5.11304786</v>
+        <v>5.18096086</v>
       </c>
       <c r="D137" t="n">
-        <v>72.40000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E137" t="n">
-        <v>72.40000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>64.5</v>
+        <v>73.05</v>
       </c>
       <c r="G137" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-14.15</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>139.59</v>
+        <v>-286.2</v>
       </c>
       <c r="C138" t="n">
-        <v>5.12700686</v>
+        <v>5.15234086</v>
       </c>
       <c r="D138" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>64.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>61.75</v>
+        <v>73.05</v>
       </c>
       <c r="G138" t="n">
-        <v>62.1</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>-4.31</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1468.42</v>
+        <v>48.88</v>
       </c>
       <c r="C139" t="n">
-        <v>5.27384886</v>
+        <v>5.15722886</v>
       </c>
       <c r="D139" t="n">
-        <v>62.6</v>
+        <v>76.8</v>
       </c>
       <c r="E139" t="n">
-        <v>63.35</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>61</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G139" t="n">
-        <v>61.6</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>292.93</v>
+        <v>-55.96</v>
       </c>
       <c r="C140" t="n">
-        <v>5.30314186</v>
+        <v>5.15163286</v>
       </c>
       <c r="D140" t="n">
-        <v>62.5</v>
+        <v>75.05</v>
       </c>
       <c r="E140" t="n">
-        <v>63.85</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>61.55</v>
+        <v>74.25</v>
       </c>
       <c r="G140" t="n">
-        <v>62.25</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>1.06</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>17.9</v>
+        <v>-385.85</v>
       </c>
       <c r="C141" t="n">
-        <v>5.30493186</v>
+        <v>5.11304786</v>
       </c>
       <c r="D141" t="n">
-        <v>63.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E141" t="n">
-        <v>64.95</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F141" t="n">
-        <v>61.35</v>
+        <v>64.5</v>
       </c>
       <c r="G141" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.72</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-224.88</v>
+        <v>139.59</v>
       </c>
       <c r="C142" t="n">
-        <v>5.28244386</v>
+        <v>5.12700686</v>
       </c>
       <c r="D142" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E142" t="n">
-        <v>62.25</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>60.4</v>
+        <v>61.75</v>
       </c>
       <c r="G142" t="n">
-        <v>62.15</v>
+        <v>62.1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.57</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-244.5</v>
+        <v>1468.42</v>
       </c>
       <c r="C143" t="n">
-        <v>5.25799386</v>
+        <v>5.27384886</v>
       </c>
       <c r="D143" t="n">
-        <v>61.9</v>
+        <v>62.6</v>
       </c>
       <c r="E143" t="n">
-        <v>62.35</v>
+        <v>63.35</v>
       </c>
       <c r="F143" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G143" t="n">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.14</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-302.48</v>
+        <v>292.93</v>
       </c>
       <c r="C144" t="n">
-        <v>5.22774586</v>
+        <v>5.30314186</v>
       </c>
       <c r="D144" t="n">
-        <v>60.1</v>
+        <v>62.5</v>
       </c>
       <c r="E144" t="n">
-        <v>61</v>
+        <v>63.85</v>
       </c>
       <c r="F144" t="n">
-        <v>58.6</v>
+        <v>61.55</v>
       </c>
       <c r="G144" t="n">
-        <v>60.45</v>
+        <v>62.25</v>
       </c>
       <c r="H144" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-177.8636</v>
+        <v>17.9</v>
       </c>
       <c r="C145" t="n">
-        <v>5.2099595</v>
+        <v>5.30493186</v>
       </c>
       <c r="D145" t="n">
-        <v>60</v>
+        <v>63.2</v>
       </c>
       <c r="E145" t="n">
-        <v>60.05</v>
+        <v>64.95</v>
       </c>
       <c r="F145" t="n">
-        <v>55.7</v>
+        <v>61.35</v>
       </c>
       <c r="G145" t="n">
-        <v>57.85</v>
+        <v>61.8</v>
       </c>
       <c r="H145" t="n">
-        <v>-4.3</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-228.55</v>
+        <v>-224.88</v>
       </c>
       <c r="C146" t="n">
-        <v>5.1871045</v>
+        <v>5.28244386</v>
       </c>
       <c r="D146" t="n">
-        <v>56.95</v>
+        <v>61.8</v>
       </c>
       <c r="E146" t="n">
-        <v>59.1</v>
+        <v>62.25</v>
       </c>
       <c r="F146" t="n">
-        <v>56</v>
+        <v>60.4</v>
       </c>
       <c r="G146" t="n">
-        <v>58.55</v>
+        <v>62.15</v>
       </c>
       <c r="H146" t="n">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>423.9973</v>
+        <v>-244.5</v>
       </c>
       <c r="C147" t="n">
-        <v>5.22950423</v>
+        <v>5.25799386</v>
       </c>
       <c r="D147" t="n">
-        <v>57.05</v>
+        <v>61.9</v>
       </c>
       <c r="E147" t="n">
-        <v>62</v>
+        <v>62.35</v>
       </c>
       <c r="F147" t="n">
-        <v>56.55</v>
+        <v>59.9</v>
       </c>
       <c r="G147" t="n">
-        <v>61.9</v>
+        <v>60.2</v>
       </c>
       <c r="H147" t="n">
-        <v>5.72</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-119.16</v>
+        <v>-302.48</v>
       </c>
       <c r="C148" t="n">
-        <v>5.21758823</v>
+        <v>5.22774586</v>
       </c>
       <c r="D148" t="n">
-        <v>60.5</v>
+        <v>60.1</v>
       </c>
       <c r="E148" t="n">
-        <v>60.75</v>
+        <v>61</v>
       </c>
       <c r="F148" t="n">
-        <v>58.75</v>
+        <v>58.6</v>
       </c>
       <c r="G148" t="n">
-        <v>59.1</v>
+        <v>60.45</v>
       </c>
       <c r="H148" t="n">
-        <v>-4.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-301.92</v>
+        <v>-177.8636</v>
       </c>
       <c r="C149" t="n">
-        <v>5.18739623</v>
+        <v>5.2099595</v>
       </c>
       <c r="D149" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="E149" t="n">
-        <v>58.95</v>
+        <v>60.05</v>
       </c>
       <c r="F149" t="n">
-        <v>56.85</v>
+        <v>55.7</v>
       </c>
       <c r="G149" t="n">
-        <v>57.25</v>
+        <v>57.85</v>
       </c>
       <c r="H149" t="n">
-        <v>-3.13</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>112.29</v>
+        <v>-228.55</v>
       </c>
       <c r="C150" t="n">
-        <v>5.19862523</v>
+        <v>5.1871045</v>
       </c>
       <c r="D150" t="n">
-        <v>57.1</v>
+        <v>56.95</v>
       </c>
       <c r="E150" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
       <c r="F150" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="G150" t="n">
-        <v>56.65</v>
+        <v>58.55</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.05</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-62.4836</v>
+        <v>423.9973</v>
       </c>
       <c r="C151" t="n">
-        <v>5.19237687</v>
+        <v>5.22950423</v>
       </c>
       <c r="D151" t="n">
-        <v>55.3</v>
+        <v>57.05</v>
       </c>
       <c r="E151" t="n">
-        <v>57.9</v>
+        <v>62</v>
       </c>
       <c r="F151" t="n">
-        <v>54.95</v>
+        <v>56.55</v>
       </c>
       <c r="G151" t="n">
-        <v>57.35</v>
+        <v>61.9</v>
       </c>
       <c r="H151" t="n">
-        <v>1.24</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-29.35</v>
+        <v>-119.16</v>
       </c>
       <c r="C152" t="n">
-        <v>5.18944187</v>
+        <v>5.21758823</v>
       </c>
       <c r="D152" t="n">
-        <v>56.2</v>
+        <v>60.5</v>
       </c>
       <c r="E152" t="n">
-        <v>57.1</v>
+        <v>60.75</v>
       </c>
       <c r="F152" t="n">
-        <v>55.8</v>
+        <v>58.75</v>
       </c>
       <c r="G152" t="n">
-        <v>55.85</v>
+        <v>59.1</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.62</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>54.46</v>
+        <v>-301.92</v>
       </c>
       <c r="C153" t="n">
-        <v>5.19488787</v>
+        <v>5.18739623</v>
       </c>
       <c r="D153" t="n">
-        <v>55.3</v>
+        <v>58.95</v>
       </c>
       <c r="E153" t="n">
-        <v>55.55</v>
+        <v>58.95</v>
       </c>
       <c r="F153" t="n">
-        <v>53.25</v>
+        <v>56.85</v>
       </c>
       <c r="G153" t="n">
-        <v>54.7</v>
+        <v>57.25</v>
       </c>
       <c r="H153" t="n">
-        <v>-2.06</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>17.32</v>
+        <v>112.29</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19661987</v>
+        <v>5.19862523</v>
       </c>
       <c r="D154" t="n">
-        <v>54</v>
+        <v>57.1</v>
       </c>
       <c r="E154" t="n">
-        <v>54.1</v>
+        <v>57.6</v>
       </c>
       <c r="F154" t="n">
-        <v>52.25</v>
+        <v>56.5</v>
       </c>
       <c r="G154" t="n">
-        <v>53.15</v>
+        <v>56.65</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.83</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>93.42</v>
+        <v>-62.4836</v>
       </c>
       <c r="C155" t="n">
-        <v>5.20596187</v>
+        <v>5.19237687</v>
       </c>
       <c r="D155" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>53.25</v>
+        <v>54.95</v>
       </c>
       <c r="G155" t="n">
-        <v>57</v>
+        <v>57.35</v>
       </c>
       <c r="H155" t="n">
-        <v>7.24</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>64.81</v>
+        <v>-29.35</v>
       </c>
       <c r="C156" t="n">
-        <v>5.21244287</v>
+        <v>5.18944187</v>
       </c>
       <c r="D156" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="E156" t="n">
-        <v>58.05</v>
+        <v>57.1</v>
       </c>
       <c r="F156" t="n">
-        <v>56.5</v>
+        <v>55.8</v>
       </c>
       <c r="G156" t="n">
-        <v>56.85</v>
+        <v>55.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.26</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-172.75</v>
+        <v>54.46</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19516787</v>
+        <v>5.19488787</v>
       </c>
       <c r="D157" t="n">
-        <v>56.85</v>
+        <v>55.3</v>
       </c>
       <c r="E157" t="n">
-        <v>57.2</v>
+        <v>55.55</v>
       </c>
       <c r="F157" t="n">
-        <v>55</v>
+        <v>53.25</v>
       </c>
       <c r="G157" t="n">
-        <v>56</v>
+        <v>54.7</v>
       </c>
       <c r="H157" t="n">
-        <v>-1.5</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-24.86</v>
+        <v>17.32</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19268187</v>
+        <v>5.19661987</v>
       </c>
       <c r="D158" t="n">
-        <v>55.75</v>
+        <v>54</v>
       </c>
       <c r="E158" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="F158" t="n">
-        <v>53.7</v>
+        <v>52.25</v>
       </c>
       <c r="G158" t="n">
-        <v>53.9</v>
+        <v>53.15</v>
       </c>
       <c r="H158" t="n">
-        <v>-3.75</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.38</v>
+        <v>93.42</v>
       </c>
       <c r="C159" t="n">
-        <v>5.19441987</v>
+        <v>5.20596187</v>
       </c>
       <c r="D159" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E159" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F159" t="n">
         <v>53.25</v>
       </c>
-      <c r="E159" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F159" t="n">
-        <v>51.75</v>
-      </c>
       <c r="G159" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H159" t="n">
-        <v>-3.53</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>14.06</v>
+        <v>64.81</v>
       </c>
       <c r="C160" t="n">
-        <v>5.19582587</v>
+        <v>5.21244287</v>
       </c>
       <c r="D160" t="n">
-        <v>50.15</v>
+        <v>56.6</v>
       </c>
       <c r="E160" t="n">
-        <v>51.55</v>
+        <v>58.05</v>
       </c>
       <c r="F160" t="n">
-        <v>49.64</v>
+        <v>56.5</v>
       </c>
       <c r="G160" t="n">
-        <v>50.5</v>
+        <v>56.85</v>
       </c>
       <c r="H160" t="n">
-        <v>-2.88</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-21.2345</v>
+        <v>-172.75</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19370242</v>
+        <v>5.19516787</v>
       </c>
       <c r="D161" t="n">
-        <v>50</v>
+        <v>56.85</v>
       </c>
       <c r="E161" t="n">
-        <v>50.8</v>
+        <v>57.2</v>
       </c>
       <c r="F161" t="n">
-        <v>47.9</v>
+        <v>55</v>
       </c>
       <c r="G161" t="n">
-        <v>48.32</v>
+        <v>56</v>
       </c>
       <c r="H161" t="n">
-        <v>-4.32</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>47.7</v>
+        <v>-24.86</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19847242</v>
+        <v>5.19268187</v>
       </c>
       <c r="D162" t="n">
-        <v>48.98</v>
+        <v>55.75</v>
       </c>
       <c r="E162" t="n">
-        <v>49.94</v>
+        <v>55.8</v>
       </c>
       <c r="F162" t="n">
-        <v>48.18</v>
+        <v>53.7</v>
       </c>
       <c r="G162" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="H162" t="n">
-        <v>2.32</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>92.59999999999999</v>
+        <v>17.38</v>
       </c>
       <c r="C163" t="n">
-        <v>5.20773242</v>
+        <v>5.19441987</v>
       </c>
       <c r="D163" t="n">
-        <v>49.44</v>
+        <v>53.25</v>
       </c>
       <c r="E163" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="F163" t="n">
-        <v>46.74</v>
+        <v>51.75</v>
       </c>
       <c r="G163" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="H163" t="n">
-        <v>-4.13</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-95.51000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19818142</v>
+        <v>5.19582587</v>
       </c>
       <c r="D164" t="n">
-        <v>47</v>
+        <v>50.15</v>
       </c>
       <c r="E164" t="n">
-        <v>47</v>
+        <v>51.55</v>
       </c>
       <c r="F164" t="n">
-        <v>45.86</v>
+        <v>49.64</v>
       </c>
       <c r="G164" t="n">
-        <v>46.28</v>
+        <v>50.5</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.36</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-254.06</v>
+        <v>-21.2345</v>
       </c>
       <c r="C165" t="n">
-        <v>5.17277542</v>
+        <v>5.19370242</v>
       </c>
       <c r="D165" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="E165" t="n">
-        <v>47.18</v>
+        <v>50.8</v>
       </c>
       <c r="F165" t="n">
-        <v>45.76</v>
+        <v>47.9</v>
       </c>
       <c r="G165" t="n">
-        <v>45.9</v>
+        <v>48.32</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.82</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-316.19</v>
+        <v>47.7</v>
       </c>
       <c r="C166" t="n">
-        <v>5.14115642</v>
+        <v>5.19847242</v>
       </c>
       <c r="D166" t="n">
-        <v>45.9</v>
+        <v>48.98</v>
       </c>
       <c r="E166" t="n">
-        <v>46.78</v>
+        <v>49.94</v>
       </c>
       <c r="F166" t="n">
-        <v>45.26</v>
+        <v>48.18</v>
       </c>
       <c r="G166" t="n">
-        <v>46.08</v>
+        <v>49.44</v>
       </c>
       <c r="H166" t="n">
-        <v>0.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-150.87</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C167" t="n">
-        <v>5.12606942</v>
+        <v>5.20773242</v>
       </c>
       <c r="D167" t="n">
-        <v>47.7</v>
+        <v>49.44</v>
       </c>
       <c r="E167" t="n">
-        <v>48.9</v>
+        <v>49.44</v>
       </c>
       <c r="F167" t="n">
-        <v>46.64</v>
+        <v>46.74</v>
       </c>
       <c r="G167" t="n">
-        <v>46.84</v>
+        <v>47.4</v>
       </c>
       <c r="H167" t="n">
-        <v>1.65</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-236.76</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C168" t="n">
-        <v>5.10239342</v>
+        <v>5.19818142</v>
       </c>
       <c r="D168" t="n">
-        <v>46.92</v>
+        <v>47</v>
       </c>
       <c r="E168" t="n">
-        <v>48.28</v>
+        <v>47</v>
       </c>
       <c r="F168" t="n">
-        <v>46.84</v>
+        <v>45.86</v>
       </c>
       <c r="G168" t="n">
-        <v>47.36</v>
+        <v>46.28</v>
       </c>
       <c r="H168" t="n">
-        <v>1.11</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-36.92</v>
+        <v>-254.06</v>
       </c>
       <c r="C169" t="n">
-        <v>5.09870142</v>
+        <v>5.17277542</v>
       </c>
       <c r="D169" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="E169" t="n">
-        <v>47.56</v>
+        <v>47.18</v>
       </c>
       <c r="F169" t="n">
-        <v>45.72</v>
+        <v>45.76</v>
       </c>
       <c r="G169" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="H169" t="n">
-        <v>-2.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>64.78</v>
+        <v>-316.19</v>
       </c>
       <c r="C170" t="n">
-        <v>5.10517942</v>
+        <v>5.14115642</v>
       </c>
       <c r="D170" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="E170" t="n">
-        <v>48.42</v>
+        <v>46.78</v>
       </c>
       <c r="F170" t="n">
-        <v>46.26</v>
+        <v>45.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.6</v>
+        <v>46.08</v>
       </c>
       <c r="H170" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-44.41</v>
+        <v>-150.87</v>
       </c>
       <c r="C171" t="n">
-        <v>5.10073842</v>
+        <v>5.12606942</v>
       </c>
       <c r="D171" t="n">
-        <v>47.06</v>
+        <v>47.7</v>
       </c>
       <c r="E171" t="n">
-        <v>48.98</v>
+        <v>48.9</v>
       </c>
       <c r="F171" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="G171" t="n">
-        <v>48.52</v>
+        <v>46.84</v>
       </c>
       <c r="H171" t="n">
-        <v>4.12</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-124.97</v>
+        <v>-236.76</v>
       </c>
       <c r="C172" t="n">
-        <v>5.08824142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D172" t="n">
-        <v>47.6</v>
+        <v>46.92</v>
       </c>
       <c r="E172" t="n">
-        <v>48.08</v>
+        <v>48.28</v>
       </c>
       <c r="F172" t="n">
-        <v>46.72</v>
+        <v>46.84</v>
       </c>
       <c r="G172" t="n">
-        <v>46.76</v>
+        <v>47.36</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.63</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-272.6</v>
+        <v>-36.92</v>
       </c>
       <c r="C173" t="n">
-        <v>5.06098142</v>
+        <v>5.09870142</v>
       </c>
       <c r="D173" t="n">
-        <v>46.76</v>
+        <v>47</v>
       </c>
       <c r="E173" t="n">
-        <v>48.3</v>
+        <v>47.56</v>
       </c>
       <c r="F173" t="n">
-        <v>46.02</v>
+        <v>45.72</v>
       </c>
       <c r="G173" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="H173" t="n">
-        <v>1.41</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>83.54000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="C174" t="n">
-        <v>5.06933542</v>
+        <v>5.10517942</v>
       </c>
       <c r="D174" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="E174" t="n">
-        <v>47.92</v>
+        <v>48.42</v>
       </c>
       <c r="F174" t="n">
-        <v>46.46</v>
+        <v>46.26</v>
       </c>
       <c r="G174" t="n">
-        <v>47.2</v>
+        <v>46.6</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.46</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-232.94</v>
+        <v>-44.41</v>
       </c>
       <c r="C175" t="n">
-        <v>5.04604142</v>
+        <v>5.10073842</v>
       </c>
       <c r="D175" t="n">
-        <v>47.2</v>
+        <v>47.06</v>
       </c>
       <c r="E175" t="n">
-        <v>48.84</v>
+        <v>48.98</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.56</v>
+        <v>48.52</v>
       </c>
       <c r="H175" t="n">
-        <v>2.88</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-101.2265</v>
+        <v>-124.97</v>
       </c>
       <c r="C176" t="n">
-        <v>5.03591877</v>
+        <v>5.08824142</v>
       </c>
       <c r="D176" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="E176" t="n">
-        <v>49.46</v>
+        <v>48.08</v>
       </c>
       <c r="F176" t="n">
-        <v>48.24</v>
+        <v>46.72</v>
       </c>
       <c r="G176" t="n">
-        <v>48.78</v>
+        <v>46.76</v>
       </c>
       <c r="H176" t="n">
-        <v>0.45</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-146.01</v>
+        <v>-272.6</v>
       </c>
       <c r="C177" t="n">
-        <v>5.02131777</v>
+        <v>5.06098142</v>
       </c>
       <c r="D177" t="n">
-        <v>49.22</v>
+        <v>46.76</v>
       </c>
       <c r="E177" t="n">
-        <v>51</v>
+        <v>48.3</v>
       </c>
       <c r="F177" t="n">
-        <v>49.22</v>
+        <v>46.02</v>
       </c>
       <c r="G177" t="n">
-        <v>50.4</v>
+        <v>47.42</v>
       </c>
       <c r="H177" t="n">
-        <v>3.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>14.25</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>5.02274277</v>
+        <v>5.06933542</v>
       </c>
       <c r="D178" t="n">
-        <v>50.55</v>
+        <v>47.42</v>
       </c>
       <c r="E178" t="n">
-        <v>51</v>
+        <v>47.92</v>
       </c>
       <c r="F178" t="n">
-        <v>48.2</v>
+        <v>46.46</v>
       </c>
       <c r="G178" t="n">
-        <v>48.94</v>
+        <v>47.2</v>
       </c>
       <c r="H178" t="n">
-        <v>-2.9</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7.54</v>
+        <v>-232.94</v>
       </c>
       <c r="C179" t="n">
-        <v>5.02349677</v>
+        <v>5.04604142</v>
       </c>
       <c r="D179" t="n">
-        <v>49.96</v>
+        <v>47.2</v>
       </c>
       <c r="E179" t="n">
-        <v>49.98</v>
+        <v>48.84</v>
       </c>
       <c r="F179" t="n">
-        <v>48.72</v>
+        <v>46.7</v>
       </c>
       <c r="G179" t="n">
-        <v>49.12</v>
+        <v>48.56</v>
       </c>
       <c r="H179" t="n">
-        <v>0.37</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>29.93</v>
+        <v>-101.2265</v>
       </c>
       <c r="C180" t="n">
-        <v>5.02648977</v>
+        <v>5.03591877</v>
       </c>
       <c r="D180" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="E180" t="n">
-        <v>49.36</v>
+        <v>49.46</v>
       </c>
       <c r="F180" t="n">
-        <v>48.18</v>
+        <v>48.24</v>
       </c>
       <c r="G180" t="n">
-        <v>48.64</v>
+        <v>48.78</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.98</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-93.37</v>
+        <v>-146.01</v>
       </c>
       <c r="C181" t="n">
-        <v>5.01715277</v>
+        <v>5.02131777</v>
       </c>
       <c r="D181" t="n">
-        <v>48.4</v>
+        <v>49.22</v>
       </c>
       <c r="E181" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F181" t="n">
-        <v>47.2</v>
+        <v>49.22</v>
       </c>
       <c r="G181" t="n">
-        <v>47.64</v>
+        <v>50.4</v>
       </c>
       <c r="H181" t="n">
-        <v>-2.06</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-93.65000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C182" t="n">
-        <v>5.00778777</v>
+        <v>5.02274277</v>
       </c>
       <c r="D182" t="n">
-        <v>47.64</v>
+        <v>50.55</v>
       </c>
       <c r="E182" t="n">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="F182" t="n">
-        <v>47.22</v>
+        <v>48.2</v>
       </c>
       <c r="G182" t="n">
-        <v>48.96</v>
+        <v>48.94</v>
       </c>
       <c r="H182" t="n">
-        <v>2.77</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>28.06</v>
+        <v>7.54</v>
       </c>
       <c r="C183" t="n">
-        <v>5.01059377</v>
+        <v>5.02349677</v>
       </c>
       <c r="D183" t="n">
-        <v>48.36</v>
+        <v>49.96</v>
       </c>
       <c r="E183" t="n">
-        <v>48.76</v>
+        <v>49.98</v>
       </c>
       <c r="F183" t="n">
-        <v>47.52</v>
+        <v>48.72</v>
       </c>
       <c r="G183" t="n">
-        <v>47.98</v>
+        <v>49.12</v>
       </c>
       <c r="H183" t="n">
-        <v>-2</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-160.94</v>
+        <v>29.93</v>
       </c>
       <c r="C184" t="n">
-        <v>4.99449977</v>
+        <v>5.02648977</v>
       </c>
       <c r="D184" t="n">
-        <v>47.98</v>
+        <v>49.1</v>
       </c>
       <c r="E184" t="n">
-        <v>48.46</v>
+        <v>49.36</v>
       </c>
       <c r="F184" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="G184" t="n">
-        <v>48.08</v>
+        <v>48.64</v>
       </c>
       <c r="H184" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>76.84999999999999</v>
+        <v>-93.37</v>
       </c>
       <c r="C185" t="n">
-        <v>5.00218477</v>
+        <v>5.01715277</v>
       </c>
       <c r="D185" t="n">
-        <v>49.54</v>
+        <v>48.4</v>
       </c>
       <c r="E185" t="n">
-        <v>50.5</v>
+        <v>48.4</v>
       </c>
       <c r="F185" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="G185" t="n">
-        <v>49.68</v>
+        <v>47.64</v>
       </c>
       <c r="H185" t="n">
-        <v>3.33</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-70.88</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C186" t="n">
-        <v>4.99509677</v>
+        <v>5.00778777</v>
       </c>
       <c r="D186" t="n">
-        <v>51.9</v>
+        <v>47.64</v>
       </c>
       <c r="E186" t="n">
-        <v>55.6</v>
+        <v>49.3</v>
       </c>
       <c r="F186" t="n">
-        <v>51.9</v>
+        <v>47.22</v>
       </c>
       <c r="G186" t="n">
-        <v>54.6</v>
+        <v>48.96</v>
       </c>
       <c r="H186" t="n">
-        <v>9.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-223.97</v>
+        <v>28.06</v>
       </c>
       <c r="C187" t="n">
-        <v>4.97269977</v>
+        <v>5.01059377</v>
       </c>
       <c r="D187" t="n">
-        <v>54.7</v>
+        <v>48.36</v>
       </c>
       <c r="E187" t="n">
-        <v>56.1</v>
+        <v>48.76</v>
       </c>
       <c r="F187" t="n">
-        <v>53.7</v>
+        <v>47.52</v>
       </c>
       <c r="G187" t="n">
-        <v>54.25</v>
+        <v>47.98</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.64</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-908.88</v>
+        <v>-160.94</v>
       </c>
       <c r="C188" t="n">
-        <v>4.88181177</v>
+        <v>4.99449977</v>
       </c>
       <c r="D188" t="n">
-        <v>52.85</v>
+        <v>47.98</v>
       </c>
       <c r="E188" t="n">
-        <v>53.8</v>
+        <v>48.46</v>
       </c>
       <c r="F188" t="n">
-        <v>51.3</v>
+        <v>47.32</v>
       </c>
       <c r="G188" t="n">
-        <v>53.4</v>
+        <v>48.08</v>
       </c>
       <c r="H188" t="n">
-        <v>-1.57</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-219</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C189" t="n">
-        <v>4.85991177</v>
+        <v>5.00218477</v>
       </c>
       <c r="D189" t="n">
-        <v>52.75</v>
+        <v>49.54</v>
       </c>
       <c r="E189" t="n">
-        <v>54.45</v>
+        <v>50.5</v>
       </c>
       <c r="F189" t="n">
-        <v>51.45</v>
+        <v>48.9</v>
       </c>
       <c r="G189" t="n">
-        <v>51.85</v>
+        <v>49.68</v>
       </c>
       <c r="H189" t="n">
-        <v>-2.9</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>81.19</v>
+        <v>-70.88</v>
       </c>
       <c r="C190" t="n">
-        <v>4.86803077</v>
+        <v>4.99509677</v>
       </c>
       <c r="D190" t="n">
-        <v>51.85</v>
+        <v>51.9</v>
       </c>
       <c r="E190" t="n">
-        <v>51.85</v>
+        <v>55.6</v>
       </c>
       <c r="F190" t="n">
-        <v>49.6</v>
+        <v>51.9</v>
       </c>
       <c r="G190" t="n">
-        <v>50.45</v>
+        <v>54.6</v>
       </c>
       <c r="H190" t="n">
-        <v>-2.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7.21</v>
+        <v>-223.97</v>
       </c>
       <c r="C191" t="n">
-        <v>4.86875177</v>
+        <v>4.97269977</v>
       </c>
       <c r="D191" t="n">
-        <v>50.05</v>
+        <v>54.7</v>
       </c>
       <c r="E191" t="n">
-        <v>50.8</v>
+        <v>56.1</v>
       </c>
       <c r="F191" t="n">
-        <v>49.52</v>
+        <v>53.7</v>
       </c>
       <c r="G191" t="n">
-        <v>50.65</v>
+        <v>54.25</v>
       </c>
       <c r="H191" t="n">
-        <v>0.4</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>144.28</v>
+        <v>-908.88</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88317977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D192" t="n">
-        <v>50</v>
+        <v>52.85</v>
       </c>
       <c r="E192" t="n">
-        <v>50.6</v>
+        <v>53.8</v>
       </c>
       <c r="F192" t="n">
-        <v>49.08</v>
+        <v>51.3</v>
       </c>
       <c r="G192" t="n">
-        <v>49.12</v>
+        <v>53.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-3.02</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-41.02</v>
+        <v>-219</v>
       </c>
       <c r="C193" t="n">
-        <v>4.87907777</v>
+        <v>4.85991177</v>
       </c>
       <c r="D193" t="n">
-        <v>49.18</v>
+        <v>52.75</v>
       </c>
       <c r="E193" t="n">
-        <v>50.1</v>
+        <v>54.45</v>
       </c>
       <c r="F193" t="n">
-        <v>48.82</v>
+        <v>51.45</v>
       </c>
       <c r="G193" t="n">
-        <v>49.92</v>
+        <v>51.85</v>
       </c>
       <c r="H193" t="n">
-        <v>1.63</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>68.70999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="C194" t="n">
-        <v>4.88594877</v>
+        <v>4.86803077</v>
       </c>
       <c r="D194" t="n">
-        <v>50.5</v>
+        <v>51.85</v>
       </c>
       <c r="E194" t="n">
-        <v>50.95</v>
+        <v>51.85</v>
       </c>
       <c r="F194" t="n">
-        <v>49.74</v>
+        <v>49.6</v>
       </c>
       <c r="G194" t="n">
-        <v>50.1</v>
+        <v>50.45</v>
       </c>
       <c r="H194" t="n">
-        <v>0.36</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>20.01</v>
+        <v>7.21</v>
       </c>
       <c r="C195" t="n">
-        <v>4.88794977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D195" t="n">
-        <v>50</v>
+        <v>50.05</v>
       </c>
       <c r="E195" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F195" t="n">
-        <v>49.04</v>
+        <v>49.52</v>
       </c>
       <c r="G195" t="n">
-        <v>49.06</v>
+        <v>50.65</v>
       </c>
       <c r="H195" t="n">
-        <v>-2.08</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-18.77</v>
+        <v>144.28</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88607277</v>
+        <v>4.88317977</v>
       </c>
       <c r="D196" t="n">
+        <v>50</v>
+      </c>
+      <c r="E196" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="F196" t="n">
         <v>49.08</v>
       </c>
-      <c r="E196" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="F196" t="n">
-        <v>48.7</v>
-      </c>
       <c r="G196" t="n">
-        <v>49.4</v>
+        <v>49.12</v>
       </c>
       <c r="H196" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>95.14</v>
+        <v>-41.02</v>
       </c>
       <c r="C197" t="n">
-        <v>4.89558677</v>
+        <v>4.87907777</v>
       </c>
       <c r="D197" t="n">
-        <v>48.66</v>
+        <v>49.18</v>
       </c>
       <c r="E197" t="n">
-        <v>49.22</v>
+        <v>50.1</v>
       </c>
       <c r="F197" t="n">
-        <v>48.02</v>
+        <v>48.82</v>
       </c>
       <c r="G197" t="n">
-        <v>48.22</v>
+        <v>49.92</v>
       </c>
       <c r="H197" t="n">
-        <v>-2.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>6.47</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C198" t="n">
-        <v>4.89623377</v>
+        <v>4.88594877</v>
       </c>
       <c r="D198" t="n">
-        <v>48.22</v>
+        <v>50.5</v>
       </c>
       <c r="E198" t="n">
-        <v>48.22</v>
+        <v>50.95</v>
       </c>
       <c r="F198" t="n">
-        <v>47.46</v>
+        <v>49.74</v>
       </c>
       <c r="G198" t="n">
-        <v>47.46</v>
+        <v>50.1</v>
       </c>
       <c r="H198" t="n">
-        <v>-1.58</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>78.34</v>
+        <v>20.01</v>
       </c>
       <c r="C199" t="n">
-        <v>4.90406777</v>
+        <v>4.88794977</v>
       </c>
       <c r="D199" t="n">
-        <v>47.86</v>
+        <v>50</v>
       </c>
       <c r="E199" t="n">
-        <v>48.68</v>
+        <v>50.5</v>
       </c>
       <c r="F199" t="n">
-        <v>47.7</v>
+        <v>49.04</v>
       </c>
       <c r="G199" t="n">
-        <v>48.48</v>
+        <v>49.06</v>
       </c>
       <c r="H199" t="n">
-        <v>2.15</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>12.2</v>
+        <v>-18.77</v>
       </c>
       <c r="C200" t="n">
-        <v>4.90528777</v>
+        <v>4.88607277</v>
       </c>
       <c r="D200" t="n">
-        <v>48.1</v>
+        <v>49.08</v>
       </c>
       <c r="E200" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="F200" t="n">
         <v>48.7</v>
       </c>
-      <c r="F200" t="n">
-        <v>47.38</v>
-      </c>
       <c r="G200" t="n">
-        <v>47.88</v>
+        <v>49.4</v>
       </c>
       <c r="H200" t="n">
-        <v>-1.24</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-50.42</v>
+        <v>95.14</v>
       </c>
       <c r="C201" t="n">
-        <v>4.90024577</v>
+        <v>4.89558677</v>
       </c>
       <c r="D201" t="n">
-        <v>47.34</v>
+        <v>48.66</v>
       </c>
       <c r="E201" t="n">
-        <v>48.28</v>
+        <v>49.22</v>
       </c>
       <c r="F201" t="n">
-        <v>47.06</v>
+        <v>48.02</v>
       </c>
       <c r="G201" t="n">
-        <v>47.9</v>
+        <v>48.22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.04</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7.38</v>
+        <v>6.47</v>
       </c>
       <c r="C202" t="n">
-        <v>4.90098377</v>
+        <v>4.89623377</v>
       </c>
       <c r="D202" t="n">
-        <v>49.98</v>
+        <v>48.22</v>
       </c>
       <c r="E202" t="n">
-        <v>51.2</v>
+        <v>48.22</v>
       </c>
       <c r="F202" t="n">
-        <v>49.76</v>
+        <v>47.46</v>
       </c>
       <c r="G202" t="n">
-        <v>50.55</v>
+        <v>47.46</v>
       </c>
       <c r="H202" t="n">
-        <v>5.53</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.19</v>
+        <v>78.34</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90100277</v>
+        <v>4.90406777</v>
       </c>
       <c r="D203" t="n">
-        <v>50.55</v>
+        <v>47.86</v>
       </c>
       <c r="E203" t="n">
-        <v>51.8</v>
+        <v>48.68</v>
       </c>
       <c r="F203" t="n">
-        <v>50.5</v>
+        <v>47.7</v>
       </c>
       <c r="G203" t="n">
-        <v>51.2</v>
+        <v>48.48</v>
       </c>
       <c r="H203" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-404.07</v>
+        <v>12.2</v>
       </c>
       <c r="C204" t="n">
-        <v>4.86059577</v>
+        <v>4.90528777</v>
       </c>
       <c r="D204" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="E204" t="n">
-        <v>51</v>
+        <v>48.7</v>
       </c>
       <c r="F204" t="n">
-        <v>49.3</v>
+        <v>47.38</v>
       </c>
       <c r="G204" t="n">
-        <v>49.46</v>
+        <v>47.88</v>
       </c>
       <c r="H204" t="n">
-        <v>-3.4</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-104.42</v>
+        <v>-50.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.85015377</v>
+        <v>4.90024577</v>
       </c>
       <c r="D205" t="n">
-        <v>48.86</v>
+        <v>47.34</v>
       </c>
       <c r="E205" t="n">
-        <v>49.74</v>
+        <v>48.28</v>
       </c>
       <c r="F205" t="n">
-        <v>47.6</v>
+        <v>47.06</v>
       </c>
       <c r="G205" t="n">
-        <v>47.68</v>
+        <v>47.9</v>
       </c>
       <c r="H205" t="n">
-        <v>-3.6</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-9.27</v>
+        <v>7.38</v>
       </c>
       <c r="C206" t="n">
-        <v>4.84922677</v>
+        <v>4.90098377</v>
       </c>
       <c r="D206" t="n">
-        <v>47.68</v>
+        <v>49.98</v>
       </c>
       <c r="E206" t="n">
-        <v>48.9</v>
+        <v>51.2</v>
       </c>
       <c r="F206" t="n">
-        <v>47.32</v>
+        <v>49.76</v>
       </c>
       <c r="G206" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="H206" t="n">
-        <v>0.88</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-62.41</v>
+        <v>0.19</v>
       </c>
       <c r="C207" t="n">
-        <v>4.84298577</v>
+        <v>4.90100277</v>
       </c>
       <c r="D207" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="E207" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="F207" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="G207" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="H207" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-4.06</v>
+        <v>-404.07</v>
       </c>
       <c r="C208" t="n">
-        <v>4.84257977</v>
+        <v>4.86059577</v>
       </c>
       <c r="D208" t="n">
-        <v>47.8</v>
+        <v>50.3</v>
       </c>
       <c r="E208" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="F208" t="n">
-        <v>47.16</v>
+        <v>49.3</v>
       </c>
       <c r="G208" t="n">
-        <v>47.98</v>
+        <v>49.46</v>
       </c>
       <c r="H208" t="n">
-        <v>-1.28</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>107.65</v>
+        <v>-104.42</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85334477</v>
+        <v>4.85015377</v>
       </c>
       <c r="D209" t="n">
-        <v>47.86</v>
+        <v>48.86</v>
       </c>
       <c r="E209" t="n">
-        <v>48.44</v>
+        <v>49.74</v>
       </c>
       <c r="F209" t="n">
-        <v>46.5</v>
+        <v>47.6</v>
       </c>
       <c r="G209" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.33</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>137.46</v>
+        <v>-9.27</v>
       </c>
       <c r="C210" t="n">
-        <v>4.86709077</v>
+        <v>4.84922677</v>
       </c>
       <c r="D210" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="E210" t="n">
-        <v>48.22</v>
+        <v>48.9</v>
       </c>
       <c r="F210" t="n">
-        <v>46.6</v>
+        <v>47.32</v>
       </c>
       <c r="G210" t="n">
-        <v>47.06</v>
+        <v>48.1</v>
       </c>
       <c r="H210" t="n">
-        <v>-1.59</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>154.04</v>
+        <v>-62.41</v>
       </c>
       <c r="C211" t="n">
-        <v>4.88249477</v>
+        <v>4.84298577</v>
       </c>
       <c r="D211" t="n">
-        <v>46.68</v>
+        <v>48.1</v>
       </c>
       <c r="E211" t="n">
-        <v>46.76</v>
+        <v>49</v>
       </c>
       <c r="F211" t="n">
-        <v>44.56</v>
+        <v>47.5</v>
       </c>
       <c r="G211" t="n">
-        <v>45.86</v>
+        <v>48.6</v>
       </c>
       <c r="H211" t="n">
-        <v>-2.55</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>78.03</v>
+        <v>-4.06</v>
       </c>
       <c r="C212" t="n">
-        <v>4.89029777</v>
+        <v>4.84257977</v>
       </c>
       <c r="D212" t="n">
-        <v>46.56</v>
+        <v>47.8</v>
       </c>
       <c r="E212" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="F212" t="n">
-        <v>46.2</v>
+        <v>47.16</v>
       </c>
       <c r="G212" t="n">
-        <v>46.38</v>
+        <v>47.98</v>
       </c>
       <c r="H212" t="n">
-        <v>1.13</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>401.67</v>
+        <v>107.65</v>
       </c>
       <c r="C213" t="n">
-        <v>4.93046477</v>
+        <v>4.85334477</v>
       </c>
       <c r="D213" t="n">
-        <v>48.14</v>
+        <v>47.86</v>
       </c>
       <c r="E213" t="n">
-        <v>48.88</v>
+        <v>48.44</v>
       </c>
       <c r="F213" t="n">
-        <v>47.12</v>
+        <v>46.5</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>3.1</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-79.33</v>
+        <v>137.46</v>
       </c>
       <c r="C214" t="n">
-        <v>4.92253177</v>
+        <v>4.86709077</v>
       </c>
       <c r="D214" t="n">
-        <v>48.1</v>
+        <v>47.82</v>
       </c>
       <c r="E214" t="n">
-        <v>50.45</v>
+        <v>48.22</v>
       </c>
       <c r="F214" t="n">
-        <v>48.04</v>
+        <v>46.6</v>
       </c>
       <c r="G214" t="n">
-        <v>50.4</v>
+        <v>47.06</v>
       </c>
       <c r="H214" t="n">
-        <v>5.4</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-415.48</v>
+        <v>154.04</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88098377</v>
+        <v>4.88249477</v>
       </c>
       <c r="D215" t="n">
-        <v>49.44</v>
+        <v>46.68</v>
       </c>
       <c r="E215" t="n">
-        <v>50.15</v>
+        <v>46.76</v>
       </c>
       <c r="F215" t="n">
-        <v>48.88</v>
+        <v>44.56</v>
       </c>
       <c r="G215" t="n">
-        <v>49.32</v>
+        <v>45.86</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.14</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-394.96</v>
+        <v>78.03</v>
       </c>
       <c r="C216" t="n">
-        <v>4.84148777</v>
+        <v>4.89029777</v>
       </c>
       <c r="D216" t="n">
-        <v>49.08</v>
+        <v>46.56</v>
       </c>
       <c r="E216" t="n">
-        <v>49.08</v>
+        <v>48</v>
       </c>
       <c r="F216" t="n">
-        <v>47.2</v>
+        <v>46.2</v>
       </c>
       <c r="G216" t="n">
-        <v>47.62</v>
+        <v>46.38</v>
       </c>
       <c r="H216" t="n">
-        <v>-3.45</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-39.23</v>
+        <v>401.67</v>
       </c>
       <c r="C217" t="n">
-        <v>4.83756477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.2</v>
+        <v>48.14</v>
       </c>
       <c r="E217" t="n">
-        <v>47.2</v>
+        <v>48.88</v>
       </c>
       <c r="F217" t="n">
-        <v>46.42</v>
+        <v>47.12</v>
       </c>
       <c r="G217" t="n">
-        <v>46.48</v>
+        <v>47.82</v>
       </c>
       <c r="H217" t="n">
-        <v>-2.39</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>-79.33</v>
+      </c>
+      <c r="C218" t="n">
+        <v>4.92253177</v>
+      </c>
+      <c r="D218" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="F218" t="n">
+        <v>48.04</v>
+      </c>
+      <c r="G218" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="H218" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>-415.48</v>
+      </c>
+      <c r="C219" t="n">
+        <v>4.88098377</v>
+      </c>
+      <c r="D219" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="E219" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="F219" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="G219" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="H219" t="n">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>-394.96</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.84148777</v>
+      </c>
+      <c r="D220" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="E220" t="n">
+        <v>49.08</v>
+      </c>
+      <c r="F220" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G220" t="n">
+        <v>47.62</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-3.45</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>-39.23</v>
+      </c>
+      <c r="C221" t="n">
+        <v>4.83756477</v>
+      </c>
+      <c r="D221" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="E221" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="F221" t="n">
+        <v>46.42</v>
+      </c>
+      <c r="G221" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="H221" t="n">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="B218" t="n">
+      <c r="B222" t="n">
         <v>219.67</v>
       </c>
-      <c r="C218" t="n">
+      <c r="C222" t="n">
         <v>4.85953177</v>
       </c>
-      <c r="D218" t="n">
+      <c r="D222" t="n">
         <v>45.74</v>
       </c>
-      <c r="E218" t="n">
+      <c r="E222" t="n">
         <v>46.44</v>
       </c>
-      <c r="F218" t="n">
+      <c r="F222" t="n">
         <v>45.38</v>
       </c>
-      <c r="G218" t="n">
+      <c r="G222" t="n">
         <v>46.34</v>
       </c>
-      <c r="H218" t="n">
+      <c r="H222" t="n">
         <v>-0.3</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6656,6 +6656,34 @@
         <v>-0.3</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>111.68</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4.87069977</v>
+      </c>
+      <c r="D223" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="E223" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F223" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="G223" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="H223" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E79" t="n">
-        <v>73.34999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="F79" t="n">
-        <v>71.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>73.34999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="F80" t="n">
-        <v>71.5</v>
+        <v>69.55</v>
       </c>
       <c r="G80" t="n">
-        <v>72.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,3994 +2693,3882 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>72.8</v>
+        <v>70.3</v>
       </c>
       <c r="E81" t="n">
-        <v>73.34999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="F81" t="n">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="G81" t="n">
-        <v>72.3</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>-37.37</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D82" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E82" t="n">
-        <v>72.25</v>
+        <v>73.5</v>
       </c>
       <c r="F82" t="n">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G82" t="n">
-        <v>72.09999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.28</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D83" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E83" t="n">
-        <v>71.75</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>69.55</v>
+        <v>70.5</v>
       </c>
       <c r="G83" t="n">
-        <v>70.09999999999999</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>-2.77</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>39.15</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29754581</v>
+        <v>5.29772381</v>
       </c>
       <c r="D84" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="E84" t="n">
-        <v>73.3</v>
+        <v>71.8</v>
       </c>
       <c r="F84" t="n">
-        <v>70.3</v>
+        <v>68.55</v>
       </c>
       <c r="G84" t="n">
-        <v>72.84999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>3.92</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-37.37</v>
+        <v>-32.03</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29380881</v>
+        <v>5.29452081</v>
       </c>
       <c r="D85" t="n">
-        <v>71.8</v>
+        <v>69.5</v>
       </c>
       <c r="E85" t="n">
-        <v>73.5</v>
+        <v>69.5</v>
       </c>
       <c r="F85" t="n">
-        <v>71.3</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>71.75</v>
+        <v>68.75</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.51</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-245.51</v>
       </c>
       <c r="C86" t="n">
-        <v>5.29380881</v>
+        <v>5.26996981</v>
       </c>
       <c r="D86" t="n">
-        <v>72.8</v>
+        <v>67.75</v>
       </c>
       <c r="E86" t="n">
-        <v>73.15000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>70.5</v>
+        <v>67</v>
       </c>
       <c r="G86" t="n">
-        <v>71.84999999999999</v>
+        <v>68</v>
       </c>
       <c r="H86" t="n">
-        <v>0.14</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39.15</v>
+        <v>24.99</v>
       </c>
       <c r="C87" t="n">
-        <v>5.29772381</v>
+        <v>5.27246881</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
       <c r="F87" t="n">
-        <v>68.55</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>68.65000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="H87" t="n">
-        <v>-4.45</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-32.03</v>
+        <v>-70.5937</v>
       </c>
       <c r="C88" t="n">
-        <v>5.29452081</v>
+        <v>5.26540944</v>
       </c>
       <c r="D88" t="n">
-        <v>69.5</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>69.5</v>
+        <v>66.8</v>
       </c>
       <c r="F88" t="n">
-        <v>68.15000000000001</v>
+        <v>64.45</v>
       </c>
       <c r="G88" t="n">
-        <v>68.75</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-245.51</v>
+        <v>-83.42</v>
       </c>
       <c r="C89" t="n">
-        <v>5.26996981</v>
+        <v>5.25706744</v>
       </c>
       <c r="D89" t="n">
-        <v>67.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>70.15000000000001</v>
+        <v>68</v>
       </c>
       <c r="F89" t="n">
-        <v>67</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>68</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.09</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24.99</v>
+        <v>32.9872</v>
       </c>
       <c r="C90" t="n">
-        <v>5.27246881</v>
+        <v>5.26036616</v>
       </c>
       <c r="D90" t="n">
-        <v>68.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="E90" t="n">
-        <v>69</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>65.65000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>66.55</v>
+        <v>67.45</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.13</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-70.5937</v>
+        <v>-168.98</v>
       </c>
       <c r="C91" t="n">
-        <v>5.26540944</v>
+        <v>5.24346816</v>
       </c>
       <c r="D91" t="n">
-        <v>65.84999999999999</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>66.8</v>
+        <v>69</v>
       </c>
       <c r="F91" t="n">
-        <v>64.45</v>
+        <v>64.7</v>
       </c>
       <c r="G91" t="n">
-        <v>65.84999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-83.42</v>
+        <v>-195.54</v>
       </c>
       <c r="C92" t="n">
-        <v>5.25706744</v>
+        <v>5.22391416</v>
       </c>
       <c r="D92" t="n">
-        <v>66.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>68</v>
+        <v>70.2</v>
       </c>
       <c r="F92" t="n">
-        <v>65.09999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="G92" t="n">
-        <v>65.59999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.38</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>32.9872</v>
+        <v>16.18</v>
       </c>
       <c r="C93" t="n">
-        <v>5.26036616</v>
+        <v>5.22553216</v>
       </c>
       <c r="D93" t="n">
-        <v>65.5</v>
+        <v>69.25</v>
       </c>
       <c r="E93" t="n">
-        <v>67.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.34999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="G93" t="n">
-        <v>67.45</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>2.82</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-168.98</v>
+        <v>13.87</v>
       </c>
       <c r="C94" t="n">
-        <v>5.24346816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D94" t="n">
-        <v>64.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E94" t="n">
-        <v>69</v>
+        <v>71.3</v>
       </c>
       <c r="F94" t="n">
-        <v>64.7</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>68.90000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>2.15</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-195.54</v>
+        <v>-145.08</v>
       </c>
       <c r="C95" t="n">
-        <v>5.22391416</v>
+        <v>5.21241116</v>
       </c>
       <c r="D95" t="n">
-        <v>69.90000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E95" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="F95" t="n">
-        <v>67.95</v>
+        <v>67.3</v>
       </c>
       <c r="G95" t="n">
-        <v>69.05</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.22</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>16.18</v>
+        <v>25.02</v>
       </c>
       <c r="C96" t="n">
-        <v>5.22553216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D96" t="n">
-        <v>69.25</v>
+        <v>67.5</v>
       </c>
       <c r="E96" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>69.05</v>
+        <v>66.3</v>
       </c>
       <c r="G96" t="n">
-        <v>69.84999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>1.16</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.87</v>
+        <v>-6.25</v>
       </c>
       <c r="C97" t="n">
-        <v>5.22691916</v>
+        <v>5.21428816</v>
       </c>
       <c r="D97" t="n">
-        <v>70.95</v>
+        <v>71.25</v>
       </c>
       <c r="E97" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="G97" t="n">
         <v>71.3</v>
       </c>
-      <c r="F97" t="n">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="G97" t="n">
-        <v>70.15000000000001</v>
-      </c>
       <c r="H97" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-145.08</v>
+        <v>-48.58</v>
       </c>
       <c r="C98" t="n">
-        <v>5.21241116</v>
+        <v>5.20943016</v>
       </c>
       <c r="D98" t="n">
-        <v>68.95</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>69</v>
+        <v>71.25</v>
       </c>
       <c r="F98" t="n">
-        <v>67.3</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>67.90000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>-3.21</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25.02</v>
+        <v>-197.18</v>
       </c>
       <c r="C99" t="n">
-        <v>5.21491316</v>
+        <v>5.18971216</v>
       </c>
       <c r="D99" t="n">
-        <v>67.5</v>
+        <v>66.2</v>
       </c>
       <c r="E99" t="n">
-        <v>70.09999999999999</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>66.3</v>
+        <v>65.8</v>
       </c>
       <c r="G99" t="n">
-        <v>69.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="H99" t="n">
-        <v>2.95</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-6.25</v>
+        <v>426.64</v>
       </c>
       <c r="C100" t="n">
-        <v>5.21428816</v>
+        <v>5.23237616</v>
       </c>
       <c r="D100" t="n">
-        <v>71.25</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>73.3</v>
+        <v>68.7</v>
       </c>
       <c r="F100" t="n">
-        <v>70.84999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>71.3</v>
+        <v>66.8</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-48.58</v>
+        <v>41.4993</v>
       </c>
       <c r="C101" t="n">
-        <v>5.20943016</v>
+        <v>5.23652609</v>
       </c>
       <c r="D101" t="n">
-        <v>70.65000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>71.25</v>
+        <v>66.05</v>
       </c>
       <c r="F101" t="n">
-        <v>66.34999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G101" t="n">
-        <v>66.84999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-6.24</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-197.18</v>
+        <v>-220.5688</v>
       </c>
       <c r="C102" t="n">
-        <v>5.18971216</v>
+        <v>5.21446921</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.34999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F102" t="n">
-        <v>65.8</v>
+        <v>63.45</v>
       </c>
       <c r="G102" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>426.64</v>
+        <v>215.27</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23237616</v>
+        <v>5.23599621</v>
       </c>
       <c r="D103" t="n">
-        <v>67</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>68.7</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>66.34999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="G103" t="n">
-        <v>66.8</v>
+        <v>70.45</v>
       </c>
       <c r="H103" t="n">
-        <v>1.21</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>41.4993</v>
+        <v>-160.53</v>
       </c>
       <c r="C104" t="n">
-        <v>5.23652609</v>
+        <v>5.21994321</v>
       </c>
       <c r="D104" t="n">
-        <v>65.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>66.05</v>
+        <v>70.8</v>
       </c>
       <c r="F104" t="n">
-        <v>64.2</v>
+        <v>68.7</v>
       </c>
       <c r="G104" t="n">
-        <v>64.8</v>
+        <v>69</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.99</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-220.5688</v>
+        <v>-304.01</v>
       </c>
       <c r="C105" t="n">
-        <v>5.21446921</v>
+        <v>5.18954221</v>
       </c>
       <c r="D105" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="E105" t="n">
-        <v>67.65000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F105" t="n">
-        <v>63.45</v>
+        <v>68.3</v>
       </c>
       <c r="G105" t="n">
-        <v>67.59999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H105" t="n">
-        <v>4.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>215.27</v>
+        <v>-30.3</v>
       </c>
       <c r="C106" t="n">
-        <v>5.23599621</v>
+        <v>5.18651221</v>
       </c>
       <c r="D106" t="n">
-        <v>69.59999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="E106" t="n">
-        <v>71.34999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>69.45</v>
+        <v>68</v>
       </c>
       <c r="G106" t="n">
-        <v>70.45</v>
+        <v>68.8</v>
       </c>
       <c r="H106" t="n">
-        <v>4.22</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-160.53</v>
+        <v>-92.3</v>
       </c>
       <c r="C107" t="n">
-        <v>5.21994321</v>
+        <v>5.17728221</v>
       </c>
       <c r="D107" t="n">
-        <v>69.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E107" t="n">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
       <c r="G107" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.06</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-304.01</v>
+        <v>25.43</v>
       </c>
       <c r="C108" t="n">
-        <v>5.18954221</v>
+        <v>5.17982521</v>
       </c>
       <c r="D108" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>71.5</v>
+        <v>71.45</v>
       </c>
       <c r="F108" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>70.05</v>
+        <v>71.2</v>
       </c>
       <c r="H108" t="n">
-        <v>1.52</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-30.3</v>
+        <v>136.53</v>
       </c>
       <c r="C109" t="n">
-        <v>5.18651221</v>
+        <v>5.19347821</v>
       </c>
       <c r="D109" t="n">
-        <v>68.05</v>
+        <v>71.2</v>
       </c>
       <c r="E109" t="n">
-        <v>69.34999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G109" t="n">
-        <v>68.8</v>
+        <v>71.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-92.3</v>
+        <v>-224.29</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17728221</v>
+        <v>5.17104921</v>
       </c>
       <c r="D110" t="n">
-        <v>68.8</v>
+        <v>73.45</v>
       </c>
       <c r="E110" t="n">
-        <v>69.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="F110" t="n">
-        <v>67.2</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>67.7</v>
+        <v>73.3</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.6</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>25.43</v>
+        <v>97.7422</v>
       </c>
       <c r="C111" t="n">
-        <v>5.17982521</v>
+        <v>5.18082343</v>
       </c>
       <c r="D111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="E111" t="n">
-        <v>71.45</v>
+        <v>73.5</v>
       </c>
       <c r="F111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G111" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>5.17</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>136.53</v>
+        <v>-116.85</v>
       </c>
       <c r="C112" t="n">
-        <v>5.19347821</v>
+        <v>5.16913843</v>
       </c>
       <c r="D112" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E112" t="n">
-        <v>73.40000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="F112" t="n">
-        <v>70</v>
+        <v>71.55</v>
       </c>
       <c r="G112" t="n">
-        <v>71.8</v>
+        <v>74.2</v>
       </c>
       <c r="H112" t="n">
-        <v>0.84</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-224.29</v>
+        <v>32.76</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17104921</v>
+        <v>5.17241443</v>
       </c>
       <c r="D113" t="n">
-        <v>73.45</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F113" t="n">
-        <v>71.65000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="G113" t="n">
-        <v>73.3</v>
+        <v>73.7</v>
       </c>
       <c r="H113" t="n">
-        <v>2.09</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>97.7422</v>
+        <v>-19.6</v>
       </c>
       <c r="C114" t="n">
-        <v>5.18082343</v>
+        <v>5.17045443</v>
       </c>
       <c r="D114" t="n">
-        <v>71.95</v>
+        <v>73.7</v>
       </c>
       <c r="E114" t="n">
-        <v>73.5</v>
+        <v>73.95</v>
       </c>
       <c r="F114" t="n">
-        <v>71.75</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.91</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-116.85</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>5.16913843</v>
+        <v>5.17787843</v>
       </c>
       <c r="D115" t="n">
-        <v>71.90000000000001</v>
+        <v>73.75</v>
       </c>
       <c r="E115" t="n">
-        <v>76.45</v>
+        <v>73.75</v>
       </c>
       <c r="F115" t="n">
-        <v>71.55</v>
+        <v>70.5</v>
       </c>
       <c r="G115" t="n">
-        <v>74.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>3.2</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>32.76</v>
+        <v>15.04</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17241443</v>
+        <v>5.17938243</v>
       </c>
       <c r="D116" t="n">
-        <v>74.09999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E116" t="n">
-        <v>75</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>73.25</v>
+        <v>70.95</v>
       </c>
       <c r="G116" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.67</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-19.6</v>
+        <v>213.47</v>
       </c>
       <c r="C117" t="n">
-        <v>5.17045443</v>
+        <v>5.20072943</v>
       </c>
       <c r="D117" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>73.95</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>71.65000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>73</v>
+        <v>71.45</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.95</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>74.23999999999999</v>
+        <v>-167.67</v>
       </c>
       <c r="C118" t="n">
-        <v>5.17787843</v>
+        <v>5.18396243</v>
       </c>
       <c r="D118" t="n">
-        <v>73.75</v>
+        <v>72</v>
       </c>
       <c r="E118" t="n">
-        <v>73.75</v>
+        <v>73.45</v>
       </c>
       <c r="F118" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>70.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.88</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15.04</v>
+        <v>-78.5919</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17938243</v>
+        <v>5.17610324</v>
       </c>
       <c r="D119" t="n">
-        <v>70.95</v>
+        <v>73.3</v>
       </c>
       <c r="E119" t="n">
-        <v>72.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F119" t="n">
-        <v>70.95</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H119" t="n">
-        <v>0.99</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>213.47</v>
+        <v>-54.57</v>
       </c>
       <c r="C120" t="n">
-        <v>5.20072943</v>
+        <v>5.17064624</v>
       </c>
       <c r="D120" t="n">
-        <v>71.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E120" t="n">
-        <v>71.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>70.40000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G120" t="n">
-        <v>71.45</v>
+        <v>73.45</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-167.67</v>
+        <v>32.9</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18396243</v>
+        <v>5.17393624</v>
       </c>
       <c r="D121" t="n">
-        <v>72</v>
+        <v>73.45</v>
       </c>
       <c r="E121" t="n">
-        <v>73.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>70.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G121" t="n">
-        <v>73.3</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>2.59</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-78.5919</v>
+        <v>41.93</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17610324</v>
+        <v>5.17812924</v>
       </c>
       <c r="D122" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="E122" t="n">
-        <v>73.3</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>71.84999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G122" t="n">
-        <v>73.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.14</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-54.57</v>
+        <v>52.87</v>
       </c>
       <c r="C123" t="n">
-        <v>5.17064624</v>
+        <v>5.18341624</v>
       </c>
       <c r="D123" t="n">
-        <v>72.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>73.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="F123" t="n">
-        <v>71.95</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>73.45</v>
+        <v>69.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0.34</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>32.9</v>
+        <v>291.58</v>
       </c>
       <c r="C124" t="n">
-        <v>5.17393624</v>
+        <v>5.21257424</v>
       </c>
       <c r="D124" t="n">
-        <v>73.45</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>74.40000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F124" t="n">
-        <v>71.75</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>73.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.41</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>41.93</v>
+        <v>-60.7601</v>
       </c>
       <c r="C125" t="n">
-        <v>5.17812924</v>
+        <v>5.20649823</v>
       </c>
       <c r="D125" t="n">
-        <v>73</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E125" t="n">
-        <v>73.65000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="F125" t="n">
-        <v>68.7</v>
+        <v>68.45</v>
       </c>
       <c r="G125" t="n">
-        <v>69.90000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="H125" t="n">
-        <v>-4.44</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>52.87</v>
+        <v>264.89</v>
       </c>
       <c r="C126" t="n">
-        <v>5.18341624</v>
+        <v>5.23298723</v>
       </c>
       <c r="D126" t="n">
-        <v>70.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>70.5</v>
+        <v>69.75</v>
       </c>
       <c r="F126" t="n">
-        <v>68.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="G126" t="n">
-        <v>69.7</v>
+        <v>67.55</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.29</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>291.58</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>5.21257424</v>
+        <v>5.23298723</v>
       </c>
       <c r="D127" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="E127" t="n">
-        <v>69.45</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>66.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G127" t="n">
-        <v>67</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>-3.87</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-60.7601</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>5.20649823</v>
+        <v>5.23298723</v>
       </c>
       <c r="D128" t="n">
-        <v>69.40000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="E128" t="n">
-        <v>70.25</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>68.45</v>
+        <v>68.2</v>
       </c>
       <c r="G128" t="n">
-        <v>69.25</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>3.36</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>264.89</v>
+        <v>-369.37</v>
       </c>
       <c r="C129" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D129" t="n">
-        <v>68.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E129" t="n">
-        <v>69.75</v>
+        <v>69.5</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.55</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.45</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D130" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="E130" t="n">
-        <v>69.75</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="G130" t="n">
-        <v>67.55</v>
+        <v>69.95</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>68.9663</v>
       </c>
       <c r="C131" t="n">
-        <v>5.23298723</v>
+        <v>5.20294686</v>
       </c>
       <c r="D131" t="n">
-        <v>69</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>71.15000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F131" t="n">
-        <v>68.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>70.15000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="H131" t="n">
-        <v>3.85</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>-247.41</v>
       </c>
       <c r="C132" t="n">
-        <v>5.23298723</v>
+        <v>5.17820586</v>
       </c>
       <c r="D132" t="n">
-        <v>69.25</v>
+        <v>69.5</v>
       </c>
       <c r="E132" t="n">
-        <v>70.09999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>68.2</v>
+        <v>69.45</v>
       </c>
       <c r="G132" t="n">
-        <v>69.65000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.71</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-369.37</v>
+        <v>27.55</v>
       </c>
       <c r="C133" t="n">
-        <v>5.19605023</v>
+        <v>5.18096086</v>
       </c>
       <c r="D133" t="n">
-        <v>69.5</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E133" t="n">
-        <v>69.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>67.3</v>
+        <v>73.05</v>
       </c>
       <c r="G133" t="n">
-        <v>67.84999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>-2.58</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>-286.2</v>
       </c>
       <c r="C134" t="n">
-        <v>5.19605023</v>
+        <v>5.15234086</v>
       </c>
       <c r="D134" t="n">
-        <v>68.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>70.34999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>68.5</v>
+        <v>73.05</v>
       </c>
       <c r="G134" t="n">
-        <v>69.95</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>3.1</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>68.9663</v>
+        <v>48.88</v>
       </c>
       <c r="C135" t="n">
-        <v>5.20294686</v>
+        <v>5.15722886</v>
       </c>
       <c r="D135" t="n">
-        <v>68.34999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="E135" t="n">
-        <v>70.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>68.34999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>70.05</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H135" t="n">
-        <v>0.14</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-247.41</v>
+        <v>-55.96</v>
       </c>
       <c r="C136" t="n">
-        <v>5.17820586</v>
+        <v>5.15163286</v>
       </c>
       <c r="D136" t="n">
-        <v>69.5</v>
+        <v>75.05</v>
       </c>
       <c r="E136" t="n">
-        <v>74.15000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>69.45</v>
+        <v>74.25</v>
       </c>
       <c r="G136" t="n">
-        <v>73.84999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>5.42</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>27.55</v>
+        <v>-385.85</v>
       </c>
       <c r="C137" t="n">
-        <v>5.18096086</v>
+        <v>5.11304786</v>
       </c>
       <c r="D137" t="n">
-        <v>73.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>75.15000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>73.05</v>
+        <v>64.5</v>
       </c>
       <c r="G137" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.61</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-286.2</v>
+        <v>139.59</v>
       </c>
       <c r="C138" t="n">
-        <v>5.15234086</v>
+        <v>5.12700686</v>
       </c>
       <c r="D138" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>74.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>73.05</v>
+        <v>61.75</v>
       </c>
       <c r="G138" t="n">
-        <v>73.65000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.34</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>48.88</v>
+        <v>1468.42</v>
       </c>
       <c r="C139" t="n">
-        <v>5.15722886</v>
+        <v>5.27384886</v>
       </c>
       <c r="D139" t="n">
-        <v>76.8</v>
+        <v>62.6</v>
       </c>
       <c r="E139" t="n">
-        <v>78.90000000000001</v>
+        <v>63.35</v>
       </c>
       <c r="F139" t="n">
-        <v>75.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="G139" t="n">
-        <v>76.84999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="H139" t="n">
-        <v>4.34</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-55.96</v>
+        <v>292.93</v>
       </c>
       <c r="C140" t="n">
-        <v>5.15163286</v>
+        <v>5.30314186</v>
       </c>
       <c r="D140" t="n">
-        <v>75.05</v>
+        <v>62.5</v>
       </c>
       <c r="E140" t="n">
-        <v>75.90000000000001</v>
+        <v>63.85</v>
       </c>
       <c r="F140" t="n">
-        <v>74.25</v>
+        <v>61.55</v>
       </c>
       <c r="G140" t="n">
-        <v>75.59999999999999</v>
+        <v>62.25</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.63</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-385.85</v>
+        <v>17.9</v>
       </c>
       <c r="C141" t="n">
-        <v>5.11304786</v>
+        <v>5.30493186</v>
       </c>
       <c r="D141" t="n">
-        <v>72.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="E141" t="n">
-        <v>72.40000000000001</v>
+        <v>64.95</v>
       </c>
       <c r="F141" t="n">
-        <v>64.5</v>
+        <v>61.35</v>
       </c>
       <c r="G141" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-14.15</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>139.59</v>
+        <v>-224.88</v>
       </c>
       <c r="C142" t="n">
-        <v>5.12700686</v>
+        <v>5.28244386</v>
       </c>
       <c r="D142" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="E142" t="n">
-        <v>64.90000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="F142" t="n">
-        <v>61.75</v>
+        <v>60.4</v>
       </c>
       <c r="G142" t="n">
-        <v>62.1</v>
+        <v>62.15</v>
       </c>
       <c r="H142" t="n">
-        <v>-4.31</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1468.42</v>
+        <v>-244.5</v>
       </c>
       <c r="C143" t="n">
-        <v>5.27384886</v>
+        <v>5.25799386</v>
       </c>
       <c r="D143" t="n">
-        <v>62.6</v>
+        <v>61.9</v>
       </c>
       <c r="E143" t="n">
-        <v>63.35</v>
+        <v>62.35</v>
       </c>
       <c r="F143" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="G143" t="n">
-        <v>61.6</v>
+        <v>60.2</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>292.93</v>
+        <v>-302.48</v>
       </c>
       <c r="C144" t="n">
-        <v>5.30314186</v>
+        <v>5.22774586</v>
       </c>
       <c r="D144" t="n">
-        <v>62.5</v>
+        <v>60.1</v>
       </c>
       <c r="E144" t="n">
-        <v>63.85</v>
+        <v>61</v>
       </c>
       <c r="F144" t="n">
-        <v>61.55</v>
+        <v>58.6</v>
       </c>
       <c r="G144" t="n">
-        <v>62.25</v>
+        <v>60.45</v>
       </c>
       <c r="H144" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>17.9</v>
+        <v>-177.8636</v>
       </c>
       <c r="C145" t="n">
-        <v>5.30493186</v>
+        <v>5.2099595</v>
       </c>
       <c r="D145" t="n">
-        <v>63.2</v>
+        <v>60</v>
       </c>
       <c r="E145" t="n">
-        <v>64.95</v>
+        <v>60.05</v>
       </c>
       <c r="F145" t="n">
-        <v>61.35</v>
+        <v>55.7</v>
       </c>
       <c r="G145" t="n">
-        <v>61.8</v>
+        <v>57.85</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.72</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-224.88</v>
+        <v>-228.55</v>
       </c>
       <c r="C146" t="n">
-        <v>5.28244386</v>
+        <v>5.1871045</v>
       </c>
       <c r="D146" t="n">
-        <v>61.8</v>
+        <v>56.95</v>
       </c>
       <c r="E146" t="n">
-        <v>62.25</v>
+        <v>59.1</v>
       </c>
       <c r="F146" t="n">
-        <v>60.4</v>
+        <v>56</v>
       </c>
       <c r="G146" t="n">
-        <v>62.15</v>
+        <v>58.55</v>
       </c>
       <c r="H146" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-244.5</v>
+        <v>423.9973</v>
       </c>
       <c r="C147" t="n">
-        <v>5.25799386</v>
+        <v>5.22950423</v>
       </c>
       <c r="D147" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="E147" t="n">
+        <v>62</v>
+      </c>
+      <c r="F147" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G147" t="n">
         <v>61.9</v>
       </c>
-      <c r="E147" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="F147" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G147" t="n">
-        <v>60.2</v>
-      </c>
       <c r="H147" t="n">
-        <v>-3.14</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-302.48</v>
+        <v>-119.16</v>
       </c>
       <c r="C148" t="n">
-        <v>5.22774586</v>
+        <v>5.21758823</v>
       </c>
       <c r="D148" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="E148" t="n">
-        <v>61</v>
+        <v>60.75</v>
       </c>
       <c r="F148" t="n">
-        <v>58.6</v>
+        <v>58.75</v>
       </c>
       <c r="G148" t="n">
-        <v>60.45</v>
+        <v>59.1</v>
       </c>
       <c r="H148" t="n">
-        <v>0.42</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-177.8636</v>
+        <v>-301.92</v>
       </c>
       <c r="C149" t="n">
-        <v>5.2099595</v>
+        <v>5.18739623</v>
       </c>
       <c r="D149" t="n">
-        <v>60</v>
+        <v>58.95</v>
       </c>
       <c r="E149" t="n">
-        <v>60.05</v>
+        <v>58.95</v>
       </c>
       <c r="F149" t="n">
-        <v>55.7</v>
+        <v>56.85</v>
       </c>
       <c r="G149" t="n">
-        <v>57.85</v>
+        <v>57.25</v>
       </c>
       <c r="H149" t="n">
-        <v>-4.3</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-228.55</v>
+        <v>112.29</v>
       </c>
       <c r="C150" t="n">
-        <v>5.1871045</v>
+        <v>5.19862523</v>
       </c>
       <c r="D150" t="n">
-        <v>56.95</v>
+        <v>57.1</v>
       </c>
       <c r="E150" t="n">
-        <v>59.1</v>
+        <v>57.6</v>
       </c>
       <c r="F150" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G150" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="H150" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>423.9973</v>
+        <v>-62.4836</v>
       </c>
       <c r="C151" t="n">
-        <v>5.22950423</v>
+        <v>5.19237687</v>
       </c>
       <c r="D151" t="n">
-        <v>57.05</v>
+        <v>55.3</v>
       </c>
       <c r="E151" t="n">
-        <v>62</v>
+        <v>57.9</v>
       </c>
       <c r="F151" t="n">
-        <v>56.55</v>
+        <v>54.95</v>
       </c>
       <c r="G151" t="n">
-        <v>61.9</v>
+        <v>57.35</v>
       </c>
       <c r="H151" t="n">
-        <v>5.72</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-119.16</v>
+        <v>-29.35</v>
       </c>
       <c r="C152" t="n">
-        <v>5.21758823</v>
+        <v>5.18944187</v>
       </c>
       <c r="D152" t="n">
-        <v>60.5</v>
+        <v>56.2</v>
       </c>
       <c r="E152" t="n">
-        <v>60.75</v>
+        <v>57.1</v>
       </c>
       <c r="F152" t="n">
-        <v>58.75</v>
+        <v>55.8</v>
       </c>
       <c r="G152" t="n">
-        <v>59.1</v>
+        <v>55.85</v>
       </c>
       <c r="H152" t="n">
-        <v>-4.52</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-301.92</v>
+        <v>54.46</v>
       </c>
       <c r="C153" t="n">
-        <v>5.18739623</v>
+        <v>5.19488787</v>
       </c>
       <c r="D153" t="n">
-        <v>58.95</v>
+        <v>55.3</v>
       </c>
       <c r="E153" t="n">
-        <v>58.95</v>
+        <v>55.55</v>
       </c>
       <c r="F153" t="n">
-        <v>56.85</v>
+        <v>53.25</v>
       </c>
       <c r="G153" t="n">
-        <v>57.25</v>
+        <v>54.7</v>
       </c>
       <c r="H153" t="n">
-        <v>-3.13</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>112.29</v>
+        <v>17.32</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19862523</v>
+        <v>5.19661987</v>
       </c>
       <c r="D154" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E154" t="n">
-        <v>57.6</v>
+        <v>54.1</v>
       </c>
       <c r="F154" t="n">
-        <v>56.5</v>
+        <v>52.25</v>
       </c>
       <c r="G154" t="n">
-        <v>56.65</v>
+        <v>53.15</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.05</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-62.4836</v>
+        <v>93.42</v>
       </c>
       <c r="C155" t="n">
-        <v>5.19237687</v>
+        <v>5.20596187</v>
       </c>
       <c r="D155" t="n">
-        <v>55.3</v>
+        <v>53.7</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>54.95</v>
+        <v>53.25</v>
       </c>
       <c r="G155" t="n">
-        <v>57.35</v>
+        <v>57</v>
       </c>
       <c r="H155" t="n">
-        <v>1.24</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-29.35</v>
+        <v>64.81</v>
       </c>
       <c r="C156" t="n">
-        <v>5.18944187</v>
+        <v>5.21244287</v>
       </c>
       <c r="D156" t="n">
-        <v>56.2</v>
+        <v>56.6</v>
       </c>
       <c r="E156" t="n">
-        <v>57.1</v>
+        <v>58.05</v>
       </c>
       <c r="F156" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="G156" t="n">
-        <v>55.85</v>
+        <v>56.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.62</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>54.46</v>
+        <v>-172.75</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19488787</v>
+        <v>5.19516787</v>
       </c>
       <c r="D157" t="n">
-        <v>55.3</v>
+        <v>56.85</v>
       </c>
       <c r="E157" t="n">
-        <v>55.55</v>
+        <v>57.2</v>
       </c>
       <c r="F157" t="n">
-        <v>53.25</v>
+        <v>55</v>
       </c>
       <c r="G157" t="n">
-        <v>54.7</v>
+        <v>56</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.06</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>17.32</v>
+        <v>-24.86</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19661987</v>
+        <v>5.19268187</v>
       </c>
       <c r="D158" t="n">
-        <v>54</v>
+        <v>55.75</v>
       </c>
       <c r="E158" t="n">
-        <v>54.1</v>
+        <v>55.8</v>
       </c>
       <c r="F158" t="n">
-        <v>52.25</v>
+        <v>53.7</v>
       </c>
       <c r="G158" t="n">
-        <v>53.15</v>
+        <v>53.9</v>
       </c>
       <c r="H158" t="n">
-        <v>-2.83</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>93.42</v>
+        <v>17.38</v>
       </c>
       <c r="C159" t="n">
-        <v>5.20596187</v>
+        <v>5.19441987</v>
       </c>
       <c r="D159" t="n">
-        <v>53.7</v>
+        <v>53.25</v>
       </c>
       <c r="E159" t="n">
-        <v>57.9</v>
+        <v>53.9</v>
       </c>
       <c r="F159" t="n">
-        <v>53.25</v>
+        <v>51.75</v>
       </c>
       <c r="G159" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H159" t="n">
-        <v>7.24</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>64.81</v>
+        <v>14.06</v>
       </c>
       <c r="C160" t="n">
-        <v>5.21244287</v>
+        <v>5.19582587</v>
       </c>
       <c r="D160" t="n">
-        <v>56.6</v>
+        <v>50.15</v>
       </c>
       <c r="E160" t="n">
-        <v>58.05</v>
+        <v>51.55</v>
       </c>
       <c r="F160" t="n">
-        <v>56.5</v>
+        <v>49.64</v>
       </c>
       <c r="G160" t="n">
-        <v>56.85</v>
+        <v>50.5</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.26</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-172.75</v>
+        <v>-21.2345</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19516787</v>
+        <v>5.19370242</v>
       </c>
       <c r="D161" t="n">
-        <v>56.85</v>
+        <v>50</v>
       </c>
       <c r="E161" t="n">
-        <v>57.2</v>
+        <v>50.8</v>
       </c>
       <c r="F161" t="n">
-        <v>55</v>
+        <v>47.9</v>
       </c>
       <c r="G161" t="n">
-        <v>56</v>
+        <v>48.32</v>
       </c>
       <c r="H161" t="n">
-        <v>-1.5</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-24.86</v>
+        <v>47.7</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19268187</v>
+        <v>5.19847242</v>
       </c>
       <c r="D162" t="n">
-        <v>55.75</v>
+        <v>48.98</v>
       </c>
       <c r="E162" t="n">
-        <v>55.8</v>
+        <v>49.94</v>
       </c>
       <c r="F162" t="n">
-        <v>53.7</v>
+        <v>48.18</v>
       </c>
       <c r="G162" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="H162" t="n">
-        <v>-3.75</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>17.38</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C163" t="n">
-        <v>5.19441987</v>
+        <v>5.20773242</v>
       </c>
       <c r="D163" t="n">
-        <v>53.25</v>
+        <v>49.44</v>
       </c>
       <c r="E163" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="F163" t="n">
-        <v>51.75</v>
+        <v>46.74</v>
       </c>
       <c r="G163" t="n">
-        <v>52</v>
+        <v>47.4</v>
       </c>
       <c r="H163" t="n">
-        <v>-3.53</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>14.06</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19582587</v>
+        <v>5.19818142</v>
       </c>
       <c r="D164" t="n">
-        <v>50.15</v>
+        <v>47</v>
       </c>
       <c r="E164" t="n">
-        <v>51.55</v>
+        <v>47</v>
       </c>
       <c r="F164" t="n">
-        <v>49.64</v>
+        <v>45.86</v>
       </c>
       <c r="G164" t="n">
-        <v>50.5</v>
+        <v>46.28</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.88</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-21.2345</v>
+        <v>-254.06</v>
       </c>
       <c r="C165" t="n">
-        <v>5.19370242</v>
+        <v>5.17277542</v>
       </c>
       <c r="D165" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="E165" t="n">
-        <v>50.8</v>
+        <v>47.18</v>
       </c>
       <c r="F165" t="n">
-        <v>47.9</v>
+        <v>45.76</v>
       </c>
       <c r="G165" t="n">
-        <v>48.32</v>
+        <v>45.9</v>
       </c>
       <c r="H165" t="n">
-        <v>-4.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>47.7</v>
+        <v>-316.19</v>
       </c>
       <c r="C166" t="n">
-        <v>5.19847242</v>
+        <v>5.14115642</v>
       </c>
       <c r="D166" t="n">
-        <v>48.98</v>
+        <v>45.9</v>
       </c>
       <c r="E166" t="n">
-        <v>49.94</v>
+        <v>46.78</v>
       </c>
       <c r="F166" t="n">
-        <v>48.18</v>
+        <v>45.26</v>
       </c>
       <c r="G166" t="n">
-        <v>49.44</v>
+        <v>46.08</v>
       </c>
       <c r="H166" t="n">
-        <v>2.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>92.59999999999999</v>
+        <v>-150.87</v>
       </c>
       <c r="C167" t="n">
-        <v>5.20773242</v>
+        <v>5.12606942</v>
       </c>
       <c r="D167" t="n">
-        <v>49.44</v>
+        <v>47.7</v>
       </c>
       <c r="E167" t="n">
-        <v>49.44</v>
+        <v>48.9</v>
       </c>
       <c r="F167" t="n">
-        <v>46.74</v>
+        <v>46.64</v>
       </c>
       <c r="G167" t="n">
-        <v>47.4</v>
+        <v>46.84</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.13</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-95.51000000000001</v>
+        <v>-236.76</v>
       </c>
       <c r="C168" t="n">
-        <v>5.19818142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D168" t="n">
-        <v>47</v>
+        <v>46.92</v>
       </c>
       <c r="E168" t="n">
-        <v>47</v>
+        <v>48.28</v>
       </c>
       <c r="F168" t="n">
-        <v>45.86</v>
+        <v>46.84</v>
       </c>
       <c r="G168" t="n">
-        <v>46.28</v>
+        <v>47.36</v>
       </c>
       <c r="H168" t="n">
-        <v>-2.36</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-254.06</v>
+        <v>-36.92</v>
       </c>
       <c r="C169" t="n">
-        <v>5.17277542</v>
+        <v>5.09870142</v>
       </c>
       <c r="D169" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E169" t="n">
-        <v>47.18</v>
+        <v>47.56</v>
       </c>
       <c r="F169" t="n">
-        <v>45.76</v>
+        <v>45.72</v>
       </c>
       <c r="G169" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.82</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-316.19</v>
+        <v>64.78</v>
       </c>
       <c r="C170" t="n">
-        <v>5.14115642</v>
+        <v>5.10517942</v>
       </c>
       <c r="D170" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="E170" t="n">
-        <v>46.78</v>
+        <v>48.42</v>
       </c>
       <c r="F170" t="n">
-        <v>45.26</v>
+        <v>46.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.08</v>
+        <v>46.6</v>
       </c>
       <c r="H170" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-150.87</v>
+        <v>-44.41</v>
       </c>
       <c r="C171" t="n">
-        <v>5.12606942</v>
+        <v>5.10073842</v>
       </c>
       <c r="D171" t="n">
-        <v>47.7</v>
+        <v>47.06</v>
       </c>
       <c r="E171" t="n">
-        <v>48.9</v>
+        <v>48.98</v>
       </c>
       <c r="F171" t="n">
-        <v>46.64</v>
+        <v>46.7</v>
       </c>
       <c r="G171" t="n">
-        <v>46.84</v>
+        <v>48.52</v>
       </c>
       <c r="H171" t="n">
-        <v>1.65</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-236.76</v>
+        <v>-124.97</v>
       </c>
       <c r="C172" t="n">
-        <v>5.10239342</v>
+        <v>5.08824142</v>
       </c>
       <c r="D172" t="n">
-        <v>46.92</v>
+        <v>47.6</v>
       </c>
       <c r="E172" t="n">
-        <v>48.28</v>
+        <v>48.08</v>
       </c>
       <c r="F172" t="n">
-        <v>46.84</v>
+        <v>46.72</v>
       </c>
       <c r="G172" t="n">
-        <v>47.36</v>
+        <v>46.76</v>
       </c>
       <c r="H172" t="n">
-        <v>1.11</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-36.92</v>
+        <v>-272.6</v>
       </c>
       <c r="C173" t="n">
-        <v>5.09870142</v>
+        <v>5.06098142</v>
       </c>
       <c r="D173" t="n">
-        <v>47</v>
+        <v>46.76</v>
       </c>
       <c r="E173" t="n">
-        <v>47.56</v>
+        <v>48.3</v>
       </c>
       <c r="F173" t="n">
-        <v>45.72</v>
+        <v>46.02</v>
       </c>
       <c r="G173" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="H173" t="n">
-        <v>-2.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>64.78</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C174" t="n">
-        <v>5.10517942</v>
+        <v>5.06933542</v>
       </c>
       <c r="D174" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="E174" t="n">
-        <v>48.42</v>
+        <v>47.92</v>
       </c>
       <c r="F174" t="n">
-        <v>46.26</v>
+        <v>46.46</v>
       </c>
       <c r="G174" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="H174" t="n">
-        <v>0.73</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-44.41</v>
+        <v>-232.94</v>
       </c>
       <c r="C175" t="n">
-        <v>5.10073842</v>
+        <v>5.04604142</v>
       </c>
       <c r="D175" t="n">
-        <v>47.06</v>
+        <v>47.2</v>
       </c>
       <c r="E175" t="n">
-        <v>48.98</v>
+        <v>48.84</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.52</v>
+        <v>48.56</v>
       </c>
       <c r="H175" t="n">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-124.97</v>
+        <v>-101.2265</v>
       </c>
       <c r="C176" t="n">
-        <v>5.08824142</v>
+        <v>5.03591877</v>
       </c>
       <c r="D176" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="E176" t="n">
-        <v>48.08</v>
+        <v>49.46</v>
       </c>
       <c r="F176" t="n">
-        <v>46.72</v>
+        <v>48.24</v>
       </c>
       <c r="G176" t="n">
-        <v>46.76</v>
+        <v>48.78</v>
       </c>
       <c r="H176" t="n">
-        <v>-3.63</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-272.6</v>
+        <v>-146.01</v>
       </c>
       <c r="C177" t="n">
-        <v>5.06098142</v>
+        <v>5.02131777</v>
       </c>
       <c r="D177" t="n">
-        <v>46.76</v>
+        <v>49.22</v>
       </c>
       <c r="E177" t="n">
-        <v>48.3</v>
+        <v>51</v>
       </c>
       <c r="F177" t="n">
-        <v>46.02</v>
+        <v>49.22</v>
       </c>
       <c r="G177" t="n">
-        <v>47.42</v>
+        <v>50.4</v>
       </c>
       <c r="H177" t="n">
-        <v>1.41</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>83.54000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C178" t="n">
-        <v>5.06933542</v>
+        <v>5.02274277</v>
       </c>
       <c r="D178" t="n">
-        <v>47.42</v>
+        <v>50.55</v>
       </c>
       <c r="E178" t="n">
-        <v>47.92</v>
+        <v>51</v>
       </c>
       <c r="F178" t="n">
-        <v>46.46</v>
+        <v>48.2</v>
       </c>
       <c r="G178" t="n">
-        <v>47.2</v>
+        <v>48.94</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.46</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-232.94</v>
+        <v>7.54</v>
       </c>
       <c r="C179" t="n">
-        <v>5.04604142</v>
+        <v>5.02349677</v>
       </c>
       <c r="D179" t="n">
-        <v>47.2</v>
+        <v>49.96</v>
       </c>
       <c r="E179" t="n">
-        <v>48.84</v>
+        <v>49.98</v>
       </c>
       <c r="F179" t="n">
-        <v>46.7</v>
+        <v>48.72</v>
       </c>
       <c r="G179" t="n">
-        <v>48.56</v>
+        <v>49.12</v>
       </c>
       <c r="H179" t="n">
-        <v>2.88</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-101.2265</v>
+        <v>29.93</v>
       </c>
       <c r="C180" t="n">
-        <v>5.03591877</v>
+        <v>5.02648977</v>
       </c>
       <c r="D180" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="E180" t="n">
-        <v>49.46</v>
+        <v>49.36</v>
       </c>
       <c r="F180" t="n">
-        <v>48.24</v>
+        <v>48.18</v>
       </c>
       <c r="G180" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="H180" t="n">
-        <v>0.45</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-146.01</v>
+        <v>-93.37</v>
       </c>
       <c r="C181" t="n">
-        <v>5.02131777</v>
+        <v>5.01715277</v>
       </c>
       <c r="D181" t="n">
-        <v>49.22</v>
+        <v>48.4</v>
       </c>
       <c r="E181" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
       <c r="F181" t="n">
-        <v>49.22</v>
+        <v>47.2</v>
       </c>
       <c r="G181" t="n">
-        <v>50.4</v>
+        <v>47.64</v>
       </c>
       <c r="H181" t="n">
-        <v>3.32</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>14.25</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C182" t="n">
-        <v>5.02274277</v>
+        <v>5.00778777</v>
       </c>
       <c r="D182" t="n">
-        <v>50.55</v>
+        <v>47.64</v>
       </c>
       <c r="E182" t="n">
-        <v>51</v>
+        <v>49.3</v>
       </c>
       <c r="F182" t="n">
-        <v>48.2</v>
+        <v>47.22</v>
       </c>
       <c r="G182" t="n">
-        <v>48.94</v>
+        <v>48.96</v>
       </c>
       <c r="H182" t="n">
-        <v>-2.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7.54</v>
+        <v>28.06</v>
       </c>
       <c r="C183" t="n">
-        <v>5.02349677</v>
+        <v>5.01059377</v>
       </c>
       <c r="D183" t="n">
-        <v>49.96</v>
+        <v>48.36</v>
       </c>
       <c r="E183" t="n">
-        <v>49.98</v>
+        <v>48.76</v>
       </c>
       <c r="F183" t="n">
-        <v>48.72</v>
+        <v>47.52</v>
       </c>
       <c r="G183" t="n">
-        <v>49.12</v>
+        <v>47.98</v>
       </c>
       <c r="H183" t="n">
-        <v>0.37</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>29.93</v>
+        <v>-160.94</v>
       </c>
       <c r="C184" t="n">
-        <v>5.02648977</v>
+        <v>4.99449977</v>
       </c>
       <c r="D184" t="n">
-        <v>49.1</v>
+        <v>47.98</v>
       </c>
       <c r="E184" t="n">
-        <v>49.36</v>
+        <v>48.46</v>
       </c>
       <c r="F184" t="n">
-        <v>48.18</v>
+        <v>47.32</v>
       </c>
       <c r="G184" t="n">
-        <v>48.64</v>
+        <v>48.08</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.98</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-93.37</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C185" t="n">
-        <v>5.01715277</v>
+        <v>5.00218477</v>
       </c>
       <c r="D185" t="n">
-        <v>48.4</v>
+        <v>49.54</v>
       </c>
       <c r="E185" t="n">
-        <v>48.4</v>
+        <v>50.5</v>
       </c>
       <c r="F185" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="G185" t="n">
-        <v>47.64</v>
+        <v>49.68</v>
       </c>
       <c r="H185" t="n">
-        <v>-2.06</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-93.65000000000001</v>
+        <v>-70.88</v>
       </c>
       <c r="C186" t="n">
-        <v>5.00778777</v>
+        <v>4.99509677</v>
       </c>
       <c r="D186" t="n">
-        <v>47.64</v>
+        <v>51.9</v>
       </c>
       <c r="E186" t="n">
-        <v>49.3</v>
+        <v>55.6</v>
       </c>
       <c r="F186" t="n">
-        <v>47.22</v>
+        <v>51.9</v>
       </c>
       <c r="G186" t="n">
-        <v>48.96</v>
+        <v>54.6</v>
       </c>
       <c r="H186" t="n">
-        <v>2.77</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>28.06</v>
+        <v>-223.97</v>
       </c>
       <c r="C187" t="n">
-        <v>5.01059377</v>
+        <v>4.97269977</v>
       </c>
       <c r="D187" t="n">
-        <v>48.36</v>
+        <v>54.7</v>
       </c>
       <c r="E187" t="n">
-        <v>48.76</v>
+        <v>56.1</v>
       </c>
       <c r="F187" t="n">
-        <v>47.52</v>
+        <v>53.7</v>
       </c>
       <c r="G187" t="n">
-        <v>47.98</v>
+        <v>54.25</v>
       </c>
       <c r="H187" t="n">
-        <v>-2</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-160.94</v>
+        <v>-908.88</v>
       </c>
       <c r="C188" t="n">
-        <v>4.99449977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D188" t="n">
-        <v>47.98</v>
+        <v>52.85</v>
       </c>
       <c r="E188" t="n">
-        <v>48.46</v>
+        <v>53.8</v>
       </c>
       <c r="F188" t="n">
-        <v>47.32</v>
+        <v>51.3</v>
       </c>
       <c r="G188" t="n">
-        <v>48.08</v>
+        <v>53.4</v>
       </c>
       <c r="H188" t="n">
-        <v>0.21</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>76.84999999999999</v>
+        <v>-219</v>
       </c>
       <c r="C189" t="n">
-        <v>5.00218477</v>
+        <v>4.85991177</v>
       </c>
       <c r="D189" t="n">
-        <v>49.54</v>
+        <v>52.75</v>
       </c>
       <c r="E189" t="n">
-        <v>50.5</v>
+        <v>54.45</v>
       </c>
       <c r="F189" t="n">
-        <v>48.9</v>
+        <v>51.45</v>
       </c>
       <c r="G189" t="n">
-        <v>49.68</v>
+        <v>51.85</v>
       </c>
       <c r="H189" t="n">
-        <v>3.33</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>-70.88</v>
+        <v>81.19</v>
       </c>
       <c r="C190" t="n">
-        <v>4.99509677</v>
+        <v>4.86803077</v>
       </c>
       <c r="D190" t="n">
-        <v>51.9</v>
+        <v>51.85</v>
       </c>
       <c r="E190" t="n">
-        <v>55.6</v>
+        <v>51.85</v>
       </c>
       <c r="F190" t="n">
-        <v>51.9</v>
+        <v>49.6</v>
       </c>
       <c r="G190" t="n">
-        <v>54.6</v>
+        <v>50.45</v>
       </c>
       <c r="H190" t="n">
-        <v>9.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-223.97</v>
+        <v>7.21</v>
       </c>
       <c r="C191" t="n">
-        <v>4.97269977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D191" t="n">
-        <v>54.7</v>
+        <v>50.05</v>
       </c>
       <c r="E191" t="n">
-        <v>56.1</v>
+        <v>50.8</v>
       </c>
       <c r="F191" t="n">
-        <v>53.7</v>
+        <v>49.52</v>
       </c>
       <c r="G191" t="n">
-        <v>54.25</v>
+        <v>50.65</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.64</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-908.88</v>
+        <v>144.28</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88181177</v>
+        <v>4.88317977</v>
       </c>
       <c r="D192" t="n">
-        <v>52.85</v>
+        <v>50</v>
       </c>
       <c r="E192" t="n">
-        <v>53.8</v>
+        <v>50.6</v>
       </c>
       <c r="F192" t="n">
-        <v>51.3</v>
+        <v>49.08</v>
       </c>
       <c r="G192" t="n">
-        <v>53.4</v>
+        <v>49.12</v>
       </c>
       <c r="H192" t="n">
-        <v>-1.57</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-219</v>
+        <v>-41.02</v>
       </c>
       <c r="C193" t="n">
-        <v>4.85991177</v>
+        <v>4.87907777</v>
       </c>
       <c r="D193" t="n">
-        <v>52.75</v>
+        <v>49.18</v>
       </c>
       <c r="E193" t="n">
-        <v>54.45</v>
+        <v>50.1</v>
       </c>
       <c r="F193" t="n">
-        <v>51.45</v>
+        <v>48.82</v>
       </c>
       <c r="G193" t="n">
-        <v>51.85</v>
+        <v>49.92</v>
       </c>
       <c r="H193" t="n">
-        <v>-2.9</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>81.19</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C194" t="n">
-        <v>4.86803077</v>
+        <v>4.88594877</v>
       </c>
       <c r="D194" t="n">
-        <v>51.85</v>
+        <v>50.5</v>
       </c>
       <c r="E194" t="n">
-        <v>51.85</v>
+        <v>50.95</v>
       </c>
       <c r="F194" t="n">
-        <v>49.6</v>
+        <v>49.74</v>
       </c>
       <c r="G194" t="n">
-        <v>50.45</v>
+        <v>50.1</v>
       </c>
       <c r="H194" t="n">
-        <v>-2.7</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.21</v>
+        <v>20.01</v>
       </c>
       <c r="C195" t="n">
-        <v>4.86875177</v>
+        <v>4.88794977</v>
       </c>
       <c r="D195" t="n">
-        <v>50.05</v>
+        <v>50</v>
       </c>
       <c r="E195" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="F195" t="n">
-        <v>49.52</v>
+        <v>49.04</v>
       </c>
       <c r="G195" t="n">
-        <v>50.65</v>
+        <v>49.06</v>
       </c>
       <c r="H195" t="n">
-        <v>0.4</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>144.28</v>
+        <v>-18.77</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88317977</v>
+        <v>4.88607277</v>
       </c>
       <c r="D196" t="n">
-        <v>50</v>
+        <v>49.08</v>
       </c>
       <c r="E196" t="n">
-        <v>50.6</v>
+        <v>49.78</v>
       </c>
       <c r="F196" t="n">
-        <v>49.08</v>
+        <v>48.7</v>
       </c>
       <c r="G196" t="n">
-        <v>49.12</v>
+        <v>49.4</v>
       </c>
       <c r="H196" t="n">
-        <v>-3.02</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-41.02</v>
+        <v>95.14</v>
       </c>
       <c r="C197" t="n">
-        <v>4.87907777</v>
+        <v>4.89558677</v>
       </c>
       <c r="D197" t="n">
-        <v>49.18</v>
+        <v>48.66</v>
       </c>
       <c r="E197" t="n">
-        <v>50.1</v>
+        <v>49.22</v>
       </c>
       <c r="F197" t="n">
-        <v>48.82</v>
+        <v>48.02</v>
       </c>
       <c r="G197" t="n">
-        <v>49.92</v>
+        <v>48.22</v>
       </c>
       <c r="H197" t="n">
-        <v>1.63</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>68.70999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="C198" t="n">
-        <v>4.88594877</v>
+        <v>4.89623377</v>
       </c>
       <c r="D198" t="n">
-        <v>50.5</v>
+        <v>48.22</v>
       </c>
       <c r="E198" t="n">
-        <v>50.95</v>
+        <v>48.22</v>
       </c>
       <c r="F198" t="n">
-        <v>49.74</v>
+        <v>47.46</v>
       </c>
       <c r="G198" t="n">
-        <v>50.1</v>
+        <v>47.46</v>
       </c>
       <c r="H198" t="n">
-        <v>0.36</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>20.01</v>
+        <v>78.34</v>
       </c>
       <c r="C199" t="n">
-        <v>4.88794977</v>
+        <v>4.90406777</v>
       </c>
       <c r="D199" t="n">
-        <v>50</v>
+        <v>47.86</v>
       </c>
       <c r="E199" t="n">
-        <v>50.5</v>
+        <v>48.68</v>
       </c>
       <c r="F199" t="n">
-        <v>49.04</v>
+        <v>47.7</v>
       </c>
       <c r="G199" t="n">
-        <v>49.06</v>
+        <v>48.48</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-18.77</v>
+        <v>12.2</v>
       </c>
       <c r="C200" t="n">
-        <v>4.88607277</v>
+        <v>4.90528777</v>
       </c>
       <c r="D200" t="n">
-        <v>49.08</v>
+        <v>48.1</v>
       </c>
       <c r="E200" t="n">
-        <v>49.78</v>
+        <v>48.7</v>
       </c>
       <c r="F200" t="n">
-        <v>48.7</v>
+        <v>47.38</v>
       </c>
       <c r="G200" t="n">
-        <v>49.4</v>
+        <v>47.88</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>95.14</v>
+        <v>-50.42</v>
       </c>
       <c r="C201" t="n">
-        <v>4.89558677</v>
+        <v>4.90024577</v>
       </c>
       <c r="D201" t="n">
-        <v>48.66</v>
+        <v>47.34</v>
       </c>
       <c r="E201" t="n">
-        <v>49.22</v>
+        <v>48.28</v>
       </c>
       <c r="F201" t="n">
-        <v>48.02</v>
+        <v>47.06</v>
       </c>
       <c r="G201" t="n">
-        <v>48.22</v>
+        <v>47.9</v>
       </c>
       <c r="H201" t="n">
-        <v>-2.39</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>6.47</v>
+        <v>7.38</v>
       </c>
       <c r="C202" t="n">
-        <v>4.89623377</v>
+        <v>4.90098377</v>
       </c>
       <c r="D202" t="n">
-        <v>48.22</v>
+        <v>49.98</v>
       </c>
       <c r="E202" t="n">
-        <v>48.22</v>
+        <v>51.2</v>
       </c>
       <c r="F202" t="n">
-        <v>47.46</v>
+        <v>49.76</v>
       </c>
       <c r="G202" t="n">
-        <v>47.46</v>
+        <v>50.55</v>
       </c>
       <c r="H202" t="n">
-        <v>-1.58</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>78.34</v>
+        <v>0.19</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90406777</v>
+        <v>4.90100277</v>
       </c>
       <c r="D203" t="n">
-        <v>47.86</v>
+        <v>50.55</v>
       </c>
       <c r="E203" t="n">
-        <v>48.68</v>
+        <v>51.8</v>
       </c>
       <c r="F203" t="n">
-        <v>47.7</v>
+        <v>50.5</v>
       </c>
       <c r="G203" t="n">
-        <v>48.48</v>
+        <v>51.2</v>
       </c>
       <c r="H203" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12.2</v>
+        <v>-404.07</v>
       </c>
       <c r="C204" t="n">
-        <v>4.90528777</v>
+        <v>4.86059577</v>
       </c>
       <c r="D204" t="n">
-        <v>48.1</v>
+        <v>50.3</v>
       </c>
       <c r="E204" t="n">
-        <v>48.7</v>
+        <v>51</v>
       </c>
       <c r="F204" t="n">
-        <v>47.38</v>
+        <v>49.3</v>
       </c>
       <c r="G204" t="n">
-        <v>47.88</v>
+        <v>49.46</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.24</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-50.42</v>
+        <v>-104.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.90024577</v>
+        <v>4.85015377</v>
       </c>
       <c r="D205" t="n">
-        <v>47.34</v>
+        <v>48.86</v>
       </c>
       <c r="E205" t="n">
-        <v>48.28</v>
+        <v>49.74</v>
       </c>
       <c r="F205" t="n">
-        <v>47.06</v>
+        <v>47.6</v>
       </c>
       <c r="G205" t="n">
-        <v>47.9</v>
+        <v>47.68</v>
       </c>
       <c r="H205" t="n">
-        <v>0.04</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7.38</v>
+        <v>-9.27</v>
       </c>
       <c r="C206" t="n">
-        <v>4.90098377</v>
+        <v>4.84922677</v>
       </c>
       <c r="D206" t="n">
-        <v>49.98</v>
+        <v>47.68</v>
       </c>
       <c r="E206" t="n">
-        <v>51.2</v>
+        <v>48.9</v>
       </c>
       <c r="F206" t="n">
-        <v>49.76</v>
+        <v>47.32</v>
       </c>
       <c r="G206" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="H206" t="n">
-        <v>5.53</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.19</v>
+        <v>-62.41</v>
       </c>
       <c r="C207" t="n">
-        <v>4.90100277</v>
+        <v>4.84298577</v>
       </c>
       <c r="D207" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="E207" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F207" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="G207" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="H207" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-404.07</v>
+        <v>-4.06</v>
       </c>
       <c r="C208" t="n">
-        <v>4.86059577</v>
+        <v>4.84257977</v>
       </c>
       <c r="D208" t="n">
-        <v>50.3</v>
+        <v>47.8</v>
       </c>
       <c r="E208" t="n">
-        <v>51</v>
+        <v>48.6</v>
       </c>
       <c r="F208" t="n">
-        <v>49.3</v>
+        <v>47.16</v>
       </c>
       <c r="G208" t="n">
-        <v>49.46</v>
+        <v>47.98</v>
       </c>
       <c r="H208" t="n">
-        <v>-3.4</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-104.42</v>
+        <v>107.65</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85015377</v>
+        <v>4.85334477</v>
       </c>
       <c r="D209" t="n">
-        <v>48.86</v>
+        <v>47.86</v>
       </c>
       <c r="E209" t="n">
-        <v>49.74</v>
+        <v>48.44</v>
       </c>
       <c r="F209" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="G209" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="H209" t="n">
-        <v>-3.6</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-9.27</v>
+        <v>137.46</v>
       </c>
       <c r="C210" t="n">
-        <v>4.84922677</v>
+        <v>4.86709077</v>
       </c>
       <c r="D210" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="E210" t="n">
-        <v>48.9</v>
+        <v>48.22</v>
       </c>
       <c r="F210" t="n">
-        <v>47.32</v>
+        <v>46.6</v>
       </c>
       <c r="G210" t="n">
-        <v>48.1</v>
+        <v>47.06</v>
       </c>
       <c r="H210" t="n">
-        <v>0.88</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-62.41</v>
+        <v>154.04</v>
       </c>
       <c r="C211" t="n">
-        <v>4.84298577</v>
+        <v>4.88249477</v>
       </c>
       <c r="D211" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="E211" t="n">
-        <v>49</v>
+        <v>46.76</v>
       </c>
       <c r="F211" t="n">
-        <v>47.5</v>
+        <v>44.56</v>
       </c>
       <c r="G211" t="n">
-        <v>48.6</v>
+        <v>45.86</v>
       </c>
       <c r="H211" t="n">
-        <v>1.04</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-4.06</v>
+        <v>78.03</v>
       </c>
       <c r="C212" t="n">
-        <v>4.84257977</v>
+        <v>4.89029777</v>
       </c>
       <c r="D212" t="n">
-        <v>47.8</v>
+        <v>46.56</v>
       </c>
       <c r="E212" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="F212" t="n">
-        <v>47.16</v>
+        <v>46.2</v>
       </c>
       <c r="G212" t="n">
-        <v>47.98</v>
+        <v>46.38</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.28</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>107.65</v>
+        <v>401.67</v>
       </c>
       <c r="C213" t="n">
-        <v>4.85334477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.86</v>
+        <v>48.14</v>
       </c>
       <c r="E213" t="n">
-        <v>48.44</v>
+        <v>48.88</v>
       </c>
       <c r="F213" t="n">
-        <v>46.5</v>
+        <v>47.12</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.33</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>137.46</v>
+        <v>-79.33</v>
       </c>
       <c r="C214" t="n">
-        <v>4.86709077</v>
+        <v>4.92253177</v>
       </c>
       <c r="D214" t="n">
-        <v>47.82</v>
+        <v>48.1</v>
       </c>
       <c r="E214" t="n">
-        <v>48.22</v>
+        <v>50.45</v>
       </c>
       <c r="F214" t="n">
-        <v>46.6</v>
+        <v>48.04</v>
       </c>
       <c r="G214" t="n">
-        <v>47.06</v>
+        <v>50.4</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.59</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>154.04</v>
+        <v>-415.48</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88249477</v>
+        <v>4.88098377</v>
       </c>
       <c r="D215" t="n">
-        <v>46.68</v>
+        <v>49.44</v>
       </c>
       <c r="E215" t="n">
-        <v>46.76</v>
+        <v>50.15</v>
       </c>
       <c r="F215" t="n">
-        <v>44.56</v>
+        <v>48.88</v>
       </c>
       <c r="G215" t="n">
-        <v>45.86</v>
+        <v>49.32</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>78.03</v>
+        <v>-394.96</v>
       </c>
       <c r="C216" t="n">
-        <v>4.89029777</v>
+        <v>4.84148777</v>
       </c>
       <c r="D216" t="n">
-        <v>46.56</v>
+        <v>49.08</v>
       </c>
       <c r="E216" t="n">
-        <v>48</v>
+        <v>49.08</v>
       </c>
       <c r="F216" t="n">
-        <v>46.2</v>
+        <v>47.2</v>
       </c>
       <c r="G216" t="n">
-        <v>46.38</v>
+        <v>47.62</v>
       </c>
       <c r="H216" t="n">
-        <v>1.13</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>401.67</v>
+        <v>-39.23</v>
       </c>
       <c r="C217" t="n">
-        <v>4.93046477</v>
+        <v>4.83756477</v>
       </c>
       <c r="D217" t="n">
-        <v>48.14</v>
+        <v>47.2</v>
       </c>
       <c r="E217" t="n">
-        <v>48.88</v>
+        <v>47.2</v>
       </c>
       <c r="F217" t="n">
-        <v>47.12</v>
+        <v>46.42</v>
       </c>
       <c r="G217" t="n">
-        <v>47.82</v>
+        <v>46.48</v>
       </c>
       <c r="H217" t="n">
-        <v>3.1</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-79.33</v>
+        <v>219.67</v>
       </c>
       <c r="C218" t="n">
-        <v>4.92253177</v>
+        <v>4.85953177</v>
       </c>
       <c r="D218" t="n">
-        <v>48.1</v>
+        <v>45.74</v>
       </c>
       <c r="E218" t="n">
-        <v>50.45</v>
+        <v>46.44</v>
       </c>
       <c r="F218" t="n">
-        <v>48.04</v>
+        <v>45.38</v>
       </c>
       <c r="G218" t="n">
-        <v>50.4</v>
+        <v>46.34</v>
       </c>
       <c r="H218" t="n">
-        <v>5.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-415.48</v>
+        <v>111.68</v>
       </c>
       <c r="C219" t="n">
-        <v>4.88098377</v>
+        <v>4.87069977</v>
       </c>
       <c r="D219" t="n">
-        <v>49.44</v>
+        <v>45.9</v>
       </c>
       <c r="E219" t="n">
-        <v>50.15</v>
+        <v>47.8</v>
       </c>
       <c r="F219" t="n">
-        <v>48.88</v>
+        <v>45.84</v>
       </c>
       <c r="G219" t="n">
-        <v>49.32</v>
+        <v>47.52</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>-394.96</v>
-      </c>
-      <c r="C220" t="n">
-        <v>4.84148777</v>
-      </c>
-      <c r="D220" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="E220" t="n">
-        <v>49.08</v>
-      </c>
-      <c r="F220" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="G220" t="n">
-        <v>47.62</v>
-      </c>
-      <c r="H220" t="n">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="B221" t="n">
-        <v>-39.23</v>
-      </c>
-      <c r="C221" t="n">
-        <v>4.83756477</v>
-      </c>
-      <c r="D221" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="E221" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="F221" t="n">
-        <v>46.42</v>
-      </c>
-      <c r="G221" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="H221" t="n">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B222" t="n">
-        <v>219.67</v>
-      </c>
-      <c r="C222" t="n">
-        <v>4.85953177</v>
-      </c>
-      <c r="D222" t="n">
-        <v>45.74</v>
-      </c>
-      <c r="E222" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="F222" t="n">
-        <v>45.38</v>
-      </c>
-      <c r="G222" t="n">
-        <v>46.34</v>
-      </c>
-      <c r="H222" t="n">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B223" t="n">
-        <v>111.68</v>
-      </c>
-      <c r="C223" t="n">
-        <v>4.87069977</v>
-      </c>
-      <c r="D223" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="E223" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="F223" t="n">
-        <v>45.84</v>
-      </c>
-      <c r="G223" t="n">
-        <v>47.52</v>
-      </c>
-      <c r="H223" t="n">
         <v>2.55</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6389,7 +6389,7 @@
         <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>48.14</v>
+        <v>47.28</v>
       </c>
       <c r="E213" t="n">
         <v>48.88</v>
@@ -6570,6 +6570,34 @@
       </c>
       <c r="H219" t="n">
         <v>2.55</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.87069977</v>
+      </c>
+      <c r="D220" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="E220" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="F220" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="G220" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-1.05</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6389,7 +6389,7 @@
         <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.28</v>
+        <v>48.14</v>
       </c>
       <c r="E213" t="n">
         <v>48.88</v>
@@ -6570,34 +6570,6 @@
       </c>
       <c r="H219" t="n">
         <v>2.55</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
-      <c r="C220" t="n">
-        <v>4.87069977</v>
-      </c>
-      <c r="D220" t="n">
-        <v>47.52</v>
-      </c>
-      <c r="E220" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="F220" t="n">
-        <v>46.54</v>
-      </c>
-      <c r="G220" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="H220" t="n">
-        <v>-1.05</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6572,6 +6572,34 @@
         <v>2.55</v>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.87069977</v>
+      </c>
+      <c r="D220" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="E220" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="F220" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="G220" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="H220" t="n">
+        <v>-2.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0</v>
+        <v>47.5</v>
       </c>
       <c r="C220" t="n">
-        <v>4.87069977</v>
+        <v>4.87544977</v>
       </c>
       <c r="D220" t="n">
         <v>47.52</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H220"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6389,7 +6389,7 @@
         <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>48.14</v>
+        <v>47.28</v>
       </c>
       <c r="E213" t="n">
         <v>48.88</v>
@@ -6598,6 +6598,34 @@
       </c>
       <c r="H220" t="n">
         <v>-2.95</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>0</v>
+      </c>
+      <c r="C221" t="n">
+        <v>4.87544977</v>
+      </c>
+      <c r="D221" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="E221" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F221" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="G221" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -6607,10 +6607,10 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0</v>
+        <v>-30.32</v>
       </c>
       <c r="C221" t="n">
-        <v>4.87544977</v>
+        <v>4.87241777</v>
       </c>
       <c r="D221" t="n">
         <v>46.92</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6628,6 +6628,34 @@
         <v>0.78</v>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>0</v>
+      </c>
+      <c r="C222" t="n">
+        <v>4.87241777</v>
+      </c>
+      <c r="D222" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="E222" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F222" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="G222" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0</v>
+        <v>15.46</v>
       </c>
       <c r="C222" t="n">
-        <v>4.87241777</v>
+        <v>4.87396377</v>
       </c>
       <c r="D222" t="n">
         <v>46.9</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H222"/>
+  <dimension ref="A1:H226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="E79" t="n">
-        <v>72.25</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>69.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G79" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E80" t="n">
-        <v>71.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F80" t="n">
-        <v>69.55</v>
+        <v>71.5</v>
       </c>
       <c r="G80" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,3966 +2693,4078 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>70.3</v>
+        <v>72.8</v>
       </c>
       <c r="E81" t="n">
-        <v>73.3</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>70.3</v>
+        <v>71.5</v>
       </c>
       <c r="G81" t="n">
-        <v>72.84999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H81" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-37.37</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D82" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>73.5</v>
+        <v>72.25</v>
       </c>
       <c r="F82" t="n">
-        <v>71.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.51</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D83" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>73.15000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="F83" t="n">
-        <v>70.5</v>
+        <v>69.55</v>
       </c>
       <c r="G83" t="n">
-        <v>71.84999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>0.14</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>39.15</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29772381</v>
+        <v>5.29754581</v>
       </c>
       <c r="D84" t="n">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="E84" t="n">
-        <v>71.8</v>
+        <v>73.3</v>
       </c>
       <c r="F84" t="n">
-        <v>68.55</v>
+        <v>70.3</v>
       </c>
       <c r="G84" t="n">
-        <v>68.65000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-4.45</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-32.03</v>
+        <v>-37.37</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29452081</v>
+        <v>5.29380881</v>
       </c>
       <c r="D85" t="n">
-        <v>69.5</v>
+        <v>71.8</v>
       </c>
       <c r="E85" t="n">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="F85" t="n">
-        <v>68.15000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G85" t="n">
-        <v>68.75</v>
+        <v>71.75</v>
       </c>
       <c r="H85" t="n">
-        <v>0.15</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-245.51</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>5.26996981</v>
+        <v>5.29380881</v>
       </c>
       <c r="D86" t="n">
-        <v>67.75</v>
+        <v>72.8</v>
       </c>
       <c r="E86" t="n">
-        <v>70.15000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>67</v>
+        <v>70.5</v>
       </c>
       <c r="G86" t="n">
-        <v>68</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.99</v>
+        <v>39.15</v>
       </c>
       <c r="C87" t="n">
-        <v>5.27246881</v>
+        <v>5.29772381</v>
       </c>
       <c r="D87" t="n">
-        <v>68.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>69</v>
+        <v>71.8</v>
       </c>
       <c r="F87" t="n">
-        <v>65.65000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="G87" t="n">
-        <v>66.55</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-2.13</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-70.5937</v>
+        <v>-32.03</v>
       </c>
       <c r="C88" t="n">
-        <v>5.26540944</v>
+        <v>5.29452081</v>
       </c>
       <c r="D88" t="n">
-        <v>65.84999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E88" t="n">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="F88" t="n">
-        <v>64.45</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>65.84999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-83.42</v>
+        <v>-245.51</v>
       </c>
       <c r="C89" t="n">
-        <v>5.25706744</v>
+        <v>5.26996981</v>
       </c>
       <c r="D89" t="n">
-        <v>66.90000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="E89" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>67</v>
+      </c>
+      <c r="G89" t="n">
         <v>68</v>
       </c>
-      <c r="F89" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="H89" t="n">
-        <v>-0.38</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>32.9872</v>
+        <v>24.99</v>
       </c>
       <c r="C90" t="n">
-        <v>5.26036616</v>
+        <v>5.27246881</v>
       </c>
       <c r="D90" t="n">
-        <v>65.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>67.65000000000001</v>
+        <v>69</v>
       </c>
       <c r="F90" t="n">
-        <v>65.34999999999999</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>67.45</v>
+        <v>66.55</v>
       </c>
       <c r="H90" t="n">
-        <v>2.82</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-168.98</v>
+        <v>-70.5937</v>
       </c>
       <c r="C91" t="n">
-        <v>5.24346816</v>
+        <v>5.26540944</v>
       </c>
       <c r="D91" t="n">
-        <v>64.84999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>69</v>
+        <v>66.8</v>
       </c>
       <c r="F91" t="n">
-        <v>64.7</v>
+        <v>64.45</v>
       </c>
       <c r="G91" t="n">
-        <v>68.90000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>2.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-195.54</v>
+        <v>-83.42</v>
       </c>
       <c r="C92" t="n">
-        <v>5.22391416</v>
+        <v>5.25706744</v>
       </c>
       <c r="D92" t="n">
-        <v>69.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>70.2</v>
+        <v>68</v>
       </c>
       <c r="F92" t="n">
-        <v>67.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>69.05</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>0.22</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>16.18</v>
+        <v>32.9872</v>
       </c>
       <c r="C93" t="n">
-        <v>5.22553216</v>
+        <v>5.26036616</v>
       </c>
       <c r="D93" t="n">
-        <v>69.25</v>
+        <v>65.5</v>
       </c>
       <c r="E93" t="n">
-        <v>70.8</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>69.05</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>69.84999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="H93" t="n">
-        <v>1.16</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.87</v>
+        <v>-168.98</v>
       </c>
       <c r="C94" t="n">
-        <v>5.22691916</v>
+        <v>5.24346816</v>
       </c>
       <c r="D94" t="n">
-        <v>70.95</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="F94" t="n">
-        <v>69.15000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G94" t="n">
-        <v>70.15000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-145.08</v>
+        <v>-195.54</v>
       </c>
       <c r="C95" t="n">
-        <v>5.21241116</v>
+        <v>5.22391416</v>
       </c>
       <c r="D95" t="n">
-        <v>68.95</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>69</v>
+        <v>70.2</v>
       </c>
       <c r="F95" t="n">
-        <v>67.3</v>
+        <v>67.95</v>
       </c>
       <c r="G95" t="n">
-        <v>67.90000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="H95" t="n">
-        <v>-3.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.02</v>
+        <v>16.18</v>
       </c>
       <c r="C96" t="n">
-        <v>5.21491316</v>
+        <v>5.22553216</v>
       </c>
       <c r="D96" t="n">
-        <v>67.5</v>
+        <v>69.25</v>
       </c>
       <c r="E96" t="n">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F96" t="n">
-        <v>66.3</v>
+        <v>69.05</v>
       </c>
       <c r="G96" t="n">
-        <v>69.90000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>2.95</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-6.25</v>
+        <v>13.87</v>
       </c>
       <c r="C97" t="n">
-        <v>5.21428816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D97" t="n">
-        <v>71.25</v>
+        <v>70.95</v>
       </c>
       <c r="E97" t="n">
-        <v>73.3</v>
+        <v>71.3</v>
       </c>
       <c r="F97" t="n">
-        <v>70.84999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>71.3</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-48.58</v>
+        <v>-145.08</v>
       </c>
       <c r="C98" t="n">
-        <v>5.20943016</v>
+        <v>5.21241116</v>
       </c>
       <c r="D98" t="n">
-        <v>70.65000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E98" t="n">
-        <v>71.25</v>
+        <v>69</v>
       </c>
       <c r="F98" t="n">
-        <v>66.34999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G98" t="n">
-        <v>66.84999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>-6.24</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-197.18</v>
+        <v>25.02</v>
       </c>
       <c r="C99" t="n">
-        <v>5.18971216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D99" t="n">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="E99" t="n">
-        <v>67.34999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="G99" t="n">
-        <v>66</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.27</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>426.64</v>
+        <v>-6.25</v>
       </c>
       <c r="C100" t="n">
-        <v>5.23237616</v>
+        <v>5.21428816</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>71.25</v>
       </c>
       <c r="E100" t="n">
-        <v>68.7</v>
+        <v>73.3</v>
       </c>
       <c r="F100" t="n">
-        <v>66.34999999999999</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>66.8</v>
+        <v>71.3</v>
       </c>
       <c r="H100" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>41.4993</v>
+        <v>-48.58</v>
       </c>
       <c r="C101" t="n">
-        <v>5.23652609</v>
+        <v>5.20943016</v>
       </c>
       <c r="D101" t="n">
-        <v>65.59999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>66.05</v>
+        <v>71.25</v>
       </c>
       <c r="F101" t="n">
-        <v>64.2</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>64.8</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.99</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-220.5688</v>
+        <v>-197.18</v>
       </c>
       <c r="C102" t="n">
-        <v>5.21446921</v>
+        <v>5.18971216</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.65000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>63.45</v>
+        <v>65.8</v>
       </c>
       <c r="G102" t="n">
-        <v>67.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="H102" t="n">
-        <v>4.32</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>215.27</v>
+        <v>426.64</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23599621</v>
+        <v>5.23237616</v>
       </c>
       <c r="D103" t="n">
-        <v>69.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="E103" t="n">
-        <v>71.34999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F103" t="n">
-        <v>69.45</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>70.45</v>
+        <v>66.8</v>
       </c>
       <c r="H103" t="n">
-        <v>4.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-160.53</v>
+        <v>41.4993</v>
       </c>
       <c r="C104" t="n">
-        <v>5.21994321</v>
+        <v>5.23652609</v>
       </c>
       <c r="D104" t="n">
-        <v>69.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>70.8</v>
+        <v>66.05</v>
       </c>
       <c r="F104" t="n">
-        <v>68.7</v>
+        <v>64.2</v>
       </c>
       <c r="G104" t="n">
-        <v>69</v>
+        <v>64.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.06</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-304.01</v>
+        <v>-220.5688</v>
       </c>
       <c r="C105" t="n">
-        <v>5.18954221</v>
+        <v>5.21446921</v>
       </c>
       <c r="D105" t="n">
-        <v>69</v>
+        <v>66.2</v>
       </c>
       <c r="E105" t="n">
-        <v>71.5</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>68.3</v>
+        <v>63.45</v>
       </c>
       <c r="G105" t="n">
-        <v>70.05</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>1.52</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-30.3</v>
+        <v>215.27</v>
       </c>
       <c r="C106" t="n">
-        <v>5.18651221</v>
+        <v>5.23599621</v>
       </c>
       <c r="D106" t="n">
-        <v>68.05</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>69.34999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>68</v>
+        <v>69.45</v>
       </c>
       <c r="G106" t="n">
-        <v>68.8</v>
+        <v>70.45</v>
       </c>
       <c r="H106" t="n">
-        <v>-1.78</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-92.3</v>
+        <v>-160.53</v>
       </c>
       <c r="C107" t="n">
-        <v>5.17728221</v>
+        <v>5.21994321</v>
       </c>
       <c r="D107" t="n">
-        <v>68.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>69.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F107" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="G107" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.6</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>25.43</v>
+        <v>-304.01</v>
       </c>
       <c r="C108" t="n">
-        <v>5.17982521</v>
+        <v>5.18954221</v>
       </c>
       <c r="D108" t="n">
-        <v>68.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="E108" t="n">
-        <v>71.45</v>
+        <v>71.5</v>
       </c>
       <c r="F108" t="n">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G108" t="n">
-        <v>71.2</v>
+        <v>70.05</v>
       </c>
       <c r="H108" t="n">
-        <v>5.17</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>136.53</v>
+        <v>-30.3</v>
       </c>
       <c r="C109" t="n">
-        <v>5.19347821</v>
+        <v>5.18651221</v>
       </c>
       <c r="D109" t="n">
-        <v>71.2</v>
+        <v>68.05</v>
       </c>
       <c r="E109" t="n">
-        <v>73.40000000000001</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G109" t="n">
-        <v>71.8</v>
+        <v>68.8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.84</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-224.29</v>
+        <v>-92.3</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17104921</v>
+        <v>5.17728221</v>
       </c>
       <c r="D110" t="n">
-        <v>73.45</v>
+        <v>68.8</v>
       </c>
       <c r="E110" t="n">
-        <v>74</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>71.65000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="G110" t="n">
-        <v>73.3</v>
+        <v>67.7</v>
       </c>
       <c r="H110" t="n">
-        <v>2.09</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>97.7422</v>
+        <v>25.43</v>
       </c>
       <c r="C111" t="n">
-        <v>5.18082343</v>
+        <v>5.17982521</v>
       </c>
       <c r="D111" t="n">
-        <v>71.95</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>73.5</v>
+        <v>71.45</v>
       </c>
       <c r="F111" t="n">
-        <v>71.75</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G111" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.91</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-116.85</v>
+        <v>136.53</v>
       </c>
       <c r="C112" t="n">
-        <v>5.16913843</v>
+        <v>5.19347821</v>
       </c>
       <c r="D112" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E112" t="n">
-        <v>76.45</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>71.55</v>
+        <v>70</v>
       </c>
       <c r="G112" t="n">
-        <v>74.2</v>
+        <v>71.8</v>
       </c>
       <c r="H112" t="n">
-        <v>3.2</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>32.76</v>
+        <v>-224.29</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17241443</v>
+        <v>5.17104921</v>
       </c>
       <c r="D113" t="n">
-        <v>74.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E113" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F113" t="n">
-        <v>73.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>73.7</v>
+        <v>73.3</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.67</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-19.6</v>
+        <v>97.7422</v>
       </c>
       <c r="C114" t="n">
-        <v>5.17045443</v>
+        <v>5.18082343</v>
       </c>
       <c r="D114" t="n">
-        <v>73.7</v>
+        <v>71.95</v>
       </c>
       <c r="E114" t="n">
-        <v>73.95</v>
+        <v>73.5</v>
       </c>
       <c r="F114" t="n">
-        <v>71.65000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="G114" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.95</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>74.23999999999999</v>
+        <v>-116.85</v>
       </c>
       <c r="C115" t="n">
-        <v>5.17787843</v>
+        <v>5.16913843</v>
       </c>
       <c r="D115" t="n">
-        <v>73.75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>73.75</v>
+        <v>76.45</v>
       </c>
       <c r="F115" t="n">
-        <v>70.5</v>
+        <v>71.55</v>
       </c>
       <c r="G115" t="n">
-        <v>70.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>15.04</v>
+        <v>32.76</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17938243</v>
+        <v>5.17241443</v>
       </c>
       <c r="D116" t="n">
-        <v>70.95</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>72.15000000000001</v>
+        <v>75</v>
       </c>
       <c r="F116" t="n">
-        <v>70.95</v>
+        <v>73.25</v>
       </c>
       <c r="G116" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H116" t="n">
-        <v>0.99</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>213.47</v>
+        <v>-19.6</v>
       </c>
       <c r="C117" t="n">
-        <v>5.20072943</v>
+        <v>5.17045443</v>
       </c>
       <c r="D117" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E117" t="n">
-        <v>71.90000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="F117" t="n">
-        <v>70.40000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>71.45</v>
+        <v>73</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.21</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-167.67</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>5.18396243</v>
+        <v>5.17787843</v>
       </c>
       <c r="D118" t="n">
-        <v>72</v>
+        <v>73.75</v>
       </c>
       <c r="E118" t="n">
-        <v>73.45</v>
+        <v>73.75</v>
       </c>
       <c r="F118" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G118" t="n">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>2.59</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-78.5919</v>
+        <v>15.04</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17610324</v>
+        <v>5.17938243</v>
       </c>
       <c r="D119" t="n">
-        <v>73.3</v>
+        <v>70.95</v>
       </c>
       <c r="E119" t="n">
-        <v>73.3</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>71.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="G119" t="n">
-        <v>73.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.14</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-54.57</v>
+        <v>213.47</v>
       </c>
       <c r="C120" t="n">
-        <v>5.17064624</v>
+        <v>5.20072943</v>
       </c>
       <c r="D120" t="n">
-        <v>72.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>73.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>71.95</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>73.45</v>
+        <v>71.45</v>
       </c>
       <c r="H120" t="n">
-        <v>0.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>32.9</v>
+        <v>-167.67</v>
       </c>
       <c r="C121" t="n">
-        <v>5.17393624</v>
+        <v>5.18396243</v>
       </c>
       <c r="D121" t="n">
+        <v>72</v>
+      </c>
+      <c r="E121" t="n">
         <v>73.45</v>
       </c>
-      <c r="E121" t="n">
-        <v>74.40000000000001</v>
-      </c>
       <c r="F121" t="n">
-        <v>71.75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>73.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.41</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>41.93</v>
+        <v>-78.5919</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17812924</v>
+        <v>5.17610324</v>
       </c>
       <c r="D122" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="E122" t="n">
-        <v>73.65000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F122" t="n">
-        <v>68.7</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>69.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.44</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>52.87</v>
+        <v>-54.57</v>
       </c>
       <c r="C123" t="n">
-        <v>5.18341624</v>
+        <v>5.17064624</v>
       </c>
       <c r="D123" t="n">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E123" t="n">
-        <v>70.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>68.90000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G123" t="n">
-        <v>69.7</v>
+        <v>73.45</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>291.58</v>
+        <v>32.9</v>
       </c>
       <c r="C124" t="n">
-        <v>5.21257424</v>
+        <v>5.17393624</v>
       </c>
       <c r="D124" t="n">
-        <v>69.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E124" t="n">
-        <v>69.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>66.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G124" t="n">
-        <v>67</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>-3.87</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-60.7601</v>
+        <v>41.93</v>
       </c>
       <c r="C125" t="n">
-        <v>5.20649823</v>
+        <v>5.17812924</v>
       </c>
       <c r="D125" t="n">
-        <v>69.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E125" t="n">
-        <v>70.25</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>68.45</v>
+        <v>68.7</v>
       </c>
       <c r="G125" t="n">
-        <v>69.25</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>3.36</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>264.89</v>
+        <v>52.87</v>
       </c>
       <c r="C126" t="n">
-        <v>5.23298723</v>
+        <v>5.18341624</v>
       </c>
       <c r="D126" t="n">
-        <v>68.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>69.75</v>
+        <v>70.5</v>
       </c>
       <c r="F126" t="n">
-        <v>67.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>67.55</v>
+        <v>69.7</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.45</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>291.58</v>
       </c>
       <c r="C127" t="n">
-        <v>5.23298723</v>
+        <v>5.21257424</v>
       </c>
       <c r="D127" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>71.15000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F127" t="n">
-        <v>68.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G127" t="n">
-        <v>70.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H127" t="n">
-        <v>3.85</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-60.7601</v>
       </c>
       <c r="C128" t="n">
-        <v>5.23298723</v>
+        <v>5.20649823</v>
       </c>
       <c r="D128" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="F128" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="G128" t="n">
         <v>69.25</v>
       </c>
-      <c r="E128" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F128" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="G128" t="n">
-        <v>69.65000000000001</v>
-      </c>
       <c r="H128" t="n">
-        <v>-0.71</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-369.37</v>
+        <v>264.89</v>
       </c>
       <c r="C129" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D129" t="n">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E129" t="n">
-        <v>69.5</v>
+        <v>69.75</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.84999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.58</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D130" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E130" t="n">
-        <v>70.34999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="F130" t="n">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="G130" t="n">
-        <v>69.95</v>
+        <v>67.55</v>
       </c>
       <c r="H130" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>68.9663</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>5.20294686</v>
+        <v>5.23298723</v>
       </c>
       <c r="D131" t="n">
-        <v>68.34999999999999</v>
+        <v>69</v>
       </c>
       <c r="E131" t="n">
-        <v>70.3</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>68.34999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G131" t="n">
-        <v>70.05</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>0.14</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-247.41</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>5.17820586</v>
+        <v>5.23298723</v>
       </c>
       <c r="D132" t="n">
-        <v>69.5</v>
+        <v>69.25</v>
       </c>
       <c r="E132" t="n">
-        <v>74.15000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>69.45</v>
+        <v>68.2</v>
       </c>
       <c r="G132" t="n">
-        <v>73.84999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>5.42</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>27.55</v>
+        <v>-369.37</v>
       </c>
       <c r="C133" t="n">
-        <v>5.18096086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D133" t="n">
-        <v>73.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E133" t="n">
-        <v>75.15000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F133" t="n">
-        <v>73.05</v>
+        <v>67.3</v>
       </c>
       <c r="G133" t="n">
-        <v>73.40000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.61</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-286.2</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5.15234086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D134" t="n">
-        <v>73.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="E134" t="n">
-        <v>74.40000000000001</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>73.05</v>
+        <v>68.5</v>
       </c>
       <c r="G134" t="n">
-        <v>73.65000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="H134" t="n">
-        <v>0.34</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>48.88</v>
+        <v>68.9663</v>
       </c>
       <c r="C135" t="n">
-        <v>5.15722886</v>
+        <v>5.20294686</v>
       </c>
       <c r="D135" t="n">
-        <v>76.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>78.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F135" t="n">
-        <v>75.40000000000001</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>76.84999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H135" t="n">
-        <v>4.34</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-55.96</v>
+        <v>-247.41</v>
       </c>
       <c r="C136" t="n">
-        <v>5.15163286</v>
+        <v>5.17820586</v>
       </c>
       <c r="D136" t="n">
-        <v>75.05</v>
+        <v>69.5</v>
       </c>
       <c r="E136" t="n">
-        <v>75.90000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>74.25</v>
+        <v>69.45</v>
       </c>
       <c r="G136" t="n">
-        <v>75.59999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.63</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-385.85</v>
+        <v>27.55</v>
       </c>
       <c r="C137" t="n">
-        <v>5.11304786</v>
+        <v>5.18096086</v>
       </c>
       <c r="D137" t="n">
-        <v>72.40000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E137" t="n">
-        <v>72.40000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>64.5</v>
+        <v>73.05</v>
       </c>
       <c r="G137" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-14.15</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>139.59</v>
+        <v>-286.2</v>
       </c>
       <c r="C138" t="n">
-        <v>5.12700686</v>
+        <v>5.15234086</v>
       </c>
       <c r="D138" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>64.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>61.75</v>
+        <v>73.05</v>
       </c>
       <c r="G138" t="n">
-        <v>62.1</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>-4.31</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1468.42</v>
+        <v>48.88</v>
       </c>
       <c r="C139" t="n">
-        <v>5.27384886</v>
+        <v>5.15722886</v>
       </c>
       <c r="D139" t="n">
-        <v>62.6</v>
+        <v>76.8</v>
       </c>
       <c r="E139" t="n">
-        <v>63.35</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>61</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G139" t="n">
-        <v>61.6</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>292.93</v>
+        <v>-55.96</v>
       </c>
       <c r="C140" t="n">
-        <v>5.30314186</v>
+        <v>5.15163286</v>
       </c>
       <c r="D140" t="n">
-        <v>62.5</v>
+        <v>75.05</v>
       </c>
       <c r="E140" t="n">
-        <v>63.85</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>61.55</v>
+        <v>74.25</v>
       </c>
       <c r="G140" t="n">
-        <v>62.25</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>1.06</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>17.9</v>
+        <v>-385.85</v>
       </c>
       <c r="C141" t="n">
-        <v>5.30493186</v>
+        <v>5.11304786</v>
       </c>
       <c r="D141" t="n">
-        <v>63.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E141" t="n">
-        <v>64.95</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F141" t="n">
-        <v>61.35</v>
+        <v>64.5</v>
       </c>
       <c r="G141" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.72</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-224.88</v>
+        <v>139.59</v>
       </c>
       <c r="C142" t="n">
-        <v>5.28244386</v>
+        <v>5.12700686</v>
       </c>
       <c r="D142" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E142" t="n">
-        <v>62.25</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>60.4</v>
+        <v>61.75</v>
       </c>
       <c r="G142" t="n">
-        <v>62.15</v>
+        <v>62.1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.57</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-244.5</v>
+        <v>1468.42</v>
       </c>
       <c r="C143" t="n">
-        <v>5.25799386</v>
+        <v>5.27384886</v>
       </c>
       <c r="D143" t="n">
-        <v>61.9</v>
+        <v>62.6</v>
       </c>
       <c r="E143" t="n">
-        <v>62.35</v>
+        <v>63.35</v>
       </c>
       <c r="F143" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G143" t="n">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.14</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-302.48</v>
+        <v>292.93</v>
       </c>
       <c r="C144" t="n">
-        <v>5.22774586</v>
+        <v>5.30314186</v>
       </c>
       <c r="D144" t="n">
-        <v>60.1</v>
+        <v>62.5</v>
       </c>
       <c r="E144" t="n">
-        <v>61</v>
+        <v>63.85</v>
       </c>
       <c r="F144" t="n">
-        <v>58.6</v>
+        <v>61.55</v>
       </c>
       <c r="G144" t="n">
-        <v>60.45</v>
+        <v>62.25</v>
       </c>
       <c r="H144" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-177.8636</v>
+        <v>17.9</v>
       </c>
       <c r="C145" t="n">
-        <v>5.2099595</v>
+        <v>5.30493186</v>
       </c>
       <c r="D145" t="n">
-        <v>60</v>
+        <v>63.2</v>
       </c>
       <c r="E145" t="n">
-        <v>60.05</v>
+        <v>64.95</v>
       </c>
       <c r="F145" t="n">
-        <v>55.7</v>
+        <v>61.35</v>
       </c>
       <c r="G145" t="n">
-        <v>57.85</v>
+        <v>61.8</v>
       </c>
       <c r="H145" t="n">
-        <v>-4.3</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-228.55</v>
+        <v>-224.88</v>
       </c>
       <c r="C146" t="n">
-        <v>5.1871045</v>
+        <v>5.28244386</v>
       </c>
       <c r="D146" t="n">
-        <v>56.95</v>
+        <v>61.8</v>
       </c>
       <c r="E146" t="n">
-        <v>59.1</v>
+        <v>62.25</v>
       </c>
       <c r="F146" t="n">
-        <v>56</v>
+        <v>60.4</v>
       </c>
       <c r="G146" t="n">
-        <v>58.55</v>
+        <v>62.15</v>
       </c>
       <c r="H146" t="n">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>423.9973</v>
+        <v>-244.5</v>
       </c>
       <c r="C147" t="n">
-        <v>5.22950423</v>
+        <v>5.25799386</v>
       </c>
       <c r="D147" t="n">
-        <v>57.05</v>
+        <v>61.9</v>
       </c>
       <c r="E147" t="n">
-        <v>62</v>
+        <v>62.35</v>
       </c>
       <c r="F147" t="n">
-        <v>56.55</v>
+        <v>59.9</v>
       </c>
       <c r="G147" t="n">
-        <v>61.9</v>
+        <v>60.2</v>
       </c>
       <c r="H147" t="n">
-        <v>5.72</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-119.16</v>
+        <v>-302.48</v>
       </c>
       <c r="C148" t="n">
-        <v>5.21758823</v>
+        <v>5.22774586</v>
       </c>
       <c r="D148" t="n">
-        <v>60.5</v>
+        <v>60.1</v>
       </c>
       <c r="E148" t="n">
-        <v>60.75</v>
+        <v>61</v>
       </c>
       <c r="F148" t="n">
-        <v>58.75</v>
+        <v>58.6</v>
       </c>
       <c r="G148" t="n">
-        <v>59.1</v>
+        <v>60.45</v>
       </c>
       <c r="H148" t="n">
-        <v>-4.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-301.92</v>
+        <v>-177.8636</v>
       </c>
       <c r="C149" t="n">
-        <v>5.18739623</v>
+        <v>5.2099595</v>
       </c>
       <c r="D149" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="E149" t="n">
-        <v>58.95</v>
+        <v>60.05</v>
       </c>
       <c r="F149" t="n">
-        <v>56.85</v>
+        <v>55.7</v>
       </c>
       <c r="G149" t="n">
-        <v>57.25</v>
+        <v>57.85</v>
       </c>
       <c r="H149" t="n">
-        <v>-3.13</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>112.29</v>
+        <v>-228.55</v>
       </c>
       <c r="C150" t="n">
-        <v>5.19862523</v>
+        <v>5.1871045</v>
       </c>
       <c r="D150" t="n">
-        <v>57.1</v>
+        <v>56.95</v>
       </c>
       <c r="E150" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
       <c r="F150" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="G150" t="n">
-        <v>56.65</v>
+        <v>58.55</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.05</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-62.4836</v>
+        <v>423.9973</v>
       </c>
       <c r="C151" t="n">
-        <v>5.19237687</v>
+        <v>5.22950423</v>
       </c>
       <c r="D151" t="n">
-        <v>55.3</v>
+        <v>57.05</v>
       </c>
       <c r="E151" t="n">
-        <v>57.9</v>
+        <v>62</v>
       </c>
       <c r="F151" t="n">
-        <v>54.95</v>
+        <v>56.55</v>
       </c>
       <c r="G151" t="n">
-        <v>57.35</v>
+        <v>61.9</v>
       </c>
       <c r="H151" t="n">
-        <v>1.24</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-29.35</v>
+        <v>-119.16</v>
       </c>
       <c r="C152" t="n">
-        <v>5.18944187</v>
+        <v>5.21758823</v>
       </c>
       <c r="D152" t="n">
-        <v>56.2</v>
+        <v>60.5</v>
       </c>
       <c r="E152" t="n">
-        <v>57.1</v>
+        <v>60.75</v>
       </c>
       <c r="F152" t="n">
-        <v>55.8</v>
+        <v>58.75</v>
       </c>
       <c r="G152" t="n">
-        <v>55.85</v>
+        <v>59.1</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.62</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>54.46</v>
+        <v>-301.92</v>
       </c>
       <c r="C153" t="n">
-        <v>5.19488787</v>
+        <v>5.18739623</v>
       </c>
       <c r="D153" t="n">
-        <v>55.3</v>
+        <v>58.95</v>
       </c>
       <c r="E153" t="n">
-        <v>55.55</v>
+        <v>58.95</v>
       </c>
       <c r="F153" t="n">
-        <v>53.25</v>
+        <v>56.85</v>
       </c>
       <c r="G153" t="n">
-        <v>54.7</v>
+        <v>57.25</v>
       </c>
       <c r="H153" t="n">
-        <v>-2.06</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>17.32</v>
+        <v>112.29</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19661987</v>
+        <v>5.19862523</v>
       </c>
       <c r="D154" t="n">
-        <v>54</v>
+        <v>57.1</v>
       </c>
       <c r="E154" t="n">
-        <v>54.1</v>
+        <v>57.6</v>
       </c>
       <c r="F154" t="n">
-        <v>52.25</v>
+        <v>56.5</v>
       </c>
       <c r="G154" t="n">
-        <v>53.15</v>
+        <v>56.65</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.83</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>93.42</v>
+        <v>-62.4836</v>
       </c>
       <c r="C155" t="n">
-        <v>5.20596187</v>
+        <v>5.19237687</v>
       </c>
       <c r="D155" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>53.25</v>
+        <v>54.95</v>
       </c>
       <c r="G155" t="n">
-        <v>57</v>
+        <v>57.35</v>
       </c>
       <c r="H155" t="n">
-        <v>7.24</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>64.81</v>
+        <v>-29.35</v>
       </c>
       <c r="C156" t="n">
-        <v>5.21244287</v>
+        <v>5.18944187</v>
       </c>
       <c r="D156" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="E156" t="n">
-        <v>58.05</v>
+        <v>57.1</v>
       </c>
       <c r="F156" t="n">
-        <v>56.5</v>
+        <v>55.8</v>
       </c>
       <c r="G156" t="n">
-        <v>56.85</v>
+        <v>55.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.26</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-172.75</v>
+        <v>54.46</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19516787</v>
+        <v>5.19488787</v>
       </c>
       <c r="D157" t="n">
-        <v>56.85</v>
+        <v>55.3</v>
       </c>
       <c r="E157" t="n">
-        <v>57.2</v>
+        <v>55.55</v>
       </c>
       <c r="F157" t="n">
-        <v>55</v>
+        <v>53.25</v>
       </c>
       <c r="G157" t="n">
-        <v>56</v>
+        <v>54.7</v>
       </c>
       <c r="H157" t="n">
-        <v>-1.5</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-24.86</v>
+        <v>17.32</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19268187</v>
+        <v>5.19661987</v>
       </c>
       <c r="D158" t="n">
-        <v>55.75</v>
+        <v>54</v>
       </c>
       <c r="E158" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="F158" t="n">
-        <v>53.7</v>
+        <v>52.25</v>
       </c>
       <c r="G158" t="n">
-        <v>53.9</v>
+        <v>53.15</v>
       </c>
       <c r="H158" t="n">
-        <v>-3.75</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.38</v>
+        <v>93.42</v>
       </c>
       <c r="C159" t="n">
-        <v>5.19441987</v>
+        <v>5.20596187</v>
       </c>
       <c r="D159" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E159" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F159" t="n">
         <v>53.25</v>
       </c>
-      <c r="E159" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F159" t="n">
-        <v>51.75</v>
-      </c>
       <c r="G159" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H159" t="n">
-        <v>-3.53</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>14.06</v>
+        <v>64.81</v>
       </c>
       <c r="C160" t="n">
-        <v>5.19582587</v>
+        <v>5.21244287</v>
       </c>
       <c r="D160" t="n">
-        <v>50.15</v>
+        <v>56.6</v>
       </c>
       <c r="E160" t="n">
-        <v>51.55</v>
+        <v>58.05</v>
       </c>
       <c r="F160" t="n">
-        <v>49.64</v>
+        <v>56.5</v>
       </c>
       <c r="G160" t="n">
-        <v>50.5</v>
+        <v>56.85</v>
       </c>
       <c r="H160" t="n">
-        <v>-2.88</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-21.2345</v>
+        <v>-172.75</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19370242</v>
+        <v>5.19516787</v>
       </c>
       <c r="D161" t="n">
-        <v>50</v>
+        <v>56.85</v>
       </c>
       <c r="E161" t="n">
-        <v>50.8</v>
+        <v>57.2</v>
       </c>
       <c r="F161" t="n">
-        <v>47.9</v>
+        <v>55</v>
       </c>
       <c r="G161" t="n">
-        <v>48.32</v>
+        <v>56</v>
       </c>
       <c r="H161" t="n">
-        <v>-4.32</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>47.7</v>
+        <v>-24.86</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19847242</v>
+        <v>5.19268187</v>
       </c>
       <c r="D162" t="n">
-        <v>48.98</v>
+        <v>55.75</v>
       </c>
       <c r="E162" t="n">
-        <v>49.94</v>
+        <v>55.8</v>
       </c>
       <c r="F162" t="n">
-        <v>48.18</v>
+        <v>53.7</v>
       </c>
       <c r="G162" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="H162" t="n">
-        <v>2.32</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>92.59999999999999</v>
+        <v>17.38</v>
       </c>
       <c r="C163" t="n">
-        <v>5.20773242</v>
+        <v>5.19441987</v>
       </c>
       <c r="D163" t="n">
-        <v>49.44</v>
+        <v>53.25</v>
       </c>
       <c r="E163" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="F163" t="n">
-        <v>46.74</v>
+        <v>51.75</v>
       </c>
       <c r="G163" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="H163" t="n">
-        <v>-4.13</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-95.51000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19818142</v>
+        <v>5.19582587</v>
       </c>
       <c r="D164" t="n">
-        <v>47</v>
+        <v>50.15</v>
       </c>
       <c r="E164" t="n">
-        <v>47</v>
+        <v>51.55</v>
       </c>
       <c r="F164" t="n">
-        <v>45.86</v>
+        <v>49.64</v>
       </c>
       <c r="G164" t="n">
-        <v>46.28</v>
+        <v>50.5</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.36</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-254.06</v>
+        <v>-21.2345</v>
       </c>
       <c r="C165" t="n">
-        <v>5.17277542</v>
+        <v>5.19370242</v>
       </c>
       <c r="D165" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="E165" t="n">
-        <v>47.18</v>
+        <v>50.8</v>
       </c>
       <c r="F165" t="n">
-        <v>45.76</v>
+        <v>47.9</v>
       </c>
       <c r="G165" t="n">
-        <v>45.9</v>
+        <v>48.32</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.82</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-316.19</v>
+        <v>47.7</v>
       </c>
       <c r="C166" t="n">
-        <v>5.14115642</v>
+        <v>5.19847242</v>
       </c>
       <c r="D166" t="n">
-        <v>45.9</v>
+        <v>48.98</v>
       </c>
       <c r="E166" t="n">
-        <v>46.78</v>
+        <v>49.94</v>
       </c>
       <c r="F166" t="n">
-        <v>45.26</v>
+        <v>48.18</v>
       </c>
       <c r="G166" t="n">
-        <v>46.08</v>
+        <v>49.44</v>
       </c>
       <c r="H166" t="n">
-        <v>0.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-150.87</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C167" t="n">
-        <v>5.12606942</v>
+        <v>5.20773242</v>
       </c>
       <c r="D167" t="n">
-        <v>47.7</v>
+        <v>49.44</v>
       </c>
       <c r="E167" t="n">
-        <v>48.9</v>
+        <v>49.44</v>
       </c>
       <c r="F167" t="n">
-        <v>46.64</v>
+        <v>46.74</v>
       </c>
       <c r="G167" t="n">
-        <v>46.84</v>
+        <v>47.4</v>
       </c>
       <c r="H167" t="n">
-        <v>1.65</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-236.76</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C168" t="n">
-        <v>5.10239342</v>
+        <v>5.19818142</v>
       </c>
       <c r="D168" t="n">
-        <v>46.92</v>
+        <v>47</v>
       </c>
       <c r="E168" t="n">
-        <v>48.28</v>
+        <v>47</v>
       </c>
       <c r="F168" t="n">
-        <v>46.84</v>
+        <v>45.86</v>
       </c>
       <c r="G168" t="n">
-        <v>47.36</v>
+        <v>46.28</v>
       </c>
       <c r="H168" t="n">
-        <v>1.11</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-36.92</v>
+        <v>-254.06</v>
       </c>
       <c r="C169" t="n">
-        <v>5.09870142</v>
+        <v>5.17277542</v>
       </c>
       <c r="D169" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="E169" t="n">
-        <v>47.56</v>
+        <v>47.18</v>
       </c>
       <c r="F169" t="n">
-        <v>45.72</v>
+        <v>45.76</v>
       </c>
       <c r="G169" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="H169" t="n">
-        <v>-2.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>64.78</v>
+        <v>-316.19</v>
       </c>
       <c r="C170" t="n">
-        <v>5.10517942</v>
+        <v>5.14115642</v>
       </c>
       <c r="D170" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="E170" t="n">
-        <v>48.42</v>
+        <v>46.78</v>
       </c>
       <c r="F170" t="n">
-        <v>46.26</v>
+        <v>45.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.6</v>
+        <v>46.08</v>
       </c>
       <c r="H170" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-44.41</v>
+        <v>-150.87</v>
       </c>
       <c r="C171" t="n">
-        <v>5.10073842</v>
+        <v>5.12606942</v>
       </c>
       <c r="D171" t="n">
-        <v>47.06</v>
+        <v>47.7</v>
       </c>
       <c r="E171" t="n">
-        <v>48.98</v>
+        <v>48.9</v>
       </c>
       <c r="F171" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="G171" t="n">
-        <v>48.52</v>
+        <v>46.84</v>
       </c>
       <c r="H171" t="n">
-        <v>4.12</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-124.97</v>
+        <v>-236.76</v>
       </c>
       <c r="C172" t="n">
-        <v>5.08824142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D172" t="n">
-        <v>47.6</v>
+        <v>46.92</v>
       </c>
       <c r="E172" t="n">
-        <v>48.08</v>
+        <v>48.28</v>
       </c>
       <c r="F172" t="n">
-        <v>46.72</v>
+        <v>46.84</v>
       </c>
       <c r="G172" t="n">
-        <v>46.76</v>
+        <v>47.36</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.63</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-272.6</v>
+        <v>-36.92</v>
       </c>
       <c r="C173" t="n">
-        <v>5.06098142</v>
+        <v>5.09870142</v>
       </c>
       <c r="D173" t="n">
-        <v>46.76</v>
+        <v>47</v>
       </c>
       <c r="E173" t="n">
-        <v>48.3</v>
+        <v>47.56</v>
       </c>
       <c r="F173" t="n">
-        <v>46.02</v>
+        <v>45.72</v>
       </c>
       <c r="G173" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="H173" t="n">
-        <v>1.41</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>83.54000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="C174" t="n">
-        <v>5.06933542</v>
+        <v>5.10517942</v>
       </c>
       <c r="D174" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="E174" t="n">
-        <v>47.92</v>
+        <v>48.42</v>
       </c>
       <c r="F174" t="n">
-        <v>46.46</v>
+        <v>46.26</v>
       </c>
       <c r="G174" t="n">
-        <v>47.2</v>
+        <v>46.6</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.46</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-232.94</v>
+        <v>-44.41</v>
       </c>
       <c r="C175" t="n">
-        <v>5.04604142</v>
+        <v>5.10073842</v>
       </c>
       <c r="D175" t="n">
-        <v>47.2</v>
+        <v>47.06</v>
       </c>
       <c r="E175" t="n">
-        <v>48.84</v>
+        <v>48.98</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.56</v>
+        <v>48.52</v>
       </c>
       <c r="H175" t="n">
-        <v>2.88</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-101.2265</v>
+        <v>-124.97</v>
       </c>
       <c r="C176" t="n">
-        <v>5.03591877</v>
+        <v>5.08824142</v>
       </c>
       <c r="D176" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="E176" t="n">
-        <v>49.46</v>
+        <v>48.08</v>
       </c>
       <c r="F176" t="n">
-        <v>48.24</v>
+        <v>46.72</v>
       </c>
       <c r="G176" t="n">
-        <v>48.78</v>
+        <v>46.76</v>
       </c>
       <c r="H176" t="n">
-        <v>0.45</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-146.01</v>
+        <v>-272.6</v>
       </c>
       <c r="C177" t="n">
-        <v>5.02131777</v>
+        <v>5.06098142</v>
       </c>
       <c r="D177" t="n">
-        <v>49.22</v>
+        <v>46.76</v>
       </c>
       <c r="E177" t="n">
-        <v>51</v>
+        <v>48.3</v>
       </c>
       <c r="F177" t="n">
-        <v>49.22</v>
+        <v>46.02</v>
       </c>
       <c r="G177" t="n">
-        <v>50.4</v>
+        <v>47.42</v>
       </c>
       <c r="H177" t="n">
-        <v>3.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>14.25</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>5.02274277</v>
+        <v>5.06933542</v>
       </c>
       <c r="D178" t="n">
-        <v>50.55</v>
+        <v>47.42</v>
       </c>
       <c r="E178" t="n">
-        <v>51</v>
+        <v>47.92</v>
       </c>
       <c r="F178" t="n">
-        <v>48.2</v>
+        <v>46.46</v>
       </c>
       <c r="G178" t="n">
-        <v>48.94</v>
+        <v>47.2</v>
       </c>
       <c r="H178" t="n">
-        <v>-2.9</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7.54</v>
+        <v>-232.94</v>
       </c>
       <c r="C179" t="n">
-        <v>5.02349677</v>
+        <v>5.04604142</v>
       </c>
       <c r="D179" t="n">
-        <v>49.96</v>
+        <v>47.2</v>
       </c>
       <c r="E179" t="n">
-        <v>49.98</v>
+        <v>48.84</v>
       </c>
       <c r="F179" t="n">
-        <v>48.72</v>
+        <v>46.7</v>
       </c>
       <c r="G179" t="n">
-        <v>49.12</v>
+        <v>48.56</v>
       </c>
       <c r="H179" t="n">
-        <v>0.37</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>29.93</v>
+        <v>-101.2265</v>
       </c>
       <c r="C180" t="n">
-        <v>5.02648977</v>
+        <v>5.03591877</v>
       </c>
       <c r="D180" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="E180" t="n">
-        <v>49.36</v>
+        <v>49.46</v>
       </c>
       <c r="F180" t="n">
-        <v>48.18</v>
+        <v>48.24</v>
       </c>
       <c r="G180" t="n">
-        <v>48.64</v>
+        <v>48.78</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.98</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-93.37</v>
+        <v>-146.01</v>
       </c>
       <c r="C181" t="n">
-        <v>5.01715277</v>
+        <v>5.02131777</v>
       </c>
       <c r="D181" t="n">
-        <v>48.4</v>
+        <v>49.22</v>
       </c>
       <c r="E181" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F181" t="n">
-        <v>47.2</v>
+        <v>49.22</v>
       </c>
       <c r="G181" t="n">
-        <v>47.64</v>
+        <v>50.4</v>
       </c>
       <c r="H181" t="n">
-        <v>-2.06</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-93.65000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C182" t="n">
-        <v>5.00778777</v>
+        <v>5.02274277</v>
       </c>
       <c r="D182" t="n">
-        <v>47.64</v>
+        <v>50.55</v>
       </c>
       <c r="E182" t="n">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="F182" t="n">
-        <v>47.22</v>
+        <v>48.2</v>
       </c>
       <c r="G182" t="n">
-        <v>48.96</v>
+        <v>48.94</v>
       </c>
       <c r="H182" t="n">
-        <v>2.77</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>28.06</v>
+        <v>7.54</v>
       </c>
       <c r="C183" t="n">
-        <v>5.01059377</v>
+        <v>5.02349677</v>
       </c>
       <c r="D183" t="n">
-        <v>48.36</v>
+        <v>49.96</v>
       </c>
       <c r="E183" t="n">
-        <v>48.76</v>
+        <v>49.98</v>
       </c>
       <c r="F183" t="n">
-        <v>47.52</v>
+        <v>48.72</v>
       </c>
       <c r="G183" t="n">
-        <v>47.98</v>
+        <v>49.12</v>
       </c>
       <c r="H183" t="n">
-        <v>-2</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-160.94</v>
+        <v>29.93</v>
       </c>
       <c r="C184" t="n">
-        <v>4.99449977</v>
+        <v>5.02648977</v>
       </c>
       <c r="D184" t="n">
-        <v>47.98</v>
+        <v>49.1</v>
       </c>
       <c r="E184" t="n">
-        <v>48.46</v>
+        <v>49.36</v>
       </c>
       <c r="F184" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="G184" t="n">
-        <v>48.08</v>
+        <v>48.64</v>
       </c>
       <c r="H184" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>76.84999999999999</v>
+        <v>-93.37</v>
       </c>
       <c r="C185" t="n">
-        <v>5.00218477</v>
+        <v>5.01715277</v>
       </c>
       <c r="D185" t="n">
-        <v>49.54</v>
+        <v>48.4</v>
       </c>
       <c r="E185" t="n">
-        <v>50.5</v>
+        <v>48.4</v>
       </c>
       <c r="F185" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="G185" t="n">
-        <v>49.68</v>
+        <v>47.64</v>
       </c>
       <c r="H185" t="n">
-        <v>3.33</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-70.88</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C186" t="n">
-        <v>4.99509677</v>
+        <v>5.00778777</v>
       </c>
       <c r="D186" t="n">
-        <v>51.9</v>
+        <v>47.64</v>
       </c>
       <c r="E186" t="n">
-        <v>55.6</v>
+        <v>49.3</v>
       </c>
       <c r="F186" t="n">
-        <v>51.9</v>
+        <v>47.22</v>
       </c>
       <c r="G186" t="n">
-        <v>54.6</v>
+        <v>48.96</v>
       </c>
       <c r="H186" t="n">
-        <v>9.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-223.97</v>
+        <v>28.06</v>
       </c>
       <c r="C187" t="n">
-        <v>4.97269977</v>
+        <v>5.01059377</v>
       </c>
       <c r="D187" t="n">
-        <v>54.7</v>
+        <v>48.36</v>
       </c>
       <c r="E187" t="n">
-        <v>56.1</v>
+        <v>48.76</v>
       </c>
       <c r="F187" t="n">
-        <v>53.7</v>
+        <v>47.52</v>
       </c>
       <c r="G187" t="n">
-        <v>54.25</v>
+        <v>47.98</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.64</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-908.88</v>
+        <v>-160.94</v>
       </c>
       <c r="C188" t="n">
-        <v>4.88181177</v>
+        <v>4.99449977</v>
       </c>
       <c r="D188" t="n">
-        <v>52.85</v>
+        <v>47.98</v>
       </c>
       <c r="E188" t="n">
-        <v>53.8</v>
+        <v>48.46</v>
       </c>
       <c r="F188" t="n">
-        <v>51.3</v>
+        <v>47.32</v>
       </c>
       <c r="G188" t="n">
-        <v>53.4</v>
+        <v>48.08</v>
       </c>
       <c r="H188" t="n">
-        <v>-1.57</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-219</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C189" t="n">
-        <v>4.85991177</v>
+        <v>5.00218477</v>
       </c>
       <c r="D189" t="n">
-        <v>52.75</v>
+        <v>49.54</v>
       </c>
       <c r="E189" t="n">
-        <v>54.45</v>
+        <v>50.5</v>
       </c>
       <c r="F189" t="n">
-        <v>51.45</v>
+        <v>48.9</v>
       </c>
       <c r="G189" t="n">
-        <v>51.85</v>
+        <v>49.68</v>
       </c>
       <c r="H189" t="n">
-        <v>-2.9</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>81.19</v>
+        <v>-70.88</v>
       </c>
       <c r="C190" t="n">
-        <v>4.86803077</v>
+        <v>4.99509677</v>
       </c>
       <c r="D190" t="n">
-        <v>51.85</v>
+        <v>51.9</v>
       </c>
       <c r="E190" t="n">
-        <v>51.85</v>
+        <v>55.6</v>
       </c>
       <c r="F190" t="n">
-        <v>49.6</v>
+        <v>51.9</v>
       </c>
       <c r="G190" t="n">
-        <v>50.45</v>
+        <v>54.6</v>
       </c>
       <c r="H190" t="n">
-        <v>-2.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7.21</v>
+        <v>-223.97</v>
       </c>
       <c r="C191" t="n">
-        <v>4.86875177</v>
+        <v>4.97269977</v>
       </c>
       <c r="D191" t="n">
-        <v>50.05</v>
+        <v>54.7</v>
       </c>
       <c r="E191" t="n">
-        <v>50.8</v>
+        <v>56.1</v>
       </c>
       <c r="F191" t="n">
-        <v>49.52</v>
+        <v>53.7</v>
       </c>
       <c r="G191" t="n">
-        <v>50.65</v>
+        <v>54.25</v>
       </c>
       <c r="H191" t="n">
-        <v>0.4</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>144.28</v>
+        <v>-908.88</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88317977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D192" t="n">
-        <v>50</v>
+        <v>52.85</v>
       </c>
       <c r="E192" t="n">
-        <v>50.6</v>
+        <v>53.8</v>
       </c>
       <c r="F192" t="n">
-        <v>49.08</v>
+        <v>51.3</v>
       </c>
       <c r="G192" t="n">
-        <v>49.12</v>
+        <v>53.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-3.02</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-41.02</v>
+        <v>-219</v>
       </c>
       <c r="C193" t="n">
-        <v>4.87907777</v>
+        <v>4.85991177</v>
       </c>
       <c r="D193" t="n">
-        <v>49.18</v>
+        <v>52.75</v>
       </c>
       <c r="E193" t="n">
-        <v>50.1</v>
+        <v>54.45</v>
       </c>
       <c r="F193" t="n">
-        <v>48.82</v>
+        <v>51.45</v>
       </c>
       <c r="G193" t="n">
-        <v>49.92</v>
+        <v>51.85</v>
       </c>
       <c r="H193" t="n">
-        <v>1.63</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>68.70999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="C194" t="n">
-        <v>4.88594877</v>
+        <v>4.86803077</v>
       </c>
       <c r="D194" t="n">
-        <v>50.5</v>
+        <v>51.85</v>
       </c>
       <c r="E194" t="n">
-        <v>50.95</v>
+        <v>51.85</v>
       </c>
       <c r="F194" t="n">
-        <v>49.74</v>
+        <v>49.6</v>
       </c>
       <c r="G194" t="n">
-        <v>50.1</v>
+        <v>50.45</v>
       </c>
       <c r="H194" t="n">
-        <v>0.36</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>20.01</v>
+        <v>7.21</v>
       </c>
       <c r="C195" t="n">
-        <v>4.88794977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D195" t="n">
-        <v>50</v>
+        <v>50.05</v>
       </c>
       <c r="E195" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F195" t="n">
-        <v>49.04</v>
+        <v>49.52</v>
       </c>
       <c r="G195" t="n">
-        <v>49.06</v>
+        <v>50.65</v>
       </c>
       <c r="H195" t="n">
-        <v>-2.08</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-18.77</v>
+        <v>144.28</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88607277</v>
+        <v>4.88317977</v>
       </c>
       <c r="D196" t="n">
+        <v>50</v>
+      </c>
+      <c r="E196" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="F196" t="n">
         <v>49.08</v>
       </c>
-      <c r="E196" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="F196" t="n">
-        <v>48.7</v>
-      </c>
       <c r="G196" t="n">
-        <v>49.4</v>
+        <v>49.12</v>
       </c>
       <c r="H196" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>95.14</v>
+        <v>-41.02</v>
       </c>
       <c r="C197" t="n">
-        <v>4.89558677</v>
+        <v>4.87907777</v>
       </c>
       <c r="D197" t="n">
-        <v>48.66</v>
+        <v>49.18</v>
       </c>
       <c r="E197" t="n">
-        <v>49.22</v>
+        <v>50.1</v>
       </c>
       <c r="F197" t="n">
-        <v>48.02</v>
+        <v>48.82</v>
       </c>
       <c r="G197" t="n">
-        <v>48.22</v>
+        <v>49.92</v>
       </c>
       <c r="H197" t="n">
-        <v>-2.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>6.47</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C198" t="n">
-        <v>4.89623377</v>
+        <v>4.88594877</v>
       </c>
       <c r="D198" t="n">
-        <v>48.22</v>
+        <v>50.5</v>
       </c>
       <c r="E198" t="n">
-        <v>48.22</v>
+        <v>50.95</v>
       </c>
       <c r="F198" t="n">
-        <v>47.46</v>
+        <v>49.74</v>
       </c>
       <c r="G198" t="n">
-        <v>47.46</v>
+        <v>50.1</v>
       </c>
       <c r="H198" t="n">
-        <v>-1.58</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>78.34</v>
+        <v>20.01</v>
       </c>
       <c r="C199" t="n">
-        <v>4.90406777</v>
+        <v>4.88794977</v>
       </c>
       <c r="D199" t="n">
-        <v>47.86</v>
+        <v>50</v>
       </c>
       <c r="E199" t="n">
-        <v>48.68</v>
+        <v>50.5</v>
       </c>
       <c r="F199" t="n">
-        <v>47.7</v>
+        <v>49.04</v>
       </c>
       <c r="G199" t="n">
-        <v>48.48</v>
+        <v>49.06</v>
       </c>
       <c r="H199" t="n">
-        <v>2.15</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>12.2</v>
+        <v>-18.77</v>
       </c>
       <c r="C200" t="n">
-        <v>4.90528777</v>
+        <v>4.88607277</v>
       </c>
       <c r="D200" t="n">
-        <v>48.1</v>
+        <v>49.08</v>
       </c>
       <c r="E200" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="F200" t="n">
         <v>48.7</v>
       </c>
-      <c r="F200" t="n">
-        <v>47.38</v>
-      </c>
       <c r="G200" t="n">
-        <v>47.88</v>
+        <v>49.4</v>
       </c>
       <c r="H200" t="n">
-        <v>-1.24</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-50.42</v>
+        <v>95.14</v>
       </c>
       <c r="C201" t="n">
-        <v>4.90024577</v>
+        <v>4.89558677</v>
       </c>
       <c r="D201" t="n">
-        <v>47.34</v>
+        <v>48.66</v>
       </c>
       <c r="E201" t="n">
-        <v>48.28</v>
+        <v>49.22</v>
       </c>
       <c r="F201" t="n">
-        <v>47.06</v>
+        <v>48.02</v>
       </c>
       <c r="G201" t="n">
-        <v>47.9</v>
+        <v>48.22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.04</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7.38</v>
+        <v>6.47</v>
       </c>
       <c r="C202" t="n">
-        <v>4.90098377</v>
+        <v>4.89623377</v>
       </c>
       <c r="D202" t="n">
-        <v>49.98</v>
+        <v>48.22</v>
       </c>
       <c r="E202" t="n">
-        <v>51.2</v>
+        <v>48.22</v>
       </c>
       <c r="F202" t="n">
-        <v>49.76</v>
+        <v>47.46</v>
       </c>
       <c r="G202" t="n">
-        <v>50.55</v>
+        <v>47.46</v>
       </c>
       <c r="H202" t="n">
-        <v>5.53</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.19</v>
+        <v>78.34</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90100277</v>
+        <v>4.90406777</v>
       </c>
       <c r="D203" t="n">
-        <v>50.55</v>
+        <v>47.86</v>
       </c>
       <c r="E203" t="n">
-        <v>51.8</v>
+        <v>48.68</v>
       </c>
       <c r="F203" t="n">
-        <v>50.5</v>
+        <v>47.7</v>
       </c>
       <c r="G203" t="n">
-        <v>51.2</v>
+        <v>48.48</v>
       </c>
       <c r="H203" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-404.07</v>
+        <v>12.2</v>
       </c>
       <c r="C204" t="n">
-        <v>4.86059577</v>
+        <v>4.90528777</v>
       </c>
       <c r="D204" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="E204" t="n">
-        <v>51</v>
+        <v>48.7</v>
       </c>
       <c r="F204" t="n">
-        <v>49.3</v>
+        <v>47.38</v>
       </c>
       <c r="G204" t="n">
-        <v>49.46</v>
+        <v>47.88</v>
       </c>
       <c r="H204" t="n">
-        <v>-3.4</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-104.42</v>
+        <v>-50.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.85015377</v>
+        <v>4.90024577</v>
       </c>
       <c r="D205" t="n">
-        <v>48.86</v>
+        <v>47.34</v>
       </c>
       <c r="E205" t="n">
-        <v>49.74</v>
+        <v>48.28</v>
       </c>
       <c r="F205" t="n">
-        <v>47.6</v>
+        <v>47.06</v>
       </c>
       <c r="G205" t="n">
-        <v>47.68</v>
+        <v>47.9</v>
       </c>
       <c r="H205" t="n">
-        <v>-3.6</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-9.27</v>
+        <v>7.38</v>
       </c>
       <c r="C206" t="n">
-        <v>4.84922677</v>
+        <v>4.90098377</v>
       </c>
       <c r="D206" t="n">
-        <v>47.68</v>
+        <v>49.98</v>
       </c>
       <c r="E206" t="n">
-        <v>48.9</v>
+        <v>51.2</v>
       </c>
       <c r="F206" t="n">
-        <v>47.32</v>
+        <v>49.76</v>
       </c>
       <c r="G206" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="H206" t="n">
-        <v>0.88</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-62.41</v>
+        <v>0.19</v>
       </c>
       <c r="C207" t="n">
-        <v>4.84298577</v>
+        <v>4.90100277</v>
       </c>
       <c r="D207" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="E207" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="F207" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="G207" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="H207" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-4.06</v>
+        <v>-404.07</v>
       </c>
       <c r="C208" t="n">
-        <v>4.84257977</v>
+        <v>4.86059577</v>
       </c>
       <c r="D208" t="n">
-        <v>47.8</v>
+        <v>50.3</v>
       </c>
       <c r="E208" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="F208" t="n">
-        <v>47.16</v>
+        <v>49.3</v>
       </c>
       <c r="G208" t="n">
-        <v>47.98</v>
+        <v>49.46</v>
       </c>
       <c r="H208" t="n">
-        <v>-1.28</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>107.65</v>
+        <v>-104.42</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85334477</v>
+        <v>4.85015377</v>
       </c>
       <c r="D209" t="n">
-        <v>47.86</v>
+        <v>48.86</v>
       </c>
       <c r="E209" t="n">
-        <v>48.44</v>
+        <v>49.74</v>
       </c>
       <c r="F209" t="n">
-        <v>46.5</v>
+        <v>47.6</v>
       </c>
       <c r="G209" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.33</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>137.46</v>
+        <v>-9.27</v>
       </c>
       <c r="C210" t="n">
-        <v>4.86709077</v>
+        <v>4.84922677</v>
       </c>
       <c r="D210" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="E210" t="n">
-        <v>48.22</v>
+        <v>48.9</v>
       </c>
       <c r="F210" t="n">
-        <v>46.6</v>
+        <v>47.32</v>
       </c>
       <c r="G210" t="n">
-        <v>47.06</v>
+        <v>48.1</v>
       </c>
       <c r="H210" t="n">
-        <v>-1.59</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>154.04</v>
+        <v>-62.41</v>
       </c>
       <c r="C211" t="n">
-        <v>4.88249477</v>
+        <v>4.84298577</v>
       </c>
       <c r="D211" t="n">
-        <v>46.68</v>
+        <v>48.1</v>
       </c>
       <c r="E211" t="n">
-        <v>46.76</v>
+        <v>49</v>
       </c>
       <c r="F211" t="n">
-        <v>44.56</v>
+        <v>47.5</v>
       </c>
       <c r="G211" t="n">
-        <v>45.86</v>
+        <v>48.6</v>
       </c>
       <c r="H211" t="n">
-        <v>-2.55</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>78.03</v>
+        <v>-4.06</v>
       </c>
       <c r="C212" t="n">
-        <v>4.89029777</v>
+        <v>4.84257977</v>
       </c>
       <c r="D212" t="n">
-        <v>46.56</v>
+        <v>47.8</v>
       </c>
       <c r="E212" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="F212" t="n">
-        <v>46.2</v>
+        <v>47.16</v>
       </c>
       <c r="G212" t="n">
-        <v>46.38</v>
+        <v>47.98</v>
       </c>
       <c r="H212" t="n">
-        <v>1.13</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>401.67</v>
+        <v>107.65</v>
       </c>
       <c r="C213" t="n">
-        <v>4.93046477</v>
+        <v>4.85334477</v>
       </c>
       <c r="D213" t="n">
-        <v>48.14</v>
+        <v>47.86</v>
       </c>
       <c r="E213" t="n">
-        <v>48.88</v>
+        <v>48.44</v>
       </c>
       <c r="F213" t="n">
-        <v>47.12</v>
+        <v>46.5</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>3.1</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-79.33</v>
+        <v>137.46</v>
       </c>
       <c r="C214" t="n">
-        <v>4.92253177</v>
+        <v>4.86709077</v>
       </c>
       <c r="D214" t="n">
-        <v>48.1</v>
+        <v>47.82</v>
       </c>
       <c r="E214" t="n">
-        <v>50.45</v>
+        <v>48.22</v>
       </c>
       <c r="F214" t="n">
-        <v>48.04</v>
+        <v>46.6</v>
       </c>
       <c r="G214" t="n">
-        <v>50.4</v>
+        <v>47.06</v>
       </c>
       <c r="H214" t="n">
-        <v>5.4</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-415.48</v>
+        <v>154.04</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88098377</v>
+        <v>4.88249477</v>
       </c>
       <c r="D215" t="n">
-        <v>49.44</v>
+        <v>46.68</v>
       </c>
       <c r="E215" t="n">
-        <v>50.15</v>
+        <v>46.76</v>
       </c>
       <c r="F215" t="n">
-        <v>48.88</v>
+        <v>44.56</v>
       </c>
       <c r="G215" t="n">
-        <v>49.32</v>
+        <v>45.86</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.14</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-394.96</v>
+        <v>78.03</v>
       </c>
       <c r="C216" t="n">
-        <v>4.84148777</v>
+        <v>4.89029777</v>
       </c>
       <c r="D216" t="n">
-        <v>49.08</v>
+        <v>46.56</v>
       </c>
       <c r="E216" t="n">
-        <v>49.08</v>
+        <v>48</v>
       </c>
       <c r="F216" t="n">
-        <v>47.2</v>
+        <v>46.2</v>
       </c>
       <c r="G216" t="n">
-        <v>47.62</v>
+        <v>46.38</v>
       </c>
       <c r="H216" t="n">
-        <v>-3.45</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-39.23</v>
+        <v>401.67</v>
       </c>
       <c r="C217" t="n">
-        <v>4.83756477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.2</v>
+        <v>48.14</v>
       </c>
       <c r="E217" t="n">
-        <v>47.2</v>
+        <v>48.88</v>
       </c>
       <c r="F217" t="n">
-        <v>46.42</v>
+        <v>47.12</v>
       </c>
       <c r="G217" t="n">
-        <v>46.48</v>
+        <v>47.82</v>
       </c>
       <c r="H217" t="n">
-        <v>-2.39</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>219.67</v>
+        <v>-79.33</v>
       </c>
       <c r="C218" t="n">
-        <v>4.85953177</v>
+        <v>4.92253177</v>
       </c>
       <c r="D218" t="n">
-        <v>45.74</v>
+        <v>48.1</v>
       </c>
       <c r="E218" t="n">
-        <v>46.44</v>
+        <v>50.45</v>
       </c>
       <c r="F218" t="n">
-        <v>45.38</v>
+        <v>48.04</v>
       </c>
       <c r="G218" t="n">
-        <v>46.34</v>
+        <v>50.4</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>111.68</v>
+        <v>-415.48</v>
       </c>
       <c r="C219" t="n">
-        <v>4.87069977</v>
+        <v>4.88098377</v>
       </c>
       <c r="D219" t="n">
-        <v>45.9</v>
+        <v>49.44</v>
       </c>
       <c r="E219" t="n">
-        <v>47.8</v>
+        <v>50.15</v>
       </c>
       <c r="F219" t="n">
-        <v>45.84</v>
+        <v>48.88</v>
       </c>
       <c r="G219" t="n">
-        <v>47.52</v>
+        <v>49.32</v>
       </c>
       <c r="H219" t="n">
-        <v>2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>47.5</v>
+        <v>-394.96</v>
       </c>
       <c r="C220" t="n">
-        <v>4.87544977</v>
+        <v>4.84148777</v>
       </c>
       <c r="D220" t="n">
-        <v>47.52</v>
+        <v>49.08</v>
       </c>
       <c r="E220" t="n">
-        <v>48.06</v>
+        <v>49.08</v>
       </c>
       <c r="F220" t="n">
-        <v>46.06</v>
+        <v>47.2</v>
       </c>
       <c r="G220" t="n">
-        <v>46.12</v>
+        <v>47.62</v>
       </c>
       <c r="H220" t="n">
-        <v>-2.95</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-30.32</v>
+        <v>-39.23</v>
       </c>
       <c r="C221" t="n">
-        <v>4.87241777</v>
+        <v>4.83756477</v>
       </c>
       <c r="D221" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E221" t="n">
-        <v>47.42</v>
+        <v>47.2</v>
       </c>
       <c r="F221" t="n">
-        <v>45.94</v>
+        <v>46.42</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>0.78</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>219.67</v>
+      </c>
+      <c r="C222" t="n">
+        <v>4.85953177</v>
+      </c>
+      <c r="D222" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="E222" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="F222" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="G222" t="n">
+        <v>46.34</v>
+      </c>
+      <c r="H222" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>111.68</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4.87069977</v>
+      </c>
+      <c r="D223" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="E223" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F223" t="n">
+        <v>45.84</v>
+      </c>
+      <c r="G223" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="H223" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4.87544977</v>
+      </c>
+      <c r="D224" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="E224" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="F224" t="n">
+        <v>46.06</v>
+      </c>
+      <c r="G224" t="n">
+        <v>46.12</v>
+      </c>
+      <c r="H224" t="n">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-30.32</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.87241777</v>
+      </c>
+      <c r="D225" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="E225" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F225" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="G225" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="B222" t="n">
+      <c r="B226" t="n">
         <v>15.46</v>
       </c>
-      <c r="C222" t="n">
+      <c r="C226" t="n">
         <v>4.87396377</v>
       </c>
-      <c r="D222" t="n">
+      <c r="D226" t="n">
         <v>46.9</v>
       </c>
-      <c r="E222" t="n">
+      <c r="E226" t="n">
         <v>47.5</v>
       </c>
-      <c r="F222" t="n">
+      <c r="F226" t="n">
         <v>44.94</v>
       </c>
-      <c r="G222" t="n">
+      <c r="G226" t="n">
         <v>46.88</v>
       </c>
-      <c r="H222" t="n">
+      <c r="H226" t="n">
         <v>0.86</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6768,6 +6768,34 @@
         <v>0.86</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4.87396377</v>
+      </c>
+      <c r="D227" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="E227" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="F227" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G227" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E79" t="n">
-        <v>73.34999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="F79" t="n">
-        <v>71.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>73.34999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="F80" t="n">
-        <v>71.5</v>
+        <v>69.55</v>
       </c>
       <c r="G80" t="n">
-        <v>72.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4106 +2693,3994 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>72.8</v>
+        <v>70.3</v>
       </c>
       <c r="E81" t="n">
-        <v>73.34999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="F81" t="n">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="G81" t="n">
-        <v>72.3</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>-37.37</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D82" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E82" t="n">
-        <v>72.25</v>
+        <v>73.5</v>
       </c>
       <c r="F82" t="n">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G82" t="n">
-        <v>72.09999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.28</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D83" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E83" t="n">
-        <v>71.75</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>69.55</v>
+        <v>70.5</v>
       </c>
       <c r="G83" t="n">
-        <v>70.09999999999999</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>-2.77</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>39.15</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29754581</v>
+        <v>5.29772381</v>
       </c>
       <c r="D84" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="E84" t="n">
-        <v>73.3</v>
+        <v>71.8</v>
       </c>
       <c r="F84" t="n">
-        <v>70.3</v>
+        <v>68.55</v>
       </c>
       <c r="G84" t="n">
-        <v>72.84999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>3.92</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-37.37</v>
+        <v>-32.03</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29380881</v>
+        <v>5.29452081</v>
       </c>
       <c r="D85" t="n">
-        <v>71.8</v>
+        <v>69.5</v>
       </c>
       <c r="E85" t="n">
-        <v>73.5</v>
+        <v>69.5</v>
       </c>
       <c r="F85" t="n">
-        <v>71.3</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>71.75</v>
+        <v>68.75</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.51</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-245.51</v>
       </c>
       <c r="C86" t="n">
-        <v>5.29380881</v>
+        <v>5.26996981</v>
       </c>
       <c r="D86" t="n">
-        <v>72.8</v>
+        <v>67.75</v>
       </c>
       <c r="E86" t="n">
-        <v>73.15000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>70.5</v>
+        <v>67</v>
       </c>
       <c r="G86" t="n">
-        <v>71.84999999999999</v>
+        <v>68</v>
       </c>
       <c r="H86" t="n">
-        <v>0.14</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39.15</v>
+        <v>24.99</v>
       </c>
       <c r="C87" t="n">
-        <v>5.29772381</v>
+        <v>5.27246881</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
       <c r="F87" t="n">
-        <v>68.55</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>68.65000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="H87" t="n">
-        <v>-4.45</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-32.03</v>
+        <v>-70.5937</v>
       </c>
       <c r="C88" t="n">
-        <v>5.29452081</v>
+        <v>5.26540944</v>
       </c>
       <c r="D88" t="n">
-        <v>69.5</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>69.5</v>
+        <v>66.8</v>
       </c>
       <c r="F88" t="n">
-        <v>68.15000000000001</v>
+        <v>64.45</v>
       </c>
       <c r="G88" t="n">
-        <v>68.75</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-245.51</v>
+        <v>-83.42</v>
       </c>
       <c r="C89" t="n">
-        <v>5.26996981</v>
+        <v>5.25706744</v>
       </c>
       <c r="D89" t="n">
-        <v>67.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>70.15000000000001</v>
+        <v>68</v>
       </c>
       <c r="F89" t="n">
-        <v>67</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>68</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.09</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24.99</v>
+        <v>32.9872</v>
       </c>
       <c r="C90" t="n">
-        <v>5.27246881</v>
+        <v>5.26036616</v>
       </c>
       <c r="D90" t="n">
-        <v>68.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="E90" t="n">
-        <v>69</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>65.65000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>66.55</v>
+        <v>67.45</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.13</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-70.5937</v>
+        <v>-168.98</v>
       </c>
       <c r="C91" t="n">
-        <v>5.26540944</v>
+        <v>5.24346816</v>
       </c>
       <c r="D91" t="n">
-        <v>65.84999999999999</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>66.8</v>
+        <v>69</v>
       </c>
       <c r="F91" t="n">
-        <v>64.45</v>
+        <v>64.7</v>
       </c>
       <c r="G91" t="n">
-        <v>65.84999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-83.42</v>
+        <v>-195.54</v>
       </c>
       <c r="C92" t="n">
-        <v>5.25706744</v>
+        <v>5.22391416</v>
       </c>
       <c r="D92" t="n">
-        <v>66.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>68</v>
+        <v>70.2</v>
       </c>
       <c r="F92" t="n">
-        <v>65.09999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="G92" t="n">
-        <v>65.59999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.38</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>32.9872</v>
+        <v>16.18</v>
       </c>
       <c r="C93" t="n">
-        <v>5.26036616</v>
+        <v>5.22553216</v>
       </c>
       <c r="D93" t="n">
-        <v>65.5</v>
+        <v>69.25</v>
       </c>
       <c r="E93" t="n">
-        <v>67.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.34999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="G93" t="n">
-        <v>67.45</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>2.82</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-168.98</v>
+        <v>13.87</v>
       </c>
       <c r="C94" t="n">
-        <v>5.24346816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D94" t="n">
-        <v>64.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E94" t="n">
-        <v>69</v>
+        <v>71.3</v>
       </c>
       <c r="F94" t="n">
-        <v>64.7</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>68.90000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>2.15</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-195.54</v>
+        <v>-145.08</v>
       </c>
       <c r="C95" t="n">
-        <v>5.22391416</v>
+        <v>5.21241116</v>
       </c>
       <c r="D95" t="n">
-        <v>69.90000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E95" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="F95" t="n">
-        <v>67.95</v>
+        <v>67.3</v>
       </c>
       <c r="G95" t="n">
-        <v>69.05</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.22</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>16.18</v>
+        <v>25.02</v>
       </c>
       <c r="C96" t="n">
-        <v>5.22553216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D96" t="n">
-        <v>69.25</v>
+        <v>67.5</v>
       </c>
       <c r="E96" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>69.05</v>
+        <v>66.3</v>
       </c>
       <c r="G96" t="n">
-        <v>69.84999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>1.16</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.87</v>
+        <v>-6.25</v>
       </c>
       <c r="C97" t="n">
-        <v>5.22691916</v>
+        <v>5.21428816</v>
       </c>
       <c r="D97" t="n">
-        <v>70.95</v>
+        <v>71.25</v>
       </c>
       <c r="E97" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="G97" t="n">
         <v>71.3</v>
       </c>
-      <c r="F97" t="n">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="G97" t="n">
-        <v>70.15000000000001</v>
-      </c>
       <c r="H97" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-145.08</v>
+        <v>-48.58</v>
       </c>
       <c r="C98" t="n">
-        <v>5.21241116</v>
+        <v>5.20943016</v>
       </c>
       <c r="D98" t="n">
-        <v>68.95</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>69</v>
+        <v>71.25</v>
       </c>
       <c r="F98" t="n">
-        <v>67.3</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>67.90000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>-3.21</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25.02</v>
+        <v>-197.18</v>
       </c>
       <c r="C99" t="n">
-        <v>5.21491316</v>
+        <v>5.18971216</v>
       </c>
       <c r="D99" t="n">
-        <v>67.5</v>
+        <v>66.2</v>
       </c>
       <c r="E99" t="n">
-        <v>70.09999999999999</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>66.3</v>
+        <v>65.8</v>
       </c>
       <c r="G99" t="n">
-        <v>69.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="H99" t="n">
-        <v>2.95</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-6.25</v>
+        <v>426.64</v>
       </c>
       <c r="C100" t="n">
-        <v>5.21428816</v>
+        <v>5.23237616</v>
       </c>
       <c r="D100" t="n">
-        <v>71.25</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>73.3</v>
+        <v>68.7</v>
       </c>
       <c r="F100" t="n">
-        <v>70.84999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>71.3</v>
+        <v>66.8</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-48.58</v>
+        <v>41.4993</v>
       </c>
       <c r="C101" t="n">
-        <v>5.20943016</v>
+        <v>5.23652609</v>
       </c>
       <c r="D101" t="n">
-        <v>70.65000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>71.25</v>
+        <v>66.05</v>
       </c>
       <c r="F101" t="n">
-        <v>66.34999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G101" t="n">
-        <v>66.84999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-6.24</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-197.18</v>
+        <v>-220.5688</v>
       </c>
       <c r="C102" t="n">
-        <v>5.18971216</v>
+        <v>5.21446921</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.34999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F102" t="n">
-        <v>65.8</v>
+        <v>63.45</v>
       </c>
       <c r="G102" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>426.64</v>
+        <v>215.27</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23237616</v>
+        <v>5.23599621</v>
       </c>
       <c r="D103" t="n">
-        <v>67</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>68.7</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>66.34999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="G103" t="n">
-        <v>66.8</v>
+        <v>70.45</v>
       </c>
       <c r="H103" t="n">
-        <v>1.21</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>41.4993</v>
+        <v>-160.53</v>
       </c>
       <c r="C104" t="n">
-        <v>5.23652609</v>
+        <v>5.21994321</v>
       </c>
       <c r="D104" t="n">
-        <v>65.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>66.05</v>
+        <v>70.8</v>
       </c>
       <c r="F104" t="n">
-        <v>64.2</v>
+        <v>68.7</v>
       </c>
       <c r="G104" t="n">
-        <v>64.8</v>
+        <v>69</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.99</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-220.5688</v>
+        <v>-304.01</v>
       </c>
       <c r="C105" t="n">
-        <v>5.21446921</v>
+        <v>5.18954221</v>
       </c>
       <c r="D105" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="E105" t="n">
-        <v>67.65000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F105" t="n">
-        <v>63.45</v>
+        <v>68.3</v>
       </c>
       <c r="G105" t="n">
-        <v>67.59999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H105" t="n">
-        <v>4.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>215.27</v>
+        <v>-30.3</v>
       </c>
       <c r="C106" t="n">
-        <v>5.23599621</v>
+        <v>5.18651221</v>
       </c>
       <c r="D106" t="n">
-        <v>69.59999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="E106" t="n">
-        <v>71.34999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>69.45</v>
+        <v>68</v>
       </c>
       <c r="G106" t="n">
-        <v>70.45</v>
+        <v>68.8</v>
       </c>
       <c r="H106" t="n">
-        <v>4.22</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-160.53</v>
+        <v>-92.3</v>
       </c>
       <c r="C107" t="n">
-        <v>5.21994321</v>
+        <v>5.17728221</v>
       </c>
       <c r="D107" t="n">
-        <v>69.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E107" t="n">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
       <c r="G107" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.06</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-304.01</v>
+        <v>25.43</v>
       </c>
       <c r="C108" t="n">
-        <v>5.18954221</v>
+        <v>5.17982521</v>
       </c>
       <c r="D108" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>71.5</v>
+        <v>71.45</v>
       </c>
       <c r="F108" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>70.05</v>
+        <v>71.2</v>
       </c>
       <c r="H108" t="n">
-        <v>1.52</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-30.3</v>
+        <v>136.53</v>
       </c>
       <c r="C109" t="n">
-        <v>5.18651221</v>
+        <v>5.19347821</v>
       </c>
       <c r="D109" t="n">
-        <v>68.05</v>
+        <v>71.2</v>
       </c>
       <c r="E109" t="n">
-        <v>69.34999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G109" t="n">
-        <v>68.8</v>
+        <v>71.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-92.3</v>
+        <v>-224.29</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17728221</v>
+        <v>5.17104921</v>
       </c>
       <c r="D110" t="n">
-        <v>68.8</v>
+        <v>73.45</v>
       </c>
       <c r="E110" t="n">
-        <v>69.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="F110" t="n">
-        <v>67.2</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>67.7</v>
+        <v>73.3</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.6</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>25.43</v>
+        <v>97.7422</v>
       </c>
       <c r="C111" t="n">
-        <v>5.17982521</v>
+        <v>5.18082343</v>
       </c>
       <c r="D111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="E111" t="n">
-        <v>71.45</v>
+        <v>73.5</v>
       </c>
       <c r="F111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G111" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>5.17</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>136.53</v>
+        <v>-116.85</v>
       </c>
       <c r="C112" t="n">
-        <v>5.19347821</v>
+        <v>5.16913843</v>
       </c>
       <c r="D112" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E112" t="n">
-        <v>73.40000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="F112" t="n">
-        <v>70</v>
+        <v>71.55</v>
       </c>
       <c r="G112" t="n">
-        <v>71.8</v>
+        <v>74.2</v>
       </c>
       <c r="H112" t="n">
-        <v>0.84</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-224.29</v>
+        <v>32.76</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17104921</v>
+        <v>5.17241443</v>
       </c>
       <c r="D113" t="n">
-        <v>73.45</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F113" t="n">
-        <v>71.65000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="G113" t="n">
-        <v>73.3</v>
+        <v>73.7</v>
       </c>
       <c r="H113" t="n">
-        <v>2.09</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>97.7422</v>
+        <v>-19.6</v>
       </c>
       <c r="C114" t="n">
-        <v>5.18082343</v>
+        <v>5.17045443</v>
       </c>
       <c r="D114" t="n">
-        <v>71.95</v>
+        <v>73.7</v>
       </c>
       <c r="E114" t="n">
-        <v>73.5</v>
+        <v>73.95</v>
       </c>
       <c r="F114" t="n">
-        <v>71.75</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.91</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-116.85</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>5.16913843</v>
+        <v>5.17787843</v>
       </c>
       <c r="D115" t="n">
-        <v>71.90000000000001</v>
+        <v>73.75</v>
       </c>
       <c r="E115" t="n">
-        <v>76.45</v>
+        <v>73.75</v>
       </c>
       <c r="F115" t="n">
-        <v>71.55</v>
+        <v>70.5</v>
       </c>
       <c r="G115" t="n">
-        <v>74.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>3.2</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>32.76</v>
+        <v>15.04</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17241443</v>
+        <v>5.17938243</v>
       </c>
       <c r="D116" t="n">
-        <v>74.09999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E116" t="n">
-        <v>75</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>73.25</v>
+        <v>70.95</v>
       </c>
       <c r="G116" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.67</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-19.6</v>
+        <v>213.47</v>
       </c>
       <c r="C117" t="n">
-        <v>5.17045443</v>
+        <v>5.20072943</v>
       </c>
       <c r="D117" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>73.95</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>71.65000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>73</v>
+        <v>71.45</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.95</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>74.23999999999999</v>
+        <v>-167.67</v>
       </c>
       <c r="C118" t="n">
-        <v>5.17787843</v>
+        <v>5.18396243</v>
       </c>
       <c r="D118" t="n">
-        <v>73.75</v>
+        <v>72</v>
       </c>
       <c r="E118" t="n">
-        <v>73.75</v>
+        <v>73.45</v>
       </c>
       <c r="F118" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>70.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.88</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15.04</v>
+        <v>-78.5919</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17938243</v>
+        <v>5.17610324</v>
       </c>
       <c r="D119" t="n">
-        <v>70.95</v>
+        <v>73.3</v>
       </c>
       <c r="E119" t="n">
-        <v>72.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F119" t="n">
-        <v>70.95</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H119" t="n">
-        <v>0.99</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>213.47</v>
+        <v>-54.57</v>
       </c>
       <c r="C120" t="n">
-        <v>5.20072943</v>
+        <v>5.17064624</v>
       </c>
       <c r="D120" t="n">
-        <v>71.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E120" t="n">
-        <v>71.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>70.40000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G120" t="n">
-        <v>71.45</v>
+        <v>73.45</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-167.67</v>
+        <v>32.9</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18396243</v>
+        <v>5.17393624</v>
       </c>
       <c r="D121" t="n">
-        <v>72</v>
+        <v>73.45</v>
       </c>
       <c r="E121" t="n">
-        <v>73.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>70.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G121" t="n">
-        <v>73.3</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>2.59</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-78.5919</v>
+        <v>41.93</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17610324</v>
+        <v>5.17812924</v>
       </c>
       <c r="D122" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="E122" t="n">
-        <v>73.3</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>71.84999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G122" t="n">
-        <v>73.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.14</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-54.57</v>
+        <v>52.87</v>
       </c>
       <c r="C123" t="n">
-        <v>5.17064624</v>
+        <v>5.18341624</v>
       </c>
       <c r="D123" t="n">
-        <v>72.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>73.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="F123" t="n">
-        <v>71.95</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>73.45</v>
+        <v>69.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0.34</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>32.9</v>
+        <v>291.58</v>
       </c>
       <c r="C124" t="n">
-        <v>5.17393624</v>
+        <v>5.21257424</v>
       </c>
       <c r="D124" t="n">
-        <v>73.45</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>74.40000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F124" t="n">
-        <v>71.75</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>73.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.41</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>41.93</v>
+        <v>-60.7601</v>
       </c>
       <c r="C125" t="n">
-        <v>5.17812924</v>
+        <v>5.20649823</v>
       </c>
       <c r="D125" t="n">
-        <v>73</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E125" t="n">
-        <v>73.65000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="F125" t="n">
-        <v>68.7</v>
+        <v>68.45</v>
       </c>
       <c r="G125" t="n">
-        <v>69.90000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="H125" t="n">
-        <v>-4.44</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>52.87</v>
+        <v>264.89</v>
       </c>
       <c r="C126" t="n">
-        <v>5.18341624</v>
+        <v>5.23298723</v>
       </c>
       <c r="D126" t="n">
-        <v>70.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>70.5</v>
+        <v>69.75</v>
       </c>
       <c r="F126" t="n">
-        <v>68.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="G126" t="n">
-        <v>69.7</v>
+        <v>67.55</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.29</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>291.58</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>5.21257424</v>
+        <v>5.23298723</v>
       </c>
       <c r="D127" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="E127" t="n">
-        <v>69.45</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>66.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G127" t="n">
-        <v>67</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>-3.87</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-60.7601</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>5.20649823</v>
+        <v>5.23298723</v>
       </c>
       <c r="D128" t="n">
-        <v>69.40000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="E128" t="n">
-        <v>70.25</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>68.45</v>
+        <v>68.2</v>
       </c>
       <c r="G128" t="n">
-        <v>69.25</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>3.36</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>264.89</v>
+        <v>-369.37</v>
       </c>
       <c r="C129" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D129" t="n">
-        <v>68.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E129" t="n">
-        <v>69.75</v>
+        <v>69.5</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.55</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.45</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D130" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="E130" t="n">
-        <v>69.75</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="G130" t="n">
-        <v>67.55</v>
+        <v>69.95</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>68.9663</v>
       </c>
       <c r="C131" t="n">
-        <v>5.23298723</v>
+        <v>5.20294686</v>
       </c>
       <c r="D131" t="n">
-        <v>69</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>71.15000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F131" t="n">
-        <v>68.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>70.15000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="H131" t="n">
-        <v>3.85</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>-247.41</v>
       </c>
       <c r="C132" t="n">
-        <v>5.23298723</v>
+        <v>5.17820586</v>
       </c>
       <c r="D132" t="n">
-        <v>69.25</v>
+        <v>69.5</v>
       </c>
       <c r="E132" t="n">
-        <v>70.09999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>68.2</v>
+        <v>69.45</v>
       </c>
       <c r="G132" t="n">
-        <v>69.65000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.71</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-369.37</v>
+        <v>27.55</v>
       </c>
       <c r="C133" t="n">
-        <v>5.19605023</v>
+        <v>5.18096086</v>
       </c>
       <c r="D133" t="n">
-        <v>69.5</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E133" t="n">
-        <v>69.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>67.3</v>
+        <v>73.05</v>
       </c>
       <c r="G133" t="n">
-        <v>67.84999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>-2.58</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>-286.2</v>
       </c>
       <c r="C134" t="n">
-        <v>5.19605023</v>
+        <v>5.15234086</v>
       </c>
       <c r="D134" t="n">
-        <v>68.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>70.34999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>68.5</v>
+        <v>73.05</v>
       </c>
       <c r="G134" t="n">
-        <v>69.95</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>3.1</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>68.9663</v>
+        <v>48.88</v>
       </c>
       <c r="C135" t="n">
-        <v>5.20294686</v>
+        <v>5.15722886</v>
       </c>
       <c r="D135" t="n">
-        <v>68.34999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="E135" t="n">
-        <v>70.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>68.34999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>70.05</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H135" t="n">
-        <v>0.14</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-247.41</v>
+        <v>-55.96</v>
       </c>
       <c r="C136" t="n">
-        <v>5.17820586</v>
+        <v>5.15163286</v>
       </c>
       <c r="D136" t="n">
-        <v>69.5</v>
+        <v>75.05</v>
       </c>
       <c r="E136" t="n">
-        <v>74.15000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>69.45</v>
+        <v>74.25</v>
       </c>
       <c r="G136" t="n">
-        <v>73.84999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>5.42</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>27.55</v>
+        <v>-385.85</v>
       </c>
       <c r="C137" t="n">
-        <v>5.18096086</v>
+        <v>5.11304786</v>
       </c>
       <c r="D137" t="n">
-        <v>73.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>75.15000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>73.05</v>
+        <v>64.5</v>
       </c>
       <c r="G137" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.61</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-286.2</v>
+        <v>139.59</v>
       </c>
       <c r="C138" t="n">
-        <v>5.15234086</v>
+        <v>5.12700686</v>
       </c>
       <c r="D138" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>74.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>73.05</v>
+        <v>61.75</v>
       </c>
       <c r="G138" t="n">
-        <v>73.65000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.34</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>48.88</v>
+        <v>1468.42</v>
       </c>
       <c r="C139" t="n">
-        <v>5.15722886</v>
+        <v>5.27384886</v>
       </c>
       <c r="D139" t="n">
-        <v>76.8</v>
+        <v>62.6</v>
       </c>
       <c r="E139" t="n">
-        <v>78.90000000000001</v>
+        <v>63.35</v>
       </c>
       <c r="F139" t="n">
-        <v>75.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="G139" t="n">
-        <v>76.84999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="H139" t="n">
-        <v>4.34</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-55.96</v>
+        <v>292.93</v>
       </c>
       <c r="C140" t="n">
-        <v>5.15163286</v>
+        <v>5.30314186</v>
       </c>
       <c r="D140" t="n">
-        <v>75.05</v>
+        <v>62.5</v>
       </c>
       <c r="E140" t="n">
-        <v>75.90000000000001</v>
+        <v>63.85</v>
       </c>
       <c r="F140" t="n">
-        <v>74.25</v>
+        <v>61.55</v>
       </c>
       <c r="G140" t="n">
-        <v>75.59999999999999</v>
+        <v>62.25</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.63</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-385.85</v>
+        <v>17.9</v>
       </c>
       <c r="C141" t="n">
-        <v>5.11304786</v>
+        <v>5.30493186</v>
       </c>
       <c r="D141" t="n">
-        <v>72.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="E141" t="n">
-        <v>72.40000000000001</v>
+        <v>64.95</v>
       </c>
       <c r="F141" t="n">
-        <v>64.5</v>
+        <v>61.35</v>
       </c>
       <c r="G141" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-14.15</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>139.59</v>
+        <v>-224.88</v>
       </c>
       <c r="C142" t="n">
-        <v>5.12700686</v>
+        <v>5.28244386</v>
       </c>
       <c r="D142" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="E142" t="n">
-        <v>64.90000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="F142" t="n">
-        <v>61.75</v>
+        <v>60.4</v>
       </c>
       <c r="G142" t="n">
-        <v>62.1</v>
+        <v>62.15</v>
       </c>
       <c r="H142" t="n">
-        <v>-4.31</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1468.42</v>
+        <v>-244.5</v>
       </c>
       <c r="C143" t="n">
-        <v>5.27384886</v>
+        <v>5.25799386</v>
       </c>
       <c r="D143" t="n">
-        <v>62.6</v>
+        <v>61.9</v>
       </c>
       <c r="E143" t="n">
-        <v>63.35</v>
+        <v>62.35</v>
       </c>
       <c r="F143" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="G143" t="n">
-        <v>61.6</v>
+        <v>60.2</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>292.93</v>
+        <v>-302.48</v>
       </c>
       <c r="C144" t="n">
-        <v>5.30314186</v>
+        <v>5.22774586</v>
       </c>
       <c r="D144" t="n">
-        <v>62.5</v>
+        <v>60.1</v>
       </c>
       <c r="E144" t="n">
-        <v>63.85</v>
+        <v>61</v>
       </c>
       <c r="F144" t="n">
-        <v>61.55</v>
+        <v>58.6</v>
       </c>
       <c r="G144" t="n">
-        <v>62.25</v>
+        <v>60.45</v>
       </c>
       <c r="H144" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>17.9</v>
+        <v>-177.8636</v>
       </c>
       <c r="C145" t="n">
-        <v>5.30493186</v>
+        <v>5.2099595</v>
       </c>
       <c r="D145" t="n">
-        <v>63.2</v>
+        <v>60</v>
       </c>
       <c r="E145" t="n">
-        <v>64.95</v>
+        <v>60.05</v>
       </c>
       <c r="F145" t="n">
-        <v>61.35</v>
+        <v>55.7</v>
       </c>
       <c r="G145" t="n">
-        <v>61.8</v>
+        <v>57.85</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.72</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-224.88</v>
+        <v>-228.55</v>
       </c>
       <c r="C146" t="n">
-        <v>5.28244386</v>
+        <v>5.1871045</v>
       </c>
       <c r="D146" t="n">
-        <v>61.8</v>
+        <v>56.95</v>
       </c>
       <c r="E146" t="n">
-        <v>62.25</v>
+        <v>59.1</v>
       </c>
       <c r="F146" t="n">
-        <v>60.4</v>
+        <v>56</v>
       </c>
       <c r="G146" t="n">
-        <v>62.15</v>
+        <v>58.55</v>
       </c>
       <c r="H146" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-244.5</v>
+        <v>423.9973</v>
       </c>
       <c r="C147" t="n">
-        <v>5.25799386</v>
+        <v>5.22950423</v>
       </c>
       <c r="D147" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="E147" t="n">
+        <v>62</v>
+      </c>
+      <c r="F147" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G147" t="n">
         <v>61.9</v>
       </c>
-      <c r="E147" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="F147" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G147" t="n">
-        <v>60.2</v>
-      </c>
       <c r="H147" t="n">
-        <v>-3.14</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-302.48</v>
+        <v>-119.16</v>
       </c>
       <c r="C148" t="n">
-        <v>5.22774586</v>
+        <v>5.21758823</v>
       </c>
       <c r="D148" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="E148" t="n">
-        <v>61</v>
+        <v>60.75</v>
       </c>
       <c r="F148" t="n">
-        <v>58.6</v>
+        <v>58.75</v>
       </c>
       <c r="G148" t="n">
-        <v>60.45</v>
+        <v>59.1</v>
       </c>
       <c r="H148" t="n">
-        <v>0.42</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-177.8636</v>
+        <v>-301.92</v>
       </c>
       <c r="C149" t="n">
-        <v>5.2099595</v>
+        <v>5.18739623</v>
       </c>
       <c r="D149" t="n">
-        <v>60</v>
+        <v>58.95</v>
       </c>
       <c r="E149" t="n">
-        <v>60.05</v>
+        <v>58.95</v>
       </c>
       <c r="F149" t="n">
-        <v>55.7</v>
+        <v>56.85</v>
       </c>
       <c r="G149" t="n">
-        <v>57.85</v>
+        <v>57.25</v>
       </c>
       <c r="H149" t="n">
-        <v>-4.3</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-228.55</v>
+        <v>112.29</v>
       </c>
       <c r="C150" t="n">
-        <v>5.1871045</v>
+        <v>5.19862523</v>
       </c>
       <c r="D150" t="n">
-        <v>56.95</v>
+        <v>57.1</v>
       </c>
       <c r="E150" t="n">
-        <v>59.1</v>
+        <v>57.6</v>
       </c>
       <c r="F150" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G150" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="H150" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>423.9973</v>
+        <v>-62.4836</v>
       </c>
       <c r="C151" t="n">
-        <v>5.22950423</v>
+        <v>5.19237687</v>
       </c>
       <c r="D151" t="n">
-        <v>57.05</v>
+        <v>55.3</v>
       </c>
       <c r="E151" t="n">
-        <v>62</v>
+        <v>57.9</v>
       </c>
       <c r="F151" t="n">
-        <v>56.55</v>
+        <v>54.95</v>
       </c>
       <c r="G151" t="n">
-        <v>61.9</v>
+        <v>57.35</v>
       </c>
       <c r="H151" t="n">
-        <v>5.72</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-119.16</v>
+        <v>-29.35</v>
       </c>
       <c r="C152" t="n">
-        <v>5.21758823</v>
+        <v>5.18944187</v>
       </c>
       <c r="D152" t="n">
-        <v>60.5</v>
+        <v>56.2</v>
       </c>
       <c r="E152" t="n">
-        <v>60.75</v>
+        <v>57.1</v>
       </c>
       <c r="F152" t="n">
-        <v>58.75</v>
+        <v>55.8</v>
       </c>
       <c r="G152" t="n">
-        <v>59.1</v>
+        <v>55.85</v>
       </c>
       <c r="H152" t="n">
-        <v>-4.52</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-301.92</v>
+        <v>54.46</v>
       </c>
       <c r="C153" t="n">
-        <v>5.18739623</v>
+        <v>5.19488787</v>
       </c>
       <c r="D153" t="n">
-        <v>58.95</v>
+        <v>55.3</v>
       </c>
       <c r="E153" t="n">
-        <v>58.95</v>
+        <v>55.55</v>
       </c>
       <c r="F153" t="n">
-        <v>56.85</v>
+        <v>53.25</v>
       </c>
       <c r="G153" t="n">
-        <v>57.25</v>
+        <v>54.7</v>
       </c>
       <c r="H153" t="n">
-        <v>-3.13</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>112.29</v>
+        <v>17.32</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19862523</v>
+        <v>5.19661987</v>
       </c>
       <c r="D154" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E154" t="n">
-        <v>57.6</v>
+        <v>54.1</v>
       </c>
       <c r="F154" t="n">
-        <v>56.5</v>
+        <v>52.25</v>
       </c>
       <c r="G154" t="n">
-        <v>56.65</v>
+        <v>53.15</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.05</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-62.4836</v>
+        <v>93.42</v>
       </c>
       <c r="C155" t="n">
-        <v>5.19237687</v>
+        <v>5.20596187</v>
       </c>
       <c r="D155" t="n">
-        <v>55.3</v>
+        <v>53.7</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>54.95</v>
+        <v>53.25</v>
       </c>
       <c r="G155" t="n">
-        <v>57.35</v>
+        <v>57</v>
       </c>
       <c r="H155" t="n">
-        <v>1.24</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-29.35</v>
+        <v>64.81</v>
       </c>
       <c r="C156" t="n">
-        <v>5.18944187</v>
+        <v>5.21244287</v>
       </c>
       <c r="D156" t="n">
-        <v>56.2</v>
+        <v>56.6</v>
       </c>
       <c r="E156" t="n">
-        <v>57.1</v>
+        <v>58.05</v>
       </c>
       <c r="F156" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="G156" t="n">
-        <v>55.85</v>
+        <v>56.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.62</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>54.46</v>
+        <v>-172.75</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19488787</v>
+        <v>5.19516787</v>
       </c>
       <c r="D157" t="n">
-        <v>55.3</v>
+        <v>56.85</v>
       </c>
       <c r="E157" t="n">
-        <v>55.55</v>
+        <v>57.2</v>
       </c>
       <c r="F157" t="n">
-        <v>53.25</v>
+        <v>55</v>
       </c>
       <c r="G157" t="n">
-        <v>54.7</v>
+        <v>56</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.06</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>17.32</v>
+        <v>-24.86</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19661987</v>
+        <v>5.19268187</v>
       </c>
       <c r="D158" t="n">
-        <v>54</v>
+        <v>55.75</v>
       </c>
       <c r="E158" t="n">
-        <v>54.1</v>
+        <v>55.8</v>
       </c>
       <c r="F158" t="n">
-        <v>52.25</v>
+        <v>53.7</v>
       </c>
       <c r="G158" t="n">
-        <v>53.15</v>
+        <v>53.9</v>
       </c>
       <c r="H158" t="n">
-        <v>-2.83</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>93.42</v>
+        <v>17.38</v>
       </c>
       <c r="C159" t="n">
-        <v>5.20596187</v>
+        <v>5.19441987</v>
       </c>
       <c r="D159" t="n">
-        <v>53.7</v>
+        <v>53.25</v>
       </c>
       <c r="E159" t="n">
-        <v>57.9</v>
+        <v>53.9</v>
       </c>
       <c r="F159" t="n">
-        <v>53.25</v>
+        <v>51.75</v>
       </c>
       <c r="G159" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H159" t="n">
-        <v>7.24</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>64.81</v>
+        <v>14.06</v>
       </c>
       <c r="C160" t="n">
-        <v>5.21244287</v>
+        <v>5.19582587</v>
       </c>
       <c r="D160" t="n">
-        <v>56.6</v>
+        <v>50.15</v>
       </c>
       <c r="E160" t="n">
-        <v>58.05</v>
+        <v>51.55</v>
       </c>
       <c r="F160" t="n">
-        <v>56.5</v>
+        <v>49.64</v>
       </c>
       <c r="G160" t="n">
-        <v>56.85</v>
+        <v>50.5</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.26</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-172.75</v>
+        <v>-21.2345</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19516787</v>
+        <v>5.19370242</v>
       </c>
       <c r="D161" t="n">
-        <v>56.85</v>
+        <v>50</v>
       </c>
       <c r="E161" t="n">
-        <v>57.2</v>
+        <v>50.8</v>
       </c>
       <c r="F161" t="n">
-        <v>55</v>
+        <v>47.9</v>
       </c>
       <c r="G161" t="n">
-        <v>56</v>
+        <v>48.32</v>
       </c>
       <c r="H161" t="n">
-        <v>-1.5</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-24.86</v>
+        <v>47.7</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19268187</v>
+        <v>5.19847242</v>
       </c>
       <c r="D162" t="n">
-        <v>55.75</v>
+        <v>48.98</v>
       </c>
       <c r="E162" t="n">
-        <v>55.8</v>
+        <v>49.94</v>
       </c>
       <c r="F162" t="n">
-        <v>53.7</v>
+        <v>48.18</v>
       </c>
       <c r="G162" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="H162" t="n">
-        <v>-3.75</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>17.38</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C163" t="n">
-        <v>5.19441987</v>
+        <v>5.20773242</v>
       </c>
       <c r="D163" t="n">
-        <v>53.25</v>
+        <v>49.44</v>
       </c>
       <c r="E163" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="F163" t="n">
-        <v>51.75</v>
+        <v>46.74</v>
       </c>
       <c r="G163" t="n">
-        <v>52</v>
+        <v>47.4</v>
       </c>
       <c r="H163" t="n">
-        <v>-3.53</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>14.06</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19582587</v>
+        <v>5.19818142</v>
       </c>
       <c r="D164" t="n">
-        <v>50.15</v>
+        <v>47</v>
       </c>
       <c r="E164" t="n">
-        <v>51.55</v>
+        <v>47</v>
       </c>
       <c r="F164" t="n">
-        <v>49.64</v>
+        <v>45.86</v>
       </c>
       <c r="G164" t="n">
-        <v>50.5</v>
+        <v>46.28</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.88</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-21.2345</v>
+        <v>-254.06</v>
       </c>
       <c r="C165" t="n">
-        <v>5.19370242</v>
+        <v>5.17277542</v>
       </c>
       <c r="D165" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="E165" t="n">
-        <v>50.8</v>
+        <v>47.18</v>
       </c>
       <c r="F165" t="n">
-        <v>47.9</v>
+        <v>45.76</v>
       </c>
       <c r="G165" t="n">
-        <v>48.32</v>
+        <v>45.9</v>
       </c>
       <c r="H165" t="n">
-        <v>-4.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>47.7</v>
+        <v>-316.19</v>
       </c>
       <c r="C166" t="n">
-        <v>5.19847242</v>
+        <v>5.14115642</v>
       </c>
       <c r="D166" t="n">
-        <v>48.98</v>
+        <v>45.9</v>
       </c>
       <c r="E166" t="n">
-        <v>49.94</v>
+        <v>46.78</v>
       </c>
       <c r="F166" t="n">
-        <v>48.18</v>
+        <v>45.26</v>
       </c>
       <c r="G166" t="n">
-        <v>49.44</v>
+        <v>46.08</v>
       </c>
       <c r="H166" t="n">
-        <v>2.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>92.59999999999999</v>
+        <v>-150.87</v>
       </c>
       <c r="C167" t="n">
-        <v>5.20773242</v>
+        <v>5.12606942</v>
       </c>
       <c r="D167" t="n">
-        <v>49.44</v>
+        <v>47.7</v>
       </c>
       <c r="E167" t="n">
-        <v>49.44</v>
+        <v>48.9</v>
       </c>
       <c r="F167" t="n">
-        <v>46.74</v>
+        <v>46.64</v>
       </c>
       <c r="G167" t="n">
-        <v>47.4</v>
+        <v>46.84</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.13</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-95.51000000000001</v>
+        <v>-236.76</v>
       </c>
       <c r="C168" t="n">
-        <v>5.19818142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D168" t="n">
-        <v>47</v>
+        <v>46.92</v>
       </c>
       <c r="E168" t="n">
-        <v>47</v>
+        <v>48.28</v>
       </c>
       <c r="F168" t="n">
-        <v>45.86</v>
+        <v>46.84</v>
       </c>
       <c r="G168" t="n">
-        <v>46.28</v>
+        <v>47.36</v>
       </c>
       <c r="H168" t="n">
-        <v>-2.36</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-254.06</v>
+        <v>-36.92</v>
       </c>
       <c r="C169" t="n">
-        <v>5.17277542</v>
+        <v>5.09870142</v>
       </c>
       <c r="D169" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E169" t="n">
-        <v>47.18</v>
+        <v>47.56</v>
       </c>
       <c r="F169" t="n">
-        <v>45.76</v>
+        <v>45.72</v>
       </c>
       <c r="G169" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.82</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-316.19</v>
+        <v>64.78</v>
       </c>
       <c r="C170" t="n">
-        <v>5.14115642</v>
+        <v>5.10517942</v>
       </c>
       <c r="D170" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="E170" t="n">
-        <v>46.78</v>
+        <v>48.42</v>
       </c>
       <c r="F170" t="n">
-        <v>45.26</v>
+        <v>46.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.08</v>
+        <v>46.6</v>
       </c>
       <c r="H170" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-150.87</v>
+        <v>-44.41</v>
       </c>
       <c r="C171" t="n">
-        <v>5.12606942</v>
+        <v>5.10073842</v>
       </c>
       <c r="D171" t="n">
-        <v>47.7</v>
+        <v>47.06</v>
       </c>
       <c r="E171" t="n">
-        <v>48.9</v>
+        <v>48.98</v>
       </c>
       <c r="F171" t="n">
-        <v>46.64</v>
+        <v>46.7</v>
       </c>
       <c r="G171" t="n">
-        <v>46.84</v>
+        <v>48.52</v>
       </c>
       <c r="H171" t="n">
-        <v>1.65</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-236.76</v>
+        <v>-124.97</v>
       </c>
       <c r="C172" t="n">
-        <v>5.10239342</v>
+        <v>5.08824142</v>
       </c>
       <c r="D172" t="n">
-        <v>46.92</v>
+        <v>47.6</v>
       </c>
       <c r="E172" t="n">
-        <v>48.28</v>
+        <v>48.08</v>
       </c>
       <c r="F172" t="n">
-        <v>46.84</v>
+        <v>46.72</v>
       </c>
       <c r="G172" t="n">
-        <v>47.36</v>
+        <v>46.76</v>
       </c>
       <c r="H172" t="n">
-        <v>1.11</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-36.92</v>
+        <v>-272.6</v>
       </c>
       <c r="C173" t="n">
-        <v>5.09870142</v>
+        <v>5.06098142</v>
       </c>
       <c r="D173" t="n">
-        <v>47</v>
+        <v>46.76</v>
       </c>
       <c r="E173" t="n">
-        <v>47.56</v>
+        <v>48.3</v>
       </c>
       <c r="F173" t="n">
-        <v>45.72</v>
+        <v>46.02</v>
       </c>
       <c r="G173" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="H173" t="n">
-        <v>-2.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>64.78</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C174" t="n">
-        <v>5.10517942</v>
+        <v>5.06933542</v>
       </c>
       <c r="D174" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="E174" t="n">
-        <v>48.42</v>
+        <v>47.92</v>
       </c>
       <c r="F174" t="n">
-        <v>46.26</v>
+        <v>46.46</v>
       </c>
       <c r="G174" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="H174" t="n">
-        <v>0.73</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-44.41</v>
+        <v>-232.94</v>
       </c>
       <c r="C175" t="n">
-        <v>5.10073842</v>
+        <v>5.04604142</v>
       </c>
       <c r="D175" t="n">
-        <v>47.06</v>
+        <v>47.2</v>
       </c>
       <c r="E175" t="n">
-        <v>48.98</v>
+        <v>48.84</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.52</v>
+        <v>48.56</v>
       </c>
       <c r="H175" t="n">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-124.97</v>
+        <v>-101.2265</v>
       </c>
       <c r="C176" t="n">
-        <v>5.08824142</v>
+        <v>5.03591877</v>
       </c>
       <c r="D176" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="E176" t="n">
-        <v>48.08</v>
+        <v>49.46</v>
       </c>
       <c r="F176" t="n">
-        <v>46.72</v>
+        <v>48.24</v>
       </c>
       <c r="G176" t="n">
-        <v>46.76</v>
+        <v>48.78</v>
       </c>
       <c r="H176" t="n">
-        <v>-3.63</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-272.6</v>
+        <v>-146.01</v>
       </c>
       <c r="C177" t="n">
-        <v>5.06098142</v>
+        <v>5.02131777</v>
       </c>
       <c r="D177" t="n">
-        <v>46.76</v>
+        <v>49.22</v>
       </c>
       <c r="E177" t="n">
-        <v>48.3</v>
+        <v>51</v>
       </c>
       <c r="F177" t="n">
-        <v>46.02</v>
+        <v>49.22</v>
       </c>
       <c r="G177" t="n">
-        <v>47.42</v>
+        <v>50.4</v>
       </c>
       <c r="H177" t="n">
-        <v>1.41</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>83.54000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C178" t="n">
-        <v>5.06933542</v>
+        <v>5.02274277</v>
       </c>
       <c r="D178" t="n">
-        <v>47.42</v>
+        <v>50.55</v>
       </c>
       <c r="E178" t="n">
-        <v>47.92</v>
+        <v>51</v>
       </c>
       <c r="F178" t="n">
-        <v>46.46</v>
+        <v>48.2</v>
       </c>
       <c r="G178" t="n">
-        <v>47.2</v>
+        <v>48.94</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.46</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-232.94</v>
+        <v>7.54</v>
       </c>
       <c r="C179" t="n">
-        <v>5.04604142</v>
+        <v>5.02349677</v>
       </c>
       <c r="D179" t="n">
-        <v>47.2</v>
+        <v>49.96</v>
       </c>
       <c r="E179" t="n">
-        <v>48.84</v>
+        <v>49.98</v>
       </c>
       <c r="F179" t="n">
-        <v>46.7</v>
+        <v>48.72</v>
       </c>
       <c r="G179" t="n">
-        <v>48.56</v>
+        <v>49.12</v>
       </c>
       <c r="H179" t="n">
-        <v>2.88</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-101.2265</v>
+        <v>29.93</v>
       </c>
       <c r="C180" t="n">
-        <v>5.03591877</v>
+        <v>5.02648977</v>
       </c>
       <c r="D180" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="E180" t="n">
-        <v>49.46</v>
+        <v>49.36</v>
       </c>
       <c r="F180" t="n">
-        <v>48.24</v>
+        <v>48.18</v>
       </c>
       <c r="G180" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="H180" t="n">
-        <v>0.45</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-146.01</v>
+        <v>-93.37</v>
       </c>
       <c r="C181" t="n">
-        <v>5.02131777</v>
+        <v>5.01715277</v>
       </c>
       <c r="D181" t="n">
-        <v>49.22</v>
+        <v>48.4</v>
       </c>
       <c r="E181" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
       <c r="F181" t="n">
-        <v>49.22</v>
+        <v>47.2</v>
       </c>
       <c r="G181" t="n">
-        <v>50.4</v>
+        <v>47.64</v>
       </c>
       <c r="H181" t="n">
-        <v>3.32</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>14.25</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C182" t="n">
-        <v>5.02274277</v>
+        <v>5.00778777</v>
       </c>
       <c r="D182" t="n">
-        <v>50.55</v>
+        <v>47.64</v>
       </c>
       <c r="E182" t="n">
-        <v>51</v>
+        <v>49.3</v>
       </c>
       <c r="F182" t="n">
-        <v>48.2</v>
+        <v>47.22</v>
       </c>
       <c r="G182" t="n">
-        <v>48.94</v>
+        <v>48.96</v>
       </c>
       <c r="H182" t="n">
-        <v>-2.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7.54</v>
+        <v>28.06</v>
       </c>
       <c r="C183" t="n">
-        <v>5.02349677</v>
+        <v>5.01059377</v>
       </c>
       <c r="D183" t="n">
-        <v>49.96</v>
+        <v>48.36</v>
       </c>
       <c r="E183" t="n">
-        <v>49.98</v>
+        <v>48.76</v>
       </c>
       <c r="F183" t="n">
-        <v>48.72</v>
+        <v>47.52</v>
       </c>
       <c r="G183" t="n">
-        <v>49.12</v>
+        <v>47.98</v>
       </c>
       <c r="H183" t="n">
-        <v>0.37</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>29.93</v>
+        <v>-160.94</v>
       </c>
       <c r="C184" t="n">
-        <v>5.02648977</v>
+        <v>4.99449977</v>
       </c>
       <c r="D184" t="n">
-        <v>49.1</v>
+        <v>47.98</v>
       </c>
       <c r="E184" t="n">
-        <v>49.36</v>
+        <v>48.46</v>
       </c>
       <c r="F184" t="n">
-        <v>48.18</v>
+        <v>47.32</v>
       </c>
       <c r="G184" t="n">
-        <v>48.64</v>
+        <v>48.08</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.98</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-93.37</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C185" t="n">
-        <v>5.01715277</v>
+        <v>5.00218477</v>
       </c>
       <c r="D185" t="n">
-        <v>48.4</v>
+        <v>49.54</v>
       </c>
       <c r="E185" t="n">
-        <v>48.4</v>
+        <v>50.5</v>
       </c>
       <c r="F185" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="G185" t="n">
-        <v>47.64</v>
+        <v>49.68</v>
       </c>
       <c r="H185" t="n">
-        <v>-2.06</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-93.65000000000001</v>
+        <v>-70.88</v>
       </c>
       <c r="C186" t="n">
-        <v>5.00778777</v>
+        <v>4.99509677</v>
       </c>
       <c r="D186" t="n">
-        <v>47.64</v>
+        <v>51.9</v>
       </c>
       <c r="E186" t="n">
-        <v>49.3</v>
+        <v>55.6</v>
       </c>
       <c r="F186" t="n">
-        <v>47.22</v>
+        <v>51.9</v>
       </c>
       <c r="G186" t="n">
-        <v>48.96</v>
+        <v>54.6</v>
       </c>
       <c r="H186" t="n">
-        <v>2.77</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>28.06</v>
+        <v>-223.97</v>
       </c>
       <c r="C187" t="n">
-        <v>5.01059377</v>
+        <v>4.97269977</v>
       </c>
       <c r="D187" t="n">
-        <v>48.36</v>
+        <v>54.7</v>
       </c>
       <c r="E187" t="n">
-        <v>48.76</v>
+        <v>56.1</v>
       </c>
       <c r="F187" t="n">
-        <v>47.52</v>
+        <v>53.7</v>
       </c>
       <c r="G187" t="n">
-        <v>47.98</v>
+        <v>54.25</v>
       </c>
       <c r="H187" t="n">
-        <v>-2</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-160.94</v>
+        <v>-908.88</v>
       </c>
       <c r="C188" t="n">
-        <v>4.99449977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D188" t="n">
-        <v>47.98</v>
+        <v>52.85</v>
       </c>
       <c r="E188" t="n">
-        <v>48.46</v>
+        <v>53.8</v>
       </c>
       <c r="F188" t="n">
-        <v>47.32</v>
+        <v>51.3</v>
       </c>
       <c r="G188" t="n">
-        <v>48.08</v>
+        <v>53.4</v>
       </c>
       <c r="H188" t="n">
-        <v>0.21</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>76.84999999999999</v>
+        <v>-219</v>
       </c>
       <c r="C189" t="n">
-        <v>5.00218477</v>
+        <v>4.85991177</v>
       </c>
       <c r="D189" t="n">
-        <v>49.54</v>
+        <v>52.75</v>
       </c>
       <c r="E189" t="n">
-        <v>50.5</v>
+        <v>54.45</v>
       </c>
       <c r="F189" t="n">
-        <v>48.9</v>
+        <v>51.45</v>
       </c>
       <c r="G189" t="n">
-        <v>49.68</v>
+        <v>51.85</v>
       </c>
       <c r="H189" t="n">
-        <v>3.33</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>-70.88</v>
+        <v>81.19</v>
       </c>
       <c r="C190" t="n">
-        <v>4.99509677</v>
+        <v>4.86803077</v>
       </c>
       <c r="D190" t="n">
-        <v>51.9</v>
+        <v>51.85</v>
       </c>
       <c r="E190" t="n">
-        <v>55.6</v>
+        <v>51.85</v>
       </c>
       <c r="F190" t="n">
-        <v>51.9</v>
+        <v>49.6</v>
       </c>
       <c r="G190" t="n">
-        <v>54.6</v>
+        <v>50.45</v>
       </c>
       <c r="H190" t="n">
-        <v>9.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-223.97</v>
+        <v>7.21</v>
       </c>
       <c r="C191" t="n">
-        <v>4.97269977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D191" t="n">
-        <v>54.7</v>
+        <v>50.05</v>
       </c>
       <c r="E191" t="n">
-        <v>56.1</v>
+        <v>50.8</v>
       </c>
       <c r="F191" t="n">
-        <v>53.7</v>
+        <v>49.52</v>
       </c>
       <c r="G191" t="n">
-        <v>54.25</v>
+        <v>50.65</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.64</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-908.88</v>
+        <v>144.28</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88181177</v>
+        <v>4.88317977</v>
       </c>
       <c r="D192" t="n">
-        <v>52.85</v>
+        <v>50</v>
       </c>
       <c r="E192" t="n">
-        <v>53.8</v>
+        <v>50.6</v>
       </c>
       <c r="F192" t="n">
-        <v>51.3</v>
+        <v>49.08</v>
       </c>
       <c r="G192" t="n">
-        <v>53.4</v>
+        <v>49.12</v>
       </c>
       <c r="H192" t="n">
-        <v>-1.57</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-219</v>
+        <v>-41.02</v>
       </c>
       <c r="C193" t="n">
-        <v>4.85991177</v>
+        <v>4.87907777</v>
       </c>
       <c r="D193" t="n">
-        <v>52.75</v>
+        <v>49.18</v>
       </c>
       <c r="E193" t="n">
-        <v>54.45</v>
+        <v>50.1</v>
       </c>
       <c r="F193" t="n">
-        <v>51.45</v>
+        <v>48.82</v>
       </c>
       <c r="G193" t="n">
-        <v>51.85</v>
+        <v>49.92</v>
       </c>
       <c r="H193" t="n">
-        <v>-2.9</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>81.19</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C194" t="n">
-        <v>4.86803077</v>
+        <v>4.88594877</v>
       </c>
       <c r="D194" t="n">
-        <v>51.85</v>
+        <v>50.5</v>
       </c>
       <c r="E194" t="n">
-        <v>51.85</v>
+        <v>50.95</v>
       </c>
       <c r="F194" t="n">
-        <v>49.6</v>
+        <v>49.74</v>
       </c>
       <c r="G194" t="n">
-        <v>50.45</v>
+        <v>50.1</v>
       </c>
       <c r="H194" t="n">
-        <v>-2.7</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.21</v>
+        <v>20.01</v>
       </c>
       <c r="C195" t="n">
-        <v>4.86875177</v>
+        <v>4.88794977</v>
       </c>
       <c r="D195" t="n">
-        <v>50.05</v>
+        <v>50</v>
       </c>
       <c r="E195" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="F195" t="n">
-        <v>49.52</v>
+        <v>49.04</v>
       </c>
       <c r="G195" t="n">
-        <v>50.65</v>
+        <v>49.06</v>
       </c>
       <c r="H195" t="n">
-        <v>0.4</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>144.28</v>
+        <v>-18.77</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88317977</v>
+        <v>4.88607277</v>
       </c>
       <c r="D196" t="n">
-        <v>50</v>
+        <v>49.08</v>
       </c>
       <c r="E196" t="n">
-        <v>50.6</v>
+        <v>49.78</v>
       </c>
       <c r="F196" t="n">
-        <v>49.08</v>
+        <v>48.7</v>
       </c>
       <c r="G196" t="n">
-        <v>49.12</v>
+        <v>49.4</v>
       </c>
       <c r="H196" t="n">
-        <v>-3.02</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-41.02</v>
+        <v>95.14</v>
       </c>
       <c r="C197" t="n">
-        <v>4.87907777</v>
+        <v>4.89558677</v>
       </c>
       <c r="D197" t="n">
-        <v>49.18</v>
+        <v>48.66</v>
       </c>
       <c r="E197" t="n">
-        <v>50.1</v>
+        <v>49.22</v>
       </c>
       <c r="F197" t="n">
-        <v>48.82</v>
+        <v>48.02</v>
       </c>
       <c r="G197" t="n">
-        <v>49.92</v>
+        <v>48.22</v>
       </c>
       <c r="H197" t="n">
-        <v>1.63</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>68.70999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="C198" t="n">
-        <v>4.88594877</v>
+        <v>4.89623377</v>
       </c>
       <c r="D198" t="n">
-        <v>50.5</v>
+        <v>48.22</v>
       </c>
       <c r="E198" t="n">
-        <v>50.95</v>
+        <v>48.22</v>
       </c>
       <c r="F198" t="n">
-        <v>49.74</v>
+        <v>47.46</v>
       </c>
       <c r="G198" t="n">
-        <v>50.1</v>
+        <v>47.46</v>
       </c>
       <c r="H198" t="n">
-        <v>0.36</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>20.01</v>
+        <v>78.34</v>
       </c>
       <c r="C199" t="n">
-        <v>4.88794977</v>
+        <v>4.90406777</v>
       </c>
       <c r="D199" t="n">
-        <v>50</v>
+        <v>47.86</v>
       </c>
       <c r="E199" t="n">
-        <v>50.5</v>
+        <v>48.68</v>
       </c>
       <c r="F199" t="n">
-        <v>49.04</v>
+        <v>47.7</v>
       </c>
       <c r="G199" t="n">
-        <v>49.06</v>
+        <v>48.48</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-18.77</v>
+        <v>12.2</v>
       </c>
       <c r="C200" t="n">
-        <v>4.88607277</v>
+        <v>4.90528777</v>
       </c>
       <c r="D200" t="n">
-        <v>49.08</v>
+        <v>48.1</v>
       </c>
       <c r="E200" t="n">
-        <v>49.78</v>
+        <v>48.7</v>
       </c>
       <c r="F200" t="n">
-        <v>48.7</v>
+        <v>47.38</v>
       </c>
       <c r="G200" t="n">
-        <v>49.4</v>
+        <v>47.88</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>95.14</v>
+        <v>-50.42</v>
       </c>
       <c r="C201" t="n">
-        <v>4.89558677</v>
+        <v>4.90024577</v>
       </c>
       <c r="D201" t="n">
-        <v>48.66</v>
+        <v>47.34</v>
       </c>
       <c r="E201" t="n">
-        <v>49.22</v>
+        <v>48.28</v>
       </c>
       <c r="F201" t="n">
-        <v>48.02</v>
+        <v>47.06</v>
       </c>
       <c r="G201" t="n">
-        <v>48.22</v>
+        <v>47.9</v>
       </c>
       <c r="H201" t="n">
-        <v>-2.39</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>6.47</v>
+        <v>7.38</v>
       </c>
       <c r="C202" t="n">
-        <v>4.89623377</v>
+        <v>4.90098377</v>
       </c>
       <c r="D202" t="n">
-        <v>48.22</v>
+        <v>49.98</v>
       </c>
       <c r="E202" t="n">
-        <v>48.22</v>
+        <v>51.2</v>
       </c>
       <c r="F202" t="n">
-        <v>47.46</v>
+        <v>49.76</v>
       </c>
       <c r="G202" t="n">
-        <v>47.46</v>
+        <v>50.55</v>
       </c>
       <c r="H202" t="n">
-        <v>-1.58</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>78.34</v>
+        <v>0.19</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90406777</v>
+        <v>4.90100277</v>
       </c>
       <c r="D203" t="n">
-        <v>47.86</v>
+        <v>50.55</v>
       </c>
       <c r="E203" t="n">
-        <v>48.68</v>
+        <v>51.8</v>
       </c>
       <c r="F203" t="n">
-        <v>47.7</v>
+        <v>50.5</v>
       </c>
       <c r="G203" t="n">
-        <v>48.48</v>
+        <v>51.2</v>
       </c>
       <c r="H203" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12.2</v>
+        <v>-404.07</v>
       </c>
       <c r="C204" t="n">
-        <v>4.90528777</v>
+        <v>4.86059577</v>
       </c>
       <c r="D204" t="n">
-        <v>48.1</v>
+        <v>50.3</v>
       </c>
       <c r="E204" t="n">
-        <v>48.7</v>
+        <v>51</v>
       </c>
       <c r="F204" t="n">
-        <v>47.38</v>
+        <v>49.3</v>
       </c>
       <c r="G204" t="n">
-        <v>47.88</v>
+        <v>49.46</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.24</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-50.42</v>
+        <v>-104.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.90024577</v>
+        <v>4.85015377</v>
       </c>
       <c r="D205" t="n">
-        <v>47.34</v>
+        <v>48.86</v>
       </c>
       <c r="E205" t="n">
-        <v>48.28</v>
+        <v>49.74</v>
       </c>
       <c r="F205" t="n">
-        <v>47.06</v>
+        <v>47.6</v>
       </c>
       <c r="G205" t="n">
-        <v>47.9</v>
+        <v>47.68</v>
       </c>
       <c r="H205" t="n">
-        <v>0.04</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7.38</v>
+        <v>-9.27</v>
       </c>
       <c r="C206" t="n">
-        <v>4.90098377</v>
+        <v>4.84922677</v>
       </c>
       <c r="D206" t="n">
-        <v>49.98</v>
+        <v>47.68</v>
       </c>
       <c r="E206" t="n">
-        <v>51.2</v>
+        <v>48.9</v>
       </c>
       <c r="F206" t="n">
-        <v>49.76</v>
+        <v>47.32</v>
       </c>
       <c r="G206" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="H206" t="n">
-        <v>5.53</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.19</v>
+        <v>-62.41</v>
       </c>
       <c r="C207" t="n">
-        <v>4.90100277</v>
+        <v>4.84298577</v>
       </c>
       <c r="D207" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="E207" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F207" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="G207" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="H207" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-404.07</v>
+        <v>-4.06</v>
       </c>
       <c r="C208" t="n">
-        <v>4.86059577</v>
+        <v>4.84257977</v>
       </c>
       <c r="D208" t="n">
-        <v>50.3</v>
+        <v>47.8</v>
       </c>
       <c r="E208" t="n">
-        <v>51</v>
+        <v>48.6</v>
       </c>
       <c r="F208" t="n">
-        <v>49.3</v>
+        <v>47.16</v>
       </c>
       <c r="G208" t="n">
-        <v>49.46</v>
+        <v>47.98</v>
       </c>
       <c r="H208" t="n">
-        <v>-3.4</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-104.42</v>
+        <v>107.65</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85015377</v>
+        <v>4.85334477</v>
       </c>
       <c r="D209" t="n">
-        <v>48.86</v>
+        <v>47.86</v>
       </c>
       <c r="E209" t="n">
-        <v>49.74</v>
+        <v>48.44</v>
       </c>
       <c r="F209" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="G209" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="H209" t="n">
-        <v>-3.6</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-9.27</v>
+        <v>137.46</v>
       </c>
       <c r="C210" t="n">
-        <v>4.84922677</v>
+        <v>4.86709077</v>
       </c>
       <c r="D210" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="E210" t="n">
-        <v>48.9</v>
+        <v>48.22</v>
       </c>
       <c r="F210" t="n">
-        <v>47.32</v>
+        <v>46.6</v>
       </c>
       <c r="G210" t="n">
-        <v>48.1</v>
+        <v>47.06</v>
       </c>
       <c r="H210" t="n">
-        <v>0.88</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-62.41</v>
+        <v>154.04</v>
       </c>
       <c r="C211" t="n">
-        <v>4.84298577</v>
+        <v>4.88249477</v>
       </c>
       <c r="D211" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="E211" t="n">
-        <v>49</v>
+        <v>46.76</v>
       </c>
       <c r="F211" t="n">
-        <v>47.5</v>
+        <v>44.56</v>
       </c>
       <c r="G211" t="n">
-        <v>48.6</v>
+        <v>45.86</v>
       </c>
       <c r="H211" t="n">
-        <v>1.04</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-4.06</v>
+        <v>78.03</v>
       </c>
       <c r="C212" t="n">
-        <v>4.84257977</v>
+        <v>4.89029777</v>
       </c>
       <c r="D212" t="n">
-        <v>47.8</v>
+        <v>46.56</v>
       </c>
       <c r="E212" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="F212" t="n">
-        <v>47.16</v>
+        <v>46.2</v>
       </c>
       <c r="G212" t="n">
-        <v>47.98</v>
+        <v>46.38</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.28</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>107.65</v>
+        <v>401.67</v>
       </c>
       <c r="C213" t="n">
-        <v>4.85334477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.86</v>
+        <v>48.14</v>
       </c>
       <c r="E213" t="n">
-        <v>48.44</v>
+        <v>48.88</v>
       </c>
       <c r="F213" t="n">
-        <v>46.5</v>
+        <v>47.12</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.33</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>137.46</v>
+        <v>-79.33</v>
       </c>
       <c r="C214" t="n">
-        <v>4.86709077</v>
+        <v>4.92253177</v>
       </c>
       <c r="D214" t="n">
-        <v>47.82</v>
+        <v>48.1</v>
       </c>
       <c r="E214" t="n">
-        <v>48.22</v>
+        <v>50.45</v>
       </c>
       <c r="F214" t="n">
-        <v>46.6</v>
+        <v>48.04</v>
       </c>
       <c r="G214" t="n">
-        <v>47.06</v>
+        <v>50.4</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.59</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>154.04</v>
+        <v>-415.48</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88249477</v>
+        <v>4.88098377</v>
       </c>
       <c r="D215" t="n">
-        <v>46.68</v>
+        <v>49.44</v>
       </c>
       <c r="E215" t="n">
-        <v>46.76</v>
+        <v>50.15</v>
       </c>
       <c r="F215" t="n">
-        <v>44.56</v>
+        <v>48.88</v>
       </c>
       <c r="G215" t="n">
-        <v>45.86</v>
+        <v>49.32</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>78.03</v>
+        <v>-394.96</v>
       </c>
       <c r="C216" t="n">
-        <v>4.89029777</v>
+        <v>4.84148777</v>
       </c>
       <c r="D216" t="n">
-        <v>46.56</v>
+        <v>49.08</v>
       </c>
       <c r="E216" t="n">
-        <v>48</v>
+        <v>49.08</v>
       </c>
       <c r="F216" t="n">
-        <v>46.2</v>
+        <v>47.2</v>
       </c>
       <c r="G216" t="n">
-        <v>46.38</v>
+        <v>47.62</v>
       </c>
       <c r="H216" t="n">
-        <v>1.13</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>401.67</v>
+        <v>-39.23</v>
       </c>
       <c r="C217" t="n">
-        <v>4.93046477</v>
+        <v>4.83756477</v>
       </c>
       <c r="D217" t="n">
-        <v>48.14</v>
+        <v>47.2</v>
       </c>
       <c r="E217" t="n">
-        <v>48.88</v>
+        <v>47.2</v>
       </c>
       <c r="F217" t="n">
-        <v>47.12</v>
+        <v>46.42</v>
       </c>
       <c r="G217" t="n">
-        <v>47.82</v>
+        <v>46.48</v>
       </c>
       <c r="H217" t="n">
-        <v>3.1</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-79.33</v>
+        <v>219.67</v>
       </c>
       <c r="C218" t="n">
-        <v>4.92253177</v>
+        <v>4.85953177</v>
       </c>
       <c r="D218" t="n">
-        <v>48.1</v>
+        <v>45.74</v>
       </c>
       <c r="E218" t="n">
-        <v>50.45</v>
+        <v>46.44</v>
       </c>
       <c r="F218" t="n">
-        <v>48.04</v>
+        <v>45.38</v>
       </c>
       <c r="G218" t="n">
-        <v>50.4</v>
+        <v>46.34</v>
       </c>
       <c r="H218" t="n">
-        <v>5.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-415.48</v>
+        <v>111.68</v>
       </c>
       <c r="C219" t="n">
-        <v>4.88098377</v>
+        <v>4.87069977</v>
       </c>
       <c r="D219" t="n">
-        <v>49.44</v>
+        <v>45.9</v>
       </c>
       <c r="E219" t="n">
-        <v>50.15</v>
+        <v>47.8</v>
       </c>
       <c r="F219" t="n">
-        <v>48.88</v>
+        <v>45.84</v>
       </c>
       <c r="G219" t="n">
-        <v>49.32</v>
+        <v>47.52</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.14</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>-394.96</v>
+        <v>47.5</v>
       </c>
       <c r="C220" t="n">
-        <v>4.84148777</v>
+        <v>4.87544977</v>
       </c>
       <c r="D220" t="n">
-        <v>49.08</v>
+        <v>47.52</v>
       </c>
       <c r="E220" t="n">
-        <v>49.08</v>
+        <v>48.06</v>
       </c>
       <c r="F220" t="n">
-        <v>47.2</v>
+        <v>46.06</v>
       </c>
       <c r="G220" t="n">
-        <v>47.62</v>
+        <v>46.12</v>
       </c>
       <c r="H220" t="n">
-        <v>-3.45</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-39.23</v>
+        <v>-30.32</v>
       </c>
       <c r="C221" t="n">
-        <v>4.83756477</v>
+        <v>4.87241777</v>
       </c>
       <c r="D221" t="n">
-        <v>47.2</v>
+        <v>46.92</v>
       </c>
       <c r="E221" t="n">
-        <v>47.2</v>
+        <v>47.42</v>
       </c>
       <c r="F221" t="n">
-        <v>46.42</v>
+        <v>45.94</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>-2.39</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>219.67</v>
+        <v>15.46</v>
       </c>
       <c r="C222" t="n">
-        <v>4.85953177</v>
+        <v>4.87396377</v>
       </c>
       <c r="D222" t="n">
-        <v>45.74</v>
+        <v>46.9</v>
       </c>
       <c r="E222" t="n">
-        <v>46.44</v>
+        <v>47.5</v>
       </c>
       <c r="F222" t="n">
-        <v>45.38</v>
+        <v>44.94</v>
       </c>
       <c r="G222" t="n">
-        <v>46.34</v>
+        <v>46.88</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.3</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>111.68</v>
+        <v>57.59</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87069977</v>
+        <v>4.87972277</v>
       </c>
       <c r="D223" t="n">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
       <c r="E223" t="n">
-        <v>47.8</v>
+        <v>48.46</v>
       </c>
       <c r="F223" t="n">
-        <v>45.84</v>
+        <v>46.8</v>
       </c>
       <c r="G223" t="n">
-        <v>47.52</v>
+        <v>47.56</v>
       </c>
       <c r="H223" t="n">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B224" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="C224" t="n">
-        <v>4.87544977</v>
-      </c>
-      <c r="D224" t="n">
-        <v>47.52</v>
-      </c>
-      <c r="E224" t="n">
-        <v>48.06</v>
-      </c>
-      <c r="F224" t="n">
-        <v>46.06</v>
-      </c>
-      <c r="G224" t="n">
-        <v>46.12</v>
-      </c>
-      <c r="H224" t="n">
-        <v>-2.95</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B225" t="n">
-        <v>-30.32</v>
-      </c>
-      <c r="C225" t="n">
-        <v>4.87241777</v>
-      </c>
-      <c r="D225" t="n">
-        <v>46.92</v>
-      </c>
-      <c r="E225" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="F225" t="n">
-        <v>45.94</v>
-      </c>
-      <c r="G225" t="n">
-        <v>46.48</v>
-      </c>
-      <c r="H225" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="C226" t="n">
-        <v>4.87396377</v>
-      </c>
-      <c r="D226" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="E226" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F226" t="n">
-        <v>44.94</v>
-      </c>
-      <c r="G226" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="H226" t="n">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>0</v>
-      </c>
-      <c r="C227" t="n">
-        <v>4.87396377</v>
-      </c>
-      <c r="D227" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="E227" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="F227" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G227" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="H227" t="n">
         <v>1.45</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H223"/>
+  <dimension ref="A1:H224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6389,7 +6389,7 @@
         <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>48.14</v>
+        <v>47.28</v>
       </c>
       <c r="E213" t="n">
         <v>48.88</v>
@@ -6682,6 +6682,34 @@
       </c>
       <c r="H223" t="n">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>0</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4.87972277</v>
+      </c>
+      <c r="D224" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="E224" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="F224" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="G224" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="H224" t="n">
+        <v>-4.37</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -6691,10 +6691,10 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0</v>
+        <v>112.19</v>
       </c>
       <c r="C224" t="n">
-        <v>4.87972277</v>
+        <v>4.89094177</v>
       </c>
       <c r="D224" t="n">
         <v>47.54</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H224"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6712,6 +6712,34 @@
         <v>-4.37</v>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>0</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.89094177</v>
+      </c>
+      <c r="D225" t="n">
+        <v>45</v>
+      </c>
+      <c r="E225" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="F225" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="G225" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="H225" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="E79" t="n">
-        <v>72.25</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>69.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G79" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E80" t="n">
-        <v>71.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F80" t="n">
-        <v>69.55</v>
+        <v>71.5</v>
       </c>
       <c r="G80" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4051 +2693,4163 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>70.3</v>
+        <v>72.8</v>
       </c>
       <c r="E81" t="n">
-        <v>73.3</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>70.3</v>
+        <v>71.5</v>
       </c>
       <c r="G81" t="n">
-        <v>72.84999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H81" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-37.37</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D82" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>73.5</v>
+        <v>72.25</v>
       </c>
       <c r="F82" t="n">
-        <v>71.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.51</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D83" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>73.15000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="F83" t="n">
-        <v>70.5</v>
+        <v>69.55</v>
       </c>
       <c r="G83" t="n">
-        <v>71.84999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>0.14</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>39.15</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29772381</v>
+        <v>5.29754581</v>
       </c>
       <c r="D84" t="n">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="E84" t="n">
-        <v>71.8</v>
+        <v>73.3</v>
       </c>
       <c r="F84" t="n">
-        <v>68.55</v>
+        <v>70.3</v>
       </c>
       <c r="G84" t="n">
-        <v>68.65000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-4.45</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-32.03</v>
+        <v>-37.37</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29452081</v>
+        <v>5.29380881</v>
       </c>
       <c r="D85" t="n">
-        <v>69.5</v>
+        <v>71.8</v>
       </c>
       <c r="E85" t="n">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="F85" t="n">
-        <v>68.15000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G85" t="n">
-        <v>68.75</v>
+        <v>71.75</v>
       </c>
       <c r="H85" t="n">
-        <v>0.15</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-245.51</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>5.26996981</v>
+        <v>5.29380881</v>
       </c>
       <c r="D86" t="n">
-        <v>67.75</v>
+        <v>72.8</v>
       </c>
       <c r="E86" t="n">
-        <v>70.15000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>67</v>
+        <v>70.5</v>
       </c>
       <c r="G86" t="n">
-        <v>68</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.99</v>
+        <v>39.15</v>
       </c>
       <c r="C87" t="n">
-        <v>5.27246881</v>
+        <v>5.29772381</v>
       </c>
       <c r="D87" t="n">
-        <v>68.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>69</v>
+        <v>71.8</v>
       </c>
       <c r="F87" t="n">
-        <v>65.65000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="G87" t="n">
-        <v>66.55</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-2.13</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-70.5937</v>
+        <v>-32.03</v>
       </c>
       <c r="C88" t="n">
-        <v>5.26540944</v>
+        <v>5.29452081</v>
       </c>
       <c r="D88" t="n">
-        <v>65.84999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E88" t="n">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="F88" t="n">
-        <v>64.45</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>65.84999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-83.42</v>
+        <v>-245.51</v>
       </c>
       <c r="C89" t="n">
-        <v>5.25706744</v>
+        <v>5.26996981</v>
       </c>
       <c r="D89" t="n">
-        <v>66.90000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="E89" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>67</v>
+      </c>
+      <c r="G89" t="n">
         <v>68</v>
       </c>
-      <c r="F89" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="H89" t="n">
-        <v>-0.38</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>32.9872</v>
+        <v>24.99</v>
       </c>
       <c r="C90" t="n">
-        <v>5.26036616</v>
+        <v>5.27246881</v>
       </c>
       <c r="D90" t="n">
-        <v>65.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>67.65000000000001</v>
+        <v>69</v>
       </c>
       <c r="F90" t="n">
-        <v>65.34999999999999</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>67.45</v>
+        <v>66.55</v>
       </c>
       <c r="H90" t="n">
-        <v>2.82</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-168.98</v>
+        <v>-70.5937</v>
       </c>
       <c r="C91" t="n">
-        <v>5.24346816</v>
+        <v>5.26540944</v>
       </c>
       <c r="D91" t="n">
-        <v>64.84999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>69</v>
+        <v>66.8</v>
       </c>
       <c r="F91" t="n">
-        <v>64.7</v>
+        <v>64.45</v>
       </c>
       <c r="G91" t="n">
-        <v>68.90000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>2.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-195.54</v>
+        <v>-83.42</v>
       </c>
       <c r="C92" t="n">
-        <v>5.22391416</v>
+        <v>5.25706744</v>
       </c>
       <c r="D92" t="n">
-        <v>69.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>70.2</v>
+        <v>68</v>
       </c>
       <c r="F92" t="n">
-        <v>67.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>69.05</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>0.22</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>16.18</v>
+        <v>32.9872</v>
       </c>
       <c r="C93" t="n">
-        <v>5.22553216</v>
+        <v>5.26036616</v>
       </c>
       <c r="D93" t="n">
-        <v>69.25</v>
+        <v>65.5</v>
       </c>
       <c r="E93" t="n">
-        <v>70.8</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>69.05</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>69.84999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="H93" t="n">
-        <v>1.16</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.87</v>
+        <v>-168.98</v>
       </c>
       <c r="C94" t="n">
-        <v>5.22691916</v>
+        <v>5.24346816</v>
       </c>
       <c r="D94" t="n">
-        <v>70.95</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="F94" t="n">
-        <v>69.15000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G94" t="n">
-        <v>70.15000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-145.08</v>
+        <v>-195.54</v>
       </c>
       <c r="C95" t="n">
-        <v>5.21241116</v>
+        <v>5.22391416</v>
       </c>
       <c r="D95" t="n">
-        <v>68.95</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>69</v>
+        <v>70.2</v>
       </c>
       <c r="F95" t="n">
-        <v>67.3</v>
+        <v>67.95</v>
       </c>
       <c r="G95" t="n">
-        <v>67.90000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="H95" t="n">
-        <v>-3.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.02</v>
+        <v>16.18</v>
       </c>
       <c r="C96" t="n">
-        <v>5.21491316</v>
+        <v>5.22553216</v>
       </c>
       <c r="D96" t="n">
-        <v>67.5</v>
+        <v>69.25</v>
       </c>
       <c r="E96" t="n">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F96" t="n">
-        <v>66.3</v>
+        <v>69.05</v>
       </c>
       <c r="G96" t="n">
-        <v>69.90000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>2.95</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-6.25</v>
+        <v>13.87</v>
       </c>
       <c r="C97" t="n">
-        <v>5.21428816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D97" t="n">
-        <v>71.25</v>
+        <v>70.95</v>
       </c>
       <c r="E97" t="n">
-        <v>73.3</v>
+        <v>71.3</v>
       </c>
       <c r="F97" t="n">
-        <v>70.84999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>71.3</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-48.58</v>
+        <v>-145.08</v>
       </c>
       <c r="C98" t="n">
-        <v>5.20943016</v>
+        <v>5.21241116</v>
       </c>
       <c r="D98" t="n">
-        <v>70.65000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E98" t="n">
-        <v>71.25</v>
+        <v>69</v>
       </c>
       <c r="F98" t="n">
-        <v>66.34999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G98" t="n">
-        <v>66.84999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>-6.24</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-197.18</v>
+        <v>25.02</v>
       </c>
       <c r="C99" t="n">
-        <v>5.18971216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D99" t="n">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="E99" t="n">
-        <v>67.34999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="G99" t="n">
-        <v>66</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.27</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>426.64</v>
+        <v>-6.25</v>
       </c>
       <c r="C100" t="n">
-        <v>5.23237616</v>
+        <v>5.21428816</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>71.25</v>
       </c>
       <c r="E100" t="n">
-        <v>68.7</v>
+        <v>73.3</v>
       </c>
       <c r="F100" t="n">
-        <v>66.34999999999999</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>66.8</v>
+        <v>71.3</v>
       </c>
       <c r="H100" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>41.4993</v>
+        <v>-48.58</v>
       </c>
       <c r="C101" t="n">
-        <v>5.23652609</v>
+        <v>5.20943016</v>
       </c>
       <c r="D101" t="n">
-        <v>65.59999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>66.05</v>
+        <v>71.25</v>
       </c>
       <c r="F101" t="n">
-        <v>64.2</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>64.8</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.99</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-220.5688</v>
+        <v>-197.18</v>
       </c>
       <c r="C102" t="n">
-        <v>5.21446921</v>
+        <v>5.18971216</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.65000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>63.45</v>
+        <v>65.8</v>
       </c>
       <c r="G102" t="n">
-        <v>67.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="H102" t="n">
-        <v>4.32</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>215.27</v>
+        <v>426.64</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23599621</v>
+        <v>5.23237616</v>
       </c>
       <c r="D103" t="n">
-        <v>69.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="E103" t="n">
-        <v>71.34999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F103" t="n">
-        <v>69.45</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>70.45</v>
+        <v>66.8</v>
       </c>
       <c r="H103" t="n">
-        <v>4.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-160.53</v>
+        <v>41.4993</v>
       </c>
       <c r="C104" t="n">
-        <v>5.21994321</v>
+        <v>5.23652609</v>
       </c>
       <c r="D104" t="n">
-        <v>69.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>70.8</v>
+        <v>66.05</v>
       </c>
       <c r="F104" t="n">
-        <v>68.7</v>
+        <v>64.2</v>
       </c>
       <c r="G104" t="n">
-        <v>69</v>
+        <v>64.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.06</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-304.01</v>
+        <v>-220.5688</v>
       </c>
       <c r="C105" t="n">
-        <v>5.18954221</v>
+        <v>5.21446921</v>
       </c>
       <c r="D105" t="n">
-        <v>69</v>
+        <v>66.2</v>
       </c>
       <c r="E105" t="n">
-        <v>71.5</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>68.3</v>
+        <v>63.45</v>
       </c>
       <c r="G105" t="n">
-        <v>70.05</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>1.52</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-30.3</v>
+        <v>215.27</v>
       </c>
       <c r="C106" t="n">
-        <v>5.18651221</v>
+        <v>5.23599621</v>
       </c>
       <c r="D106" t="n">
-        <v>68.05</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>69.34999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>68</v>
+        <v>69.45</v>
       </c>
       <c r="G106" t="n">
-        <v>68.8</v>
+        <v>70.45</v>
       </c>
       <c r="H106" t="n">
-        <v>-1.78</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-92.3</v>
+        <v>-160.53</v>
       </c>
       <c r="C107" t="n">
-        <v>5.17728221</v>
+        <v>5.21994321</v>
       </c>
       <c r="D107" t="n">
-        <v>68.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>69.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F107" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="G107" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.6</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>25.43</v>
+        <v>-304.01</v>
       </c>
       <c r="C108" t="n">
-        <v>5.17982521</v>
+        <v>5.18954221</v>
       </c>
       <c r="D108" t="n">
-        <v>68.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="E108" t="n">
-        <v>71.45</v>
+        <v>71.5</v>
       </c>
       <c r="F108" t="n">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G108" t="n">
-        <v>71.2</v>
+        <v>70.05</v>
       </c>
       <c r="H108" t="n">
-        <v>5.17</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>136.53</v>
+        <v>-30.3</v>
       </c>
       <c r="C109" t="n">
-        <v>5.19347821</v>
+        <v>5.18651221</v>
       </c>
       <c r="D109" t="n">
-        <v>71.2</v>
+        <v>68.05</v>
       </c>
       <c r="E109" t="n">
-        <v>73.40000000000001</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G109" t="n">
-        <v>71.8</v>
+        <v>68.8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.84</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-224.29</v>
+        <v>-92.3</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17104921</v>
+        <v>5.17728221</v>
       </c>
       <c r="D110" t="n">
-        <v>73.45</v>
+        <v>68.8</v>
       </c>
       <c r="E110" t="n">
-        <v>74</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>71.65000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="G110" t="n">
-        <v>73.3</v>
+        <v>67.7</v>
       </c>
       <c r="H110" t="n">
-        <v>2.09</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>97.7422</v>
+        <v>25.43</v>
       </c>
       <c r="C111" t="n">
-        <v>5.18082343</v>
+        <v>5.17982521</v>
       </c>
       <c r="D111" t="n">
-        <v>71.95</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>73.5</v>
+        <v>71.45</v>
       </c>
       <c r="F111" t="n">
-        <v>71.75</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G111" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.91</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-116.85</v>
+        <v>136.53</v>
       </c>
       <c r="C112" t="n">
-        <v>5.16913843</v>
+        <v>5.19347821</v>
       </c>
       <c r="D112" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E112" t="n">
-        <v>76.45</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>71.55</v>
+        <v>70</v>
       </c>
       <c r="G112" t="n">
-        <v>74.2</v>
+        <v>71.8</v>
       </c>
       <c r="H112" t="n">
-        <v>3.2</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>32.76</v>
+        <v>-224.29</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17241443</v>
+        <v>5.17104921</v>
       </c>
       <c r="D113" t="n">
-        <v>74.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E113" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F113" t="n">
-        <v>73.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>73.7</v>
+        <v>73.3</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.67</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-19.6</v>
+        <v>97.7422</v>
       </c>
       <c r="C114" t="n">
-        <v>5.17045443</v>
+        <v>5.18082343</v>
       </c>
       <c r="D114" t="n">
-        <v>73.7</v>
+        <v>71.95</v>
       </c>
       <c r="E114" t="n">
-        <v>73.95</v>
+        <v>73.5</v>
       </c>
       <c r="F114" t="n">
-        <v>71.65000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="G114" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.95</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>74.23999999999999</v>
+        <v>-116.85</v>
       </c>
       <c r="C115" t="n">
-        <v>5.17787843</v>
+        <v>5.16913843</v>
       </c>
       <c r="D115" t="n">
-        <v>73.75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>73.75</v>
+        <v>76.45</v>
       </c>
       <c r="F115" t="n">
-        <v>70.5</v>
+        <v>71.55</v>
       </c>
       <c r="G115" t="n">
-        <v>70.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>15.04</v>
+        <v>32.76</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17938243</v>
+        <v>5.17241443</v>
       </c>
       <c r="D116" t="n">
-        <v>70.95</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>72.15000000000001</v>
+        <v>75</v>
       </c>
       <c r="F116" t="n">
-        <v>70.95</v>
+        <v>73.25</v>
       </c>
       <c r="G116" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H116" t="n">
-        <v>0.99</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>213.47</v>
+        <v>-19.6</v>
       </c>
       <c r="C117" t="n">
-        <v>5.20072943</v>
+        <v>5.17045443</v>
       </c>
       <c r="D117" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E117" t="n">
-        <v>71.90000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="F117" t="n">
-        <v>70.40000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>71.45</v>
+        <v>73</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.21</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-167.67</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>5.18396243</v>
+        <v>5.17787843</v>
       </c>
       <c r="D118" t="n">
-        <v>72</v>
+        <v>73.75</v>
       </c>
       <c r="E118" t="n">
-        <v>73.45</v>
+        <v>73.75</v>
       </c>
       <c r="F118" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G118" t="n">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>2.59</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-78.5919</v>
+        <v>15.04</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17610324</v>
+        <v>5.17938243</v>
       </c>
       <c r="D119" t="n">
-        <v>73.3</v>
+        <v>70.95</v>
       </c>
       <c r="E119" t="n">
-        <v>73.3</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>71.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="G119" t="n">
-        <v>73.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.14</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-54.57</v>
+        <v>213.47</v>
       </c>
       <c r="C120" t="n">
-        <v>5.17064624</v>
+        <v>5.20072943</v>
       </c>
       <c r="D120" t="n">
-        <v>72.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>73.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>71.95</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>73.45</v>
+        <v>71.45</v>
       </c>
       <c r="H120" t="n">
-        <v>0.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>32.9</v>
+        <v>-167.67</v>
       </c>
       <c r="C121" t="n">
-        <v>5.17393624</v>
+        <v>5.18396243</v>
       </c>
       <c r="D121" t="n">
+        <v>72</v>
+      </c>
+      <c r="E121" t="n">
         <v>73.45</v>
       </c>
-      <c r="E121" t="n">
-        <v>74.40000000000001</v>
-      </c>
       <c r="F121" t="n">
-        <v>71.75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>73.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.41</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>41.93</v>
+        <v>-78.5919</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17812924</v>
+        <v>5.17610324</v>
       </c>
       <c r="D122" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="E122" t="n">
-        <v>73.65000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F122" t="n">
-        <v>68.7</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>69.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.44</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>52.87</v>
+        <v>-54.57</v>
       </c>
       <c r="C123" t="n">
-        <v>5.18341624</v>
+        <v>5.17064624</v>
       </c>
       <c r="D123" t="n">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E123" t="n">
-        <v>70.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>68.90000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G123" t="n">
-        <v>69.7</v>
+        <v>73.45</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>291.58</v>
+        <v>32.9</v>
       </c>
       <c r="C124" t="n">
-        <v>5.21257424</v>
+        <v>5.17393624</v>
       </c>
       <c r="D124" t="n">
-        <v>69.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E124" t="n">
-        <v>69.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>66.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G124" t="n">
-        <v>67</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>-3.87</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-60.7601</v>
+        <v>41.93</v>
       </c>
       <c r="C125" t="n">
-        <v>5.20649823</v>
+        <v>5.17812924</v>
       </c>
       <c r="D125" t="n">
-        <v>69.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E125" t="n">
-        <v>70.25</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>68.45</v>
+        <v>68.7</v>
       </c>
       <c r="G125" t="n">
-        <v>69.25</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>3.36</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>264.89</v>
+        <v>52.87</v>
       </c>
       <c r="C126" t="n">
-        <v>5.23298723</v>
+        <v>5.18341624</v>
       </c>
       <c r="D126" t="n">
-        <v>68.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>69.75</v>
+        <v>70.5</v>
       </c>
       <c r="F126" t="n">
-        <v>67.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>67.55</v>
+        <v>69.7</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.45</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>291.58</v>
       </c>
       <c r="C127" t="n">
-        <v>5.23298723</v>
+        <v>5.21257424</v>
       </c>
       <c r="D127" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>71.15000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F127" t="n">
-        <v>68.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G127" t="n">
-        <v>70.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H127" t="n">
-        <v>3.85</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-60.7601</v>
       </c>
       <c r="C128" t="n">
-        <v>5.23298723</v>
+        <v>5.20649823</v>
       </c>
       <c r="D128" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="F128" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="G128" t="n">
         <v>69.25</v>
       </c>
-      <c r="E128" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F128" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="G128" t="n">
-        <v>69.65000000000001</v>
-      </c>
       <c r="H128" t="n">
-        <v>-0.71</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-369.37</v>
+        <v>264.89</v>
       </c>
       <c r="C129" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D129" t="n">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E129" t="n">
-        <v>69.5</v>
+        <v>69.75</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.84999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.58</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D130" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E130" t="n">
-        <v>70.34999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="F130" t="n">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="G130" t="n">
-        <v>69.95</v>
+        <v>67.55</v>
       </c>
       <c r="H130" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>68.9663</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>5.20294686</v>
+        <v>5.23298723</v>
       </c>
       <c r="D131" t="n">
-        <v>68.34999999999999</v>
+        <v>69</v>
       </c>
       <c r="E131" t="n">
-        <v>70.3</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>68.34999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G131" t="n">
-        <v>70.05</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>0.14</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-247.41</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>5.17820586</v>
+        <v>5.23298723</v>
       </c>
       <c r="D132" t="n">
-        <v>69.5</v>
+        <v>69.25</v>
       </c>
       <c r="E132" t="n">
-        <v>74.15000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>69.45</v>
+        <v>68.2</v>
       </c>
       <c r="G132" t="n">
-        <v>73.84999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>5.42</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>27.55</v>
+        <v>-369.37</v>
       </c>
       <c r="C133" t="n">
-        <v>5.18096086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D133" t="n">
-        <v>73.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E133" t="n">
-        <v>75.15000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F133" t="n">
-        <v>73.05</v>
+        <v>67.3</v>
       </c>
       <c r="G133" t="n">
-        <v>73.40000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.61</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-286.2</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5.15234086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D134" t="n">
-        <v>73.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="E134" t="n">
-        <v>74.40000000000001</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>73.05</v>
+        <v>68.5</v>
       </c>
       <c r="G134" t="n">
-        <v>73.65000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="H134" t="n">
-        <v>0.34</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>48.88</v>
+        <v>68.9663</v>
       </c>
       <c r="C135" t="n">
-        <v>5.15722886</v>
+        <v>5.20294686</v>
       </c>
       <c r="D135" t="n">
-        <v>76.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>78.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F135" t="n">
-        <v>75.40000000000001</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>76.84999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H135" t="n">
-        <v>4.34</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-55.96</v>
+        <v>-247.41</v>
       </c>
       <c r="C136" t="n">
-        <v>5.15163286</v>
+        <v>5.17820586</v>
       </c>
       <c r="D136" t="n">
-        <v>75.05</v>
+        <v>69.5</v>
       </c>
       <c r="E136" t="n">
-        <v>75.90000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>74.25</v>
+        <v>69.45</v>
       </c>
       <c r="G136" t="n">
-        <v>75.59999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.63</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-385.85</v>
+        <v>27.55</v>
       </c>
       <c r="C137" t="n">
-        <v>5.11304786</v>
+        <v>5.18096086</v>
       </c>
       <c r="D137" t="n">
-        <v>72.40000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E137" t="n">
-        <v>72.40000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>64.5</v>
+        <v>73.05</v>
       </c>
       <c r="G137" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-14.15</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>139.59</v>
+        <v>-286.2</v>
       </c>
       <c r="C138" t="n">
-        <v>5.12700686</v>
+        <v>5.15234086</v>
       </c>
       <c r="D138" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>64.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>61.75</v>
+        <v>73.05</v>
       </c>
       <c r="G138" t="n">
-        <v>62.1</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>-4.31</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1468.42</v>
+        <v>48.88</v>
       </c>
       <c r="C139" t="n">
-        <v>5.27384886</v>
+        <v>5.15722886</v>
       </c>
       <c r="D139" t="n">
-        <v>62.6</v>
+        <v>76.8</v>
       </c>
       <c r="E139" t="n">
-        <v>63.35</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>61</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G139" t="n">
-        <v>61.6</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>292.93</v>
+        <v>-55.96</v>
       </c>
       <c r="C140" t="n">
-        <v>5.30314186</v>
+        <v>5.15163286</v>
       </c>
       <c r="D140" t="n">
-        <v>62.5</v>
+        <v>75.05</v>
       </c>
       <c r="E140" t="n">
-        <v>63.85</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>61.55</v>
+        <v>74.25</v>
       </c>
       <c r="G140" t="n">
-        <v>62.25</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>1.06</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>17.9</v>
+        <v>-385.85</v>
       </c>
       <c r="C141" t="n">
-        <v>5.30493186</v>
+        <v>5.11304786</v>
       </c>
       <c r="D141" t="n">
-        <v>63.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E141" t="n">
-        <v>64.95</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F141" t="n">
-        <v>61.35</v>
+        <v>64.5</v>
       </c>
       <c r="G141" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.72</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-224.88</v>
+        <v>139.59</v>
       </c>
       <c r="C142" t="n">
-        <v>5.28244386</v>
+        <v>5.12700686</v>
       </c>
       <c r="D142" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E142" t="n">
-        <v>62.25</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>60.4</v>
+        <v>61.75</v>
       </c>
       <c r="G142" t="n">
-        <v>62.15</v>
+        <v>62.1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.57</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-244.5</v>
+        <v>1468.42</v>
       </c>
       <c r="C143" t="n">
-        <v>5.25799386</v>
+        <v>5.27384886</v>
       </c>
       <c r="D143" t="n">
-        <v>61.9</v>
+        <v>62.6</v>
       </c>
       <c r="E143" t="n">
-        <v>62.35</v>
+        <v>63.35</v>
       </c>
       <c r="F143" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G143" t="n">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.14</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-302.48</v>
+        <v>292.93</v>
       </c>
       <c r="C144" t="n">
-        <v>5.22774586</v>
+        <v>5.30314186</v>
       </c>
       <c r="D144" t="n">
-        <v>60.1</v>
+        <v>62.5</v>
       </c>
       <c r="E144" t="n">
-        <v>61</v>
+        <v>63.85</v>
       </c>
       <c r="F144" t="n">
-        <v>58.6</v>
+        <v>61.55</v>
       </c>
       <c r="G144" t="n">
-        <v>60.45</v>
+        <v>62.25</v>
       </c>
       <c r="H144" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-177.8636</v>
+        <v>17.9</v>
       </c>
       <c r="C145" t="n">
-        <v>5.2099595</v>
+        <v>5.30493186</v>
       </c>
       <c r="D145" t="n">
-        <v>60</v>
+        <v>63.2</v>
       </c>
       <c r="E145" t="n">
-        <v>60.05</v>
+        <v>64.95</v>
       </c>
       <c r="F145" t="n">
-        <v>55.7</v>
+        <v>61.35</v>
       </c>
       <c r="G145" t="n">
-        <v>57.85</v>
+        <v>61.8</v>
       </c>
       <c r="H145" t="n">
-        <v>-4.3</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-228.55</v>
+        <v>-224.88</v>
       </c>
       <c r="C146" t="n">
-        <v>5.1871045</v>
+        <v>5.28244386</v>
       </c>
       <c r="D146" t="n">
-        <v>56.95</v>
+        <v>61.8</v>
       </c>
       <c r="E146" t="n">
-        <v>59.1</v>
+        <v>62.25</v>
       </c>
       <c r="F146" t="n">
-        <v>56</v>
+        <v>60.4</v>
       </c>
       <c r="G146" t="n">
-        <v>58.55</v>
+        <v>62.15</v>
       </c>
       <c r="H146" t="n">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>423.9973</v>
+        <v>-244.5</v>
       </c>
       <c r="C147" t="n">
-        <v>5.22950423</v>
+        <v>5.25799386</v>
       </c>
       <c r="D147" t="n">
-        <v>57.05</v>
+        <v>61.9</v>
       </c>
       <c r="E147" t="n">
-        <v>62</v>
+        <v>62.35</v>
       </c>
       <c r="F147" t="n">
-        <v>56.55</v>
+        <v>59.9</v>
       </c>
       <c r="G147" t="n">
-        <v>61.9</v>
+        <v>60.2</v>
       </c>
       <c r="H147" t="n">
-        <v>5.72</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-119.16</v>
+        <v>-302.48</v>
       </c>
       <c r="C148" t="n">
-        <v>5.21758823</v>
+        <v>5.22774586</v>
       </c>
       <c r="D148" t="n">
-        <v>60.5</v>
+        <v>60.1</v>
       </c>
       <c r="E148" t="n">
-        <v>60.75</v>
+        <v>61</v>
       </c>
       <c r="F148" t="n">
-        <v>58.75</v>
+        <v>58.6</v>
       </c>
       <c r="G148" t="n">
-        <v>59.1</v>
+        <v>60.45</v>
       </c>
       <c r="H148" t="n">
-        <v>-4.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-301.92</v>
+        <v>-177.8636</v>
       </c>
       <c r="C149" t="n">
-        <v>5.18739623</v>
+        <v>5.2099595</v>
       </c>
       <c r="D149" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="E149" t="n">
-        <v>58.95</v>
+        <v>60.05</v>
       </c>
       <c r="F149" t="n">
-        <v>56.85</v>
+        <v>55.7</v>
       </c>
       <c r="G149" t="n">
-        <v>57.25</v>
+        <v>57.85</v>
       </c>
       <c r="H149" t="n">
-        <v>-3.13</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>112.29</v>
+        <v>-228.55</v>
       </c>
       <c r="C150" t="n">
-        <v>5.19862523</v>
+        <v>5.1871045</v>
       </c>
       <c r="D150" t="n">
-        <v>57.1</v>
+        <v>56.95</v>
       </c>
       <c r="E150" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
       <c r="F150" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="G150" t="n">
-        <v>56.65</v>
+        <v>58.55</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.05</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-62.4836</v>
+        <v>423.9973</v>
       </c>
       <c r="C151" t="n">
-        <v>5.19237687</v>
+        <v>5.22950423</v>
       </c>
       <c r="D151" t="n">
-        <v>55.3</v>
+        <v>57.05</v>
       </c>
       <c r="E151" t="n">
-        <v>57.9</v>
+        <v>62</v>
       </c>
       <c r="F151" t="n">
-        <v>54.95</v>
+        <v>56.55</v>
       </c>
       <c r="G151" t="n">
-        <v>57.35</v>
+        <v>61.9</v>
       </c>
       <c r="H151" t="n">
-        <v>1.24</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-29.35</v>
+        <v>-119.16</v>
       </c>
       <c r="C152" t="n">
-        <v>5.18944187</v>
+        <v>5.21758823</v>
       </c>
       <c r="D152" t="n">
-        <v>56.2</v>
+        <v>60.5</v>
       </c>
       <c r="E152" t="n">
-        <v>57.1</v>
+        <v>60.75</v>
       </c>
       <c r="F152" t="n">
-        <v>55.8</v>
+        <v>58.75</v>
       </c>
       <c r="G152" t="n">
-        <v>55.85</v>
+        <v>59.1</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.62</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>54.46</v>
+        <v>-301.92</v>
       </c>
       <c r="C153" t="n">
-        <v>5.19488787</v>
+        <v>5.18739623</v>
       </c>
       <c r="D153" t="n">
-        <v>55.3</v>
+        <v>58.95</v>
       </c>
       <c r="E153" t="n">
-        <v>55.55</v>
+        <v>58.95</v>
       </c>
       <c r="F153" t="n">
-        <v>53.25</v>
+        <v>56.85</v>
       </c>
       <c r="G153" t="n">
-        <v>54.7</v>
+        <v>57.25</v>
       </c>
       <c r="H153" t="n">
-        <v>-2.06</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>17.32</v>
+        <v>112.29</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19661987</v>
+        <v>5.19862523</v>
       </c>
       <c r="D154" t="n">
-        <v>54</v>
+        <v>57.1</v>
       </c>
       <c r="E154" t="n">
-        <v>54.1</v>
+        <v>57.6</v>
       </c>
       <c r="F154" t="n">
-        <v>52.25</v>
+        <v>56.5</v>
       </c>
       <c r="G154" t="n">
-        <v>53.15</v>
+        <v>56.65</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.83</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>93.42</v>
+        <v>-62.4836</v>
       </c>
       <c r="C155" t="n">
-        <v>5.20596187</v>
+        <v>5.19237687</v>
       </c>
       <c r="D155" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>53.25</v>
+        <v>54.95</v>
       </c>
       <c r="G155" t="n">
-        <v>57</v>
+        <v>57.35</v>
       </c>
       <c r="H155" t="n">
-        <v>7.24</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>64.81</v>
+        <v>-29.35</v>
       </c>
       <c r="C156" t="n">
-        <v>5.21244287</v>
+        <v>5.18944187</v>
       </c>
       <c r="D156" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="E156" t="n">
-        <v>58.05</v>
+        <v>57.1</v>
       </c>
       <c r="F156" t="n">
-        <v>56.5</v>
+        <v>55.8</v>
       </c>
       <c r="G156" t="n">
-        <v>56.85</v>
+        <v>55.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.26</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-172.75</v>
+        <v>54.46</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19516787</v>
+        <v>5.19488787</v>
       </c>
       <c r="D157" t="n">
-        <v>56.85</v>
+        <v>55.3</v>
       </c>
       <c r="E157" t="n">
-        <v>57.2</v>
+        <v>55.55</v>
       </c>
       <c r="F157" t="n">
-        <v>55</v>
+        <v>53.25</v>
       </c>
       <c r="G157" t="n">
-        <v>56</v>
+        <v>54.7</v>
       </c>
       <c r="H157" t="n">
-        <v>-1.5</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-24.86</v>
+        <v>17.32</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19268187</v>
+        <v>5.19661987</v>
       </c>
       <c r="D158" t="n">
-        <v>55.75</v>
+        <v>54</v>
       </c>
       <c r="E158" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="F158" t="n">
-        <v>53.7</v>
+        <v>52.25</v>
       </c>
       <c r="G158" t="n">
-        <v>53.9</v>
+        <v>53.15</v>
       </c>
       <c r="H158" t="n">
-        <v>-3.75</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.38</v>
+        <v>93.42</v>
       </c>
       <c r="C159" t="n">
-        <v>5.19441987</v>
+        <v>5.20596187</v>
       </c>
       <c r="D159" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E159" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F159" t="n">
         <v>53.25</v>
       </c>
-      <c r="E159" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F159" t="n">
-        <v>51.75</v>
-      </c>
       <c r="G159" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H159" t="n">
-        <v>-3.53</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>14.06</v>
+        <v>64.81</v>
       </c>
       <c r="C160" t="n">
-        <v>5.19582587</v>
+        <v>5.21244287</v>
       </c>
       <c r="D160" t="n">
-        <v>50.15</v>
+        <v>56.6</v>
       </c>
       <c r="E160" t="n">
-        <v>51.55</v>
+        <v>58.05</v>
       </c>
       <c r="F160" t="n">
-        <v>49.64</v>
+        <v>56.5</v>
       </c>
       <c r="G160" t="n">
-        <v>50.5</v>
+        <v>56.85</v>
       </c>
       <c r="H160" t="n">
-        <v>-2.88</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-21.2345</v>
+        <v>-172.75</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19370242</v>
+        <v>5.19516787</v>
       </c>
       <c r="D161" t="n">
-        <v>50</v>
+        <v>56.85</v>
       </c>
       <c r="E161" t="n">
-        <v>50.8</v>
+        <v>57.2</v>
       </c>
       <c r="F161" t="n">
-        <v>47.9</v>
+        <v>55</v>
       </c>
       <c r="G161" t="n">
-        <v>48.32</v>
+        <v>56</v>
       </c>
       <c r="H161" t="n">
-        <v>-4.32</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>47.7</v>
+        <v>-24.86</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19847242</v>
+        <v>5.19268187</v>
       </c>
       <c r="D162" t="n">
-        <v>48.98</v>
+        <v>55.75</v>
       </c>
       <c r="E162" t="n">
-        <v>49.94</v>
+        <v>55.8</v>
       </c>
       <c r="F162" t="n">
-        <v>48.18</v>
+        <v>53.7</v>
       </c>
       <c r="G162" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="H162" t="n">
-        <v>2.32</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>92.59999999999999</v>
+        <v>17.38</v>
       </c>
       <c r="C163" t="n">
-        <v>5.20773242</v>
+        <v>5.19441987</v>
       </c>
       <c r="D163" t="n">
-        <v>49.44</v>
+        <v>53.25</v>
       </c>
       <c r="E163" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="F163" t="n">
-        <v>46.74</v>
+        <v>51.75</v>
       </c>
       <c r="G163" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="H163" t="n">
-        <v>-4.13</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-95.51000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19818142</v>
+        <v>5.19582587</v>
       </c>
       <c r="D164" t="n">
-        <v>47</v>
+        <v>50.15</v>
       </c>
       <c r="E164" t="n">
-        <v>47</v>
+        <v>51.55</v>
       </c>
       <c r="F164" t="n">
-        <v>45.86</v>
+        <v>49.64</v>
       </c>
       <c r="G164" t="n">
-        <v>46.28</v>
+        <v>50.5</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.36</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-254.06</v>
+        <v>-21.2345</v>
       </c>
       <c r="C165" t="n">
-        <v>5.17277542</v>
+        <v>5.19370242</v>
       </c>
       <c r="D165" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="E165" t="n">
-        <v>47.18</v>
+        <v>50.8</v>
       </c>
       <c r="F165" t="n">
-        <v>45.76</v>
+        <v>47.9</v>
       </c>
       <c r="G165" t="n">
-        <v>45.9</v>
+        <v>48.32</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.82</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-316.19</v>
+        <v>47.7</v>
       </c>
       <c r="C166" t="n">
-        <v>5.14115642</v>
+        <v>5.19847242</v>
       </c>
       <c r="D166" t="n">
-        <v>45.9</v>
+        <v>48.98</v>
       </c>
       <c r="E166" t="n">
-        <v>46.78</v>
+        <v>49.94</v>
       </c>
       <c r="F166" t="n">
-        <v>45.26</v>
+        <v>48.18</v>
       </c>
       <c r="G166" t="n">
-        <v>46.08</v>
+        <v>49.44</v>
       </c>
       <c r="H166" t="n">
-        <v>0.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-150.87</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C167" t="n">
-        <v>5.12606942</v>
+        <v>5.20773242</v>
       </c>
       <c r="D167" t="n">
-        <v>47.7</v>
+        <v>49.44</v>
       </c>
       <c r="E167" t="n">
-        <v>48.9</v>
+        <v>49.44</v>
       </c>
       <c r="F167" t="n">
-        <v>46.64</v>
+        <v>46.74</v>
       </c>
       <c r="G167" t="n">
-        <v>46.84</v>
+        <v>47.4</v>
       </c>
       <c r="H167" t="n">
-        <v>1.65</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-236.76</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C168" t="n">
-        <v>5.10239342</v>
+        <v>5.19818142</v>
       </c>
       <c r="D168" t="n">
-        <v>46.92</v>
+        <v>47</v>
       </c>
       <c r="E168" t="n">
-        <v>48.28</v>
+        <v>47</v>
       </c>
       <c r="F168" t="n">
-        <v>46.84</v>
+        <v>45.86</v>
       </c>
       <c r="G168" t="n">
-        <v>47.36</v>
+        <v>46.28</v>
       </c>
       <c r="H168" t="n">
-        <v>1.11</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-36.92</v>
+        <v>-254.06</v>
       </c>
       <c r="C169" t="n">
-        <v>5.09870142</v>
+        <v>5.17277542</v>
       </c>
       <c r="D169" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="E169" t="n">
-        <v>47.56</v>
+        <v>47.18</v>
       </c>
       <c r="F169" t="n">
-        <v>45.72</v>
+        <v>45.76</v>
       </c>
       <c r="G169" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="H169" t="n">
-        <v>-2.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>64.78</v>
+        <v>-316.19</v>
       </c>
       <c r="C170" t="n">
-        <v>5.10517942</v>
+        <v>5.14115642</v>
       </c>
       <c r="D170" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="E170" t="n">
-        <v>48.42</v>
+        <v>46.78</v>
       </c>
       <c r="F170" t="n">
-        <v>46.26</v>
+        <v>45.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.6</v>
+        <v>46.08</v>
       </c>
       <c r="H170" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-44.41</v>
+        <v>-150.87</v>
       </c>
       <c r="C171" t="n">
-        <v>5.10073842</v>
+        <v>5.12606942</v>
       </c>
       <c r="D171" t="n">
-        <v>47.06</v>
+        <v>47.7</v>
       </c>
       <c r="E171" t="n">
-        <v>48.98</v>
+        <v>48.9</v>
       </c>
       <c r="F171" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="G171" t="n">
-        <v>48.52</v>
+        <v>46.84</v>
       </c>
       <c r="H171" t="n">
-        <v>4.12</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-124.97</v>
+        <v>-236.76</v>
       </c>
       <c r="C172" t="n">
-        <v>5.08824142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D172" t="n">
-        <v>47.6</v>
+        <v>46.92</v>
       </c>
       <c r="E172" t="n">
-        <v>48.08</v>
+        <v>48.28</v>
       </c>
       <c r="F172" t="n">
-        <v>46.72</v>
+        <v>46.84</v>
       </c>
       <c r="G172" t="n">
-        <v>46.76</v>
+        <v>47.36</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.63</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-272.6</v>
+        <v>-36.92</v>
       </c>
       <c r="C173" t="n">
-        <v>5.06098142</v>
+        <v>5.09870142</v>
       </c>
       <c r="D173" t="n">
-        <v>46.76</v>
+        <v>47</v>
       </c>
       <c r="E173" t="n">
-        <v>48.3</v>
+        <v>47.56</v>
       </c>
       <c r="F173" t="n">
-        <v>46.02</v>
+        <v>45.72</v>
       </c>
       <c r="G173" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="H173" t="n">
-        <v>1.41</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>83.54000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="C174" t="n">
-        <v>5.06933542</v>
+        <v>5.10517942</v>
       </c>
       <c r="D174" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="E174" t="n">
-        <v>47.92</v>
+        <v>48.42</v>
       </c>
       <c r="F174" t="n">
-        <v>46.46</v>
+        <v>46.26</v>
       </c>
       <c r="G174" t="n">
-        <v>47.2</v>
+        <v>46.6</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.46</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-232.94</v>
+        <v>-44.41</v>
       </c>
       <c r="C175" t="n">
-        <v>5.04604142</v>
+        <v>5.10073842</v>
       </c>
       <c r="D175" t="n">
-        <v>47.2</v>
+        <v>47.06</v>
       </c>
       <c r="E175" t="n">
-        <v>48.84</v>
+        <v>48.98</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.56</v>
+        <v>48.52</v>
       </c>
       <c r="H175" t="n">
-        <v>2.88</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-101.2265</v>
+        <v>-124.97</v>
       </c>
       <c r="C176" t="n">
-        <v>5.03591877</v>
+        <v>5.08824142</v>
       </c>
       <c r="D176" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="E176" t="n">
-        <v>49.46</v>
+        <v>48.08</v>
       </c>
       <c r="F176" t="n">
-        <v>48.24</v>
+        <v>46.72</v>
       </c>
       <c r="G176" t="n">
-        <v>48.78</v>
+        <v>46.76</v>
       </c>
       <c r="H176" t="n">
-        <v>0.45</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-146.01</v>
+        <v>-272.6</v>
       </c>
       <c r="C177" t="n">
-        <v>5.02131777</v>
+        <v>5.06098142</v>
       </c>
       <c r="D177" t="n">
-        <v>49.22</v>
+        <v>46.76</v>
       </c>
       <c r="E177" t="n">
-        <v>51</v>
+        <v>48.3</v>
       </c>
       <c r="F177" t="n">
-        <v>49.22</v>
+        <v>46.02</v>
       </c>
       <c r="G177" t="n">
-        <v>50.4</v>
+        <v>47.42</v>
       </c>
       <c r="H177" t="n">
-        <v>3.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>14.25</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>5.02274277</v>
+        <v>5.06933542</v>
       </c>
       <c r="D178" t="n">
-        <v>50.55</v>
+        <v>47.42</v>
       </c>
       <c r="E178" t="n">
-        <v>51</v>
+        <v>47.92</v>
       </c>
       <c r="F178" t="n">
-        <v>48.2</v>
+        <v>46.46</v>
       </c>
       <c r="G178" t="n">
-        <v>48.94</v>
+        <v>47.2</v>
       </c>
       <c r="H178" t="n">
-        <v>-2.9</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7.54</v>
+        <v>-232.94</v>
       </c>
       <c r="C179" t="n">
-        <v>5.02349677</v>
+        <v>5.04604142</v>
       </c>
       <c r="D179" t="n">
-        <v>49.96</v>
+        <v>47.2</v>
       </c>
       <c r="E179" t="n">
-        <v>49.98</v>
+        <v>48.84</v>
       </c>
       <c r="F179" t="n">
-        <v>48.72</v>
+        <v>46.7</v>
       </c>
       <c r="G179" t="n">
-        <v>49.12</v>
+        <v>48.56</v>
       </c>
       <c r="H179" t="n">
-        <v>0.37</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>29.93</v>
+        <v>-101.2265</v>
       </c>
       <c r="C180" t="n">
-        <v>5.02648977</v>
+        <v>5.03591877</v>
       </c>
       <c r="D180" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="E180" t="n">
-        <v>49.36</v>
+        <v>49.46</v>
       </c>
       <c r="F180" t="n">
-        <v>48.18</v>
+        <v>48.24</v>
       </c>
       <c r="G180" t="n">
-        <v>48.64</v>
+        <v>48.78</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.98</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-93.37</v>
+        <v>-146.01</v>
       </c>
       <c r="C181" t="n">
-        <v>5.01715277</v>
+        <v>5.02131777</v>
       </c>
       <c r="D181" t="n">
-        <v>48.4</v>
+        <v>49.22</v>
       </c>
       <c r="E181" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F181" t="n">
-        <v>47.2</v>
+        <v>49.22</v>
       </c>
       <c r="G181" t="n">
-        <v>47.64</v>
+        <v>50.4</v>
       </c>
       <c r="H181" t="n">
-        <v>-2.06</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-93.65000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C182" t="n">
-        <v>5.00778777</v>
+        <v>5.02274277</v>
       </c>
       <c r="D182" t="n">
-        <v>47.64</v>
+        <v>50.55</v>
       </c>
       <c r="E182" t="n">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="F182" t="n">
-        <v>47.22</v>
+        <v>48.2</v>
       </c>
       <c r="G182" t="n">
-        <v>48.96</v>
+        <v>48.94</v>
       </c>
       <c r="H182" t="n">
-        <v>2.77</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>28.06</v>
+        <v>7.54</v>
       </c>
       <c r="C183" t="n">
-        <v>5.01059377</v>
+        <v>5.02349677</v>
       </c>
       <c r="D183" t="n">
-        <v>48.36</v>
+        <v>49.96</v>
       </c>
       <c r="E183" t="n">
-        <v>48.76</v>
+        <v>49.98</v>
       </c>
       <c r="F183" t="n">
-        <v>47.52</v>
+        <v>48.72</v>
       </c>
       <c r="G183" t="n">
-        <v>47.98</v>
+        <v>49.12</v>
       </c>
       <c r="H183" t="n">
-        <v>-2</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-160.94</v>
+        <v>29.93</v>
       </c>
       <c r="C184" t="n">
-        <v>4.99449977</v>
+        <v>5.02648977</v>
       </c>
       <c r="D184" t="n">
-        <v>47.98</v>
+        <v>49.1</v>
       </c>
       <c r="E184" t="n">
-        <v>48.46</v>
+        <v>49.36</v>
       </c>
       <c r="F184" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="G184" t="n">
-        <v>48.08</v>
+        <v>48.64</v>
       </c>
       <c r="H184" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>76.84999999999999</v>
+        <v>-93.37</v>
       </c>
       <c r="C185" t="n">
-        <v>5.00218477</v>
+        <v>5.01715277</v>
       </c>
       <c r="D185" t="n">
-        <v>49.54</v>
+        <v>48.4</v>
       </c>
       <c r="E185" t="n">
-        <v>50.5</v>
+        <v>48.4</v>
       </c>
       <c r="F185" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="G185" t="n">
-        <v>49.68</v>
+        <v>47.64</v>
       </c>
       <c r="H185" t="n">
-        <v>3.33</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-70.88</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C186" t="n">
-        <v>4.99509677</v>
+        <v>5.00778777</v>
       </c>
       <c r="D186" t="n">
-        <v>51.9</v>
+        <v>47.64</v>
       </c>
       <c r="E186" t="n">
-        <v>55.6</v>
+        <v>49.3</v>
       </c>
       <c r="F186" t="n">
-        <v>51.9</v>
+        <v>47.22</v>
       </c>
       <c r="G186" t="n">
-        <v>54.6</v>
+        <v>48.96</v>
       </c>
       <c r="H186" t="n">
-        <v>9.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-223.97</v>
+        <v>28.06</v>
       </c>
       <c r="C187" t="n">
-        <v>4.97269977</v>
+        <v>5.01059377</v>
       </c>
       <c r="D187" t="n">
-        <v>54.7</v>
+        <v>48.36</v>
       </c>
       <c r="E187" t="n">
-        <v>56.1</v>
+        <v>48.76</v>
       </c>
       <c r="F187" t="n">
-        <v>53.7</v>
+        <v>47.52</v>
       </c>
       <c r="G187" t="n">
-        <v>54.25</v>
+        <v>47.98</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.64</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-908.88</v>
+        <v>-160.94</v>
       </c>
       <c r="C188" t="n">
-        <v>4.88181177</v>
+        <v>4.99449977</v>
       </c>
       <c r="D188" t="n">
-        <v>52.85</v>
+        <v>47.98</v>
       </c>
       <c r="E188" t="n">
-        <v>53.8</v>
+        <v>48.46</v>
       </c>
       <c r="F188" t="n">
-        <v>51.3</v>
+        <v>47.32</v>
       </c>
       <c r="G188" t="n">
-        <v>53.4</v>
+        <v>48.08</v>
       </c>
       <c r="H188" t="n">
-        <v>-1.57</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-219</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C189" t="n">
-        <v>4.85991177</v>
+        <v>5.00218477</v>
       </c>
       <c r="D189" t="n">
-        <v>52.75</v>
+        <v>49.54</v>
       </c>
       <c r="E189" t="n">
-        <v>54.45</v>
+        <v>50.5</v>
       </c>
       <c r="F189" t="n">
-        <v>51.45</v>
+        <v>48.9</v>
       </c>
       <c r="G189" t="n">
-        <v>51.85</v>
+        <v>49.68</v>
       </c>
       <c r="H189" t="n">
-        <v>-2.9</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>81.19</v>
+        <v>-70.88</v>
       </c>
       <c r="C190" t="n">
-        <v>4.86803077</v>
+        <v>4.99509677</v>
       </c>
       <c r="D190" t="n">
-        <v>51.85</v>
+        <v>51.9</v>
       </c>
       <c r="E190" t="n">
-        <v>51.85</v>
+        <v>55.6</v>
       </c>
       <c r="F190" t="n">
-        <v>49.6</v>
+        <v>51.9</v>
       </c>
       <c r="G190" t="n">
-        <v>50.45</v>
+        <v>54.6</v>
       </c>
       <c r="H190" t="n">
-        <v>-2.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7.21</v>
+        <v>-223.97</v>
       </c>
       <c r="C191" t="n">
-        <v>4.86875177</v>
+        <v>4.97269977</v>
       </c>
       <c r="D191" t="n">
-        <v>50.05</v>
+        <v>54.7</v>
       </c>
       <c r="E191" t="n">
-        <v>50.8</v>
+        <v>56.1</v>
       </c>
       <c r="F191" t="n">
-        <v>49.52</v>
+        <v>53.7</v>
       </c>
       <c r="G191" t="n">
-        <v>50.65</v>
+        <v>54.25</v>
       </c>
       <c r="H191" t="n">
-        <v>0.4</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>144.28</v>
+        <v>-908.88</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88317977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D192" t="n">
-        <v>50</v>
+        <v>52.85</v>
       </c>
       <c r="E192" t="n">
-        <v>50.6</v>
+        <v>53.8</v>
       </c>
       <c r="F192" t="n">
-        <v>49.08</v>
+        <v>51.3</v>
       </c>
       <c r="G192" t="n">
-        <v>49.12</v>
+        <v>53.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-3.02</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-41.02</v>
+        <v>-219</v>
       </c>
       <c r="C193" t="n">
-        <v>4.87907777</v>
+        <v>4.85991177</v>
       </c>
       <c r="D193" t="n">
-        <v>49.18</v>
+        <v>52.75</v>
       </c>
       <c r="E193" t="n">
-        <v>50.1</v>
+        <v>54.45</v>
       </c>
       <c r="F193" t="n">
-        <v>48.82</v>
+        <v>51.45</v>
       </c>
       <c r="G193" t="n">
-        <v>49.92</v>
+        <v>51.85</v>
       </c>
       <c r="H193" t="n">
-        <v>1.63</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>68.70999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="C194" t="n">
-        <v>4.88594877</v>
+        <v>4.86803077</v>
       </c>
       <c r="D194" t="n">
-        <v>50.5</v>
+        <v>51.85</v>
       </c>
       <c r="E194" t="n">
-        <v>50.95</v>
+        <v>51.85</v>
       </c>
       <c r="F194" t="n">
-        <v>49.74</v>
+        <v>49.6</v>
       </c>
       <c r="G194" t="n">
-        <v>50.1</v>
+        <v>50.45</v>
       </c>
       <c r="H194" t="n">
-        <v>0.36</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>20.01</v>
+        <v>7.21</v>
       </c>
       <c r="C195" t="n">
-        <v>4.88794977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D195" t="n">
-        <v>50</v>
+        <v>50.05</v>
       </c>
       <c r="E195" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F195" t="n">
-        <v>49.04</v>
+        <v>49.52</v>
       </c>
       <c r="G195" t="n">
-        <v>49.06</v>
+        <v>50.65</v>
       </c>
       <c r="H195" t="n">
-        <v>-2.08</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-18.77</v>
+        <v>144.28</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88607277</v>
+        <v>4.88317977</v>
       </c>
       <c r="D196" t="n">
+        <v>50</v>
+      </c>
+      <c r="E196" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="F196" t="n">
         <v>49.08</v>
       </c>
-      <c r="E196" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="F196" t="n">
-        <v>48.7</v>
-      </c>
       <c r="G196" t="n">
-        <v>49.4</v>
+        <v>49.12</v>
       </c>
       <c r="H196" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>95.14</v>
+        <v>-41.02</v>
       </c>
       <c r="C197" t="n">
-        <v>4.89558677</v>
+        <v>4.87907777</v>
       </c>
       <c r="D197" t="n">
-        <v>48.66</v>
+        <v>49.18</v>
       </c>
       <c r="E197" t="n">
-        <v>49.22</v>
+        <v>50.1</v>
       </c>
       <c r="F197" t="n">
-        <v>48.02</v>
+        <v>48.82</v>
       </c>
       <c r="G197" t="n">
-        <v>48.22</v>
+        <v>49.92</v>
       </c>
       <c r="H197" t="n">
-        <v>-2.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>6.47</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C198" t="n">
-        <v>4.89623377</v>
+        <v>4.88594877</v>
       </c>
       <c r="D198" t="n">
-        <v>48.22</v>
+        <v>50.5</v>
       </c>
       <c r="E198" t="n">
-        <v>48.22</v>
+        <v>50.95</v>
       </c>
       <c r="F198" t="n">
-        <v>47.46</v>
+        <v>49.74</v>
       </c>
       <c r="G198" t="n">
-        <v>47.46</v>
+        <v>50.1</v>
       </c>
       <c r="H198" t="n">
-        <v>-1.58</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>78.34</v>
+        <v>20.01</v>
       </c>
       <c r="C199" t="n">
-        <v>4.90406777</v>
+        <v>4.88794977</v>
       </c>
       <c r="D199" t="n">
-        <v>47.86</v>
+        <v>50</v>
       </c>
       <c r="E199" t="n">
-        <v>48.68</v>
+        <v>50.5</v>
       </c>
       <c r="F199" t="n">
-        <v>47.7</v>
+        <v>49.04</v>
       </c>
       <c r="G199" t="n">
-        <v>48.48</v>
+        <v>49.06</v>
       </c>
       <c r="H199" t="n">
-        <v>2.15</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>12.2</v>
+        <v>-18.77</v>
       </c>
       <c r="C200" t="n">
-        <v>4.90528777</v>
+        <v>4.88607277</v>
       </c>
       <c r="D200" t="n">
-        <v>48.1</v>
+        <v>49.08</v>
       </c>
       <c r="E200" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="F200" t="n">
         <v>48.7</v>
       </c>
-      <c r="F200" t="n">
-        <v>47.38</v>
-      </c>
       <c r="G200" t="n">
-        <v>47.88</v>
+        <v>49.4</v>
       </c>
       <c r="H200" t="n">
-        <v>-1.24</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-50.42</v>
+        <v>95.14</v>
       </c>
       <c r="C201" t="n">
-        <v>4.90024577</v>
+        <v>4.89558677</v>
       </c>
       <c r="D201" t="n">
-        <v>47.34</v>
+        <v>48.66</v>
       </c>
       <c r="E201" t="n">
-        <v>48.28</v>
+        <v>49.22</v>
       </c>
       <c r="F201" t="n">
-        <v>47.06</v>
+        <v>48.02</v>
       </c>
       <c r="G201" t="n">
-        <v>47.9</v>
+        <v>48.22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.04</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7.38</v>
+        <v>6.47</v>
       </c>
       <c r="C202" t="n">
-        <v>4.90098377</v>
+        <v>4.89623377</v>
       </c>
       <c r="D202" t="n">
-        <v>49.98</v>
+        <v>48.22</v>
       </c>
       <c r="E202" t="n">
-        <v>51.2</v>
+        <v>48.22</v>
       </c>
       <c r="F202" t="n">
-        <v>49.76</v>
+        <v>47.46</v>
       </c>
       <c r="G202" t="n">
-        <v>50.55</v>
+        <v>47.46</v>
       </c>
       <c r="H202" t="n">
-        <v>5.53</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.19</v>
+        <v>78.34</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90100277</v>
+        <v>4.90406777</v>
       </c>
       <c r="D203" t="n">
-        <v>50.55</v>
+        <v>47.86</v>
       </c>
       <c r="E203" t="n">
-        <v>51.8</v>
+        <v>48.68</v>
       </c>
       <c r="F203" t="n">
-        <v>50.5</v>
+        <v>47.7</v>
       </c>
       <c r="G203" t="n">
-        <v>51.2</v>
+        <v>48.48</v>
       </c>
       <c r="H203" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-404.07</v>
+        <v>12.2</v>
       </c>
       <c r="C204" t="n">
-        <v>4.86059577</v>
+        <v>4.90528777</v>
       </c>
       <c r="D204" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="E204" t="n">
-        <v>51</v>
+        <v>48.7</v>
       </c>
       <c r="F204" t="n">
-        <v>49.3</v>
+        <v>47.38</v>
       </c>
       <c r="G204" t="n">
-        <v>49.46</v>
+        <v>47.88</v>
       </c>
       <c r="H204" t="n">
-        <v>-3.4</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-104.42</v>
+        <v>-50.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.85015377</v>
+        <v>4.90024577</v>
       </c>
       <c r="D205" t="n">
-        <v>48.86</v>
+        <v>47.34</v>
       </c>
       <c r="E205" t="n">
-        <v>49.74</v>
+        <v>48.28</v>
       </c>
       <c r="F205" t="n">
-        <v>47.6</v>
+        <v>47.06</v>
       </c>
       <c r="G205" t="n">
-        <v>47.68</v>
+        <v>47.9</v>
       </c>
       <c r="H205" t="n">
-        <v>-3.6</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-9.27</v>
+        <v>7.38</v>
       </c>
       <c r="C206" t="n">
-        <v>4.84922677</v>
+        <v>4.90098377</v>
       </c>
       <c r="D206" t="n">
-        <v>47.68</v>
+        <v>49.98</v>
       </c>
       <c r="E206" t="n">
-        <v>48.9</v>
+        <v>51.2</v>
       </c>
       <c r="F206" t="n">
-        <v>47.32</v>
+        <v>49.76</v>
       </c>
       <c r="G206" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="H206" t="n">
-        <v>0.88</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-62.41</v>
+        <v>0.19</v>
       </c>
       <c r="C207" t="n">
-        <v>4.84298577</v>
+        <v>4.90100277</v>
       </c>
       <c r="D207" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="E207" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="F207" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="G207" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="H207" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-4.06</v>
+        <v>-404.07</v>
       </c>
       <c r="C208" t="n">
-        <v>4.84257977</v>
+        <v>4.86059577</v>
       </c>
       <c r="D208" t="n">
-        <v>47.8</v>
+        <v>50.3</v>
       </c>
       <c r="E208" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="F208" t="n">
-        <v>47.16</v>
+        <v>49.3</v>
       </c>
       <c r="G208" t="n">
-        <v>47.98</v>
+        <v>49.46</v>
       </c>
       <c r="H208" t="n">
-        <v>-1.28</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>107.65</v>
+        <v>-104.42</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85334477</v>
+        <v>4.85015377</v>
       </c>
       <c r="D209" t="n">
-        <v>47.86</v>
+        <v>48.86</v>
       </c>
       <c r="E209" t="n">
-        <v>48.44</v>
+        <v>49.74</v>
       </c>
       <c r="F209" t="n">
-        <v>46.5</v>
+        <v>47.6</v>
       </c>
       <c r="G209" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.33</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>137.46</v>
+        <v>-9.27</v>
       </c>
       <c r="C210" t="n">
-        <v>4.86709077</v>
+        <v>4.84922677</v>
       </c>
       <c r="D210" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="E210" t="n">
-        <v>48.22</v>
+        <v>48.9</v>
       </c>
       <c r="F210" t="n">
-        <v>46.6</v>
+        <v>47.32</v>
       </c>
       <c r="G210" t="n">
-        <v>47.06</v>
+        <v>48.1</v>
       </c>
       <c r="H210" t="n">
-        <v>-1.59</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>154.04</v>
+        <v>-62.41</v>
       </c>
       <c r="C211" t="n">
-        <v>4.88249477</v>
+        <v>4.84298577</v>
       </c>
       <c r="D211" t="n">
-        <v>46.68</v>
+        <v>48.1</v>
       </c>
       <c r="E211" t="n">
-        <v>46.76</v>
+        <v>49</v>
       </c>
       <c r="F211" t="n">
-        <v>44.56</v>
+        <v>47.5</v>
       </c>
       <c r="G211" t="n">
-        <v>45.86</v>
+        <v>48.6</v>
       </c>
       <c r="H211" t="n">
-        <v>-2.55</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>78.03</v>
+        <v>-4.06</v>
       </c>
       <c r="C212" t="n">
-        <v>4.89029777</v>
+        <v>4.84257977</v>
       </c>
       <c r="D212" t="n">
-        <v>46.56</v>
+        <v>47.8</v>
       </c>
       <c r="E212" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="F212" t="n">
-        <v>46.2</v>
+        <v>47.16</v>
       </c>
       <c r="G212" t="n">
-        <v>46.38</v>
+        <v>47.98</v>
       </c>
       <c r="H212" t="n">
-        <v>1.13</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>401.67</v>
+        <v>107.65</v>
       </c>
       <c r="C213" t="n">
-        <v>4.93046477</v>
+        <v>4.85334477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.28</v>
+        <v>47.86</v>
       </c>
       <c r="E213" t="n">
-        <v>48.88</v>
+        <v>48.44</v>
       </c>
       <c r="F213" t="n">
-        <v>47.12</v>
+        <v>46.5</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>3.1</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-79.33</v>
+        <v>137.46</v>
       </c>
       <c r="C214" t="n">
-        <v>4.92253177</v>
+        <v>4.86709077</v>
       </c>
       <c r="D214" t="n">
-        <v>48.1</v>
+        <v>47.82</v>
       </c>
       <c r="E214" t="n">
-        <v>50.45</v>
+        <v>48.22</v>
       </c>
       <c r="F214" t="n">
-        <v>48.04</v>
+        <v>46.6</v>
       </c>
       <c r="G214" t="n">
-        <v>50.4</v>
+        <v>47.06</v>
       </c>
       <c r="H214" t="n">
-        <v>5.4</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-415.48</v>
+        <v>154.04</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88098377</v>
+        <v>4.88249477</v>
       </c>
       <c r="D215" t="n">
-        <v>49.44</v>
+        <v>46.68</v>
       </c>
       <c r="E215" t="n">
-        <v>50.15</v>
+        <v>46.76</v>
       </c>
       <c r="F215" t="n">
-        <v>48.88</v>
+        <v>44.56</v>
       </c>
       <c r="G215" t="n">
-        <v>49.32</v>
+        <v>45.86</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.14</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-394.96</v>
+        <v>78.03</v>
       </c>
       <c r="C216" t="n">
-        <v>4.84148777</v>
+        <v>4.89029777</v>
       </c>
       <c r="D216" t="n">
-        <v>49.08</v>
+        <v>46.56</v>
       </c>
       <c r="E216" t="n">
-        <v>49.08</v>
+        <v>48</v>
       </c>
       <c r="F216" t="n">
-        <v>47.2</v>
+        <v>46.2</v>
       </c>
       <c r="G216" t="n">
-        <v>47.62</v>
+        <v>46.38</v>
       </c>
       <c r="H216" t="n">
-        <v>-3.45</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-39.23</v>
+        <v>401.67</v>
       </c>
       <c r="C217" t="n">
-        <v>4.83756477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.2</v>
+        <v>47.28</v>
       </c>
       <c r="E217" t="n">
-        <v>47.2</v>
+        <v>48.88</v>
       </c>
       <c r="F217" t="n">
-        <v>46.42</v>
+        <v>47.12</v>
       </c>
       <c r="G217" t="n">
-        <v>46.48</v>
+        <v>47.82</v>
       </c>
       <c r="H217" t="n">
-        <v>-2.39</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>219.67</v>
+        <v>-79.33</v>
       </c>
       <c r="C218" t="n">
-        <v>4.85953177</v>
+        <v>4.92253177</v>
       </c>
       <c r="D218" t="n">
-        <v>45.74</v>
+        <v>48.1</v>
       </c>
       <c r="E218" t="n">
-        <v>46.44</v>
+        <v>50.45</v>
       </c>
       <c r="F218" t="n">
-        <v>45.38</v>
+        <v>48.04</v>
       </c>
       <c r="G218" t="n">
-        <v>46.34</v>
+        <v>50.4</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>111.68</v>
+        <v>-415.48</v>
       </c>
       <c r="C219" t="n">
-        <v>4.87069977</v>
+        <v>4.88098377</v>
       </c>
       <c r="D219" t="n">
-        <v>45.9</v>
+        <v>49.44</v>
       </c>
       <c r="E219" t="n">
-        <v>47.8</v>
+        <v>50.15</v>
       </c>
       <c r="F219" t="n">
-        <v>45.84</v>
+        <v>48.88</v>
       </c>
       <c r="G219" t="n">
-        <v>47.52</v>
+        <v>49.32</v>
       </c>
       <c r="H219" t="n">
-        <v>2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>47.5</v>
+        <v>-394.96</v>
       </c>
       <c r="C220" t="n">
-        <v>4.87544977</v>
+        <v>4.84148777</v>
       </c>
       <c r="D220" t="n">
-        <v>47.52</v>
+        <v>49.08</v>
       </c>
       <c r="E220" t="n">
-        <v>48.06</v>
+        <v>49.08</v>
       </c>
       <c r="F220" t="n">
-        <v>46.06</v>
+        <v>47.2</v>
       </c>
       <c r="G220" t="n">
-        <v>46.12</v>
+        <v>47.62</v>
       </c>
       <c r="H220" t="n">
-        <v>-2.95</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-30.32</v>
+        <v>-39.23</v>
       </c>
       <c r="C221" t="n">
-        <v>4.87241777</v>
+        <v>4.83756477</v>
       </c>
       <c r="D221" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E221" t="n">
-        <v>47.42</v>
+        <v>47.2</v>
       </c>
       <c r="F221" t="n">
-        <v>45.94</v>
+        <v>46.42</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>0.78</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>15.46</v>
+        <v>219.67</v>
       </c>
       <c r="C222" t="n">
-        <v>4.87396377</v>
+        <v>4.85953177</v>
       </c>
       <c r="D222" t="n">
-        <v>46.9</v>
+        <v>45.74</v>
       </c>
       <c r="E222" t="n">
-        <v>47.5</v>
+        <v>46.44</v>
       </c>
       <c r="F222" t="n">
-        <v>44.94</v>
+        <v>45.38</v>
       </c>
       <c r="G222" t="n">
-        <v>46.88</v>
+        <v>46.34</v>
       </c>
       <c r="H222" t="n">
-        <v>0.86</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>57.59</v>
+        <v>111.68</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87972277</v>
+        <v>4.87069977</v>
       </c>
       <c r="D223" t="n">
-        <v>46.9</v>
+        <v>45.9</v>
       </c>
       <c r="E223" t="n">
-        <v>48.46</v>
+        <v>47.8</v>
       </c>
       <c r="F223" t="n">
-        <v>46.8</v>
+        <v>45.84</v>
       </c>
       <c r="G223" t="n">
-        <v>47.56</v>
+        <v>47.52</v>
       </c>
       <c r="H223" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>112.19</v>
+        <v>47.5</v>
       </c>
       <c r="C224" t="n">
-        <v>4.89094177</v>
+        <v>4.87544977</v>
       </c>
       <c r="D224" t="n">
-        <v>47.54</v>
+        <v>47.52</v>
       </c>
       <c r="E224" t="n">
-        <v>47.54</v>
+        <v>48.06</v>
       </c>
       <c r="F224" t="n">
-        <v>44.82</v>
+        <v>46.06</v>
       </c>
       <c r="G224" t="n">
-        <v>45.48</v>
+        <v>46.12</v>
       </c>
       <c r="H224" t="n">
-        <v>-4.37</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-30.32</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.87241777</v>
+      </c>
+      <c r="D225" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="E225" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F225" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="G225" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="C226" t="n">
+        <v>4.87396377</v>
+      </c>
+      <c r="D226" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="E226" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F226" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="G226" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4.87972277</v>
+      </c>
+      <c r="D227" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="E227" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="F227" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G227" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>112.19</v>
+      </c>
+      <c r="C228" t="n">
+        <v>4.89094177</v>
+      </c>
+      <c r="D228" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="E228" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="F228" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="G228" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B225" t="n">
+      <c r="B229" t="n">
         <v>0</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C229" t="n">
         <v>4.89094177</v>
       </c>
-      <c r="D225" t="n">
+      <c r="D229" t="n">
         <v>45</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E229" t="n">
         <v>45.8</v>
       </c>
-      <c r="F225" t="n">
+      <c r="F229" t="n">
         <v>44.68</v>
       </c>
-      <c r="G225" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="H225" t="n">
-        <v>-0.31</v>
+      <c r="G229" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="H229" t="n">
+        <v>-0.88</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E79" t="n">
-        <v>73.34999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="F79" t="n">
-        <v>71.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>73.34999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="F80" t="n">
-        <v>71.5</v>
+        <v>69.55</v>
       </c>
       <c r="G80" t="n">
-        <v>72.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4162 +2693,4050 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>72.8</v>
+        <v>70.3</v>
       </c>
       <c r="E81" t="n">
-        <v>73.34999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="F81" t="n">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="G81" t="n">
-        <v>72.3</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>-37.37</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D82" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E82" t="n">
-        <v>72.25</v>
+        <v>73.5</v>
       </c>
       <c r="F82" t="n">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G82" t="n">
-        <v>72.09999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.28</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D83" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E83" t="n">
-        <v>71.75</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>69.55</v>
+        <v>70.5</v>
       </c>
       <c r="G83" t="n">
-        <v>70.09999999999999</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>-2.77</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>39.15</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29754581</v>
+        <v>5.29772381</v>
       </c>
       <c r="D84" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="E84" t="n">
-        <v>73.3</v>
+        <v>71.8</v>
       </c>
       <c r="F84" t="n">
-        <v>70.3</v>
+        <v>68.55</v>
       </c>
       <c r="G84" t="n">
-        <v>72.84999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>3.92</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-37.37</v>
+        <v>-32.03</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29380881</v>
+        <v>5.29452081</v>
       </c>
       <c r="D85" t="n">
-        <v>71.8</v>
+        <v>69.5</v>
       </c>
       <c r="E85" t="n">
-        <v>73.5</v>
+        <v>69.5</v>
       </c>
       <c r="F85" t="n">
-        <v>71.3</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>71.75</v>
+        <v>68.75</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.51</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-245.51</v>
       </c>
       <c r="C86" t="n">
-        <v>5.29380881</v>
+        <v>5.26996981</v>
       </c>
       <c r="D86" t="n">
-        <v>72.8</v>
+        <v>67.75</v>
       </c>
       <c r="E86" t="n">
-        <v>73.15000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>70.5</v>
+        <v>67</v>
       </c>
       <c r="G86" t="n">
-        <v>71.84999999999999</v>
+        <v>68</v>
       </c>
       <c r="H86" t="n">
-        <v>0.14</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39.15</v>
+        <v>24.99</v>
       </c>
       <c r="C87" t="n">
-        <v>5.29772381</v>
+        <v>5.27246881</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
       <c r="F87" t="n">
-        <v>68.55</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>68.65000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="H87" t="n">
-        <v>-4.45</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-32.03</v>
+        <v>-70.5937</v>
       </c>
       <c r="C88" t="n">
-        <v>5.29452081</v>
+        <v>5.26540944</v>
       </c>
       <c r="D88" t="n">
-        <v>69.5</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>69.5</v>
+        <v>66.8</v>
       </c>
       <c r="F88" t="n">
-        <v>68.15000000000001</v>
+        <v>64.45</v>
       </c>
       <c r="G88" t="n">
-        <v>68.75</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-245.51</v>
+        <v>-83.42</v>
       </c>
       <c r="C89" t="n">
-        <v>5.26996981</v>
+        <v>5.25706744</v>
       </c>
       <c r="D89" t="n">
-        <v>67.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>70.15000000000001</v>
+        <v>68</v>
       </c>
       <c r="F89" t="n">
-        <v>67</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>68</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.09</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24.99</v>
+        <v>32.9872</v>
       </c>
       <c r="C90" t="n">
-        <v>5.27246881</v>
+        <v>5.26036616</v>
       </c>
       <c r="D90" t="n">
-        <v>68.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="E90" t="n">
-        <v>69</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>65.65000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>66.55</v>
+        <v>67.45</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.13</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-70.5937</v>
+        <v>-168.98</v>
       </c>
       <c r="C91" t="n">
-        <v>5.26540944</v>
+        <v>5.24346816</v>
       </c>
       <c r="D91" t="n">
-        <v>65.84999999999999</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>66.8</v>
+        <v>69</v>
       </c>
       <c r="F91" t="n">
-        <v>64.45</v>
+        <v>64.7</v>
       </c>
       <c r="G91" t="n">
-        <v>65.84999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-83.42</v>
+        <v>-195.54</v>
       </c>
       <c r="C92" t="n">
-        <v>5.25706744</v>
+        <v>5.22391416</v>
       </c>
       <c r="D92" t="n">
-        <v>66.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>68</v>
+        <v>70.2</v>
       </c>
       <c r="F92" t="n">
-        <v>65.09999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="G92" t="n">
-        <v>65.59999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.38</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>32.9872</v>
+        <v>16.18</v>
       </c>
       <c r="C93" t="n">
-        <v>5.26036616</v>
+        <v>5.22553216</v>
       </c>
       <c r="D93" t="n">
-        <v>65.5</v>
+        <v>69.25</v>
       </c>
       <c r="E93" t="n">
-        <v>67.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.34999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="G93" t="n">
-        <v>67.45</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>2.82</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-168.98</v>
+        <v>13.87</v>
       </c>
       <c r="C94" t="n">
-        <v>5.24346816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D94" t="n">
-        <v>64.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E94" t="n">
-        <v>69</v>
+        <v>71.3</v>
       </c>
       <c r="F94" t="n">
-        <v>64.7</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>68.90000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>2.15</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-195.54</v>
+        <v>-145.08</v>
       </c>
       <c r="C95" t="n">
-        <v>5.22391416</v>
+        <v>5.21241116</v>
       </c>
       <c r="D95" t="n">
-        <v>69.90000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E95" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="F95" t="n">
-        <v>67.95</v>
+        <v>67.3</v>
       </c>
       <c r="G95" t="n">
-        <v>69.05</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.22</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>16.18</v>
+        <v>25.02</v>
       </c>
       <c r="C96" t="n">
-        <v>5.22553216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D96" t="n">
-        <v>69.25</v>
+        <v>67.5</v>
       </c>
       <c r="E96" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>69.05</v>
+        <v>66.3</v>
       </c>
       <c r="G96" t="n">
-        <v>69.84999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>1.16</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.87</v>
+        <v>-6.25</v>
       </c>
       <c r="C97" t="n">
-        <v>5.22691916</v>
+        <v>5.21428816</v>
       </c>
       <c r="D97" t="n">
-        <v>70.95</v>
+        <v>71.25</v>
       </c>
       <c r="E97" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="G97" t="n">
         <v>71.3</v>
       </c>
-      <c r="F97" t="n">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="G97" t="n">
-        <v>70.15000000000001</v>
-      </c>
       <c r="H97" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-145.08</v>
+        <v>-48.58</v>
       </c>
       <c r="C98" t="n">
-        <v>5.21241116</v>
+        <v>5.20943016</v>
       </c>
       <c r="D98" t="n">
-        <v>68.95</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>69</v>
+        <v>71.25</v>
       </c>
       <c r="F98" t="n">
-        <v>67.3</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>67.90000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>-3.21</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25.02</v>
+        <v>-197.18</v>
       </c>
       <c r="C99" t="n">
-        <v>5.21491316</v>
+        <v>5.18971216</v>
       </c>
       <c r="D99" t="n">
-        <v>67.5</v>
+        <v>66.2</v>
       </c>
       <c r="E99" t="n">
-        <v>70.09999999999999</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>66.3</v>
+        <v>65.8</v>
       </c>
       <c r="G99" t="n">
-        <v>69.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="H99" t="n">
-        <v>2.95</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-6.25</v>
+        <v>426.64</v>
       </c>
       <c r="C100" t="n">
-        <v>5.21428816</v>
+        <v>5.23237616</v>
       </c>
       <c r="D100" t="n">
-        <v>71.25</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>73.3</v>
+        <v>68.7</v>
       </c>
       <c r="F100" t="n">
-        <v>70.84999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>71.3</v>
+        <v>66.8</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-48.58</v>
+        <v>41.4993</v>
       </c>
       <c r="C101" t="n">
-        <v>5.20943016</v>
+        <v>5.23652609</v>
       </c>
       <c r="D101" t="n">
-        <v>70.65000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>71.25</v>
+        <v>66.05</v>
       </c>
       <c r="F101" t="n">
-        <v>66.34999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G101" t="n">
-        <v>66.84999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-6.24</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-197.18</v>
+        <v>-220.5688</v>
       </c>
       <c r="C102" t="n">
-        <v>5.18971216</v>
+        <v>5.21446921</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.34999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F102" t="n">
-        <v>65.8</v>
+        <v>63.45</v>
       </c>
       <c r="G102" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>426.64</v>
+        <v>215.27</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23237616</v>
+        <v>5.23599621</v>
       </c>
       <c r="D103" t="n">
-        <v>67</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>68.7</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>66.34999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="G103" t="n">
-        <v>66.8</v>
+        <v>70.45</v>
       </c>
       <c r="H103" t="n">
-        <v>1.21</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>41.4993</v>
+        <v>-160.53</v>
       </c>
       <c r="C104" t="n">
-        <v>5.23652609</v>
+        <v>5.21994321</v>
       </c>
       <c r="D104" t="n">
-        <v>65.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>66.05</v>
+        <v>70.8</v>
       </c>
       <c r="F104" t="n">
-        <v>64.2</v>
+        <v>68.7</v>
       </c>
       <c r="G104" t="n">
-        <v>64.8</v>
+        <v>69</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.99</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-220.5688</v>
+        <v>-304.01</v>
       </c>
       <c r="C105" t="n">
-        <v>5.21446921</v>
+        <v>5.18954221</v>
       </c>
       <c r="D105" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="E105" t="n">
-        <v>67.65000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F105" t="n">
-        <v>63.45</v>
+        <v>68.3</v>
       </c>
       <c r="G105" t="n">
-        <v>67.59999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H105" t="n">
-        <v>4.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>215.27</v>
+        <v>-30.3</v>
       </c>
       <c r="C106" t="n">
-        <v>5.23599621</v>
+        <v>5.18651221</v>
       </c>
       <c r="D106" t="n">
-        <v>69.59999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="E106" t="n">
-        <v>71.34999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>69.45</v>
+        <v>68</v>
       </c>
       <c r="G106" t="n">
-        <v>70.45</v>
+        <v>68.8</v>
       </c>
       <c r="H106" t="n">
-        <v>4.22</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-160.53</v>
+        <v>-92.3</v>
       </c>
       <c r="C107" t="n">
-        <v>5.21994321</v>
+        <v>5.17728221</v>
       </c>
       <c r="D107" t="n">
-        <v>69.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E107" t="n">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
       <c r="G107" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.06</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-304.01</v>
+        <v>25.43</v>
       </c>
       <c r="C108" t="n">
-        <v>5.18954221</v>
+        <v>5.17982521</v>
       </c>
       <c r="D108" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>71.5</v>
+        <v>71.45</v>
       </c>
       <c r="F108" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>70.05</v>
+        <v>71.2</v>
       </c>
       <c r="H108" t="n">
-        <v>1.52</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-30.3</v>
+        <v>136.53</v>
       </c>
       <c r="C109" t="n">
-        <v>5.18651221</v>
+        <v>5.19347821</v>
       </c>
       <c r="D109" t="n">
-        <v>68.05</v>
+        <v>71.2</v>
       </c>
       <c r="E109" t="n">
-        <v>69.34999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G109" t="n">
-        <v>68.8</v>
+        <v>71.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-92.3</v>
+        <v>-224.29</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17728221</v>
+        <v>5.17104921</v>
       </c>
       <c r="D110" t="n">
-        <v>68.8</v>
+        <v>73.45</v>
       </c>
       <c r="E110" t="n">
-        <v>69.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="F110" t="n">
-        <v>67.2</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>67.7</v>
+        <v>73.3</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.6</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>25.43</v>
+        <v>97.7422</v>
       </c>
       <c r="C111" t="n">
-        <v>5.17982521</v>
+        <v>5.18082343</v>
       </c>
       <c r="D111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="E111" t="n">
-        <v>71.45</v>
+        <v>73.5</v>
       </c>
       <c r="F111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G111" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>5.17</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>136.53</v>
+        <v>-116.85</v>
       </c>
       <c r="C112" t="n">
-        <v>5.19347821</v>
+        <v>5.16913843</v>
       </c>
       <c r="D112" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E112" t="n">
-        <v>73.40000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="F112" t="n">
-        <v>70</v>
+        <v>71.55</v>
       </c>
       <c r="G112" t="n">
-        <v>71.8</v>
+        <v>74.2</v>
       </c>
       <c r="H112" t="n">
-        <v>0.84</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-224.29</v>
+        <v>32.76</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17104921</v>
+        <v>5.17241443</v>
       </c>
       <c r="D113" t="n">
-        <v>73.45</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F113" t="n">
-        <v>71.65000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="G113" t="n">
-        <v>73.3</v>
+        <v>73.7</v>
       </c>
       <c r="H113" t="n">
-        <v>2.09</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>97.7422</v>
+        <v>-19.6</v>
       </c>
       <c r="C114" t="n">
-        <v>5.18082343</v>
+        <v>5.17045443</v>
       </c>
       <c r="D114" t="n">
-        <v>71.95</v>
+        <v>73.7</v>
       </c>
       <c r="E114" t="n">
-        <v>73.5</v>
+        <v>73.95</v>
       </c>
       <c r="F114" t="n">
-        <v>71.75</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.91</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-116.85</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>5.16913843</v>
+        <v>5.17787843</v>
       </c>
       <c r="D115" t="n">
-        <v>71.90000000000001</v>
+        <v>73.75</v>
       </c>
       <c r="E115" t="n">
-        <v>76.45</v>
+        <v>73.75</v>
       </c>
       <c r="F115" t="n">
-        <v>71.55</v>
+        <v>70.5</v>
       </c>
       <c r="G115" t="n">
-        <v>74.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>3.2</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>32.76</v>
+        <v>15.04</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17241443</v>
+        <v>5.17938243</v>
       </c>
       <c r="D116" t="n">
-        <v>74.09999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E116" t="n">
-        <v>75</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>73.25</v>
+        <v>70.95</v>
       </c>
       <c r="G116" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.67</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-19.6</v>
+        <v>213.47</v>
       </c>
       <c r="C117" t="n">
-        <v>5.17045443</v>
+        <v>5.20072943</v>
       </c>
       <c r="D117" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>73.95</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>71.65000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>73</v>
+        <v>71.45</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.95</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>74.23999999999999</v>
+        <v>-167.67</v>
       </c>
       <c r="C118" t="n">
-        <v>5.17787843</v>
+        <v>5.18396243</v>
       </c>
       <c r="D118" t="n">
-        <v>73.75</v>
+        <v>72</v>
       </c>
       <c r="E118" t="n">
-        <v>73.75</v>
+        <v>73.45</v>
       </c>
       <c r="F118" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>70.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.88</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15.04</v>
+        <v>-78.5919</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17938243</v>
+        <v>5.17610324</v>
       </c>
       <c r="D119" t="n">
-        <v>70.95</v>
+        <v>73.3</v>
       </c>
       <c r="E119" t="n">
-        <v>72.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F119" t="n">
-        <v>70.95</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H119" t="n">
-        <v>0.99</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>213.47</v>
+        <v>-54.57</v>
       </c>
       <c r="C120" t="n">
-        <v>5.20072943</v>
+        <v>5.17064624</v>
       </c>
       <c r="D120" t="n">
-        <v>71.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E120" t="n">
-        <v>71.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>70.40000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G120" t="n">
-        <v>71.45</v>
+        <v>73.45</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-167.67</v>
+        <v>32.9</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18396243</v>
+        <v>5.17393624</v>
       </c>
       <c r="D121" t="n">
-        <v>72</v>
+        <v>73.45</v>
       </c>
       <c r="E121" t="n">
-        <v>73.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>70.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G121" t="n">
-        <v>73.3</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>2.59</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-78.5919</v>
+        <v>41.93</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17610324</v>
+        <v>5.17812924</v>
       </c>
       <c r="D122" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="E122" t="n">
-        <v>73.3</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>71.84999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G122" t="n">
-        <v>73.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.14</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-54.57</v>
+        <v>52.87</v>
       </c>
       <c r="C123" t="n">
-        <v>5.17064624</v>
+        <v>5.18341624</v>
       </c>
       <c r="D123" t="n">
-        <v>72.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>73.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="F123" t="n">
-        <v>71.95</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>73.45</v>
+        <v>69.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0.34</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>32.9</v>
+        <v>291.58</v>
       </c>
       <c r="C124" t="n">
-        <v>5.17393624</v>
+        <v>5.21257424</v>
       </c>
       <c r="D124" t="n">
-        <v>73.45</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>74.40000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F124" t="n">
-        <v>71.75</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>73.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.41</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>41.93</v>
+        <v>-60.7601</v>
       </c>
       <c r="C125" t="n">
-        <v>5.17812924</v>
+        <v>5.20649823</v>
       </c>
       <c r="D125" t="n">
-        <v>73</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E125" t="n">
-        <v>73.65000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="F125" t="n">
-        <v>68.7</v>
+        <v>68.45</v>
       </c>
       <c r="G125" t="n">
-        <v>69.90000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="H125" t="n">
-        <v>-4.44</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>52.87</v>
+        <v>264.89</v>
       </c>
       <c r="C126" t="n">
-        <v>5.18341624</v>
+        <v>5.23298723</v>
       </c>
       <c r="D126" t="n">
-        <v>70.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>70.5</v>
+        <v>69.75</v>
       </c>
       <c r="F126" t="n">
-        <v>68.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="G126" t="n">
-        <v>69.7</v>
+        <v>67.55</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.29</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>291.58</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>5.21257424</v>
+        <v>5.23298723</v>
       </c>
       <c r="D127" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="E127" t="n">
-        <v>69.45</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>66.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G127" t="n">
-        <v>67</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>-3.87</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-60.7601</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>5.20649823</v>
+        <v>5.23298723</v>
       </c>
       <c r="D128" t="n">
-        <v>69.40000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="E128" t="n">
-        <v>70.25</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>68.45</v>
+        <v>68.2</v>
       </c>
       <c r="G128" t="n">
-        <v>69.25</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>3.36</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>264.89</v>
+        <v>-369.37</v>
       </c>
       <c r="C129" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D129" t="n">
-        <v>68.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E129" t="n">
-        <v>69.75</v>
+        <v>69.5</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.55</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.45</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D130" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="E130" t="n">
-        <v>69.75</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="G130" t="n">
-        <v>67.55</v>
+        <v>69.95</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>68.9663</v>
       </c>
       <c r="C131" t="n">
-        <v>5.23298723</v>
+        <v>5.20294686</v>
       </c>
       <c r="D131" t="n">
-        <v>69</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>71.15000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F131" t="n">
-        <v>68.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>70.15000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="H131" t="n">
-        <v>3.85</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>-247.41</v>
       </c>
       <c r="C132" t="n">
-        <v>5.23298723</v>
+        <v>5.17820586</v>
       </c>
       <c r="D132" t="n">
-        <v>69.25</v>
+        <v>69.5</v>
       </c>
       <c r="E132" t="n">
-        <v>70.09999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>68.2</v>
+        <v>69.45</v>
       </c>
       <c r="G132" t="n">
-        <v>69.65000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.71</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-369.37</v>
+        <v>27.55</v>
       </c>
       <c r="C133" t="n">
-        <v>5.19605023</v>
+        <v>5.18096086</v>
       </c>
       <c r="D133" t="n">
-        <v>69.5</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E133" t="n">
-        <v>69.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>67.3</v>
+        <v>73.05</v>
       </c>
       <c r="G133" t="n">
-        <v>67.84999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>-2.58</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>-286.2</v>
       </c>
       <c r="C134" t="n">
-        <v>5.19605023</v>
+        <v>5.15234086</v>
       </c>
       <c r="D134" t="n">
-        <v>68.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>70.34999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>68.5</v>
+        <v>73.05</v>
       </c>
       <c r="G134" t="n">
-        <v>69.95</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>3.1</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>68.9663</v>
+        <v>48.88</v>
       </c>
       <c r="C135" t="n">
-        <v>5.20294686</v>
+        <v>5.15722886</v>
       </c>
       <c r="D135" t="n">
-        <v>68.34999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="E135" t="n">
-        <v>70.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>68.34999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>70.05</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H135" t="n">
-        <v>0.14</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-247.41</v>
+        <v>-55.96</v>
       </c>
       <c r="C136" t="n">
-        <v>5.17820586</v>
+        <v>5.15163286</v>
       </c>
       <c r="D136" t="n">
-        <v>69.5</v>
+        <v>75.05</v>
       </c>
       <c r="E136" t="n">
-        <v>74.15000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>69.45</v>
+        <v>74.25</v>
       </c>
       <c r="G136" t="n">
-        <v>73.84999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>5.42</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>27.55</v>
+        <v>-385.85</v>
       </c>
       <c r="C137" t="n">
-        <v>5.18096086</v>
+        <v>5.11304786</v>
       </c>
       <c r="D137" t="n">
-        <v>73.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>75.15000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>73.05</v>
+        <v>64.5</v>
       </c>
       <c r="G137" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.61</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-286.2</v>
+        <v>139.59</v>
       </c>
       <c r="C138" t="n">
-        <v>5.15234086</v>
+        <v>5.12700686</v>
       </c>
       <c r="D138" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>74.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>73.05</v>
+        <v>61.75</v>
       </c>
       <c r="G138" t="n">
-        <v>73.65000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.34</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>48.88</v>
+        <v>1468.42</v>
       </c>
       <c r="C139" t="n">
-        <v>5.15722886</v>
+        <v>5.27384886</v>
       </c>
       <c r="D139" t="n">
-        <v>76.8</v>
+        <v>62.6</v>
       </c>
       <c r="E139" t="n">
-        <v>78.90000000000001</v>
+        <v>63.35</v>
       </c>
       <c r="F139" t="n">
-        <v>75.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="G139" t="n">
-        <v>76.84999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="H139" t="n">
-        <v>4.34</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-55.96</v>
+        <v>292.93</v>
       </c>
       <c r="C140" t="n">
-        <v>5.15163286</v>
+        <v>5.30314186</v>
       </c>
       <c r="D140" t="n">
-        <v>75.05</v>
+        <v>62.5</v>
       </c>
       <c r="E140" t="n">
-        <v>75.90000000000001</v>
+        <v>63.85</v>
       </c>
       <c r="F140" t="n">
-        <v>74.25</v>
+        <v>61.55</v>
       </c>
       <c r="G140" t="n">
-        <v>75.59999999999999</v>
+        <v>62.25</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.63</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-385.85</v>
+        <v>17.9</v>
       </c>
       <c r="C141" t="n">
-        <v>5.11304786</v>
+        <v>5.30493186</v>
       </c>
       <c r="D141" t="n">
-        <v>72.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="E141" t="n">
-        <v>72.40000000000001</v>
+        <v>64.95</v>
       </c>
       <c r="F141" t="n">
-        <v>64.5</v>
+        <v>61.35</v>
       </c>
       <c r="G141" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-14.15</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>139.59</v>
+        <v>-224.88</v>
       </c>
       <c r="C142" t="n">
-        <v>5.12700686</v>
+        <v>5.28244386</v>
       </c>
       <c r="D142" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="E142" t="n">
-        <v>64.90000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="F142" t="n">
-        <v>61.75</v>
+        <v>60.4</v>
       </c>
       <c r="G142" t="n">
-        <v>62.1</v>
+        <v>62.15</v>
       </c>
       <c r="H142" t="n">
-        <v>-4.31</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1468.42</v>
+        <v>-244.5</v>
       </c>
       <c r="C143" t="n">
-        <v>5.27384886</v>
+        <v>5.25799386</v>
       </c>
       <c r="D143" t="n">
-        <v>62.6</v>
+        <v>61.9</v>
       </c>
       <c r="E143" t="n">
-        <v>63.35</v>
+        <v>62.35</v>
       </c>
       <c r="F143" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="G143" t="n">
-        <v>61.6</v>
+        <v>60.2</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>292.93</v>
+        <v>-302.48</v>
       </c>
       <c r="C144" t="n">
-        <v>5.30314186</v>
+        <v>5.22774586</v>
       </c>
       <c r="D144" t="n">
-        <v>62.5</v>
+        <v>60.1</v>
       </c>
       <c r="E144" t="n">
-        <v>63.85</v>
+        <v>61</v>
       </c>
       <c r="F144" t="n">
-        <v>61.55</v>
+        <v>58.6</v>
       </c>
       <c r="G144" t="n">
-        <v>62.25</v>
+        <v>60.45</v>
       </c>
       <c r="H144" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>17.9</v>
+        <v>-177.8636</v>
       </c>
       <c r="C145" t="n">
-        <v>5.30493186</v>
+        <v>5.2099595</v>
       </c>
       <c r="D145" t="n">
-        <v>63.2</v>
+        <v>60</v>
       </c>
       <c r="E145" t="n">
-        <v>64.95</v>
+        <v>60.05</v>
       </c>
       <c r="F145" t="n">
-        <v>61.35</v>
+        <v>55.7</v>
       </c>
       <c r="G145" t="n">
-        <v>61.8</v>
+        <v>57.85</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.72</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-224.88</v>
+        <v>-228.55</v>
       </c>
       <c r="C146" t="n">
-        <v>5.28244386</v>
+        <v>5.1871045</v>
       </c>
       <c r="D146" t="n">
-        <v>61.8</v>
+        <v>56.95</v>
       </c>
       <c r="E146" t="n">
-        <v>62.25</v>
+        <v>59.1</v>
       </c>
       <c r="F146" t="n">
-        <v>60.4</v>
+        <v>56</v>
       </c>
       <c r="G146" t="n">
-        <v>62.15</v>
+        <v>58.55</v>
       </c>
       <c r="H146" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-244.5</v>
+        <v>423.9973</v>
       </c>
       <c r="C147" t="n">
-        <v>5.25799386</v>
+        <v>5.22950423</v>
       </c>
       <c r="D147" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="E147" t="n">
+        <v>62</v>
+      </c>
+      <c r="F147" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G147" t="n">
         <v>61.9</v>
       </c>
-      <c r="E147" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="F147" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G147" t="n">
-        <v>60.2</v>
-      </c>
       <c r="H147" t="n">
-        <v>-3.14</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-302.48</v>
+        <v>-119.16</v>
       </c>
       <c r="C148" t="n">
-        <v>5.22774586</v>
+        <v>5.21758823</v>
       </c>
       <c r="D148" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="E148" t="n">
-        <v>61</v>
+        <v>60.75</v>
       </c>
       <c r="F148" t="n">
-        <v>58.6</v>
+        <v>58.75</v>
       </c>
       <c r="G148" t="n">
-        <v>60.45</v>
+        <v>59.1</v>
       </c>
       <c r="H148" t="n">
-        <v>0.42</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-177.8636</v>
+        <v>-301.92</v>
       </c>
       <c r="C149" t="n">
-        <v>5.2099595</v>
+        <v>5.18739623</v>
       </c>
       <c r="D149" t="n">
-        <v>60</v>
+        <v>58.95</v>
       </c>
       <c r="E149" t="n">
-        <v>60.05</v>
+        <v>58.95</v>
       </c>
       <c r="F149" t="n">
-        <v>55.7</v>
+        <v>56.85</v>
       </c>
       <c r="G149" t="n">
-        <v>57.85</v>
+        <v>57.25</v>
       </c>
       <c r="H149" t="n">
-        <v>-4.3</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-228.55</v>
+        <v>112.29</v>
       </c>
       <c r="C150" t="n">
-        <v>5.1871045</v>
+        <v>5.19862523</v>
       </c>
       <c r="D150" t="n">
-        <v>56.95</v>
+        <v>57.1</v>
       </c>
       <c r="E150" t="n">
-        <v>59.1</v>
+        <v>57.6</v>
       </c>
       <c r="F150" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G150" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="H150" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>423.9973</v>
+        <v>-62.4836</v>
       </c>
       <c r="C151" t="n">
-        <v>5.22950423</v>
+        <v>5.19237687</v>
       </c>
       <c r="D151" t="n">
-        <v>57.05</v>
+        <v>55.3</v>
       </c>
       <c r="E151" t="n">
-        <v>62</v>
+        <v>57.9</v>
       </c>
       <c r="F151" t="n">
-        <v>56.55</v>
+        <v>54.95</v>
       </c>
       <c r="G151" t="n">
-        <v>61.9</v>
+        <v>57.35</v>
       </c>
       <c r="H151" t="n">
-        <v>5.72</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-119.16</v>
+        <v>-29.35</v>
       </c>
       <c r="C152" t="n">
-        <v>5.21758823</v>
+        <v>5.18944187</v>
       </c>
       <c r="D152" t="n">
-        <v>60.5</v>
+        <v>56.2</v>
       </c>
       <c r="E152" t="n">
-        <v>60.75</v>
+        <v>57.1</v>
       </c>
       <c r="F152" t="n">
-        <v>58.75</v>
+        <v>55.8</v>
       </c>
       <c r="G152" t="n">
-        <v>59.1</v>
+        <v>55.85</v>
       </c>
       <c r="H152" t="n">
-        <v>-4.52</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-301.92</v>
+        <v>54.46</v>
       </c>
       <c r="C153" t="n">
-        <v>5.18739623</v>
+        <v>5.19488787</v>
       </c>
       <c r="D153" t="n">
-        <v>58.95</v>
+        <v>55.3</v>
       </c>
       <c r="E153" t="n">
-        <v>58.95</v>
+        <v>55.55</v>
       </c>
       <c r="F153" t="n">
-        <v>56.85</v>
+        <v>53.25</v>
       </c>
       <c r="G153" t="n">
-        <v>57.25</v>
+        <v>54.7</v>
       </c>
       <c r="H153" t="n">
-        <v>-3.13</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>112.29</v>
+        <v>17.32</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19862523</v>
+        <v>5.19661987</v>
       </c>
       <c r="D154" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E154" t="n">
-        <v>57.6</v>
+        <v>54.1</v>
       </c>
       <c r="F154" t="n">
-        <v>56.5</v>
+        <v>52.25</v>
       </c>
       <c r="G154" t="n">
-        <v>56.65</v>
+        <v>53.15</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.05</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-62.4836</v>
+        <v>93.42</v>
       </c>
       <c r="C155" t="n">
-        <v>5.19237687</v>
+        <v>5.20596187</v>
       </c>
       <c r="D155" t="n">
-        <v>55.3</v>
+        <v>53.7</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>54.95</v>
+        <v>53.25</v>
       </c>
       <c r="G155" t="n">
-        <v>57.35</v>
+        <v>57</v>
       </c>
       <c r="H155" t="n">
-        <v>1.24</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-29.35</v>
+        <v>64.81</v>
       </c>
       <c r="C156" t="n">
-        <v>5.18944187</v>
+        <v>5.21244287</v>
       </c>
       <c r="D156" t="n">
-        <v>56.2</v>
+        <v>56.6</v>
       </c>
       <c r="E156" t="n">
-        <v>57.1</v>
+        <v>58.05</v>
       </c>
       <c r="F156" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="G156" t="n">
-        <v>55.85</v>
+        <v>56.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.62</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>54.46</v>
+        <v>-172.75</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19488787</v>
+        <v>5.19516787</v>
       </c>
       <c r="D157" t="n">
-        <v>55.3</v>
+        <v>56.85</v>
       </c>
       <c r="E157" t="n">
-        <v>55.55</v>
+        <v>57.2</v>
       </c>
       <c r="F157" t="n">
-        <v>53.25</v>
+        <v>55</v>
       </c>
       <c r="G157" t="n">
-        <v>54.7</v>
+        <v>56</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.06</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>17.32</v>
+        <v>-24.86</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19661987</v>
+        <v>5.19268187</v>
       </c>
       <c r="D158" t="n">
-        <v>54</v>
+        <v>55.75</v>
       </c>
       <c r="E158" t="n">
-        <v>54.1</v>
+        <v>55.8</v>
       </c>
       <c r="F158" t="n">
-        <v>52.25</v>
+        <v>53.7</v>
       </c>
       <c r="G158" t="n">
-        <v>53.15</v>
+        <v>53.9</v>
       </c>
       <c r="H158" t="n">
-        <v>-2.83</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>93.42</v>
+        <v>17.38</v>
       </c>
       <c r="C159" t="n">
-        <v>5.20596187</v>
+        <v>5.19441987</v>
       </c>
       <c r="D159" t="n">
-        <v>53.7</v>
+        <v>53.25</v>
       </c>
       <c r="E159" t="n">
-        <v>57.9</v>
+        <v>53.9</v>
       </c>
       <c r="F159" t="n">
-        <v>53.25</v>
+        <v>51.75</v>
       </c>
       <c r="G159" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H159" t="n">
-        <v>7.24</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>64.81</v>
+        <v>14.06</v>
       </c>
       <c r="C160" t="n">
-        <v>5.21244287</v>
+        <v>5.19582587</v>
       </c>
       <c r="D160" t="n">
-        <v>56.6</v>
+        <v>50.15</v>
       </c>
       <c r="E160" t="n">
-        <v>58.05</v>
+        <v>51.55</v>
       </c>
       <c r="F160" t="n">
-        <v>56.5</v>
+        <v>49.64</v>
       </c>
       <c r="G160" t="n">
-        <v>56.85</v>
+        <v>50.5</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.26</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-172.75</v>
+        <v>-21.2345</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19516787</v>
+        <v>5.19370242</v>
       </c>
       <c r="D161" t="n">
-        <v>56.85</v>
+        <v>50</v>
       </c>
       <c r="E161" t="n">
-        <v>57.2</v>
+        <v>50.8</v>
       </c>
       <c r="F161" t="n">
-        <v>55</v>
+        <v>47.9</v>
       </c>
       <c r="G161" t="n">
-        <v>56</v>
+        <v>48.32</v>
       </c>
       <c r="H161" t="n">
-        <v>-1.5</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-24.86</v>
+        <v>47.7</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19268187</v>
+        <v>5.19847242</v>
       </c>
       <c r="D162" t="n">
-        <v>55.75</v>
+        <v>48.98</v>
       </c>
       <c r="E162" t="n">
-        <v>55.8</v>
+        <v>49.94</v>
       </c>
       <c r="F162" t="n">
-        <v>53.7</v>
+        <v>48.18</v>
       </c>
       <c r="G162" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="H162" t="n">
-        <v>-3.75</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>17.38</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C163" t="n">
-        <v>5.19441987</v>
+        <v>5.20773242</v>
       </c>
       <c r="D163" t="n">
-        <v>53.25</v>
+        <v>49.44</v>
       </c>
       <c r="E163" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="F163" t="n">
-        <v>51.75</v>
+        <v>46.74</v>
       </c>
       <c r="G163" t="n">
-        <v>52</v>
+        <v>47.4</v>
       </c>
       <c r="H163" t="n">
-        <v>-3.53</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>14.06</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19582587</v>
+        <v>5.19818142</v>
       </c>
       <c r="D164" t="n">
-        <v>50.15</v>
+        <v>47</v>
       </c>
       <c r="E164" t="n">
-        <v>51.55</v>
+        <v>47</v>
       </c>
       <c r="F164" t="n">
-        <v>49.64</v>
+        <v>45.86</v>
       </c>
       <c r="G164" t="n">
-        <v>50.5</v>
+        <v>46.28</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.88</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-21.2345</v>
+        <v>-254.06</v>
       </c>
       <c r="C165" t="n">
-        <v>5.19370242</v>
+        <v>5.17277542</v>
       </c>
       <c r="D165" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="E165" t="n">
-        <v>50.8</v>
+        <v>47.18</v>
       </c>
       <c r="F165" t="n">
-        <v>47.9</v>
+        <v>45.76</v>
       </c>
       <c r="G165" t="n">
-        <v>48.32</v>
+        <v>45.9</v>
       </c>
       <c r="H165" t="n">
-        <v>-4.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>47.7</v>
+        <v>-316.19</v>
       </c>
       <c r="C166" t="n">
-        <v>5.19847242</v>
+        <v>5.14115642</v>
       </c>
       <c r="D166" t="n">
-        <v>48.98</v>
+        <v>45.9</v>
       </c>
       <c r="E166" t="n">
-        <v>49.94</v>
+        <v>46.78</v>
       </c>
       <c r="F166" t="n">
-        <v>48.18</v>
+        <v>45.26</v>
       </c>
       <c r="G166" t="n">
-        <v>49.44</v>
+        <v>46.08</v>
       </c>
       <c r="H166" t="n">
-        <v>2.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>92.59999999999999</v>
+        <v>-150.87</v>
       </c>
       <c r="C167" t="n">
-        <v>5.20773242</v>
+        <v>5.12606942</v>
       </c>
       <c r="D167" t="n">
-        <v>49.44</v>
+        <v>47.7</v>
       </c>
       <c r="E167" t="n">
-        <v>49.44</v>
+        <v>48.9</v>
       </c>
       <c r="F167" t="n">
-        <v>46.74</v>
+        <v>46.64</v>
       </c>
       <c r="G167" t="n">
-        <v>47.4</v>
+        <v>46.84</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.13</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-95.51000000000001</v>
+        <v>-236.76</v>
       </c>
       <c r="C168" t="n">
-        <v>5.19818142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D168" t="n">
-        <v>47</v>
+        <v>46.92</v>
       </c>
       <c r="E168" t="n">
-        <v>47</v>
+        <v>48.28</v>
       </c>
       <c r="F168" t="n">
-        <v>45.86</v>
+        <v>46.84</v>
       </c>
       <c r="G168" t="n">
-        <v>46.28</v>
+        <v>47.36</v>
       </c>
       <c r="H168" t="n">
-        <v>-2.36</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-254.06</v>
+        <v>-36.92</v>
       </c>
       <c r="C169" t="n">
-        <v>5.17277542</v>
+        <v>5.09870142</v>
       </c>
       <c r="D169" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E169" t="n">
-        <v>47.18</v>
+        <v>47.56</v>
       </c>
       <c r="F169" t="n">
-        <v>45.76</v>
+        <v>45.72</v>
       </c>
       <c r="G169" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.82</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-316.19</v>
+        <v>64.78</v>
       </c>
       <c r="C170" t="n">
-        <v>5.14115642</v>
+        <v>5.10517942</v>
       </c>
       <c r="D170" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="E170" t="n">
-        <v>46.78</v>
+        <v>48.42</v>
       </c>
       <c r="F170" t="n">
-        <v>45.26</v>
+        <v>46.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.08</v>
+        <v>46.6</v>
       </c>
       <c r="H170" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-150.87</v>
+        <v>-44.41</v>
       </c>
       <c r="C171" t="n">
-        <v>5.12606942</v>
+        <v>5.10073842</v>
       </c>
       <c r="D171" t="n">
-        <v>47.7</v>
+        <v>47.06</v>
       </c>
       <c r="E171" t="n">
-        <v>48.9</v>
+        <v>48.98</v>
       </c>
       <c r="F171" t="n">
-        <v>46.64</v>
+        <v>46.7</v>
       </c>
       <c r="G171" t="n">
-        <v>46.84</v>
+        <v>48.52</v>
       </c>
       <c r="H171" t="n">
-        <v>1.65</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-236.76</v>
+        <v>-124.97</v>
       </c>
       <c r="C172" t="n">
-        <v>5.10239342</v>
+        <v>5.08824142</v>
       </c>
       <c r="D172" t="n">
-        <v>46.92</v>
+        <v>47.6</v>
       </c>
       <c r="E172" t="n">
-        <v>48.28</v>
+        <v>48.08</v>
       </c>
       <c r="F172" t="n">
-        <v>46.84</v>
+        <v>46.72</v>
       </c>
       <c r="G172" t="n">
-        <v>47.36</v>
+        <v>46.76</v>
       </c>
       <c r="H172" t="n">
-        <v>1.11</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-36.92</v>
+        <v>-272.6</v>
       </c>
       <c r="C173" t="n">
-        <v>5.09870142</v>
+        <v>5.06098142</v>
       </c>
       <c r="D173" t="n">
-        <v>47</v>
+        <v>46.76</v>
       </c>
       <c r="E173" t="n">
-        <v>47.56</v>
+        <v>48.3</v>
       </c>
       <c r="F173" t="n">
-        <v>45.72</v>
+        <v>46.02</v>
       </c>
       <c r="G173" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="H173" t="n">
-        <v>-2.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>64.78</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C174" t="n">
-        <v>5.10517942</v>
+        <v>5.06933542</v>
       </c>
       <c r="D174" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="E174" t="n">
-        <v>48.42</v>
+        <v>47.92</v>
       </c>
       <c r="F174" t="n">
-        <v>46.26</v>
+        <v>46.46</v>
       </c>
       <c r="G174" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="H174" t="n">
-        <v>0.73</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-44.41</v>
+        <v>-232.94</v>
       </c>
       <c r="C175" t="n">
-        <v>5.10073842</v>
+        <v>5.04604142</v>
       </c>
       <c r="D175" t="n">
-        <v>47.06</v>
+        <v>47.2</v>
       </c>
       <c r="E175" t="n">
-        <v>48.98</v>
+        <v>48.84</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.52</v>
+        <v>48.56</v>
       </c>
       <c r="H175" t="n">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-124.97</v>
+        <v>-101.2265</v>
       </c>
       <c r="C176" t="n">
-        <v>5.08824142</v>
+        <v>5.03591877</v>
       </c>
       <c r="D176" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="E176" t="n">
-        <v>48.08</v>
+        <v>49.46</v>
       </c>
       <c r="F176" t="n">
-        <v>46.72</v>
+        <v>48.24</v>
       </c>
       <c r="G176" t="n">
-        <v>46.76</v>
+        <v>48.78</v>
       </c>
       <c r="H176" t="n">
-        <v>-3.63</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-272.6</v>
+        <v>-146.01</v>
       </c>
       <c r="C177" t="n">
-        <v>5.06098142</v>
+        <v>5.02131777</v>
       </c>
       <c r="D177" t="n">
-        <v>46.76</v>
+        <v>49.22</v>
       </c>
       <c r="E177" t="n">
-        <v>48.3</v>
+        <v>51</v>
       </c>
       <c r="F177" t="n">
-        <v>46.02</v>
+        <v>49.22</v>
       </c>
       <c r="G177" t="n">
-        <v>47.42</v>
+        <v>50.4</v>
       </c>
       <c r="H177" t="n">
-        <v>1.41</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>83.54000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C178" t="n">
-        <v>5.06933542</v>
+        <v>5.02274277</v>
       </c>
       <c r="D178" t="n">
-        <v>47.42</v>
+        <v>50.55</v>
       </c>
       <c r="E178" t="n">
-        <v>47.92</v>
+        <v>51</v>
       </c>
       <c r="F178" t="n">
-        <v>46.46</v>
+        <v>48.2</v>
       </c>
       <c r="G178" t="n">
-        <v>47.2</v>
+        <v>48.94</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.46</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-232.94</v>
+        <v>7.54</v>
       </c>
       <c r="C179" t="n">
-        <v>5.04604142</v>
+        <v>5.02349677</v>
       </c>
       <c r="D179" t="n">
-        <v>47.2</v>
+        <v>49.96</v>
       </c>
       <c r="E179" t="n">
-        <v>48.84</v>
+        <v>49.98</v>
       </c>
       <c r="F179" t="n">
-        <v>46.7</v>
+        <v>48.72</v>
       </c>
       <c r="G179" t="n">
-        <v>48.56</v>
+        <v>49.12</v>
       </c>
       <c r="H179" t="n">
-        <v>2.88</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-101.2265</v>
+        <v>29.93</v>
       </c>
       <c r="C180" t="n">
-        <v>5.03591877</v>
+        <v>5.02648977</v>
       </c>
       <c r="D180" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="E180" t="n">
-        <v>49.46</v>
+        <v>49.36</v>
       </c>
       <c r="F180" t="n">
-        <v>48.24</v>
+        <v>48.18</v>
       </c>
       <c r="G180" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="H180" t="n">
-        <v>0.45</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-146.01</v>
+        <v>-93.37</v>
       </c>
       <c r="C181" t="n">
-        <v>5.02131777</v>
+        <v>5.01715277</v>
       </c>
       <c r="D181" t="n">
-        <v>49.22</v>
+        <v>48.4</v>
       </c>
       <c r="E181" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
       <c r="F181" t="n">
-        <v>49.22</v>
+        <v>47.2</v>
       </c>
       <c r="G181" t="n">
-        <v>50.4</v>
+        <v>47.64</v>
       </c>
       <c r="H181" t="n">
-        <v>3.32</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>14.25</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C182" t="n">
-        <v>5.02274277</v>
+        <v>5.00778777</v>
       </c>
       <c r="D182" t="n">
-        <v>50.55</v>
+        <v>47.64</v>
       </c>
       <c r="E182" t="n">
-        <v>51</v>
+        <v>49.3</v>
       </c>
       <c r="F182" t="n">
-        <v>48.2</v>
+        <v>47.22</v>
       </c>
       <c r="G182" t="n">
-        <v>48.94</v>
+        <v>48.96</v>
       </c>
       <c r="H182" t="n">
-        <v>-2.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7.54</v>
+        <v>28.06</v>
       </c>
       <c r="C183" t="n">
-        <v>5.02349677</v>
+        <v>5.01059377</v>
       </c>
       <c r="D183" t="n">
-        <v>49.96</v>
+        <v>48.36</v>
       </c>
       <c r="E183" t="n">
-        <v>49.98</v>
+        <v>48.76</v>
       </c>
       <c r="F183" t="n">
-        <v>48.72</v>
+        <v>47.52</v>
       </c>
       <c r="G183" t="n">
-        <v>49.12</v>
+        <v>47.98</v>
       </c>
       <c r="H183" t="n">
-        <v>0.37</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>29.93</v>
+        <v>-160.94</v>
       </c>
       <c r="C184" t="n">
-        <v>5.02648977</v>
+        <v>4.99449977</v>
       </c>
       <c r="D184" t="n">
-        <v>49.1</v>
+        <v>47.98</v>
       </c>
       <c r="E184" t="n">
-        <v>49.36</v>
+        <v>48.46</v>
       </c>
       <c r="F184" t="n">
-        <v>48.18</v>
+        <v>47.32</v>
       </c>
       <c r="G184" t="n">
-        <v>48.64</v>
+        <v>48.08</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.98</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-93.37</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C185" t="n">
-        <v>5.01715277</v>
+        <v>5.00218477</v>
       </c>
       <c r="D185" t="n">
-        <v>48.4</v>
+        <v>49.54</v>
       </c>
       <c r="E185" t="n">
-        <v>48.4</v>
+        <v>50.5</v>
       </c>
       <c r="F185" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="G185" t="n">
-        <v>47.64</v>
+        <v>49.68</v>
       </c>
       <c r="H185" t="n">
-        <v>-2.06</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-93.65000000000001</v>
+        <v>-70.88</v>
       </c>
       <c r="C186" t="n">
-        <v>5.00778777</v>
+        <v>4.99509677</v>
       </c>
       <c r="D186" t="n">
-        <v>47.64</v>
+        <v>51.9</v>
       </c>
       <c r="E186" t="n">
-        <v>49.3</v>
+        <v>55.6</v>
       </c>
       <c r="F186" t="n">
-        <v>47.22</v>
+        <v>51.9</v>
       </c>
       <c r="G186" t="n">
-        <v>48.96</v>
+        <v>54.6</v>
       </c>
       <c r="H186" t="n">
-        <v>2.77</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>28.06</v>
+        <v>-223.97</v>
       </c>
       <c r="C187" t="n">
-        <v>5.01059377</v>
+        <v>4.97269977</v>
       </c>
       <c r="D187" t="n">
-        <v>48.36</v>
+        <v>54.7</v>
       </c>
       <c r="E187" t="n">
-        <v>48.76</v>
+        <v>56.1</v>
       </c>
       <c r="F187" t="n">
-        <v>47.52</v>
+        <v>53.7</v>
       </c>
       <c r="G187" t="n">
-        <v>47.98</v>
+        <v>54.25</v>
       </c>
       <c r="H187" t="n">
-        <v>-2</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-160.94</v>
+        <v>-908.88</v>
       </c>
       <c r="C188" t="n">
-        <v>4.99449977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D188" t="n">
-        <v>47.98</v>
+        <v>52.85</v>
       </c>
       <c r="E188" t="n">
-        <v>48.46</v>
+        <v>53.8</v>
       </c>
       <c r="F188" t="n">
-        <v>47.32</v>
+        <v>51.3</v>
       </c>
       <c r="G188" t="n">
-        <v>48.08</v>
+        <v>53.4</v>
       </c>
       <c r="H188" t="n">
-        <v>0.21</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>76.84999999999999</v>
+        <v>-219</v>
       </c>
       <c r="C189" t="n">
-        <v>5.00218477</v>
+        <v>4.85991177</v>
       </c>
       <c r="D189" t="n">
-        <v>49.54</v>
+        <v>52.75</v>
       </c>
       <c r="E189" t="n">
-        <v>50.5</v>
+        <v>54.45</v>
       </c>
       <c r="F189" t="n">
-        <v>48.9</v>
+        <v>51.45</v>
       </c>
       <c r="G189" t="n">
-        <v>49.68</v>
+        <v>51.85</v>
       </c>
       <c r="H189" t="n">
-        <v>3.33</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>-70.88</v>
+        <v>81.19</v>
       </c>
       <c r="C190" t="n">
-        <v>4.99509677</v>
+        <v>4.86803077</v>
       </c>
       <c r="D190" t="n">
-        <v>51.9</v>
+        <v>51.85</v>
       </c>
       <c r="E190" t="n">
-        <v>55.6</v>
+        <v>51.85</v>
       </c>
       <c r="F190" t="n">
-        <v>51.9</v>
+        <v>49.6</v>
       </c>
       <c r="G190" t="n">
-        <v>54.6</v>
+        <v>50.45</v>
       </c>
       <c r="H190" t="n">
-        <v>9.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-223.97</v>
+        <v>7.21</v>
       </c>
       <c r="C191" t="n">
-        <v>4.97269977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D191" t="n">
-        <v>54.7</v>
+        <v>50.05</v>
       </c>
       <c r="E191" t="n">
-        <v>56.1</v>
+        <v>50.8</v>
       </c>
       <c r="F191" t="n">
-        <v>53.7</v>
+        <v>49.52</v>
       </c>
       <c r="G191" t="n">
-        <v>54.25</v>
+        <v>50.65</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.64</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-908.88</v>
+        <v>144.28</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88181177</v>
+        <v>4.88317977</v>
       </c>
       <c r="D192" t="n">
-        <v>52.85</v>
+        <v>50</v>
       </c>
       <c r="E192" t="n">
-        <v>53.8</v>
+        <v>50.6</v>
       </c>
       <c r="F192" t="n">
-        <v>51.3</v>
+        <v>49.08</v>
       </c>
       <c r="G192" t="n">
-        <v>53.4</v>
+        <v>49.12</v>
       </c>
       <c r="H192" t="n">
-        <v>-1.57</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-219</v>
+        <v>-41.02</v>
       </c>
       <c r="C193" t="n">
-        <v>4.85991177</v>
+        <v>4.87907777</v>
       </c>
       <c r="D193" t="n">
-        <v>52.75</v>
+        <v>49.18</v>
       </c>
       <c r="E193" t="n">
-        <v>54.45</v>
+        <v>50.1</v>
       </c>
       <c r="F193" t="n">
-        <v>51.45</v>
+        <v>48.82</v>
       </c>
       <c r="G193" t="n">
-        <v>51.85</v>
+        <v>49.92</v>
       </c>
       <c r="H193" t="n">
-        <v>-2.9</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>81.19</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C194" t="n">
-        <v>4.86803077</v>
+        <v>4.88594877</v>
       </c>
       <c r="D194" t="n">
-        <v>51.85</v>
+        <v>50.5</v>
       </c>
       <c r="E194" t="n">
-        <v>51.85</v>
+        <v>50.95</v>
       </c>
       <c r="F194" t="n">
-        <v>49.6</v>
+        <v>49.74</v>
       </c>
       <c r="G194" t="n">
-        <v>50.45</v>
+        <v>50.1</v>
       </c>
       <c r="H194" t="n">
-        <v>-2.7</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.21</v>
+        <v>20.01</v>
       </c>
       <c r="C195" t="n">
-        <v>4.86875177</v>
+        <v>4.88794977</v>
       </c>
       <c r="D195" t="n">
-        <v>50.05</v>
+        <v>50</v>
       </c>
       <c r="E195" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="F195" t="n">
-        <v>49.52</v>
+        <v>49.04</v>
       </c>
       <c r="G195" t="n">
-        <v>50.65</v>
+        <v>49.06</v>
       </c>
       <c r="H195" t="n">
-        <v>0.4</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>144.28</v>
+        <v>-18.77</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88317977</v>
+        <v>4.88607277</v>
       </c>
       <c r="D196" t="n">
-        <v>50</v>
+        <v>49.08</v>
       </c>
       <c r="E196" t="n">
-        <v>50.6</v>
+        <v>49.78</v>
       </c>
       <c r="F196" t="n">
-        <v>49.08</v>
+        <v>48.7</v>
       </c>
       <c r="G196" t="n">
-        <v>49.12</v>
+        <v>49.4</v>
       </c>
       <c r="H196" t="n">
-        <v>-3.02</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-41.02</v>
+        <v>95.14</v>
       </c>
       <c r="C197" t="n">
-        <v>4.87907777</v>
+        <v>4.89558677</v>
       </c>
       <c r="D197" t="n">
-        <v>49.18</v>
+        <v>48.66</v>
       </c>
       <c r="E197" t="n">
-        <v>50.1</v>
+        <v>49.22</v>
       </c>
       <c r="F197" t="n">
-        <v>48.82</v>
+        <v>48.02</v>
       </c>
       <c r="G197" t="n">
-        <v>49.92</v>
+        <v>48.22</v>
       </c>
       <c r="H197" t="n">
-        <v>1.63</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>68.70999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="C198" t="n">
-        <v>4.88594877</v>
+        <v>4.89623377</v>
       </c>
       <c r="D198" t="n">
-        <v>50.5</v>
+        <v>48.22</v>
       </c>
       <c r="E198" t="n">
-        <v>50.95</v>
+        <v>48.22</v>
       </c>
       <c r="F198" t="n">
-        <v>49.74</v>
+        <v>47.46</v>
       </c>
       <c r="G198" t="n">
-        <v>50.1</v>
+        <v>47.46</v>
       </c>
       <c r="H198" t="n">
-        <v>0.36</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>20.01</v>
+        <v>78.34</v>
       </c>
       <c r="C199" t="n">
-        <v>4.88794977</v>
+        <v>4.90406777</v>
       </c>
       <c r="D199" t="n">
-        <v>50</v>
+        <v>47.86</v>
       </c>
       <c r="E199" t="n">
-        <v>50.5</v>
+        <v>48.68</v>
       </c>
       <c r="F199" t="n">
-        <v>49.04</v>
+        <v>47.7</v>
       </c>
       <c r="G199" t="n">
-        <v>49.06</v>
+        <v>48.48</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-18.77</v>
+        <v>12.2</v>
       </c>
       <c r="C200" t="n">
-        <v>4.88607277</v>
+        <v>4.90528777</v>
       </c>
       <c r="D200" t="n">
-        <v>49.08</v>
+        <v>48.1</v>
       </c>
       <c r="E200" t="n">
-        <v>49.78</v>
+        <v>48.7</v>
       </c>
       <c r="F200" t="n">
-        <v>48.7</v>
+        <v>47.38</v>
       </c>
       <c r="G200" t="n">
-        <v>49.4</v>
+        <v>47.88</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>95.14</v>
+        <v>-50.42</v>
       </c>
       <c r="C201" t="n">
-        <v>4.89558677</v>
+        <v>4.90024577</v>
       </c>
       <c r="D201" t="n">
-        <v>48.66</v>
+        <v>47.34</v>
       </c>
       <c r="E201" t="n">
-        <v>49.22</v>
+        <v>48.28</v>
       </c>
       <c r="F201" t="n">
-        <v>48.02</v>
+        <v>47.06</v>
       </c>
       <c r="G201" t="n">
-        <v>48.22</v>
+        <v>47.9</v>
       </c>
       <c r="H201" t="n">
-        <v>-2.39</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>6.47</v>
+        <v>7.38</v>
       </c>
       <c r="C202" t="n">
-        <v>4.89623377</v>
+        <v>4.90098377</v>
       </c>
       <c r="D202" t="n">
-        <v>48.22</v>
+        <v>49.98</v>
       </c>
       <c r="E202" t="n">
-        <v>48.22</v>
+        <v>51.2</v>
       </c>
       <c r="F202" t="n">
-        <v>47.46</v>
+        <v>49.76</v>
       </c>
       <c r="G202" t="n">
-        <v>47.46</v>
+        <v>50.55</v>
       </c>
       <c r="H202" t="n">
-        <v>-1.58</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>78.34</v>
+        <v>0.19</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90406777</v>
+        <v>4.90100277</v>
       </c>
       <c r="D203" t="n">
-        <v>47.86</v>
+        <v>50.55</v>
       </c>
       <c r="E203" t="n">
-        <v>48.68</v>
+        <v>51.8</v>
       </c>
       <c r="F203" t="n">
-        <v>47.7</v>
+        <v>50.5</v>
       </c>
       <c r="G203" t="n">
-        <v>48.48</v>
+        <v>51.2</v>
       </c>
       <c r="H203" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12.2</v>
+        <v>-404.07</v>
       </c>
       <c r="C204" t="n">
-        <v>4.90528777</v>
+        <v>4.86059577</v>
       </c>
       <c r="D204" t="n">
-        <v>48.1</v>
+        <v>50.3</v>
       </c>
       <c r="E204" t="n">
-        <v>48.7</v>
+        <v>51</v>
       </c>
       <c r="F204" t="n">
-        <v>47.38</v>
+        <v>49.3</v>
       </c>
       <c r="G204" t="n">
-        <v>47.88</v>
+        <v>49.46</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.24</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-50.42</v>
+        <v>-104.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.90024577</v>
+        <v>4.85015377</v>
       </c>
       <c r="D205" t="n">
-        <v>47.34</v>
+        <v>48.86</v>
       </c>
       <c r="E205" t="n">
-        <v>48.28</v>
+        <v>49.74</v>
       </c>
       <c r="F205" t="n">
-        <v>47.06</v>
+        <v>47.6</v>
       </c>
       <c r="G205" t="n">
-        <v>47.9</v>
+        <v>47.68</v>
       </c>
       <c r="H205" t="n">
-        <v>0.04</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7.38</v>
+        <v>-9.27</v>
       </c>
       <c r="C206" t="n">
-        <v>4.90098377</v>
+        <v>4.84922677</v>
       </c>
       <c r="D206" t="n">
-        <v>49.98</v>
+        <v>47.68</v>
       </c>
       <c r="E206" t="n">
-        <v>51.2</v>
+        <v>48.9</v>
       </c>
       <c r="F206" t="n">
-        <v>49.76</v>
+        <v>47.32</v>
       </c>
       <c r="G206" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="H206" t="n">
-        <v>5.53</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.19</v>
+        <v>-62.41</v>
       </c>
       <c r="C207" t="n">
-        <v>4.90100277</v>
+        <v>4.84298577</v>
       </c>
       <c r="D207" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="E207" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F207" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="G207" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="H207" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-404.07</v>
+        <v>-4.06</v>
       </c>
       <c r="C208" t="n">
-        <v>4.86059577</v>
+        <v>4.84257977</v>
       </c>
       <c r="D208" t="n">
-        <v>50.3</v>
+        <v>47.8</v>
       </c>
       <c r="E208" t="n">
-        <v>51</v>
+        <v>48.6</v>
       </c>
       <c r="F208" t="n">
-        <v>49.3</v>
+        <v>47.16</v>
       </c>
       <c r="G208" t="n">
-        <v>49.46</v>
+        <v>47.98</v>
       </c>
       <c r="H208" t="n">
-        <v>-3.4</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-104.42</v>
+        <v>107.65</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85015377</v>
+        <v>4.85334477</v>
       </c>
       <c r="D209" t="n">
-        <v>48.86</v>
+        <v>47.86</v>
       </c>
       <c r="E209" t="n">
-        <v>49.74</v>
+        <v>48.44</v>
       </c>
       <c r="F209" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="G209" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="H209" t="n">
-        <v>-3.6</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-9.27</v>
+        <v>137.46</v>
       </c>
       <c r="C210" t="n">
-        <v>4.84922677</v>
+        <v>4.86709077</v>
       </c>
       <c r="D210" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="E210" t="n">
-        <v>48.9</v>
+        <v>48.22</v>
       </c>
       <c r="F210" t="n">
-        <v>47.32</v>
+        <v>46.6</v>
       </c>
       <c r="G210" t="n">
-        <v>48.1</v>
+        <v>47.06</v>
       </c>
       <c r="H210" t="n">
-        <v>0.88</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-62.41</v>
+        <v>154.04</v>
       </c>
       <c r="C211" t="n">
-        <v>4.84298577</v>
+        <v>4.88249477</v>
       </c>
       <c r="D211" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="E211" t="n">
-        <v>49</v>
+        <v>46.76</v>
       </c>
       <c r="F211" t="n">
-        <v>47.5</v>
+        <v>44.56</v>
       </c>
       <c r="G211" t="n">
-        <v>48.6</v>
+        <v>45.86</v>
       </c>
       <c r="H211" t="n">
-        <v>1.04</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-4.06</v>
+        <v>78.03</v>
       </c>
       <c r="C212" t="n">
-        <v>4.84257977</v>
+        <v>4.89029777</v>
       </c>
       <c r="D212" t="n">
-        <v>47.8</v>
+        <v>46.56</v>
       </c>
       <c r="E212" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="F212" t="n">
-        <v>47.16</v>
+        <v>46.2</v>
       </c>
       <c r="G212" t="n">
-        <v>47.98</v>
+        <v>46.38</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.28</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>107.65</v>
+        <v>401.67</v>
       </c>
       <c r="C213" t="n">
-        <v>4.85334477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.86</v>
+        <v>47.28</v>
       </c>
       <c r="E213" t="n">
-        <v>48.44</v>
+        <v>48.88</v>
       </c>
       <c r="F213" t="n">
-        <v>46.5</v>
+        <v>47.12</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.33</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>137.46</v>
+        <v>-79.33</v>
       </c>
       <c r="C214" t="n">
-        <v>4.86709077</v>
+        <v>4.92253177</v>
       </c>
       <c r="D214" t="n">
-        <v>47.82</v>
+        <v>48.1</v>
       </c>
       <c r="E214" t="n">
-        <v>48.22</v>
+        <v>50.45</v>
       </c>
       <c r="F214" t="n">
-        <v>46.6</v>
+        <v>48.04</v>
       </c>
       <c r="G214" t="n">
-        <v>47.06</v>
+        <v>50.4</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.59</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>154.04</v>
+        <v>-415.48</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88249477</v>
+        <v>4.88098377</v>
       </c>
       <c r="D215" t="n">
-        <v>46.68</v>
+        <v>49.44</v>
       </c>
       <c r="E215" t="n">
-        <v>46.76</v>
+        <v>50.15</v>
       </c>
       <c r="F215" t="n">
-        <v>44.56</v>
+        <v>48.88</v>
       </c>
       <c r="G215" t="n">
-        <v>45.86</v>
+        <v>49.32</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>78.03</v>
+        <v>-394.96</v>
       </c>
       <c r="C216" t="n">
-        <v>4.89029777</v>
+        <v>4.84148777</v>
       </c>
       <c r="D216" t="n">
-        <v>46.56</v>
+        <v>49.08</v>
       </c>
       <c r="E216" t="n">
-        <v>48</v>
+        <v>49.08</v>
       </c>
       <c r="F216" t="n">
-        <v>46.2</v>
+        <v>47.2</v>
       </c>
       <c r="G216" t="n">
-        <v>46.38</v>
+        <v>47.62</v>
       </c>
       <c r="H216" t="n">
-        <v>1.13</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>401.67</v>
+        <v>-39.23</v>
       </c>
       <c r="C217" t="n">
-        <v>4.93046477</v>
+        <v>4.83756477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.28</v>
+        <v>47.2</v>
       </c>
       <c r="E217" t="n">
-        <v>48.88</v>
+        <v>47.2</v>
       </c>
       <c r="F217" t="n">
-        <v>47.12</v>
+        <v>46.42</v>
       </c>
       <c r="G217" t="n">
-        <v>47.82</v>
+        <v>46.48</v>
       </c>
       <c r="H217" t="n">
-        <v>3.1</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-79.33</v>
+        <v>219.67</v>
       </c>
       <c r="C218" t="n">
-        <v>4.92253177</v>
+        <v>4.85953177</v>
       </c>
       <c r="D218" t="n">
-        <v>48.1</v>
+        <v>45.74</v>
       </c>
       <c r="E218" t="n">
-        <v>50.45</v>
+        <v>46.44</v>
       </c>
       <c r="F218" t="n">
-        <v>48.04</v>
+        <v>45.38</v>
       </c>
       <c r="G218" t="n">
-        <v>50.4</v>
+        <v>46.34</v>
       </c>
       <c r="H218" t="n">
-        <v>5.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-415.48</v>
+        <v>111.68</v>
       </c>
       <c r="C219" t="n">
-        <v>4.88098377</v>
+        <v>4.87069977</v>
       </c>
       <c r="D219" t="n">
-        <v>49.44</v>
+        <v>45.9</v>
       </c>
       <c r="E219" t="n">
-        <v>50.15</v>
+        <v>47.8</v>
       </c>
       <c r="F219" t="n">
-        <v>48.88</v>
+        <v>45.84</v>
       </c>
       <c r="G219" t="n">
-        <v>49.32</v>
+        <v>47.52</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.14</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>-394.96</v>
+        <v>47.5</v>
       </c>
       <c r="C220" t="n">
-        <v>4.84148777</v>
+        <v>4.87544977</v>
       </c>
       <c r="D220" t="n">
-        <v>49.08</v>
+        <v>47.52</v>
       </c>
       <c r="E220" t="n">
-        <v>49.08</v>
+        <v>48.06</v>
       </c>
       <c r="F220" t="n">
-        <v>47.2</v>
+        <v>46.06</v>
       </c>
       <c r="G220" t="n">
-        <v>47.62</v>
+        <v>46.12</v>
       </c>
       <c r="H220" t="n">
-        <v>-3.45</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-39.23</v>
+        <v>-30.32</v>
       </c>
       <c r="C221" t="n">
-        <v>4.83756477</v>
+        <v>4.87241777</v>
       </c>
       <c r="D221" t="n">
-        <v>47.2</v>
+        <v>46.92</v>
       </c>
       <c r="E221" t="n">
-        <v>47.2</v>
+        <v>47.42</v>
       </c>
       <c r="F221" t="n">
-        <v>46.42</v>
+        <v>45.94</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>-2.39</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>219.67</v>
+        <v>15.46</v>
       </c>
       <c r="C222" t="n">
-        <v>4.85953177</v>
+        <v>4.87396377</v>
       </c>
       <c r="D222" t="n">
-        <v>45.74</v>
+        <v>46.9</v>
       </c>
       <c r="E222" t="n">
-        <v>46.44</v>
+        <v>47.5</v>
       </c>
       <c r="F222" t="n">
-        <v>45.38</v>
+        <v>44.94</v>
       </c>
       <c r="G222" t="n">
-        <v>46.34</v>
+        <v>46.88</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.3</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>111.68</v>
+        <v>57.59</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87069977</v>
+        <v>4.87972277</v>
       </c>
       <c r="D223" t="n">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
       <c r="E223" t="n">
-        <v>47.8</v>
+        <v>48.46</v>
       </c>
       <c r="F223" t="n">
-        <v>45.84</v>
+        <v>46.8</v>
       </c>
       <c r="G223" t="n">
-        <v>47.52</v>
+        <v>47.56</v>
       </c>
       <c r="H223" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>47.5</v>
+        <v>112.19</v>
       </c>
       <c r="C224" t="n">
-        <v>4.87544977</v>
+        <v>4.89094177</v>
       </c>
       <c r="D224" t="n">
-        <v>47.52</v>
+        <v>47.54</v>
       </c>
       <c r="E224" t="n">
-        <v>48.06</v>
+        <v>47.54</v>
       </c>
       <c r="F224" t="n">
-        <v>46.06</v>
+        <v>44.82</v>
       </c>
       <c r="G224" t="n">
-        <v>46.12</v>
+        <v>45.48</v>
       </c>
       <c r="H224" t="n">
-        <v>-2.95</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-30.32</v>
+        <v>-42.06</v>
       </c>
       <c r="C225" t="n">
-        <v>4.87241777</v>
+        <v>4.88673577</v>
       </c>
       <c r="D225" t="n">
-        <v>46.92</v>
+        <v>45</v>
       </c>
       <c r="E225" t="n">
-        <v>47.42</v>
+        <v>45.8</v>
       </c>
       <c r="F225" t="n">
-        <v>45.94</v>
+        <v>44.68</v>
       </c>
       <c r="G225" t="n">
-        <v>46.48</v>
+        <v>45.08</v>
       </c>
       <c r="H225" t="n">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B226" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="C226" t="n">
-        <v>4.87396377</v>
-      </c>
-      <c r="D226" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="E226" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="F226" t="n">
-        <v>44.94</v>
-      </c>
-      <c r="G226" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="H226" t="n">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>57.59</v>
-      </c>
-      <c r="C227" t="n">
-        <v>4.87972277</v>
-      </c>
-      <c r="D227" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="E227" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="F227" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G227" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="H227" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>112.19</v>
-      </c>
-      <c r="C228" t="n">
-        <v>4.89094177</v>
-      </c>
-      <c r="D228" t="n">
-        <v>47.54</v>
-      </c>
-      <c r="E228" t="n">
-        <v>47.54</v>
-      </c>
-      <c r="F228" t="n">
-        <v>44.82</v>
-      </c>
-      <c r="G228" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="H228" t="n">
-        <v>-4.37</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>0</v>
-      </c>
-      <c r="C229" t="n">
-        <v>4.89094177</v>
-      </c>
-      <c r="D229" t="n">
-        <v>45</v>
-      </c>
-      <c r="E229" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="F229" t="n">
-        <v>44.68</v>
-      </c>
-      <c r="G229" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="H229" t="n">
         <v>-0.88</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H225"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="E79" t="n">
-        <v>72.25</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>69.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G79" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E80" t="n">
-        <v>71.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F80" t="n">
-        <v>69.55</v>
+        <v>71.5</v>
       </c>
       <c r="G80" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4050 +2693,4162 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>70.3</v>
+        <v>72.8</v>
       </c>
       <c r="E81" t="n">
-        <v>73.3</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>70.3</v>
+        <v>71.5</v>
       </c>
       <c r="G81" t="n">
-        <v>72.84999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H81" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-37.37</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D82" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>73.5</v>
+        <v>72.25</v>
       </c>
       <c r="F82" t="n">
-        <v>71.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.51</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D83" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>73.15000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="F83" t="n">
-        <v>70.5</v>
+        <v>69.55</v>
       </c>
       <c r="G83" t="n">
-        <v>71.84999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>0.14</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>39.15</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29772381</v>
+        <v>5.29754581</v>
       </c>
       <c r="D84" t="n">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="E84" t="n">
-        <v>71.8</v>
+        <v>73.3</v>
       </c>
       <c r="F84" t="n">
-        <v>68.55</v>
+        <v>70.3</v>
       </c>
       <c r="G84" t="n">
-        <v>68.65000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-4.45</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-32.03</v>
+        <v>-37.37</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29452081</v>
+        <v>5.29380881</v>
       </c>
       <c r="D85" t="n">
-        <v>69.5</v>
+        <v>71.8</v>
       </c>
       <c r="E85" t="n">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="F85" t="n">
-        <v>68.15000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G85" t="n">
-        <v>68.75</v>
+        <v>71.75</v>
       </c>
       <c r="H85" t="n">
-        <v>0.15</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-245.51</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>5.26996981</v>
+        <v>5.29380881</v>
       </c>
       <c r="D86" t="n">
-        <v>67.75</v>
+        <v>72.8</v>
       </c>
       <c r="E86" t="n">
-        <v>70.15000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>67</v>
+        <v>70.5</v>
       </c>
       <c r="G86" t="n">
-        <v>68</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.99</v>
+        <v>39.15</v>
       </c>
       <c r="C87" t="n">
-        <v>5.27246881</v>
+        <v>5.29772381</v>
       </c>
       <c r="D87" t="n">
-        <v>68.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>69</v>
+        <v>71.8</v>
       </c>
       <c r="F87" t="n">
-        <v>65.65000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="G87" t="n">
-        <v>66.55</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-2.13</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-70.5937</v>
+        <v>-32.03</v>
       </c>
       <c r="C88" t="n">
-        <v>5.26540944</v>
+        <v>5.29452081</v>
       </c>
       <c r="D88" t="n">
-        <v>65.84999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E88" t="n">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="F88" t="n">
-        <v>64.45</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>65.84999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-83.42</v>
+        <v>-245.51</v>
       </c>
       <c r="C89" t="n">
-        <v>5.25706744</v>
+        <v>5.26996981</v>
       </c>
       <c r="D89" t="n">
-        <v>66.90000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="E89" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>67</v>
+      </c>
+      <c r="G89" t="n">
         <v>68</v>
       </c>
-      <c r="F89" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="H89" t="n">
-        <v>-0.38</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>32.9872</v>
+        <v>24.99</v>
       </c>
       <c r="C90" t="n">
-        <v>5.26036616</v>
+        <v>5.27246881</v>
       </c>
       <c r="D90" t="n">
-        <v>65.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>67.65000000000001</v>
+        <v>69</v>
       </c>
       <c r="F90" t="n">
-        <v>65.34999999999999</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>67.45</v>
+        <v>66.55</v>
       </c>
       <c r="H90" t="n">
-        <v>2.82</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-168.98</v>
+        <v>-70.5937</v>
       </c>
       <c r="C91" t="n">
-        <v>5.24346816</v>
+        <v>5.26540944</v>
       </c>
       <c r="D91" t="n">
-        <v>64.84999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>69</v>
+        <v>66.8</v>
       </c>
       <c r="F91" t="n">
-        <v>64.7</v>
+        <v>64.45</v>
       </c>
       <c r="G91" t="n">
-        <v>68.90000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>2.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-195.54</v>
+        <v>-83.42</v>
       </c>
       <c r="C92" t="n">
-        <v>5.22391416</v>
+        <v>5.25706744</v>
       </c>
       <c r="D92" t="n">
-        <v>69.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>70.2</v>
+        <v>68</v>
       </c>
       <c r="F92" t="n">
-        <v>67.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>69.05</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>0.22</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>16.18</v>
+        <v>32.9872</v>
       </c>
       <c r="C93" t="n">
-        <v>5.22553216</v>
+        <v>5.26036616</v>
       </c>
       <c r="D93" t="n">
-        <v>69.25</v>
+        <v>65.5</v>
       </c>
       <c r="E93" t="n">
-        <v>70.8</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>69.05</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>69.84999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="H93" t="n">
-        <v>1.16</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.87</v>
+        <v>-168.98</v>
       </c>
       <c r="C94" t="n">
-        <v>5.22691916</v>
+        <v>5.24346816</v>
       </c>
       <c r="D94" t="n">
-        <v>70.95</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="F94" t="n">
-        <v>69.15000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G94" t="n">
-        <v>70.15000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-145.08</v>
+        <v>-195.54</v>
       </c>
       <c r="C95" t="n">
-        <v>5.21241116</v>
+        <v>5.22391416</v>
       </c>
       <c r="D95" t="n">
-        <v>68.95</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>69</v>
+        <v>70.2</v>
       </c>
       <c r="F95" t="n">
-        <v>67.3</v>
+        <v>67.95</v>
       </c>
       <c r="G95" t="n">
-        <v>67.90000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="H95" t="n">
-        <v>-3.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.02</v>
+        <v>16.18</v>
       </c>
       <c r="C96" t="n">
-        <v>5.21491316</v>
+        <v>5.22553216</v>
       </c>
       <c r="D96" t="n">
-        <v>67.5</v>
+        <v>69.25</v>
       </c>
       <c r="E96" t="n">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F96" t="n">
-        <v>66.3</v>
+        <v>69.05</v>
       </c>
       <c r="G96" t="n">
-        <v>69.90000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>2.95</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-6.25</v>
+        <v>13.87</v>
       </c>
       <c r="C97" t="n">
-        <v>5.21428816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D97" t="n">
-        <v>71.25</v>
+        <v>70.95</v>
       </c>
       <c r="E97" t="n">
-        <v>73.3</v>
+        <v>71.3</v>
       </c>
       <c r="F97" t="n">
-        <v>70.84999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>71.3</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-48.58</v>
+        <v>-145.08</v>
       </c>
       <c r="C98" t="n">
-        <v>5.20943016</v>
+        <v>5.21241116</v>
       </c>
       <c r="D98" t="n">
-        <v>70.65000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E98" t="n">
-        <v>71.25</v>
+        <v>69</v>
       </c>
       <c r="F98" t="n">
-        <v>66.34999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G98" t="n">
-        <v>66.84999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>-6.24</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-197.18</v>
+        <v>25.02</v>
       </c>
       <c r="C99" t="n">
-        <v>5.18971216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D99" t="n">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="E99" t="n">
-        <v>67.34999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="G99" t="n">
-        <v>66</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.27</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>426.64</v>
+        <v>-6.25</v>
       </c>
       <c r="C100" t="n">
-        <v>5.23237616</v>
+        <v>5.21428816</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>71.25</v>
       </c>
       <c r="E100" t="n">
-        <v>68.7</v>
+        <v>73.3</v>
       </c>
       <c r="F100" t="n">
-        <v>66.34999999999999</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>66.8</v>
+        <v>71.3</v>
       </c>
       <c r="H100" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>41.4993</v>
+        <v>-48.58</v>
       </c>
       <c r="C101" t="n">
-        <v>5.23652609</v>
+        <v>5.20943016</v>
       </c>
       <c r="D101" t="n">
-        <v>65.59999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>66.05</v>
+        <v>71.25</v>
       </c>
       <c r="F101" t="n">
-        <v>64.2</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>64.8</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.99</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-220.5688</v>
+        <v>-197.18</v>
       </c>
       <c r="C102" t="n">
-        <v>5.21446921</v>
+        <v>5.18971216</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.65000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>63.45</v>
+        <v>65.8</v>
       </c>
       <c r="G102" t="n">
-        <v>67.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="H102" t="n">
-        <v>4.32</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>215.27</v>
+        <v>426.64</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23599621</v>
+        <v>5.23237616</v>
       </c>
       <c r="D103" t="n">
-        <v>69.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="E103" t="n">
-        <v>71.34999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F103" t="n">
-        <v>69.45</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>70.45</v>
+        <v>66.8</v>
       </c>
       <c r="H103" t="n">
-        <v>4.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-160.53</v>
+        <v>41.4993</v>
       </c>
       <c r="C104" t="n">
-        <v>5.21994321</v>
+        <v>5.23652609</v>
       </c>
       <c r="D104" t="n">
-        <v>69.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>70.8</v>
+        <v>66.05</v>
       </c>
       <c r="F104" t="n">
-        <v>68.7</v>
+        <v>64.2</v>
       </c>
       <c r="G104" t="n">
-        <v>69</v>
+        <v>64.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.06</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-304.01</v>
+        <v>-220.5688</v>
       </c>
       <c r="C105" t="n">
-        <v>5.18954221</v>
+        <v>5.21446921</v>
       </c>
       <c r="D105" t="n">
-        <v>69</v>
+        <v>66.2</v>
       </c>
       <c r="E105" t="n">
-        <v>71.5</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>68.3</v>
+        <v>63.45</v>
       </c>
       <c r="G105" t="n">
-        <v>70.05</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>1.52</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-30.3</v>
+        <v>215.27</v>
       </c>
       <c r="C106" t="n">
-        <v>5.18651221</v>
+        <v>5.23599621</v>
       </c>
       <c r="D106" t="n">
-        <v>68.05</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>69.34999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>68</v>
+        <v>69.45</v>
       </c>
       <c r="G106" t="n">
-        <v>68.8</v>
+        <v>70.45</v>
       </c>
       <c r="H106" t="n">
-        <v>-1.78</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-92.3</v>
+        <v>-160.53</v>
       </c>
       <c r="C107" t="n">
-        <v>5.17728221</v>
+        <v>5.21994321</v>
       </c>
       <c r="D107" t="n">
-        <v>68.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>69.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F107" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="G107" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.6</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>25.43</v>
+        <v>-304.01</v>
       </c>
       <c r="C108" t="n">
-        <v>5.17982521</v>
+        <v>5.18954221</v>
       </c>
       <c r="D108" t="n">
-        <v>68.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="E108" t="n">
-        <v>71.45</v>
+        <v>71.5</v>
       </c>
       <c r="F108" t="n">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G108" t="n">
-        <v>71.2</v>
+        <v>70.05</v>
       </c>
       <c r="H108" t="n">
-        <v>5.17</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>136.53</v>
+        <v>-30.3</v>
       </c>
       <c r="C109" t="n">
-        <v>5.19347821</v>
+        <v>5.18651221</v>
       </c>
       <c r="D109" t="n">
-        <v>71.2</v>
+        <v>68.05</v>
       </c>
       <c r="E109" t="n">
-        <v>73.40000000000001</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G109" t="n">
-        <v>71.8</v>
+        <v>68.8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.84</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-224.29</v>
+        <v>-92.3</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17104921</v>
+        <v>5.17728221</v>
       </c>
       <c r="D110" t="n">
-        <v>73.45</v>
+        <v>68.8</v>
       </c>
       <c r="E110" t="n">
-        <v>74</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>71.65000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="G110" t="n">
-        <v>73.3</v>
+        <v>67.7</v>
       </c>
       <c r="H110" t="n">
-        <v>2.09</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>97.7422</v>
+        <v>25.43</v>
       </c>
       <c r="C111" t="n">
-        <v>5.18082343</v>
+        <v>5.17982521</v>
       </c>
       <c r="D111" t="n">
-        <v>71.95</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>73.5</v>
+        <v>71.45</v>
       </c>
       <c r="F111" t="n">
-        <v>71.75</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G111" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.91</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-116.85</v>
+        <v>136.53</v>
       </c>
       <c r="C112" t="n">
-        <v>5.16913843</v>
+        <v>5.19347821</v>
       </c>
       <c r="D112" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E112" t="n">
-        <v>76.45</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>71.55</v>
+        <v>70</v>
       </c>
       <c r="G112" t="n">
-        <v>74.2</v>
+        <v>71.8</v>
       </c>
       <c r="H112" t="n">
-        <v>3.2</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>32.76</v>
+        <v>-224.29</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17241443</v>
+        <v>5.17104921</v>
       </c>
       <c r="D113" t="n">
-        <v>74.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E113" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F113" t="n">
-        <v>73.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>73.7</v>
+        <v>73.3</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.67</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-19.6</v>
+        <v>97.7422</v>
       </c>
       <c r="C114" t="n">
-        <v>5.17045443</v>
+        <v>5.18082343</v>
       </c>
       <c r="D114" t="n">
-        <v>73.7</v>
+        <v>71.95</v>
       </c>
       <c r="E114" t="n">
-        <v>73.95</v>
+        <v>73.5</v>
       </c>
       <c r="F114" t="n">
-        <v>71.65000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="G114" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.95</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>74.23999999999999</v>
+        <v>-116.85</v>
       </c>
       <c r="C115" t="n">
-        <v>5.17787843</v>
+        <v>5.16913843</v>
       </c>
       <c r="D115" t="n">
-        <v>73.75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>73.75</v>
+        <v>76.45</v>
       </c>
       <c r="F115" t="n">
-        <v>70.5</v>
+        <v>71.55</v>
       </c>
       <c r="G115" t="n">
-        <v>70.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>15.04</v>
+        <v>32.76</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17938243</v>
+        <v>5.17241443</v>
       </c>
       <c r="D116" t="n">
-        <v>70.95</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>72.15000000000001</v>
+        <v>75</v>
       </c>
       <c r="F116" t="n">
-        <v>70.95</v>
+        <v>73.25</v>
       </c>
       <c r="G116" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H116" t="n">
-        <v>0.99</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>213.47</v>
+        <v>-19.6</v>
       </c>
       <c r="C117" t="n">
-        <v>5.20072943</v>
+        <v>5.17045443</v>
       </c>
       <c r="D117" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E117" t="n">
-        <v>71.90000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="F117" t="n">
-        <v>70.40000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>71.45</v>
+        <v>73</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.21</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-167.67</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>5.18396243</v>
+        <v>5.17787843</v>
       </c>
       <c r="D118" t="n">
-        <v>72</v>
+        <v>73.75</v>
       </c>
       <c r="E118" t="n">
-        <v>73.45</v>
+        <v>73.75</v>
       </c>
       <c r="F118" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G118" t="n">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>2.59</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-78.5919</v>
+        <v>15.04</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17610324</v>
+        <v>5.17938243</v>
       </c>
       <c r="D119" t="n">
-        <v>73.3</v>
+        <v>70.95</v>
       </c>
       <c r="E119" t="n">
-        <v>73.3</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>71.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="G119" t="n">
-        <v>73.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.14</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-54.57</v>
+        <v>213.47</v>
       </c>
       <c r="C120" t="n">
-        <v>5.17064624</v>
+        <v>5.20072943</v>
       </c>
       <c r="D120" t="n">
-        <v>72.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>73.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>71.95</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>73.45</v>
+        <v>71.45</v>
       </c>
       <c r="H120" t="n">
-        <v>0.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>32.9</v>
+        <v>-167.67</v>
       </c>
       <c r="C121" t="n">
-        <v>5.17393624</v>
+        <v>5.18396243</v>
       </c>
       <c r="D121" t="n">
+        <v>72</v>
+      </c>
+      <c r="E121" t="n">
         <v>73.45</v>
       </c>
-      <c r="E121" t="n">
-        <v>74.40000000000001</v>
-      </c>
       <c r="F121" t="n">
-        <v>71.75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>73.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.41</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>41.93</v>
+        <v>-78.5919</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17812924</v>
+        <v>5.17610324</v>
       </c>
       <c r="D122" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="E122" t="n">
-        <v>73.65000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F122" t="n">
-        <v>68.7</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>69.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.44</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>52.87</v>
+        <v>-54.57</v>
       </c>
       <c r="C123" t="n">
-        <v>5.18341624</v>
+        <v>5.17064624</v>
       </c>
       <c r="D123" t="n">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E123" t="n">
-        <v>70.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>68.90000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G123" t="n">
-        <v>69.7</v>
+        <v>73.45</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>291.58</v>
+        <v>32.9</v>
       </c>
       <c r="C124" t="n">
-        <v>5.21257424</v>
+        <v>5.17393624</v>
       </c>
       <c r="D124" t="n">
-        <v>69.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E124" t="n">
-        <v>69.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>66.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G124" t="n">
-        <v>67</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>-3.87</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-60.7601</v>
+        <v>41.93</v>
       </c>
       <c r="C125" t="n">
-        <v>5.20649823</v>
+        <v>5.17812924</v>
       </c>
       <c r="D125" t="n">
-        <v>69.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E125" t="n">
-        <v>70.25</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>68.45</v>
+        <v>68.7</v>
       </c>
       <c r="G125" t="n">
-        <v>69.25</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>3.36</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>264.89</v>
+        <v>52.87</v>
       </c>
       <c r="C126" t="n">
-        <v>5.23298723</v>
+        <v>5.18341624</v>
       </c>
       <c r="D126" t="n">
-        <v>68.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>69.75</v>
+        <v>70.5</v>
       </c>
       <c r="F126" t="n">
-        <v>67.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>67.55</v>
+        <v>69.7</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.45</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>291.58</v>
       </c>
       <c r="C127" t="n">
-        <v>5.23298723</v>
+        <v>5.21257424</v>
       </c>
       <c r="D127" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>71.15000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F127" t="n">
-        <v>68.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G127" t="n">
-        <v>70.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H127" t="n">
-        <v>3.85</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-60.7601</v>
       </c>
       <c r="C128" t="n">
-        <v>5.23298723</v>
+        <v>5.20649823</v>
       </c>
       <c r="D128" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="F128" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="G128" t="n">
         <v>69.25</v>
       </c>
-      <c r="E128" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F128" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="G128" t="n">
-        <v>69.65000000000001</v>
-      </c>
       <c r="H128" t="n">
-        <v>-0.71</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-369.37</v>
+        <v>264.89</v>
       </c>
       <c r="C129" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D129" t="n">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E129" t="n">
-        <v>69.5</v>
+        <v>69.75</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.84999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.58</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D130" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E130" t="n">
-        <v>70.34999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="F130" t="n">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="G130" t="n">
-        <v>69.95</v>
+        <v>67.55</v>
       </c>
       <c r="H130" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>68.9663</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>5.20294686</v>
+        <v>5.23298723</v>
       </c>
       <c r="D131" t="n">
-        <v>68.34999999999999</v>
+        <v>69</v>
       </c>
       <c r="E131" t="n">
-        <v>70.3</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>68.34999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G131" t="n">
-        <v>70.05</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>0.14</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-247.41</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>5.17820586</v>
+        <v>5.23298723</v>
       </c>
       <c r="D132" t="n">
-        <v>69.5</v>
+        <v>69.25</v>
       </c>
       <c r="E132" t="n">
-        <v>74.15000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>69.45</v>
+        <v>68.2</v>
       </c>
       <c r="G132" t="n">
-        <v>73.84999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>5.42</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>27.55</v>
+        <v>-369.37</v>
       </c>
       <c r="C133" t="n">
-        <v>5.18096086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D133" t="n">
-        <v>73.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E133" t="n">
-        <v>75.15000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F133" t="n">
-        <v>73.05</v>
+        <v>67.3</v>
       </c>
       <c r="G133" t="n">
-        <v>73.40000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.61</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-286.2</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5.15234086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D134" t="n">
-        <v>73.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="E134" t="n">
-        <v>74.40000000000001</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>73.05</v>
+        <v>68.5</v>
       </c>
       <c r="G134" t="n">
-        <v>73.65000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="H134" t="n">
-        <v>0.34</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>48.88</v>
+        <v>68.9663</v>
       </c>
       <c r="C135" t="n">
-        <v>5.15722886</v>
+        <v>5.20294686</v>
       </c>
       <c r="D135" t="n">
-        <v>76.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>78.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F135" t="n">
-        <v>75.40000000000001</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>76.84999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H135" t="n">
-        <v>4.34</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-55.96</v>
+        <v>-247.41</v>
       </c>
       <c r="C136" t="n">
-        <v>5.15163286</v>
+        <v>5.17820586</v>
       </c>
       <c r="D136" t="n">
-        <v>75.05</v>
+        <v>69.5</v>
       </c>
       <c r="E136" t="n">
-        <v>75.90000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>74.25</v>
+        <v>69.45</v>
       </c>
       <c r="G136" t="n">
-        <v>75.59999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.63</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-385.85</v>
+        <v>27.55</v>
       </c>
       <c r="C137" t="n">
-        <v>5.11304786</v>
+        <v>5.18096086</v>
       </c>
       <c r="D137" t="n">
-        <v>72.40000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E137" t="n">
-        <v>72.40000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>64.5</v>
+        <v>73.05</v>
       </c>
       <c r="G137" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-14.15</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>139.59</v>
+        <v>-286.2</v>
       </c>
       <c r="C138" t="n">
-        <v>5.12700686</v>
+        <v>5.15234086</v>
       </c>
       <c r="D138" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>64.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>61.75</v>
+        <v>73.05</v>
       </c>
       <c r="G138" t="n">
-        <v>62.1</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>-4.31</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1468.42</v>
+        <v>48.88</v>
       </c>
       <c r="C139" t="n">
-        <v>5.27384886</v>
+        <v>5.15722886</v>
       </c>
       <c r="D139" t="n">
-        <v>62.6</v>
+        <v>76.8</v>
       </c>
       <c r="E139" t="n">
-        <v>63.35</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>61</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G139" t="n">
-        <v>61.6</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>292.93</v>
+        <v>-55.96</v>
       </c>
       <c r="C140" t="n">
-        <v>5.30314186</v>
+        <v>5.15163286</v>
       </c>
       <c r="D140" t="n">
-        <v>62.5</v>
+        <v>75.05</v>
       </c>
       <c r="E140" t="n">
-        <v>63.85</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>61.55</v>
+        <v>74.25</v>
       </c>
       <c r="G140" t="n">
-        <v>62.25</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>1.06</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>17.9</v>
+        <v>-385.85</v>
       </c>
       <c r="C141" t="n">
-        <v>5.30493186</v>
+        <v>5.11304786</v>
       </c>
       <c r="D141" t="n">
-        <v>63.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E141" t="n">
-        <v>64.95</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F141" t="n">
-        <v>61.35</v>
+        <v>64.5</v>
       </c>
       <c r="G141" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.72</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-224.88</v>
+        <v>139.59</v>
       </c>
       <c r="C142" t="n">
-        <v>5.28244386</v>
+        <v>5.12700686</v>
       </c>
       <c r="D142" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E142" t="n">
-        <v>62.25</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>60.4</v>
+        <v>61.75</v>
       </c>
       <c r="G142" t="n">
-        <v>62.15</v>
+        <v>62.1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.57</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-244.5</v>
+        <v>1468.42</v>
       </c>
       <c r="C143" t="n">
-        <v>5.25799386</v>
+        <v>5.27384886</v>
       </c>
       <c r="D143" t="n">
-        <v>61.9</v>
+        <v>62.6</v>
       </c>
       <c r="E143" t="n">
-        <v>62.35</v>
+        <v>63.35</v>
       </c>
       <c r="F143" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G143" t="n">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.14</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-302.48</v>
+        <v>292.93</v>
       </c>
       <c r="C144" t="n">
-        <v>5.22774586</v>
+        <v>5.30314186</v>
       </c>
       <c r="D144" t="n">
-        <v>60.1</v>
+        <v>62.5</v>
       </c>
       <c r="E144" t="n">
-        <v>61</v>
+        <v>63.85</v>
       </c>
       <c r="F144" t="n">
-        <v>58.6</v>
+        <v>61.55</v>
       </c>
       <c r="G144" t="n">
-        <v>60.45</v>
+        <v>62.25</v>
       </c>
       <c r="H144" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-177.8636</v>
+        <v>17.9</v>
       </c>
       <c r="C145" t="n">
-        <v>5.2099595</v>
+        <v>5.30493186</v>
       </c>
       <c r="D145" t="n">
-        <v>60</v>
+        <v>63.2</v>
       </c>
       <c r="E145" t="n">
-        <v>60.05</v>
+        <v>64.95</v>
       </c>
       <c r="F145" t="n">
-        <v>55.7</v>
+        <v>61.35</v>
       </c>
       <c r="G145" t="n">
-        <v>57.85</v>
+        <v>61.8</v>
       </c>
       <c r="H145" t="n">
-        <v>-4.3</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-228.55</v>
+        <v>-224.88</v>
       </c>
       <c r="C146" t="n">
-        <v>5.1871045</v>
+        <v>5.28244386</v>
       </c>
       <c r="D146" t="n">
-        <v>56.95</v>
+        <v>61.8</v>
       </c>
       <c r="E146" t="n">
-        <v>59.1</v>
+        <v>62.25</v>
       </c>
       <c r="F146" t="n">
-        <v>56</v>
+        <v>60.4</v>
       </c>
       <c r="G146" t="n">
-        <v>58.55</v>
+        <v>62.15</v>
       </c>
       <c r="H146" t="n">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>423.9973</v>
+        <v>-244.5</v>
       </c>
       <c r="C147" t="n">
-        <v>5.22950423</v>
+        <v>5.25799386</v>
       </c>
       <c r="D147" t="n">
-        <v>57.05</v>
+        <v>61.9</v>
       </c>
       <c r="E147" t="n">
-        <v>62</v>
+        <v>62.35</v>
       </c>
       <c r="F147" t="n">
-        <v>56.55</v>
+        <v>59.9</v>
       </c>
       <c r="G147" t="n">
-        <v>61.9</v>
+        <v>60.2</v>
       </c>
       <c r="H147" t="n">
-        <v>5.72</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-119.16</v>
+        <v>-302.48</v>
       </c>
       <c r="C148" t="n">
-        <v>5.21758823</v>
+        <v>5.22774586</v>
       </c>
       <c r="D148" t="n">
-        <v>60.5</v>
+        <v>60.1</v>
       </c>
       <c r="E148" t="n">
-        <v>60.75</v>
+        <v>61</v>
       </c>
       <c r="F148" t="n">
-        <v>58.75</v>
+        <v>58.6</v>
       </c>
       <c r="G148" t="n">
-        <v>59.1</v>
+        <v>60.45</v>
       </c>
       <c r="H148" t="n">
-        <v>-4.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-301.92</v>
+        <v>-177.8636</v>
       </c>
       <c r="C149" t="n">
-        <v>5.18739623</v>
+        <v>5.2099595</v>
       </c>
       <c r="D149" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="E149" t="n">
-        <v>58.95</v>
+        <v>60.05</v>
       </c>
       <c r="F149" t="n">
-        <v>56.85</v>
+        <v>55.7</v>
       </c>
       <c r="G149" t="n">
-        <v>57.25</v>
+        <v>57.85</v>
       </c>
       <c r="H149" t="n">
-        <v>-3.13</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>112.29</v>
+        <v>-228.55</v>
       </c>
       <c r="C150" t="n">
-        <v>5.19862523</v>
+        <v>5.1871045</v>
       </c>
       <c r="D150" t="n">
-        <v>57.1</v>
+        <v>56.95</v>
       </c>
       <c r="E150" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
       <c r="F150" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="G150" t="n">
-        <v>56.65</v>
+        <v>58.55</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.05</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-62.4836</v>
+        <v>423.9973</v>
       </c>
       <c r="C151" t="n">
-        <v>5.19237687</v>
+        <v>5.22950423</v>
       </c>
       <c r="D151" t="n">
-        <v>55.3</v>
+        <v>57.05</v>
       </c>
       <c r="E151" t="n">
-        <v>57.9</v>
+        <v>62</v>
       </c>
       <c r="F151" t="n">
-        <v>54.95</v>
+        <v>56.55</v>
       </c>
       <c r="G151" t="n">
-        <v>57.35</v>
+        <v>61.9</v>
       </c>
       <c r="H151" t="n">
-        <v>1.24</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-29.35</v>
+        <v>-119.16</v>
       </c>
       <c r="C152" t="n">
-        <v>5.18944187</v>
+        <v>5.21758823</v>
       </c>
       <c r="D152" t="n">
-        <v>56.2</v>
+        <v>60.5</v>
       </c>
       <c r="E152" t="n">
-        <v>57.1</v>
+        <v>60.75</v>
       </c>
       <c r="F152" t="n">
-        <v>55.8</v>
+        <v>58.75</v>
       </c>
       <c r="G152" t="n">
-        <v>55.85</v>
+        <v>59.1</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.62</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>54.46</v>
+        <v>-301.92</v>
       </c>
       <c r="C153" t="n">
-        <v>5.19488787</v>
+        <v>5.18739623</v>
       </c>
       <c r="D153" t="n">
-        <v>55.3</v>
+        <v>58.95</v>
       </c>
       <c r="E153" t="n">
-        <v>55.55</v>
+        <v>58.95</v>
       </c>
       <c r="F153" t="n">
-        <v>53.25</v>
+        <v>56.85</v>
       </c>
       <c r="G153" t="n">
-        <v>54.7</v>
+        <v>57.25</v>
       </c>
       <c r="H153" t="n">
-        <v>-2.06</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>17.32</v>
+        <v>112.29</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19661987</v>
+        <v>5.19862523</v>
       </c>
       <c r="D154" t="n">
-        <v>54</v>
+        <v>57.1</v>
       </c>
       <c r="E154" t="n">
-        <v>54.1</v>
+        <v>57.6</v>
       </c>
       <c r="F154" t="n">
-        <v>52.25</v>
+        <v>56.5</v>
       </c>
       <c r="G154" t="n">
-        <v>53.15</v>
+        <v>56.65</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.83</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>93.42</v>
+        <v>-62.4836</v>
       </c>
       <c r="C155" t="n">
-        <v>5.20596187</v>
+        <v>5.19237687</v>
       </c>
       <c r="D155" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>53.25</v>
+        <v>54.95</v>
       </c>
       <c r="G155" t="n">
-        <v>57</v>
+        <v>57.35</v>
       </c>
       <c r="H155" t="n">
-        <v>7.24</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>64.81</v>
+        <v>-29.35</v>
       </c>
       <c r="C156" t="n">
-        <v>5.21244287</v>
+        <v>5.18944187</v>
       </c>
       <c r="D156" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="E156" t="n">
-        <v>58.05</v>
+        <v>57.1</v>
       </c>
       <c r="F156" t="n">
-        <v>56.5</v>
+        <v>55.8</v>
       </c>
       <c r="G156" t="n">
-        <v>56.85</v>
+        <v>55.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.26</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-172.75</v>
+        <v>54.46</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19516787</v>
+        <v>5.19488787</v>
       </c>
       <c r="D157" t="n">
-        <v>56.85</v>
+        <v>55.3</v>
       </c>
       <c r="E157" t="n">
-        <v>57.2</v>
+        <v>55.55</v>
       </c>
       <c r="F157" t="n">
-        <v>55</v>
+        <v>53.25</v>
       </c>
       <c r="G157" t="n">
-        <v>56</v>
+        <v>54.7</v>
       </c>
       <c r="H157" t="n">
-        <v>-1.5</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-24.86</v>
+        <v>17.32</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19268187</v>
+        <v>5.19661987</v>
       </c>
       <c r="D158" t="n">
-        <v>55.75</v>
+        <v>54</v>
       </c>
       <c r="E158" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="F158" t="n">
-        <v>53.7</v>
+        <v>52.25</v>
       </c>
       <c r="G158" t="n">
-        <v>53.9</v>
+        <v>53.15</v>
       </c>
       <c r="H158" t="n">
-        <v>-3.75</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.38</v>
+        <v>93.42</v>
       </c>
       <c r="C159" t="n">
-        <v>5.19441987</v>
+        <v>5.20596187</v>
       </c>
       <c r="D159" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E159" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F159" t="n">
         <v>53.25</v>
       </c>
-      <c r="E159" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F159" t="n">
-        <v>51.75</v>
-      </c>
       <c r="G159" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H159" t="n">
-        <v>-3.53</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>14.06</v>
+        <v>64.81</v>
       </c>
       <c r="C160" t="n">
-        <v>5.19582587</v>
+        <v>5.21244287</v>
       </c>
       <c r="D160" t="n">
-        <v>50.15</v>
+        <v>56.6</v>
       </c>
       <c r="E160" t="n">
-        <v>51.55</v>
+        <v>58.05</v>
       </c>
       <c r="F160" t="n">
-        <v>49.64</v>
+        <v>56.5</v>
       </c>
       <c r="G160" t="n">
-        <v>50.5</v>
+        <v>56.85</v>
       </c>
       <c r="H160" t="n">
-        <v>-2.88</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-21.2345</v>
+        <v>-172.75</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19370242</v>
+        <v>5.19516787</v>
       </c>
       <c r="D161" t="n">
-        <v>50</v>
+        <v>56.85</v>
       </c>
       <c r="E161" t="n">
-        <v>50.8</v>
+        <v>57.2</v>
       </c>
       <c r="F161" t="n">
-        <v>47.9</v>
+        <v>55</v>
       </c>
       <c r="G161" t="n">
-        <v>48.32</v>
+        <v>56</v>
       </c>
       <c r="H161" t="n">
-        <v>-4.32</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>47.7</v>
+        <v>-24.86</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19847242</v>
+        <v>5.19268187</v>
       </c>
       <c r="D162" t="n">
-        <v>48.98</v>
+        <v>55.75</v>
       </c>
       <c r="E162" t="n">
-        <v>49.94</v>
+        <v>55.8</v>
       </c>
       <c r="F162" t="n">
-        <v>48.18</v>
+        <v>53.7</v>
       </c>
       <c r="G162" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="H162" t="n">
-        <v>2.32</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>92.59999999999999</v>
+        <v>17.38</v>
       </c>
       <c r="C163" t="n">
-        <v>5.20773242</v>
+        <v>5.19441987</v>
       </c>
       <c r="D163" t="n">
-        <v>49.44</v>
+        <v>53.25</v>
       </c>
       <c r="E163" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="F163" t="n">
-        <v>46.74</v>
+        <v>51.75</v>
       </c>
       <c r="G163" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="H163" t="n">
-        <v>-4.13</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-95.51000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19818142</v>
+        <v>5.19582587</v>
       </c>
       <c r="D164" t="n">
-        <v>47</v>
+        <v>50.15</v>
       </c>
       <c r="E164" t="n">
-        <v>47</v>
+        <v>51.55</v>
       </c>
       <c r="F164" t="n">
-        <v>45.86</v>
+        <v>49.64</v>
       </c>
       <c r="G164" t="n">
-        <v>46.28</v>
+        <v>50.5</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.36</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-254.06</v>
+        <v>-21.2345</v>
       </c>
       <c r="C165" t="n">
-        <v>5.17277542</v>
+        <v>5.19370242</v>
       </c>
       <c r="D165" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="E165" t="n">
-        <v>47.18</v>
+        <v>50.8</v>
       </c>
       <c r="F165" t="n">
-        <v>45.76</v>
+        <v>47.9</v>
       </c>
       <c r="G165" t="n">
-        <v>45.9</v>
+        <v>48.32</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.82</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-316.19</v>
+        <v>47.7</v>
       </c>
       <c r="C166" t="n">
-        <v>5.14115642</v>
+        <v>5.19847242</v>
       </c>
       <c r="D166" t="n">
-        <v>45.9</v>
+        <v>48.98</v>
       </c>
       <c r="E166" t="n">
-        <v>46.78</v>
+        <v>49.94</v>
       </c>
       <c r="F166" t="n">
-        <v>45.26</v>
+        <v>48.18</v>
       </c>
       <c r="G166" t="n">
-        <v>46.08</v>
+        <v>49.44</v>
       </c>
       <c r="H166" t="n">
-        <v>0.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-150.87</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C167" t="n">
-        <v>5.12606942</v>
+        <v>5.20773242</v>
       </c>
       <c r="D167" t="n">
-        <v>47.7</v>
+        <v>49.44</v>
       </c>
       <c r="E167" t="n">
-        <v>48.9</v>
+        <v>49.44</v>
       </c>
       <c r="F167" t="n">
-        <v>46.64</v>
+        <v>46.74</v>
       </c>
       <c r="G167" t="n">
-        <v>46.84</v>
+        <v>47.4</v>
       </c>
       <c r="H167" t="n">
-        <v>1.65</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-236.76</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C168" t="n">
-        <v>5.10239342</v>
+        <v>5.19818142</v>
       </c>
       <c r="D168" t="n">
-        <v>46.92</v>
+        <v>47</v>
       </c>
       <c r="E168" t="n">
-        <v>48.28</v>
+        <v>47</v>
       </c>
       <c r="F168" t="n">
-        <v>46.84</v>
+        <v>45.86</v>
       </c>
       <c r="G168" t="n">
-        <v>47.36</v>
+        <v>46.28</v>
       </c>
       <c r="H168" t="n">
-        <v>1.11</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-36.92</v>
+        <v>-254.06</v>
       </c>
       <c r="C169" t="n">
-        <v>5.09870142</v>
+        <v>5.17277542</v>
       </c>
       <c r="D169" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="E169" t="n">
-        <v>47.56</v>
+        <v>47.18</v>
       </c>
       <c r="F169" t="n">
-        <v>45.72</v>
+        <v>45.76</v>
       </c>
       <c r="G169" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="H169" t="n">
-        <v>-2.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>64.78</v>
+        <v>-316.19</v>
       </c>
       <c r="C170" t="n">
-        <v>5.10517942</v>
+        <v>5.14115642</v>
       </c>
       <c r="D170" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="E170" t="n">
-        <v>48.42</v>
+        <v>46.78</v>
       </c>
       <c r="F170" t="n">
-        <v>46.26</v>
+        <v>45.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.6</v>
+        <v>46.08</v>
       </c>
       <c r="H170" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-44.41</v>
+        <v>-150.87</v>
       </c>
       <c r="C171" t="n">
-        <v>5.10073842</v>
+        <v>5.12606942</v>
       </c>
       <c r="D171" t="n">
-        <v>47.06</v>
+        <v>47.7</v>
       </c>
       <c r="E171" t="n">
-        <v>48.98</v>
+        <v>48.9</v>
       </c>
       <c r="F171" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="G171" t="n">
-        <v>48.52</v>
+        <v>46.84</v>
       </c>
       <c r="H171" t="n">
-        <v>4.12</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-124.97</v>
+        <v>-236.76</v>
       </c>
       <c r="C172" t="n">
-        <v>5.08824142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D172" t="n">
-        <v>47.6</v>
+        <v>46.92</v>
       </c>
       <c r="E172" t="n">
-        <v>48.08</v>
+        <v>48.28</v>
       </c>
       <c r="F172" t="n">
-        <v>46.72</v>
+        <v>46.84</v>
       </c>
       <c r="G172" t="n">
-        <v>46.76</v>
+        <v>47.36</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.63</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-272.6</v>
+        <v>-36.92</v>
       </c>
       <c r="C173" t="n">
-        <v>5.06098142</v>
+        <v>5.09870142</v>
       </c>
       <c r="D173" t="n">
-        <v>46.76</v>
+        <v>47</v>
       </c>
       <c r="E173" t="n">
-        <v>48.3</v>
+        <v>47.56</v>
       </c>
       <c r="F173" t="n">
-        <v>46.02</v>
+        <v>45.72</v>
       </c>
       <c r="G173" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="H173" t="n">
-        <v>1.41</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>83.54000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="C174" t="n">
-        <v>5.06933542</v>
+        <v>5.10517942</v>
       </c>
       <c r="D174" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="E174" t="n">
-        <v>47.92</v>
+        <v>48.42</v>
       </c>
       <c r="F174" t="n">
-        <v>46.46</v>
+        <v>46.26</v>
       </c>
       <c r="G174" t="n">
-        <v>47.2</v>
+        <v>46.6</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.46</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-232.94</v>
+        <v>-44.41</v>
       </c>
       <c r="C175" t="n">
-        <v>5.04604142</v>
+        <v>5.10073842</v>
       </c>
       <c r="D175" t="n">
-        <v>47.2</v>
+        <v>47.06</v>
       </c>
       <c r="E175" t="n">
-        <v>48.84</v>
+        <v>48.98</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.56</v>
+        <v>48.52</v>
       </c>
       <c r="H175" t="n">
-        <v>2.88</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-101.2265</v>
+        <v>-124.97</v>
       </c>
       <c r="C176" t="n">
-        <v>5.03591877</v>
+        <v>5.08824142</v>
       </c>
       <c r="D176" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="E176" t="n">
-        <v>49.46</v>
+        <v>48.08</v>
       </c>
       <c r="F176" t="n">
-        <v>48.24</v>
+        <v>46.72</v>
       </c>
       <c r="G176" t="n">
-        <v>48.78</v>
+        <v>46.76</v>
       </c>
       <c r="H176" t="n">
-        <v>0.45</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-146.01</v>
+        <v>-272.6</v>
       </c>
       <c r="C177" t="n">
-        <v>5.02131777</v>
+        <v>5.06098142</v>
       </c>
       <c r="D177" t="n">
-        <v>49.22</v>
+        <v>46.76</v>
       </c>
       <c r="E177" t="n">
-        <v>51</v>
+        <v>48.3</v>
       </c>
       <c r="F177" t="n">
-        <v>49.22</v>
+        <v>46.02</v>
       </c>
       <c r="G177" t="n">
-        <v>50.4</v>
+        <v>47.42</v>
       </c>
       <c r="H177" t="n">
-        <v>3.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>14.25</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>5.02274277</v>
+        <v>5.06933542</v>
       </c>
       <c r="D178" t="n">
-        <v>50.55</v>
+        <v>47.42</v>
       </c>
       <c r="E178" t="n">
-        <v>51</v>
+        <v>47.92</v>
       </c>
       <c r="F178" t="n">
-        <v>48.2</v>
+        <v>46.46</v>
       </c>
       <c r="G178" t="n">
-        <v>48.94</v>
+        <v>47.2</v>
       </c>
       <c r="H178" t="n">
-        <v>-2.9</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7.54</v>
+        <v>-232.94</v>
       </c>
       <c r="C179" t="n">
-        <v>5.02349677</v>
+        <v>5.04604142</v>
       </c>
       <c r="D179" t="n">
-        <v>49.96</v>
+        <v>47.2</v>
       </c>
       <c r="E179" t="n">
-        <v>49.98</v>
+        <v>48.84</v>
       </c>
       <c r="F179" t="n">
-        <v>48.72</v>
+        <v>46.7</v>
       </c>
       <c r="G179" t="n">
-        <v>49.12</v>
+        <v>48.56</v>
       </c>
       <c r="H179" t="n">
-        <v>0.37</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>29.93</v>
+        <v>-101.2265</v>
       </c>
       <c r="C180" t="n">
-        <v>5.02648977</v>
+        <v>5.03591877</v>
       </c>
       <c r="D180" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="E180" t="n">
-        <v>49.36</v>
+        <v>49.46</v>
       </c>
       <c r="F180" t="n">
-        <v>48.18</v>
+        <v>48.24</v>
       </c>
       <c r="G180" t="n">
-        <v>48.64</v>
+        <v>48.78</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.98</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-93.37</v>
+        <v>-146.01</v>
       </c>
       <c r="C181" t="n">
-        <v>5.01715277</v>
+        <v>5.02131777</v>
       </c>
       <c r="D181" t="n">
-        <v>48.4</v>
+        <v>49.22</v>
       </c>
       <c r="E181" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F181" t="n">
-        <v>47.2</v>
+        <v>49.22</v>
       </c>
       <c r="G181" t="n">
-        <v>47.64</v>
+        <v>50.4</v>
       </c>
       <c r="H181" t="n">
-        <v>-2.06</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-93.65000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C182" t="n">
-        <v>5.00778777</v>
+        <v>5.02274277</v>
       </c>
       <c r="D182" t="n">
-        <v>47.64</v>
+        <v>50.55</v>
       </c>
       <c r="E182" t="n">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="F182" t="n">
-        <v>47.22</v>
+        <v>48.2</v>
       </c>
       <c r="G182" t="n">
-        <v>48.96</v>
+        <v>48.94</v>
       </c>
       <c r="H182" t="n">
-        <v>2.77</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>28.06</v>
+        <v>7.54</v>
       </c>
       <c r="C183" t="n">
-        <v>5.01059377</v>
+        <v>5.02349677</v>
       </c>
       <c r="D183" t="n">
-        <v>48.36</v>
+        <v>49.96</v>
       </c>
       <c r="E183" t="n">
-        <v>48.76</v>
+        <v>49.98</v>
       </c>
       <c r="F183" t="n">
-        <v>47.52</v>
+        <v>48.72</v>
       </c>
       <c r="G183" t="n">
-        <v>47.98</v>
+        <v>49.12</v>
       </c>
       <c r="H183" t="n">
-        <v>-2</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-160.94</v>
+        <v>29.93</v>
       </c>
       <c r="C184" t="n">
-        <v>4.99449977</v>
+        <v>5.02648977</v>
       </c>
       <c r="D184" t="n">
-        <v>47.98</v>
+        <v>49.1</v>
       </c>
       <c r="E184" t="n">
-        <v>48.46</v>
+        <v>49.36</v>
       </c>
       <c r="F184" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="G184" t="n">
-        <v>48.08</v>
+        <v>48.64</v>
       </c>
       <c r="H184" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>76.84999999999999</v>
+        <v>-93.37</v>
       </c>
       <c r="C185" t="n">
-        <v>5.00218477</v>
+        <v>5.01715277</v>
       </c>
       <c r="D185" t="n">
-        <v>49.54</v>
+        <v>48.4</v>
       </c>
       <c r="E185" t="n">
-        <v>50.5</v>
+        <v>48.4</v>
       </c>
       <c r="F185" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="G185" t="n">
-        <v>49.68</v>
+        <v>47.64</v>
       </c>
       <c r="H185" t="n">
-        <v>3.33</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-70.88</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C186" t="n">
-        <v>4.99509677</v>
+        <v>5.00778777</v>
       </c>
       <c r="D186" t="n">
-        <v>51.9</v>
+        <v>47.64</v>
       </c>
       <c r="E186" t="n">
-        <v>55.6</v>
+        <v>49.3</v>
       </c>
       <c r="F186" t="n">
-        <v>51.9</v>
+        <v>47.22</v>
       </c>
       <c r="G186" t="n">
-        <v>54.6</v>
+        <v>48.96</v>
       </c>
       <c r="H186" t="n">
-        <v>9.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-223.97</v>
+        <v>28.06</v>
       </c>
       <c r="C187" t="n">
-        <v>4.97269977</v>
+        <v>5.01059377</v>
       </c>
       <c r="D187" t="n">
-        <v>54.7</v>
+        <v>48.36</v>
       </c>
       <c r="E187" t="n">
-        <v>56.1</v>
+        <v>48.76</v>
       </c>
       <c r="F187" t="n">
-        <v>53.7</v>
+        <v>47.52</v>
       </c>
       <c r="G187" t="n">
-        <v>54.25</v>
+        <v>47.98</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.64</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-908.88</v>
+        <v>-160.94</v>
       </c>
       <c r="C188" t="n">
-        <v>4.88181177</v>
+        <v>4.99449977</v>
       </c>
       <c r="D188" t="n">
-        <v>52.85</v>
+        <v>47.98</v>
       </c>
       <c r="E188" t="n">
-        <v>53.8</v>
+        <v>48.46</v>
       </c>
       <c r="F188" t="n">
-        <v>51.3</v>
+        <v>47.32</v>
       </c>
       <c r="G188" t="n">
-        <v>53.4</v>
+        <v>48.08</v>
       </c>
       <c r="H188" t="n">
-        <v>-1.57</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-219</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C189" t="n">
-        <v>4.85991177</v>
+        <v>5.00218477</v>
       </c>
       <c r="D189" t="n">
-        <v>52.75</v>
+        <v>49.54</v>
       </c>
       <c r="E189" t="n">
-        <v>54.45</v>
+        <v>50.5</v>
       </c>
       <c r="F189" t="n">
-        <v>51.45</v>
+        <v>48.9</v>
       </c>
       <c r="G189" t="n">
-        <v>51.85</v>
+        <v>49.68</v>
       </c>
       <c r="H189" t="n">
-        <v>-2.9</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>81.19</v>
+        <v>-70.88</v>
       </c>
       <c r="C190" t="n">
-        <v>4.86803077</v>
+        <v>4.99509677</v>
       </c>
       <c r="D190" t="n">
-        <v>51.85</v>
+        <v>51.9</v>
       </c>
       <c r="E190" t="n">
-        <v>51.85</v>
+        <v>55.6</v>
       </c>
       <c r="F190" t="n">
-        <v>49.6</v>
+        <v>51.9</v>
       </c>
       <c r="G190" t="n">
-        <v>50.45</v>
+        <v>54.6</v>
       </c>
       <c r="H190" t="n">
-        <v>-2.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7.21</v>
+        <v>-223.97</v>
       </c>
       <c r="C191" t="n">
-        <v>4.86875177</v>
+        <v>4.97269977</v>
       </c>
       <c r="D191" t="n">
-        <v>50.05</v>
+        <v>54.7</v>
       </c>
       <c r="E191" t="n">
-        <v>50.8</v>
+        <v>56.1</v>
       </c>
       <c r="F191" t="n">
-        <v>49.52</v>
+        <v>53.7</v>
       </c>
       <c r="G191" t="n">
-        <v>50.65</v>
+        <v>54.25</v>
       </c>
       <c r="H191" t="n">
-        <v>0.4</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>144.28</v>
+        <v>-908.88</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88317977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D192" t="n">
-        <v>50</v>
+        <v>52.85</v>
       </c>
       <c r="E192" t="n">
-        <v>50.6</v>
+        <v>53.8</v>
       </c>
       <c r="F192" t="n">
-        <v>49.08</v>
+        <v>51.3</v>
       </c>
       <c r="G192" t="n">
-        <v>49.12</v>
+        <v>53.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-3.02</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-41.02</v>
+        <v>-219</v>
       </c>
       <c r="C193" t="n">
-        <v>4.87907777</v>
+        <v>4.85991177</v>
       </c>
       <c r="D193" t="n">
-        <v>49.18</v>
+        <v>52.75</v>
       </c>
       <c r="E193" t="n">
-        <v>50.1</v>
+        <v>54.45</v>
       </c>
       <c r="F193" t="n">
-        <v>48.82</v>
+        <v>51.45</v>
       </c>
       <c r="G193" t="n">
-        <v>49.92</v>
+        <v>51.85</v>
       </c>
       <c r="H193" t="n">
-        <v>1.63</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>68.70999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="C194" t="n">
-        <v>4.88594877</v>
+        <v>4.86803077</v>
       </c>
       <c r="D194" t="n">
-        <v>50.5</v>
+        <v>51.85</v>
       </c>
       <c r="E194" t="n">
-        <v>50.95</v>
+        <v>51.85</v>
       </c>
       <c r="F194" t="n">
-        <v>49.74</v>
+        <v>49.6</v>
       </c>
       <c r="G194" t="n">
-        <v>50.1</v>
+        <v>50.45</v>
       </c>
       <c r="H194" t="n">
-        <v>0.36</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>20.01</v>
+        <v>7.21</v>
       </c>
       <c r="C195" t="n">
-        <v>4.88794977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D195" t="n">
-        <v>50</v>
+        <v>50.05</v>
       </c>
       <c r="E195" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F195" t="n">
-        <v>49.04</v>
+        <v>49.52</v>
       </c>
       <c r="G195" t="n">
-        <v>49.06</v>
+        <v>50.65</v>
       </c>
       <c r="H195" t="n">
-        <v>-2.08</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-18.77</v>
+        <v>144.28</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88607277</v>
+        <v>4.88317977</v>
       </c>
       <c r="D196" t="n">
+        <v>50</v>
+      </c>
+      <c r="E196" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="F196" t="n">
         <v>49.08</v>
       </c>
-      <c r="E196" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="F196" t="n">
-        <v>48.7</v>
-      </c>
       <c r="G196" t="n">
-        <v>49.4</v>
+        <v>49.12</v>
       </c>
       <c r="H196" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>95.14</v>
+        <v>-41.02</v>
       </c>
       <c r="C197" t="n">
-        <v>4.89558677</v>
+        <v>4.87907777</v>
       </c>
       <c r="D197" t="n">
-        <v>48.66</v>
+        <v>49.18</v>
       </c>
       <c r="E197" t="n">
-        <v>49.22</v>
+        <v>50.1</v>
       </c>
       <c r="F197" t="n">
-        <v>48.02</v>
+        <v>48.82</v>
       </c>
       <c r="G197" t="n">
-        <v>48.22</v>
+        <v>49.92</v>
       </c>
       <c r="H197" t="n">
-        <v>-2.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>6.47</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C198" t="n">
-        <v>4.89623377</v>
+        <v>4.88594877</v>
       </c>
       <c r="D198" t="n">
-        <v>48.22</v>
+        <v>50.5</v>
       </c>
       <c r="E198" t="n">
-        <v>48.22</v>
+        <v>50.95</v>
       </c>
       <c r="F198" t="n">
-        <v>47.46</v>
+        <v>49.74</v>
       </c>
       <c r="G198" t="n">
-        <v>47.46</v>
+        <v>50.1</v>
       </c>
       <c r="H198" t="n">
-        <v>-1.58</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>78.34</v>
+        <v>20.01</v>
       </c>
       <c r="C199" t="n">
-        <v>4.90406777</v>
+        <v>4.88794977</v>
       </c>
       <c r="D199" t="n">
-        <v>47.86</v>
+        <v>50</v>
       </c>
       <c r="E199" t="n">
-        <v>48.68</v>
+        <v>50.5</v>
       </c>
       <c r="F199" t="n">
-        <v>47.7</v>
+        <v>49.04</v>
       </c>
       <c r="G199" t="n">
-        <v>48.48</v>
+        <v>49.06</v>
       </c>
       <c r="H199" t="n">
-        <v>2.15</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>12.2</v>
+        <v>-18.77</v>
       </c>
       <c r="C200" t="n">
-        <v>4.90528777</v>
+        <v>4.88607277</v>
       </c>
       <c r="D200" t="n">
-        <v>48.1</v>
+        <v>49.08</v>
       </c>
       <c r="E200" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="F200" t="n">
         <v>48.7</v>
       </c>
-      <c r="F200" t="n">
-        <v>47.38</v>
-      </c>
       <c r="G200" t="n">
-        <v>47.88</v>
+        <v>49.4</v>
       </c>
       <c r="H200" t="n">
-        <v>-1.24</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-50.42</v>
+        <v>95.14</v>
       </c>
       <c r="C201" t="n">
-        <v>4.90024577</v>
+        <v>4.89558677</v>
       </c>
       <c r="D201" t="n">
-        <v>47.34</v>
+        <v>48.66</v>
       </c>
       <c r="E201" t="n">
-        <v>48.28</v>
+        <v>49.22</v>
       </c>
       <c r="F201" t="n">
-        <v>47.06</v>
+        <v>48.02</v>
       </c>
       <c r="G201" t="n">
-        <v>47.9</v>
+        <v>48.22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.04</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7.38</v>
+        <v>6.47</v>
       </c>
       <c r="C202" t="n">
-        <v>4.90098377</v>
+        <v>4.89623377</v>
       </c>
       <c r="D202" t="n">
-        <v>49.98</v>
+        <v>48.22</v>
       </c>
       <c r="E202" t="n">
-        <v>51.2</v>
+        <v>48.22</v>
       </c>
       <c r="F202" t="n">
-        <v>49.76</v>
+        <v>47.46</v>
       </c>
       <c r="G202" t="n">
-        <v>50.55</v>
+        <v>47.46</v>
       </c>
       <c r="H202" t="n">
-        <v>5.53</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.19</v>
+        <v>78.34</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90100277</v>
+        <v>4.90406777</v>
       </c>
       <c r="D203" t="n">
-        <v>50.55</v>
+        <v>47.86</v>
       </c>
       <c r="E203" t="n">
-        <v>51.8</v>
+        <v>48.68</v>
       </c>
       <c r="F203" t="n">
-        <v>50.5</v>
+        <v>47.7</v>
       </c>
       <c r="G203" t="n">
-        <v>51.2</v>
+        <v>48.48</v>
       </c>
       <c r="H203" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-404.07</v>
+        <v>12.2</v>
       </c>
       <c r="C204" t="n">
-        <v>4.86059577</v>
+        <v>4.90528777</v>
       </c>
       <c r="D204" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="E204" t="n">
-        <v>51</v>
+        <v>48.7</v>
       </c>
       <c r="F204" t="n">
-        <v>49.3</v>
+        <v>47.38</v>
       </c>
       <c r="G204" t="n">
-        <v>49.46</v>
+        <v>47.88</v>
       </c>
       <c r="H204" t="n">
-        <v>-3.4</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-104.42</v>
+        <v>-50.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.85015377</v>
+        <v>4.90024577</v>
       </c>
       <c r="D205" t="n">
-        <v>48.86</v>
+        <v>47.34</v>
       </c>
       <c r="E205" t="n">
-        <v>49.74</v>
+        <v>48.28</v>
       </c>
       <c r="F205" t="n">
-        <v>47.6</v>
+        <v>47.06</v>
       </c>
       <c r="G205" t="n">
-        <v>47.68</v>
+        <v>47.9</v>
       </c>
       <c r="H205" t="n">
-        <v>-3.6</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-9.27</v>
+        <v>7.38</v>
       </c>
       <c r="C206" t="n">
-        <v>4.84922677</v>
+        <v>4.90098377</v>
       </c>
       <c r="D206" t="n">
-        <v>47.68</v>
+        <v>49.98</v>
       </c>
       <c r="E206" t="n">
-        <v>48.9</v>
+        <v>51.2</v>
       </c>
       <c r="F206" t="n">
-        <v>47.32</v>
+        <v>49.76</v>
       </c>
       <c r="G206" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="H206" t="n">
-        <v>0.88</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-62.41</v>
+        <v>0.19</v>
       </c>
       <c r="C207" t="n">
-        <v>4.84298577</v>
+        <v>4.90100277</v>
       </c>
       <c r="D207" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="E207" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="F207" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="G207" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="H207" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-4.06</v>
+        <v>-404.07</v>
       </c>
       <c r="C208" t="n">
-        <v>4.84257977</v>
+        <v>4.86059577</v>
       </c>
       <c r="D208" t="n">
-        <v>47.8</v>
+        <v>50.3</v>
       </c>
       <c r="E208" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="F208" t="n">
-        <v>47.16</v>
+        <v>49.3</v>
       </c>
       <c r="G208" t="n">
-        <v>47.98</v>
+        <v>49.46</v>
       </c>
       <c r="H208" t="n">
-        <v>-1.28</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>107.65</v>
+        <v>-104.42</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85334477</v>
+        <v>4.85015377</v>
       </c>
       <c r="D209" t="n">
-        <v>47.86</v>
+        <v>48.86</v>
       </c>
       <c r="E209" t="n">
-        <v>48.44</v>
+        <v>49.74</v>
       </c>
       <c r="F209" t="n">
-        <v>46.5</v>
+        <v>47.6</v>
       </c>
       <c r="G209" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.33</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>137.46</v>
+        <v>-9.27</v>
       </c>
       <c r="C210" t="n">
-        <v>4.86709077</v>
+        <v>4.84922677</v>
       </c>
       <c r="D210" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="E210" t="n">
-        <v>48.22</v>
+        <v>48.9</v>
       </c>
       <c r="F210" t="n">
-        <v>46.6</v>
+        <v>47.32</v>
       </c>
       <c r="G210" t="n">
-        <v>47.06</v>
+        <v>48.1</v>
       </c>
       <c r="H210" t="n">
-        <v>-1.59</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>154.04</v>
+        <v>-62.41</v>
       </c>
       <c r="C211" t="n">
-        <v>4.88249477</v>
+        <v>4.84298577</v>
       </c>
       <c r="D211" t="n">
-        <v>46.68</v>
+        <v>48.1</v>
       </c>
       <c r="E211" t="n">
-        <v>46.76</v>
+        <v>49</v>
       </c>
       <c r="F211" t="n">
-        <v>44.56</v>
+        <v>47.5</v>
       </c>
       <c r="G211" t="n">
-        <v>45.86</v>
+        <v>48.6</v>
       </c>
       <c r="H211" t="n">
-        <v>-2.55</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>78.03</v>
+        <v>-4.06</v>
       </c>
       <c r="C212" t="n">
-        <v>4.89029777</v>
+        <v>4.84257977</v>
       </c>
       <c r="D212" t="n">
-        <v>46.56</v>
+        <v>47.8</v>
       </c>
       <c r="E212" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="F212" t="n">
-        <v>46.2</v>
+        <v>47.16</v>
       </c>
       <c r="G212" t="n">
-        <v>46.38</v>
+        <v>47.98</v>
       </c>
       <c r="H212" t="n">
-        <v>1.13</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>401.67</v>
+        <v>107.65</v>
       </c>
       <c r="C213" t="n">
-        <v>4.93046477</v>
+        <v>4.85334477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.28</v>
+        <v>47.86</v>
       </c>
       <c r="E213" t="n">
-        <v>48.88</v>
+        <v>48.44</v>
       </c>
       <c r="F213" t="n">
-        <v>47.12</v>
+        <v>46.5</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>3.1</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-79.33</v>
+        <v>137.46</v>
       </c>
       <c r="C214" t="n">
-        <v>4.92253177</v>
+        <v>4.86709077</v>
       </c>
       <c r="D214" t="n">
-        <v>48.1</v>
+        <v>47.82</v>
       </c>
       <c r="E214" t="n">
-        <v>50.45</v>
+        <v>48.22</v>
       </c>
       <c r="F214" t="n">
-        <v>48.04</v>
+        <v>46.6</v>
       </c>
       <c r="G214" t="n">
-        <v>50.4</v>
+        <v>47.06</v>
       </c>
       <c r="H214" t="n">
-        <v>5.4</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-415.48</v>
+        <v>154.04</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88098377</v>
+        <v>4.88249477</v>
       </c>
       <c r="D215" t="n">
-        <v>49.44</v>
+        <v>46.68</v>
       </c>
       <c r="E215" t="n">
-        <v>50.15</v>
+        <v>46.76</v>
       </c>
       <c r="F215" t="n">
-        <v>48.88</v>
+        <v>44.56</v>
       </c>
       <c r="G215" t="n">
-        <v>49.32</v>
+        <v>45.86</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.14</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-394.96</v>
+        <v>78.03</v>
       </c>
       <c r="C216" t="n">
-        <v>4.84148777</v>
+        <v>4.89029777</v>
       </c>
       <c r="D216" t="n">
-        <v>49.08</v>
+        <v>46.56</v>
       </c>
       <c r="E216" t="n">
-        <v>49.08</v>
+        <v>48</v>
       </c>
       <c r="F216" t="n">
-        <v>47.2</v>
+        <v>46.2</v>
       </c>
       <c r="G216" t="n">
-        <v>47.62</v>
+        <v>46.38</v>
       </c>
       <c r="H216" t="n">
-        <v>-3.45</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-39.23</v>
+        <v>401.67</v>
       </c>
       <c r="C217" t="n">
-        <v>4.83756477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.2</v>
+        <v>47.28</v>
       </c>
       <c r="E217" t="n">
-        <v>47.2</v>
+        <v>48.88</v>
       </c>
       <c r="F217" t="n">
-        <v>46.42</v>
+        <v>47.12</v>
       </c>
       <c r="G217" t="n">
-        <v>46.48</v>
+        <v>47.82</v>
       </c>
       <c r="H217" t="n">
-        <v>-2.39</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>219.67</v>
+        <v>-79.33</v>
       </c>
       <c r="C218" t="n">
-        <v>4.85953177</v>
+        <v>4.92253177</v>
       </c>
       <c r="D218" t="n">
-        <v>45.74</v>
+        <v>48.1</v>
       </c>
       <c r="E218" t="n">
-        <v>46.44</v>
+        <v>50.45</v>
       </c>
       <c r="F218" t="n">
-        <v>45.38</v>
+        <v>48.04</v>
       </c>
       <c r="G218" t="n">
-        <v>46.34</v>
+        <v>50.4</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>111.68</v>
+        <v>-415.48</v>
       </c>
       <c r="C219" t="n">
-        <v>4.87069977</v>
+        <v>4.88098377</v>
       </c>
       <c r="D219" t="n">
-        <v>45.9</v>
+        <v>49.44</v>
       </c>
       <c r="E219" t="n">
-        <v>47.8</v>
+        <v>50.15</v>
       </c>
       <c r="F219" t="n">
-        <v>45.84</v>
+        <v>48.88</v>
       </c>
       <c r="G219" t="n">
-        <v>47.52</v>
+        <v>49.32</v>
       </c>
       <c r="H219" t="n">
-        <v>2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>47.5</v>
+        <v>-394.96</v>
       </c>
       <c r="C220" t="n">
-        <v>4.87544977</v>
+        <v>4.84148777</v>
       </c>
       <c r="D220" t="n">
-        <v>47.52</v>
+        <v>49.08</v>
       </c>
       <c r="E220" t="n">
-        <v>48.06</v>
+        <v>49.08</v>
       </c>
       <c r="F220" t="n">
-        <v>46.06</v>
+        <v>47.2</v>
       </c>
       <c r="G220" t="n">
-        <v>46.12</v>
+        <v>47.62</v>
       </c>
       <c r="H220" t="n">
-        <v>-2.95</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-30.32</v>
+        <v>-39.23</v>
       </c>
       <c r="C221" t="n">
-        <v>4.87241777</v>
+        <v>4.83756477</v>
       </c>
       <c r="D221" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E221" t="n">
-        <v>47.42</v>
+        <v>47.2</v>
       </c>
       <c r="F221" t="n">
-        <v>45.94</v>
+        <v>46.42</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>0.78</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>15.46</v>
+        <v>219.67</v>
       </c>
       <c r="C222" t="n">
-        <v>4.87396377</v>
+        <v>4.85953177</v>
       </c>
       <c r="D222" t="n">
-        <v>46.9</v>
+        <v>45.74</v>
       </c>
       <c r="E222" t="n">
-        <v>47.5</v>
+        <v>46.44</v>
       </c>
       <c r="F222" t="n">
-        <v>44.94</v>
+        <v>45.38</v>
       </c>
       <c r="G222" t="n">
-        <v>46.88</v>
+        <v>46.34</v>
       </c>
       <c r="H222" t="n">
-        <v>0.86</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>57.59</v>
+        <v>111.68</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87972277</v>
+        <v>4.87069977</v>
       </c>
       <c r="D223" t="n">
-        <v>46.9</v>
+        <v>45.9</v>
       </c>
       <c r="E223" t="n">
-        <v>48.46</v>
+        <v>47.8</v>
       </c>
       <c r="F223" t="n">
-        <v>46.8</v>
+        <v>45.84</v>
       </c>
       <c r="G223" t="n">
-        <v>47.56</v>
+        <v>47.52</v>
       </c>
       <c r="H223" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>112.19</v>
+        <v>47.5</v>
       </c>
       <c r="C224" t="n">
-        <v>4.89094177</v>
+        <v>4.87544977</v>
       </c>
       <c r="D224" t="n">
-        <v>47.54</v>
+        <v>47.52</v>
       </c>
       <c r="E224" t="n">
-        <v>47.54</v>
+        <v>48.06</v>
       </c>
       <c r="F224" t="n">
-        <v>44.82</v>
+        <v>46.06</v>
       </c>
       <c r="G224" t="n">
-        <v>45.48</v>
+        <v>46.12</v>
       </c>
       <c r="H224" t="n">
-        <v>-4.37</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>-30.32</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.87241777</v>
+      </c>
+      <c r="D225" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="E225" t="n">
+        <v>47.42</v>
+      </c>
+      <c r="F225" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="G225" t="n">
+        <v>46.48</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>15.46</v>
+      </c>
+      <c r="C226" t="n">
+        <v>4.87396377</v>
+      </c>
+      <c r="D226" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="E226" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F226" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="G226" t="n">
+        <v>46.88</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>57.59</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4.87972277</v>
+      </c>
+      <c r="D227" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="E227" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="F227" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="G227" t="n">
+        <v>47.56</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>112.19</v>
+      </c>
+      <c r="C228" t="n">
+        <v>4.89094177</v>
+      </c>
+      <c r="D228" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="E228" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="F228" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="G228" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="B225" t="n">
+      <c r="B229" t="n">
         <v>-42.06</v>
       </c>
-      <c r="C225" t="n">
+      <c r="C229" t="n">
         <v>4.88673577</v>
       </c>
-      <c r="D225" t="n">
+      <c r="D229" t="n">
         <v>45</v>
       </c>
-      <c r="E225" t="n">
+      <c r="E229" t="n">
         <v>45.8</v>
       </c>
-      <c r="F225" t="n">
+      <c r="F229" t="n">
         <v>44.68</v>
       </c>
-      <c r="G225" t="n">
+      <c r="G229" t="n">
         <v>45.08</v>
       </c>
-      <c r="H225" t="n">
+      <c r="H229" t="n">
         <v>-0.88</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E79" t="n">
-        <v>73.34999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="F79" t="n">
-        <v>71.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>73.34999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="F80" t="n">
-        <v>71.5</v>
+        <v>69.55</v>
       </c>
       <c r="G80" t="n">
-        <v>72.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4163 +2693,4079 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>72.8</v>
+        <v>70.3</v>
       </c>
       <c r="E81" t="n">
-        <v>73.34999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="F81" t="n">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="G81" t="n">
-        <v>72.3</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>-37.37</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D82" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E82" t="n">
-        <v>72.25</v>
+        <v>73.5</v>
       </c>
       <c r="F82" t="n">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G82" t="n">
-        <v>72.09999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.28</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D83" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E83" t="n">
-        <v>71.75</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>69.55</v>
+        <v>70.5</v>
       </c>
       <c r="G83" t="n">
-        <v>70.09999999999999</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>-2.77</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>39.15</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29754581</v>
+        <v>5.29772381</v>
       </c>
       <c r="D84" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="E84" t="n">
-        <v>73.3</v>
+        <v>71.8</v>
       </c>
       <c r="F84" t="n">
-        <v>70.3</v>
+        <v>68.55</v>
       </c>
       <c r="G84" t="n">
-        <v>72.84999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>3.92</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-37.37</v>
+        <v>-32.03</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29380881</v>
+        <v>5.29452081</v>
       </c>
       <c r="D85" t="n">
-        <v>71.8</v>
+        <v>69.5</v>
       </c>
       <c r="E85" t="n">
-        <v>73.5</v>
+        <v>69.5</v>
       </c>
       <c r="F85" t="n">
-        <v>71.3</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>71.75</v>
+        <v>68.75</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.51</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-245.51</v>
       </c>
       <c r="C86" t="n">
-        <v>5.29380881</v>
+        <v>5.26996981</v>
       </c>
       <c r="D86" t="n">
-        <v>72.8</v>
+        <v>67.75</v>
       </c>
       <c r="E86" t="n">
-        <v>73.15000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>70.5</v>
+        <v>67</v>
       </c>
       <c r="G86" t="n">
-        <v>71.84999999999999</v>
+        <v>68</v>
       </c>
       <c r="H86" t="n">
-        <v>0.14</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39.15</v>
+        <v>24.99</v>
       </c>
       <c r="C87" t="n">
-        <v>5.29772381</v>
+        <v>5.27246881</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
       <c r="F87" t="n">
-        <v>68.55</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>68.65000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="H87" t="n">
-        <v>-4.45</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-32.03</v>
+        <v>-70.5937</v>
       </c>
       <c r="C88" t="n">
-        <v>5.29452081</v>
+        <v>5.26540944</v>
       </c>
       <c r="D88" t="n">
-        <v>69.5</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>69.5</v>
+        <v>66.8</v>
       </c>
       <c r="F88" t="n">
-        <v>68.15000000000001</v>
+        <v>64.45</v>
       </c>
       <c r="G88" t="n">
-        <v>68.75</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-245.51</v>
+        <v>-83.42</v>
       </c>
       <c r="C89" t="n">
-        <v>5.26996981</v>
+        <v>5.25706744</v>
       </c>
       <c r="D89" t="n">
-        <v>67.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>70.15000000000001</v>
+        <v>68</v>
       </c>
       <c r="F89" t="n">
-        <v>67</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>68</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.09</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24.99</v>
+        <v>32.9872</v>
       </c>
       <c r="C90" t="n">
-        <v>5.27246881</v>
+        <v>5.26036616</v>
       </c>
       <c r="D90" t="n">
-        <v>68.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="E90" t="n">
-        <v>69</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>65.65000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>66.55</v>
+        <v>67.45</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.13</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-70.5937</v>
+        <v>-168.98</v>
       </c>
       <c r="C91" t="n">
-        <v>5.26540944</v>
+        <v>5.24346816</v>
       </c>
       <c r="D91" t="n">
-        <v>65.84999999999999</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>66.8</v>
+        <v>69</v>
       </c>
       <c r="F91" t="n">
-        <v>64.45</v>
+        <v>64.7</v>
       </c>
       <c r="G91" t="n">
-        <v>65.84999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-83.42</v>
+        <v>-195.54</v>
       </c>
       <c r="C92" t="n">
-        <v>5.25706744</v>
+        <v>5.22391416</v>
       </c>
       <c r="D92" t="n">
-        <v>66.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>68</v>
+        <v>70.2</v>
       </c>
       <c r="F92" t="n">
-        <v>65.09999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="G92" t="n">
-        <v>65.59999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.38</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>32.9872</v>
+        <v>16.18</v>
       </c>
       <c r="C93" t="n">
-        <v>5.26036616</v>
+        <v>5.22553216</v>
       </c>
       <c r="D93" t="n">
-        <v>65.5</v>
+        <v>69.25</v>
       </c>
       <c r="E93" t="n">
-        <v>67.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.34999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="G93" t="n">
-        <v>67.45</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>2.82</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-168.98</v>
+        <v>13.87</v>
       </c>
       <c r="C94" t="n">
-        <v>5.24346816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D94" t="n">
-        <v>64.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E94" t="n">
-        <v>69</v>
+        <v>71.3</v>
       </c>
       <c r="F94" t="n">
-        <v>64.7</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>68.90000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>2.15</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-195.54</v>
+        <v>-145.08</v>
       </c>
       <c r="C95" t="n">
-        <v>5.22391416</v>
+        <v>5.21241116</v>
       </c>
       <c r="D95" t="n">
-        <v>69.90000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E95" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="F95" t="n">
-        <v>67.95</v>
+        <v>67.3</v>
       </c>
       <c r="G95" t="n">
-        <v>69.05</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.22</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>16.18</v>
+        <v>25.02</v>
       </c>
       <c r="C96" t="n">
-        <v>5.22553216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D96" t="n">
-        <v>69.25</v>
+        <v>67.5</v>
       </c>
       <c r="E96" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>69.05</v>
+        <v>66.3</v>
       </c>
       <c r="G96" t="n">
-        <v>69.84999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>1.16</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.87</v>
+        <v>-6.25</v>
       </c>
       <c r="C97" t="n">
-        <v>5.22691916</v>
+        <v>5.21428816</v>
       </c>
       <c r="D97" t="n">
-        <v>70.95</v>
+        <v>71.25</v>
       </c>
       <c r="E97" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="G97" t="n">
         <v>71.3</v>
       </c>
-      <c r="F97" t="n">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="G97" t="n">
-        <v>70.15000000000001</v>
-      </c>
       <c r="H97" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-145.08</v>
+        <v>-48.58</v>
       </c>
       <c r="C98" t="n">
-        <v>5.21241116</v>
+        <v>5.20943016</v>
       </c>
       <c r="D98" t="n">
-        <v>68.95</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>69</v>
+        <v>71.25</v>
       </c>
       <c r="F98" t="n">
-        <v>67.3</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>67.90000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>-3.21</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25.02</v>
+        <v>-197.18</v>
       </c>
       <c r="C99" t="n">
-        <v>5.21491316</v>
+        <v>5.18971216</v>
       </c>
       <c r="D99" t="n">
-        <v>67.5</v>
+        <v>66.2</v>
       </c>
       <c r="E99" t="n">
-        <v>70.09999999999999</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>66.3</v>
+        <v>65.8</v>
       </c>
       <c r="G99" t="n">
-        <v>69.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="H99" t="n">
-        <v>2.95</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-6.25</v>
+        <v>426.64</v>
       </c>
       <c r="C100" t="n">
-        <v>5.21428816</v>
+        <v>5.23237616</v>
       </c>
       <c r="D100" t="n">
-        <v>71.25</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>73.3</v>
+        <v>68.7</v>
       </c>
       <c r="F100" t="n">
-        <v>70.84999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>71.3</v>
+        <v>66.8</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-48.58</v>
+        <v>41.4993</v>
       </c>
       <c r="C101" t="n">
-        <v>5.20943016</v>
+        <v>5.23652609</v>
       </c>
       <c r="D101" t="n">
-        <v>70.65000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>71.25</v>
+        <v>66.05</v>
       </c>
       <c r="F101" t="n">
-        <v>66.34999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G101" t="n">
-        <v>66.84999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-6.24</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-197.18</v>
+        <v>-220.5688</v>
       </c>
       <c r="C102" t="n">
-        <v>5.18971216</v>
+        <v>5.21446921</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.34999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F102" t="n">
-        <v>65.8</v>
+        <v>63.45</v>
       </c>
       <c r="G102" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>426.64</v>
+        <v>215.27</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23237616</v>
+        <v>5.23599621</v>
       </c>
       <c r="D103" t="n">
-        <v>67</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>68.7</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>66.34999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="G103" t="n">
-        <v>66.8</v>
+        <v>70.45</v>
       </c>
       <c r="H103" t="n">
-        <v>1.21</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>41.4993</v>
+        <v>-160.53</v>
       </c>
       <c r="C104" t="n">
-        <v>5.23652609</v>
+        <v>5.21994321</v>
       </c>
       <c r="D104" t="n">
-        <v>65.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>66.05</v>
+        <v>70.8</v>
       </c>
       <c r="F104" t="n">
-        <v>64.2</v>
+        <v>68.7</v>
       </c>
       <c r="G104" t="n">
-        <v>64.8</v>
+        <v>69</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.99</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-220.5688</v>
+        <v>-304.01</v>
       </c>
       <c r="C105" t="n">
-        <v>5.21446921</v>
+        <v>5.18954221</v>
       </c>
       <c r="D105" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="E105" t="n">
-        <v>67.65000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F105" t="n">
-        <v>63.45</v>
+        <v>68.3</v>
       </c>
       <c r="G105" t="n">
-        <v>67.59999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H105" t="n">
-        <v>4.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>215.27</v>
+        <v>-30.3</v>
       </c>
       <c r="C106" t="n">
-        <v>5.23599621</v>
+        <v>5.18651221</v>
       </c>
       <c r="D106" t="n">
-        <v>69.59999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="E106" t="n">
-        <v>71.34999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>69.45</v>
+        <v>68</v>
       </c>
       <c r="G106" t="n">
-        <v>70.45</v>
+        <v>68.8</v>
       </c>
       <c r="H106" t="n">
-        <v>4.22</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-160.53</v>
+        <v>-92.3</v>
       </c>
       <c r="C107" t="n">
-        <v>5.21994321</v>
+        <v>5.17728221</v>
       </c>
       <c r="D107" t="n">
-        <v>69.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E107" t="n">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
       <c r="G107" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.06</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-304.01</v>
+        <v>25.43</v>
       </c>
       <c r="C108" t="n">
-        <v>5.18954221</v>
+        <v>5.17982521</v>
       </c>
       <c r="D108" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>71.5</v>
+        <v>71.45</v>
       </c>
       <c r="F108" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>70.05</v>
+        <v>71.2</v>
       </c>
       <c r="H108" t="n">
-        <v>1.52</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-30.3</v>
+        <v>136.53</v>
       </c>
       <c r="C109" t="n">
-        <v>5.18651221</v>
+        <v>5.19347821</v>
       </c>
       <c r="D109" t="n">
-        <v>68.05</v>
+        <v>71.2</v>
       </c>
       <c r="E109" t="n">
-        <v>69.34999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G109" t="n">
-        <v>68.8</v>
+        <v>71.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-92.3</v>
+        <v>-224.29</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17728221</v>
+        <v>5.17104921</v>
       </c>
       <c r="D110" t="n">
-        <v>68.8</v>
+        <v>73.45</v>
       </c>
       <c r="E110" t="n">
-        <v>69.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="F110" t="n">
-        <v>67.2</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>67.7</v>
+        <v>73.3</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.6</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>25.43</v>
+        <v>97.7422</v>
       </c>
       <c r="C111" t="n">
-        <v>5.17982521</v>
+        <v>5.18082343</v>
       </c>
       <c r="D111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="E111" t="n">
-        <v>71.45</v>
+        <v>73.5</v>
       </c>
       <c r="F111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G111" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>5.17</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>136.53</v>
+        <v>-116.85</v>
       </c>
       <c r="C112" t="n">
-        <v>5.19347821</v>
+        <v>5.16913843</v>
       </c>
       <c r="D112" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E112" t="n">
-        <v>73.40000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="F112" t="n">
-        <v>70</v>
+        <v>71.55</v>
       </c>
       <c r="G112" t="n">
-        <v>71.8</v>
+        <v>74.2</v>
       </c>
       <c r="H112" t="n">
-        <v>0.84</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-224.29</v>
+        <v>32.76</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17104921</v>
+        <v>5.17241443</v>
       </c>
       <c r="D113" t="n">
-        <v>73.45</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F113" t="n">
-        <v>71.65000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="G113" t="n">
-        <v>73.3</v>
+        <v>73.7</v>
       </c>
       <c r="H113" t="n">
-        <v>2.09</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>97.7422</v>
+        <v>-19.6</v>
       </c>
       <c r="C114" t="n">
-        <v>5.18082343</v>
+        <v>5.17045443</v>
       </c>
       <c r="D114" t="n">
-        <v>71.95</v>
+        <v>73.7</v>
       </c>
       <c r="E114" t="n">
-        <v>73.5</v>
+        <v>73.95</v>
       </c>
       <c r="F114" t="n">
-        <v>71.75</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.91</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-116.85</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>5.16913843</v>
+        <v>5.17787843</v>
       </c>
       <c r="D115" t="n">
-        <v>71.90000000000001</v>
+        <v>73.75</v>
       </c>
       <c r="E115" t="n">
-        <v>76.45</v>
+        <v>73.75</v>
       </c>
       <c r="F115" t="n">
-        <v>71.55</v>
+        <v>70.5</v>
       </c>
       <c r="G115" t="n">
-        <v>74.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>3.2</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>32.76</v>
+        <v>15.04</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17241443</v>
+        <v>5.17938243</v>
       </c>
       <c r="D116" t="n">
-        <v>74.09999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E116" t="n">
-        <v>75</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>73.25</v>
+        <v>70.95</v>
       </c>
       <c r="G116" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.67</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-19.6</v>
+        <v>213.47</v>
       </c>
       <c r="C117" t="n">
-        <v>5.17045443</v>
+        <v>5.20072943</v>
       </c>
       <c r="D117" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>73.95</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>71.65000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>73</v>
+        <v>71.45</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.95</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>74.23999999999999</v>
+        <v>-167.67</v>
       </c>
       <c r="C118" t="n">
-        <v>5.17787843</v>
+        <v>5.18396243</v>
       </c>
       <c r="D118" t="n">
-        <v>73.75</v>
+        <v>72</v>
       </c>
       <c r="E118" t="n">
-        <v>73.75</v>
+        <v>73.45</v>
       </c>
       <c r="F118" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>70.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.88</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15.04</v>
+        <v>-78.5919</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17938243</v>
+        <v>5.17610324</v>
       </c>
       <c r="D119" t="n">
-        <v>70.95</v>
+        <v>73.3</v>
       </c>
       <c r="E119" t="n">
-        <v>72.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F119" t="n">
-        <v>70.95</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H119" t="n">
-        <v>0.99</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>213.47</v>
+        <v>-54.57</v>
       </c>
       <c r="C120" t="n">
-        <v>5.20072943</v>
+        <v>5.17064624</v>
       </c>
       <c r="D120" t="n">
-        <v>71.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E120" t="n">
-        <v>71.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>70.40000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G120" t="n">
-        <v>71.45</v>
+        <v>73.45</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-167.67</v>
+        <v>32.9</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18396243</v>
+        <v>5.17393624</v>
       </c>
       <c r="D121" t="n">
-        <v>72</v>
+        <v>73.45</v>
       </c>
       <c r="E121" t="n">
-        <v>73.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>70.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G121" t="n">
-        <v>73.3</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>2.59</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-78.5919</v>
+        <v>41.93</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17610324</v>
+        <v>5.17812924</v>
       </c>
       <c r="D122" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="E122" t="n">
-        <v>73.3</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>71.84999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G122" t="n">
-        <v>73.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.14</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-54.57</v>
+        <v>52.87</v>
       </c>
       <c r="C123" t="n">
-        <v>5.17064624</v>
+        <v>5.18341624</v>
       </c>
       <c r="D123" t="n">
-        <v>72.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>73.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="F123" t="n">
-        <v>71.95</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>73.45</v>
+        <v>69.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0.34</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>32.9</v>
+        <v>291.58</v>
       </c>
       <c r="C124" t="n">
-        <v>5.17393624</v>
+        <v>5.21257424</v>
       </c>
       <c r="D124" t="n">
-        <v>73.45</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>74.40000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F124" t="n">
-        <v>71.75</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>73.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.41</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>41.93</v>
+        <v>-60.7601</v>
       </c>
       <c r="C125" t="n">
-        <v>5.17812924</v>
+        <v>5.20649823</v>
       </c>
       <c r="D125" t="n">
-        <v>73</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E125" t="n">
-        <v>73.65000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="F125" t="n">
-        <v>68.7</v>
+        <v>68.45</v>
       </c>
       <c r="G125" t="n">
-        <v>69.90000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="H125" t="n">
-        <v>-4.44</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>52.87</v>
+        <v>264.89</v>
       </c>
       <c r="C126" t="n">
-        <v>5.18341624</v>
+        <v>5.23298723</v>
       </c>
       <c r="D126" t="n">
-        <v>70.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>70.5</v>
+        <v>69.75</v>
       </c>
       <c r="F126" t="n">
-        <v>68.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="G126" t="n">
-        <v>69.7</v>
+        <v>67.55</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.29</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>291.58</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>5.21257424</v>
+        <v>5.23298723</v>
       </c>
       <c r="D127" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="E127" t="n">
-        <v>69.45</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>66.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G127" t="n">
-        <v>67</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>-3.87</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-60.7601</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>5.20649823</v>
+        <v>5.23298723</v>
       </c>
       <c r="D128" t="n">
-        <v>69.40000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="E128" t="n">
-        <v>70.25</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>68.45</v>
+        <v>68.2</v>
       </c>
       <c r="G128" t="n">
-        <v>69.25</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>3.36</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>264.89</v>
+        <v>-369.37</v>
       </c>
       <c r="C129" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D129" t="n">
-        <v>68.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E129" t="n">
-        <v>69.75</v>
+        <v>69.5</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.55</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.45</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D130" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="E130" t="n">
-        <v>69.75</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="G130" t="n">
-        <v>67.55</v>
+        <v>69.95</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>68.9663</v>
       </c>
       <c r="C131" t="n">
-        <v>5.23298723</v>
+        <v>5.20294686</v>
       </c>
       <c r="D131" t="n">
-        <v>69</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>71.15000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F131" t="n">
-        <v>68.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>70.15000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="H131" t="n">
-        <v>3.85</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>-247.41</v>
       </c>
       <c r="C132" t="n">
-        <v>5.23298723</v>
+        <v>5.17820586</v>
       </c>
       <c r="D132" t="n">
-        <v>69.25</v>
+        <v>69.5</v>
       </c>
       <c r="E132" t="n">
-        <v>70.09999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>68.2</v>
+        <v>69.45</v>
       </c>
       <c r="G132" t="n">
-        <v>69.65000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.71</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-369.37</v>
+        <v>27.55</v>
       </c>
       <c r="C133" t="n">
-        <v>5.19605023</v>
+        <v>5.18096086</v>
       </c>
       <c r="D133" t="n">
-        <v>69.5</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E133" t="n">
-        <v>69.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>67.3</v>
+        <v>73.05</v>
       </c>
       <c r="G133" t="n">
-        <v>67.84999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>-2.58</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>-286.2</v>
       </c>
       <c r="C134" t="n">
-        <v>5.19605023</v>
+        <v>5.15234086</v>
       </c>
       <c r="D134" t="n">
-        <v>68.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>70.34999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>68.5</v>
+        <v>73.05</v>
       </c>
       <c r="G134" t="n">
-        <v>69.95</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>3.1</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>68.9663</v>
+        <v>48.88</v>
       </c>
       <c r="C135" t="n">
-        <v>5.20294686</v>
+        <v>5.15722886</v>
       </c>
       <c r="D135" t="n">
-        <v>68.34999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="E135" t="n">
-        <v>70.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>68.34999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>70.05</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H135" t="n">
-        <v>0.14</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-247.41</v>
+        <v>-55.96</v>
       </c>
       <c r="C136" t="n">
-        <v>5.17820586</v>
+        <v>5.15163286</v>
       </c>
       <c r="D136" t="n">
-        <v>69.5</v>
+        <v>75.05</v>
       </c>
       <c r="E136" t="n">
-        <v>74.15000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>69.45</v>
+        <v>74.25</v>
       </c>
       <c r="G136" t="n">
-        <v>73.84999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>5.42</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>27.55</v>
+        <v>-385.85</v>
       </c>
       <c r="C137" t="n">
-        <v>5.18096086</v>
+        <v>5.11304786</v>
       </c>
       <c r="D137" t="n">
-        <v>73.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>75.15000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>73.05</v>
+        <v>64.5</v>
       </c>
       <c r="G137" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.61</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-286.2</v>
+        <v>139.59</v>
       </c>
       <c r="C138" t="n">
-        <v>5.15234086</v>
+        <v>5.12700686</v>
       </c>
       <c r="D138" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>74.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>73.05</v>
+        <v>61.75</v>
       </c>
       <c r="G138" t="n">
-        <v>73.65000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.34</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>48.88</v>
+        <v>1468.42</v>
       </c>
       <c r="C139" t="n">
-        <v>5.15722886</v>
+        <v>5.27384886</v>
       </c>
       <c r="D139" t="n">
-        <v>76.8</v>
+        <v>62.6</v>
       </c>
       <c r="E139" t="n">
-        <v>78.90000000000001</v>
+        <v>63.35</v>
       </c>
       <c r="F139" t="n">
-        <v>75.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="G139" t="n">
-        <v>76.84999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="H139" t="n">
-        <v>4.34</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-55.96</v>
+        <v>292.93</v>
       </c>
       <c r="C140" t="n">
-        <v>5.15163286</v>
+        <v>5.30314186</v>
       </c>
       <c r="D140" t="n">
-        <v>75.05</v>
+        <v>62.5</v>
       </c>
       <c r="E140" t="n">
-        <v>75.90000000000001</v>
+        <v>63.85</v>
       </c>
       <c r="F140" t="n">
-        <v>74.25</v>
+        <v>61.55</v>
       </c>
       <c r="G140" t="n">
-        <v>75.59999999999999</v>
+        <v>62.25</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.63</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-385.85</v>
+        <v>17.9</v>
       </c>
       <c r="C141" t="n">
-        <v>5.11304786</v>
+        <v>5.30493186</v>
       </c>
       <c r="D141" t="n">
-        <v>72.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="E141" t="n">
-        <v>72.40000000000001</v>
+        <v>64.95</v>
       </c>
       <c r="F141" t="n">
-        <v>64.5</v>
+        <v>61.35</v>
       </c>
       <c r="G141" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-14.15</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>139.59</v>
+        <v>-224.88</v>
       </c>
       <c r="C142" t="n">
-        <v>5.12700686</v>
+        <v>5.28244386</v>
       </c>
       <c r="D142" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="E142" t="n">
-        <v>64.90000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="F142" t="n">
-        <v>61.75</v>
+        <v>60.4</v>
       </c>
       <c r="G142" t="n">
-        <v>62.1</v>
+        <v>62.15</v>
       </c>
       <c r="H142" t="n">
-        <v>-4.31</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1468.42</v>
+        <v>-244.5</v>
       </c>
       <c r="C143" t="n">
-        <v>5.27384886</v>
+        <v>5.25799386</v>
       </c>
       <c r="D143" t="n">
-        <v>62.6</v>
+        <v>61.9</v>
       </c>
       <c r="E143" t="n">
-        <v>63.35</v>
+        <v>62.35</v>
       </c>
       <c r="F143" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="G143" t="n">
-        <v>61.6</v>
+        <v>60.2</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>292.93</v>
+        <v>-302.48</v>
       </c>
       <c r="C144" t="n">
-        <v>5.30314186</v>
+        <v>5.22774586</v>
       </c>
       <c r="D144" t="n">
-        <v>62.5</v>
+        <v>60.1</v>
       </c>
       <c r="E144" t="n">
-        <v>63.85</v>
+        <v>61</v>
       </c>
       <c r="F144" t="n">
-        <v>61.55</v>
+        <v>58.6</v>
       </c>
       <c r="G144" t="n">
-        <v>62.25</v>
+        <v>60.45</v>
       </c>
       <c r="H144" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>17.9</v>
+        <v>-177.8636</v>
       </c>
       <c r="C145" t="n">
-        <v>5.30493186</v>
+        <v>5.2099595</v>
       </c>
       <c r="D145" t="n">
-        <v>63.2</v>
+        <v>60</v>
       </c>
       <c r="E145" t="n">
-        <v>64.95</v>
+        <v>60.05</v>
       </c>
       <c r="F145" t="n">
-        <v>61.35</v>
+        <v>55.7</v>
       </c>
       <c r="G145" t="n">
-        <v>61.8</v>
+        <v>57.85</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.72</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-224.88</v>
+        <v>-228.55</v>
       </c>
       <c r="C146" t="n">
-        <v>5.28244386</v>
+        <v>5.1871045</v>
       </c>
       <c r="D146" t="n">
-        <v>61.8</v>
+        <v>56.95</v>
       </c>
       <c r="E146" t="n">
-        <v>62.25</v>
+        <v>59.1</v>
       </c>
       <c r="F146" t="n">
-        <v>60.4</v>
+        <v>56</v>
       </c>
       <c r="G146" t="n">
-        <v>62.15</v>
+        <v>58.55</v>
       </c>
       <c r="H146" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-244.5</v>
+        <v>423.9973</v>
       </c>
       <c r="C147" t="n">
-        <v>5.25799386</v>
+        <v>5.22950423</v>
       </c>
       <c r="D147" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="E147" t="n">
+        <v>62</v>
+      </c>
+      <c r="F147" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G147" t="n">
         <v>61.9</v>
       </c>
-      <c r="E147" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="F147" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G147" t="n">
-        <v>60.2</v>
-      </c>
       <c r="H147" t="n">
-        <v>-3.14</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-302.48</v>
+        <v>-119.16</v>
       </c>
       <c r="C148" t="n">
-        <v>5.22774586</v>
+        <v>5.21758823</v>
       </c>
       <c r="D148" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="E148" t="n">
-        <v>61</v>
+        <v>60.75</v>
       </c>
       <c r="F148" t="n">
-        <v>58.6</v>
+        <v>58.75</v>
       </c>
       <c r="G148" t="n">
-        <v>60.45</v>
+        <v>59.1</v>
       </c>
       <c r="H148" t="n">
-        <v>0.42</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-177.8636</v>
+        <v>-301.92</v>
       </c>
       <c r="C149" t="n">
-        <v>5.2099595</v>
+        <v>5.18739623</v>
       </c>
       <c r="D149" t="n">
-        <v>60</v>
+        <v>58.95</v>
       </c>
       <c r="E149" t="n">
-        <v>60.05</v>
+        <v>58.95</v>
       </c>
       <c r="F149" t="n">
-        <v>55.7</v>
+        <v>56.85</v>
       </c>
       <c r="G149" t="n">
-        <v>57.85</v>
+        <v>57.25</v>
       </c>
       <c r="H149" t="n">
-        <v>-4.3</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-228.55</v>
+        <v>112.29</v>
       </c>
       <c r="C150" t="n">
-        <v>5.1871045</v>
+        <v>5.19862523</v>
       </c>
       <c r="D150" t="n">
-        <v>56.95</v>
+        <v>57.1</v>
       </c>
       <c r="E150" t="n">
-        <v>59.1</v>
+        <v>57.6</v>
       </c>
       <c r="F150" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G150" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="H150" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>423.9973</v>
+        <v>-62.4836</v>
       </c>
       <c r="C151" t="n">
-        <v>5.22950423</v>
+        <v>5.19237687</v>
       </c>
       <c r="D151" t="n">
-        <v>57.05</v>
+        <v>55.3</v>
       </c>
       <c r="E151" t="n">
-        <v>62</v>
+        <v>57.9</v>
       </c>
       <c r="F151" t="n">
-        <v>56.55</v>
+        <v>54.95</v>
       </c>
       <c r="G151" t="n">
-        <v>61.9</v>
+        <v>57.35</v>
       </c>
       <c r="H151" t="n">
-        <v>5.72</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-119.16</v>
+        <v>-29.35</v>
       </c>
       <c r="C152" t="n">
-        <v>5.21758823</v>
+        <v>5.18944187</v>
       </c>
       <c r="D152" t="n">
-        <v>60.5</v>
+        <v>56.2</v>
       </c>
       <c r="E152" t="n">
-        <v>60.75</v>
+        <v>57.1</v>
       </c>
       <c r="F152" t="n">
-        <v>58.75</v>
+        <v>55.8</v>
       </c>
       <c r="G152" t="n">
-        <v>59.1</v>
+        <v>55.85</v>
       </c>
       <c r="H152" t="n">
-        <v>-4.52</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-301.92</v>
+        <v>54.46</v>
       </c>
       <c r="C153" t="n">
-        <v>5.18739623</v>
+        <v>5.19488787</v>
       </c>
       <c r="D153" t="n">
-        <v>58.95</v>
+        <v>55.3</v>
       </c>
       <c r="E153" t="n">
-        <v>58.95</v>
+        <v>55.55</v>
       </c>
       <c r="F153" t="n">
-        <v>56.85</v>
+        <v>53.25</v>
       </c>
       <c r="G153" t="n">
-        <v>57.25</v>
+        <v>54.7</v>
       </c>
       <c r="H153" t="n">
-        <v>-3.13</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>112.29</v>
+        <v>17.32</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19862523</v>
+        <v>5.19661987</v>
       </c>
       <c r="D154" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E154" t="n">
-        <v>57.6</v>
+        <v>54.1</v>
       </c>
       <c r="F154" t="n">
-        <v>56.5</v>
+        <v>52.25</v>
       </c>
       <c r="G154" t="n">
-        <v>56.65</v>
+        <v>53.15</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.05</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-62.4836</v>
+        <v>93.42</v>
       </c>
       <c r="C155" t="n">
-        <v>5.19237687</v>
+        <v>5.20596187</v>
       </c>
       <c r="D155" t="n">
-        <v>55.3</v>
+        <v>53.7</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>54.95</v>
+        <v>53.25</v>
       </c>
       <c r="G155" t="n">
-        <v>57.35</v>
+        <v>57</v>
       </c>
       <c r="H155" t="n">
-        <v>1.24</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-29.35</v>
+        <v>64.81</v>
       </c>
       <c r="C156" t="n">
-        <v>5.18944187</v>
+        <v>5.21244287</v>
       </c>
       <c r="D156" t="n">
-        <v>56.2</v>
+        <v>56.6</v>
       </c>
       <c r="E156" t="n">
-        <v>57.1</v>
+        <v>58.05</v>
       </c>
       <c r="F156" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="G156" t="n">
-        <v>55.85</v>
+        <v>56.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.62</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>54.46</v>
+        <v>-172.75</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19488787</v>
+        <v>5.19516787</v>
       </c>
       <c r="D157" t="n">
-        <v>55.3</v>
+        <v>56.85</v>
       </c>
       <c r="E157" t="n">
-        <v>55.55</v>
+        <v>57.2</v>
       </c>
       <c r="F157" t="n">
-        <v>53.25</v>
+        <v>55</v>
       </c>
       <c r="G157" t="n">
-        <v>54.7</v>
+        <v>56</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.06</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>17.32</v>
+        <v>-24.86</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19661987</v>
+        <v>5.19268187</v>
       </c>
       <c r="D158" t="n">
-        <v>54</v>
+        <v>55.75</v>
       </c>
       <c r="E158" t="n">
-        <v>54.1</v>
+        <v>55.8</v>
       </c>
       <c r="F158" t="n">
-        <v>52.25</v>
+        <v>53.7</v>
       </c>
       <c r="G158" t="n">
-        <v>53.15</v>
+        <v>53.9</v>
       </c>
       <c r="H158" t="n">
-        <v>-2.83</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>93.42</v>
+        <v>17.38</v>
       </c>
       <c r="C159" t="n">
-        <v>5.20596187</v>
+        <v>5.19441987</v>
       </c>
       <c r="D159" t="n">
-        <v>53.7</v>
+        <v>53.25</v>
       </c>
       <c r="E159" t="n">
-        <v>57.9</v>
+        <v>53.9</v>
       </c>
       <c r="F159" t="n">
-        <v>53.25</v>
+        <v>51.75</v>
       </c>
       <c r="G159" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H159" t="n">
-        <v>7.24</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>64.81</v>
+        <v>14.06</v>
       </c>
       <c r="C160" t="n">
-        <v>5.21244287</v>
+        <v>5.19582587</v>
       </c>
       <c r="D160" t="n">
-        <v>56.6</v>
+        <v>50.15</v>
       </c>
       <c r="E160" t="n">
-        <v>58.05</v>
+        <v>51.55</v>
       </c>
       <c r="F160" t="n">
-        <v>56.5</v>
+        <v>49.64</v>
       </c>
       <c r="G160" t="n">
-        <v>56.85</v>
+        <v>50.5</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.26</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-172.75</v>
+        <v>-21.2345</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19516787</v>
+        <v>5.19370242</v>
       </c>
       <c r="D161" t="n">
-        <v>56.85</v>
+        <v>50</v>
       </c>
       <c r="E161" t="n">
-        <v>57.2</v>
+        <v>50.8</v>
       </c>
       <c r="F161" t="n">
-        <v>55</v>
+        <v>47.9</v>
       </c>
       <c r="G161" t="n">
-        <v>56</v>
+        <v>48.32</v>
       </c>
       <c r="H161" t="n">
-        <v>-1.5</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-24.86</v>
+        <v>47.7</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19268187</v>
+        <v>5.19847242</v>
       </c>
       <c r="D162" t="n">
-        <v>55.75</v>
+        <v>48.98</v>
       </c>
       <c r="E162" t="n">
-        <v>55.8</v>
+        <v>49.94</v>
       </c>
       <c r="F162" t="n">
-        <v>53.7</v>
+        <v>48.18</v>
       </c>
       <c r="G162" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="H162" t="n">
-        <v>-3.75</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>17.38</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C163" t="n">
-        <v>5.19441987</v>
+        <v>5.20773242</v>
       </c>
       <c r="D163" t="n">
-        <v>53.25</v>
+        <v>49.44</v>
       </c>
       <c r="E163" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="F163" t="n">
-        <v>51.75</v>
+        <v>46.74</v>
       </c>
       <c r="G163" t="n">
-        <v>52</v>
+        <v>47.4</v>
       </c>
       <c r="H163" t="n">
-        <v>-3.53</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>14.06</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19582587</v>
+        <v>5.19818142</v>
       </c>
       <c r="D164" t="n">
-        <v>50.15</v>
+        <v>47</v>
       </c>
       <c r="E164" t="n">
-        <v>51.55</v>
+        <v>47</v>
       </c>
       <c r="F164" t="n">
-        <v>49.64</v>
+        <v>45.86</v>
       </c>
       <c r="G164" t="n">
-        <v>50.5</v>
+        <v>46.28</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.88</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-21.2345</v>
+        <v>-254.06</v>
       </c>
       <c r="C165" t="n">
-        <v>5.19370242</v>
+        <v>5.17277542</v>
       </c>
       <c r="D165" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="E165" t="n">
-        <v>50.8</v>
+        <v>47.18</v>
       </c>
       <c r="F165" t="n">
-        <v>47.9</v>
+        <v>45.76</v>
       </c>
       <c r="G165" t="n">
-        <v>48.32</v>
+        <v>45.9</v>
       </c>
       <c r="H165" t="n">
-        <v>-4.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>47.7</v>
+        <v>-316.19</v>
       </c>
       <c r="C166" t="n">
-        <v>5.19847242</v>
+        <v>5.14115642</v>
       </c>
       <c r="D166" t="n">
-        <v>48.98</v>
+        <v>45.9</v>
       </c>
       <c r="E166" t="n">
-        <v>49.94</v>
+        <v>46.78</v>
       </c>
       <c r="F166" t="n">
-        <v>48.18</v>
+        <v>45.26</v>
       </c>
       <c r="G166" t="n">
-        <v>49.44</v>
+        <v>46.08</v>
       </c>
       <c r="H166" t="n">
-        <v>2.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>92.59999999999999</v>
+        <v>-150.87</v>
       </c>
       <c r="C167" t="n">
-        <v>5.20773242</v>
+        <v>5.12606942</v>
       </c>
       <c r="D167" t="n">
-        <v>49.44</v>
+        <v>47.7</v>
       </c>
       <c r="E167" t="n">
-        <v>49.44</v>
+        <v>48.9</v>
       </c>
       <c r="F167" t="n">
-        <v>46.74</v>
+        <v>46.64</v>
       </c>
       <c r="G167" t="n">
-        <v>47.4</v>
+        <v>46.84</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.13</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-95.51000000000001</v>
+        <v>-236.76</v>
       </c>
       <c r="C168" t="n">
-        <v>5.19818142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D168" t="n">
-        <v>47</v>
+        <v>46.92</v>
       </c>
       <c r="E168" t="n">
-        <v>47</v>
+        <v>48.28</v>
       </c>
       <c r="F168" t="n">
-        <v>45.86</v>
+        <v>46.84</v>
       </c>
       <c r="G168" t="n">
-        <v>46.28</v>
+        <v>47.36</v>
       </c>
       <c r="H168" t="n">
-        <v>-2.36</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-254.06</v>
+        <v>-36.92</v>
       </c>
       <c r="C169" t="n">
-        <v>5.17277542</v>
+        <v>5.09870142</v>
       </c>
       <c r="D169" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E169" t="n">
-        <v>47.18</v>
+        <v>47.56</v>
       </c>
       <c r="F169" t="n">
-        <v>45.76</v>
+        <v>45.72</v>
       </c>
       <c r="G169" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.82</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-316.19</v>
+        <v>64.78</v>
       </c>
       <c r="C170" t="n">
-        <v>5.14115642</v>
+        <v>5.10517942</v>
       </c>
       <c r="D170" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="E170" t="n">
-        <v>46.78</v>
+        <v>48.42</v>
       </c>
       <c r="F170" t="n">
-        <v>45.26</v>
+        <v>46.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.08</v>
+        <v>46.6</v>
       </c>
       <c r="H170" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-150.87</v>
+        <v>-44.41</v>
       </c>
       <c r="C171" t="n">
-        <v>5.12606942</v>
+        <v>5.10073842</v>
       </c>
       <c r="D171" t="n">
-        <v>47.7</v>
+        <v>47.06</v>
       </c>
       <c r="E171" t="n">
-        <v>48.9</v>
+        <v>48.98</v>
       </c>
       <c r="F171" t="n">
-        <v>46.64</v>
+        <v>46.7</v>
       </c>
       <c r="G171" t="n">
-        <v>46.84</v>
+        <v>48.52</v>
       </c>
       <c r="H171" t="n">
-        <v>1.65</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-236.76</v>
+        <v>-124.97</v>
       </c>
       <c r="C172" t="n">
-        <v>5.10239342</v>
+        <v>5.08824142</v>
       </c>
       <c r="D172" t="n">
-        <v>46.92</v>
+        <v>47.6</v>
       </c>
       <c r="E172" t="n">
-        <v>48.28</v>
+        <v>48.08</v>
       </c>
       <c r="F172" t="n">
-        <v>46.84</v>
+        <v>46.72</v>
       </c>
       <c r="G172" t="n">
-        <v>47.36</v>
+        <v>46.76</v>
       </c>
       <c r="H172" t="n">
-        <v>1.11</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-36.92</v>
+        <v>-272.6</v>
       </c>
       <c r="C173" t="n">
-        <v>5.09870142</v>
+        <v>5.06098142</v>
       </c>
       <c r="D173" t="n">
-        <v>47</v>
+        <v>46.76</v>
       </c>
       <c r="E173" t="n">
-        <v>47.56</v>
+        <v>48.3</v>
       </c>
       <c r="F173" t="n">
-        <v>45.72</v>
+        <v>46.02</v>
       </c>
       <c r="G173" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="H173" t="n">
-        <v>-2.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>64.78</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C174" t="n">
-        <v>5.10517942</v>
+        <v>5.06933542</v>
       </c>
       <c r="D174" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="E174" t="n">
-        <v>48.42</v>
+        <v>47.92</v>
       </c>
       <c r="F174" t="n">
-        <v>46.26</v>
+        <v>46.46</v>
       </c>
       <c r="G174" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="H174" t="n">
-        <v>0.73</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-44.41</v>
+        <v>-232.94</v>
       </c>
       <c r="C175" t="n">
-        <v>5.10073842</v>
+        <v>5.04604142</v>
       </c>
       <c r="D175" t="n">
-        <v>47.06</v>
+        <v>47.2</v>
       </c>
       <c r="E175" t="n">
-        <v>48.98</v>
+        <v>48.84</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.52</v>
+        <v>48.56</v>
       </c>
       <c r="H175" t="n">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-124.97</v>
+        <v>-101.2265</v>
       </c>
       <c r="C176" t="n">
-        <v>5.08824142</v>
+        <v>5.03591877</v>
       </c>
       <c r="D176" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="E176" t="n">
-        <v>48.08</v>
+        <v>49.46</v>
       </c>
       <c r="F176" t="n">
-        <v>46.72</v>
+        <v>48.24</v>
       </c>
       <c r="G176" t="n">
-        <v>46.76</v>
+        <v>48.78</v>
       </c>
       <c r="H176" t="n">
-        <v>-3.63</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-272.6</v>
+        <v>-146.01</v>
       </c>
       <c r="C177" t="n">
-        <v>5.06098142</v>
+        <v>5.02131777</v>
       </c>
       <c r="D177" t="n">
-        <v>46.76</v>
+        <v>49.22</v>
       </c>
       <c r="E177" t="n">
-        <v>48.3</v>
+        <v>51</v>
       </c>
       <c r="F177" t="n">
-        <v>46.02</v>
+        <v>49.22</v>
       </c>
       <c r="G177" t="n">
-        <v>47.42</v>
+        <v>50.4</v>
       </c>
       <c r="H177" t="n">
-        <v>1.41</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>83.54000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C178" t="n">
-        <v>5.06933542</v>
+        <v>5.02274277</v>
       </c>
       <c r="D178" t="n">
-        <v>47.42</v>
+        <v>50.55</v>
       </c>
       <c r="E178" t="n">
-        <v>47.92</v>
+        <v>51</v>
       </c>
       <c r="F178" t="n">
-        <v>46.46</v>
+        <v>48.2</v>
       </c>
       <c r="G178" t="n">
-        <v>47.2</v>
+        <v>48.94</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.46</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-232.94</v>
+        <v>7.54</v>
       </c>
       <c r="C179" t="n">
-        <v>5.04604142</v>
+        <v>5.02349677</v>
       </c>
       <c r="D179" t="n">
-        <v>47.2</v>
+        <v>49.96</v>
       </c>
       <c r="E179" t="n">
-        <v>48.84</v>
+        <v>49.98</v>
       </c>
       <c r="F179" t="n">
-        <v>46.7</v>
+        <v>48.72</v>
       </c>
       <c r="G179" t="n">
-        <v>48.56</v>
+        <v>49.12</v>
       </c>
       <c r="H179" t="n">
-        <v>2.88</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-101.2265</v>
+        <v>29.93</v>
       </c>
       <c r="C180" t="n">
-        <v>5.03591877</v>
+        <v>5.02648977</v>
       </c>
       <c r="D180" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="E180" t="n">
-        <v>49.46</v>
+        <v>49.36</v>
       </c>
       <c r="F180" t="n">
-        <v>48.24</v>
+        <v>48.18</v>
       </c>
       <c r="G180" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="H180" t="n">
-        <v>0.45</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-146.01</v>
+        <v>-93.37</v>
       </c>
       <c r="C181" t="n">
-        <v>5.02131777</v>
+        <v>5.01715277</v>
       </c>
       <c r="D181" t="n">
-        <v>49.22</v>
+        <v>48.4</v>
       </c>
       <c r="E181" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
       <c r="F181" t="n">
-        <v>49.22</v>
+        <v>47.2</v>
       </c>
       <c r="G181" t="n">
-        <v>50.4</v>
+        <v>47.64</v>
       </c>
       <c r="H181" t="n">
-        <v>3.32</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>14.25</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C182" t="n">
-        <v>5.02274277</v>
+        <v>5.00778777</v>
       </c>
       <c r="D182" t="n">
-        <v>50.55</v>
+        <v>47.64</v>
       </c>
       <c r="E182" t="n">
-        <v>51</v>
+        <v>49.3</v>
       </c>
       <c r="F182" t="n">
-        <v>48.2</v>
+        <v>47.22</v>
       </c>
       <c r="G182" t="n">
-        <v>48.94</v>
+        <v>48.96</v>
       </c>
       <c r="H182" t="n">
-        <v>-2.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7.54</v>
+        <v>28.06</v>
       </c>
       <c r="C183" t="n">
-        <v>5.02349677</v>
+        <v>5.01059377</v>
       </c>
       <c r="D183" t="n">
-        <v>49.96</v>
+        <v>48.36</v>
       </c>
       <c r="E183" t="n">
-        <v>49.98</v>
+        <v>48.76</v>
       </c>
       <c r="F183" t="n">
-        <v>48.72</v>
+        <v>47.52</v>
       </c>
       <c r="G183" t="n">
-        <v>49.12</v>
+        <v>47.98</v>
       </c>
       <c r="H183" t="n">
-        <v>0.37</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>29.93</v>
+        <v>-160.94</v>
       </c>
       <c r="C184" t="n">
-        <v>5.02648977</v>
+        <v>4.99449977</v>
       </c>
       <c r="D184" t="n">
-        <v>49.1</v>
+        <v>47.98</v>
       </c>
       <c r="E184" t="n">
-        <v>49.36</v>
+        <v>48.46</v>
       </c>
       <c r="F184" t="n">
-        <v>48.18</v>
+        <v>47.32</v>
       </c>
       <c r="G184" t="n">
-        <v>48.64</v>
+        <v>48.08</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.98</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-93.37</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C185" t="n">
-        <v>5.01715277</v>
+        <v>5.00218477</v>
       </c>
       <c r="D185" t="n">
-        <v>48.4</v>
+        <v>49.54</v>
       </c>
       <c r="E185" t="n">
-        <v>48.4</v>
+        <v>50.5</v>
       </c>
       <c r="F185" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="G185" t="n">
-        <v>47.64</v>
+        <v>49.68</v>
       </c>
       <c r="H185" t="n">
-        <v>-2.06</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-93.65000000000001</v>
+        <v>-70.88</v>
       </c>
       <c r="C186" t="n">
-        <v>5.00778777</v>
+        <v>4.99509677</v>
       </c>
       <c r="D186" t="n">
-        <v>47.64</v>
+        <v>51.9</v>
       </c>
       <c r="E186" t="n">
-        <v>49.3</v>
+        <v>55.6</v>
       </c>
       <c r="F186" t="n">
-        <v>47.22</v>
+        <v>51.9</v>
       </c>
       <c r="G186" t="n">
-        <v>48.96</v>
+        <v>54.6</v>
       </c>
       <c r="H186" t="n">
-        <v>2.77</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>28.06</v>
+        <v>-223.97</v>
       </c>
       <c r="C187" t="n">
-        <v>5.01059377</v>
+        <v>4.97269977</v>
       </c>
       <c r="D187" t="n">
-        <v>48.36</v>
+        <v>54.7</v>
       </c>
       <c r="E187" t="n">
-        <v>48.76</v>
+        <v>56.1</v>
       </c>
       <c r="F187" t="n">
-        <v>47.52</v>
+        <v>53.7</v>
       </c>
       <c r="G187" t="n">
-        <v>47.98</v>
+        <v>54.25</v>
       </c>
       <c r="H187" t="n">
-        <v>-2</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-160.94</v>
+        <v>-908.88</v>
       </c>
       <c r="C188" t="n">
-        <v>4.99449977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D188" t="n">
-        <v>47.98</v>
+        <v>52.85</v>
       </c>
       <c r="E188" t="n">
-        <v>48.46</v>
+        <v>53.8</v>
       </c>
       <c r="F188" t="n">
-        <v>47.32</v>
+        <v>51.3</v>
       </c>
       <c r="G188" t="n">
-        <v>48.08</v>
+        <v>53.4</v>
       </c>
       <c r="H188" t="n">
-        <v>0.21</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>76.84999999999999</v>
+        <v>-219</v>
       </c>
       <c r="C189" t="n">
-        <v>5.00218477</v>
+        <v>4.85991177</v>
       </c>
       <c r="D189" t="n">
-        <v>49.54</v>
+        <v>52.75</v>
       </c>
       <c r="E189" t="n">
-        <v>50.5</v>
+        <v>54.45</v>
       </c>
       <c r="F189" t="n">
-        <v>48.9</v>
+        <v>51.45</v>
       </c>
       <c r="G189" t="n">
-        <v>49.68</v>
+        <v>51.85</v>
       </c>
       <c r="H189" t="n">
-        <v>3.33</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>-70.88</v>
+        <v>81.19</v>
       </c>
       <c r="C190" t="n">
-        <v>4.99509677</v>
+        <v>4.86803077</v>
       </c>
       <c r="D190" t="n">
-        <v>51.9</v>
+        <v>51.85</v>
       </c>
       <c r="E190" t="n">
-        <v>55.6</v>
+        <v>51.85</v>
       </c>
       <c r="F190" t="n">
-        <v>51.9</v>
+        <v>49.6</v>
       </c>
       <c r="G190" t="n">
-        <v>54.6</v>
+        <v>50.45</v>
       </c>
       <c r="H190" t="n">
-        <v>9.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-223.97</v>
+        <v>7.21</v>
       </c>
       <c r="C191" t="n">
-        <v>4.97269977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D191" t="n">
-        <v>54.7</v>
+        <v>50.05</v>
       </c>
       <c r="E191" t="n">
-        <v>56.1</v>
+        <v>50.8</v>
       </c>
       <c r="F191" t="n">
-        <v>53.7</v>
+        <v>49.52</v>
       </c>
       <c r="G191" t="n">
-        <v>54.25</v>
+        <v>50.65</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.64</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-908.88</v>
+        <v>144.28</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88181177</v>
+        <v>4.88317977</v>
       </c>
       <c r="D192" t="n">
-        <v>52.85</v>
+        <v>50</v>
       </c>
       <c r="E192" t="n">
-        <v>53.8</v>
+        <v>50.6</v>
       </c>
       <c r="F192" t="n">
-        <v>51.3</v>
+        <v>49.08</v>
       </c>
       <c r="G192" t="n">
-        <v>53.4</v>
+        <v>49.12</v>
       </c>
       <c r="H192" t="n">
-        <v>-1.57</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-219</v>
+        <v>-41.02</v>
       </c>
       <c r="C193" t="n">
-        <v>4.85991177</v>
+        <v>4.87907777</v>
       </c>
       <c r="D193" t="n">
-        <v>52.75</v>
+        <v>49.18</v>
       </c>
       <c r="E193" t="n">
-        <v>54.45</v>
+        <v>50.1</v>
       </c>
       <c r="F193" t="n">
-        <v>51.45</v>
+        <v>48.82</v>
       </c>
       <c r="G193" t="n">
-        <v>51.85</v>
+        <v>49.92</v>
       </c>
       <c r="H193" t="n">
-        <v>-2.9</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>81.19</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C194" t="n">
-        <v>4.86803077</v>
+        <v>4.88594877</v>
       </c>
       <c r="D194" t="n">
-        <v>51.85</v>
+        <v>50.5</v>
       </c>
       <c r="E194" t="n">
-        <v>51.85</v>
+        <v>50.95</v>
       </c>
       <c r="F194" t="n">
-        <v>49.6</v>
+        <v>49.74</v>
       </c>
       <c r="G194" t="n">
-        <v>50.45</v>
+        <v>50.1</v>
       </c>
       <c r="H194" t="n">
-        <v>-2.7</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.21</v>
+        <v>20.01</v>
       </c>
       <c r="C195" t="n">
-        <v>4.86875177</v>
+        <v>4.88794977</v>
       </c>
       <c r="D195" t="n">
-        <v>50.05</v>
+        <v>50</v>
       </c>
       <c r="E195" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="F195" t="n">
-        <v>49.52</v>
+        <v>49.04</v>
       </c>
       <c r="G195" t="n">
-        <v>50.65</v>
+        <v>49.06</v>
       </c>
       <c r="H195" t="n">
-        <v>0.4</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>144.28</v>
+        <v>-18.77</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88317977</v>
+        <v>4.88607277</v>
       </c>
       <c r="D196" t="n">
-        <v>50</v>
+        <v>49.08</v>
       </c>
       <c r="E196" t="n">
-        <v>50.6</v>
+        <v>49.78</v>
       </c>
       <c r="F196" t="n">
-        <v>49.08</v>
+        <v>48.7</v>
       </c>
       <c r="G196" t="n">
-        <v>49.12</v>
+        <v>49.4</v>
       </c>
       <c r="H196" t="n">
-        <v>-3.02</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-41.02</v>
+        <v>95.14</v>
       </c>
       <c r="C197" t="n">
-        <v>4.87907777</v>
+        <v>4.89558677</v>
       </c>
       <c r="D197" t="n">
-        <v>49.18</v>
+        <v>48.66</v>
       </c>
       <c r="E197" t="n">
-        <v>50.1</v>
+        <v>49.22</v>
       </c>
       <c r="F197" t="n">
-        <v>48.82</v>
+        <v>48.02</v>
       </c>
       <c r="G197" t="n">
-        <v>49.92</v>
+        <v>48.22</v>
       </c>
       <c r="H197" t="n">
-        <v>1.63</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>68.70999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="C198" t="n">
-        <v>4.88594877</v>
+        <v>4.89623377</v>
       </c>
       <c r="D198" t="n">
-        <v>50.5</v>
+        <v>48.22</v>
       </c>
       <c r="E198" t="n">
-        <v>50.95</v>
+        <v>48.22</v>
       </c>
       <c r="F198" t="n">
-        <v>49.74</v>
+        <v>47.46</v>
       </c>
       <c r="G198" t="n">
-        <v>50.1</v>
+        <v>47.46</v>
       </c>
       <c r="H198" t="n">
-        <v>0.36</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>20.01</v>
+        <v>78.34</v>
       </c>
       <c r="C199" t="n">
-        <v>4.88794977</v>
+        <v>4.90406777</v>
       </c>
       <c r="D199" t="n">
-        <v>50</v>
+        <v>47.86</v>
       </c>
       <c r="E199" t="n">
-        <v>50.5</v>
+        <v>48.68</v>
       </c>
       <c r="F199" t="n">
-        <v>49.04</v>
+        <v>47.7</v>
       </c>
       <c r="G199" t="n">
-        <v>49.06</v>
+        <v>48.48</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-18.77</v>
+        <v>12.2</v>
       </c>
       <c r="C200" t="n">
-        <v>4.88607277</v>
+        <v>4.90528777</v>
       </c>
       <c r="D200" t="n">
-        <v>49.08</v>
+        <v>48.1</v>
       </c>
       <c r="E200" t="n">
-        <v>49.78</v>
+        <v>48.7</v>
       </c>
       <c r="F200" t="n">
-        <v>48.7</v>
+        <v>47.38</v>
       </c>
       <c r="G200" t="n">
-        <v>49.4</v>
+        <v>47.88</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>95.14</v>
+        <v>-50.42</v>
       </c>
       <c r="C201" t="n">
-        <v>4.89558677</v>
+        <v>4.90024577</v>
       </c>
       <c r="D201" t="n">
-        <v>48.66</v>
+        <v>47.34</v>
       </c>
       <c r="E201" t="n">
-        <v>49.22</v>
+        <v>48.28</v>
       </c>
       <c r="F201" t="n">
-        <v>48.02</v>
+        <v>47.06</v>
       </c>
       <c r="G201" t="n">
-        <v>48.22</v>
+        <v>47.9</v>
       </c>
       <c r="H201" t="n">
-        <v>-2.39</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>6.47</v>
+        <v>7.38</v>
       </c>
       <c r="C202" t="n">
-        <v>4.89623377</v>
+        <v>4.90098377</v>
       </c>
       <c r="D202" t="n">
-        <v>48.22</v>
+        <v>49.98</v>
       </c>
       <c r="E202" t="n">
-        <v>48.22</v>
+        <v>51.2</v>
       </c>
       <c r="F202" t="n">
-        <v>47.46</v>
+        <v>49.76</v>
       </c>
       <c r="G202" t="n">
-        <v>47.46</v>
+        <v>50.55</v>
       </c>
       <c r="H202" t="n">
-        <v>-1.58</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>78.34</v>
+        <v>0.19</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90406777</v>
+        <v>4.90100277</v>
       </c>
       <c r="D203" t="n">
-        <v>47.86</v>
+        <v>50.55</v>
       </c>
       <c r="E203" t="n">
-        <v>48.68</v>
+        <v>51.8</v>
       </c>
       <c r="F203" t="n">
-        <v>47.7</v>
+        <v>50.5</v>
       </c>
       <c r="G203" t="n">
-        <v>48.48</v>
+        <v>51.2</v>
       </c>
       <c r="H203" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12.2</v>
+        <v>-404.07</v>
       </c>
       <c r="C204" t="n">
-        <v>4.90528777</v>
+        <v>4.86059577</v>
       </c>
       <c r="D204" t="n">
-        <v>48.1</v>
+        <v>50.3</v>
       </c>
       <c r="E204" t="n">
-        <v>48.7</v>
+        <v>51</v>
       </c>
       <c r="F204" t="n">
-        <v>47.38</v>
+        <v>49.3</v>
       </c>
       <c r="G204" t="n">
-        <v>47.88</v>
+        <v>49.46</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.24</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-50.42</v>
+        <v>-104.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.90024577</v>
+        <v>4.85015377</v>
       </c>
       <c r="D205" t="n">
-        <v>47.34</v>
+        <v>48.86</v>
       </c>
       <c r="E205" t="n">
-        <v>48.28</v>
+        <v>49.74</v>
       </c>
       <c r="F205" t="n">
-        <v>47.06</v>
+        <v>47.6</v>
       </c>
       <c r="G205" t="n">
-        <v>47.9</v>
+        <v>47.68</v>
       </c>
       <c r="H205" t="n">
-        <v>0.04</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7.38</v>
+        <v>-9.27</v>
       </c>
       <c r="C206" t="n">
-        <v>4.90098377</v>
+        <v>4.84922677</v>
       </c>
       <c r="D206" t="n">
-        <v>49.98</v>
+        <v>47.68</v>
       </c>
       <c r="E206" t="n">
-        <v>51.2</v>
+        <v>48.9</v>
       </c>
       <c r="F206" t="n">
-        <v>49.76</v>
+        <v>47.32</v>
       </c>
       <c r="G206" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="H206" t="n">
-        <v>5.53</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.19</v>
+        <v>-62.41</v>
       </c>
       <c r="C207" t="n">
-        <v>4.90100277</v>
+        <v>4.84298577</v>
       </c>
       <c r="D207" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="E207" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F207" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="G207" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="H207" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-404.07</v>
+        <v>-4.06</v>
       </c>
       <c r="C208" t="n">
-        <v>4.86059577</v>
+        <v>4.84257977</v>
       </c>
       <c r="D208" t="n">
-        <v>50.3</v>
+        <v>47.8</v>
       </c>
       <c r="E208" t="n">
-        <v>51</v>
+        <v>48.6</v>
       </c>
       <c r="F208" t="n">
-        <v>49.3</v>
+        <v>47.16</v>
       </c>
       <c r="G208" t="n">
-        <v>49.46</v>
+        <v>47.98</v>
       </c>
       <c r="H208" t="n">
-        <v>-3.4</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-104.42</v>
+        <v>107.65</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85015377</v>
+        <v>4.85334477</v>
       </c>
       <c r="D209" t="n">
-        <v>48.86</v>
+        <v>47.86</v>
       </c>
       <c r="E209" t="n">
-        <v>49.74</v>
+        <v>48.44</v>
       </c>
       <c r="F209" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="G209" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="H209" t="n">
-        <v>-3.6</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-9.27</v>
+        <v>137.46</v>
       </c>
       <c r="C210" t="n">
-        <v>4.84922677</v>
+        <v>4.86709077</v>
       </c>
       <c r="D210" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="E210" t="n">
-        <v>48.9</v>
+        <v>48.22</v>
       </c>
       <c r="F210" t="n">
-        <v>47.32</v>
+        <v>46.6</v>
       </c>
       <c r="G210" t="n">
-        <v>48.1</v>
+        <v>47.06</v>
       </c>
       <c r="H210" t="n">
-        <v>0.88</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-62.41</v>
+        <v>154.04</v>
       </c>
       <c r="C211" t="n">
-        <v>4.84298577</v>
+        <v>4.88249477</v>
       </c>
       <c r="D211" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="E211" t="n">
-        <v>49</v>
+        <v>46.76</v>
       </c>
       <c r="F211" t="n">
-        <v>47.5</v>
+        <v>44.56</v>
       </c>
       <c r="G211" t="n">
-        <v>48.6</v>
+        <v>45.86</v>
       </c>
       <c r="H211" t="n">
-        <v>1.04</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-4.06</v>
+        <v>78.03</v>
       </c>
       <c r="C212" t="n">
-        <v>4.84257977</v>
+        <v>4.89029777</v>
       </c>
       <c r="D212" t="n">
-        <v>47.8</v>
+        <v>46.56</v>
       </c>
       <c r="E212" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="F212" t="n">
-        <v>47.16</v>
+        <v>46.2</v>
       </c>
       <c r="G212" t="n">
-        <v>47.98</v>
+        <v>46.38</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.28</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>107.65</v>
+        <v>401.67</v>
       </c>
       <c r="C213" t="n">
-        <v>4.85334477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.86</v>
+        <v>47.28</v>
       </c>
       <c r="E213" t="n">
-        <v>48.44</v>
+        <v>48.88</v>
       </c>
       <c r="F213" t="n">
-        <v>46.5</v>
+        <v>47.12</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.33</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>137.46</v>
+        <v>-79.33</v>
       </c>
       <c r="C214" t="n">
-        <v>4.86709077</v>
+        <v>4.92253177</v>
       </c>
       <c r="D214" t="n">
-        <v>47.82</v>
+        <v>48.1</v>
       </c>
       <c r="E214" t="n">
-        <v>48.22</v>
+        <v>50.45</v>
       </c>
       <c r="F214" t="n">
-        <v>46.6</v>
+        <v>48.04</v>
       </c>
       <c r="G214" t="n">
-        <v>47.06</v>
+        <v>50.4</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.59</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>154.04</v>
+        <v>-415.48</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88249477</v>
+        <v>4.88098377</v>
       </c>
       <c r="D215" t="n">
-        <v>46.68</v>
+        <v>49.44</v>
       </c>
       <c r="E215" t="n">
-        <v>46.76</v>
+        <v>50.15</v>
       </c>
       <c r="F215" t="n">
-        <v>44.56</v>
+        <v>48.88</v>
       </c>
       <c r="G215" t="n">
-        <v>45.86</v>
+        <v>49.32</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>78.03</v>
+        <v>-394.96</v>
       </c>
       <c r="C216" t="n">
-        <v>4.89029777</v>
+        <v>4.84148777</v>
       </c>
       <c r="D216" t="n">
-        <v>46.56</v>
+        <v>49.08</v>
       </c>
       <c r="E216" t="n">
-        <v>48</v>
+        <v>49.08</v>
       </c>
       <c r="F216" t="n">
-        <v>46.2</v>
+        <v>47.2</v>
       </c>
       <c r="G216" t="n">
-        <v>46.38</v>
+        <v>47.62</v>
       </c>
       <c r="H216" t="n">
-        <v>1.13</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>401.67</v>
+        <v>-39.23</v>
       </c>
       <c r="C217" t="n">
-        <v>4.93046477</v>
+        <v>4.83756477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.28</v>
+        <v>47.2</v>
       </c>
       <c r="E217" t="n">
-        <v>48.88</v>
+        <v>47.2</v>
       </c>
       <c r="F217" t="n">
-        <v>47.12</v>
+        <v>46.42</v>
       </c>
       <c r="G217" t="n">
-        <v>47.82</v>
+        <v>46.48</v>
       </c>
       <c r="H217" t="n">
-        <v>3.1</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-79.33</v>
+        <v>219.67</v>
       </c>
       <c r="C218" t="n">
-        <v>4.92253177</v>
+        <v>4.85953177</v>
       </c>
       <c r="D218" t="n">
-        <v>48.1</v>
+        <v>45.74</v>
       </c>
       <c r="E218" t="n">
-        <v>50.45</v>
+        <v>46.44</v>
       </c>
       <c r="F218" t="n">
-        <v>48.04</v>
+        <v>45.38</v>
       </c>
       <c r="G218" t="n">
-        <v>50.4</v>
+        <v>46.34</v>
       </c>
       <c r="H218" t="n">
-        <v>5.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-415.48</v>
+        <v>111.68</v>
       </c>
       <c r="C219" t="n">
-        <v>4.88098377</v>
+        <v>4.87069977</v>
       </c>
       <c r="D219" t="n">
-        <v>49.44</v>
+        <v>45.9</v>
       </c>
       <c r="E219" t="n">
-        <v>50.15</v>
+        <v>47.8</v>
       </c>
       <c r="F219" t="n">
-        <v>48.88</v>
+        <v>45.84</v>
       </c>
       <c r="G219" t="n">
-        <v>49.32</v>
+        <v>47.52</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.14</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>-394.96</v>
+        <v>47.5</v>
       </c>
       <c r="C220" t="n">
-        <v>4.84148777</v>
+        <v>4.87544977</v>
       </c>
       <c r="D220" t="n">
-        <v>49.08</v>
+        <v>47.52</v>
       </c>
       <c r="E220" t="n">
-        <v>49.08</v>
+        <v>48.06</v>
       </c>
       <c r="F220" t="n">
-        <v>47.2</v>
+        <v>46.06</v>
       </c>
       <c r="G220" t="n">
-        <v>47.62</v>
+        <v>46.12</v>
       </c>
       <c r="H220" t="n">
-        <v>-3.45</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-39.23</v>
+        <v>-30.32</v>
       </c>
       <c r="C221" t="n">
-        <v>4.83756477</v>
+        <v>4.87241777</v>
       </c>
       <c r="D221" t="n">
-        <v>47.2</v>
+        <v>46.92</v>
       </c>
       <c r="E221" t="n">
-        <v>47.2</v>
+        <v>47.42</v>
       </c>
       <c r="F221" t="n">
-        <v>46.42</v>
+        <v>45.94</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>-2.39</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>219.67</v>
+        <v>15.46</v>
       </c>
       <c r="C222" t="n">
-        <v>4.85953177</v>
+        <v>4.87396377</v>
       </c>
       <c r="D222" t="n">
-        <v>45.74</v>
+        <v>46.9</v>
       </c>
       <c r="E222" t="n">
-        <v>46.44</v>
+        <v>47.5</v>
       </c>
       <c r="F222" t="n">
-        <v>45.38</v>
+        <v>44.94</v>
       </c>
       <c r="G222" t="n">
-        <v>46.34</v>
+        <v>46.88</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.3</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>111.68</v>
+        <v>57.59</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87069977</v>
+        <v>4.87972277</v>
       </c>
       <c r="D223" t="n">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
       <c r="E223" t="n">
-        <v>47.8</v>
+        <v>48.46</v>
       </c>
       <c r="F223" t="n">
-        <v>45.84</v>
+        <v>46.8</v>
       </c>
       <c r="G223" t="n">
-        <v>47.52</v>
+        <v>47.56</v>
       </c>
       <c r="H223" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>47.5</v>
+        <v>112.19</v>
       </c>
       <c r="C224" t="n">
-        <v>4.87544977</v>
+        <v>4.89094177</v>
       </c>
       <c r="D224" t="n">
-        <v>47.52</v>
+        <v>47.54</v>
       </c>
       <c r="E224" t="n">
-        <v>48.06</v>
+        <v>47.54</v>
       </c>
       <c r="F224" t="n">
-        <v>46.06</v>
+        <v>44.82</v>
       </c>
       <c r="G224" t="n">
-        <v>46.12</v>
+        <v>45.48</v>
       </c>
       <c r="H224" t="n">
-        <v>-2.95</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-30.32</v>
+        <v>-42.06</v>
       </c>
       <c r="C225" t="n">
-        <v>4.87241777</v>
+        <v>4.88673577</v>
       </c>
       <c r="D225" t="n">
-        <v>46.92</v>
+        <v>45</v>
       </c>
       <c r="E225" t="n">
-        <v>47.42</v>
+        <v>45.8</v>
       </c>
       <c r="F225" t="n">
-        <v>45.94</v>
+        <v>44.68</v>
       </c>
       <c r="G225" t="n">
-        <v>46.48</v>
+        <v>45.08</v>
       </c>
       <c r="H225" t="n">
-        <v>0.78</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>15.46</v>
+        <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>4.87396377</v>
+        <v>4.88673577</v>
       </c>
       <c r="D226" t="n">
-        <v>46.9</v>
+        <v>45.72</v>
       </c>
       <c r="E226" t="n">
-        <v>47.5</v>
+        <v>46.54</v>
       </c>
       <c r="F226" t="n">
-        <v>44.94</v>
+        <v>45.34</v>
       </c>
       <c r="G226" t="n">
-        <v>46.88</v>
+        <v>46.24</v>
       </c>
       <c r="H226" t="n">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B227" t="n">
-        <v>57.59</v>
-      </c>
-      <c r="C227" t="n">
-        <v>4.87972277</v>
-      </c>
-      <c r="D227" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="E227" t="n">
-        <v>48.46</v>
-      </c>
-      <c r="F227" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="G227" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="H227" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B228" t="n">
-        <v>112.19</v>
-      </c>
-      <c r="C228" t="n">
-        <v>4.89094177</v>
-      </c>
-      <c r="D228" t="n">
-        <v>47.54</v>
-      </c>
-      <c r="E228" t="n">
-        <v>47.54</v>
-      </c>
-      <c r="F228" t="n">
-        <v>44.82</v>
-      </c>
-      <c r="G228" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="H228" t="n">
-        <v>-4.37</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>-42.06</v>
-      </c>
-      <c r="C229" t="n">
-        <v>4.88673577</v>
-      </c>
-      <c r="D229" t="n">
-        <v>45</v>
-      </c>
-      <c r="E229" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="F229" t="n">
-        <v>44.68</v>
-      </c>
-      <c r="G229" t="n">
-        <v>45.08</v>
-      </c>
-      <c r="H229" t="n">
-        <v>-0.88</v>
+        <v>2.57</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -6747,10 +6747,10 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>201.66</v>
       </c>
       <c r="C226" t="n">
-        <v>4.88673577</v>
+        <v>4.90690177</v>
       </c>
       <c r="D226" t="n">
         <v>45.72</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6768,6 +6768,34 @@
         <v>2.57</v>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>0</v>
+      </c>
+      <c r="C227" t="n">
+        <v>4.90690177</v>
+      </c>
+      <c r="D227" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="E227" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="F227" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="G227" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="H227" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -6775,10 +6775,10 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0</v>
+        <v>138.5</v>
       </c>
       <c r="C227" t="n">
-        <v>4.90690177</v>
+        <v>4.92075177</v>
       </c>
       <c r="D227" t="n">
         <v>45.48</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H227"/>
+  <dimension ref="A1:H228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6796,6 +6796,34 @@
         <v>1.12</v>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>0</v>
+      </c>
+      <c r="C228" t="n">
+        <v>4.92075177</v>
+      </c>
+      <c r="D228" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="E228" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="F228" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G228" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-3.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H228"/>
+  <dimension ref="A1:H233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="E79" t="n">
-        <v>72.25</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>69.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G79" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E80" t="n">
-        <v>71.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F80" t="n">
-        <v>69.55</v>
+        <v>71.5</v>
       </c>
       <c r="G80" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4135 +2693,4275 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>70.3</v>
+        <v>72.8</v>
       </c>
       <c r="E81" t="n">
-        <v>73.3</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>70.3</v>
+        <v>71.5</v>
       </c>
       <c r="G81" t="n">
-        <v>72.84999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H81" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-37.37</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D82" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>73.5</v>
+        <v>72.25</v>
       </c>
       <c r="F82" t="n">
-        <v>71.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.51</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D83" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>73.15000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="F83" t="n">
-        <v>70.5</v>
+        <v>69.55</v>
       </c>
       <c r="G83" t="n">
-        <v>71.84999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>0.14</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>39.15</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29772381</v>
+        <v>5.29754581</v>
       </c>
       <c r="D84" t="n">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="E84" t="n">
-        <v>71.8</v>
+        <v>73.3</v>
       </c>
       <c r="F84" t="n">
-        <v>68.55</v>
+        <v>70.3</v>
       </c>
       <c r="G84" t="n">
-        <v>68.65000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-4.45</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-32.03</v>
+        <v>-37.37</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29452081</v>
+        <v>5.29380881</v>
       </c>
       <c r="D85" t="n">
-        <v>69.5</v>
+        <v>71.8</v>
       </c>
       <c r="E85" t="n">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="F85" t="n">
-        <v>68.15000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G85" t="n">
-        <v>68.75</v>
+        <v>71.75</v>
       </c>
       <c r="H85" t="n">
-        <v>0.15</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-245.51</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>5.26996981</v>
+        <v>5.29380881</v>
       </c>
       <c r="D86" t="n">
-        <v>67.75</v>
+        <v>72.8</v>
       </c>
       <c r="E86" t="n">
-        <v>70.15000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>67</v>
+        <v>70.5</v>
       </c>
       <c r="G86" t="n">
-        <v>68</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.99</v>
+        <v>39.15</v>
       </c>
       <c r="C87" t="n">
-        <v>5.27246881</v>
+        <v>5.29772381</v>
       </c>
       <c r="D87" t="n">
-        <v>68.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>69</v>
+        <v>71.8</v>
       </c>
       <c r="F87" t="n">
-        <v>65.65000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="G87" t="n">
-        <v>66.55</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-2.13</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-70.5937</v>
+        <v>-32.03</v>
       </c>
       <c r="C88" t="n">
-        <v>5.26540944</v>
+        <v>5.29452081</v>
       </c>
       <c r="D88" t="n">
-        <v>65.84999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E88" t="n">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="F88" t="n">
-        <v>64.45</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>65.84999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-83.42</v>
+        <v>-245.51</v>
       </c>
       <c r="C89" t="n">
-        <v>5.25706744</v>
+        <v>5.26996981</v>
       </c>
       <c r="D89" t="n">
-        <v>66.90000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="E89" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>67</v>
+      </c>
+      <c r="G89" t="n">
         <v>68</v>
       </c>
-      <c r="F89" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="H89" t="n">
-        <v>-0.38</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>32.9872</v>
+        <v>24.99</v>
       </c>
       <c r="C90" t="n">
-        <v>5.26036616</v>
+        <v>5.27246881</v>
       </c>
       <c r="D90" t="n">
-        <v>65.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>67.65000000000001</v>
+        <v>69</v>
       </c>
       <c r="F90" t="n">
-        <v>65.34999999999999</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>67.45</v>
+        <v>66.55</v>
       </c>
       <c r="H90" t="n">
-        <v>2.82</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-168.98</v>
+        <v>-70.5937</v>
       </c>
       <c r="C91" t="n">
-        <v>5.24346816</v>
+        <v>5.26540944</v>
       </c>
       <c r="D91" t="n">
-        <v>64.84999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>69</v>
+        <v>66.8</v>
       </c>
       <c r="F91" t="n">
-        <v>64.7</v>
+        <v>64.45</v>
       </c>
       <c r="G91" t="n">
-        <v>68.90000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>2.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-195.54</v>
+        <v>-83.42</v>
       </c>
       <c r="C92" t="n">
-        <v>5.22391416</v>
+        <v>5.25706744</v>
       </c>
       <c r="D92" t="n">
-        <v>69.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>70.2</v>
+        <v>68</v>
       </c>
       <c r="F92" t="n">
-        <v>67.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>69.05</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>0.22</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>16.18</v>
+        <v>32.9872</v>
       </c>
       <c r="C93" t="n">
-        <v>5.22553216</v>
+        <v>5.26036616</v>
       </c>
       <c r="D93" t="n">
-        <v>69.25</v>
+        <v>65.5</v>
       </c>
       <c r="E93" t="n">
-        <v>70.8</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>69.05</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>69.84999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="H93" t="n">
-        <v>1.16</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.87</v>
+        <v>-168.98</v>
       </c>
       <c r="C94" t="n">
-        <v>5.22691916</v>
+        <v>5.24346816</v>
       </c>
       <c r="D94" t="n">
-        <v>70.95</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="F94" t="n">
-        <v>69.15000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G94" t="n">
-        <v>70.15000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-145.08</v>
+        <v>-195.54</v>
       </c>
       <c r="C95" t="n">
-        <v>5.21241116</v>
+        <v>5.22391416</v>
       </c>
       <c r="D95" t="n">
-        <v>68.95</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>69</v>
+        <v>70.2</v>
       </c>
       <c r="F95" t="n">
-        <v>67.3</v>
+        <v>67.95</v>
       </c>
       <c r="G95" t="n">
-        <v>67.90000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="H95" t="n">
-        <v>-3.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.02</v>
+        <v>16.18</v>
       </c>
       <c r="C96" t="n">
-        <v>5.21491316</v>
+        <v>5.22553216</v>
       </c>
       <c r="D96" t="n">
-        <v>67.5</v>
+        <v>69.25</v>
       </c>
       <c r="E96" t="n">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F96" t="n">
-        <v>66.3</v>
+        <v>69.05</v>
       </c>
       <c r="G96" t="n">
-        <v>69.90000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>2.95</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-6.25</v>
+        <v>13.87</v>
       </c>
       <c r="C97" t="n">
-        <v>5.21428816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D97" t="n">
-        <v>71.25</v>
+        <v>70.95</v>
       </c>
       <c r="E97" t="n">
-        <v>73.3</v>
+        <v>71.3</v>
       </c>
       <c r="F97" t="n">
-        <v>70.84999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>71.3</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-48.58</v>
+        <v>-145.08</v>
       </c>
       <c r="C98" t="n">
-        <v>5.20943016</v>
+        <v>5.21241116</v>
       </c>
       <c r="D98" t="n">
-        <v>70.65000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E98" t="n">
-        <v>71.25</v>
+        <v>69</v>
       </c>
       <c r="F98" t="n">
-        <v>66.34999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G98" t="n">
-        <v>66.84999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>-6.24</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-197.18</v>
+        <v>25.02</v>
       </c>
       <c r="C99" t="n">
-        <v>5.18971216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D99" t="n">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="E99" t="n">
-        <v>67.34999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="G99" t="n">
-        <v>66</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.27</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>426.64</v>
+        <v>-6.25</v>
       </c>
       <c r="C100" t="n">
-        <v>5.23237616</v>
+        <v>5.21428816</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>71.25</v>
       </c>
       <c r="E100" t="n">
-        <v>68.7</v>
+        <v>73.3</v>
       </c>
       <c r="F100" t="n">
-        <v>66.34999999999999</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>66.8</v>
+        <v>71.3</v>
       </c>
       <c r="H100" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>41.4993</v>
+        <v>-48.58</v>
       </c>
       <c r="C101" t="n">
-        <v>5.23652609</v>
+        <v>5.20943016</v>
       </c>
       <c r="D101" t="n">
-        <v>65.59999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>66.05</v>
+        <v>71.25</v>
       </c>
       <c r="F101" t="n">
-        <v>64.2</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>64.8</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.99</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-220.5688</v>
+        <v>-197.18</v>
       </c>
       <c r="C102" t="n">
-        <v>5.21446921</v>
+        <v>5.18971216</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.65000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>63.45</v>
+        <v>65.8</v>
       </c>
       <c r="G102" t="n">
-        <v>67.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="H102" t="n">
-        <v>4.32</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>215.27</v>
+        <v>426.64</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23599621</v>
+        <v>5.23237616</v>
       </c>
       <c r="D103" t="n">
-        <v>69.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="E103" t="n">
-        <v>71.34999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F103" t="n">
-        <v>69.45</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>70.45</v>
+        <v>66.8</v>
       </c>
       <c r="H103" t="n">
-        <v>4.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-160.53</v>
+        <v>41.4993</v>
       </c>
       <c r="C104" t="n">
-        <v>5.21994321</v>
+        <v>5.23652609</v>
       </c>
       <c r="D104" t="n">
-        <v>69.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>70.8</v>
+        <v>66.05</v>
       </c>
       <c r="F104" t="n">
-        <v>68.7</v>
+        <v>64.2</v>
       </c>
       <c r="G104" t="n">
-        <v>69</v>
+        <v>64.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.06</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-304.01</v>
+        <v>-220.5688</v>
       </c>
       <c r="C105" t="n">
-        <v>5.18954221</v>
+        <v>5.21446921</v>
       </c>
       <c r="D105" t="n">
-        <v>69</v>
+        <v>66.2</v>
       </c>
       <c r="E105" t="n">
-        <v>71.5</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>68.3</v>
+        <v>63.45</v>
       </c>
       <c r="G105" t="n">
-        <v>70.05</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>1.52</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-30.3</v>
+        <v>215.27</v>
       </c>
       <c r="C106" t="n">
-        <v>5.18651221</v>
+        <v>5.23599621</v>
       </c>
       <c r="D106" t="n">
-        <v>68.05</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>69.34999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>68</v>
+        <v>69.45</v>
       </c>
       <c r="G106" t="n">
-        <v>68.8</v>
+        <v>70.45</v>
       </c>
       <c r="H106" t="n">
-        <v>-1.78</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-92.3</v>
+        <v>-160.53</v>
       </c>
       <c r="C107" t="n">
-        <v>5.17728221</v>
+        <v>5.21994321</v>
       </c>
       <c r="D107" t="n">
-        <v>68.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>69.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F107" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="G107" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.6</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>25.43</v>
+        <v>-304.01</v>
       </c>
       <c r="C108" t="n">
-        <v>5.17982521</v>
+        <v>5.18954221</v>
       </c>
       <c r="D108" t="n">
-        <v>68.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="E108" t="n">
-        <v>71.45</v>
+        <v>71.5</v>
       </c>
       <c r="F108" t="n">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G108" t="n">
-        <v>71.2</v>
+        <v>70.05</v>
       </c>
       <c r="H108" t="n">
-        <v>5.17</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>136.53</v>
+        <v>-30.3</v>
       </c>
       <c r="C109" t="n">
-        <v>5.19347821</v>
+        <v>5.18651221</v>
       </c>
       <c r="D109" t="n">
-        <v>71.2</v>
+        <v>68.05</v>
       </c>
       <c r="E109" t="n">
-        <v>73.40000000000001</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G109" t="n">
-        <v>71.8</v>
+        <v>68.8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.84</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-224.29</v>
+        <v>-92.3</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17104921</v>
+        <v>5.17728221</v>
       </c>
       <c r="D110" t="n">
-        <v>73.45</v>
+        <v>68.8</v>
       </c>
       <c r="E110" t="n">
-        <v>74</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>71.65000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="G110" t="n">
-        <v>73.3</v>
+        <v>67.7</v>
       </c>
       <c r="H110" t="n">
-        <v>2.09</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>97.7422</v>
+        <v>25.43</v>
       </c>
       <c r="C111" t="n">
-        <v>5.18082343</v>
+        <v>5.17982521</v>
       </c>
       <c r="D111" t="n">
-        <v>71.95</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>73.5</v>
+        <v>71.45</v>
       </c>
       <c r="F111" t="n">
-        <v>71.75</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G111" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.91</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-116.85</v>
+        <v>136.53</v>
       </c>
       <c r="C112" t="n">
-        <v>5.16913843</v>
+        <v>5.19347821</v>
       </c>
       <c r="D112" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E112" t="n">
-        <v>76.45</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>71.55</v>
+        <v>70</v>
       </c>
       <c r="G112" t="n">
-        <v>74.2</v>
+        <v>71.8</v>
       </c>
       <c r="H112" t="n">
-        <v>3.2</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>32.76</v>
+        <v>-224.29</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17241443</v>
+        <v>5.17104921</v>
       </c>
       <c r="D113" t="n">
-        <v>74.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E113" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F113" t="n">
-        <v>73.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>73.7</v>
+        <v>73.3</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.67</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-19.6</v>
+        <v>97.7422</v>
       </c>
       <c r="C114" t="n">
-        <v>5.17045443</v>
+        <v>5.18082343</v>
       </c>
       <c r="D114" t="n">
-        <v>73.7</v>
+        <v>71.95</v>
       </c>
       <c r="E114" t="n">
-        <v>73.95</v>
+        <v>73.5</v>
       </c>
       <c r="F114" t="n">
-        <v>71.65000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="G114" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.95</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>74.23999999999999</v>
+        <v>-116.85</v>
       </c>
       <c r="C115" t="n">
-        <v>5.17787843</v>
+        <v>5.16913843</v>
       </c>
       <c r="D115" t="n">
-        <v>73.75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>73.75</v>
+        <v>76.45</v>
       </c>
       <c r="F115" t="n">
-        <v>70.5</v>
+        <v>71.55</v>
       </c>
       <c r="G115" t="n">
-        <v>70.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>15.04</v>
+        <v>32.76</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17938243</v>
+        <v>5.17241443</v>
       </c>
       <c r="D116" t="n">
-        <v>70.95</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>72.15000000000001</v>
+        <v>75</v>
       </c>
       <c r="F116" t="n">
-        <v>70.95</v>
+        <v>73.25</v>
       </c>
       <c r="G116" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H116" t="n">
-        <v>0.99</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>213.47</v>
+        <v>-19.6</v>
       </c>
       <c r="C117" t="n">
-        <v>5.20072943</v>
+        <v>5.17045443</v>
       </c>
       <c r="D117" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E117" t="n">
-        <v>71.90000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="F117" t="n">
-        <v>70.40000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>71.45</v>
+        <v>73</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.21</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-167.67</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>5.18396243</v>
+        <v>5.17787843</v>
       </c>
       <c r="D118" t="n">
-        <v>72</v>
+        <v>73.75</v>
       </c>
       <c r="E118" t="n">
-        <v>73.45</v>
+        <v>73.75</v>
       </c>
       <c r="F118" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G118" t="n">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>2.59</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-78.5919</v>
+        <v>15.04</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17610324</v>
+        <v>5.17938243</v>
       </c>
       <c r="D119" t="n">
-        <v>73.3</v>
+        <v>70.95</v>
       </c>
       <c r="E119" t="n">
-        <v>73.3</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>71.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="G119" t="n">
-        <v>73.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.14</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-54.57</v>
+        <v>213.47</v>
       </c>
       <c r="C120" t="n">
-        <v>5.17064624</v>
+        <v>5.20072943</v>
       </c>
       <c r="D120" t="n">
-        <v>72.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>73.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>71.95</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>73.45</v>
+        <v>71.45</v>
       </c>
       <c r="H120" t="n">
-        <v>0.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>32.9</v>
+        <v>-167.67</v>
       </c>
       <c r="C121" t="n">
-        <v>5.17393624</v>
+        <v>5.18396243</v>
       </c>
       <c r="D121" t="n">
+        <v>72</v>
+      </c>
+      <c r="E121" t="n">
         <v>73.45</v>
       </c>
-      <c r="E121" t="n">
-        <v>74.40000000000001</v>
-      </c>
       <c r="F121" t="n">
-        <v>71.75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>73.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.41</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>41.93</v>
+        <v>-78.5919</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17812924</v>
+        <v>5.17610324</v>
       </c>
       <c r="D122" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="E122" t="n">
-        <v>73.65000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F122" t="n">
-        <v>68.7</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>69.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.44</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>52.87</v>
+        <v>-54.57</v>
       </c>
       <c r="C123" t="n">
-        <v>5.18341624</v>
+        <v>5.17064624</v>
       </c>
       <c r="D123" t="n">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E123" t="n">
-        <v>70.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>68.90000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G123" t="n">
-        <v>69.7</v>
+        <v>73.45</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>291.58</v>
+        <v>32.9</v>
       </c>
       <c r="C124" t="n">
-        <v>5.21257424</v>
+        <v>5.17393624</v>
       </c>
       <c r="D124" t="n">
-        <v>69.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E124" t="n">
-        <v>69.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>66.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G124" t="n">
-        <v>67</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>-3.87</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-60.7601</v>
+        <v>41.93</v>
       </c>
       <c r="C125" t="n">
-        <v>5.20649823</v>
+        <v>5.17812924</v>
       </c>
       <c r="D125" t="n">
-        <v>69.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E125" t="n">
-        <v>70.25</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>68.45</v>
+        <v>68.7</v>
       </c>
       <c r="G125" t="n">
-        <v>69.25</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>3.36</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>264.89</v>
+        <v>52.87</v>
       </c>
       <c r="C126" t="n">
-        <v>5.23298723</v>
+        <v>5.18341624</v>
       </c>
       <c r="D126" t="n">
-        <v>68.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>69.75</v>
+        <v>70.5</v>
       </c>
       <c r="F126" t="n">
-        <v>67.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>67.55</v>
+        <v>69.7</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.45</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>291.58</v>
       </c>
       <c r="C127" t="n">
-        <v>5.23298723</v>
+        <v>5.21257424</v>
       </c>
       <c r="D127" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>71.15000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F127" t="n">
-        <v>68.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G127" t="n">
-        <v>70.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H127" t="n">
-        <v>3.85</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-60.7601</v>
       </c>
       <c r="C128" t="n">
-        <v>5.23298723</v>
+        <v>5.20649823</v>
       </c>
       <c r="D128" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="F128" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="G128" t="n">
         <v>69.25</v>
       </c>
-      <c r="E128" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F128" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="G128" t="n">
-        <v>69.65000000000001</v>
-      </c>
       <c r="H128" t="n">
-        <v>-0.71</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-369.37</v>
+        <v>264.89</v>
       </c>
       <c r="C129" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D129" t="n">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E129" t="n">
-        <v>69.5</v>
+        <v>69.75</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.84999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.58</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D130" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E130" t="n">
-        <v>70.34999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="F130" t="n">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="G130" t="n">
-        <v>69.95</v>
+        <v>67.55</v>
       </c>
       <c r="H130" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>68.9663</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>5.20294686</v>
+        <v>5.23298723</v>
       </c>
       <c r="D131" t="n">
-        <v>68.34999999999999</v>
+        <v>69</v>
       </c>
       <c r="E131" t="n">
-        <v>70.3</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>68.34999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G131" t="n">
-        <v>70.05</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>0.14</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-247.41</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>5.17820586</v>
+        <v>5.23298723</v>
       </c>
       <c r="D132" t="n">
-        <v>69.5</v>
+        <v>69.25</v>
       </c>
       <c r="E132" t="n">
-        <v>74.15000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>69.45</v>
+        <v>68.2</v>
       </c>
       <c r="G132" t="n">
-        <v>73.84999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>5.42</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>27.55</v>
+        <v>-369.37</v>
       </c>
       <c r="C133" t="n">
-        <v>5.18096086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D133" t="n">
-        <v>73.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E133" t="n">
-        <v>75.15000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F133" t="n">
-        <v>73.05</v>
+        <v>67.3</v>
       </c>
       <c r="G133" t="n">
-        <v>73.40000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.61</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-286.2</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5.15234086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D134" t="n">
-        <v>73.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="E134" t="n">
-        <v>74.40000000000001</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>73.05</v>
+        <v>68.5</v>
       </c>
       <c r="G134" t="n">
-        <v>73.65000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="H134" t="n">
-        <v>0.34</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>48.88</v>
+        <v>68.9663</v>
       </c>
       <c r="C135" t="n">
-        <v>5.15722886</v>
+        <v>5.20294686</v>
       </c>
       <c r="D135" t="n">
-        <v>76.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>78.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F135" t="n">
-        <v>75.40000000000001</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>76.84999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H135" t="n">
-        <v>4.34</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-55.96</v>
+        <v>-247.41</v>
       </c>
       <c r="C136" t="n">
-        <v>5.15163286</v>
+        <v>5.17820586</v>
       </c>
       <c r="D136" t="n">
-        <v>75.05</v>
+        <v>69.5</v>
       </c>
       <c r="E136" t="n">
-        <v>75.90000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>74.25</v>
+        <v>69.45</v>
       </c>
       <c r="G136" t="n">
-        <v>75.59999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.63</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-385.85</v>
+        <v>27.55</v>
       </c>
       <c r="C137" t="n">
-        <v>5.11304786</v>
+        <v>5.18096086</v>
       </c>
       <c r="D137" t="n">
-        <v>72.40000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E137" t="n">
-        <v>72.40000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>64.5</v>
+        <v>73.05</v>
       </c>
       <c r="G137" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-14.15</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>139.59</v>
+        <v>-286.2</v>
       </c>
       <c r="C138" t="n">
-        <v>5.12700686</v>
+        <v>5.15234086</v>
       </c>
       <c r="D138" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>64.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>61.75</v>
+        <v>73.05</v>
       </c>
       <c r="G138" t="n">
-        <v>62.1</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>-4.31</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1468.42</v>
+        <v>48.88</v>
       </c>
       <c r="C139" t="n">
-        <v>5.27384886</v>
+        <v>5.15722886</v>
       </c>
       <c r="D139" t="n">
-        <v>62.6</v>
+        <v>76.8</v>
       </c>
       <c r="E139" t="n">
-        <v>63.35</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>61</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G139" t="n">
-        <v>61.6</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>292.93</v>
+        <v>-55.96</v>
       </c>
       <c r="C140" t="n">
-        <v>5.30314186</v>
+        <v>5.15163286</v>
       </c>
       <c r="D140" t="n">
-        <v>62.5</v>
+        <v>75.05</v>
       </c>
       <c r="E140" t="n">
-        <v>63.85</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>61.55</v>
+        <v>74.25</v>
       </c>
       <c r="G140" t="n">
-        <v>62.25</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>1.06</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>17.9</v>
+        <v>-385.85</v>
       </c>
       <c r="C141" t="n">
-        <v>5.30493186</v>
+        <v>5.11304786</v>
       </c>
       <c r="D141" t="n">
-        <v>63.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E141" t="n">
-        <v>64.95</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F141" t="n">
-        <v>61.35</v>
+        <v>64.5</v>
       </c>
       <c r="G141" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.72</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-224.88</v>
+        <v>139.59</v>
       </c>
       <c r="C142" t="n">
-        <v>5.28244386</v>
+        <v>5.12700686</v>
       </c>
       <c r="D142" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E142" t="n">
-        <v>62.25</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>60.4</v>
+        <v>61.75</v>
       </c>
       <c r="G142" t="n">
-        <v>62.15</v>
+        <v>62.1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.57</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-244.5</v>
+        <v>1468.42</v>
       </c>
       <c r="C143" t="n">
-        <v>5.25799386</v>
+        <v>5.27384886</v>
       </c>
       <c r="D143" t="n">
-        <v>61.9</v>
+        <v>62.6</v>
       </c>
       <c r="E143" t="n">
-        <v>62.35</v>
+        <v>63.35</v>
       </c>
       <c r="F143" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G143" t="n">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.14</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-302.48</v>
+        <v>292.93</v>
       </c>
       <c r="C144" t="n">
-        <v>5.22774586</v>
+        <v>5.30314186</v>
       </c>
       <c r="D144" t="n">
-        <v>60.1</v>
+        <v>62.5</v>
       </c>
       <c r="E144" t="n">
-        <v>61</v>
+        <v>63.85</v>
       </c>
       <c r="F144" t="n">
-        <v>58.6</v>
+        <v>61.55</v>
       </c>
       <c r="G144" t="n">
-        <v>60.45</v>
+        <v>62.25</v>
       </c>
       <c r="H144" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-177.8636</v>
+        <v>17.9</v>
       </c>
       <c r="C145" t="n">
-        <v>5.2099595</v>
+        <v>5.30493186</v>
       </c>
       <c r="D145" t="n">
-        <v>60</v>
+        <v>63.2</v>
       </c>
       <c r="E145" t="n">
-        <v>60.05</v>
+        <v>64.95</v>
       </c>
       <c r="F145" t="n">
-        <v>55.7</v>
+        <v>61.35</v>
       </c>
       <c r="G145" t="n">
-        <v>57.85</v>
+        <v>61.8</v>
       </c>
       <c r="H145" t="n">
-        <v>-4.3</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-228.55</v>
+        <v>-224.88</v>
       </c>
       <c r="C146" t="n">
-        <v>5.1871045</v>
+        <v>5.28244386</v>
       </c>
       <c r="D146" t="n">
-        <v>56.95</v>
+        <v>61.8</v>
       </c>
       <c r="E146" t="n">
-        <v>59.1</v>
+        <v>62.25</v>
       </c>
       <c r="F146" t="n">
-        <v>56</v>
+        <v>60.4</v>
       </c>
       <c r="G146" t="n">
-        <v>58.55</v>
+        <v>62.15</v>
       </c>
       <c r="H146" t="n">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>423.9973</v>
+        <v>-244.5</v>
       </c>
       <c r="C147" t="n">
-        <v>5.22950423</v>
+        <v>5.25799386</v>
       </c>
       <c r="D147" t="n">
-        <v>57.05</v>
+        <v>61.9</v>
       </c>
       <c r="E147" t="n">
-        <v>62</v>
+        <v>62.35</v>
       </c>
       <c r="F147" t="n">
-        <v>56.55</v>
+        <v>59.9</v>
       </c>
       <c r="G147" t="n">
-        <v>61.9</v>
+        <v>60.2</v>
       </c>
       <c r="H147" t="n">
-        <v>5.72</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-119.16</v>
+        <v>-302.48</v>
       </c>
       <c r="C148" t="n">
-        <v>5.21758823</v>
+        <v>5.22774586</v>
       </c>
       <c r="D148" t="n">
-        <v>60.5</v>
+        <v>60.1</v>
       </c>
       <c r="E148" t="n">
-        <v>60.75</v>
+        <v>61</v>
       </c>
       <c r="F148" t="n">
-        <v>58.75</v>
+        <v>58.6</v>
       </c>
       <c r="G148" t="n">
-        <v>59.1</v>
+        <v>60.45</v>
       </c>
       <c r="H148" t="n">
-        <v>-4.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-301.92</v>
+        <v>-177.8636</v>
       </c>
       <c r="C149" t="n">
-        <v>5.18739623</v>
+        <v>5.2099595</v>
       </c>
       <c r="D149" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="E149" t="n">
-        <v>58.95</v>
+        <v>60.05</v>
       </c>
       <c r="F149" t="n">
-        <v>56.85</v>
+        <v>55.7</v>
       </c>
       <c r="G149" t="n">
-        <v>57.25</v>
+        <v>57.85</v>
       </c>
       <c r="H149" t="n">
-        <v>-3.13</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>112.29</v>
+        <v>-228.55</v>
       </c>
       <c r="C150" t="n">
-        <v>5.19862523</v>
+        <v>5.1871045</v>
       </c>
       <c r="D150" t="n">
-        <v>57.1</v>
+        <v>56.95</v>
       </c>
       <c r="E150" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
       <c r="F150" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="G150" t="n">
-        <v>56.65</v>
+        <v>58.55</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.05</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-62.4836</v>
+        <v>423.9973</v>
       </c>
       <c r="C151" t="n">
-        <v>5.19237687</v>
+        <v>5.22950423</v>
       </c>
       <c r="D151" t="n">
-        <v>55.3</v>
+        <v>57.05</v>
       </c>
       <c r="E151" t="n">
-        <v>57.9</v>
+        <v>62</v>
       </c>
       <c r="F151" t="n">
-        <v>54.95</v>
+        <v>56.55</v>
       </c>
       <c r="G151" t="n">
-        <v>57.35</v>
+        <v>61.9</v>
       </c>
       <c r="H151" t="n">
-        <v>1.24</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-29.35</v>
+        <v>-119.16</v>
       </c>
       <c r="C152" t="n">
-        <v>5.18944187</v>
+        <v>5.21758823</v>
       </c>
       <c r="D152" t="n">
-        <v>56.2</v>
+        <v>60.5</v>
       </c>
       <c r="E152" t="n">
-        <v>57.1</v>
+        <v>60.75</v>
       </c>
       <c r="F152" t="n">
-        <v>55.8</v>
+        <v>58.75</v>
       </c>
       <c r="G152" t="n">
-        <v>55.85</v>
+        <v>59.1</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.62</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>54.46</v>
+        <v>-301.92</v>
       </c>
       <c r="C153" t="n">
-        <v>5.19488787</v>
+        <v>5.18739623</v>
       </c>
       <c r="D153" t="n">
-        <v>55.3</v>
+        <v>58.95</v>
       </c>
       <c r="E153" t="n">
-        <v>55.55</v>
+        <v>58.95</v>
       </c>
       <c r="F153" t="n">
-        <v>53.25</v>
+        <v>56.85</v>
       </c>
       <c r="G153" t="n">
-        <v>54.7</v>
+        <v>57.25</v>
       </c>
       <c r="H153" t="n">
-        <v>-2.06</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>17.32</v>
+        <v>112.29</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19661987</v>
+        <v>5.19862523</v>
       </c>
       <c r="D154" t="n">
-        <v>54</v>
+        <v>57.1</v>
       </c>
       <c r="E154" t="n">
-        <v>54.1</v>
+        <v>57.6</v>
       </c>
       <c r="F154" t="n">
-        <v>52.25</v>
+        <v>56.5</v>
       </c>
       <c r="G154" t="n">
-        <v>53.15</v>
+        <v>56.65</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.83</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>93.42</v>
+        <v>-62.4836</v>
       </c>
       <c r="C155" t="n">
-        <v>5.20596187</v>
+        <v>5.19237687</v>
       </c>
       <c r="D155" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>53.25</v>
+        <v>54.95</v>
       </c>
       <c r="G155" t="n">
-        <v>57</v>
+        <v>57.35</v>
       </c>
       <c r="H155" t="n">
-        <v>7.24</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>64.81</v>
+        <v>-29.35</v>
       </c>
       <c r="C156" t="n">
-        <v>5.21244287</v>
+        <v>5.18944187</v>
       </c>
       <c r="D156" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="E156" t="n">
-        <v>58.05</v>
+        <v>57.1</v>
       </c>
       <c r="F156" t="n">
-        <v>56.5</v>
+        <v>55.8</v>
       </c>
       <c r="G156" t="n">
-        <v>56.85</v>
+        <v>55.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.26</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-172.75</v>
+        <v>54.46</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19516787</v>
+        <v>5.19488787</v>
       </c>
       <c r="D157" t="n">
-        <v>56.85</v>
+        <v>55.3</v>
       </c>
       <c r="E157" t="n">
-        <v>57.2</v>
+        <v>55.55</v>
       </c>
       <c r="F157" t="n">
-        <v>55</v>
+        <v>53.25</v>
       </c>
       <c r="G157" t="n">
-        <v>56</v>
+        <v>54.7</v>
       </c>
       <c r="H157" t="n">
-        <v>-1.5</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-24.86</v>
+        <v>17.32</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19268187</v>
+        <v>5.19661987</v>
       </c>
       <c r="D158" t="n">
-        <v>55.75</v>
+        <v>54</v>
       </c>
       <c r="E158" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="F158" t="n">
-        <v>53.7</v>
+        <v>52.25</v>
       </c>
       <c r="G158" t="n">
-        <v>53.9</v>
+        <v>53.15</v>
       </c>
       <c r="H158" t="n">
-        <v>-3.75</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.38</v>
+        <v>93.42</v>
       </c>
       <c r="C159" t="n">
-        <v>5.19441987</v>
+        <v>5.20596187</v>
       </c>
       <c r="D159" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E159" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F159" t="n">
         <v>53.25</v>
       </c>
-      <c r="E159" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F159" t="n">
-        <v>51.75</v>
-      </c>
       <c r="G159" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H159" t="n">
-        <v>-3.53</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>14.06</v>
+        <v>64.81</v>
       </c>
       <c r="C160" t="n">
-        <v>5.19582587</v>
+        <v>5.21244287</v>
       </c>
       <c r="D160" t="n">
-        <v>50.15</v>
+        <v>56.6</v>
       </c>
       <c r="E160" t="n">
-        <v>51.55</v>
+        <v>58.05</v>
       </c>
       <c r="F160" t="n">
-        <v>49.64</v>
+        <v>56.5</v>
       </c>
       <c r="G160" t="n">
-        <v>50.5</v>
+        <v>56.85</v>
       </c>
       <c r="H160" t="n">
-        <v>-2.88</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-21.2345</v>
+        <v>-172.75</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19370242</v>
+        <v>5.19516787</v>
       </c>
       <c r="D161" t="n">
-        <v>50</v>
+        <v>56.85</v>
       </c>
       <c r="E161" t="n">
-        <v>50.8</v>
+        <v>57.2</v>
       </c>
       <c r="F161" t="n">
-        <v>47.9</v>
+        <v>55</v>
       </c>
       <c r="G161" t="n">
-        <v>48.32</v>
+        <v>56</v>
       </c>
       <c r="H161" t="n">
-        <v>-4.32</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>47.7</v>
+        <v>-24.86</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19847242</v>
+        <v>5.19268187</v>
       </c>
       <c r="D162" t="n">
-        <v>48.98</v>
+        <v>55.75</v>
       </c>
       <c r="E162" t="n">
-        <v>49.94</v>
+        <v>55.8</v>
       </c>
       <c r="F162" t="n">
-        <v>48.18</v>
+        <v>53.7</v>
       </c>
       <c r="G162" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="H162" t="n">
-        <v>2.32</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>92.59999999999999</v>
+        <v>17.38</v>
       </c>
       <c r="C163" t="n">
-        <v>5.20773242</v>
+        <v>5.19441987</v>
       </c>
       <c r="D163" t="n">
-        <v>49.44</v>
+        <v>53.25</v>
       </c>
       <c r="E163" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="F163" t="n">
-        <v>46.74</v>
+        <v>51.75</v>
       </c>
       <c r="G163" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="H163" t="n">
-        <v>-4.13</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-95.51000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19818142</v>
+        <v>5.19582587</v>
       </c>
       <c r="D164" t="n">
-        <v>47</v>
+        <v>50.15</v>
       </c>
       <c r="E164" t="n">
-        <v>47</v>
+        <v>51.55</v>
       </c>
       <c r="F164" t="n">
-        <v>45.86</v>
+        <v>49.64</v>
       </c>
       <c r="G164" t="n">
-        <v>46.28</v>
+        <v>50.5</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.36</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-254.06</v>
+        <v>-21.2345</v>
       </c>
       <c r="C165" t="n">
-        <v>5.17277542</v>
+        <v>5.19370242</v>
       </c>
       <c r="D165" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="E165" t="n">
-        <v>47.18</v>
+        <v>50.8</v>
       </c>
       <c r="F165" t="n">
-        <v>45.76</v>
+        <v>47.9</v>
       </c>
       <c r="G165" t="n">
-        <v>45.9</v>
+        <v>48.32</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.82</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-316.19</v>
+        <v>47.7</v>
       </c>
       <c r="C166" t="n">
-        <v>5.14115642</v>
+        <v>5.19847242</v>
       </c>
       <c r="D166" t="n">
-        <v>45.9</v>
+        <v>48.98</v>
       </c>
       <c r="E166" t="n">
-        <v>46.78</v>
+        <v>49.94</v>
       </c>
       <c r="F166" t="n">
-        <v>45.26</v>
+        <v>48.18</v>
       </c>
       <c r="G166" t="n">
-        <v>46.08</v>
+        <v>49.44</v>
       </c>
       <c r="H166" t="n">
-        <v>0.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-150.87</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C167" t="n">
-        <v>5.12606942</v>
+        <v>5.20773242</v>
       </c>
       <c r="D167" t="n">
-        <v>47.7</v>
+        <v>49.44</v>
       </c>
       <c r="E167" t="n">
-        <v>48.9</v>
+        <v>49.44</v>
       </c>
       <c r="F167" t="n">
-        <v>46.64</v>
+        <v>46.74</v>
       </c>
       <c r="G167" t="n">
-        <v>46.84</v>
+        <v>47.4</v>
       </c>
       <c r="H167" t="n">
-        <v>1.65</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-236.76</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C168" t="n">
-        <v>5.10239342</v>
+        <v>5.19818142</v>
       </c>
       <c r="D168" t="n">
-        <v>46.92</v>
+        <v>47</v>
       </c>
       <c r="E168" t="n">
-        <v>48.28</v>
+        <v>47</v>
       </c>
       <c r="F168" t="n">
-        <v>46.84</v>
+        <v>45.86</v>
       </c>
       <c r="G168" t="n">
-        <v>47.36</v>
+        <v>46.28</v>
       </c>
       <c r="H168" t="n">
-        <v>1.11</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-36.92</v>
+        <v>-254.06</v>
       </c>
       <c r="C169" t="n">
-        <v>5.09870142</v>
+        <v>5.17277542</v>
       </c>
       <c r="D169" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="E169" t="n">
-        <v>47.56</v>
+        <v>47.18</v>
       </c>
       <c r="F169" t="n">
-        <v>45.72</v>
+        <v>45.76</v>
       </c>
       <c r="G169" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="H169" t="n">
-        <v>-2.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>64.78</v>
+        <v>-316.19</v>
       </c>
       <c r="C170" t="n">
-        <v>5.10517942</v>
+        <v>5.14115642</v>
       </c>
       <c r="D170" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="E170" t="n">
-        <v>48.42</v>
+        <v>46.78</v>
       </c>
       <c r="F170" t="n">
-        <v>46.26</v>
+        <v>45.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.6</v>
+        <v>46.08</v>
       </c>
       <c r="H170" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-44.41</v>
+        <v>-150.87</v>
       </c>
       <c r="C171" t="n">
-        <v>5.10073842</v>
+        <v>5.12606942</v>
       </c>
       <c r="D171" t="n">
-        <v>47.06</v>
+        <v>47.7</v>
       </c>
       <c r="E171" t="n">
-        <v>48.98</v>
+        <v>48.9</v>
       </c>
       <c r="F171" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="G171" t="n">
-        <v>48.52</v>
+        <v>46.84</v>
       </c>
       <c r="H171" t="n">
-        <v>4.12</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-124.97</v>
+        <v>-236.76</v>
       </c>
       <c r="C172" t="n">
-        <v>5.08824142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D172" t="n">
-        <v>47.6</v>
+        <v>46.92</v>
       </c>
       <c r="E172" t="n">
-        <v>48.08</v>
+        <v>48.28</v>
       </c>
       <c r="F172" t="n">
-        <v>46.72</v>
+        <v>46.84</v>
       </c>
       <c r="G172" t="n">
-        <v>46.76</v>
+        <v>47.36</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.63</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-272.6</v>
+        <v>-36.92</v>
       </c>
       <c r="C173" t="n">
-        <v>5.06098142</v>
+        <v>5.09870142</v>
       </c>
       <c r="D173" t="n">
-        <v>46.76</v>
+        <v>47</v>
       </c>
       <c r="E173" t="n">
-        <v>48.3</v>
+        <v>47.56</v>
       </c>
       <c r="F173" t="n">
-        <v>46.02</v>
+        <v>45.72</v>
       </c>
       <c r="G173" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="H173" t="n">
-        <v>1.41</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>83.54000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="C174" t="n">
-        <v>5.06933542</v>
+        <v>5.10517942</v>
       </c>
       <c r="D174" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="E174" t="n">
-        <v>47.92</v>
+        <v>48.42</v>
       </c>
       <c r="F174" t="n">
-        <v>46.46</v>
+        <v>46.26</v>
       </c>
       <c r="G174" t="n">
-        <v>47.2</v>
+        <v>46.6</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.46</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-232.94</v>
+        <v>-44.41</v>
       </c>
       <c r="C175" t="n">
-        <v>5.04604142</v>
+        <v>5.10073842</v>
       </c>
       <c r="D175" t="n">
-        <v>47.2</v>
+        <v>47.06</v>
       </c>
       <c r="E175" t="n">
-        <v>48.84</v>
+        <v>48.98</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.56</v>
+        <v>48.52</v>
       </c>
       <c r="H175" t="n">
-        <v>2.88</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-101.2265</v>
+        <v>-124.97</v>
       </c>
       <c r="C176" t="n">
-        <v>5.03591877</v>
+        <v>5.08824142</v>
       </c>
       <c r="D176" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="E176" t="n">
-        <v>49.46</v>
+        <v>48.08</v>
       </c>
       <c r="F176" t="n">
-        <v>48.24</v>
+        <v>46.72</v>
       </c>
       <c r="G176" t="n">
-        <v>48.78</v>
+        <v>46.76</v>
       </c>
       <c r="H176" t="n">
-        <v>0.45</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-146.01</v>
+        <v>-272.6</v>
       </c>
       <c r="C177" t="n">
-        <v>5.02131777</v>
+        <v>5.06098142</v>
       </c>
       <c r="D177" t="n">
-        <v>49.22</v>
+        <v>46.76</v>
       </c>
       <c r="E177" t="n">
-        <v>51</v>
+        <v>48.3</v>
       </c>
       <c r="F177" t="n">
-        <v>49.22</v>
+        <v>46.02</v>
       </c>
       <c r="G177" t="n">
-        <v>50.4</v>
+        <v>47.42</v>
       </c>
       <c r="H177" t="n">
-        <v>3.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>14.25</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>5.02274277</v>
+        <v>5.06933542</v>
       </c>
       <c r="D178" t="n">
-        <v>50.55</v>
+        <v>47.42</v>
       </c>
       <c r="E178" t="n">
-        <v>51</v>
+        <v>47.92</v>
       </c>
       <c r="F178" t="n">
-        <v>48.2</v>
+        <v>46.46</v>
       </c>
       <c r="G178" t="n">
-        <v>48.94</v>
+        <v>47.2</v>
       </c>
       <c r="H178" t="n">
-        <v>-2.9</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7.54</v>
+        <v>-232.94</v>
       </c>
       <c r="C179" t="n">
-        <v>5.02349677</v>
+        <v>5.04604142</v>
       </c>
       <c r="D179" t="n">
-        <v>49.96</v>
+        <v>47.2</v>
       </c>
       <c r="E179" t="n">
-        <v>49.98</v>
+        <v>48.84</v>
       </c>
       <c r="F179" t="n">
-        <v>48.72</v>
+        <v>46.7</v>
       </c>
       <c r="G179" t="n">
-        <v>49.12</v>
+        <v>48.56</v>
       </c>
       <c r="H179" t="n">
-        <v>0.37</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>29.93</v>
+        <v>-101.2265</v>
       </c>
       <c r="C180" t="n">
-        <v>5.02648977</v>
+        <v>5.03591877</v>
       </c>
       <c r="D180" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="E180" t="n">
-        <v>49.36</v>
+        <v>49.46</v>
       </c>
       <c r="F180" t="n">
-        <v>48.18</v>
+        <v>48.24</v>
       </c>
       <c r="G180" t="n">
-        <v>48.64</v>
+        <v>48.78</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.98</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-93.37</v>
+        <v>-146.01</v>
       </c>
       <c r="C181" t="n">
-        <v>5.01715277</v>
+        <v>5.02131777</v>
       </c>
       <c r="D181" t="n">
-        <v>48.4</v>
+        <v>49.22</v>
       </c>
       <c r="E181" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F181" t="n">
-        <v>47.2</v>
+        <v>49.22</v>
       </c>
       <c r="G181" t="n">
-        <v>47.64</v>
+        <v>50.4</v>
       </c>
       <c r="H181" t="n">
-        <v>-2.06</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-93.65000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C182" t="n">
-        <v>5.00778777</v>
+        <v>5.02274277</v>
       </c>
       <c r="D182" t="n">
-        <v>47.64</v>
+        <v>50.55</v>
       </c>
       <c r="E182" t="n">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="F182" t="n">
-        <v>47.22</v>
+        <v>48.2</v>
       </c>
       <c r="G182" t="n">
-        <v>48.96</v>
+        <v>48.94</v>
       </c>
       <c r="H182" t="n">
-        <v>2.77</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>28.06</v>
+        <v>7.54</v>
       </c>
       <c r="C183" t="n">
-        <v>5.01059377</v>
+        <v>5.02349677</v>
       </c>
       <c r="D183" t="n">
-        <v>48.36</v>
+        <v>49.96</v>
       </c>
       <c r="E183" t="n">
-        <v>48.76</v>
+        <v>49.98</v>
       </c>
       <c r="F183" t="n">
-        <v>47.52</v>
+        <v>48.72</v>
       </c>
       <c r="G183" t="n">
-        <v>47.98</v>
+        <v>49.12</v>
       </c>
       <c r="H183" t="n">
-        <v>-2</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-160.94</v>
+        <v>29.93</v>
       </c>
       <c r="C184" t="n">
-        <v>4.99449977</v>
+        <v>5.02648977</v>
       </c>
       <c r="D184" t="n">
-        <v>47.98</v>
+        <v>49.1</v>
       </c>
       <c r="E184" t="n">
-        <v>48.46</v>
+        <v>49.36</v>
       </c>
       <c r="F184" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="G184" t="n">
-        <v>48.08</v>
+        <v>48.64</v>
       </c>
       <c r="H184" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>76.84999999999999</v>
+        <v>-93.37</v>
       </c>
       <c r="C185" t="n">
-        <v>5.00218477</v>
+        <v>5.01715277</v>
       </c>
       <c r="D185" t="n">
-        <v>49.54</v>
+        <v>48.4</v>
       </c>
       <c r="E185" t="n">
-        <v>50.5</v>
+        <v>48.4</v>
       </c>
       <c r="F185" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="G185" t="n">
-        <v>49.68</v>
+        <v>47.64</v>
       </c>
       <c r="H185" t="n">
-        <v>3.33</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-70.88</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C186" t="n">
-        <v>4.99509677</v>
+        <v>5.00778777</v>
       </c>
       <c r="D186" t="n">
-        <v>51.9</v>
+        <v>47.64</v>
       </c>
       <c r="E186" t="n">
-        <v>55.6</v>
+        <v>49.3</v>
       </c>
       <c r="F186" t="n">
-        <v>51.9</v>
+        <v>47.22</v>
       </c>
       <c r="G186" t="n">
-        <v>54.6</v>
+        <v>48.96</v>
       </c>
       <c r="H186" t="n">
-        <v>9.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-223.97</v>
+        <v>28.06</v>
       </c>
       <c r="C187" t="n">
-        <v>4.97269977</v>
+        <v>5.01059377</v>
       </c>
       <c r="D187" t="n">
-        <v>54.7</v>
+        <v>48.36</v>
       </c>
       <c r="E187" t="n">
-        <v>56.1</v>
+        <v>48.76</v>
       </c>
       <c r="F187" t="n">
-        <v>53.7</v>
+        <v>47.52</v>
       </c>
       <c r="G187" t="n">
-        <v>54.25</v>
+        <v>47.98</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.64</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-908.88</v>
+        <v>-160.94</v>
       </c>
       <c r="C188" t="n">
-        <v>4.88181177</v>
+        <v>4.99449977</v>
       </c>
       <c r="D188" t="n">
-        <v>52.85</v>
+        <v>47.98</v>
       </c>
       <c r="E188" t="n">
-        <v>53.8</v>
+        <v>48.46</v>
       </c>
       <c r="F188" t="n">
-        <v>51.3</v>
+        <v>47.32</v>
       </c>
       <c r="G188" t="n">
-        <v>53.4</v>
+        <v>48.08</v>
       </c>
       <c r="H188" t="n">
-        <v>-1.57</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-219</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C189" t="n">
-        <v>4.85991177</v>
+        <v>5.00218477</v>
       </c>
       <c r="D189" t="n">
-        <v>52.75</v>
+        <v>49.54</v>
       </c>
       <c r="E189" t="n">
-        <v>54.45</v>
+        <v>50.5</v>
       </c>
       <c r="F189" t="n">
-        <v>51.45</v>
+        <v>48.9</v>
       </c>
       <c r="G189" t="n">
-        <v>51.85</v>
+        <v>49.68</v>
       </c>
       <c r="H189" t="n">
-        <v>-2.9</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>81.19</v>
+        <v>-70.88</v>
       </c>
       <c r="C190" t="n">
-        <v>4.86803077</v>
+        <v>4.99509677</v>
       </c>
       <c r="D190" t="n">
-        <v>51.85</v>
+        <v>51.9</v>
       </c>
       <c r="E190" t="n">
-        <v>51.85</v>
+        <v>55.6</v>
       </c>
       <c r="F190" t="n">
-        <v>49.6</v>
+        <v>51.9</v>
       </c>
       <c r="G190" t="n">
-        <v>50.45</v>
+        <v>54.6</v>
       </c>
       <c r="H190" t="n">
-        <v>-2.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7.21</v>
+        <v>-223.97</v>
       </c>
       <c r="C191" t="n">
-        <v>4.86875177</v>
+        <v>4.97269977</v>
       </c>
       <c r="D191" t="n">
-        <v>50.05</v>
+        <v>54.7</v>
       </c>
       <c r="E191" t="n">
-        <v>50.8</v>
+        <v>56.1</v>
       </c>
       <c r="F191" t="n">
-        <v>49.52</v>
+        <v>53.7</v>
       </c>
       <c r="G191" t="n">
-        <v>50.65</v>
+        <v>54.25</v>
       </c>
       <c r="H191" t="n">
-        <v>0.4</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>144.28</v>
+        <v>-908.88</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88317977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D192" t="n">
-        <v>50</v>
+        <v>52.85</v>
       </c>
       <c r="E192" t="n">
-        <v>50.6</v>
+        <v>53.8</v>
       </c>
       <c r="F192" t="n">
-        <v>49.08</v>
+        <v>51.3</v>
       </c>
       <c r="G192" t="n">
-        <v>49.12</v>
+        <v>53.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-3.02</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-41.02</v>
+        <v>-219</v>
       </c>
       <c r="C193" t="n">
-        <v>4.87907777</v>
+        <v>4.85991177</v>
       </c>
       <c r="D193" t="n">
-        <v>49.18</v>
+        <v>52.75</v>
       </c>
       <c r="E193" t="n">
-        <v>50.1</v>
+        <v>54.45</v>
       </c>
       <c r="F193" t="n">
-        <v>48.82</v>
+        <v>51.45</v>
       </c>
       <c r="G193" t="n">
-        <v>49.92</v>
+        <v>51.85</v>
       </c>
       <c r="H193" t="n">
-        <v>1.63</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>68.70999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="C194" t="n">
-        <v>4.88594877</v>
+        <v>4.86803077</v>
       </c>
       <c r="D194" t="n">
-        <v>50.5</v>
+        <v>51.85</v>
       </c>
       <c r="E194" t="n">
-        <v>50.95</v>
+        <v>51.85</v>
       </c>
       <c r="F194" t="n">
-        <v>49.74</v>
+        <v>49.6</v>
       </c>
       <c r="G194" t="n">
-        <v>50.1</v>
+        <v>50.45</v>
       </c>
       <c r="H194" t="n">
-        <v>0.36</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>20.01</v>
+        <v>7.21</v>
       </c>
       <c r="C195" t="n">
-        <v>4.88794977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D195" t="n">
-        <v>50</v>
+        <v>50.05</v>
       </c>
       <c r="E195" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F195" t="n">
-        <v>49.04</v>
+        <v>49.52</v>
       </c>
       <c r="G195" t="n">
-        <v>49.06</v>
+        <v>50.65</v>
       </c>
       <c r="H195" t="n">
-        <v>-2.08</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-18.77</v>
+        <v>144.28</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88607277</v>
+        <v>4.88317977</v>
       </c>
       <c r="D196" t="n">
+        <v>50</v>
+      </c>
+      <c r="E196" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="F196" t="n">
         <v>49.08</v>
       </c>
-      <c r="E196" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="F196" t="n">
-        <v>48.7</v>
-      </c>
       <c r="G196" t="n">
-        <v>49.4</v>
+        <v>49.12</v>
       </c>
       <c r="H196" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>95.14</v>
+        <v>-41.02</v>
       </c>
       <c r="C197" t="n">
-        <v>4.89558677</v>
+        <v>4.87907777</v>
       </c>
       <c r="D197" t="n">
-        <v>48.66</v>
+        <v>49.18</v>
       </c>
       <c r="E197" t="n">
-        <v>49.22</v>
+        <v>50.1</v>
       </c>
       <c r="F197" t="n">
-        <v>48.02</v>
+        <v>48.82</v>
       </c>
       <c r="G197" t="n">
-        <v>48.22</v>
+        <v>49.92</v>
       </c>
       <c r="H197" t="n">
-        <v>-2.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>6.47</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C198" t="n">
-        <v>4.89623377</v>
+        <v>4.88594877</v>
       </c>
       <c r="D198" t="n">
-        <v>48.22</v>
+        <v>50.5</v>
       </c>
       <c r="E198" t="n">
-        <v>48.22</v>
+        <v>50.95</v>
       </c>
       <c r="F198" t="n">
-        <v>47.46</v>
+        <v>49.74</v>
       </c>
       <c r="G198" t="n">
-        <v>47.46</v>
+        <v>50.1</v>
       </c>
       <c r="H198" t="n">
-        <v>-1.58</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>78.34</v>
+        <v>20.01</v>
       </c>
       <c r="C199" t="n">
-        <v>4.90406777</v>
+        <v>4.88794977</v>
       </c>
       <c r="D199" t="n">
-        <v>47.86</v>
+        <v>50</v>
       </c>
       <c r="E199" t="n">
-        <v>48.68</v>
+        <v>50.5</v>
       </c>
       <c r="F199" t="n">
-        <v>47.7</v>
+        <v>49.04</v>
       </c>
       <c r="G199" t="n">
-        <v>48.48</v>
+        <v>49.06</v>
       </c>
       <c r="H199" t="n">
-        <v>2.15</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>12.2</v>
+        <v>-18.77</v>
       </c>
       <c r="C200" t="n">
-        <v>4.90528777</v>
+        <v>4.88607277</v>
       </c>
       <c r="D200" t="n">
-        <v>48.1</v>
+        <v>49.08</v>
       </c>
       <c r="E200" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="F200" t="n">
         <v>48.7</v>
       </c>
-      <c r="F200" t="n">
-        <v>47.38</v>
-      </c>
       <c r="G200" t="n">
-        <v>47.88</v>
+        <v>49.4</v>
       </c>
       <c r="H200" t="n">
-        <v>-1.24</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-50.42</v>
+        <v>95.14</v>
       </c>
       <c r="C201" t="n">
-        <v>4.90024577</v>
+        <v>4.89558677</v>
       </c>
       <c r="D201" t="n">
-        <v>47.34</v>
+        <v>48.66</v>
       </c>
       <c r="E201" t="n">
-        <v>48.28</v>
+        <v>49.22</v>
       </c>
       <c r="F201" t="n">
-        <v>47.06</v>
+        <v>48.02</v>
       </c>
       <c r="G201" t="n">
-        <v>47.9</v>
+        <v>48.22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.04</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7.38</v>
+        <v>6.47</v>
       </c>
       <c r="C202" t="n">
-        <v>4.90098377</v>
+        <v>4.89623377</v>
       </c>
       <c r="D202" t="n">
-        <v>49.98</v>
+        <v>48.22</v>
       </c>
       <c r="E202" t="n">
-        <v>51.2</v>
+        <v>48.22</v>
       </c>
       <c r="F202" t="n">
-        <v>49.76</v>
+        <v>47.46</v>
       </c>
       <c r="G202" t="n">
-        <v>50.55</v>
+        <v>47.46</v>
       </c>
       <c r="H202" t="n">
-        <v>5.53</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.19</v>
+        <v>78.34</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90100277</v>
+        <v>4.90406777</v>
       </c>
       <c r="D203" t="n">
-        <v>50.55</v>
+        <v>47.86</v>
       </c>
       <c r="E203" t="n">
-        <v>51.8</v>
+        <v>48.68</v>
       </c>
       <c r="F203" t="n">
-        <v>50.5</v>
+        <v>47.7</v>
       </c>
       <c r="G203" t="n">
-        <v>51.2</v>
+        <v>48.48</v>
       </c>
       <c r="H203" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-404.07</v>
+        <v>12.2</v>
       </c>
       <c r="C204" t="n">
-        <v>4.86059577</v>
+        <v>4.90528777</v>
       </c>
       <c r="D204" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="E204" t="n">
-        <v>51</v>
+        <v>48.7</v>
       </c>
       <c r="F204" t="n">
-        <v>49.3</v>
+        <v>47.38</v>
       </c>
       <c r="G204" t="n">
-        <v>49.46</v>
+        <v>47.88</v>
       </c>
       <c r="H204" t="n">
-        <v>-3.4</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-104.42</v>
+        <v>-50.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.85015377</v>
+        <v>4.90024577</v>
       </c>
       <c r="D205" t="n">
-        <v>48.86</v>
+        <v>47.34</v>
       </c>
       <c r="E205" t="n">
-        <v>49.74</v>
+        <v>48.28</v>
       </c>
       <c r="F205" t="n">
-        <v>47.6</v>
+        <v>47.06</v>
       </c>
       <c r="G205" t="n">
-        <v>47.68</v>
+        <v>47.9</v>
       </c>
       <c r="H205" t="n">
-        <v>-3.6</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-9.27</v>
+        <v>7.38</v>
       </c>
       <c r="C206" t="n">
-        <v>4.84922677</v>
+        <v>4.90098377</v>
       </c>
       <c r="D206" t="n">
-        <v>47.68</v>
+        <v>49.98</v>
       </c>
       <c r="E206" t="n">
-        <v>48.9</v>
+        <v>51.2</v>
       </c>
       <c r="F206" t="n">
-        <v>47.32</v>
+        <v>49.76</v>
       </c>
       <c r="G206" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="H206" t="n">
-        <v>0.88</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-62.41</v>
+        <v>0.19</v>
       </c>
       <c r="C207" t="n">
-        <v>4.84298577</v>
+        <v>4.90100277</v>
       </c>
       <c r="D207" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="E207" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="F207" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="G207" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="H207" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-4.06</v>
+        <v>-404.07</v>
       </c>
       <c r="C208" t="n">
-        <v>4.84257977</v>
+        <v>4.86059577</v>
       </c>
       <c r="D208" t="n">
-        <v>47.8</v>
+        <v>50.3</v>
       </c>
       <c r="E208" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="F208" t="n">
-        <v>47.16</v>
+        <v>49.3</v>
       </c>
       <c r="G208" t="n">
-        <v>47.98</v>
+        <v>49.46</v>
       </c>
       <c r="H208" t="n">
-        <v>-1.28</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>107.65</v>
+        <v>-104.42</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85334477</v>
+        <v>4.85015377</v>
       </c>
       <c r="D209" t="n">
-        <v>47.86</v>
+        <v>48.86</v>
       </c>
       <c r="E209" t="n">
-        <v>48.44</v>
+        <v>49.74</v>
       </c>
       <c r="F209" t="n">
-        <v>46.5</v>
+        <v>47.6</v>
       </c>
       <c r="G209" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.33</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>137.46</v>
+        <v>-9.27</v>
       </c>
       <c r="C210" t="n">
-        <v>4.86709077</v>
+        <v>4.84922677</v>
       </c>
       <c r="D210" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="E210" t="n">
-        <v>48.22</v>
+        <v>48.9</v>
       </c>
       <c r="F210" t="n">
-        <v>46.6</v>
+        <v>47.32</v>
       </c>
       <c r="G210" t="n">
-        <v>47.06</v>
+        <v>48.1</v>
       </c>
       <c r="H210" t="n">
-        <v>-1.59</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>154.04</v>
+        <v>-62.41</v>
       </c>
       <c r="C211" t="n">
-        <v>4.88249477</v>
+        <v>4.84298577</v>
       </c>
       <c r="D211" t="n">
-        <v>46.68</v>
+        <v>48.1</v>
       </c>
       <c r="E211" t="n">
-        <v>46.76</v>
+        <v>49</v>
       </c>
       <c r="F211" t="n">
-        <v>44.56</v>
+        <v>47.5</v>
       </c>
       <c r="G211" t="n">
-        <v>45.86</v>
+        <v>48.6</v>
       </c>
       <c r="H211" t="n">
-        <v>-2.55</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>78.03</v>
+        <v>-4.06</v>
       </c>
       <c r="C212" t="n">
-        <v>4.89029777</v>
+        <v>4.84257977</v>
       </c>
       <c r="D212" t="n">
-        <v>46.56</v>
+        <v>47.8</v>
       </c>
       <c r="E212" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="F212" t="n">
-        <v>46.2</v>
+        <v>47.16</v>
       </c>
       <c r="G212" t="n">
-        <v>46.38</v>
+        <v>47.98</v>
       </c>
       <c r="H212" t="n">
-        <v>1.13</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>401.67</v>
+        <v>107.65</v>
       </c>
       <c r="C213" t="n">
-        <v>4.93046477</v>
+        <v>4.85334477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.28</v>
+        <v>47.86</v>
       </c>
       <c r="E213" t="n">
-        <v>48.88</v>
+        <v>48.44</v>
       </c>
       <c r="F213" t="n">
-        <v>47.12</v>
+        <v>46.5</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>3.1</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-79.33</v>
+        <v>137.46</v>
       </c>
       <c r="C214" t="n">
-        <v>4.92253177</v>
+        <v>4.86709077</v>
       </c>
       <c r="D214" t="n">
-        <v>48.1</v>
+        <v>47.82</v>
       </c>
       <c r="E214" t="n">
-        <v>50.45</v>
+        <v>48.22</v>
       </c>
       <c r="F214" t="n">
-        <v>48.04</v>
+        <v>46.6</v>
       </c>
       <c r="G214" t="n">
-        <v>50.4</v>
+        <v>47.06</v>
       </c>
       <c r="H214" t="n">
-        <v>5.4</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-415.48</v>
+        <v>154.04</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88098377</v>
+        <v>4.88249477</v>
       </c>
       <c r="D215" t="n">
-        <v>49.44</v>
+        <v>46.68</v>
       </c>
       <c r="E215" t="n">
-        <v>50.15</v>
+        <v>46.76</v>
       </c>
       <c r="F215" t="n">
-        <v>48.88</v>
+        <v>44.56</v>
       </c>
       <c r="G215" t="n">
-        <v>49.32</v>
+        <v>45.86</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.14</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-394.96</v>
+        <v>78.03</v>
       </c>
       <c r="C216" t="n">
-        <v>4.84148777</v>
+        <v>4.89029777</v>
       </c>
       <c r="D216" t="n">
-        <v>49.08</v>
+        <v>46.56</v>
       </c>
       <c r="E216" t="n">
-        <v>49.08</v>
+        <v>48</v>
       </c>
       <c r="F216" t="n">
-        <v>47.2</v>
+        <v>46.2</v>
       </c>
       <c r="G216" t="n">
-        <v>47.62</v>
+        <v>46.38</v>
       </c>
       <c r="H216" t="n">
-        <v>-3.45</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-39.23</v>
+        <v>401.67</v>
       </c>
       <c r="C217" t="n">
-        <v>4.83756477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.2</v>
+        <v>47.28</v>
       </c>
       <c r="E217" t="n">
-        <v>47.2</v>
+        <v>48.88</v>
       </c>
       <c r="F217" t="n">
-        <v>46.42</v>
+        <v>47.12</v>
       </c>
       <c r="G217" t="n">
-        <v>46.48</v>
+        <v>47.82</v>
       </c>
       <c r="H217" t="n">
-        <v>-2.39</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>219.67</v>
+        <v>-79.33</v>
       </c>
       <c r="C218" t="n">
-        <v>4.85953177</v>
+        <v>4.92253177</v>
       </c>
       <c r="D218" t="n">
-        <v>45.74</v>
+        <v>48.1</v>
       </c>
       <c r="E218" t="n">
-        <v>46.44</v>
+        <v>50.45</v>
       </c>
       <c r="F218" t="n">
-        <v>45.38</v>
+        <v>48.04</v>
       </c>
       <c r="G218" t="n">
-        <v>46.34</v>
+        <v>50.4</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>111.68</v>
+        <v>-415.48</v>
       </c>
       <c r="C219" t="n">
-        <v>4.87069977</v>
+        <v>4.88098377</v>
       </c>
       <c r="D219" t="n">
-        <v>45.9</v>
+        <v>49.44</v>
       </c>
       <c r="E219" t="n">
-        <v>47.8</v>
+        <v>50.15</v>
       </c>
       <c r="F219" t="n">
-        <v>45.84</v>
+        <v>48.88</v>
       </c>
       <c r="G219" t="n">
-        <v>47.52</v>
+        <v>49.32</v>
       </c>
       <c r="H219" t="n">
-        <v>2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>47.5</v>
+        <v>-394.96</v>
       </c>
       <c r="C220" t="n">
-        <v>4.87544977</v>
+        <v>4.84148777</v>
       </c>
       <c r="D220" t="n">
-        <v>47.52</v>
+        <v>49.08</v>
       </c>
       <c r="E220" t="n">
-        <v>48.06</v>
+        <v>49.08</v>
       </c>
       <c r="F220" t="n">
-        <v>46.06</v>
+        <v>47.2</v>
       </c>
       <c r="G220" t="n">
-        <v>46.12</v>
+        <v>47.62</v>
       </c>
       <c r="H220" t="n">
-        <v>-2.95</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-30.32</v>
+        <v>-39.23</v>
       </c>
       <c r="C221" t="n">
-        <v>4.87241777</v>
+        <v>4.83756477</v>
       </c>
       <c r="D221" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E221" t="n">
-        <v>47.42</v>
+        <v>47.2</v>
       </c>
       <c r="F221" t="n">
-        <v>45.94</v>
+        <v>46.42</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>0.78</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>15.46</v>
+        <v>219.67</v>
       </c>
       <c r="C222" t="n">
-        <v>4.87396377</v>
+        <v>4.85953177</v>
       </c>
       <c r="D222" t="n">
-        <v>46.9</v>
+        <v>45.74</v>
       </c>
       <c r="E222" t="n">
-        <v>47.5</v>
+        <v>46.44</v>
       </c>
       <c r="F222" t="n">
-        <v>44.94</v>
+        <v>45.38</v>
       </c>
       <c r="G222" t="n">
-        <v>46.88</v>
+        <v>46.34</v>
       </c>
       <c r="H222" t="n">
-        <v>0.86</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>57.59</v>
+        <v>111.68</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87972277</v>
+        <v>4.87069977</v>
       </c>
       <c r="D223" t="n">
-        <v>46.9</v>
+        <v>45.9</v>
       </c>
       <c r="E223" t="n">
-        <v>48.46</v>
+        <v>47.8</v>
       </c>
       <c r="F223" t="n">
-        <v>46.8</v>
+        <v>45.84</v>
       </c>
       <c r="G223" t="n">
-        <v>47.56</v>
+        <v>47.52</v>
       </c>
       <c r="H223" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>112.19</v>
+        <v>47.5</v>
       </c>
       <c r="C224" t="n">
-        <v>4.89094177</v>
+        <v>4.87544977</v>
       </c>
       <c r="D224" t="n">
-        <v>47.54</v>
+        <v>47.52</v>
       </c>
       <c r="E224" t="n">
-        <v>47.54</v>
+        <v>48.06</v>
       </c>
       <c r="F224" t="n">
-        <v>44.82</v>
+        <v>46.06</v>
       </c>
       <c r="G224" t="n">
-        <v>45.48</v>
+        <v>46.12</v>
       </c>
       <c r="H224" t="n">
-        <v>-4.37</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-42.06</v>
+        <v>-30.32</v>
       </c>
       <c r="C225" t="n">
-        <v>4.88673577</v>
+        <v>4.87241777</v>
       </c>
       <c r="D225" t="n">
-        <v>45</v>
+        <v>46.92</v>
       </c>
       <c r="E225" t="n">
-        <v>45.8</v>
+        <v>47.42</v>
       </c>
       <c r="F225" t="n">
-        <v>44.68</v>
+        <v>45.94</v>
       </c>
       <c r="G225" t="n">
-        <v>45.08</v>
+        <v>46.48</v>
       </c>
       <c r="H225" t="n">
-        <v>-0.88</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>201.66</v>
+        <v>15.46</v>
       </c>
       <c r="C226" t="n">
-        <v>4.90690177</v>
+        <v>4.87396377</v>
       </c>
       <c r="D226" t="n">
-        <v>45.72</v>
+        <v>46.9</v>
       </c>
       <c r="E226" t="n">
-        <v>46.54</v>
+        <v>47.5</v>
       </c>
       <c r="F226" t="n">
-        <v>45.34</v>
+        <v>44.94</v>
       </c>
       <c r="G226" t="n">
-        <v>46.24</v>
+        <v>46.88</v>
       </c>
       <c r="H226" t="n">
-        <v>2.57</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>138.5</v>
+        <v>57.59</v>
       </c>
       <c r="C227" t="n">
-        <v>4.92075177</v>
+        <v>4.87972277</v>
       </c>
       <c r="D227" t="n">
-        <v>45.48</v>
+        <v>46.9</v>
       </c>
       <c r="E227" t="n">
-        <v>47.3</v>
+        <v>48.46</v>
       </c>
       <c r="F227" t="n">
-        <v>45.48</v>
+        <v>46.8</v>
       </c>
       <c r="G227" t="n">
-        <v>46.76</v>
+        <v>47.56</v>
       </c>
       <c r="H227" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>112.19</v>
+      </c>
+      <c r="C228" t="n">
+        <v>4.89094177</v>
+      </c>
+      <c r="D228" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="E228" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="F228" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="G228" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="H228" t="n">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>-42.06</v>
+      </c>
+      <c r="C229" t="n">
+        <v>4.88673577</v>
+      </c>
+      <c r="D229" t="n">
+        <v>45</v>
+      </c>
+      <c r="E229" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="F229" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="G229" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="H229" t="n">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>201.66</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4.90690177</v>
+      </c>
+      <c r="D230" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="E230" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="F230" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="G230" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="H230" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4.92075177</v>
+      </c>
+      <c r="D231" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="E231" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="F231" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="G231" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="B228" t="n">
+      <c r="B232" t="n">
         <v>0</v>
       </c>
-      <c r="C228" t="n">
+      <c r="C232" t="n">
         <v>4.92075177</v>
       </c>
-      <c r="D228" t="n">
+      <c r="D232" t="n">
         <v>46.76</v>
       </c>
-      <c r="E228" t="n">
+      <c r="E232" t="n">
         <v>46.76</v>
       </c>
-      <c r="F228" t="n">
+      <c r="F232" t="n">
         <v>44.9</v>
       </c>
-      <c r="G228" t="n">
+      <c r="G232" t="n">
         <v>45.24</v>
       </c>
-      <c r="H228" t="n">
+      <c r="H232" t="n">
         <v>-3.25</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4.92075177</v>
+      </c>
+      <c r="D233" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="E233" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="F233" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="G233" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1.11</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H233"/>
+  <dimension ref="A1:H229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E79" t="n">
-        <v>73.34999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="F79" t="n">
-        <v>71.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>73.34999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="F80" t="n">
-        <v>71.5</v>
+        <v>69.55</v>
       </c>
       <c r="G80" t="n">
-        <v>72.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4274 +2693,4162 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>72.8</v>
+        <v>70.3</v>
       </c>
       <c r="E81" t="n">
-        <v>73.34999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="F81" t="n">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="G81" t="n">
-        <v>72.3</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>-37.37</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D82" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E82" t="n">
-        <v>72.25</v>
+        <v>73.5</v>
       </c>
       <c r="F82" t="n">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G82" t="n">
-        <v>72.09999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.28</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D83" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E83" t="n">
-        <v>71.75</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>69.55</v>
+        <v>70.5</v>
       </c>
       <c r="G83" t="n">
-        <v>70.09999999999999</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>-2.77</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>39.15</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29754581</v>
+        <v>5.29772381</v>
       </c>
       <c r="D84" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="E84" t="n">
-        <v>73.3</v>
+        <v>71.8</v>
       </c>
       <c r="F84" t="n">
-        <v>70.3</v>
+        <v>68.55</v>
       </c>
       <c r="G84" t="n">
-        <v>72.84999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>3.92</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-37.37</v>
+        <v>-32.03</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29380881</v>
+        <v>5.29452081</v>
       </c>
       <c r="D85" t="n">
-        <v>71.8</v>
+        <v>69.5</v>
       </c>
       <c r="E85" t="n">
-        <v>73.5</v>
+        <v>69.5</v>
       </c>
       <c r="F85" t="n">
-        <v>71.3</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>71.75</v>
+        <v>68.75</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.51</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-245.51</v>
       </c>
       <c r="C86" t="n">
-        <v>5.29380881</v>
+        <v>5.26996981</v>
       </c>
       <c r="D86" t="n">
-        <v>72.8</v>
+        <v>67.75</v>
       </c>
       <c r="E86" t="n">
-        <v>73.15000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>70.5</v>
+        <v>67</v>
       </c>
       <c r="G86" t="n">
-        <v>71.84999999999999</v>
+        <v>68</v>
       </c>
       <c r="H86" t="n">
-        <v>0.14</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39.15</v>
+        <v>24.99</v>
       </c>
       <c r="C87" t="n">
-        <v>5.29772381</v>
+        <v>5.27246881</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
       <c r="F87" t="n">
-        <v>68.55</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>68.65000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="H87" t="n">
-        <v>-4.45</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-32.03</v>
+        <v>-70.5937</v>
       </c>
       <c r="C88" t="n">
-        <v>5.29452081</v>
+        <v>5.26540944</v>
       </c>
       <c r="D88" t="n">
-        <v>69.5</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>69.5</v>
+        <v>66.8</v>
       </c>
       <c r="F88" t="n">
-        <v>68.15000000000001</v>
+        <v>64.45</v>
       </c>
       <c r="G88" t="n">
-        <v>68.75</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-245.51</v>
+        <v>-83.42</v>
       </c>
       <c r="C89" t="n">
-        <v>5.26996981</v>
+        <v>5.25706744</v>
       </c>
       <c r="D89" t="n">
-        <v>67.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>70.15000000000001</v>
+        <v>68</v>
       </c>
       <c r="F89" t="n">
-        <v>67</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>68</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.09</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24.99</v>
+        <v>32.9872</v>
       </c>
       <c r="C90" t="n">
-        <v>5.27246881</v>
+        <v>5.26036616</v>
       </c>
       <c r="D90" t="n">
-        <v>68.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="E90" t="n">
-        <v>69</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>65.65000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>66.55</v>
+        <v>67.45</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.13</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-70.5937</v>
+        <v>-168.98</v>
       </c>
       <c r="C91" t="n">
-        <v>5.26540944</v>
+        <v>5.24346816</v>
       </c>
       <c r="D91" t="n">
-        <v>65.84999999999999</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>66.8</v>
+        <v>69</v>
       </c>
       <c r="F91" t="n">
-        <v>64.45</v>
+        <v>64.7</v>
       </c>
       <c r="G91" t="n">
-        <v>65.84999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-83.42</v>
+        <v>-195.54</v>
       </c>
       <c r="C92" t="n">
-        <v>5.25706744</v>
+        <v>5.22391416</v>
       </c>
       <c r="D92" t="n">
-        <v>66.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>68</v>
+        <v>70.2</v>
       </c>
       <c r="F92" t="n">
-        <v>65.09999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="G92" t="n">
-        <v>65.59999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.38</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>32.9872</v>
+        <v>16.18</v>
       </c>
       <c r="C93" t="n">
-        <v>5.26036616</v>
+        <v>5.22553216</v>
       </c>
       <c r="D93" t="n">
-        <v>65.5</v>
+        <v>69.25</v>
       </c>
       <c r="E93" t="n">
-        <v>67.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.34999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="G93" t="n">
-        <v>67.45</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>2.82</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-168.98</v>
+        <v>13.87</v>
       </c>
       <c r="C94" t="n">
-        <v>5.24346816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D94" t="n">
-        <v>64.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E94" t="n">
-        <v>69</v>
+        <v>71.3</v>
       </c>
       <c r="F94" t="n">
-        <v>64.7</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>68.90000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>2.15</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-195.54</v>
+        <v>-145.08</v>
       </c>
       <c r="C95" t="n">
-        <v>5.22391416</v>
+        <v>5.21241116</v>
       </c>
       <c r="D95" t="n">
-        <v>69.90000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E95" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="F95" t="n">
-        <v>67.95</v>
+        <v>67.3</v>
       </c>
       <c r="G95" t="n">
-        <v>69.05</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.22</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>16.18</v>
+        <v>25.02</v>
       </c>
       <c r="C96" t="n">
-        <v>5.22553216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D96" t="n">
-        <v>69.25</v>
+        <v>67.5</v>
       </c>
       <c r="E96" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>69.05</v>
+        <v>66.3</v>
       </c>
       <c r="G96" t="n">
-        <v>69.84999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>1.16</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.87</v>
+        <v>-6.25</v>
       </c>
       <c r="C97" t="n">
-        <v>5.22691916</v>
+        <v>5.21428816</v>
       </c>
       <c r="D97" t="n">
-        <v>70.95</v>
+        <v>71.25</v>
       </c>
       <c r="E97" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="G97" t="n">
         <v>71.3</v>
       </c>
-      <c r="F97" t="n">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="G97" t="n">
-        <v>70.15000000000001</v>
-      </c>
       <c r="H97" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-145.08</v>
+        <v>-48.58</v>
       </c>
       <c r="C98" t="n">
-        <v>5.21241116</v>
+        <v>5.20943016</v>
       </c>
       <c r="D98" t="n">
-        <v>68.95</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>69</v>
+        <v>71.25</v>
       </c>
       <c r="F98" t="n">
-        <v>67.3</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>67.90000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>-3.21</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25.02</v>
+        <v>-197.18</v>
       </c>
       <c r="C99" t="n">
-        <v>5.21491316</v>
+        <v>5.18971216</v>
       </c>
       <c r="D99" t="n">
-        <v>67.5</v>
+        <v>66.2</v>
       </c>
       <c r="E99" t="n">
-        <v>70.09999999999999</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>66.3</v>
+        <v>65.8</v>
       </c>
       <c r="G99" t="n">
-        <v>69.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="H99" t="n">
-        <v>2.95</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-6.25</v>
+        <v>426.64</v>
       </c>
       <c r="C100" t="n">
-        <v>5.21428816</v>
+        <v>5.23237616</v>
       </c>
       <c r="D100" t="n">
-        <v>71.25</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>73.3</v>
+        <v>68.7</v>
       </c>
       <c r="F100" t="n">
-        <v>70.84999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>71.3</v>
+        <v>66.8</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-48.58</v>
+        <v>41.4993</v>
       </c>
       <c r="C101" t="n">
-        <v>5.20943016</v>
+        <v>5.23652609</v>
       </c>
       <c r="D101" t="n">
-        <v>70.65000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>71.25</v>
+        <v>66.05</v>
       </c>
       <c r="F101" t="n">
-        <v>66.34999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G101" t="n">
-        <v>66.84999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-6.24</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-197.18</v>
+        <v>-220.5688</v>
       </c>
       <c r="C102" t="n">
-        <v>5.18971216</v>
+        <v>5.21446921</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.34999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F102" t="n">
-        <v>65.8</v>
+        <v>63.45</v>
       </c>
       <c r="G102" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>426.64</v>
+        <v>215.27</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23237616</v>
+        <v>5.23599621</v>
       </c>
       <c r="D103" t="n">
-        <v>67</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>68.7</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>66.34999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="G103" t="n">
-        <v>66.8</v>
+        <v>70.45</v>
       </c>
       <c r="H103" t="n">
-        <v>1.21</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>41.4993</v>
+        <v>-160.53</v>
       </c>
       <c r="C104" t="n">
-        <v>5.23652609</v>
+        <v>5.21994321</v>
       </c>
       <c r="D104" t="n">
-        <v>65.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>66.05</v>
+        <v>70.8</v>
       </c>
       <c r="F104" t="n">
-        <v>64.2</v>
+        <v>68.7</v>
       </c>
       <c r="G104" t="n">
-        <v>64.8</v>
+        <v>69</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.99</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-220.5688</v>
+        <v>-304.01</v>
       </c>
       <c r="C105" t="n">
-        <v>5.21446921</v>
+        <v>5.18954221</v>
       </c>
       <c r="D105" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="E105" t="n">
-        <v>67.65000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F105" t="n">
-        <v>63.45</v>
+        <v>68.3</v>
       </c>
       <c r="G105" t="n">
-        <v>67.59999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H105" t="n">
-        <v>4.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>215.27</v>
+        <v>-30.3</v>
       </c>
       <c r="C106" t="n">
-        <v>5.23599621</v>
+        <v>5.18651221</v>
       </c>
       <c r="D106" t="n">
-        <v>69.59999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="E106" t="n">
-        <v>71.34999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>69.45</v>
+        <v>68</v>
       </c>
       <c r="G106" t="n">
-        <v>70.45</v>
+        <v>68.8</v>
       </c>
       <c r="H106" t="n">
-        <v>4.22</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-160.53</v>
+        <v>-92.3</v>
       </c>
       <c r="C107" t="n">
-        <v>5.21994321</v>
+        <v>5.17728221</v>
       </c>
       <c r="D107" t="n">
-        <v>69.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E107" t="n">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
       <c r="G107" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.06</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-304.01</v>
+        <v>25.43</v>
       </c>
       <c r="C108" t="n">
-        <v>5.18954221</v>
+        <v>5.17982521</v>
       </c>
       <c r="D108" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>71.5</v>
+        <v>71.45</v>
       </c>
       <c r="F108" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>70.05</v>
+        <v>71.2</v>
       </c>
       <c r="H108" t="n">
-        <v>1.52</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-30.3</v>
+        <v>136.53</v>
       </c>
       <c r="C109" t="n">
-        <v>5.18651221</v>
+        <v>5.19347821</v>
       </c>
       <c r="D109" t="n">
-        <v>68.05</v>
+        <v>71.2</v>
       </c>
       <c r="E109" t="n">
-        <v>69.34999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G109" t="n">
-        <v>68.8</v>
+        <v>71.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-92.3</v>
+        <v>-224.29</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17728221</v>
+        <v>5.17104921</v>
       </c>
       <c r="D110" t="n">
-        <v>68.8</v>
+        <v>73.45</v>
       </c>
       <c r="E110" t="n">
-        <v>69.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="F110" t="n">
-        <v>67.2</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>67.7</v>
+        <v>73.3</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.6</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>25.43</v>
+        <v>97.7422</v>
       </c>
       <c r="C111" t="n">
-        <v>5.17982521</v>
+        <v>5.18082343</v>
       </c>
       <c r="D111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="E111" t="n">
-        <v>71.45</v>
+        <v>73.5</v>
       </c>
       <c r="F111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G111" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>5.17</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>136.53</v>
+        <v>-116.85</v>
       </c>
       <c r="C112" t="n">
-        <v>5.19347821</v>
+        <v>5.16913843</v>
       </c>
       <c r="D112" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E112" t="n">
-        <v>73.40000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="F112" t="n">
-        <v>70</v>
+        <v>71.55</v>
       </c>
       <c r="G112" t="n">
-        <v>71.8</v>
+        <v>74.2</v>
       </c>
       <c r="H112" t="n">
-        <v>0.84</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-224.29</v>
+        <v>32.76</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17104921</v>
+        <v>5.17241443</v>
       </c>
       <c r="D113" t="n">
-        <v>73.45</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F113" t="n">
-        <v>71.65000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="G113" t="n">
-        <v>73.3</v>
+        <v>73.7</v>
       </c>
       <c r="H113" t="n">
-        <v>2.09</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>97.7422</v>
+        <v>-19.6</v>
       </c>
       <c r="C114" t="n">
-        <v>5.18082343</v>
+        <v>5.17045443</v>
       </c>
       <c r="D114" t="n">
-        <v>71.95</v>
+        <v>73.7</v>
       </c>
       <c r="E114" t="n">
-        <v>73.5</v>
+        <v>73.95</v>
       </c>
       <c r="F114" t="n">
-        <v>71.75</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.91</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-116.85</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>5.16913843</v>
+        <v>5.17787843</v>
       </c>
       <c r="D115" t="n">
-        <v>71.90000000000001</v>
+        <v>73.75</v>
       </c>
       <c r="E115" t="n">
-        <v>76.45</v>
+        <v>73.75</v>
       </c>
       <c r="F115" t="n">
-        <v>71.55</v>
+        <v>70.5</v>
       </c>
       <c r="G115" t="n">
-        <v>74.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>3.2</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>32.76</v>
+        <v>15.04</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17241443</v>
+        <v>5.17938243</v>
       </c>
       <c r="D116" t="n">
-        <v>74.09999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E116" t="n">
-        <v>75</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>73.25</v>
+        <v>70.95</v>
       </c>
       <c r="G116" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.67</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-19.6</v>
+        <v>213.47</v>
       </c>
       <c r="C117" t="n">
-        <v>5.17045443</v>
+        <v>5.20072943</v>
       </c>
       <c r="D117" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>73.95</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>71.65000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>73</v>
+        <v>71.45</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.95</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>74.23999999999999</v>
+        <v>-167.67</v>
       </c>
       <c r="C118" t="n">
-        <v>5.17787843</v>
+        <v>5.18396243</v>
       </c>
       <c r="D118" t="n">
-        <v>73.75</v>
+        <v>72</v>
       </c>
       <c r="E118" t="n">
-        <v>73.75</v>
+        <v>73.45</v>
       </c>
       <c r="F118" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>70.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.88</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15.04</v>
+        <v>-78.5919</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17938243</v>
+        <v>5.17610324</v>
       </c>
       <c r="D119" t="n">
-        <v>70.95</v>
+        <v>73.3</v>
       </c>
       <c r="E119" t="n">
-        <v>72.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F119" t="n">
-        <v>70.95</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H119" t="n">
-        <v>0.99</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>213.47</v>
+        <v>-54.57</v>
       </c>
       <c r="C120" t="n">
-        <v>5.20072943</v>
+        <v>5.17064624</v>
       </c>
       <c r="D120" t="n">
-        <v>71.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E120" t="n">
-        <v>71.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>70.40000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G120" t="n">
-        <v>71.45</v>
+        <v>73.45</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-167.67</v>
+        <v>32.9</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18396243</v>
+        <v>5.17393624</v>
       </c>
       <c r="D121" t="n">
-        <v>72</v>
+        <v>73.45</v>
       </c>
       <c r="E121" t="n">
-        <v>73.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>70.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G121" t="n">
-        <v>73.3</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>2.59</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-78.5919</v>
+        <v>41.93</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17610324</v>
+        <v>5.17812924</v>
       </c>
       <c r="D122" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="E122" t="n">
-        <v>73.3</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>71.84999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G122" t="n">
-        <v>73.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.14</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-54.57</v>
+        <v>52.87</v>
       </c>
       <c r="C123" t="n">
-        <v>5.17064624</v>
+        <v>5.18341624</v>
       </c>
       <c r="D123" t="n">
-        <v>72.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>73.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="F123" t="n">
-        <v>71.95</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>73.45</v>
+        <v>69.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0.34</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>32.9</v>
+        <v>291.58</v>
       </c>
       <c r="C124" t="n">
-        <v>5.17393624</v>
+        <v>5.21257424</v>
       </c>
       <c r="D124" t="n">
-        <v>73.45</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>74.40000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F124" t="n">
-        <v>71.75</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>73.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.41</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>41.93</v>
+        <v>-60.7601</v>
       </c>
       <c r="C125" t="n">
-        <v>5.17812924</v>
+        <v>5.20649823</v>
       </c>
       <c r="D125" t="n">
-        <v>73</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E125" t="n">
-        <v>73.65000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="F125" t="n">
-        <v>68.7</v>
+        <v>68.45</v>
       </c>
       <c r="G125" t="n">
-        <v>69.90000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="H125" t="n">
-        <v>-4.44</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>52.87</v>
+        <v>264.89</v>
       </c>
       <c r="C126" t="n">
-        <v>5.18341624</v>
+        <v>5.23298723</v>
       </c>
       <c r="D126" t="n">
-        <v>70.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>70.5</v>
+        <v>69.75</v>
       </c>
       <c r="F126" t="n">
-        <v>68.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="G126" t="n">
-        <v>69.7</v>
+        <v>67.55</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.29</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>291.58</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>5.21257424</v>
+        <v>5.23298723</v>
       </c>
       <c r="D127" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="E127" t="n">
-        <v>69.45</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>66.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G127" t="n">
-        <v>67</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>-3.87</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-60.7601</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>5.20649823</v>
+        <v>5.23298723</v>
       </c>
       <c r="D128" t="n">
-        <v>69.40000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="E128" t="n">
-        <v>70.25</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>68.45</v>
+        <v>68.2</v>
       </c>
       <c r="G128" t="n">
-        <v>69.25</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>3.36</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>264.89</v>
+        <v>-369.37</v>
       </c>
       <c r="C129" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D129" t="n">
-        <v>68.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E129" t="n">
-        <v>69.75</v>
+        <v>69.5</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.55</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.45</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D130" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="E130" t="n">
-        <v>69.75</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="G130" t="n">
-        <v>67.55</v>
+        <v>69.95</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>68.9663</v>
       </c>
       <c r="C131" t="n">
-        <v>5.23298723</v>
+        <v>5.20294686</v>
       </c>
       <c r="D131" t="n">
-        <v>69</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>71.15000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F131" t="n">
-        <v>68.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>70.15000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="H131" t="n">
-        <v>3.85</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>-247.41</v>
       </c>
       <c r="C132" t="n">
-        <v>5.23298723</v>
+        <v>5.17820586</v>
       </c>
       <c r="D132" t="n">
-        <v>69.25</v>
+        <v>69.5</v>
       </c>
       <c r="E132" t="n">
-        <v>70.09999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>68.2</v>
+        <v>69.45</v>
       </c>
       <c r="G132" t="n">
-        <v>69.65000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.71</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-369.37</v>
+        <v>27.55</v>
       </c>
       <c r="C133" t="n">
-        <v>5.19605023</v>
+        <v>5.18096086</v>
       </c>
       <c r="D133" t="n">
-        <v>69.5</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E133" t="n">
-        <v>69.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>67.3</v>
+        <v>73.05</v>
       </c>
       <c r="G133" t="n">
-        <v>67.84999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>-2.58</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>-286.2</v>
       </c>
       <c r="C134" t="n">
-        <v>5.19605023</v>
+        <v>5.15234086</v>
       </c>
       <c r="D134" t="n">
-        <v>68.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>70.34999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>68.5</v>
+        <v>73.05</v>
       </c>
       <c r="G134" t="n">
-        <v>69.95</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>3.1</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>68.9663</v>
+        <v>48.88</v>
       </c>
       <c r="C135" t="n">
-        <v>5.20294686</v>
+        <v>5.15722886</v>
       </c>
       <c r="D135" t="n">
-        <v>68.34999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="E135" t="n">
-        <v>70.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>68.34999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>70.05</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H135" t="n">
-        <v>0.14</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-247.41</v>
+        <v>-55.96</v>
       </c>
       <c r="C136" t="n">
-        <v>5.17820586</v>
+        <v>5.15163286</v>
       </c>
       <c r="D136" t="n">
-        <v>69.5</v>
+        <v>75.05</v>
       </c>
       <c r="E136" t="n">
-        <v>74.15000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>69.45</v>
+        <v>74.25</v>
       </c>
       <c r="G136" t="n">
-        <v>73.84999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>5.42</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>27.55</v>
+        <v>-385.85</v>
       </c>
       <c r="C137" t="n">
-        <v>5.18096086</v>
+        <v>5.11304786</v>
       </c>
       <c r="D137" t="n">
-        <v>73.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>75.15000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>73.05</v>
+        <v>64.5</v>
       </c>
       <c r="G137" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.61</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-286.2</v>
+        <v>139.59</v>
       </c>
       <c r="C138" t="n">
-        <v>5.15234086</v>
+        <v>5.12700686</v>
       </c>
       <c r="D138" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>74.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>73.05</v>
+        <v>61.75</v>
       </c>
       <c r="G138" t="n">
-        <v>73.65000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.34</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>48.88</v>
+        <v>1468.42</v>
       </c>
       <c r="C139" t="n">
-        <v>5.15722886</v>
+        <v>5.27384886</v>
       </c>
       <c r="D139" t="n">
-        <v>76.8</v>
+        <v>62.6</v>
       </c>
       <c r="E139" t="n">
-        <v>78.90000000000001</v>
+        <v>63.35</v>
       </c>
       <c r="F139" t="n">
-        <v>75.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="G139" t="n">
-        <v>76.84999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="H139" t="n">
-        <v>4.34</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-55.96</v>
+        <v>292.93</v>
       </c>
       <c r="C140" t="n">
-        <v>5.15163286</v>
+        <v>5.30314186</v>
       </c>
       <c r="D140" t="n">
-        <v>75.05</v>
+        <v>62.5</v>
       </c>
       <c r="E140" t="n">
-        <v>75.90000000000001</v>
+        <v>63.85</v>
       </c>
       <c r="F140" t="n">
-        <v>74.25</v>
+        <v>61.55</v>
       </c>
       <c r="G140" t="n">
-        <v>75.59999999999999</v>
+        <v>62.25</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.63</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-385.85</v>
+        <v>17.9</v>
       </c>
       <c r="C141" t="n">
-        <v>5.11304786</v>
+        <v>5.30493186</v>
       </c>
       <c r="D141" t="n">
-        <v>72.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="E141" t="n">
-        <v>72.40000000000001</v>
+        <v>64.95</v>
       </c>
       <c r="F141" t="n">
-        <v>64.5</v>
+        <v>61.35</v>
       </c>
       <c r="G141" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-14.15</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>139.59</v>
+        <v>-224.88</v>
       </c>
       <c r="C142" t="n">
-        <v>5.12700686</v>
+        <v>5.28244386</v>
       </c>
       <c r="D142" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="E142" t="n">
-        <v>64.90000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="F142" t="n">
-        <v>61.75</v>
+        <v>60.4</v>
       </c>
       <c r="G142" t="n">
-        <v>62.1</v>
+        <v>62.15</v>
       </c>
       <c r="H142" t="n">
-        <v>-4.31</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1468.42</v>
+        <v>-244.5</v>
       </c>
       <c r="C143" t="n">
-        <v>5.27384886</v>
+        <v>5.25799386</v>
       </c>
       <c r="D143" t="n">
-        <v>62.6</v>
+        <v>61.9</v>
       </c>
       <c r="E143" t="n">
-        <v>63.35</v>
+        <v>62.35</v>
       </c>
       <c r="F143" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="G143" t="n">
-        <v>61.6</v>
+        <v>60.2</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>292.93</v>
+        <v>-302.48</v>
       </c>
       <c r="C144" t="n">
-        <v>5.30314186</v>
+        <v>5.22774586</v>
       </c>
       <c r="D144" t="n">
-        <v>62.5</v>
+        <v>60.1</v>
       </c>
       <c r="E144" t="n">
-        <v>63.85</v>
+        <v>61</v>
       </c>
       <c r="F144" t="n">
-        <v>61.55</v>
+        <v>58.6</v>
       </c>
       <c r="G144" t="n">
-        <v>62.25</v>
+        <v>60.45</v>
       </c>
       <c r="H144" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>17.9</v>
+        <v>-177.8636</v>
       </c>
       <c r="C145" t="n">
-        <v>5.30493186</v>
+        <v>5.2099595</v>
       </c>
       <c r="D145" t="n">
-        <v>63.2</v>
+        <v>60</v>
       </c>
       <c r="E145" t="n">
-        <v>64.95</v>
+        <v>60.05</v>
       </c>
       <c r="F145" t="n">
-        <v>61.35</v>
+        <v>55.7</v>
       </c>
       <c r="G145" t="n">
-        <v>61.8</v>
+        <v>57.85</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.72</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-224.88</v>
+        <v>-228.55</v>
       </c>
       <c r="C146" t="n">
-        <v>5.28244386</v>
+        <v>5.1871045</v>
       </c>
       <c r="D146" t="n">
-        <v>61.8</v>
+        <v>56.95</v>
       </c>
       <c r="E146" t="n">
-        <v>62.25</v>
+        <v>59.1</v>
       </c>
       <c r="F146" t="n">
-        <v>60.4</v>
+        <v>56</v>
       </c>
       <c r="G146" t="n">
-        <v>62.15</v>
+        <v>58.55</v>
       </c>
       <c r="H146" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-244.5</v>
+        <v>423.9973</v>
       </c>
       <c r="C147" t="n">
-        <v>5.25799386</v>
+        <v>5.22950423</v>
       </c>
       <c r="D147" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="E147" t="n">
+        <v>62</v>
+      </c>
+      <c r="F147" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G147" t="n">
         <v>61.9</v>
       </c>
-      <c r="E147" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="F147" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G147" t="n">
-        <v>60.2</v>
-      </c>
       <c r="H147" t="n">
-        <v>-3.14</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-302.48</v>
+        <v>-119.16</v>
       </c>
       <c r="C148" t="n">
-        <v>5.22774586</v>
+        <v>5.21758823</v>
       </c>
       <c r="D148" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="E148" t="n">
-        <v>61</v>
+        <v>60.75</v>
       </c>
       <c r="F148" t="n">
-        <v>58.6</v>
+        <v>58.75</v>
       </c>
       <c r="G148" t="n">
-        <v>60.45</v>
+        <v>59.1</v>
       </c>
       <c r="H148" t="n">
-        <v>0.42</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-177.8636</v>
+        <v>-301.92</v>
       </c>
       <c r="C149" t="n">
-        <v>5.2099595</v>
+        <v>5.18739623</v>
       </c>
       <c r="D149" t="n">
-        <v>60</v>
+        <v>58.95</v>
       </c>
       <c r="E149" t="n">
-        <v>60.05</v>
+        <v>58.95</v>
       </c>
       <c r="F149" t="n">
-        <v>55.7</v>
+        <v>56.85</v>
       </c>
       <c r="G149" t="n">
-        <v>57.85</v>
+        <v>57.25</v>
       </c>
       <c r="H149" t="n">
-        <v>-4.3</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-228.55</v>
+        <v>112.29</v>
       </c>
       <c r="C150" t="n">
-        <v>5.1871045</v>
+        <v>5.19862523</v>
       </c>
       <c r="D150" t="n">
-        <v>56.95</v>
+        <v>57.1</v>
       </c>
       <c r="E150" t="n">
-        <v>59.1</v>
+        <v>57.6</v>
       </c>
       <c r="F150" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G150" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="H150" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>423.9973</v>
+        <v>-62.4836</v>
       </c>
       <c r="C151" t="n">
-        <v>5.22950423</v>
+        <v>5.19237687</v>
       </c>
       <c r="D151" t="n">
-        <v>57.05</v>
+        <v>55.3</v>
       </c>
       <c r="E151" t="n">
-        <v>62</v>
+        <v>57.9</v>
       </c>
       <c r="F151" t="n">
-        <v>56.55</v>
+        <v>54.95</v>
       </c>
       <c r="G151" t="n">
-        <v>61.9</v>
+        <v>57.35</v>
       </c>
       <c r="H151" t="n">
-        <v>5.72</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-119.16</v>
+        <v>-29.35</v>
       </c>
       <c r="C152" t="n">
-        <v>5.21758823</v>
+        <v>5.18944187</v>
       </c>
       <c r="D152" t="n">
-        <v>60.5</v>
+        <v>56.2</v>
       </c>
       <c r="E152" t="n">
-        <v>60.75</v>
+        <v>57.1</v>
       </c>
       <c r="F152" t="n">
-        <v>58.75</v>
+        <v>55.8</v>
       </c>
       <c r="G152" t="n">
-        <v>59.1</v>
+        <v>55.85</v>
       </c>
       <c r="H152" t="n">
-        <v>-4.52</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-301.92</v>
+        <v>54.46</v>
       </c>
       <c r="C153" t="n">
-        <v>5.18739623</v>
+        <v>5.19488787</v>
       </c>
       <c r="D153" t="n">
-        <v>58.95</v>
+        <v>55.3</v>
       </c>
       <c r="E153" t="n">
-        <v>58.95</v>
+        <v>55.55</v>
       </c>
       <c r="F153" t="n">
-        <v>56.85</v>
+        <v>53.25</v>
       </c>
       <c r="G153" t="n">
-        <v>57.25</v>
+        <v>54.7</v>
       </c>
       <c r="H153" t="n">
-        <v>-3.13</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>112.29</v>
+        <v>17.32</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19862523</v>
+        <v>5.19661987</v>
       </c>
       <c r="D154" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E154" t="n">
-        <v>57.6</v>
+        <v>54.1</v>
       </c>
       <c r="F154" t="n">
-        <v>56.5</v>
+        <v>52.25</v>
       </c>
       <c r="G154" t="n">
-        <v>56.65</v>
+        <v>53.15</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.05</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-62.4836</v>
+        <v>93.42</v>
       </c>
       <c r="C155" t="n">
-        <v>5.19237687</v>
+        <v>5.20596187</v>
       </c>
       <c r="D155" t="n">
-        <v>55.3</v>
+        <v>53.7</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>54.95</v>
+        <v>53.25</v>
       </c>
       <c r="G155" t="n">
-        <v>57.35</v>
+        <v>57</v>
       </c>
       <c r="H155" t="n">
-        <v>1.24</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-29.35</v>
+        <v>64.81</v>
       </c>
       <c r="C156" t="n">
-        <v>5.18944187</v>
+        <v>5.21244287</v>
       </c>
       <c r="D156" t="n">
-        <v>56.2</v>
+        <v>56.6</v>
       </c>
       <c r="E156" t="n">
-        <v>57.1</v>
+        <v>58.05</v>
       </c>
       <c r="F156" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="G156" t="n">
-        <v>55.85</v>
+        <v>56.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.62</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>54.46</v>
+        <v>-172.75</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19488787</v>
+        <v>5.19516787</v>
       </c>
       <c r="D157" t="n">
-        <v>55.3</v>
+        <v>56.85</v>
       </c>
       <c r="E157" t="n">
-        <v>55.55</v>
+        <v>57.2</v>
       </c>
       <c r="F157" t="n">
-        <v>53.25</v>
+        <v>55</v>
       </c>
       <c r="G157" t="n">
-        <v>54.7</v>
+        <v>56</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.06</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>17.32</v>
+        <v>-24.86</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19661987</v>
+        <v>5.19268187</v>
       </c>
       <c r="D158" t="n">
-        <v>54</v>
+        <v>55.75</v>
       </c>
       <c r="E158" t="n">
-        <v>54.1</v>
+        <v>55.8</v>
       </c>
       <c r="F158" t="n">
-        <v>52.25</v>
+        <v>53.7</v>
       </c>
       <c r="G158" t="n">
-        <v>53.15</v>
+        <v>53.9</v>
       </c>
       <c r="H158" t="n">
-        <v>-2.83</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>93.42</v>
+        <v>17.38</v>
       </c>
       <c r="C159" t="n">
-        <v>5.20596187</v>
+        <v>5.19441987</v>
       </c>
       <c r="D159" t="n">
-        <v>53.7</v>
+        <v>53.25</v>
       </c>
       <c r="E159" t="n">
-        <v>57.9</v>
+        <v>53.9</v>
       </c>
       <c r="F159" t="n">
-        <v>53.25</v>
+        <v>51.75</v>
       </c>
       <c r="G159" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H159" t="n">
-        <v>7.24</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>64.81</v>
+        <v>14.06</v>
       </c>
       <c r="C160" t="n">
-        <v>5.21244287</v>
+        <v>5.19582587</v>
       </c>
       <c r="D160" t="n">
-        <v>56.6</v>
+        <v>50.15</v>
       </c>
       <c r="E160" t="n">
-        <v>58.05</v>
+        <v>51.55</v>
       </c>
       <c r="F160" t="n">
-        <v>56.5</v>
+        <v>49.64</v>
       </c>
       <c r="G160" t="n">
-        <v>56.85</v>
+        <v>50.5</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.26</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-172.75</v>
+        <v>-21.2345</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19516787</v>
+        <v>5.19370242</v>
       </c>
       <c r="D161" t="n">
-        <v>56.85</v>
+        <v>50</v>
       </c>
       <c r="E161" t="n">
-        <v>57.2</v>
+        <v>50.8</v>
       </c>
       <c r="F161" t="n">
-        <v>55</v>
+        <v>47.9</v>
       </c>
       <c r="G161" t="n">
-        <v>56</v>
+        <v>48.32</v>
       </c>
       <c r="H161" t="n">
-        <v>-1.5</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-24.86</v>
+        <v>47.7</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19268187</v>
+        <v>5.19847242</v>
       </c>
       <c r="D162" t="n">
-        <v>55.75</v>
+        <v>48.98</v>
       </c>
       <c r="E162" t="n">
-        <v>55.8</v>
+        <v>49.94</v>
       </c>
       <c r="F162" t="n">
-        <v>53.7</v>
+        <v>48.18</v>
       </c>
       <c r="G162" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="H162" t="n">
-        <v>-3.75</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>17.38</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C163" t="n">
-        <v>5.19441987</v>
+        <v>5.20773242</v>
       </c>
       <c r="D163" t="n">
-        <v>53.25</v>
+        <v>49.44</v>
       </c>
       <c r="E163" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="F163" t="n">
-        <v>51.75</v>
+        <v>46.74</v>
       </c>
       <c r="G163" t="n">
-        <v>52</v>
+        <v>47.4</v>
       </c>
       <c r="H163" t="n">
-        <v>-3.53</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>14.06</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19582587</v>
+        <v>5.19818142</v>
       </c>
       <c r="D164" t="n">
-        <v>50.15</v>
+        <v>47</v>
       </c>
       <c r="E164" t="n">
-        <v>51.55</v>
+        <v>47</v>
       </c>
       <c r="F164" t="n">
-        <v>49.64</v>
+        <v>45.86</v>
       </c>
       <c r="G164" t="n">
-        <v>50.5</v>
+        <v>46.28</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.88</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-21.2345</v>
+        <v>-254.06</v>
       </c>
       <c r="C165" t="n">
-        <v>5.19370242</v>
+        <v>5.17277542</v>
       </c>
       <c r="D165" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="E165" t="n">
-        <v>50.8</v>
+        <v>47.18</v>
       </c>
       <c r="F165" t="n">
-        <v>47.9</v>
+        <v>45.76</v>
       </c>
       <c r="G165" t="n">
-        <v>48.32</v>
+        <v>45.9</v>
       </c>
       <c r="H165" t="n">
-        <v>-4.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>47.7</v>
+        <v>-316.19</v>
       </c>
       <c r="C166" t="n">
-        <v>5.19847242</v>
+        <v>5.14115642</v>
       </c>
       <c r="D166" t="n">
-        <v>48.98</v>
+        <v>45.9</v>
       </c>
       <c r="E166" t="n">
-        <v>49.94</v>
+        <v>46.78</v>
       </c>
       <c r="F166" t="n">
-        <v>48.18</v>
+        <v>45.26</v>
       </c>
       <c r="G166" t="n">
-        <v>49.44</v>
+        <v>46.08</v>
       </c>
       <c r="H166" t="n">
-        <v>2.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>92.59999999999999</v>
+        <v>-150.87</v>
       </c>
       <c r="C167" t="n">
-        <v>5.20773242</v>
+        <v>5.12606942</v>
       </c>
       <c r="D167" t="n">
-        <v>49.44</v>
+        <v>47.7</v>
       </c>
       <c r="E167" t="n">
-        <v>49.44</v>
+        <v>48.9</v>
       </c>
       <c r="F167" t="n">
-        <v>46.74</v>
+        <v>46.64</v>
       </c>
       <c r="G167" t="n">
-        <v>47.4</v>
+        <v>46.84</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.13</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-95.51000000000001</v>
+        <v>-236.76</v>
       </c>
       <c r="C168" t="n">
-        <v>5.19818142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D168" t="n">
-        <v>47</v>
+        <v>46.92</v>
       </c>
       <c r="E168" t="n">
-        <v>47</v>
+        <v>48.28</v>
       </c>
       <c r="F168" t="n">
-        <v>45.86</v>
+        <v>46.84</v>
       </c>
       <c r="G168" t="n">
-        <v>46.28</v>
+        <v>47.36</v>
       </c>
       <c r="H168" t="n">
-        <v>-2.36</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-254.06</v>
+        <v>-36.92</v>
       </c>
       <c r="C169" t="n">
-        <v>5.17277542</v>
+        <v>5.09870142</v>
       </c>
       <c r="D169" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E169" t="n">
-        <v>47.18</v>
+        <v>47.56</v>
       </c>
       <c r="F169" t="n">
-        <v>45.76</v>
+        <v>45.72</v>
       </c>
       <c r="G169" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.82</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-316.19</v>
+        <v>64.78</v>
       </c>
       <c r="C170" t="n">
-        <v>5.14115642</v>
+        <v>5.10517942</v>
       </c>
       <c r="D170" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="E170" t="n">
-        <v>46.78</v>
+        <v>48.42</v>
       </c>
       <c r="F170" t="n">
-        <v>45.26</v>
+        <v>46.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.08</v>
+        <v>46.6</v>
       </c>
       <c r="H170" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-150.87</v>
+        <v>-44.41</v>
       </c>
       <c r="C171" t="n">
-        <v>5.12606942</v>
+        <v>5.10073842</v>
       </c>
       <c r="D171" t="n">
-        <v>47.7</v>
+        <v>47.06</v>
       </c>
       <c r="E171" t="n">
-        <v>48.9</v>
+        <v>48.98</v>
       </c>
       <c r="F171" t="n">
-        <v>46.64</v>
+        <v>46.7</v>
       </c>
       <c r="G171" t="n">
-        <v>46.84</v>
+        <v>48.52</v>
       </c>
       <c r="H171" t="n">
-        <v>1.65</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-236.76</v>
+        <v>-124.97</v>
       </c>
       <c r="C172" t="n">
-        <v>5.10239342</v>
+        <v>5.08824142</v>
       </c>
       <c r="D172" t="n">
-        <v>46.92</v>
+        <v>47.6</v>
       </c>
       <c r="E172" t="n">
-        <v>48.28</v>
+        <v>48.08</v>
       </c>
       <c r="F172" t="n">
-        <v>46.84</v>
+        <v>46.72</v>
       </c>
       <c r="G172" t="n">
-        <v>47.36</v>
+        <v>46.76</v>
       </c>
       <c r="H172" t="n">
-        <v>1.11</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-36.92</v>
+        <v>-272.6</v>
       </c>
       <c r="C173" t="n">
-        <v>5.09870142</v>
+        <v>5.06098142</v>
       </c>
       <c r="D173" t="n">
-        <v>47</v>
+        <v>46.76</v>
       </c>
       <c r="E173" t="n">
-        <v>47.56</v>
+        <v>48.3</v>
       </c>
       <c r="F173" t="n">
-        <v>45.72</v>
+        <v>46.02</v>
       </c>
       <c r="G173" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="H173" t="n">
-        <v>-2.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>64.78</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C174" t="n">
-        <v>5.10517942</v>
+        <v>5.06933542</v>
       </c>
       <c r="D174" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="E174" t="n">
-        <v>48.42</v>
+        <v>47.92</v>
       </c>
       <c r="F174" t="n">
-        <v>46.26</v>
+        <v>46.46</v>
       </c>
       <c r="G174" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="H174" t="n">
-        <v>0.73</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-44.41</v>
+        <v>-232.94</v>
       </c>
       <c r="C175" t="n">
-        <v>5.10073842</v>
+        <v>5.04604142</v>
       </c>
       <c r="D175" t="n">
-        <v>47.06</v>
+        <v>47.2</v>
       </c>
       <c r="E175" t="n">
-        <v>48.98</v>
+        <v>48.84</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.52</v>
+        <v>48.56</v>
       </c>
       <c r="H175" t="n">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-124.97</v>
+        <v>-101.2265</v>
       </c>
       <c r="C176" t="n">
-        <v>5.08824142</v>
+        <v>5.03591877</v>
       </c>
       <c r="D176" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="E176" t="n">
-        <v>48.08</v>
+        <v>49.46</v>
       </c>
       <c r="F176" t="n">
-        <v>46.72</v>
+        <v>48.24</v>
       </c>
       <c r="G176" t="n">
-        <v>46.76</v>
+        <v>48.78</v>
       </c>
       <c r="H176" t="n">
-        <v>-3.63</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-272.6</v>
+        <v>-146.01</v>
       </c>
       <c r="C177" t="n">
-        <v>5.06098142</v>
+        <v>5.02131777</v>
       </c>
       <c r="D177" t="n">
-        <v>46.76</v>
+        <v>49.22</v>
       </c>
       <c r="E177" t="n">
-        <v>48.3</v>
+        <v>51</v>
       </c>
       <c r="F177" t="n">
-        <v>46.02</v>
+        <v>49.22</v>
       </c>
       <c r="G177" t="n">
-        <v>47.42</v>
+        <v>50.4</v>
       </c>
       <c r="H177" t="n">
-        <v>1.41</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>83.54000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C178" t="n">
-        <v>5.06933542</v>
+        <v>5.02274277</v>
       </c>
       <c r="D178" t="n">
-        <v>47.42</v>
+        <v>50.55</v>
       </c>
       <c r="E178" t="n">
-        <v>47.92</v>
+        <v>51</v>
       </c>
       <c r="F178" t="n">
-        <v>46.46</v>
+        <v>48.2</v>
       </c>
       <c r="G178" t="n">
-        <v>47.2</v>
+        <v>48.94</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.46</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-232.94</v>
+        <v>7.54</v>
       </c>
       <c r="C179" t="n">
-        <v>5.04604142</v>
+        <v>5.02349677</v>
       </c>
       <c r="D179" t="n">
-        <v>47.2</v>
+        <v>49.96</v>
       </c>
       <c r="E179" t="n">
-        <v>48.84</v>
+        <v>49.98</v>
       </c>
       <c r="F179" t="n">
-        <v>46.7</v>
+        <v>48.72</v>
       </c>
       <c r="G179" t="n">
-        <v>48.56</v>
+        <v>49.12</v>
       </c>
       <c r="H179" t="n">
-        <v>2.88</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-101.2265</v>
+        <v>29.93</v>
       </c>
       <c r="C180" t="n">
-        <v>5.03591877</v>
+        <v>5.02648977</v>
       </c>
       <c r="D180" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="E180" t="n">
-        <v>49.46</v>
+        <v>49.36</v>
       </c>
       <c r="F180" t="n">
-        <v>48.24</v>
+        <v>48.18</v>
       </c>
       <c r="G180" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="H180" t="n">
-        <v>0.45</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-146.01</v>
+        <v>-93.37</v>
       </c>
       <c r="C181" t="n">
-        <v>5.02131777</v>
+        <v>5.01715277</v>
       </c>
       <c r="D181" t="n">
-        <v>49.22</v>
+        <v>48.4</v>
       </c>
       <c r="E181" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
       <c r="F181" t="n">
-        <v>49.22</v>
+        <v>47.2</v>
       </c>
       <c r="G181" t="n">
-        <v>50.4</v>
+        <v>47.64</v>
       </c>
       <c r="H181" t="n">
-        <v>3.32</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>14.25</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C182" t="n">
-        <v>5.02274277</v>
+        <v>5.00778777</v>
       </c>
       <c r="D182" t="n">
-        <v>50.55</v>
+        <v>47.64</v>
       </c>
       <c r="E182" t="n">
-        <v>51</v>
+        <v>49.3</v>
       </c>
       <c r="F182" t="n">
-        <v>48.2</v>
+        <v>47.22</v>
       </c>
       <c r="G182" t="n">
-        <v>48.94</v>
+        <v>48.96</v>
       </c>
       <c r="H182" t="n">
-        <v>-2.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7.54</v>
+        <v>28.06</v>
       </c>
       <c r="C183" t="n">
-        <v>5.02349677</v>
+        <v>5.01059377</v>
       </c>
       <c r="D183" t="n">
-        <v>49.96</v>
+        <v>48.36</v>
       </c>
       <c r="E183" t="n">
-        <v>49.98</v>
+        <v>48.76</v>
       </c>
       <c r="F183" t="n">
-        <v>48.72</v>
+        <v>47.52</v>
       </c>
       <c r="G183" t="n">
-        <v>49.12</v>
+        <v>47.98</v>
       </c>
       <c r="H183" t="n">
-        <v>0.37</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>29.93</v>
+        <v>-160.94</v>
       </c>
       <c r="C184" t="n">
-        <v>5.02648977</v>
+        <v>4.99449977</v>
       </c>
       <c r="D184" t="n">
-        <v>49.1</v>
+        <v>47.98</v>
       </c>
       <c r="E184" t="n">
-        <v>49.36</v>
+        <v>48.46</v>
       </c>
       <c r="F184" t="n">
-        <v>48.18</v>
+        <v>47.32</v>
       </c>
       <c r="G184" t="n">
-        <v>48.64</v>
+        <v>48.08</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.98</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-93.37</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C185" t="n">
-        <v>5.01715277</v>
+        <v>5.00218477</v>
       </c>
       <c r="D185" t="n">
-        <v>48.4</v>
+        <v>49.54</v>
       </c>
       <c r="E185" t="n">
-        <v>48.4</v>
+        <v>50.5</v>
       </c>
       <c r="F185" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="G185" t="n">
-        <v>47.64</v>
+        <v>49.68</v>
       </c>
       <c r="H185" t="n">
-        <v>-2.06</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-93.65000000000001</v>
+        <v>-70.88</v>
       </c>
       <c r="C186" t="n">
-        <v>5.00778777</v>
+        <v>4.99509677</v>
       </c>
       <c r="D186" t="n">
-        <v>47.64</v>
+        <v>51.9</v>
       </c>
       <c r="E186" t="n">
-        <v>49.3</v>
+        <v>55.6</v>
       </c>
       <c r="F186" t="n">
-        <v>47.22</v>
+        <v>51.9</v>
       </c>
       <c r="G186" t="n">
-        <v>48.96</v>
+        <v>54.6</v>
       </c>
       <c r="H186" t="n">
-        <v>2.77</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>28.06</v>
+        <v>-223.97</v>
       </c>
       <c r="C187" t="n">
-        <v>5.01059377</v>
+        <v>4.97269977</v>
       </c>
       <c r="D187" t="n">
-        <v>48.36</v>
+        <v>54.7</v>
       </c>
       <c r="E187" t="n">
-        <v>48.76</v>
+        <v>56.1</v>
       </c>
       <c r="F187" t="n">
-        <v>47.52</v>
+        <v>53.7</v>
       </c>
       <c r="G187" t="n">
-        <v>47.98</v>
+        <v>54.25</v>
       </c>
       <c r="H187" t="n">
-        <v>-2</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-160.94</v>
+        <v>-908.88</v>
       </c>
       <c r="C188" t="n">
-        <v>4.99449977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D188" t="n">
-        <v>47.98</v>
+        <v>52.85</v>
       </c>
       <c r="E188" t="n">
-        <v>48.46</v>
+        <v>53.8</v>
       </c>
       <c r="F188" t="n">
-        <v>47.32</v>
+        <v>51.3</v>
       </c>
       <c r="G188" t="n">
-        <v>48.08</v>
+        <v>53.4</v>
       </c>
       <c r="H188" t="n">
-        <v>0.21</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>76.84999999999999</v>
+        <v>-219</v>
       </c>
       <c r="C189" t="n">
-        <v>5.00218477</v>
+        <v>4.85991177</v>
       </c>
       <c r="D189" t="n">
-        <v>49.54</v>
+        <v>52.75</v>
       </c>
       <c r="E189" t="n">
-        <v>50.5</v>
+        <v>54.45</v>
       </c>
       <c r="F189" t="n">
-        <v>48.9</v>
+        <v>51.45</v>
       </c>
       <c r="G189" t="n">
-        <v>49.68</v>
+        <v>51.85</v>
       </c>
       <c r="H189" t="n">
-        <v>3.33</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>-70.88</v>
+        <v>81.19</v>
       </c>
       <c r="C190" t="n">
-        <v>4.99509677</v>
+        <v>4.86803077</v>
       </c>
       <c r="D190" t="n">
-        <v>51.9</v>
+        <v>51.85</v>
       </c>
       <c r="E190" t="n">
-        <v>55.6</v>
+        <v>51.85</v>
       </c>
       <c r="F190" t="n">
-        <v>51.9</v>
+        <v>49.6</v>
       </c>
       <c r="G190" t="n">
-        <v>54.6</v>
+        <v>50.45</v>
       </c>
       <c r="H190" t="n">
-        <v>9.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-223.97</v>
+        <v>7.21</v>
       </c>
       <c r="C191" t="n">
-        <v>4.97269977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D191" t="n">
-        <v>54.7</v>
+        <v>50.05</v>
       </c>
       <c r="E191" t="n">
-        <v>56.1</v>
+        <v>50.8</v>
       </c>
       <c r="F191" t="n">
-        <v>53.7</v>
+        <v>49.52</v>
       </c>
       <c r="G191" t="n">
-        <v>54.25</v>
+        <v>50.65</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.64</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-908.88</v>
+        <v>144.28</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88181177</v>
+        <v>4.88317977</v>
       </c>
       <c r="D192" t="n">
-        <v>52.85</v>
+        <v>50</v>
       </c>
       <c r="E192" t="n">
-        <v>53.8</v>
+        <v>50.6</v>
       </c>
       <c r="F192" t="n">
-        <v>51.3</v>
+        <v>49.08</v>
       </c>
       <c r="G192" t="n">
-        <v>53.4</v>
+        <v>49.12</v>
       </c>
       <c r="H192" t="n">
-        <v>-1.57</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-219</v>
+        <v>-41.02</v>
       </c>
       <c r="C193" t="n">
-        <v>4.85991177</v>
+        <v>4.87907777</v>
       </c>
       <c r="D193" t="n">
-        <v>52.75</v>
+        <v>49.18</v>
       </c>
       <c r="E193" t="n">
-        <v>54.45</v>
+        <v>50.1</v>
       </c>
       <c r="F193" t="n">
-        <v>51.45</v>
+        <v>48.82</v>
       </c>
       <c r="G193" t="n">
-        <v>51.85</v>
+        <v>49.92</v>
       </c>
       <c r="H193" t="n">
-        <v>-2.9</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>81.19</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C194" t="n">
-        <v>4.86803077</v>
+        <v>4.88594877</v>
       </c>
       <c r="D194" t="n">
-        <v>51.85</v>
+        <v>50.5</v>
       </c>
       <c r="E194" t="n">
-        <v>51.85</v>
+        <v>50.95</v>
       </c>
       <c r="F194" t="n">
-        <v>49.6</v>
+        <v>49.74</v>
       </c>
       <c r="G194" t="n">
-        <v>50.45</v>
+        <v>50.1</v>
       </c>
       <c r="H194" t="n">
-        <v>-2.7</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.21</v>
+        <v>20.01</v>
       </c>
       <c r="C195" t="n">
-        <v>4.86875177</v>
+        <v>4.88794977</v>
       </c>
       <c r="D195" t="n">
-        <v>50.05</v>
+        <v>50</v>
       </c>
       <c r="E195" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="F195" t="n">
-        <v>49.52</v>
+        <v>49.04</v>
       </c>
       <c r="G195" t="n">
-        <v>50.65</v>
+        <v>49.06</v>
       </c>
       <c r="H195" t="n">
-        <v>0.4</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>144.28</v>
+        <v>-18.77</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88317977</v>
+        <v>4.88607277</v>
       </c>
       <c r="D196" t="n">
-        <v>50</v>
+        <v>49.08</v>
       </c>
       <c r="E196" t="n">
-        <v>50.6</v>
+        <v>49.78</v>
       </c>
       <c r="F196" t="n">
-        <v>49.08</v>
+        <v>48.7</v>
       </c>
       <c r="G196" t="n">
-        <v>49.12</v>
+        <v>49.4</v>
       </c>
       <c r="H196" t="n">
-        <v>-3.02</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-41.02</v>
+        <v>95.14</v>
       </c>
       <c r="C197" t="n">
-        <v>4.87907777</v>
+        <v>4.89558677</v>
       </c>
       <c r="D197" t="n">
-        <v>49.18</v>
+        <v>48.66</v>
       </c>
       <c r="E197" t="n">
-        <v>50.1</v>
+        <v>49.22</v>
       </c>
       <c r="F197" t="n">
-        <v>48.82</v>
+        <v>48.02</v>
       </c>
       <c r="G197" t="n">
-        <v>49.92</v>
+        <v>48.22</v>
       </c>
       <c r="H197" t="n">
-        <v>1.63</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>68.70999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="C198" t="n">
-        <v>4.88594877</v>
+        <v>4.89623377</v>
       </c>
       <c r="D198" t="n">
-        <v>50.5</v>
+        <v>48.22</v>
       </c>
       <c r="E198" t="n">
-        <v>50.95</v>
+        <v>48.22</v>
       </c>
       <c r="F198" t="n">
-        <v>49.74</v>
+        <v>47.46</v>
       </c>
       <c r="G198" t="n">
-        <v>50.1</v>
+        <v>47.46</v>
       </c>
       <c r="H198" t="n">
-        <v>0.36</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>20.01</v>
+        <v>78.34</v>
       </c>
       <c r="C199" t="n">
-        <v>4.88794977</v>
+        <v>4.90406777</v>
       </c>
       <c r="D199" t="n">
-        <v>50</v>
+        <v>47.86</v>
       </c>
       <c r="E199" t="n">
-        <v>50.5</v>
+        <v>48.68</v>
       </c>
       <c r="F199" t="n">
-        <v>49.04</v>
+        <v>47.7</v>
       </c>
       <c r="G199" t="n">
-        <v>49.06</v>
+        <v>48.48</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-18.77</v>
+        <v>12.2</v>
       </c>
       <c r="C200" t="n">
-        <v>4.88607277</v>
+        <v>4.90528777</v>
       </c>
       <c r="D200" t="n">
-        <v>49.08</v>
+        <v>48.1</v>
       </c>
       <c r="E200" t="n">
-        <v>49.78</v>
+        <v>48.7</v>
       </c>
       <c r="F200" t="n">
-        <v>48.7</v>
+        <v>47.38</v>
       </c>
       <c r="G200" t="n">
-        <v>49.4</v>
+        <v>47.88</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>95.14</v>
+        <v>-50.42</v>
       </c>
       <c r="C201" t="n">
-        <v>4.89558677</v>
+        <v>4.90024577</v>
       </c>
       <c r="D201" t="n">
-        <v>48.66</v>
+        <v>47.34</v>
       </c>
       <c r="E201" t="n">
-        <v>49.22</v>
+        <v>48.28</v>
       </c>
       <c r="F201" t="n">
-        <v>48.02</v>
+        <v>47.06</v>
       </c>
       <c r="G201" t="n">
-        <v>48.22</v>
+        <v>47.9</v>
       </c>
       <c r="H201" t="n">
-        <v>-2.39</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>6.47</v>
+        <v>7.38</v>
       </c>
       <c r="C202" t="n">
-        <v>4.89623377</v>
+        <v>4.90098377</v>
       </c>
       <c r="D202" t="n">
-        <v>48.22</v>
+        <v>49.98</v>
       </c>
       <c r="E202" t="n">
-        <v>48.22</v>
+        <v>51.2</v>
       </c>
       <c r="F202" t="n">
-        <v>47.46</v>
+        <v>49.76</v>
       </c>
       <c r="G202" t="n">
-        <v>47.46</v>
+        <v>50.55</v>
       </c>
       <c r="H202" t="n">
-        <v>-1.58</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>78.34</v>
+        <v>0.19</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90406777</v>
+        <v>4.90100277</v>
       </c>
       <c r="D203" t="n">
-        <v>47.86</v>
+        <v>50.55</v>
       </c>
       <c r="E203" t="n">
-        <v>48.68</v>
+        <v>51.8</v>
       </c>
       <c r="F203" t="n">
-        <v>47.7</v>
+        <v>50.5</v>
       </c>
       <c r="G203" t="n">
-        <v>48.48</v>
+        <v>51.2</v>
       </c>
       <c r="H203" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12.2</v>
+        <v>-404.07</v>
       </c>
       <c r="C204" t="n">
-        <v>4.90528777</v>
+        <v>4.86059577</v>
       </c>
       <c r="D204" t="n">
-        <v>48.1</v>
+        <v>50.3</v>
       </c>
       <c r="E204" t="n">
-        <v>48.7</v>
+        <v>51</v>
       </c>
       <c r="F204" t="n">
-        <v>47.38</v>
+        <v>49.3</v>
       </c>
       <c r="G204" t="n">
-        <v>47.88</v>
+        <v>49.46</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.24</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-50.42</v>
+        <v>-104.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.90024577</v>
+        <v>4.85015377</v>
       </c>
       <c r="D205" t="n">
-        <v>47.34</v>
+        <v>48.86</v>
       </c>
       <c r="E205" t="n">
-        <v>48.28</v>
+        <v>49.74</v>
       </c>
       <c r="F205" t="n">
-        <v>47.06</v>
+        <v>47.6</v>
       </c>
       <c r="G205" t="n">
-        <v>47.9</v>
+        <v>47.68</v>
       </c>
       <c r="H205" t="n">
-        <v>0.04</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7.38</v>
+        <v>-9.27</v>
       </c>
       <c r="C206" t="n">
-        <v>4.90098377</v>
+        <v>4.84922677</v>
       </c>
       <c r="D206" t="n">
-        <v>49.98</v>
+        <v>47.68</v>
       </c>
       <c r="E206" t="n">
-        <v>51.2</v>
+        <v>48.9</v>
       </c>
       <c r="F206" t="n">
-        <v>49.76</v>
+        <v>47.32</v>
       </c>
       <c r="G206" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="H206" t="n">
-        <v>5.53</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.19</v>
+        <v>-62.41</v>
       </c>
       <c r="C207" t="n">
-        <v>4.90100277</v>
+        <v>4.84298577</v>
       </c>
       <c r="D207" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="E207" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F207" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="G207" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="H207" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-404.07</v>
+        <v>-4.06</v>
       </c>
       <c r="C208" t="n">
-        <v>4.86059577</v>
+        <v>4.84257977</v>
       </c>
       <c r="D208" t="n">
-        <v>50.3</v>
+        <v>47.8</v>
       </c>
       <c r="E208" t="n">
-        <v>51</v>
+        <v>48.6</v>
       </c>
       <c r="F208" t="n">
-        <v>49.3</v>
+        <v>47.16</v>
       </c>
       <c r="G208" t="n">
-        <v>49.46</v>
+        <v>47.98</v>
       </c>
       <c r="H208" t="n">
-        <v>-3.4</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-104.42</v>
+        <v>107.65</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85015377</v>
+        <v>4.85334477</v>
       </c>
       <c r="D209" t="n">
-        <v>48.86</v>
+        <v>47.86</v>
       </c>
       <c r="E209" t="n">
-        <v>49.74</v>
+        <v>48.44</v>
       </c>
       <c r="F209" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="G209" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="H209" t="n">
-        <v>-3.6</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-9.27</v>
+        <v>137.46</v>
       </c>
       <c r="C210" t="n">
-        <v>4.84922677</v>
+        <v>4.86709077</v>
       </c>
       <c r="D210" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="E210" t="n">
-        <v>48.9</v>
+        <v>48.22</v>
       </c>
       <c r="F210" t="n">
-        <v>47.32</v>
+        <v>46.6</v>
       </c>
       <c r="G210" t="n">
-        <v>48.1</v>
+        <v>47.06</v>
       </c>
       <c r="H210" t="n">
-        <v>0.88</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-62.41</v>
+        <v>154.04</v>
       </c>
       <c r="C211" t="n">
-        <v>4.84298577</v>
+        <v>4.88249477</v>
       </c>
       <c r="D211" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="E211" t="n">
-        <v>49</v>
+        <v>46.76</v>
       </c>
       <c r="F211" t="n">
-        <v>47.5</v>
+        <v>44.56</v>
       </c>
       <c r="G211" t="n">
-        <v>48.6</v>
+        <v>45.86</v>
       </c>
       <c r="H211" t="n">
-        <v>1.04</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-4.06</v>
+        <v>78.03</v>
       </c>
       <c r="C212" t="n">
-        <v>4.84257977</v>
+        <v>4.89029777</v>
       </c>
       <c r="D212" t="n">
-        <v>47.8</v>
+        <v>46.56</v>
       </c>
       <c r="E212" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="F212" t="n">
-        <v>47.16</v>
+        <v>46.2</v>
       </c>
       <c r="G212" t="n">
-        <v>47.98</v>
+        <v>46.38</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.28</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>107.65</v>
+        <v>401.67</v>
       </c>
       <c r="C213" t="n">
-        <v>4.85334477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.86</v>
+        <v>47.28</v>
       </c>
       <c r="E213" t="n">
-        <v>48.44</v>
+        <v>48.88</v>
       </c>
       <c r="F213" t="n">
-        <v>46.5</v>
+        <v>47.12</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.33</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>137.46</v>
+        <v>-79.33</v>
       </c>
       <c r="C214" t="n">
-        <v>4.86709077</v>
+        <v>4.92253177</v>
       </c>
       <c r="D214" t="n">
-        <v>47.82</v>
+        <v>48.1</v>
       </c>
       <c r="E214" t="n">
-        <v>48.22</v>
+        <v>50.45</v>
       </c>
       <c r="F214" t="n">
-        <v>46.6</v>
+        <v>48.04</v>
       </c>
       <c r="G214" t="n">
-        <v>47.06</v>
+        <v>50.4</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.59</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>154.04</v>
+        <v>-415.48</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88249477</v>
+        <v>4.88098377</v>
       </c>
       <c r="D215" t="n">
-        <v>46.68</v>
+        <v>49.44</v>
       </c>
       <c r="E215" t="n">
-        <v>46.76</v>
+        <v>50.15</v>
       </c>
       <c r="F215" t="n">
-        <v>44.56</v>
+        <v>48.88</v>
       </c>
       <c r="G215" t="n">
-        <v>45.86</v>
+        <v>49.32</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>78.03</v>
+        <v>-394.96</v>
       </c>
       <c r="C216" t="n">
-        <v>4.89029777</v>
+        <v>4.84148777</v>
       </c>
       <c r="D216" t="n">
-        <v>46.56</v>
+        <v>49.08</v>
       </c>
       <c r="E216" t="n">
-        <v>48</v>
+        <v>49.08</v>
       </c>
       <c r="F216" t="n">
-        <v>46.2</v>
+        <v>47.2</v>
       </c>
       <c r="G216" t="n">
-        <v>46.38</v>
+        <v>47.62</v>
       </c>
       <c r="H216" t="n">
-        <v>1.13</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>401.67</v>
+        <v>-39.23</v>
       </c>
       <c r="C217" t="n">
-        <v>4.93046477</v>
+        <v>4.83756477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.28</v>
+        <v>47.2</v>
       </c>
       <c r="E217" t="n">
-        <v>48.88</v>
+        <v>47.2</v>
       </c>
       <c r="F217" t="n">
-        <v>47.12</v>
+        <v>46.42</v>
       </c>
       <c r="G217" t="n">
-        <v>47.82</v>
+        <v>46.48</v>
       </c>
       <c r="H217" t="n">
-        <v>3.1</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-79.33</v>
+        <v>219.67</v>
       </c>
       <c r="C218" t="n">
-        <v>4.92253177</v>
+        <v>4.85953177</v>
       </c>
       <c r="D218" t="n">
-        <v>48.1</v>
+        <v>45.74</v>
       </c>
       <c r="E218" t="n">
-        <v>50.45</v>
+        <v>46.44</v>
       </c>
       <c r="F218" t="n">
-        <v>48.04</v>
+        <v>45.38</v>
       </c>
       <c r="G218" t="n">
-        <v>50.4</v>
+        <v>46.34</v>
       </c>
       <c r="H218" t="n">
-        <v>5.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-415.48</v>
+        <v>111.68</v>
       </c>
       <c r="C219" t="n">
-        <v>4.88098377</v>
+        <v>4.87069977</v>
       </c>
       <c r="D219" t="n">
-        <v>49.44</v>
+        <v>45.9</v>
       </c>
       <c r="E219" t="n">
-        <v>50.15</v>
+        <v>47.8</v>
       </c>
       <c r="F219" t="n">
-        <v>48.88</v>
+        <v>45.84</v>
       </c>
       <c r="G219" t="n">
-        <v>49.32</v>
+        <v>47.52</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.14</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>-394.96</v>
+        <v>47.5</v>
       </c>
       <c r="C220" t="n">
-        <v>4.84148777</v>
+        <v>4.87544977</v>
       </c>
       <c r="D220" t="n">
-        <v>49.08</v>
+        <v>47.52</v>
       </c>
       <c r="E220" t="n">
-        <v>49.08</v>
+        <v>48.06</v>
       </c>
       <c r="F220" t="n">
-        <v>47.2</v>
+        <v>46.06</v>
       </c>
       <c r="G220" t="n">
-        <v>47.62</v>
+        <v>46.12</v>
       </c>
       <c r="H220" t="n">
-        <v>-3.45</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-39.23</v>
+        <v>-30.32</v>
       </c>
       <c r="C221" t="n">
-        <v>4.83756477</v>
+        <v>4.87241777</v>
       </c>
       <c r="D221" t="n">
-        <v>47.2</v>
+        <v>46.92</v>
       </c>
       <c r="E221" t="n">
-        <v>47.2</v>
+        <v>47.42</v>
       </c>
       <c r="F221" t="n">
-        <v>46.42</v>
+        <v>45.94</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>-2.39</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>219.67</v>
+        <v>15.46</v>
       </c>
       <c r="C222" t="n">
-        <v>4.85953177</v>
+        <v>4.87396377</v>
       </c>
       <c r="D222" t="n">
-        <v>45.74</v>
+        <v>46.9</v>
       </c>
       <c r="E222" t="n">
-        <v>46.44</v>
+        <v>47.5</v>
       </c>
       <c r="F222" t="n">
-        <v>45.38</v>
+        <v>44.94</v>
       </c>
       <c r="G222" t="n">
-        <v>46.34</v>
+        <v>46.88</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.3</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>111.68</v>
+        <v>57.59</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87069977</v>
+        <v>4.87972277</v>
       </c>
       <c r="D223" t="n">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
       <c r="E223" t="n">
-        <v>47.8</v>
+        <v>48.46</v>
       </c>
       <c r="F223" t="n">
-        <v>45.84</v>
+        <v>46.8</v>
       </c>
       <c r="G223" t="n">
-        <v>47.52</v>
+        <v>47.56</v>
       </c>
       <c r="H223" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>47.5</v>
+        <v>112.19</v>
       </c>
       <c r="C224" t="n">
-        <v>4.87544977</v>
+        <v>4.89094177</v>
       </c>
       <c r="D224" t="n">
-        <v>47.52</v>
+        <v>47.54</v>
       </c>
       <c r="E224" t="n">
-        <v>48.06</v>
+        <v>47.54</v>
       </c>
       <c r="F224" t="n">
-        <v>46.06</v>
+        <v>44.82</v>
       </c>
       <c r="G224" t="n">
-        <v>46.12</v>
+        <v>45.48</v>
       </c>
       <c r="H224" t="n">
-        <v>-2.95</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-30.32</v>
+        <v>-42.06</v>
       </c>
       <c r="C225" t="n">
-        <v>4.87241777</v>
+        <v>4.88673577</v>
       </c>
       <c r="D225" t="n">
-        <v>46.92</v>
+        <v>45</v>
       </c>
       <c r="E225" t="n">
-        <v>47.42</v>
+        <v>45.8</v>
       </c>
       <c r="F225" t="n">
-        <v>45.94</v>
+        <v>44.68</v>
       </c>
       <c r="G225" t="n">
-        <v>46.48</v>
+        <v>45.08</v>
       </c>
       <c r="H225" t="n">
-        <v>0.78</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>15.46</v>
+        <v>201.66</v>
       </c>
       <c r="C226" t="n">
-        <v>4.87396377</v>
+        <v>4.90690177</v>
       </c>
       <c r="D226" t="n">
-        <v>46.9</v>
+        <v>45.72</v>
       </c>
       <c r="E226" t="n">
-        <v>47.5</v>
+        <v>46.54</v>
       </c>
       <c r="F226" t="n">
-        <v>44.94</v>
+        <v>45.34</v>
       </c>
       <c r="G226" t="n">
-        <v>46.88</v>
+        <v>46.24</v>
       </c>
       <c r="H226" t="n">
-        <v>0.86</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>57.59</v>
+        <v>138.5</v>
       </c>
       <c r="C227" t="n">
-        <v>4.87972277</v>
+        <v>4.92075177</v>
       </c>
       <c r="D227" t="n">
-        <v>46.9</v>
+        <v>45.48</v>
       </c>
       <c r="E227" t="n">
-        <v>48.46</v>
+        <v>47.3</v>
       </c>
       <c r="F227" t="n">
-        <v>46.8</v>
+        <v>45.48</v>
       </c>
       <c r="G227" t="n">
-        <v>47.56</v>
+        <v>46.76</v>
       </c>
       <c r="H227" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>112.19</v>
+        <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>4.89094177</v>
+        <v>4.92075177</v>
       </c>
       <c r="D228" t="n">
-        <v>47.54</v>
+        <v>46.76</v>
       </c>
       <c r="E228" t="n">
-        <v>47.54</v>
+        <v>46.76</v>
       </c>
       <c r="F228" t="n">
-        <v>44.82</v>
+        <v>44.9</v>
       </c>
       <c r="G228" t="n">
-        <v>45.48</v>
+        <v>45.24</v>
       </c>
       <c r="H228" t="n">
-        <v>-4.37</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-42.06</v>
+        <v>-223.74</v>
       </c>
       <c r="C229" t="n">
-        <v>4.88673577</v>
+        <v>4.89837777</v>
       </c>
       <c r="D229" t="n">
-        <v>45</v>
+        <v>45.38</v>
       </c>
       <c r="E229" t="n">
-        <v>45.8</v>
+        <v>46.84</v>
       </c>
       <c r="F229" t="n">
-        <v>44.68</v>
+        <v>45.36</v>
       </c>
       <c r="G229" t="n">
-        <v>45.08</v>
+        <v>45.74</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>201.66</v>
-      </c>
-      <c r="C230" t="n">
-        <v>4.90690177</v>
-      </c>
-      <c r="D230" t="n">
-        <v>45.72</v>
-      </c>
-      <c r="E230" t="n">
-        <v>46.54</v>
-      </c>
-      <c r="F230" t="n">
-        <v>45.34</v>
-      </c>
-      <c r="G230" t="n">
-        <v>46.24</v>
-      </c>
-      <c r="H230" t="n">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="C231" t="n">
-        <v>4.92075177</v>
-      </c>
-      <c r="D231" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="E231" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="F231" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="G231" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="H231" t="n">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
-      <c r="C232" t="n">
-        <v>4.92075177</v>
-      </c>
-      <c r="D232" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="E232" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="F232" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="G232" t="n">
-        <v>45.24</v>
-      </c>
-      <c r="H232" t="n">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>0</v>
-      </c>
-      <c r="C233" t="n">
-        <v>4.92075177</v>
-      </c>
-      <c r="D233" t="n">
-        <v>45.38</v>
-      </c>
-      <c r="E233" t="n">
-        <v>46.84</v>
-      </c>
-      <c r="F233" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="G233" t="n">
-        <v>45.74</v>
-      </c>
-      <c r="H233" t="n">
         <v>1.11</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6852,6 +6852,34 @@
         <v>1.11</v>
       </c>
     </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4.89837777</v>
+      </c>
+      <c r="D230" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="E230" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="F230" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="G230" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="H230" t="n">
+        <v>-2.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -6874,10 +6874,10 @@
         <v>44.3</v>
       </c>
       <c r="G230" t="n">
-        <v>44.74</v>
+        <v>44.54</v>
       </c>
       <c r="H230" t="n">
-        <v>-2.19</v>
+        <v>-2.62</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>71.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="E79" t="n">
-        <v>72.25</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>69.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="G79" t="n">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H79" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E80" t="n">
-        <v>71.75</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F80" t="n">
-        <v>69.55</v>
+        <v>71.5</v>
       </c>
       <c r="G80" t="n">
-        <v>70.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4190 +2693,4302 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>70.3</v>
+        <v>72.8</v>
       </c>
       <c r="E81" t="n">
-        <v>73.3</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="F81" t="n">
-        <v>70.3</v>
+        <v>71.5</v>
       </c>
       <c r="G81" t="n">
-        <v>72.84999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="H81" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>-37.37</v>
+        <v>0</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D82" t="n">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E82" t="n">
-        <v>73.5</v>
+        <v>72.25</v>
       </c>
       <c r="F82" t="n">
-        <v>71.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G82" t="n">
-        <v>71.75</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>-1.51</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29380881</v>
+        <v>5.29754581</v>
       </c>
       <c r="D83" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>73.15000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="F83" t="n">
-        <v>70.5</v>
+        <v>69.55</v>
       </c>
       <c r="G83" t="n">
-        <v>71.84999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>0.14</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>39.15</v>
+        <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29772381</v>
+        <v>5.29754581</v>
       </c>
       <c r="D84" t="n">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="E84" t="n">
-        <v>71.8</v>
+        <v>73.3</v>
       </c>
       <c r="F84" t="n">
-        <v>68.55</v>
+        <v>70.3</v>
       </c>
       <c r="G84" t="n">
-        <v>68.65000000000001</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H84" t="n">
-        <v>-4.45</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-32.03</v>
+        <v>-37.37</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29452081</v>
+        <v>5.29380881</v>
       </c>
       <c r="D85" t="n">
-        <v>69.5</v>
+        <v>71.8</v>
       </c>
       <c r="E85" t="n">
-        <v>69.5</v>
+        <v>73.5</v>
       </c>
       <c r="F85" t="n">
-        <v>68.15000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G85" t="n">
-        <v>68.75</v>
+        <v>71.75</v>
       </c>
       <c r="H85" t="n">
-        <v>0.15</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>-245.51</v>
+        <v>0</v>
       </c>
       <c r="C86" t="n">
-        <v>5.26996981</v>
+        <v>5.29380881</v>
       </c>
       <c r="D86" t="n">
-        <v>67.75</v>
+        <v>72.8</v>
       </c>
       <c r="E86" t="n">
-        <v>70.15000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>67</v>
+        <v>70.5</v>
       </c>
       <c r="G86" t="n">
-        <v>68</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>-1.09</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>24.99</v>
+        <v>39.15</v>
       </c>
       <c r="C87" t="n">
-        <v>5.27246881</v>
+        <v>5.29772381</v>
       </c>
       <c r="D87" t="n">
-        <v>68.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="E87" t="n">
-        <v>69</v>
+        <v>71.8</v>
       </c>
       <c r="F87" t="n">
-        <v>65.65000000000001</v>
+        <v>68.55</v>
       </c>
       <c r="G87" t="n">
-        <v>66.55</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H87" t="n">
-        <v>-2.13</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-70.5937</v>
+        <v>-32.03</v>
       </c>
       <c r="C88" t="n">
-        <v>5.26540944</v>
+        <v>5.29452081</v>
       </c>
       <c r="D88" t="n">
-        <v>65.84999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E88" t="n">
-        <v>66.8</v>
+        <v>69.5</v>
       </c>
       <c r="F88" t="n">
-        <v>64.45</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>65.84999999999999</v>
+        <v>68.75</v>
       </c>
       <c r="H88" t="n">
-        <v>-1.05</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-83.42</v>
+        <v>-245.51</v>
       </c>
       <c r="C89" t="n">
-        <v>5.25706744</v>
+        <v>5.26996981</v>
       </c>
       <c r="D89" t="n">
-        <v>66.90000000000001</v>
+        <v>67.75</v>
       </c>
       <c r="E89" t="n">
+        <v>70.15000000000001</v>
+      </c>
+      <c r="F89" t="n">
+        <v>67</v>
+      </c>
+      <c r="G89" t="n">
         <v>68</v>
       </c>
-      <c r="F89" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="G89" t="n">
-        <v>65.59999999999999</v>
-      </c>
       <c r="H89" t="n">
-        <v>-0.38</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>32.9872</v>
+        <v>24.99</v>
       </c>
       <c r="C90" t="n">
-        <v>5.26036616</v>
+        <v>5.27246881</v>
       </c>
       <c r="D90" t="n">
-        <v>65.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E90" t="n">
-        <v>67.65000000000001</v>
+        <v>69</v>
       </c>
       <c r="F90" t="n">
-        <v>65.34999999999999</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G90" t="n">
-        <v>67.45</v>
+        <v>66.55</v>
       </c>
       <c r="H90" t="n">
-        <v>2.82</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-168.98</v>
+        <v>-70.5937</v>
       </c>
       <c r="C91" t="n">
-        <v>5.24346816</v>
+        <v>5.26540944</v>
       </c>
       <c r="D91" t="n">
-        <v>64.84999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>69</v>
+        <v>66.8</v>
       </c>
       <c r="F91" t="n">
-        <v>64.7</v>
+        <v>64.45</v>
       </c>
       <c r="G91" t="n">
-        <v>68.90000000000001</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H91" t="n">
-        <v>2.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-195.54</v>
+        <v>-83.42</v>
       </c>
       <c r="C92" t="n">
-        <v>5.22391416</v>
+        <v>5.25706744</v>
       </c>
       <c r="D92" t="n">
-        <v>69.90000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>70.2</v>
+        <v>68</v>
       </c>
       <c r="F92" t="n">
-        <v>67.95</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>69.05</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H92" t="n">
-        <v>0.22</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>16.18</v>
+        <v>32.9872</v>
       </c>
       <c r="C93" t="n">
-        <v>5.22553216</v>
+        <v>5.26036616</v>
       </c>
       <c r="D93" t="n">
-        <v>69.25</v>
+        <v>65.5</v>
       </c>
       <c r="E93" t="n">
-        <v>70.8</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F93" t="n">
-        <v>69.05</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>69.84999999999999</v>
+        <v>67.45</v>
       </c>
       <c r="H93" t="n">
-        <v>1.16</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13.87</v>
+        <v>-168.98</v>
       </c>
       <c r="C94" t="n">
-        <v>5.22691916</v>
+        <v>5.24346816</v>
       </c>
       <c r="D94" t="n">
-        <v>70.95</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E94" t="n">
-        <v>71.3</v>
+        <v>69</v>
       </c>
       <c r="F94" t="n">
-        <v>69.15000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G94" t="n">
-        <v>70.15000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>0.43</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-145.08</v>
+        <v>-195.54</v>
       </c>
       <c r="C95" t="n">
-        <v>5.21241116</v>
+        <v>5.22391416</v>
       </c>
       <c r="D95" t="n">
-        <v>68.95</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E95" t="n">
-        <v>69</v>
+        <v>70.2</v>
       </c>
       <c r="F95" t="n">
-        <v>67.3</v>
+        <v>67.95</v>
       </c>
       <c r="G95" t="n">
-        <v>67.90000000000001</v>
+        <v>69.05</v>
       </c>
       <c r="H95" t="n">
-        <v>-3.21</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>25.02</v>
+        <v>16.18</v>
       </c>
       <c r="C96" t="n">
-        <v>5.21491316</v>
+        <v>5.22553216</v>
       </c>
       <c r="D96" t="n">
-        <v>67.5</v>
+        <v>69.25</v>
       </c>
       <c r="E96" t="n">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F96" t="n">
-        <v>66.3</v>
+        <v>69.05</v>
       </c>
       <c r="G96" t="n">
-        <v>69.90000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H96" t="n">
-        <v>2.95</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>-6.25</v>
+        <v>13.87</v>
       </c>
       <c r="C97" t="n">
-        <v>5.21428816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D97" t="n">
-        <v>71.25</v>
+        <v>70.95</v>
       </c>
       <c r="E97" t="n">
-        <v>73.3</v>
+        <v>71.3</v>
       </c>
       <c r="F97" t="n">
-        <v>70.84999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>71.3</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H97" t="n">
-        <v>2</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-48.58</v>
+        <v>-145.08</v>
       </c>
       <c r="C98" t="n">
-        <v>5.20943016</v>
+        <v>5.21241116</v>
       </c>
       <c r="D98" t="n">
-        <v>70.65000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E98" t="n">
-        <v>71.25</v>
+        <v>69</v>
       </c>
       <c r="F98" t="n">
-        <v>66.34999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G98" t="n">
-        <v>66.84999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H98" t="n">
-        <v>-6.24</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>-197.18</v>
+        <v>25.02</v>
       </c>
       <c r="C99" t="n">
-        <v>5.18971216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D99" t="n">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="E99" t="n">
-        <v>67.34999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>65.8</v>
+        <v>66.3</v>
       </c>
       <c r="G99" t="n">
-        <v>66</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H99" t="n">
-        <v>-1.27</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>426.64</v>
+        <v>-6.25</v>
       </c>
       <c r="C100" t="n">
-        <v>5.23237616</v>
+        <v>5.21428816</v>
       </c>
       <c r="D100" t="n">
-        <v>67</v>
+        <v>71.25</v>
       </c>
       <c r="E100" t="n">
-        <v>68.7</v>
+        <v>73.3</v>
       </c>
       <c r="F100" t="n">
-        <v>66.34999999999999</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>66.8</v>
+        <v>71.3</v>
       </c>
       <c r="H100" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>41.4993</v>
+        <v>-48.58</v>
       </c>
       <c r="C101" t="n">
-        <v>5.23652609</v>
+        <v>5.20943016</v>
       </c>
       <c r="D101" t="n">
-        <v>65.59999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E101" t="n">
-        <v>66.05</v>
+        <v>71.25</v>
       </c>
       <c r="F101" t="n">
-        <v>64.2</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G101" t="n">
-        <v>64.8</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>-2.99</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-220.5688</v>
+        <v>-197.18</v>
       </c>
       <c r="C102" t="n">
-        <v>5.21446921</v>
+        <v>5.18971216</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.65000000000001</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>63.45</v>
+        <v>65.8</v>
       </c>
       <c r="G102" t="n">
-        <v>67.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="H102" t="n">
-        <v>4.32</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>215.27</v>
+        <v>426.64</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23599621</v>
+        <v>5.23237616</v>
       </c>
       <c r="D103" t="n">
-        <v>69.59999999999999</v>
+        <v>67</v>
       </c>
       <c r="E103" t="n">
-        <v>71.34999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="F103" t="n">
-        <v>69.45</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G103" t="n">
-        <v>70.45</v>
+        <v>66.8</v>
       </c>
       <c r="H103" t="n">
-        <v>4.22</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>-160.53</v>
+        <v>41.4993</v>
       </c>
       <c r="C104" t="n">
-        <v>5.21994321</v>
+        <v>5.23652609</v>
       </c>
       <c r="D104" t="n">
-        <v>69.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E104" t="n">
-        <v>70.8</v>
+        <v>66.05</v>
       </c>
       <c r="F104" t="n">
-        <v>68.7</v>
+        <v>64.2</v>
       </c>
       <c r="G104" t="n">
-        <v>69</v>
+        <v>64.8</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.06</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-304.01</v>
+        <v>-220.5688</v>
       </c>
       <c r="C105" t="n">
-        <v>5.18954221</v>
+        <v>5.21446921</v>
       </c>
       <c r="D105" t="n">
-        <v>69</v>
+        <v>66.2</v>
       </c>
       <c r="E105" t="n">
-        <v>71.5</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F105" t="n">
-        <v>68.3</v>
+        <v>63.45</v>
       </c>
       <c r="G105" t="n">
-        <v>70.05</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H105" t="n">
-        <v>1.52</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>-30.3</v>
+        <v>215.27</v>
       </c>
       <c r="C106" t="n">
-        <v>5.18651221</v>
+        <v>5.23599621</v>
       </c>
       <c r="D106" t="n">
-        <v>68.05</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E106" t="n">
-        <v>69.34999999999999</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>68</v>
+        <v>69.45</v>
       </c>
       <c r="G106" t="n">
-        <v>68.8</v>
+        <v>70.45</v>
       </c>
       <c r="H106" t="n">
-        <v>-1.78</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-92.3</v>
+        <v>-160.53</v>
       </c>
       <c r="C107" t="n">
-        <v>5.17728221</v>
+        <v>5.21994321</v>
       </c>
       <c r="D107" t="n">
-        <v>68.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E107" t="n">
-        <v>69.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="F107" t="n">
-        <v>67.2</v>
+        <v>68.7</v>
       </c>
       <c r="G107" t="n">
-        <v>67.7</v>
+        <v>69</v>
       </c>
       <c r="H107" t="n">
-        <v>-1.6</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>25.43</v>
+        <v>-304.01</v>
       </c>
       <c r="C108" t="n">
-        <v>5.17982521</v>
+        <v>5.18954221</v>
       </c>
       <c r="D108" t="n">
-        <v>68.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="E108" t="n">
-        <v>71.45</v>
+        <v>71.5</v>
       </c>
       <c r="F108" t="n">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="G108" t="n">
-        <v>71.2</v>
+        <v>70.05</v>
       </c>
       <c r="H108" t="n">
-        <v>5.17</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>136.53</v>
+        <v>-30.3</v>
       </c>
       <c r="C109" t="n">
-        <v>5.19347821</v>
+        <v>5.18651221</v>
       </c>
       <c r="D109" t="n">
-        <v>71.2</v>
+        <v>68.05</v>
       </c>
       <c r="E109" t="n">
-        <v>73.40000000000001</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F109" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G109" t="n">
-        <v>71.8</v>
+        <v>68.8</v>
       </c>
       <c r="H109" t="n">
-        <v>0.84</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-224.29</v>
+        <v>-92.3</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17104921</v>
+        <v>5.17728221</v>
       </c>
       <c r="D110" t="n">
-        <v>73.45</v>
+        <v>68.8</v>
       </c>
       <c r="E110" t="n">
-        <v>74</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F110" t="n">
-        <v>71.65000000000001</v>
+        <v>67.2</v>
       </c>
       <c r="G110" t="n">
-        <v>73.3</v>
+        <v>67.7</v>
       </c>
       <c r="H110" t="n">
-        <v>2.09</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>97.7422</v>
+        <v>25.43</v>
       </c>
       <c r="C111" t="n">
-        <v>5.18082343</v>
+        <v>5.17982521</v>
       </c>
       <c r="D111" t="n">
-        <v>71.95</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E111" t="n">
-        <v>73.5</v>
+        <v>71.45</v>
       </c>
       <c r="F111" t="n">
-        <v>71.75</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G111" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="H111" t="n">
-        <v>-1.91</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>-116.85</v>
+        <v>136.53</v>
       </c>
       <c r="C112" t="n">
-        <v>5.16913843</v>
+        <v>5.19347821</v>
       </c>
       <c r="D112" t="n">
-        <v>71.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="E112" t="n">
-        <v>76.45</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F112" t="n">
-        <v>71.55</v>
+        <v>70</v>
       </c>
       <c r="G112" t="n">
-        <v>74.2</v>
+        <v>71.8</v>
       </c>
       <c r="H112" t="n">
-        <v>3.2</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>32.76</v>
+        <v>-224.29</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17241443</v>
+        <v>5.17104921</v>
       </c>
       <c r="D113" t="n">
-        <v>74.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E113" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F113" t="n">
-        <v>73.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G113" t="n">
-        <v>73.7</v>
+        <v>73.3</v>
       </c>
       <c r="H113" t="n">
-        <v>-0.67</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>-19.6</v>
+        <v>97.7422</v>
       </c>
       <c r="C114" t="n">
-        <v>5.17045443</v>
+        <v>5.18082343</v>
       </c>
       <c r="D114" t="n">
-        <v>73.7</v>
+        <v>71.95</v>
       </c>
       <c r="E114" t="n">
-        <v>73.95</v>
+        <v>73.5</v>
       </c>
       <c r="F114" t="n">
-        <v>71.65000000000001</v>
+        <v>71.75</v>
       </c>
       <c r="G114" t="n">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H114" t="n">
-        <v>-0.95</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>74.23999999999999</v>
+        <v>-116.85</v>
       </c>
       <c r="C115" t="n">
-        <v>5.17787843</v>
+        <v>5.16913843</v>
       </c>
       <c r="D115" t="n">
-        <v>73.75</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E115" t="n">
-        <v>73.75</v>
+        <v>76.45</v>
       </c>
       <c r="F115" t="n">
-        <v>70.5</v>
+        <v>71.55</v>
       </c>
       <c r="G115" t="n">
-        <v>70.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="H115" t="n">
-        <v>-2.88</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>15.04</v>
+        <v>32.76</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17938243</v>
+        <v>5.17241443</v>
       </c>
       <c r="D116" t="n">
-        <v>70.95</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E116" t="n">
-        <v>72.15000000000001</v>
+        <v>75</v>
       </c>
       <c r="F116" t="n">
-        <v>70.95</v>
+        <v>73.25</v>
       </c>
       <c r="G116" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="H116" t="n">
-        <v>0.99</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>213.47</v>
+        <v>-19.6</v>
       </c>
       <c r="C117" t="n">
-        <v>5.20072943</v>
+        <v>5.17045443</v>
       </c>
       <c r="D117" t="n">
-        <v>71.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="E117" t="n">
-        <v>71.90000000000001</v>
+        <v>73.95</v>
       </c>
       <c r="F117" t="n">
-        <v>70.40000000000001</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>71.45</v>
+        <v>73</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.21</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>-167.67</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>5.18396243</v>
+        <v>5.17787843</v>
       </c>
       <c r="D118" t="n">
-        <v>72</v>
+        <v>73.75</v>
       </c>
       <c r="E118" t="n">
-        <v>73.45</v>
+        <v>73.75</v>
       </c>
       <c r="F118" t="n">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="G118" t="n">
-        <v>73.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H118" t="n">
-        <v>2.59</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>-78.5919</v>
+        <v>15.04</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17610324</v>
+        <v>5.17938243</v>
       </c>
       <c r="D119" t="n">
-        <v>73.3</v>
+        <v>70.95</v>
       </c>
       <c r="E119" t="n">
-        <v>73.3</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>71.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="G119" t="n">
-        <v>73.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H119" t="n">
-        <v>-0.14</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>-54.57</v>
+        <v>213.47</v>
       </c>
       <c r="C120" t="n">
-        <v>5.17064624</v>
+        <v>5.20072943</v>
       </c>
       <c r="D120" t="n">
-        <v>72.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E120" t="n">
-        <v>73.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>71.95</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>73.45</v>
+        <v>71.45</v>
       </c>
       <c r="H120" t="n">
-        <v>0.34</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>32.9</v>
+        <v>-167.67</v>
       </c>
       <c r="C121" t="n">
-        <v>5.17393624</v>
+        <v>5.18396243</v>
       </c>
       <c r="D121" t="n">
+        <v>72</v>
+      </c>
+      <c r="E121" t="n">
         <v>73.45</v>
       </c>
-      <c r="E121" t="n">
-        <v>74.40000000000001</v>
-      </c>
       <c r="F121" t="n">
-        <v>71.75</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G121" t="n">
-        <v>73.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H121" t="n">
-        <v>-0.41</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>41.93</v>
+        <v>-78.5919</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17812924</v>
+        <v>5.17610324</v>
       </c>
       <c r="D122" t="n">
-        <v>73</v>
+        <v>73.3</v>
       </c>
       <c r="E122" t="n">
-        <v>73.65000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F122" t="n">
-        <v>68.7</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G122" t="n">
-        <v>69.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H122" t="n">
-        <v>-4.44</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>52.87</v>
+        <v>-54.57</v>
       </c>
       <c r="C123" t="n">
-        <v>5.18341624</v>
+        <v>5.17064624</v>
       </c>
       <c r="D123" t="n">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E123" t="n">
-        <v>70.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>68.90000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G123" t="n">
-        <v>69.7</v>
+        <v>73.45</v>
       </c>
       <c r="H123" t="n">
-        <v>-0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>291.58</v>
+        <v>32.9</v>
       </c>
       <c r="C124" t="n">
-        <v>5.21257424</v>
+        <v>5.17393624</v>
       </c>
       <c r="D124" t="n">
-        <v>69.09999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E124" t="n">
-        <v>69.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F124" t="n">
-        <v>66.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G124" t="n">
-        <v>67</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H124" t="n">
-        <v>-3.87</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>-60.7601</v>
+        <v>41.93</v>
       </c>
       <c r="C125" t="n">
-        <v>5.20649823</v>
+        <v>5.17812924</v>
       </c>
       <c r="D125" t="n">
-        <v>69.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="E125" t="n">
-        <v>70.25</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F125" t="n">
-        <v>68.45</v>
+        <v>68.7</v>
       </c>
       <c r="G125" t="n">
-        <v>69.25</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H125" t="n">
-        <v>3.36</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>264.89</v>
+        <v>52.87</v>
       </c>
       <c r="C126" t="n">
-        <v>5.23298723</v>
+        <v>5.18341624</v>
       </c>
       <c r="D126" t="n">
-        <v>68.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>69.75</v>
+        <v>70.5</v>
       </c>
       <c r="F126" t="n">
-        <v>67.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>67.55</v>
+        <v>69.7</v>
       </c>
       <c r="H126" t="n">
-        <v>-2.45</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0</v>
+        <v>291.58</v>
       </c>
       <c r="C127" t="n">
-        <v>5.23298723</v>
+        <v>5.21257424</v>
       </c>
       <c r="D127" t="n">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E127" t="n">
-        <v>71.15000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F127" t="n">
-        <v>68.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G127" t="n">
-        <v>70.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H127" t="n">
-        <v>3.85</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0</v>
+        <v>-60.7601</v>
       </c>
       <c r="C128" t="n">
-        <v>5.23298723</v>
+        <v>5.20649823</v>
       </c>
       <c r="D128" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="E128" t="n">
+        <v>70.25</v>
+      </c>
+      <c r="F128" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="G128" t="n">
         <v>69.25</v>
       </c>
-      <c r="E128" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="F128" t="n">
-        <v>68.2</v>
-      </c>
-      <c r="G128" t="n">
-        <v>69.65000000000001</v>
-      </c>
       <c r="H128" t="n">
-        <v>-0.71</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>-369.37</v>
+        <v>264.89</v>
       </c>
       <c r="C129" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D129" t="n">
-        <v>69.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E129" t="n">
-        <v>69.5</v>
+        <v>69.75</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.84999999999999</v>
+        <v>67.55</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.58</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.19605023</v>
+        <v>5.23298723</v>
       </c>
       <c r="D130" t="n">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E130" t="n">
-        <v>70.34999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="F130" t="n">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="G130" t="n">
-        <v>69.95</v>
+        <v>67.55</v>
       </c>
       <c r="H130" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>68.9663</v>
+        <v>0</v>
       </c>
       <c r="C131" t="n">
-        <v>5.20294686</v>
+        <v>5.23298723</v>
       </c>
       <c r="D131" t="n">
-        <v>68.34999999999999</v>
+        <v>69</v>
       </c>
       <c r="E131" t="n">
-        <v>70.3</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F131" t="n">
-        <v>68.34999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G131" t="n">
-        <v>70.05</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H131" t="n">
-        <v>0.14</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>-247.41</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
-        <v>5.17820586</v>
+        <v>5.23298723</v>
       </c>
       <c r="D132" t="n">
-        <v>69.5</v>
+        <v>69.25</v>
       </c>
       <c r="E132" t="n">
-        <v>74.15000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F132" t="n">
-        <v>69.45</v>
+        <v>68.2</v>
       </c>
       <c r="G132" t="n">
-        <v>73.84999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H132" t="n">
-        <v>5.42</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>27.55</v>
+        <v>-369.37</v>
       </c>
       <c r="C133" t="n">
-        <v>5.18096086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D133" t="n">
-        <v>73.34999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E133" t="n">
-        <v>75.15000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F133" t="n">
-        <v>73.05</v>
+        <v>67.3</v>
       </c>
       <c r="G133" t="n">
-        <v>73.40000000000001</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H133" t="n">
-        <v>-0.61</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>-286.2</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
-        <v>5.15234086</v>
+        <v>5.19605023</v>
       </c>
       <c r="D134" t="n">
-        <v>73.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="E134" t="n">
-        <v>74.40000000000001</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F134" t="n">
-        <v>73.05</v>
+        <v>68.5</v>
       </c>
       <c r="G134" t="n">
-        <v>73.65000000000001</v>
+        <v>69.95</v>
       </c>
       <c r="H134" t="n">
-        <v>0.34</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>48.88</v>
+        <v>68.9663</v>
       </c>
       <c r="C135" t="n">
-        <v>5.15722886</v>
+        <v>5.20294686</v>
       </c>
       <c r="D135" t="n">
-        <v>76.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E135" t="n">
-        <v>78.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F135" t="n">
-        <v>75.40000000000001</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G135" t="n">
-        <v>76.84999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H135" t="n">
-        <v>4.34</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-55.96</v>
+        <v>-247.41</v>
       </c>
       <c r="C136" t="n">
-        <v>5.15163286</v>
+        <v>5.17820586</v>
       </c>
       <c r="D136" t="n">
-        <v>75.05</v>
+        <v>69.5</v>
       </c>
       <c r="E136" t="n">
-        <v>75.90000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>74.25</v>
+        <v>69.45</v>
       </c>
       <c r="G136" t="n">
-        <v>75.59999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>-1.63</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>-385.85</v>
+        <v>27.55</v>
       </c>
       <c r="C137" t="n">
-        <v>5.11304786</v>
+        <v>5.18096086</v>
       </c>
       <c r="D137" t="n">
-        <v>72.40000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E137" t="n">
-        <v>72.40000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>64.5</v>
+        <v>73.05</v>
       </c>
       <c r="G137" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-14.15</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>139.59</v>
+        <v>-286.2</v>
       </c>
       <c r="C138" t="n">
-        <v>5.12700686</v>
+        <v>5.15234086</v>
       </c>
       <c r="D138" t="n">
-        <v>64.90000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>64.90000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>61.75</v>
+        <v>73.05</v>
       </c>
       <c r="G138" t="n">
-        <v>62.1</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H138" t="n">
-        <v>-4.31</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1468.42</v>
+        <v>48.88</v>
       </c>
       <c r="C139" t="n">
-        <v>5.27384886</v>
+        <v>5.15722886</v>
       </c>
       <c r="D139" t="n">
-        <v>62.6</v>
+        <v>76.8</v>
       </c>
       <c r="E139" t="n">
-        <v>63.35</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F139" t="n">
-        <v>61</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G139" t="n">
-        <v>61.6</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H139" t="n">
-        <v>-0.8100000000000001</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>292.93</v>
+        <v>-55.96</v>
       </c>
       <c r="C140" t="n">
-        <v>5.30314186</v>
+        <v>5.15163286</v>
       </c>
       <c r="D140" t="n">
-        <v>62.5</v>
+        <v>75.05</v>
       </c>
       <c r="E140" t="n">
-        <v>63.85</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F140" t="n">
-        <v>61.55</v>
+        <v>74.25</v>
       </c>
       <c r="G140" t="n">
-        <v>62.25</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H140" t="n">
-        <v>1.06</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>17.9</v>
+        <v>-385.85</v>
       </c>
       <c r="C141" t="n">
-        <v>5.30493186</v>
+        <v>5.11304786</v>
       </c>
       <c r="D141" t="n">
-        <v>63.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E141" t="n">
-        <v>64.95</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F141" t="n">
-        <v>61.35</v>
+        <v>64.5</v>
       </c>
       <c r="G141" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H141" t="n">
-        <v>-0.72</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>-224.88</v>
+        <v>139.59</v>
       </c>
       <c r="C142" t="n">
-        <v>5.28244386</v>
+        <v>5.12700686</v>
       </c>
       <c r="D142" t="n">
-        <v>61.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E142" t="n">
-        <v>62.25</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F142" t="n">
-        <v>60.4</v>
+        <v>61.75</v>
       </c>
       <c r="G142" t="n">
-        <v>62.15</v>
+        <v>62.1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.57</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>-244.5</v>
+        <v>1468.42</v>
       </c>
       <c r="C143" t="n">
-        <v>5.25799386</v>
+        <v>5.27384886</v>
       </c>
       <c r="D143" t="n">
-        <v>61.9</v>
+        <v>62.6</v>
       </c>
       <c r="E143" t="n">
-        <v>62.35</v>
+        <v>63.35</v>
       </c>
       <c r="F143" t="n">
-        <v>59.9</v>
+        <v>61</v>
       </c>
       <c r="G143" t="n">
-        <v>60.2</v>
+        <v>61.6</v>
       </c>
       <c r="H143" t="n">
-        <v>-3.14</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>-302.48</v>
+        <v>292.93</v>
       </c>
       <c r="C144" t="n">
-        <v>5.22774586</v>
+        <v>5.30314186</v>
       </c>
       <c r="D144" t="n">
-        <v>60.1</v>
+        <v>62.5</v>
       </c>
       <c r="E144" t="n">
-        <v>61</v>
+        <v>63.85</v>
       </c>
       <c r="F144" t="n">
-        <v>58.6</v>
+        <v>61.55</v>
       </c>
       <c r="G144" t="n">
-        <v>60.45</v>
+        <v>62.25</v>
       </c>
       <c r="H144" t="n">
-        <v>0.42</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>-177.8636</v>
+        <v>17.9</v>
       </c>
       <c r="C145" t="n">
-        <v>5.2099595</v>
+        <v>5.30493186</v>
       </c>
       <c r="D145" t="n">
-        <v>60</v>
+        <v>63.2</v>
       </c>
       <c r="E145" t="n">
-        <v>60.05</v>
+        <v>64.95</v>
       </c>
       <c r="F145" t="n">
-        <v>55.7</v>
+        <v>61.35</v>
       </c>
       <c r="G145" t="n">
-        <v>57.85</v>
+        <v>61.8</v>
       </c>
       <c r="H145" t="n">
-        <v>-4.3</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-228.55</v>
+        <v>-224.88</v>
       </c>
       <c r="C146" t="n">
-        <v>5.1871045</v>
+        <v>5.28244386</v>
       </c>
       <c r="D146" t="n">
-        <v>56.95</v>
+        <v>61.8</v>
       </c>
       <c r="E146" t="n">
-        <v>59.1</v>
+        <v>62.25</v>
       </c>
       <c r="F146" t="n">
-        <v>56</v>
+        <v>60.4</v>
       </c>
       <c r="G146" t="n">
-        <v>58.55</v>
+        <v>62.15</v>
       </c>
       <c r="H146" t="n">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>423.9973</v>
+        <v>-244.5</v>
       </c>
       <c r="C147" t="n">
-        <v>5.22950423</v>
+        <v>5.25799386</v>
       </c>
       <c r="D147" t="n">
-        <v>57.05</v>
+        <v>61.9</v>
       </c>
       <c r="E147" t="n">
-        <v>62</v>
+        <v>62.35</v>
       </c>
       <c r="F147" t="n">
-        <v>56.55</v>
+        <v>59.9</v>
       </c>
       <c r="G147" t="n">
-        <v>61.9</v>
+        <v>60.2</v>
       </c>
       <c r="H147" t="n">
-        <v>5.72</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-119.16</v>
+        <v>-302.48</v>
       </c>
       <c r="C148" t="n">
-        <v>5.21758823</v>
+        <v>5.22774586</v>
       </c>
       <c r="D148" t="n">
-        <v>60.5</v>
+        <v>60.1</v>
       </c>
       <c r="E148" t="n">
-        <v>60.75</v>
+        <v>61</v>
       </c>
       <c r="F148" t="n">
-        <v>58.75</v>
+        <v>58.6</v>
       </c>
       <c r="G148" t="n">
-        <v>59.1</v>
+        <v>60.45</v>
       </c>
       <c r="H148" t="n">
-        <v>-4.52</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-301.92</v>
+        <v>-177.8636</v>
       </c>
       <c r="C149" t="n">
-        <v>5.18739623</v>
+        <v>5.2099595</v>
       </c>
       <c r="D149" t="n">
-        <v>58.95</v>
+        <v>60</v>
       </c>
       <c r="E149" t="n">
-        <v>58.95</v>
+        <v>60.05</v>
       </c>
       <c r="F149" t="n">
-        <v>56.85</v>
+        <v>55.7</v>
       </c>
       <c r="G149" t="n">
-        <v>57.25</v>
+        <v>57.85</v>
       </c>
       <c r="H149" t="n">
-        <v>-3.13</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>112.29</v>
+        <v>-228.55</v>
       </c>
       <c r="C150" t="n">
-        <v>5.19862523</v>
+        <v>5.1871045</v>
       </c>
       <c r="D150" t="n">
-        <v>57.1</v>
+        <v>56.95</v>
       </c>
       <c r="E150" t="n">
-        <v>57.6</v>
+        <v>59.1</v>
       </c>
       <c r="F150" t="n">
-        <v>56.5</v>
+        <v>56</v>
       </c>
       <c r="G150" t="n">
-        <v>56.65</v>
+        <v>58.55</v>
       </c>
       <c r="H150" t="n">
-        <v>-1.05</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>-62.4836</v>
+        <v>423.9973</v>
       </c>
       <c r="C151" t="n">
-        <v>5.19237687</v>
+        <v>5.22950423</v>
       </c>
       <c r="D151" t="n">
-        <v>55.3</v>
+        <v>57.05</v>
       </c>
       <c r="E151" t="n">
-        <v>57.9</v>
+        <v>62</v>
       </c>
       <c r="F151" t="n">
-        <v>54.95</v>
+        <v>56.55</v>
       </c>
       <c r="G151" t="n">
-        <v>57.35</v>
+        <v>61.9</v>
       </c>
       <c r="H151" t="n">
-        <v>1.24</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-29.35</v>
+        <v>-119.16</v>
       </c>
       <c r="C152" t="n">
-        <v>5.18944187</v>
+        <v>5.21758823</v>
       </c>
       <c r="D152" t="n">
-        <v>56.2</v>
+        <v>60.5</v>
       </c>
       <c r="E152" t="n">
-        <v>57.1</v>
+        <v>60.75</v>
       </c>
       <c r="F152" t="n">
-        <v>55.8</v>
+        <v>58.75</v>
       </c>
       <c r="G152" t="n">
-        <v>55.85</v>
+        <v>59.1</v>
       </c>
       <c r="H152" t="n">
-        <v>-2.62</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>54.46</v>
+        <v>-301.92</v>
       </c>
       <c r="C153" t="n">
-        <v>5.19488787</v>
+        <v>5.18739623</v>
       </c>
       <c r="D153" t="n">
-        <v>55.3</v>
+        <v>58.95</v>
       </c>
       <c r="E153" t="n">
-        <v>55.55</v>
+        <v>58.95</v>
       </c>
       <c r="F153" t="n">
-        <v>53.25</v>
+        <v>56.85</v>
       </c>
       <c r="G153" t="n">
-        <v>54.7</v>
+        <v>57.25</v>
       </c>
       <c r="H153" t="n">
-        <v>-2.06</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>17.32</v>
+        <v>112.29</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19661987</v>
+        <v>5.19862523</v>
       </c>
       <c r="D154" t="n">
-        <v>54</v>
+        <v>57.1</v>
       </c>
       <c r="E154" t="n">
-        <v>54.1</v>
+        <v>57.6</v>
       </c>
       <c r="F154" t="n">
-        <v>52.25</v>
+        <v>56.5</v>
       </c>
       <c r="G154" t="n">
-        <v>53.15</v>
+        <v>56.65</v>
       </c>
       <c r="H154" t="n">
-        <v>-2.83</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>93.42</v>
+        <v>-62.4836</v>
       </c>
       <c r="C155" t="n">
-        <v>5.20596187</v>
+        <v>5.19237687</v>
       </c>
       <c r="D155" t="n">
-        <v>53.7</v>
+        <v>55.3</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>53.25</v>
+        <v>54.95</v>
       </c>
       <c r="G155" t="n">
-        <v>57</v>
+        <v>57.35</v>
       </c>
       <c r="H155" t="n">
-        <v>7.24</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>64.81</v>
+        <v>-29.35</v>
       </c>
       <c r="C156" t="n">
-        <v>5.21244287</v>
+        <v>5.18944187</v>
       </c>
       <c r="D156" t="n">
-        <v>56.6</v>
+        <v>56.2</v>
       </c>
       <c r="E156" t="n">
-        <v>58.05</v>
+        <v>57.1</v>
       </c>
       <c r="F156" t="n">
-        <v>56.5</v>
+        <v>55.8</v>
       </c>
       <c r="G156" t="n">
-        <v>56.85</v>
+        <v>55.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-0.26</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>-172.75</v>
+        <v>54.46</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19516787</v>
+        <v>5.19488787</v>
       </c>
       <c r="D157" t="n">
-        <v>56.85</v>
+        <v>55.3</v>
       </c>
       <c r="E157" t="n">
-        <v>57.2</v>
+        <v>55.55</v>
       </c>
       <c r="F157" t="n">
-        <v>55</v>
+        <v>53.25</v>
       </c>
       <c r="G157" t="n">
-        <v>56</v>
+        <v>54.7</v>
       </c>
       <c r="H157" t="n">
-        <v>-1.5</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>-24.86</v>
+        <v>17.32</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19268187</v>
+        <v>5.19661987</v>
       </c>
       <c r="D158" t="n">
-        <v>55.75</v>
+        <v>54</v>
       </c>
       <c r="E158" t="n">
-        <v>55.8</v>
+        <v>54.1</v>
       </c>
       <c r="F158" t="n">
-        <v>53.7</v>
+        <v>52.25</v>
       </c>
       <c r="G158" t="n">
-        <v>53.9</v>
+        <v>53.15</v>
       </c>
       <c r="H158" t="n">
-        <v>-3.75</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>17.38</v>
+        <v>93.42</v>
       </c>
       <c r="C159" t="n">
-        <v>5.19441987</v>
+        <v>5.20596187</v>
       </c>
       <c r="D159" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="E159" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="F159" t="n">
         <v>53.25</v>
       </c>
-      <c r="E159" t="n">
-        <v>53.9</v>
-      </c>
-      <c r="F159" t="n">
-        <v>51.75</v>
-      </c>
       <c r="G159" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="H159" t="n">
-        <v>-3.53</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>14.06</v>
+        <v>64.81</v>
       </c>
       <c r="C160" t="n">
-        <v>5.19582587</v>
+        <v>5.21244287</v>
       </c>
       <c r="D160" t="n">
-        <v>50.15</v>
+        <v>56.6</v>
       </c>
       <c r="E160" t="n">
-        <v>51.55</v>
+        <v>58.05</v>
       </c>
       <c r="F160" t="n">
-        <v>49.64</v>
+        <v>56.5</v>
       </c>
       <c r="G160" t="n">
-        <v>50.5</v>
+        <v>56.85</v>
       </c>
       <c r="H160" t="n">
-        <v>-2.88</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-21.2345</v>
+        <v>-172.75</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19370242</v>
+        <v>5.19516787</v>
       </c>
       <c r="D161" t="n">
-        <v>50</v>
+        <v>56.85</v>
       </c>
       <c r="E161" t="n">
-        <v>50.8</v>
+        <v>57.2</v>
       </c>
       <c r="F161" t="n">
-        <v>47.9</v>
+        <v>55</v>
       </c>
       <c r="G161" t="n">
-        <v>48.32</v>
+        <v>56</v>
       </c>
       <c r="H161" t="n">
-        <v>-4.32</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>47.7</v>
+        <v>-24.86</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19847242</v>
+        <v>5.19268187</v>
       </c>
       <c r="D162" t="n">
-        <v>48.98</v>
+        <v>55.75</v>
       </c>
       <c r="E162" t="n">
-        <v>49.94</v>
+        <v>55.8</v>
       </c>
       <c r="F162" t="n">
-        <v>48.18</v>
+        <v>53.7</v>
       </c>
       <c r="G162" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="H162" t="n">
-        <v>2.32</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>92.59999999999999</v>
+        <v>17.38</v>
       </c>
       <c r="C163" t="n">
-        <v>5.20773242</v>
+        <v>5.19441987</v>
       </c>
       <c r="D163" t="n">
-        <v>49.44</v>
+        <v>53.25</v>
       </c>
       <c r="E163" t="n">
-        <v>49.44</v>
+        <v>53.9</v>
       </c>
       <c r="F163" t="n">
-        <v>46.74</v>
+        <v>51.75</v>
       </c>
       <c r="G163" t="n">
-        <v>47.4</v>
+        <v>52</v>
       </c>
       <c r="H163" t="n">
-        <v>-4.13</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>-95.51000000000001</v>
+        <v>14.06</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19818142</v>
+        <v>5.19582587</v>
       </c>
       <c r="D164" t="n">
-        <v>47</v>
+        <v>50.15</v>
       </c>
       <c r="E164" t="n">
-        <v>47</v>
+        <v>51.55</v>
       </c>
       <c r="F164" t="n">
-        <v>45.86</v>
+        <v>49.64</v>
       </c>
       <c r="G164" t="n">
-        <v>46.28</v>
+        <v>50.5</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.36</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-254.06</v>
+        <v>-21.2345</v>
       </c>
       <c r="C165" t="n">
-        <v>5.17277542</v>
+        <v>5.19370242</v>
       </c>
       <c r="D165" t="n">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="E165" t="n">
-        <v>47.18</v>
+        <v>50.8</v>
       </c>
       <c r="F165" t="n">
-        <v>45.76</v>
+        <v>47.9</v>
       </c>
       <c r="G165" t="n">
-        <v>45.9</v>
+        <v>48.32</v>
       </c>
       <c r="H165" t="n">
-        <v>-0.82</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>-316.19</v>
+        <v>47.7</v>
       </c>
       <c r="C166" t="n">
-        <v>5.14115642</v>
+        <v>5.19847242</v>
       </c>
       <c r="D166" t="n">
-        <v>45.9</v>
+        <v>48.98</v>
       </c>
       <c r="E166" t="n">
-        <v>46.78</v>
+        <v>49.94</v>
       </c>
       <c r="F166" t="n">
-        <v>45.26</v>
+        <v>48.18</v>
       </c>
       <c r="G166" t="n">
-        <v>46.08</v>
+        <v>49.44</v>
       </c>
       <c r="H166" t="n">
-        <v>0.39</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>-150.87</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C167" t="n">
-        <v>5.12606942</v>
+        <v>5.20773242</v>
       </c>
       <c r="D167" t="n">
-        <v>47.7</v>
+        <v>49.44</v>
       </c>
       <c r="E167" t="n">
-        <v>48.9</v>
+        <v>49.44</v>
       </c>
       <c r="F167" t="n">
-        <v>46.64</v>
+        <v>46.74</v>
       </c>
       <c r="G167" t="n">
-        <v>46.84</v>
+        <v>47.4</v>
       </c>
       <c r="H167" t="n">
-        <v>1.65</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-236.76</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C168" t="n">
-        <v>5.10239342</v>
+        <v>5.19818142</v>
       </c>
       <c r="D168" t="n">
-        <v>46.92</v>
+        <v>47</v>
       </c>
       <c r="E168" t="n">
-        <v>48.28</v>
+        <v>47</v>
       </c>
       <c r="F168" t="n">
-        <v>46.84</v>
+        <v>45.86</v>
       </c>
       <c r="G168" t="n">
-        <v>47.36</v>
+        <v>46.28</v>
       </c>
       <c r="H168" t="n">
-        <v>1.11</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-36.92</v>
+        <v>-254.06</v>
       </c>
       <c r="C169" t="n">
-        <v>5.09870142</v>
+        <v>5.17277542</v>
       </c>
       <c r="D169" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="E169" t="n">
-        <v>47.56</v>
+        <v>47.18</v>
       </c>
       <c r="F169" t="n">
-        <v>45.72</v>
+        <v>45.76</v>
       </c>
       <c r="G169" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="H169" t="n">
-        <v>-2.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>64.78</v>
+        <v>-316.19</v>
       </c>
       <c r="C170" t="n">
-        <v>5.10517942</v>
+        <v>5.14115642</v>
       </c>
       <c r="D170" t="n">
-        <v>46.26</v>
+        <v>45.9</v>
       </c>
       <c r="E170" t="n">
-        <v>48.42</v>
+        <v>46.78</v>
       </c>
       <c r="F170" t="n">
-        <v>46.26</v>
+        <v>45.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.6</v>
+        <v>46.08</v>
       </c>
       <c r="H170" t="n">
-        <v>0.73</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-44.41</v>
+        <v>-150.87</v>
       </c>
       <c r="C171" t="n">
-        <v>5.10073842</v>
+        <v>5.12606942</v>
       </c>
       <c r="D171" t="n">
-        <v>47.06</v>
+        <v>47.7</v>
       </c>
       <c r="E171" t="n">
-        <v>48.98</v>
+        <v>48.9</v>
       </c>
       <c r="F171" t="n">
-        <v>46.7</v>
+        <v>46.64</v>
       </c>
       <c r="G171" t="n">
-        <v>48.52</v>
+        <v>46.84</v>
       </c>
       <c r="H171" t="n">
-        <v>4.12</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-124.97</v>
+        <v>-236.76</v>
       </c>
       <c r="C172" t="n">
-        <v>5.08824142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D172" t="n">
-        <v>47.6</v>
+        <v>46.92</v>
       </c>
       <c r="E172" t="n">
-        <v>48.08</v>
+        <v>48.28</v>
       </c>
       <c r="F172" t="n">
-        <v>46.72</v>
+        <v>46.84</v>
       </c>
       <c r="G172" t="n">
-        <v>46.76</v>
+        <v>47.36</v>
       </c>
       <c r="H172" t="n">
-        <v>-3.63</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-272.6</v>
+        <v>-36.92</v>
       </c>
       <c r="C173" t="n">
-        <v>5.06098142</v>
+        <v>5.09870142</v>
       </c>
       <c r="D173" t="n">
-        <v>46.76</v>
+        <v>47</v>
       </c>
       <c r="E173" t="n">
-        <v>48.3</v>
+        <v>47.56</v>
       </c>
       <c r="F173" t="n">
-        <v>46.02</v>
+        <v>45.72</v>
       </c>
       <c r="G173" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="H173" t="n">
-        <v>1.41</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>83.54000000000001</v>
+        <v>64.78</v>
       </c>
       <c r="C174" t="n">
-        <v>5.06933542</v>
+        <v>5.10517942</v>
       </c>
       <c r="D174" t="n">
-        <v>47.42</v>
+        <v>46.26</v>
       </c>
       <c r="E174" t="n">
-        <v>47.92</v>
+        <v>48.42</v>
       </c>
       <c r="F174" t="n">
-        <v>46.46</v>
+        <v>46.26</v>
       </c>
       <c r="G174" t="n">
-        <v>47.2</v>
+        <v>46.6</v>
       </c>
       <c r="H174" t="n">
-        <v>-0.46</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-232.94</v>
+        <v>-44.41</v>
       </c>
       <c r="C175" t="n">
-        <v>5.04604142</v>
+        <v>5.10073842</v>
       </c>
       <c r="D175" t="n">
-        <v>47.2</v>
+        <v>47.06</v>
       </c>
       <c r="E175" t="n">
-        <v>48.84</v>
+        <v>48.98</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.56</v>
+        <v>48.52</v>
       </c>
       <c r="H175" t="n">
-        <v>2.88</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-101.2265</v>
+        <v>-124.97</v>
       </c>
       <c r="C176" t="n">
-        <v>5.03591877</v>
+        <v>5.08824142</v>
       </c>
       <c r="D176" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="E176" t="n">
-        <v>49.46</v>
+        <v>48.08</v>
       </c>
       <c r="F176" t="n">
-        <v>48.24</v>
+        <v>46.72</v>
       </c>
       <c r="G176" t="n">
-        <v>48.78</v>
+        <v>46.76</v>
       </c>
       <c r="H176" t="n">
-        <v>0.45</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-146.01</v>
+        <v>-272.6</v>
       </c>
       <c r="C177" t="n">
-        <v>5.02131777</v>
+        <v>5.06098142</v>
       </c>
       <c r="D177" t="n">
-        <v>49.22</v>
+        <v>46.76</v>
       </c>
       <c r="E177" t="n">
-        <v>51</v>
+        <v>48.3</v>
       </c>
       <c r="F177" t="n">
-        <v>49.22</v>
+        <v>46.02</v>
       </c>
       <c r="G177" t="n">
-        <v>50.4</v>
+        <v>47.42</v>
       </c>
       <c r="H177" t="n">
-        <v>3.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>14.25</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>5.02274277</v>
+        <v>5.06933542</v>
       </c>
       <c r="D178" t="n">
-        <v>50.55</v>
+        <v>47.42</v>
       </c>
       <c r="E178" t="n">
-        <v>51</v>
+        <v>47.92</v>
       </c>
       <c r="F178" t="n">
-        <v>48.2</v>
+        <v>46.46</v>
       </c>
       <c r="G178" t="n">
-        <v>48.94</v>
+        <v>47.2</v>
       </c>
       <c r="H178" t="n">
-        <v>-2.9</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>7.54</v>
+        <v>-232.94</v>
       </c>
       <c r="C179" t="n">
-        <v>5.02349677</v>
+        <v>5.04604142</v>
       </c>
       <c r="D179" t="n">
-        <v>49.96</v>
+        <v>47.2</v>
       </c>
       <c r="E179" t="n">
-        <v>49.98</v>
+        <v>48.84</v>
       </c>
       <c r="F179" t="n">
-        <v>48.72</v>
+        <v>46.7</v>
       </c>
       <c r="G179" t="n">
-        <v>49.12</v>
+        <v>48.56</v>
       </c>
       <c r="H179" t="n">
-        <v>0.37</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>29.93</v>
+        <v>-101.2265</v>
       </c>
       <c r="C180" t="n">
-        <v>5.02648977</v>
+        <v>5.03591877</v>
       </c>
       <c r="D180" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="E180" t="n">
-        <v>49.36</v>
+        <v>49.46</v>
       </c>
       <c r="F180" t="n">
-        <v>48.18</v>
+        <v>48.24</v>
       </c>
       <c r="G180" t="n">
-        <v>48.64</v>
+        <v>48.78</v>
       </c>
       <c r="H180" t="n">
-        <v>-0.98</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-93.37</v>
+        <v>-146.01</v>
       </c>
       <c r="C181" t="n">
-        <v>5.01715277</v>
+        <v>5.02131777</v>
       </c>
       <c r="D181" t="n">
-        <v>48.4</v>
+        <v>49.22</v>
       </c>
       <c r="E181" t="n">
-        <v>48.4</v>
+        <v>51</v>
       </c>
       <c r="F181" t="n">
-        <v>47.2</v>
+        <v>49.22</v>
       </c>
       <c r="G181" t="n">
-        <v>47.64</v>
+        <v>50.4</v>
       </c>
       <c r="H181" t="n">
-        <v>-2.06</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>-93.65000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C182" t="n">
-        <v>5.00778777</v>
+        <v>5.02274277</v>
       </c>
       <c r="D182" t="n">
-        <v>47.64</v>
+        <v>50.55</v>
       </c>
       <c r="E182" t="n">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="F182" t="n">
-        <v>47.22</v>
+        <v>48.2</v>
       </c>
       <c r="G182" t="n">
-        <v>48.96</v>
+        <v>48.94</v>
       </c>
       <c r="H182" t="n">
-        <v>2.77</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>28.06</v>
+        <v>7.54</v>
       </c>
       <c r="C183" t="n">
-        <v>5.01059377</v>
+        <v>5.02349677</v>
       </c>
       <c r="D183" t="n">
-        <v>48.36</v>
+        <v>49.96</v>
       </c>
       <c r="E183" t="n">
-        <v>48.76</v>
+        <v>49.98</v>
       </c>
       <c r="F183" t="n">
-        <v>47.52</v>
+        <v>48.72</v>
       </c>
       <c r="G183" t="n">
-        <v>47.98</v>
+        <v>49.12</v>
       </c>
       <c r="H183" t="n">
-        <v>-2</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>-160.94</v>
+        <v>29.93</v>
       </c>
       <c r="C184" t="n">
-        <v>4.99449977</v>
+        <v>5.02648977</v>
       </c>
       <c r="D184" t="n">
-        <v>47.98</v>
+        <v>49.1</v>
       </c>
       <c r="E184" t="n">
-        <v>48.46</v>
+        <v>49.36</v>
       </c>
       <c r="F184" t="n">
-        <v>47.32</v>
+        <v>48.18</v>
       </c>
       <c r="G184" t="n">
-        <v>48.08</v>
+        <v>48.64</v>
       </c>
       <c r="H184" t="n">
-        <v>0.21</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>76.84999999999999</v>
+        <v>-93.37</v>
       </c>
       <c r="C185" t="n">
-        <v>5.00218477</v>
+        <v>5.01715277</v>
       </c>
       <c r="D185" t="n">
-        <v>49.54</v>
+        <v>48.4</v>
       </c>
       <c r="E185" t="n">
-        <v>50.5</v>
+        <v>48.4</v>
       </c>
       <c r="F185" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="G185" t="n">
-        <v>49.68</v>
+        <v>47.64</v>
       </c>
       <c r="H185" t="n">
-        <v>3.33</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-70.88</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C186" t="n">
-        <v>4.99509677</v>
+        <v>5.00778777</v>
       </c>
       <c r="D186" t="n">
-        <v>51.9</v>
+        <v>47.64</v>
       </c>
       <c r="E186" t="n">
-        <v>55.6</v>
+        <v>49.3</v>
       </c>
       <c r="F186" t="n">
-        <v>51.9</v>
+        <v>47.22</v>
       </c>
       <c r="G186" t="n">
-        <v>54.6</v>
+        <v>48.96</v>
       </c>
       <c r="H186" t="n">
-        <v>9.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>-223.97</v>
+        <v>28.06</v>
       </c>
       <c r="C187" t="n">
-        <v>4.97269977</v>
+        <v>5.01059377</v>
       </c>
       <c r="D187" t="n">
-        <v>54.7</v>
+        <v>48.36</v>
       </c>
       <c r="E187" t="n">
-        <v>56.1</v>
+        <v>48.76</v>
       </c>
       <c r="F187" t="n">
-        <v>53.7</v>
+        <v>47.52</v>
       </c>
       <c r="G187" t="n">
-        <v>54.25</v>
+        <v>47.98</v>
       </c>
       <c r="H187" t="n">
-        <v>-0.64</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-908.88</v>
+        <v>-160.94</v>
       </c>
       <c r="C188" t="n">
-        <v>4.88181177</v>
+        <v>4.99449977</v>
       </c>
       <c r="D188" t="n">
-        <v>52.85</v>
+        <v>47.98</v>
       </c>
       <c r="E188" t="n">
-        <v>53.8</v>
+        <v>48.46</v>
       </c>
       <c r="F188" t="n">
-        <v>51.3</v>
+        <v>47.32</v>
       </c>
       <c r="G188" t="n">
-        <v>53.4</v>
+        <v>48.08</v>
       </c>
       <c r="H188" t="n">
-        <v>-1.57</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>-219</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C189" t="n">
-        <v>4.85991177</v>
+        <v>5.00218477</v>
       </c>
       <c r="D189" t="n">
-        <v>52.75</v>
+        <v>49.54</v>
       </c>
       <c r="E189" t="n">
-        <v>54.45</v>
+        <v>50.5</v>
       </c>
       <c r="F189" t="n">
-        <v>51.45</v>
+        <v>48.9</v>
       </c>
       <c r="G189" t="n">
-        <v>51.85</v>
+        <v>49.68</v>
       </c>
       <c r="H189" t="n">
-        <v>-2.9</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>81.19</v>
+        <v>-70.88</v>
       </c>
       <c r="C190" t="n">
-        <v>4.86803077</v>
+        <v>4.99509677</v>
       </c>
       <c r="D190" t="n">
-        <v>51.85</v>
+        <v>51.9</v>
       </c>
       <c r="E190" t="n">
-        <v>51.85</v>
+        <v>55.6</v>
       </c>
       <c r="F190" t="n">
-        <v>49.6</v>
+        <v>51.9</v>
       </c>
       <c r="G190" t="n">
-        <v>50.45</v>
+        <v>54.6</v>
       </c>
       <c r="H190" t="n">
-        <v>-2.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>7.21</v>
+        <v>-223.97</v>
       </c>
       <c r="C191" t="n">
-        <v>4.86875177</v>
+        <v>4.97269977</v>
       </c>
       <c r="D191" t="n">
-        <v>50.05</v>
+        <v>54.7</v>
       </c>
       <c r="E191" t="n">
-        <v>50.8</v>
+        <v>56.1</v>
       </c>
       <c r="F191" t="n">
-        <v>49.52</v>
+        <v>53.7</v>
       </c>
       <c r="G191" t="n">
-        <v>50.65</v>
+        <v>54.25</v>
       </c>
       <c r="H191" t="n">
-        <v>0.4</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>144.28</v>
+        <v>-908.88</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88317977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D192" t="n">
-        <v>50</v>
+        <v>52.85</v>
       </c>
       <c r="E192" t="n">
-        <v>50.6</v>
+        <v>53.8</v>
       </c>
       <c r="F192" t="n">
-        <v>49.08</v>
+        <v>51.3</v>
       </c>
       <c r="G192" t="n">
-        <v>49.12</v>
+        <v>53.4</v>
       </c>
       <c r="H192" t="n">
-        <v>-3.02</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-41.02</v>
+        <v>-219</v>
       </c>
       <c r="C193" t="n">
-        <v>4.87907777</v>
+        <v>4.85991177</v>
       </c>
       <c r="D193" t="n">
-        <v>49.18</v>
+        <v>52.75</v>
       </c>
       <c r="E193" t="n">
-        <v>50.1</v>
+        <v>54.45</v>
       </c>
       <c r="F193" t="n">
-        <v>48.82</v>
+        <v>51.45</v>
       </c>
       <c r="G193" t="n">
-        <v>49.92</v>
+        <v>51.85</v>
       </c>
       <c r="H193" t="n">
-        <v>1.63</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>68.70999999999999</v>
+        <v>81.19</v>
       </c>
       <c r="C194" t="n">
-        <v>4.88594877</v>
+        <v>4.86803077</v>
       </c>
       <c r="D194" t="n">
-        <v>50.5</v>
+        <v>51.85</v>
       </c>
       <c r="E194" t="n">
-        <v>50.95</v>
+        <v>51.85</v>
       </c>
       <c r="F194" t="n">
-        <v>49.74</v>
+        <v>49.6</v>
       </c>
       <c r="G194" t="n">
-        <v>50.1</v>
+        <v>50.45</v>
       </c>
       <c r="H194" t="n">
-        <v>0.36</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>20.01</v>
+        <v>7.21</v>
       </c>
       <c r="C195" t="n">
-        <v>4.88794977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D195" t="n">
-        <v>50</v>
+        <v>50.05</v>
       </c>
       <c r="E195" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F195" t="n">
-        <v>49.04</v>
+        <v>49.52</v>
       </c>
       <c r="G195" t="n">
-        <v>49.06</v>
+        <v>50.65</v>
       </c>
       <c r="H195" t="n">
-        <v>-2.08</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>-18.77</v>
+        <v>144.28</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88607277</v>
+        <v>4.88317977</v>
       </c>
       <c r="D196" t="n">
+        <v>50</v>
+      </c>
+      <c r="E196" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="F196" t="n">
         <v>49.08</v>
       </c>
-      <c r="E196" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="F196" t="n">
-        <v>48.7</v>
-      </c>
       <c r="G196" t="n">
-        <v>49.4</v>
+        <v>49.12</v>
       </c>
       <c r="H196" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>95.14</v>
+        <v>-41.02</v>
       </c>
       <c r="C197" t="n">
-        <v>4.89558677</v>
+        <v>4.87907777</v>
       </c>
       <c r="D197" t="n">
-        <v>48.66</v>
+        <v>49.18</v>
       </c>
       <c r="E197" t="n">
-        <v>49.22</v>
+        <v>50.1</v>
       </c>
       <c r="F197" t="n">
-        <v>48.02</v>
+        <v>48.82</v>
       </c>
       <c r="G197" t="n">
-        <v>48.22</v>
+        <v>49.92</v>
       </c>
       <c r="H197" t="n">
-        <v>-2.39</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>6.47</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C198" t="n">
-        <v>4.89623377</v>
+        <v>4.88594877</v>
       </c>
       <c r="D198" t="n">
-        <v>48.22</v>
+        <v>50.5</v>
       </c>
       <c r="E198" t="n">
-        <v>48.22</v>
+        <v>50.95</v>
       </c>
       <c r="F198" t="n">
-        <v>47.46</v>
+        <v>49.74</v>
       </c>
       <c r="G198" t="n">
-        <v>47.46</v>
+        <v>50.1</v>
       </c>
       <c r="H198" t="n">
-        <v>-1.58</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>78.34</v>
+        <v>20.01</v>
       </c>
       <c r="C199" t="n">
-        <v>4.90406777</v>
+        <v>4.88794977</v>
       </c>
       <c r="D199" t="n">
-        <v>47.86</v>
+        <v>50</v>
       </c>
       <c r="E199" t="n">
-        <v>48.68</v>
+        <v>50.5</v>
       </c>
       <c r="F199" t="n">
-        <v>47.7</v>
+        <v>49.04</v>
       </c>
       <c r="G199" t="n">
-        <v>48.48</v>
+        <v>49.06</v>
       </c>
       <c r="H199" t="n">
-        <v>2.15</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>12.2</v>
+        <v>-18.77</v>
       </c>
       <c r="C200" t="n">
-        <v>4.90528777</v>
+        <v>4.88607277</v>
       </c>
       <c r="D200" t="n">
-        <v>48.1</v>
+        <v>49.08</v>
       </c>
       <c r="E200" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="F200" t="n">
         <v>48.7</v>
       </c>
-      <c r="F200" t="n">
-        <v>47.38</v>
-      </c>
       <c r="G200" t="n">
-        <v>47.88</v>
+        <v>49.4</v>
       </c>
       <c r="H200" t="n">
-        <v>-1.24</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>-50.42</v>
+        <v>95.14</v>
       </c>
       <c r="C201" t="n">
-        <v>4.90024577</v>
+        <v>4.89558677</v>
       </c>
       <c r="D201" t="n">
-        <v>47.34</v>
+        <v>48.66</v>
       </c>
       <c r="E201" t="n">
-        <v>48.28</v>
+        <v>49.22</v>
       </c>
       <c r="F201" t="n">
-        <v>47.06</v>
+        <v>48.02</v>
       </c>
       <c r="G201" t="n">
-        <v>47.9</v>
+        <v>48.22</v>
       </c>
       <c r="H201" t="n">
-        <v>0.04</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>7.38</v>
+        <v>6.47</v>
       </c>
       <c r="C202" t="n">
-        <v>4.90098377</v>
+        <v>4.89623377</v>
       </c>
       <c r="D202" t="n">
-        <v>49.98</v>
+        <v>48.22</v>
       </c>
       <c r="E202" t="n">
-        <v>51.2</v>
+        <v>48.22</v>
       </c>
       <c r="F202" t="n">
-        <v>49.76</v>
+        <v>47.46</v>
       </c>
       <c r="G202" t="n">
-        <v>50.55</v>
+        <v>47.46</v>
       </c>
       <c r="H202" t="n">
-        <v>5.53</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.19</v>
+        <v>78.34</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90100277</v>
+        <v>4.90406777</v>
       </c>
       <c r="D203" t="n">
-        <v>50.55</v>
+        <v>47.86</v>
       </c>
       <c r="E203" t="n">
-        <v>51.8</v>
+        <v>48.68</v>
       </c>
       <c r="F203" t="n">
-        <v>50.5</v>
+        <v>47.7</v>
       </c>
       <c r="G203" t="n">
-        <v>51.2</v>
+        <v>48.48</v>
       </c>
       <c r="H203" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>-404.07</v>
+        <v>12.2</v>
       </c>
       <c r="C204" t="n">
-        <v>4.86059577</v>
+        <v>4.90528777</v>
       </c>
       <c r="D204" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="E204" t="n">
-        <v>51</v>
+        <v>48.7</v>
       </c>
       <c r="F204" t="n">
-        <v>49.3</v>
+        <v>47.38</v>
       </c>
       <c r="G204" t="n">
-        <v>49.46</v>
+        <v>47.88</v>
       </c>
       <c r="H204" t="n">
-        <v>-3.4</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-104.42</v>
+        <v>-50.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.85015377</v>
+        <v>4.90024577</v>
       </c>
       <c r="D205" t="n">
-        <v>48.86</v>
+        <v>47.34</v>
       </c>
       <c r="E205" t="n">
-        <v>49.74</v>
+        <v>48.28</v>
       </c>
       <c r="F205" t="n">
-        <v>47.6</v>
+        <v>47.06</v>
       </c>
       <c r="G205" t="n">
-        <v>47.68</v>
+        <v>47.9</v>
       </c>
       <c r="H205" t="n">
-        <v>-3.6</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>-9.27</v>
+        <v>7.38</v>
       </c>
       <c r="C206" t="n">
-        <v>4.84922677</v>
+        <v>4.90098377</v>
       </c>
       <c r="D206" t="n">
-        <v>47.68</v>
+        <v>49.98</v>
       </c>
       <c r="E206" t="n">
-        <v>48.9</v>
+        <v>51.2</v>
       </c>
       <c r="F206" t="n">
-        <v>47.32</v>
+        <v>49.76</v>
       </c>
       <c r="G206" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="H206" t="n">
-        <v>0.88</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>-62.41</v>
+        <v>0.19</v>
       </c>
       <c r="C207" t="n">
-        <v>4.84298577</v>
+        <v>4.90100277</v>
       </c>
       <c r="D207" t="n">
-        <v>48.1</v>
+        <v>50.55</v>
       </c>
       <c r="E207" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="F207" t="n">
-        <v>47.5</v>
+        <v>50.5</v>
       </c>
       <c r="G207" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="H207" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-4.06</v>
+        <v>-404.07</v>
       </c>
       <c r="C208" t="n">
-        <v>4.84257977</v>
+        <v>4.86059577</v>
       </c>
       <c r="D208" t="n">
-        <v>47.8</v>
+        <v>50.3</v>
       </c>
       <c r="E208" t="n">
-        <v>48.6</v>
+        <v>51</v>
       </c>
       <c r="F208" t="n">
-        <v>47.16</v>
+        <v>49.3</v>
       </c>
       <c r="G208" t="n">
-        <v>47.98</v>
+        <v>49.46</v>
       </c>
       <c r="H208" t="n">
-        <v>-1.28</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>107.65</v>
+        <v>-104.42</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85334477</v>
+        <v>4.85015377</v>
       </c>
       <c r="D209" t="n">
-        <v>47.86</v>
+        <v>48.86</v>
       </c>
       <c r="E209" t="n">
-        <v>48.44</v>
+        <v>49.74</v>
       </c>
       <c r="F209" t="n">
-        <v>46.5</v>
+        <v>47.6</v>
       </c>
       <c r="G209" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="H209" t="n">
-        <v>-0.33</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>137.46</v>
+        <v>-9.27</v>
       </c>
       <c r="C210" t="n">
-        <v>4.86709077</v>
+        <v>4.84922677</v>
       </c>
       <c r="D210" t="n">
-        <v>47.82</v>
+        <v>47.68</v>
       </c>
       <c r="E210" t="n">
-        <v>48.22</v>
+        <v>48.9</v>
       </c>
       <c r="F210" t="n">
-        <v>46.6</v>
+        <v>47.32</v>
       </c>
       <c r="G210" t="n">
-        <v>47.06</v>
+        <v>48.1</v>
       </c>
       <c r="H210" t="n">
-        <v>-1.59</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>154.04</v>
+        <v>-62.41</v>
       </c>
       <c r="C211" t="n">
-        <v>4.88249477</v>
+        <v>4.84298577</v>
       </c>
       <c r="D211" t="n">
-        <v>46.68</v>
+        <v>48.1</v>
       </c>
       <c r="E211" t="n">
-        <v>46.76</v>
+        <v>49</v>
       </c>
       <c r="F211" t="n">
-        <v>44.56</v>
+        <v>47.5</v>
       </c>
       <c r="G211" t="n">
-        <v>45.86</v>
+        <v>48.6</v>
       </c>
       <c r="H211" t="n">
-        <v>-2.55</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>78.03</v>
+        <v>-4.06</v>
       </c>
       <c r="C212" t="n">
-        <v>4.89029777</v>
+        <v>4.84257977</v>
       </c>
       <c r="D212" t="n">
-        <v>46.56</v>
+        <v>47.8</v>
       </c>
       <c r="E212" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="F212" t="n">
-        <v>46.2</v>
+        <v>47.16</v>
       </c>
       <c r="G212" t="n">
-        <v>46.38</v>
+        <v>47.98</v>
       </c>
       <c r="H212" t="n">
-        <v>1.13</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>401.67</v>
+        <v>107.65</v>
       </c>
       <c r="C213" t="n">
-        <v>4.93046477</v>
+        <v>4.85334477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.28</v>
+        <v>47.86</v>
       </c>
       <c r="E213" t="n">
-        <v>48.88</v>
+        <v>48.44</v>
       </c>
       <c r="F213" t="n">
-        <v>47.12</v>
+        <v>46.5</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>3.1</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>-79.33</v>
+        <v>137.46</v>
       </c>
       <c r="C214" t="n">
-        <v>4.92253177</v>
+        <v>4.86709077</v>
       </c>
       <c r="D214" t="n">
-        <v>48.1</v>
+        <v>47.82</v>
       </c>
       <c r="E214" t="n">
-        <v>50.45</v>
+        <v>48.22</v>
       </c>
       <c r="F214" t="n">
-        <v>48.04</v>
+        <v>46.6</v>
       </c>
       <c r="G214" t="n">
-        <v>50.4</v>
+        <v>47.06</v>
       </c>
       <c r="H214" t="n">
-        <v>5.4</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>-415.48</v>
+        <v>154.04</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88098377</v>
+        <v>4.88249477</v>
       </c>
       <c r="D215" t="n">
-        <v>49.44</v>
+        <v>46.68</v>
       </c>
       <c r="E215" t="n">
-        <v>50.15</v>
+        <v>46.76</v>
       </c>
       <c r="F215" t="n">
-        <v>48.88</v>
+        <v>44.56</v>
       </c>
       <c r="G215" t="n">
-        <v>49.32</v>
+        <v>45.86</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.14</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>-394.96</v>
+        <v>78.03</v>
       </c>
       <c r="C216" t="n">
-        <v>4.84148777</v>
+        <v>4.89029777</v>
       </c>
       <c r="D216" t="n">
-        <v>49.08</v>
+        <v>46.56</v>
       </c>
       <c r="E216" t="n">
-        <v>49.08</v>
+        <v>48</v>
       </c>
       <c r="F216" t="n">
-        <v>47.2</v>
+        <v>46.2</v>
       </c>
       <c r="G216" t="n">
-        <v>47.62</v>
+        <v>46.38</v>
       </c>
       <c r="H216" t="n">
-        <v>-3.45</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>-39.23</v>
+        <v>401.67</v>
       </c>
       <c r="C217" t="n">
-        <v>4.83756477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.2</v>
+        <v>47.28</v>
       </c>
       <c r="E217" t="n">
-        <v>47.2</v>
+        <v>48.88</v>
       </c>
       <c r="F217" t="n">
-        <v>46.42</v>
+        <v>47.12</v>
       </c>
       <c r="G217" t="n">
-        <v>46.48</v>
+        <v>47.82</v>
       </c>
       <c r="H217" t="n">
-        <v>-2.39</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>219.67</v>
+        <v>-79.33</v>
       </c>
       <c r="C218" t="n">
-        <v>4.85953177</v>
+        <v>4.92253177</v>
       </c>
       <c r="D218" t="n">
-        <v>45.74</v>
+        <v>48.1</v>
       </c>
       <c r="E218" t="n">
-        <v>46.44</v>
+        <v>50.45</v>
       </c>
       <c r="F218" t="n">
-        <v>45.38</v>
+        <v>48.04</v>
       </c>
       <c r="G218" t="n">
-        <v>46.34</v>
+        <v>50.4</v>
       </c>
       <c r="H218" t="n">
-        <v>-0.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>111.68</v>
+        <v>-415.48</v>
       </c>
       <c r="C219" t="n">
-        <v>4.87069977</v>
+        <v>4.88098377</v>
       </c>
       <c r="D219" t="n">
-        <v>45.9</v>
+        <v>49.44</v>
       </c>
       <c r="E219" t="n">
-        <v>47.8</v>
+        <v>50.15</v>
       </c>
       <c r="F219" t="n">
-        <v>45.84</v>
+        <v>48.88</v>
       </c>
       <c r="G219" t="n">
-        <v>47.52</v>
+        <v>49.32</v>
       </c>
       <c r="H219" t="n">
-        <v>2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>47.5</v>
+        <v>-394.96</v>
       </c>
       <c r="C220" t="n">
-        <v>4.87544977</v>
+        <v>4.84148777</v>
       </c>
       <c r="D220" t="n">
-        <v>47.52</v>
+        <v>49.08</v>
       </c>
       <c r="E220" t="n">
-        <v>48.06</v>
+        <v>49.08</v>
       </c>
       <c r="F220" t="n">
-        <v>46.06</v>
+        <v>47.2</v>
       </c>
       <c r="G220" t="n">
-        <v>46.12</v>
+        <v>47.62</v>
       </c>
       <c r="H220" t="n">
-        <v>-2.95</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-30.32</v>
+        <v>-39.23</v>
       </c>
       <c r="C221" t="n">
-        <v>4.87241777</v>
+        <v>4.83756477</v>
       </c>
       <c r="D221" t="n">
-        <v>46.92</v>
+        <v>47.2</v>
       </c>
       <c r="E221" t="n">
-        <v>47.42</v>
+        <v>47.2</v>
       </c>
       <c r="F221" t="n">
-        <v>45.94</v>
+        <v>46.42</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>0.78</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>15.46</v>
+        <v>219.67</v>
       </c>
       <c r="C222" t="n">
-        <v>4.87396377</v>
+        <v>4.85953177</v>
       </c>
       <c r="D222" t="n">
-        <v>46.9</v>
+        <v>45.74</v>
       </c>
       <c r="E222" t="n">
-        <v>47.5</v>
+        <v>46.44</v>
       </c>
       <c r="F222" t="n">
-        <v>44.94</v>
+        <v>45.38</v>
       </c>
       <c r="G222" t="n">
-        <v>46.88</v>
+        <v>46.34</v>
       </c>
       <c r="H222" t="n">
-        <v>0.86</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>57.59</v>
+        <v>111.68</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87972277</v>
+        <v>4.87069977</v>
       </c>
       <c r="D223" t="n">
-        <v>46.9</v>
+        <v>45.9</v>
       </c>
       <c r="E223" t="n">
-        <v>48.46</v>
+        <v>47.8</v>
       </c>
       <c r="F223" t="n">
-        <v>46.8</v>
+        <v>45.84</v>
       </c>
       <c r="G223" t="n">
-        <v>47.56</v>
+        <v>47.52</v>
       </c>
       <c r="H223" t="n">
-        <v>1.45</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>112.19</v>
+        <v>47.5</v>
       </c>
       <c r="C224" t="n">
-        <v>4.89094177</v>
+        <v>4.87544977</v>
       </c>
       <c r="D224" t="n">
-        <v>47.54</v>
+        <v>47.52</v>
       </c>
       <c r="E224" t="n">
-        <v>47.54</v>
+        <v>48.06</v>
       </c>
       <c r="F224" t="n">
-        <v>44.82</v>
+        <v>46.06</v>
       </c>
       <c r="G224" t="n">
-        <v>45.48</v>
+        <v>46.12</v>
       </c>
       <c r="H224" t="n">
-        <v>-4.37</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-42.06</v>
+        <v>-30.32</v>
       </c>
       <c r="C225" t="n">
-        <v>4.88673577</v>
+        <v>4.87241777</v>
       </c>
       <c r="D225" t="n">
-        <v>45</v>
+        <v>46.92</v>
       </c>
       <c r="E225" t="n">
-        <v>45.8</v>
+        <v>47.42</v>
       </c>
       <c r="F225" t="n">
-        <v>44.68</v>
+        <v>45.94</v>
       </c>
       <c r="G225" t="n">
-        <v>45.08</v>
+        <v>46.48</v>
       </c>
       <c r="H225" t="n">
-        <v>-0.88</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>201.66</v>
+        <v>15.46</v>
       </c>
       <c r="C226" t="n">
-        <v>4.90690177</v>
+        <v>4.87396377</v>
       </c>
       <c r="D226" t="n">
-        <v>45.72</v>
+        <v>46.9</v>
       </c>
       <c r="E226" t="n">
-        <v>46.54</v>
+        <v>47.5</v>
       </c>
       <c r="F226" t="n">
-        <v>45.34</v>
+        <v>44.94</v>
       </c>
       <c r="G226" t="n">
-        <v>46.24</v>
+        <v>46.88</v>
       </c>
       <c r="H226" t="n">
-        <v>2.57</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>138.5</v>
+        <v>57.59</v>
       </c>
       <c r="C227" t="n">
-        <v>4.92075177</v>
+        <v>4.87972277</v>
       </c>
       <c r="D227" t="n">
-        <v>45.48</v>
+        <v>46.9</v>
       </c>
       <c r="E227" t="n">
-        <v>47.3</v>
+        <v>48.46</v>
       </c>
       <c r="F227" t="n">
-        <v>45.48</v>
+        <v>46.8</v>
       </c>
       <c r="G227" t="n">
-        <v>46.76</v>
+        <v>47.56</v>
       </c>
       <c r="H227" t="n">
-        <v>1.12</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>112.19</v>
       </c>
       <c r="C228" t="n">
-        <v>4.92075177</v>
+        <v>4.89094177</v>
       </c>
       <c r="D228" t="n">
-        <v>46.76</v>
+        <v>47.54</v>
       </c>
       <c r="E228" t="n">
-        <v>46.76</v>
+        <v>47.54</v>
       </c>
       <c r="F228" t="n">
-        <v>44.9</v>
+        <v>44.82</v>
       </c>
       <c r="G228" t="n">
-        <v>45.24</v>
+        <v>45.48</v>
       </c>
       <c r="H228" t="n">
-        <v>-3.25</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-223.74</v>
+        <v>-42.06</v>
       </c>
       <c r="C229" t="n">
-        <v>4.89837777</v>
+        <v>4.88673577</v>
       </c>
       <c r="D229" t="n">
-        <v>45.38</v>
+        <v>45</v>
       </c>
       <c r="E229" t="n">
-        <v>46.84</v>
+        <v>45.8</v>
       </c>
       <c r="F229" t="n">
-        <v>45.36</v>
+        <v>44.68</v>
       </c>
       <c r="G229" t="n">
-        <v>45.74</v>
+        <v>45.08</v>
       </c>
       <c r="H229" t="n">
-        <v>1.11</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>201.66</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4.90690177</v>
+      </c>
+      <c r="D230" t="n">
+        <v>45.72</v>
+      </c>
+      <c r="E230" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="F230" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="G230" t="n">
+        <v>46.24</v>
+      </c>
+      <c r="H230" t="n">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4.92075177</v>
+      </c>
+      <c r="D231" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="E231" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="F231" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="G231" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" t="n">
+        <v>4.92075177</v>
+      </c>
+      <c r="D232" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="E232" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="F232" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G232" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="H232" t="n">
+        <v>-3.25</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>-223.74</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4.89837777</v>
+      </c>
+      <c r="D233" t="n">
+        <v>45.38</v>
+      </c>
+      <c r="E233" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="F233" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="G233" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="H233" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="B230" t="n">
+      <c r="B234" t="n">
         <v>0</v>
       </c>
-      <c r="C230" t="n">
+      <c r="C234" t="n">
         <v>4.89837777</v>
       </c>
-      <c r="D230" t="n">
+      <c r="D234" t="n">
         <v>45.86</v>
       </c>
-      <c r="E230" t="n">
+      <c r="E234" t="n">
         <v>45.86</v>
       </c>
-      <c r="F230" t="n">
+      <c r="F234" t="n">
         <v>44.3</v>
       </c>
-      <c r="G230" t="n">
+      <c r="G234" t="n">
         <v>44.54</v>
       </c>
-      <c r="H230" t="n">
+      <c r="H234" t="n">
         <v>-2.62</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H234"/>
+  <dimension ref="A1:H230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2627,7 +2627,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -2637,25 +2637,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D79" t="n">
-        <v>72.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E79" t="n">
-        <v>73.34999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="F79" t="n">
-        <v>71.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G79" t="n">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -2665,25 +2665,25 @@
         <v>5.29754581</v>
       </c>
       <c r="D80" t="n">
-        <v>72.8</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="E80" t="n">
-        <v>73.34999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="F80" t="n">
-        <v>71.5</v>
+        <v>69.55</v>
       </c>
       <c r="G80" t="n">
-        <v>72.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -2693,4302 +2693,4190 @@
         <v>5.29754581</v>
       </c>
       <c r="D81" t="n">
-        <v>72.8</v>
+        <v>70.3</v>
       </c>
       <c r="E81" t="n">
-        <v>73.34999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="F81" t="n">
-        <v>71.5</v>
+        <v>70.3</v>
       </c>
       <c r="G81" t="n">
-        <v>72.3</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0</v>
+        <v>-37.37</v>
       </c>
       <c r="C82" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D82" t="n">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="E82" t="n">
-        <v>72.25</v>
+        <v>73.5</v>
       </c>
       <c r="F82" t="n">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G82" t="n">
-        <v>72.09999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.28</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>5.29754581</v>
+        <v>5.29380881</v>
       </c>
       <c r="D83" t="n">
-        <v>71.34999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E83" t="n">
-        <v>71.75</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F83" t="n">
-        <v>69.55</v>
+        <v>70.5</v>
       </c>
       <c r="G83" t="n">
-        <v>70.09999999999999</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="H83" t="n">
-        <v>-2.77</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0</v>
+        <v>39.15</v>
       </c>
       <c r="C84" t="n">
-        <v>5.29754581</v>
+        <v>5.29772381</v>
       </c>
       <c r="D84" t="n">
-        <v>70.3</v>
+        <v>71</v>
       </c>
       <c r="E84" t="n">
-        <v>73.3</v>
+        <v>71.8</v>
       </c>
       <c r="F84" t="n">
-        <v>70.3</v>
+        <v>68.55</v>
       </c>
       <c r="G84" t="n">
-        <v>72.84999999999999</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>3.92</v>
+        <v>-4.45</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>-37.37</v>
+        <v>-32.03</v>
       </c>
       <c r="C85" t="n">
-        <v>5.29380881</v>
+        <v>5.29452081</v>
       </c>
       <c r="D85" t="n">
-        <v>71.8</v>
+        <v>69.5</v>
       </c>
       <c r="E85" t="n">
-        <v>73.5</v>
+        <v>69.5</v>
       </c>
       <c r="F85" t="n">
-        <v>71.3</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>71.75</v>
+        <v>68.75</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.51</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>-245.51</v>
       </c>
       <c r="C86" t="n">
-        <v>5.29380881</v>
+        <v>5.26996981</v>
       </c>
       <c r="D86" t="n">
-        <v>72.8</v>
+        <v>67.75</v>
       </c>
       <c r="E86" t="n">
-        <v>73.15000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="F86" t="n">
-        <v>70.5</v>
+        <v>67</v>
       </c>
       <c r="G86" t="n">
-        <v>71.84999999999999</v>
+        <v>68</v>
       </c>
       <c r="H86" t="n">
-        <v>0.14</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>39.15</v>
+        <v>24.99</v>
       </c>
       <c r="C87" t="n">
-        <v>5.29772381</v>
+        <v>5.27246881</v>
       </c>
       <c r="D87" t="n">
-        <v>71</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="E87" t="n">
-        <v>71.8</v>
+        <v>69</v>
       </c>
       <c r="F87" t="n">
-        <v>68.55</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>68.65000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="H87" t="n">
-        <v>-4.45</v>
+        <v>-2.13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>-32.03</v>
+        <v>-70.5937</v>
       </c>
       <c r="C88" t="n">
-        <v>5.29452081</v>
+        <v>5.26540944</v>
       </c>
       <c r="D88" t="n">
-        <v>69.5</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E88" t="n">
-        <v>69.5</v>
+        <v>66.8</v>
       </c>
       <c r="F88" t="n">
-        <v>68.15000000000001</v>
+        <v>64.45</v>
       </c>
       <c r="G88" t="n">
-        <v>68.75</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H88" t="n">
-        <v>0.15</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>-245.51</v>
+        <v>-83.42</v>
       </c>
       <c r="C89" t="n">
-        <v>5.26996981</v>
+        <v>5.25706744</v>
       </c>
       <c r="D89" t="n">
-        <v>67.75</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="E89" t="n">
-        <v>70.15000000000001</v>
+        <v>68</v>
       </c>
       <c r="F89" t="n">
-        <v>67</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G89" t="n">
-        <v>68</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>-1.09</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>24.99</v>
+        <v>32.9872</v>
       </c>
       <c r="C90" t="n">
-        <v>5.27246881</v>
+        <v>5.26036616</v>
       </c>
       <c r="D90" t="n">
-        <v>68.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="E90" t="n">
-        <v>69</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F90" t="n">
-        <v>65.65000000000001</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>66.55</v>
+        <v>67.45</v>
       </c>
       <c r="H90" t="n">
-        <v>-2.13</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>-70.5937</v>
+        <v>-168.98</v>
       </c>
       <c r="C91" t="n">
-        <v>5.26540944</v>
+        <v>5.24346816</v>
       </c>
       <c r="D91" t="n">
-        <v>65.84999999999999</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E91" t="n">
-        <v>66.8</v>
+        <v>69</v>
       </c>
       <c r="F91" t="n">
-        <v>64.45</v>
+        <v>64.7</v>
       </c>
       <c r="G91" t="n">
-        <v>65.84999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>-1.05</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>-83.42</v>
+        <v>-195.54</v>
       </c>
       <c r="C92" t="n">
-        <v>5.25706744</v>
+        <v>5.22391416</v>
       </c>
       <c r="D92" t="n">
-        <v>66.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E92" t="n">
-        <v>68</v>
+        <v>70.2</v>
       </c>
       <c r="F92" t="n">
-        <v>65.09999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="G92" t="n">
-        <v>65.59999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="H92" t="n">
-        <v>-0.38</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>32.9872</v>
+        <v>16.18</v>
       </c>
       <c r="C93" t="n">
-        <v>5.26036616</v>
+        <v>5.22553216</v>
       </c>
       <c r="D93" t="n">
-        <v>65.5</v>
+        <v>69.25</v>
       </c>
       <c r="E93" t="n">
-        <v>67.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.34999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="G93" t="n">
-        <v>67.45</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>2.82</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>-168.98</v>
+        <v>13.87</v>
       </c>
       <c r="C94" t="n">
-        <v>5.24346816</v>
+        <v>5.22691916</v>
       </c>
       <c r="D94" t="n">
-        <v>64.84999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E94" t="n">
-        <v>69</v>
+        <v>71.3</v>
       </c>
       <c r="F94" t="n">
-        <v>64.7</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="G94" t="n">
-        <v>68.90000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>2.15</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>-195.54</v>
+        <v>-145.08</v>
       </c>
       <c r="C95" t="n">
-        <v>5.22391416</v>
+        <v>5.21241116</v>
       </c>
       <c r="D95" t="n">
-        <v>69.90000000000001</v>
+        <v>68.95</v>
       </c>
       <c r="E95" t="n">
-        <v>70.2</v>
+        <v>69</v>
       </c>
       <c r="F95" t="n">
-        <v>67.95</v>
+        <v>67.3</v>
       </c>
       <c r="G95" t="n">
-        <v>69.05</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H95" t="n">
-        <v>0.22</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>16.18</v>
+        <v>25.02</v>
       </c>
       <c r="C96" t="n">
-        <v>5.22553216</v>
+        <v>5.21491316</v>
       </c>
       <c r="D96" t="n">
-        <v>69.25</v>
+        <v>67.5</v>
       </c>
       <c r="E96" t="n">
-        <v>70.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>69.05</v>
+        <v>66.3</v>
       </c>
       <c r="G96" t="n">
-        <v>69.84999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H96" t="n">
-        <v>1.16</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>13.87</v>
+        <v>-6.25</v>
       </c>
       <c r="C97" t="n">
-        <v>5.22691916</v>
+        <v>5.21428816</v>
       </c>
       <c r="D97" t="n">
-        <v>70.95</v>
+        <v>71.25</v>
       </c>
       <c r="E97" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>70.84999999999999</v>
+      </c>
+      <c r="G97" t="n">
         <v>71.3</v>
       </c>
-      <c r="F97" t="n">
-        <v>69.15000000000001</v>
-      </c>
-      <c r="G97" t="n">
-        <v>70.15000000000001</v>
-      </c>
       <c r="H97" t="n">
-        <v>0.43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>-145.08</v>
+        <v>-48.58</v>
       </c>
       <c r="C98" t="n">
-        <v>5.21241116</v>
+        <v>5.20943016</v>
       </c>
       <c r="D98" t="n">
-        <v>68.95</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E98" t="n">
-        <v>69</v>
+        <v>71.25</v>
       </c>
       <c r="F98" t="n">
-        <v>67.3</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G98" t="n">
-        <v>67.90000000000001</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="H98" t="n">
-        <v>-3.21</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>25.02</v>
+        <v>-197.18</v>
       </c>
       <c r="C99" t="n">
-        <v>5.21491316</v>
+        <v>5.18971216</v>
       </c>
       <c r="D99" t="n">
-        <v>67.5</v>
+        <v>66.2</v>
       </c>
       <c r="E99" t="n">
-        <v>70.09999999999999</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F99" t="n">
-        <v>66.3</v>
+        <v>65.8</v>
       </c>
       <c r="G99" t="n">
-        <v>69.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="H99" t="n">
-        <v>2.95</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>-6.25</v>
+        <v>426.64</v>
       </c>
       <c r="C100" t="n">
-        <v>5.21428816</v>
+        <v>5.23237616</v>
       </c>
       <c r="D100" t="n">
-        <v>71.25</v>
+        <v>67</v>
       </c>
       <c r="E100" t="n">
-        <v>73.3</v>
+        <v>68.7</v>
       </c>
       <c r="F100" t="n">
-        <v>70.84999999999999</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="G100" t="n">
-        <v>71.3</v>
+        <v>66.8</v>
       </c>
       <c r="H100" t="n">
-        <v>2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>-48.58</v>
+        <v>41.4993</v>
       </c>
       <c r="C101" t="n">
-        <v>5.20943016</v>
+        <v>5.23652609</v>
       </c>
       <c r="D101" t="n">
-        <v>70.65000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E101" t="n">
-        <v>71.25</v>
+        <v>66.05</v>
       </c>
       <c r="F101" t="n">
-        <v>66.34999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G101" t="n">
-        <v>66.84999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="H101" t="n">
-        <v>-6.24</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>-197.18</v>
+        <v>-220.5688</v>
       </c>
       <c r="C102" t="n">
-        <v>5.18971216</v>
+        <v>5.21446921</v>
       </c>
       <c r="D102" t="n">
         <v>66.2</v>
       </c>
       <c r="E102" t="n">
-        <v>67.34999999999999</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="F102" t="n">
-        <v>65.8</v>
+        <v>63.45</v>
       </c>
       <c r="G102" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H102" t="n">
-        <v>-1.27</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>426.64</v>
+        <v>215.27</v>
       </c>
       <c r="C103" t="n">
-        <v>5.23237616</v>
+        <v>5.23599621</v>
       </c>
       <c r="D103" t="n">
-        <v>67</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E103" t="n">
-        <v>68.7</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F103" t="n">
-        <v>66.34999999999999</v>
+        <v>69.45</v>
       </c>
       <c r="G103" t="n">
-        <v>66.8</v>
+        <v>70.45</v>
       </c>
       <c r="H103" t="n">
-        <v>1.21</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>41.4993</v>
+        <v>-160.53</v>
       </c>
       <c r="C104" t="n">
-        <v>5.23652609</v>
+        <v>5.21994321</v>
       </c>
       <c r="D104" t="n">
-        <v>65.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="E104" t="n">
-        <v>66.05</v>
+        <v>70.8</v>
       </c>
       <c r="F104" t="n">
-        <v>64.2</v>
+        <v>68.7</v>
       </c>
       <c r="G104" t="n">
-        <v>64.8</v>
+        <v>69</v>
       </c>
       <c r="H104" t="n">
-        <v>-2.99</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>-220.5688</v>
+        <v>-304.01</v>
       </c>
       <c r="C105" t="n">
-        <v>5.21446921</v>
+        <v>5.18954221</v>
       </c>
       <c r="D105" t="n">
-        <v>66.2</v>
+        <v>69</v>
       </c>
       <c r="E105" t="n">
-        <v>67.65000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="F105" t="n">
-        <v>63.45</v>
+        <v>68.3</v>
       </c>
       <c r="G105" t="n">
-        <v>67.59999999999999</v>
+        <v>70.05</v>
       </c>
       <c r="H105" t="n">
-        <v>4.32</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>215.27</v>
+        <v>-30.3</v>
       </c>
       <c r="C106" t="n">
-        <v>5.23599621</v>
+        <v>5.18651221</v>
       </c>
       <c r="D106" t="n">
-        <v>69.59999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="E106" t="n">
-        <v>71.34999999999999</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="F106" t="n">
-        <v>69.45</v>
+        <v>68</v>
       </c>
       <c r="G106" t="n">
-        <v>70.45</v>
+        <v>68.8</v>
       </c>
       <c r="H106" t="n">
-        <v>4.22</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>-160.53</v>
+        <v>-92.3</v>
       </c>
       <c r="C107" t="n">
-        <v>5.21994321</v>
+        <v>5.17728221</v>
       </c>
       <c r="D107" t="n">
-        <v>69.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="E107" t="n">
-        <v>70.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F107" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
       <c r="G107" t="n">
-        <v>69</v>
+        <v>67.7</v>
       </c>
       <c r="H107" t="n">
-        <v>-2.06</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>-304.01</v>
+        <v>25.43</v>
       </c>
       <c r="C108" t="n">
-        <v>5.18954221</v>
+        <v>5.17982521</v>
       </c>
       <c r="D108" t="n">
-        <v>69</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E108" t="n">
-        <v>71.5</v>
+        <v>71.45</v>
       </c>
       <c r="F108" t="n">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G108" t="n">
-        <v>70.05</v>
+        <v>71.2</v>
       </c>
       <c r="H108" t="n">
-        <v>1.52</v>
+        <v>5.17</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>-30.3</v>
+        <v>136.53</v>
       </c>
       <c r="C109" t="n">
-        <v>5.18651221</v>
+        <v>5.19347821</v>
       </c>
       <c r="D109" t="n">
-        <v>68.05</v>
+        <v>71.2</v>
       </c>
       <c r="E109" t="n">
-        <v>69.34999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="F109" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G109" t="n">
-        <v>68.8</v>
+        <v>71.8</v>
       </c>
       <c r="H109" t="n">
-        <v>-1.78</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>-92.3</v>
+        <v>-224.29</v>
       </c>
       <c r="C110" t="n">
-        <v>5.17728221</v>
+        <v>5.17104921</v>
       </c>
       <c r="D110" t="n">
-        <v>68.8</v>
+        <v>73.45</v>
       </c>
       <c r="E110" t="n">
-        <v>69.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="F110" t="n">
-        <v>67.2</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G110" t="n">
-        <v>67.7</v>
+        <v>73.3</v>
       </c>
       <c r="H110" t="n">
-        <v>-1.6</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>25.43</v>
+        <v>97.7422</v>
       </c>
       <c r="C111" t="n">
-        <v>5.17982521</v>
+        <v>5.18082343</v>
       </c>
       <c r="D111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="E111" t="n">
-        <v>71.45</v>
+        <v>73.5</v>
       </c>
       <c r="F111" t="n">
-        <v>68.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G111" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H111" t="n">
-        <v>5.17</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>136.53</v>
+        <v>-116.85</v>
       </c>
       <c r="C112" t="n">
-        <v>5.19347821</v>
+        <v>5.16913843</v>
       </c>
       <c r="D112" t="n">
-        <v>71.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E112" t="n">
-        <v>73.40000000000001</v>
+        <v>76.45</v>
       </c>
       <c r="F112" t="n">
-        <v>70</v>
+        <v>71.55</v>
       </c>
       <c r="G112" t="n">
-        <v>71.8</v>
+        <v>74.2</v>
       </c>
       <c r="H112" t="n">
-        <v>0.84</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>-224.29</v>
+        <v>32.76</v>
       </c>
       <c r="C113" t="n">
-        <v>5.17104921</v>
+        <v>5.17241443</v>
       </c>
       <c r="D113" t="n">
-        <v>73.45</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E113" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F113" t="n">
-        <v>71.65000000000001</v>
+        <v>73.25</v>
       </c>
       <c r="G113" t="n">
-        <v>73.3</v>
+        <v>73.7</v>
       </c>
       <c r="H113" t="n">
-        <v>2.09</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>97.7422</v>
+        <v>-19.6</v>
       </c>
       <c r="C114" t="n">
-        <v>5.18082343</v>
+        <v>5.17045443</v>
       </c>
       <c r="D114" t="n">
-        <v>71.95</v>
+        <v>73.7</v>
       </c>
       <c r="E114" t="n">
-        <v>73.5</v>
+        <v>73.95</v>
       </c>
       <c r="F114" t="n">
-        <v>71.75</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="G114" t="n">
-        <v>71.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="H114" t="n">
-        <v>-1.91</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>-116.85</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>5.16913843</v>
+        <v>5.17787843</v>
       </c>
       <c r="D115" t="n">
-        <v>71.90000000000001</v>
+        <v>73.75</v>
       </c>
       <c r="E115" t="n">
-        <v>76.45</v>
+        <v>73.75</v>
       </c>
       <c r="F115" t="n">
-        <v>71.55</v>
+        <v>70.5</v>
       </c>
       <c r="G115" t="n">
-        <v>74.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="H115" t="n">
-        <v>3.2</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>32.76</v>
+        <v>15.04</v>
       </c>
       <c r="C116" t="n">
-        <v>5.17241443</v>
+        <v>5.17938243</v>
       </c>
       <c r="D116" t="n">
-        <v>74.09999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="E116" t="n">
-        <v>75</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F116" t="n">
-        <v>73.25</v>
+        <v>70.95</v>
       </c>
       <c r="G116" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="H116" t="n">
-        <v>-0.67</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>-19.6</v>
+        <v>213.47</v>
       </c>
       <c r="C117" t="n">
-        <v>5.17045443</v>
+        <v>5.20072943</v>
       </c>
       <c r="D117" t="n">
-        <v>73.7</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E117" t="n">
-        <v>73.95</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F117" t="n">
-        <v>71.65000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G117" t="n">
-        <v>73</v>
+        <v>71.45</v>
       </c>
       <c r="H117" t="n">
-        <v>-0.95</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>74.23999999999999</v>
+        <v>-167.67</v>
       </c>
       <c r="C118" t="n">
-        <v>5.17787843</v>
+        <v>5.18396243</v>
       </c>
       <c r="D118" t="n">
-        <v>73.75</v>
+        <v>72</v>
       </c>
       <c r="E118" t="n">
-        <v>73.75</v>
+        <v>73.45</v>
       </c>
       <c r="F118" t="n">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G118" t="n">
-        <v>70.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="H118" t="n">
-        <v>-2.88</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>15.04</v>
+        <v>-78.5919</v>
       </c>
       <c r="C119" t="n">
-        <v>5.17938243</v>
+        <v>5.17610324</v>
       </c>
       <c r="D119" t="n">
-        <v>70.95</v>
+        <v>73.3</v>
       </c>
       <c r="E119" t="n">
-        <v>72.15000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="F119" t="n">
-        <v>70.95</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="G119" t="n">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="H119" t="n">
-        <v>0.99</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>213.47</v>
+        <v>-54.57</v>
       </c>
       <c r="C120" t="n">
-        <v>5.20072943</v>
+        <v>5.17064624</v>
       </c>
       <c r="D120" t="n">
-        <v>71.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="E120" t="n">
-        <v>71.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F120" t="n">
-        <v>70.40000000000001</v>
+        <v>71.95</v>
       </c>
       <c r="G120" t="n">
-        <v>71.45</v>
+        <v>73.45</v>
       </c>
       <c r="H120" t="n">
-        <v>-0.21</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>-167.67</v>
+        <v>32.9</v>
       </c>
       <c r="C121" t="n">
-        <v>5.18396243</v>
+        <v>5.17393624</v>
       </c>
       <c r="D121" t="n">
-        <v>72</v>
+        <v>73.45</v>
       </c>
       <c r="E121" t="n">
-        <v>73.45</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F121" t="n">
-        <v>70.59999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G121" t="n">
-        <v>73.3</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>2.59</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>-78.5919</v>
+        <v>41.93</v>
       </c>
       <c r="C122" t="n">
-        <v>5.17610324</v>
+        <v>5.17812924</v>
       </c>
       <c r="D122" t="n">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="E122" t="n">
-        <v>73.3</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>71.84999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="G122" t="n">
-        <v>73.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="H122" t="n">
-        <v>-0.14</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>-54.57</v>
+        <v>52.87</v>
       </c>
       <c r="C123" t="n">
-        <v>5.17064624</v>
+        <v>5.18341624</v>
       </c>
       <c r="D123" t="n">
-        <v>72.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="E123" t="n">
-        <v>73.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="F123" t="n">
-        <v>71.95</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>73.45</v>
+        <v>69.7</v>
       </c>
       <c r="H123" t="n">
-        <v>0.34</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>32.9</v>
+        <v>291.58</v>
       </c>
       <c r="C124" t="n">
-        <v>5.17393624</v>
+        <v>5.21257424</v>
       </c>
       <c r="D124" t="n">
-        <v>73.45</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="E124" t="n">
-        <v>74.40000000000001</v>
+        <v>69.45</v>
       </c>
       <c r="F124" t="n">
-        <v>71.75</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G124" t="n">
-        <v>73.15000000000001</v>
+        <v>67</v>
       </c>
       <c r="H124" t="n">
-        <v>-0.41</v>
+        <v>-3.87</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>41.93</v>
+        <v>-60.7601</v>
       </c>
       <c r="C125" t="n">
-        <v>5.17812924</v>
+        <v>5.20649823</v>
       </c>
       <c r="D125" t="n">
-        <v>73</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E125" t="n">
-        <v>73.65000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="F125" t="n">
-        <v>68.7</v>
+        <v>68.45</v>
       </c>
       <c r="G125" t="n">
-        <v>69.90000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="H125" t="n">
-        <v>-4.44</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>52.87</v>
+        <v>264.89</v>
       </c>
       <c r="C126" t="n">
-        <v>5.18341624</v>
+        <v>5.23298723</v>
       </c>
       <c r="D126" t="n">
-        <v>70.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E126" t="n">
-        <v>70.5</v>
+        <v>69.75</v>
       </c>
       <c r="F126" t="n">
-        <v>68.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="G126" t="n">
-        <v>69.7</v>
+        <v>67.55</v>
       </c>
       <c r="H126" t="n">
-        <v>-0.29</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>291.58</v>
+        <v>0</v>
       </c>
       <c r="C127" t="n">
-        <v>5.21257424</v>
+        <v>5.23298723</v>
       </c>
       <c r="D127" t="n">
-        <v>69.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="E127" t="n">
-        <v>69.45</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>66.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="G127" t="n">
-        <v>67</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H127" t="n">
-        <v>-3.87</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>-60.7601</v>
+        <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>5.20649823</v>
+        <v>5.23298723</v>
       </c>
       <c r="D128" t="n">
-        <v>69.40000000000001</v>
+        <v>69.25</v>
       </c>
       <c r="E128" t="n">
-        <v>70.25</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>68.45</v>
+        <v>68.2</v>
       </c>
       <c r="G128" t="n">
-        <v>69.25</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="H128" t="n">
-        <v>3.36</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>264.89</v>
+        <v>-369.37</v>
       </c>
       <c r="C129" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D129" t="n">
-        <v>68.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="E129" t="n">
-        <v>69.75</v>
+        <v>69.5</v>
       </c>
       <c r="F129" t="n">
         <v>67.3</v>
       </c>
       <c r="G129" t="n">
-        <v>67.55</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="H129" t="n">
-        <v>-2.45</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B130" t="n">
         <v>0</v>
       </c>
       <c r="C130" t="n">
-        <v>5.23298723</v>
+        <v>5.19605023</v>
       </c>
       <c r="D130" t="n">
-        <v>68.59999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="E130" t="n">
-        <v>69.75</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>67.3</v>
+        <v>68.5</v>
       </c>
       <c r="G130" t="n">
-        <v>67.55</v>
+        <v>69.95</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0</v>
+        <v>68.9663</v>
       </c>
       <c r="C131" t="n">
-        <v>5.23298723</v>
+        <v>5.20294686</v>
       </c>
       <c r="D131" t="n">
-        <v>69</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E131" t="n">
-        <v>71.15000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="F131" t="n">
-        <v>68.8</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>70.15000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="H131" t="n">
-        <v>3.85</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>-247.41</v>
       </c>
       <c r="C132" t="n">
-        <v>5.23298723</v>
+        <v>5.17820586</v>
       </c>
       <c r="D132" t="n">
-        <v>69.25</v>
+        <v>69.5</v>
       </c>
       <c r="E132" t="n">
-        <v>70.09999999999999</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F132" t="n">
-        <v>68.2</v>
+        <v>69.45</v>
       </c>
       <c r="G132" t="n">
-        <v>69.65000000000001</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H132" t="n">
-        <v>-0.71</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>-369.37</v>
+        <v>27.55</v>
       </c>
       <c r="C133" t="n">
-        <v>5.19605023</v>
+        <v>5.18096086</v>
       </c>
       <c r="D133" t="n">
-        <v>69.5</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E133" t="n">
-        <v>69.5</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>67.3</v>
+        <v>73.05</v>
       </c>
       <c r="G133" t="n">
-        <v>67.84999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="H133" t="n">
-        <v>-2.58</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0</v>
+        <v>-286.2</v>
       </c>
       <c r="C134" t="n">
-        <v>5.19605023</v>
+        <v>5.15234086</v>
       </c>
       <c r="D134" t="n">
-        <v>68.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>70.34999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="F134" t="n">
-        <v>68.5</v>
+        <v>73.05</v>
       </c>
       <c r="G134" t="n">
-        <v>69.95</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="H134" t="n">
-        <v>3.1</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>68.9663</v>
+        <v>48.88</v>
       </c>
       <c r="C135" t="n">
-        <v>5.20294686</v>
+        <v>5.15722886</v>
       </c>
       <c r="D135" t="n">
-        <v>68.34999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="E135" t="n">
-        <v>70.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F135" t="n">
-        <v>68.34999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="G135" t="n">
-        <v>70.05</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="H135" t="n">
-        <v>0.14</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>-247.41</v>
+        <v>-55.96</v>
       </c>
       <c r="C136" t="n">
-        <v>5.17820586</v>
+        <v>5.15163286</v>
       </c>
       <c r="D136" t="n">
-        <v>69.5</v>
+        <v>75.05</v>
       </c>
       <c r="E136" t="n">
-        <v>74.15000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F136" t="n">
-        <v>69.45</v>
+        <v>74.25</v>
       </c>
       <c r="G136" t="n">
-        <v>73.84999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>5.42</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>27.55</v>
+        <v>-385.85</v>
       </c>
       <c r="C137" t="n">
-        <v>5.18096086</v>
+        <v>5.11304786</v>
       </c>
       <c r="D137" t="n">
-        <v>73.34999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="E137" t="n">
-        <v>75.15000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F137" t="n">
-        <v>73.05</v>
+        <v>64.5</v>
       </c>
       <c r="G137" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="H137" t="n">
-        <v>-0.61</v>
+        <v>-14.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>-286.2</v>
+        <v>139.59</v>
       </c>
       <c r="C138" t="n">
-        <v>5.15234086</v>
+        <v>5.12700686</v>
       </c>
       <c r="D138" t="n">
-        <v>73.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E138" t="n">
-        <v>74.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F138" t="n">
-        <v>73.05</v>
+        <v>61.75</v>
       </c>
       <c r="G138" t="n">
-        <v>73.65000000000001</v>
+        <v>62.1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.34</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>48.88</v>
+        <v>1468.42</v>
       </c>
       <c r="C139" t="n">
-        <v>5.15722886</v>
+        <v>5.27384886</v>
       </c>
       <c r="D139" t="n">
-        <v>76.8</v>
+        <v>62.6</v>
       </c>
       <c r="E139" t="n">
-        <v>78.90000000000001</v>
+        <v>63.35</v>
       </c>
       <c r="F139" t="n">
-        <v>75.40000000000001</v>
+        <v>61</v>
       </c>
       <c r="G139" t="n">
-        <v>76.84999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="H139" t="n">
-        <v>4.34</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>-55.96</v>
+        <v>292.93</v>
       </c>
       <c r="C140" t="n">
-        <v>5.15163286</v>
+        <v>5.30314186</v>
       </c>
       <c r="D140" t="n">
-        <v>75.05</v>
+        <v>62.5</v>
       </c>
       <c r="E140" t="n">
-        <v>75.90000000000001</v>
+        <v>63.85</v>
       </c>
       <c r="F140" t="n">
-        <v>74.25</v>
+        <v>61.55</v>
       </c>
       <c r="G140" t="n">
-        <v>75.59999999999999</v>
+        <v>62.25</v>
       </c>
       <c r="H140" t="n">
-        <v>-1.63</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>-385.85</v>
+        <v>17.9</v>
       </c>
       <c r="C141" t="n">
-        <v>5.11304786</v>
+        <v>5.30493186</v>
       </c>
       <c r="D141" t="n">
-        <v>72.40000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="E141" t="n">
-        <v>72.40000000000001</v>
+        <v>64.95</v>
       </c>
       <c r="F141" t="n">
-        <v>64.5</v>
+        <v>61.35</v>
       </c>
       <c r="G141" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="H141" t="n">
-        <v>-14.15</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>139.59</v>
+        <v>-224.88</v>
       </c>
       <c r="C142" t="n">
-        <v>5.12700686</v>
+        <v>5.28244386</v>
       </c>
       <c r="D142" t="n">
-        <v>64.90000000000001</v>
+        <v>61.8</v>
       </c>
       <c r="E142" t="n">
-        <v>64.90000000000001</v>
+        <v>62.25</v>
       </c>
       <c r="F142" t="n">
-        <v>61.75</v>
+        <v>60.4</v>
       </c>
       <c r="G142" t="n">
-        <v>62.1</v>
+        <v>62.15</v>
       </c>
       <c r="H142" t="n">
-        <v>-4.31</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1468.42</v>
+        <v>-244.5</v>
       </c>
       <c r="C143" t="n">
-        <v>5.27384886</v>
+        <v>5.25799386</v>
       </c>
       <c r="D143" t="n">
-        <v>62.6</v>
+        <v>61.9</v>
       </c>
       <c r="E143" t="n">
-        <v>63.35</v>
+        <v>62.35</v>
       </c>
       <c r="F143" t="n">
-        <v>61</v>
+        <v>59.9</v>
       </c>
       <c r="G143" t="n">
-        <v>61.6</v>
+        <v>60.2</v>
       </c>
       <c r="H143" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>292.93</v>
+        <v>-302.48</v>
       </c>
       <c r="C144" t="n">
-        <v>5.30314186</v>
+        <v>5.22774586</v>
       </c>
       <c r="D144" t="n">
-        <v>62.5</v>
+        <v>60.1</v>
       </c>
       <c r="E144" t="n">
-        <v>63.85</v>
+        <v>61</v>
       </c>
       <c r="F144" t="n">
-        <v>61.55</v>
+        <v>58.6</v>
       </c>
       <c r="G144" t="n">
-        <v>62.25</v>
+        <v>60.45</v>
       </c>
       <c r="H144" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>17.9</v>
+        <v>-177.8636</v>
       </c>
       <c r="C145" t="n">
-        <v>5.30493186</v>
+        <v>5.2099595</v>
       </c>
       <c r="D145" t="n">
-        <v>63.2</v>
+        <v>60</v>
       </c>
       <c r="E145" t="n">
-        <v>64.95</v>
+        <v>60.05</v>
       </c>
       <c r="F145" t="n">
-        <v>61.35</v>
+        <v>55.7</v>
       </c>
       <c r="G145" t="n">
-        <v>61.8</v>
+        <v>57.85</v>
       </c>
       <c r="H145" t="n">
-        <v>-0.72</v>
+        <v>-4.3</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>-224.88</v>
+        <v>-228.55</v>
       </c>
       <c r="C146" t="n">
-        <v>5.28244386</v>
+        <v>5.1871045</v>
       </c>
       <c r="D146" t="n">
-        <v>61.8</v>
+        <v>56.95</v>
       </c>
       <c r="E146" t="n">
-        <v>62.25</v>
+        <v>59.1</v>
       </c>
       <c r="F146" t="n">
-        <v>60.4</v>
+        <v>56</v>
       </c>
       <c r="G146" t="n">
-        <v>62.15</v>
+        <v>58.55</v>
       </c>
       <c r="H146" t="n">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>-244.5</v>
+        <v>423.9973</v>
       </c>
       <c r="C147" t="n">
-        <v>5.25799386</v>
+        <v>5.22950423</v>
       </c>
       <c r="D147" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="E147" t="n">
+        <v>62</v>
+      </c>
+      <c r="F147" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="G147" t="n">
         <v>61.9</v>
       </c>
-      <c r="E147" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="F147" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="G147" t="n">
-        <v>60.2</v>
-      </c>
       <c r="H147" t="n">
-        <v>-3.14</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>-302.48</v>
+        <v>-119.16</v>
       </c>
       <c r="C148" t="n">
-        <v>5.22774586</v>
+        <v>5.21758823</v>
       </c>
       <c r="D148" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="E148" t="n">
-        <v>61</v>
+        <v>60.75</v>
       </c>
       <c r="F148" t="n">
-        <v>58.6</v>
+        <v>58.75</v>
       </c>
       <c r="G148" t="n">
-        <v>60.45</v>
+        <v>59.1</v>
       </c>
       <c r="H148" t="n">
-        <v>0.42</v>
+        <v>-4.52</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>-177.8636</v>
+        <v>-301.92</v>
       </c>
       <c r="C149" t="n">
-        <v>5.2099595</v>
+        <v>5.18739623</v>
       </c>
       <c r="D149" t="n">
-        <v>60</v>
+        <v>58.95</v>
       </c>
       <c r="E149" t="n">
-        <v>60.05</v>
+        <v>58.95</v>
       </c>
       <c r="F149" t="n">
-        <v>55.7</v>
+        <v>56.85</v>
       </c>
       <c r="G149" t="n">
-        <v>57.85</v>
+        <v>57.25</v>
       </c>
       <c r="H149" t="n">
-        <v>-4.3</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>-228.55</v>
+        <v>112.29</v>
       </c>
       <c r="C150" t="n">
-        <v>5.1871045</v>
+        <v>5.19862523</v>
       </c>
       <c r="D150" t="n">
-        <v>56.95</v>
+        <v>57.1</v>
       </c>
       <c r="E150" t="n">
-        <v>59.1</v>
+        <v>57.6</v>
       </c>
       <c r="F150" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="G150" t="n">
-        <v>58.55</v>
+        <v>56.65</v>
       </c>
       <c r="H150" t="n">
-        <v>1.21</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>423.9973</v>
+        <v>-62.4836</v>
       </c>
       <c r="C151" t="n">
-        <v>5.22950423</v>
+        <v>5.19237687</v>
       </c>
       <c r="D151" t="n">
-        <v>57.05</v>
+        <v>55.3</v>
       </c>
       <c r="E151" t="n">
-        <v>62</v>
+        <v>57.9</v>
       </c>
       <c r="F151" t="n">
-        <v>56.55</v>
+        <v>54.95</v>
       </c>
       <c r="G151" t="n">
-        <v>61.9</v>
+        <v>57.35</v>
       </c>
       <c r="H151" t="n">
-        <v>5.72</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>-119.16</v>
+        <v>-29.35</v>
       </c>
       <c r="C152" t="n">
-        <v>5.21758823</v>
+        <v>5.18944187</v>
       </c>
       <c r="D152" t="n">
-        <v>60.5</v>
+        <v>56.2</v>
       </c>
       <c r="E152" t="n">
-        <v>60.75</v>
+        <v>57.1</v>
       </c>
       <c r="F152" t="n">
-        <v>58.75</v>
+        <v>55.8</v>
       </c>
       <c r="G152" t="n">
-        <v>59.1</v>
+        <v>55.85</v>
       </c>
       <c r="H152" t="n">
-        <v>-4.52</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>-301.92</v>
+        <v>54.46</v>
       </c>
       <c r="C153" t="n">
-        <v>5.18739623</v>
+        <v>5.19488787</v>
       </c>
       <c r="D153" t="n">
-        <v>58.95</v>
+        <v>55.3</v>
       </c>
       <c r="E153" t="n">
-        <v>58.95</v>
+        <v>55.55</v>
       </c>
       <c r="F153" t="n">
-        <v>56.85</v>
+        <v>53.25</v>
       </c>
       <c r="G153" t="n">
-        <v>57.25</v>
+        <v>54.7</v>
       </c>
       <c r="H153" t="n">
-        <v>-3.13</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>112.29</v>
+        <v>17.32</v>
       </c>
       <c r="C154" t="n">
-        <v>5.19862523</v>
+        <v>5.19661987</v>
       </c>
       <c r="D154" t="n">
-        <v>57.1</v>
+        <v>54</v>
       </c>
       <c r="E154" t="n">
-        <v>57.6</v>
+        <v>54.1</v>
       </c>
       <c r="F154" t="n">
-        <v>56.5</v>
+        <v>52.25</v>
       </c>
       <c r="G154" t="n">
-        <v>56.65</v>
+        <v>53.15</v>
       </c>
       <c r="H154" t="n">
-        <v>-1.05</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>-62.4836</v>
+        <v>93.42</v>
       </c>
       <c r="C155" t="n">
-        <v>5.19237687</v>
+        <v>5.20596187</v>
       </c>
       <c r="D155" t="n">
-        <v>55.3</v>
+        <v>53.7</v>
       </c>
       <c r="E155" t="n">
         <v>57.9</v>
       </c>
       <c r="F155" t="n">
-        <v>54.95</v>
+        <v>53.25</v>
       </c>
       <c r="G155" t="n">
-        <v>57.35</v>
+        <v>57</v>
       </c>
       <c r="H155" t="n">
-        <v>1.24</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>-29.35</v>
+        <v>64.81</v>
       </c>
       <c r="C156" t="n">
-        <v>5.18944187</v>
+        <v>5.21244287</v>
       </c>
       <c r="D156" t="n">
-        <v>56.2</v>
+        <v>56.6</v>
       </c>
       <c r="E156" t="n">
-        <v>57.1</v>
+        <v>58.05</v>
       </c>
       <c r="F156" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="G156" t="n">
-        <v>55.85</v>
+        <v>56.85</v>
       </c>
       <c r="H156" t="n">
-        <v>-2.62</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>54.46</v>
+        <v>-172.75</v>
       </c>
       <c r="C157" t="n">
-        <v>5.19488787</v>
+        <v>5.19516787</v>
       </c>
       <c r="D157" t="n">
-        <v>55.3</v>
+        <v>56.85</v>
       </c>
       <c r="E157" t="n">
-        <v>55.55</v>
+        <v>57.2</v>
       </c>
       <c r="F157" t="n">
-        <v>53.25</v>
+        <v>55</v>
       </c>
       <c r="G157" t="n">
-        <v>54.7</v>
+        <v>56</v>
       </c>
       <c r="H157" t="n">
-        <v>-2.06</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>17.32</v>
+        <v>-24.86</v>
       </c>
       <c r="C158" t="n">
-        <v>5.19661987</v>
+        <v>5.19268187</v>
       </c>
       <c r="D158" t="n">
-        <v>54</v>
+        <v>55.75</v>
       </c>
       <c r="E158" t="n">
-        <v>54.1</v>
+        <v>55.8</v>
       </c>
       <c r="F158" t="n">
-        <v>52.25</v>
+        <v>53.7</v>
       </c>
       <c r="G158" t="n">
-        <v>53.15</v>
+        <v>53.9</v>
       </c>
       <c r="H158" t="n">
-        <v>-2.83</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>93.42</v>
+        <v>17.38</v>
       </c>
       <c r="C159" t="n">
-        <v>5.20596187</v>
+        <v>5.19441987</v>
       </c>
       <c r="D159" t="n">
-        <v>53.7</v>
+        <v>53.25</v>
       </c>
       <c r="E159" t="n">
-        <v>57.9</v>
+        <v>53.9</v>
       </c>
       <c r="F159" t="n">
-        <v>53.25</v>
+        <v>51.75</v>
       </c>
       <c r="G159" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H159" t="n">
-        <v>7.24</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>64.81</v>
+        <v>14.06</v>
       </c>
       <c r="C160" t="n">
-        <v>5.21244287</v>
+        <v>5.19582587</v>
       </c>
       <c r="D160" t="n">
-        <v>56.6</v>
+        <v>50.15</v>
       </c>
       <c r="E160" t="n">
-        <v>58.05</v>
+        <v>51.55</v>
       </c>
       <c r="F160" t="n">
-        <v>56.5</v>
+        <v>49.64</v>
       </c>
       <c r="G160" t="n">
-        <v>56.85</v>
+        <v>50.5</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.26</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>-172.75</v>
+        <v>-21.2345</v>
       </c>
       <c r="C161" t="n">
-        <v>5.19516787</v>
+        <v>5.19370242</v>
       </c>
       <c r="D161" t="n">
-        <v>56.85</v>
+        <v>50</v>
       </c>
       <c r="E161" t="n">
-        <v>57.2</v>
+        <v>50.8</v>
       </c>
       <c r="F161" t="n">
-        <v>55</v>
+        <v>47.9</v>
       </c>
       <c r="G161" t="n">
-        <v>56</v>
+        <v>48.32</v>
       </c>
       <c r="H161" t="n">
-        <v>-1.5</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>-24.86</v>
+        <v>47.7</v>
       </c>
       <c r="C162" t="n">
-        <v>5.19268187</v>
+        <v>5.19847242</v>
       </c>
       <c r="D162" t="n">
-        <v>55.75</v>
+        <v>48.98</v>
       </c>
       <c r="E162" t="n">
-        <v>55.8</v>
+        <v>49.94</v>
       </c>
       <c r="F162" t="n">
-        <v>53.7</v>
+        <v>48.18</v>
       </c>
       <c r="G162" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="H162" t="n">
-        <v>-3.75</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>17.38</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="C163" t="n">
-        <v>5.19441987</v>
+        <v>5.20773242</v>
       </c>
       <c r="D163" t="n">
-        <v>53.25</v>
+        <v>49.44</v>
       </c>
       <c r="E163" t="n">
-        <v>53.9</v>
+        <v>49.44</v>
       </c>
       <c r="F163" t="n">
-        <v>51.75</v>
+        <v>46.74</v>
       </c>
       <c r="G163" t="n">
-        <v>52</v>
+        <v>47.4</v>
       </c>
       <c r="H163" t="n">
-        <v>-3.53</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>14.06</v>
+        <v>-95.51000000000001</v>
       </c>
       <c r="C164" t="n">
-        <v>5.19582587</v>
+        <v>5.19818142</v>
       </c>
       <c r="D164" t="n">
-        <v>50.15</v>
+        <v>47</v>
       </c>
       <c r="E164" t="n">
-        <v>51.55</v>
+        <v>47</v>
       </c>
       <c r="F164" t="n">
-        <v>49.64</v>
+        <v>45.86</v>
       </c>
       <c r="G164" t="n">
-        <v>50.5</v>
+        <v>46.28</v>
       </c>
       <c r="H164" t="n">
-        <v>-2.88</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>-21.2345</v>
+        <v>-254.06</v>
       </c>
       <c r="C165" t="n">
-        <v>5.19370242</v>
+        <v>5.17277542</v>
       </c>
       <c r="D165" t="n">
-        <v>50</v>
+        <v>46.9</v>
       </c>
       <c r="E165" t="n">
-        <v>50.8</v>
+        <v>47.18</v>
       </c>
       <c r="F165" t="n">
-        <v>47.9</v>
+        <v>45.76</v>
       </c>
       <c r="G165" t="n">
-        <v>48.32</v>
+        <v>45.9</v>
       </c>
       <c r="H165" t="n">
-        <v>-4.32</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>47.7</v>
+        <v>-316.19</v>
       </c>
       <c r="C166" t="n">
-        <v>5.19847242</v>
+        <v>5.14115642</v>
       </c>
       <c r="D166" t="n">
-        <v>48.98</v>
+        <v>45.9</v>
       </c>
       <c r="E166" t="n">
-        <v>49.94</v>
+        <v>46.78</v>
       </c>
       <c r="F166" t="n">
-        <v>48.18</v>
+        <v>45.26</v>
       </c>
       <c r="G166" t="n">
-        <v>49.44</v>
+        <v>46.08</v>
       </c>
       <c r="H166" t="n">
-        <v>2.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>92.59999999999999</v>
+        <v>-150.87</v>
       </c>
       <c r="C167" t="n">
-        <v>5.20773242</v>
+        <v>5.12606942</v>
       </c>
       <c r="D167" t="n">
-        <v>49.44</v>
+        <v>47.7</v>
       </c>
       <c r="E167" t="n">
-        <v>49.44</v>
+        <v>48.9</v>
       </c>
       <c r="F167" t="n">
-        <v>46.74</v>
+        <v>46.64</v>
       </c>
       <c r="G167" t="n">
-        <v>47.4</v>
+        <v>46.84</v>
       </c>
       <c r="H167" t="n">
-        <v>-4.13</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>-95.51000000000001</v>
+        <v>-236.76</v>
       </c>
       <c r="C168" t="n">
-        <v>5.19818142</v>
+        <v>5.10239342</v>
       </c>
       <c r="D168" t="n">
-        <v>47</v>
+        <v>46.92</v>
       </c>
       <c r="E168" t="n">
-        <v>47</v>
+        <v>48.28</v>
       </c>
       <c r="F168" t="n">
-        <v>45.86</v>
+        <v>46.84</v>
       </c>
       <c r="G168" t="n">
-        <v>46.28</v>
+        <v>47.36</v>
       </c>
       <c r="H168" t="n">
-        <v>-2.36</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>-254.06</v>
+        <v>-36.92</v>
       </c>
       <c r="C169" t="n">
-        <v>5.17277542</v>
+        <v>5.09870142</v>
       </c>
       <c r="D169" t="n">
-        <v>46.9</v>
+        <v>47</v>
       </c>
       <c r="E169" t="n">
-        <v>47.18</v>
+        <v>47.56</v>
       </c>
       <c r="F169" t="n">
-        <v>45.76</v>
+        <v>45.72</v>
       </c>
       <c r="G169" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="H169" t="n">
-        <v>-0.82</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>-316.19</v>
+        <v>64.78</v>
       </c>
       <c r="C170" t="n">
-        <v>5.14115642</v>
+        <v>5.10517942</v>
       </c>
       <c r="D170" t="n">
-        <v>45.9</v>
+        <v>46.26</v>
       </c>
       <c r="E170" t="n">
-        <v>46.78</v>
+        <v>48.42</v>
       </c>
       <c r="F170" t="n">
-        <v>45.26</v>
+        <v>46.26</v>
       </c>
       <c r="G170" t="n">
-        <v>46.08</v>
+        <v>46.6</v>
       </c>
       <c r="H170" t="n">
-        <v>0.39</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>-150.87</v>
+        <v>-44.41</v>
       </c>
       <c r="C171" t="n">
-        <v>5.12606942</v>
+        <v>5.10073842</v>
       </c>
       <c r="D171" t="n">
-        <v>47.7</v>
+        <v>47.06</v>
       </c>
       <c r="E171" t="n">
-        <v>48.9</v>
+        <v>48.98</v>
       </c>
       <c r="F171" t="n">
-        <v>46.64</v>
+        <v>46.7</v>
       </c>
       <c r="G171" t="n">
-        <v>46.84</v>
+        <v>48.52</v>
       </c>
       <c r="H171" t="n">
-        <v>1.65</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>-236.76</v>
+        <v>-124.97</v>
       </c>
       <c r="C172" t="n">
-        <v>5.10239342</v>
+        <v>5.08824142</v>
       </c>
       <c r="D172" t="n">
-        <v>46.92</v>
+        <v>47.6</v>
       </c>
       <c r="E172" t="n">
-        <v>48.28</v>
+        <v>48.08</v>
       </c>
       <c r="F172" t="n">
-        <v>46.84</v>
+        <v>46.72</v>
       </c>
       <c r="G172" t="n">
-        <v>47.36</v>
+        <v>46.76</v>
       </c>
       <c r="H172" t="n">
-        <v>1.11</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>-36.92</v>
+        <v>-272.6</v>
       </c>
       <c r="C173" t="n">
-        <v>5.09870142</v>
+        <v>5.06098142</v>
       </c>
       <c r="D173" t="n">
-        <v>47</v>
+        <v>46.76</v>
       </c>
       <c r="E173" t="n">
-        <v>47.56</v>
+        <v>48.3</v>
       </c>
       <c r="F173" t="n">
-        <v>45.72</v>
+        <v>46.02</v>
       </c>
       <c r="G173" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="H173" t="n">
-        <v>-2.32</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>64.78</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="C174" t="n">
-        <v>5.10517942</v>
+        <v>5.06933542</v>
       </c>
       <c r="D174" t="n">
-        <v>46.26</v>
+        <v>47.42</v>
       </c>
       <c r="E174" t="n">
-        <v>48.42</v>
+        <v>47.92</v>
       </c>
       <c r="F174" t="n">
-        <v>46.26</v>
+        <v>46.46</v>
       </c>
       <c r="G174" t="n">
-        <v>46.6</v>
+        <v>47.2</v>
       </c>
       <c r="H174" t="n">
-        <v>0.73</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>-44.41</v>
+        <v>-232.94</v>
       </c>
       <c r="C175" t="n">
-        <v>5.10073842</v>
+        <v>5.04604142</v>
       </c>
       <c r="D175" t="n">
-        <v>47.06</v>
+        <v>47.2</v>
       </c>
       <c r="E175" t="n">
-        <v>48.98</v>
+        <v>48.84</v>
       </c>
       <c r="F175" t="n">
         <v>46.7</v>
       </c>
       <c r="G175" t="n">
-        <v>48.52</v>
+        <v>48.56</v>
       </c>
       <c r="H175" t="n">
-        <v>4.12</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>-124.97</v>
+        <v>-101.2265</v>
       </c>
       <c r="C176" t="n">
-        <v>5.08824142</v>
+        <v>5.03591877</v>
       </c>
       <c r="D176" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="E176" t="n">
-        <v>48.08</v>
+        <v>49.46</v>
       </c>
       <c r="F176" t="n">
-        <v>46.72</v>
+        <v>48.24</v>
       </c>
       <c r="G176" t="n">
-        <v>46.76</v>
+        <v>48.78</v>
       </c>
       <c r="H176" t="n">
-        <v>-3.63</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>-272.6</v>
+        <v>-146.01</v>
       </c>
       <c r="C177" t="n">
-        <v>5.06098142</v>
+        <v>5.02131777</v>
       </c>
       <c r="D177" t="n">
-        <v>46.76</v>
+        <v>49.22</v>
       </c>
       <c r="E177" t="n">
-        <v>48.3</v>
+        <v>51</v>
       </c>
       <c r="F177" t="n">
-        <v>46.02</v>
+        <v>49.22</v>
       </c>
       <c r="G177" t="n">
-        <v>47.42</v>
+        <v>50.4</v>
       </c>
       <c r="H177" t="n">
-        <v>1.41</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>83.54000000000001</v>
+        <v>14.25</v>
       </c>
       <c r="C178" t="n">
-        <v>5.06933542</v>
+        <v>5.02274277</v>
       </c>
       <c r="D178" t="n">
-        <v>47.42</v>
+        <v>50.55</v>
       </c>
       <c r="E178" t="n">
-        <v>47.92</v>
+        <v>51</v>
       </c>
       <c r="F178" t="n">
-        <v>46.46</v>
+        <v>48.2</v>
       </c>
       <c r="G178" t="n">
-        <v>47.2</v>
+        <v>48.94</v>
       </c>
       <c r="H178" t="n">
-        <v>-0.46</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>-232.94</v>
+        <v>7.54</v>
       </c>
       <c r="C179" t="n">
-        <v>5.04604142</v>
+        <v>5.02349677</v>
       </c>
       <c r="D179" t="n">
-        <v>47.2</v>
+        <v>49.96</v>
       </c>
       <c r="E179" t="n">
-        <v>48.84</v>
+        <v>49.98</v>
       </c>
       <c r="F179" t="n">
-        <v>46.7</v>
+        <v>48.72</v>
       </c>
       <c r="G179" t="n">
-        <v>48.56</v>
+        <v>49.12</v>
       </c>
       <c r="H179" t="n">
-        <v>2.88</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>-101.2265</v>
+        <v>29.93</v>
       </c>
       <c r="C180" t="n">
-        <v>5.03591877</v>
+        <v>5.02648977</v>
       </c>
       <c r="D180" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="E180" t="n">
-        <v>49.46</v>
+        <v>49.36</v>
       </c>
       <c r="F180" t="n">
-        <v>48.24</v>
+        <v>48.18</v>
       </c>
       <c r="G180" t="n">
-        <v>48.78</v>
+        <v>48.64</v>
       </c>
       <c r="H180" t="n">
-        <v>0.45</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>-146.01</v>
+        <v>-93.37</v>
       </c>
       <c r="C181" t="n">
-        <v>5.02131777</v>
+        <v>5.01715277</v>
       </c>
       <c r="D181" t="n">
-        <v>49.22</v>
+        <v>48.4</v>
       </c>
       <c r="E181" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
       <c r="F181" t="n">
-        <v>49.22</v>
+        <v>47.2</v>
       </c>
       <c r="G181" t="n">
-        <v>50.4</v>
+        <v>47.64</v>
       </c>
       <c r="H181" t="n">
-        <v>3.32</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>14.25</v>
+        <v>-93.65000000000001</v>
       </c>
       <c r="C182" t="n">
-        <v>5.02274277</v>
+        <v>5.00778777</v>
       </c>
       <c r="D182" t="n">
-        <v>50.55</v>
+        <v>47.64</v>
       </c>
       <c r="E182" t="n">
-        <v>51</v>
+        <v>49.3</v>
       </c>
       <c r="F182" t="n">
-        <v>48.2</v>
+        <v>47.22</v>
       </c>
       <c r="G182" t="n">
-        <v>48.94</v>
+        <v>48.96</v>
       </c>
       <c r="H182" t="n">
-        <v>-2.9</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>7.54</v>
+        <v>28.06</v>
       </c>
       <c r="C183" t="n">
-        <v>5.02349677</v>
+        <v>5.01059377</v>
       </c>
       <c r="D183" t="n">
-        <v>49.96</v>
+        <v>48.36</v>
       </c>
       <c r="E183" t="n">
-        <v>49.98</v>
+        <v>48.76</v>
       </c>
       <c r="F183" t="n">
-        <v>48.72</v>
+        <v>47.52</v>
       </c>
       <c r="G183" t="n">
-        <v>49.12</v>
+        <v>47.98</v>
       </c>
       <c r="H183" t="n">
-        <v>0.37</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>29.93</v>
+        <v>-160.94</v>
       </c>
       <c r="C184" t="n">
-        <v>5.02648977</v>
+        <v>4.99449977</v>
       </c>
       <c r="D184" t="n">
-        <v>49.1</v>
+        <v>47.98</v>
       </c>
       <c r="E184" t="n">
-        <v>49.36</v>
+        <v>48.46</v>
       </c>
       <c r="F184" t="n">
-        <v>48.18</v>
+        <v>47.32</v>
       </c>
       <c r="G184" t="n">
-        <v>48.64</v>
+        <v>48.08</v>
       </c>
       <c r="H184" t="n">
-        <v>-0.98</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>-93.37</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="C185" t="n">
-        <v>5.01715277</v>
+        <v>5.00218477</v>
       </c>
       <c r="D185" t="n">
-        <v>48.4</v>
+        <v>49.54</v>
       </c>
       <c r="E185" t="n">
-        <v>48.4</v>
+        <v>50.5</v>
       </c>
       <c r="F185" t="n">
-        <v>47.2</v>
+        <v>48.9</v>
       </c>
       <c r="G185" t="n">
-        <v>47.64</v>
+        <v>49.68</v>
       </c>
       <c r="H185" t="n">
-        <v>-2.06</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>-93.65000000000001</v>
+        <v>-70.88</v>
       </c>
       <c r="C186" t="n">
-        <v>5.00778777</v>
+        <v>4.99509677</v>
       </c>
       <c r="D186" t="n">
-        <v>47.64</v>
+        <v>51.9</v>
       </c>
       <c r="E186" t="n">
-        <v>49.3</v>
+        <v>55.6</v>
       </c>
       <c r="F186" t="n">
-        <v>47.22</v>
+        <v>51.9</v>
       </c>
       <c r="G186" t="n">
-        <v>48.96</v>
+        <v>54.6</v>
       </c>
       <c r="H186" t="n">
-        <v>2.77</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>28.06</v>
+        <v>-223.97</v>
       </c>
       <c r="C187" t="n">
-        <v>5.01059377</v>
+        <v>4.97269977</v>
       </c>
       <c r="D187" t="n">
-        <v>48.36</v>
+        <v>54.7</v>
       </c>
       <c r="E187" t="n">
-        <v>48.76</v>
+        <v>56.1</v>
       </c>
       <c r="F187" t="n">
-        <v>47.52</v>
+        <v>53.7</v>
       </c>
       <c r="G187" t="n">
-        <v>47.98</v>
+        <v>54.25</v>
       </c>
       <c r="H187" t="n">
-        <v>-2</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>-160.94</v>
+        <v>-908.88</v>
       </c>
       <c r="C188" t="n">
-        <v>4.99449977</v>
+        <v>4.88181177</v>
       </c>
       <c r="D188" t="n">
-        <v>47.98</v>
+        <v>52.85</v>
       </c>
       <c r="E188" t="n">
-        <v>48.46</v>
+        <v>53.8</v>
       </c>
       <c r="F188" t="n">
-        <v>47.32</v>
+        <v>51.3</v>
       </c>
       <c r="G188" t="n">
-        <v>48.08</v>
+        <v>53.4</v>
       </c>
       <c r="H188" t="n">
-        <v>0.21</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>76.84999999999999</v>
+        <v>-219</v>
       </c>
       <c r="C189" t="n">
-        <v>5.00218477</v>
+        <v>4.85991177</v>
       </c>
       <c r="D189" t="n">
-        <v>49.54</v>
+        <v>52.75</v>
       </c>
       <c r="E189" t="n">
-        <v>50.5</v>
+        <v>54.45</v>
       </c>
       <c r="F189" t="n">
-        <v>48.9</v>
+        <v>51.45</v>
       </c>
       <c r="G189" t="n">
-        <v>49.68</v>
+        <v>51.85</v>
       </c>
       <c r="H189" t="n">
-        <v>3.33</v>
+        <v>-2.9</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>-70.88</v>
+        <v>81.19</v>
       </c>
       <c r="C190" t="n">
-        <v>4.99509677</v>
+        <v>4.86803077</v>
       </c>
       <c r="D190" t="n">
-        <v>51.9</v>
+        <v>51.85</v>
       </c>
       <c r="E190" t="n">
-        <v>55.6</v>
+        <v>51.85</v>
       </c>
       <c r="F190" t="n">
-        <v>51.9</v>
+        <v>49.6</v>
       </c>
       <c r="G190" t="n">
-        <v>54.6</v>
+        <v>50.45</v>
       </c>
       <c r="H190" t="n">
-        <v>9.9</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>-223.97</v>
+        <v>7.21</v>
       </c>
       <c r="C191" t="n">
-        <v>4.97269977</v>
+        <v>4.86875177</v>
       </c>
       <c r="D191" t="n">
-        <v>54.7</v>
+        <v>50.05</v>
       </c>
       <c r="E191" t="n">
-        <v>56.1</v>
+        <v>50.8</v>
       </c>
       <c r="F191" t="n">
-        <v>53.7</v>
+        <v>49.52</v>
       </c>
       <c r="G191" t="n">
-        <v>54.25</v>
+        <v>50.65</v>
       </c>
       <c r="H191" t="n">
-        <v>-0.64</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>-908.88</v>
+        <v>144.28</v>
       </c>
       <c r="C192" t="n">
-        <v>4.88181177</v>
+        <v>4.88317977</v>
       </c>
       <c r="D192" t="n">
-        <v>52.85</v>
+        <v>50</v>
       </c>
       <c r="E192" t="n">
-        <v>53.8</v>
+        <v>50.6</v>
       </c>
       <c r="F192" t="n">
-        <v>51.3</v>
+        <v>49.08</v>
       </c>
       <c r="G192" t="n">
-        <v>53.4</v>
+        <v>49.12</v>
       </c>
       <c r="H192" t="n">
-        <v>-1.57</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>-219</v>
+        <v>-41.02</v>
       </c>
       <c r="C193" t="n">
-        <v>4.85991177</v>
+        <v>4.87907777</v>
       </c>
       <c r="D193" t="n">
-        <v>52.75</v>
+        <v>49.18</v>
       </c>
       <c r="E193" t="n">
-        <v>54.45</v>
+        <v>50.1</v>
       </c>
       <c r="F193" t="n">
-        <v>51.45</v>
+        <v>48.82</v>
       </c>
       <c r="G193" t="n">
-        <v>51.85</v>
+        <v>49.92</v>
       </c>
       <c r="H193" t="n">
-        <v>-2.9</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>81.19</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="C194" t="n">
-        <v>4.86803077</v>
+        <v>4.88594877</v>
       </c>
       <c r="D194" t="n">
-        <v>51.85</v>
+        <v>50.5</v>
       </c>
       <c r="E194" t="n">
-        <v>51.85</v>
+        <v>50.95</v>
       </c>
       <c r="F194" t="n">
-        <v>49.6</v>
+        <v>49.74</v>
       </c>
       <c r="G194" t="n">
-        <v>50.45</v>
+        <v>50.1</v>
       </c>
       <c r="H194" t="n">
-        <v>-2.7</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>7.21</v>
+        <v>20.01</v>
       </c>
       <c r="C195" t="n">
-        <v>4.86875177</v>
+        <v>4.88794977</v>
       </c>
       <c r="D195" t="n">
-        <v>50.05</v>
+        <v>50</v>
       </c>
       <c r="E195" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="F195" t="n">
-        <v>49.52</v>
+        <v>49.04</v>
       </c>
       <c r="G195" t="n">
-        <v>50.65</v>
+        <v>49.06</v>
       </c>
       <c r="H195" t="n">
-        <v>0.4</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>144.28</v>
+        <v>-18.77</v>
       </c>
       <c r="C196" t="n">
-        <v>4.88317977</v>
+        <v>4.88607277</v>
       </c>
       <c r="D196" t="n">
-        <v>50</v>
+        <v>49.08</v>
       </c>
       <c r="E196" t="n">
-        <v>50.6</v>
+        <v>49.78</v>
       </c>
       <c r="F196" t="n">
-        <v>49.08</v>
+        <v>48.7</v>
       </c>
       <c r="G196" t="n">
-        <v>49.12</v>
+        <v>49.4</v>
       </c>
       <c r="H196" t="n">
-        <v>-3.02</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>-41.02</v>
+        <v>95.14</v>
       </c>
       <c r="C197" t="n">
-        <v>4.87907777</v>
+        <v>4.89558677</v>
       </c>
       <c r="D197" t="n">
-        <v>49.18</v>
+        <v>48.66</v>
       </c>
       <c r="E197" t="n">
-        <v>50.1</v>
+        <v>49.22</v>
       </c>
       <c r="F197" t="n">
-        <v>48.82</v>
+        <v>48.02</v>
       </c>
       <c r="G197" t="n">
-        <v>49.92</v>
+        <v>48.22</v>
       </c>
       <c r="H197" t="n">
-        <v>1.63</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>68.70999999999999</v>
+        <v>6.47</v>
       </c>
       <c r="C198" t="n">
-        <v>4.88594877</v>
+        <v>4.89623377</v>
       </c>
       <c r="D198" t="n">
-        <v>50.5</v>
+        <v>48.22</v>
       </c>
       <c r="E198" t="n">
-        <v>50.95</v>
+        <v>48.22</v>
       </c>
       <c r="F198" t="n">
-        <v>49.74</v>
+        <v>47.46</v>
       </c>
       <c r="G198" t="n">
-        <v>50.1</v>
+        <v>47.46</v>
       </c>
       <c r="H198" t="n">
-        <v>0.36</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>20.01</v>
+        <v>78.34</v>
       </c>
       <c r="C199" t="n">
-        <v>4.88794977</v>
+        <v>4.90406777</v>
       </c>
       <c r="D199" t="n">
-        <v>50</v>
+        <v>47.86</v>
       </c>
       <c r="E199" t="n">
-        <v>50.5</v>
+        <v>48.68</v>
       </c>
       <c r="F199" t="n">
-        <v>49.04</v>
+        <v>47.7</v>
       </c>
       <c r="G199" t="n">
-        <v>49.06</v>
+        <v>48.48</v>
       </c>
       <c r="H199" t="n">
-        <v>-2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>-18.77</v>
+        <v>12.2</v>
       </c>
       <c r="C200" t="n">
-        <v>4.88607277</v>
+        <v>4.90528777</v>
       </c>
       <c r="D200" t="n">
-        <v>49.08</v>
+        <v>48.1</v>
       </c>
       <c r="E200" t="n">
-        <v>49.78</v>
+        <v>48.7</v>
       </c>
       <c r="F200" t="n">
-        <v>48.7</v>
+        <v>47.38</v>
       </c>
       <c r="G200" t="n">
-        <v>49.4</v>
+        <v>47.88</v>
       </c>
       <c r="H200" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>95.14</v>
+        <v>-50.42</v>
       </c>
       <c r="C201" t="n">
-        <v>4.89558677</v>
+        <v>4.90024577</v>
       </c>
       <c r="D201" t="n">
-        <v>48.66</v>
+        <v>47.34</v>
       </c>
       <c r="E201" t="n">
-        <v>49.22</v>
+        <v>48.28</v>
       </c>
       <c r="F201" t="n">
-        <v>48.02</v>
+        <v>47.06</v>
       </c>
       <c r="G201" t="n">
-        <v>48.22</v>
+        <v>47.9</v>
       </c>
       <c r="H201" t="n">
-        <v>-2.39</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>6.47</v>
+        <v>7.38</v>
       </c>
       <c r="C202" t="n">
-        <v>4.89623377</v>
+        <v>4.90098377</v>
       </c>
       <c r="D202" t="n">
-        <v>48.22</v>
+        <v>49.98</v>
       </c>
       <c r="E202" t="n">
-        <v>48.22</v>
+        <v>51.2</v>
       </c>
       <c r="F202" t="n">
-        <v>47.46</v>
+        <v>49.76</v>
       </c>
       <c r="G202" t="n">
-        <v>47.46</v>
+        <v>50.55</v>
       </c>
       <c r="H202" t="n">
-        <v>-1.58</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>78.34</v>
+        <v>0.19</v>
       </c>
       <c r="C203" t="n">
-        <v>4.90406777</v>
+        <v>4.90100277</v>
       </c>
       <c r="D203" t="n">
-        <v>47.86</v>
+        <v>50.55</v>
       </c>
       <c r="E203" t="n">
-        <v>48.68</v>
+        <v>51.8</v>
       </c>
       <c r="F203" t="n">
-        <v>47.7</v>
+        <v>50.5</v>
       </c>
       <c r="G203" t="n">
-        <v>48.48</v>
+        <v>51.2</v>
       </c>
       <c r="H203" t="n">
-        <v>2.15</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>12.2</v>
+        <v>-404.07</v>
       </c>
       <c r="C204" t="n">
-        <v>4.90528777</v>
+        <v>4.86059577</v>
       </c>
       <c r="D204" t="n">
-        <v>48.1</v>
+        <v>50.3</v>
       </c>
       <c r="E204" t="n">
-        <v>48.7</v>
+        <v>51</v>
       </c>
       <c r="F204" t="n">
-        <v>47.38</v>
+        <v>49.3</v>
       </c>
       <c r="G204" t="n">
-        <v>47.88</v>
+        <v>49.46</v>
       </c>
       <c r="H204" t="n">
-        <v>-1.24</v>
+        <v>-3.4</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>-50.42</v>
+        <v>-104.42</v>
       </c>
       <c r="C205" t="n">
-        <v>4.90024577</v>
+        <v>4.85015377</v>
       </c>
       <c r="D205" t="n">
-        <v>47.34</v>
+        <v>48.86</v>
       </c>
       <c r="E205" t="n">
-        <v>48.28</v>
+        <v>49.74</v>
       </c>
       <c r="F205" t="n">
-        <v>47.06</v>
+        <v>47.6</v>
       </c>
       <c r="G205" t="n">
-        <v>47.9</v>
+        <v>47.68</v>
       </c>
       <c r="H205" t="n">
-        <v>0.04</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>7.38</v>
+        <v>-9.27</v>
       </c>
       <c r="C206" t="n">
-        <v>4.90098377</v>
+        <v>4.84922677</v>
       </c>
       <c r="D206" t="n">
-        <v>49.98</v>
+        <v>47.68</v>
       </c>
       <c r="E206" t="n">
-        <v>51.2</v>
+        <v>48.9</v>
       </c>
       <c r="F206" t="n">
-        <v>49.76</v>
+        <v>47.32</v>
       </c>
       <c r="G206" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="H206" t="n">
-        <v>5.53</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.19</v>
+        <v>-62.41</v>
       </c>
       <c r="C207" t="n">
-        <v>4.90100277</v>
+        <v>4.84298577</v>
       </c>
       <c r="D207" t="n">
-        <v>50.55</v>
+        <v>48.1</v>
       </c>
       <c r="E207" t="n">
-        <v>51.8</v>
+        <v>49</v>
       </c>
       <c r="F207" t="n">
-        <v>50.5</v>
+        <v>47.5</v>
       </c>
       <c r="G207" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="H207" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>-404.07</v>
+        <v>-4.06</v>
       </c>
       <c r="C208" t="n">
-        <v>4.86059577</v>
+        <v>4.84257977</v>
       </c>
       <c r="D208" t="n">
-        <v>50.3</v>
+        <v>47.8</v>
       </c>
       <c r="E208" t="n">
-        <v>51</v>
+        <v>48.6</v>
       </c>
       <c r="F208" t="n">
-        <v>49.3</v>
+        <v>47.16</v>
       </c>
       <c r="G208" t="n">
-        <v>49.46</v>
+        <v>47.98</v>
       </c>
       <c r="H208" t="n">
-        <v>-3.4</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>-104.42</v>
+        <v>107.65</v>
       </c>
       <c r="C209" t="n">
-        <v>4.85015377</v>
+        <v>4.85334477</v>
       </c>
       <c r="D209" t="n">
-        <v>48.86</v>
+        <v>47.86</v>
       </c>
       <c r="E209" t="n">
-        <v>49.74</v>
+        <v>48.44</v>
       </c>
       <c r="F209" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="G209" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="H209" t="n">
-        <v>-3.6</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>-9.27</v>
+        <v>137.46</v>
       </c>
       <c r="C210" t="n">
-        <v>4.84922677</v>
+        <v>4.86709077</v>
       </c>
       <c r="D210" t="n">
-        <v>47.68</v>
+        <v>47.82</v>
       </c>
       <c r="E210" t="n">
-        <v>48.9</v>
+        <v>48.22</v>
       </c>
       <c r="F210" t="n">
-        <v>47.32</v>
+        <v>46.6</v>
       </c>
       <c r="G210" t="n">
-        <v>48.1</v>
+        <v>47.06</v>
       </c>
       <c r="H210" t="n">
-        <v>0.88</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>-62.41</v>
+        <v>154.04</v>
       </c>
       <c r="C211" t="n">
-        <v>4.84298577</v>
+        <v>4.88249477</v>
       </c>
       <c r="D211" t="n">
-        <v>48.1</v>
+        <v>46.68</v>
       </c>
       <c r="E211" t="n">
-        <v>49</v>
+        <v>46.76</v>
       </c>
       <c r="F211" t="n">
-        <v>47.5</v>
+        <v>44.56</v>
       </c>
       <c r="G211" t="n">
-        <v>48.6</v>
+        <v>45.86</v>
       </c>
       <c r="H211" t="n">
-        <v>1.04</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>-4.06</v>
+        <v>78.03</v>
       </c>
       <c r="C212" t="n">
-        <v>4.84257977</v>
+        <v>4.89029777</v>
       </c>
       <c r="D212" t="n">
-        <v>47.8</v>
+        <v>46.56</v>
       </c>
       <c r="E212" t="n">
-        <v>48.6</v>
+        <v>48</v>
       </c>
       <c r="F212" t="n">
-        <v>47.16</v>
+        <v>46.2</v>
       </c>
       <c r="G212" t="n">
-        <v>47.98</v>
+        <v>46.38</v>
       </c>
       <c r="H212" t="n">
-        <v>-1.28</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>107.65</v>
+        <v>401.67</v>
       </c>
       <c r="C213" t="n">
-        <v>4.85334477</v>
+        <v>4.93046477</v>
       </c>
       <c r="D213" t="n">
-        <v>47.86</v>
+        <v>47.28</v>
       </c>
       <c r="E213" t="n">
-        <v>48.44</v>
+        <v>48.88</v>
       </c>
       <c r="F213" t="n">
-        <v>46.5</v>
+        <v>47.12</v>
       </c>
       <c r="G213" t="n">
         <v>47.82</v>
       </c>
       <c r="H213" t="n">
-        <v>-0.33</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>137.46</v>
+        <v>-79.33</v>
       </c>
       <c r="C214" t="n">
-        <v>4.86709077</v>
+        <v>4.92253177</v>
       </c>
       <c r="D214" t="n">
-        <v>47.82</v>
+        <v>48.1</v>
       </c>
       <c r="E214" t="n">
-        <v>48.22</v>
+        <v>50.45</v>
       </c>
       <c r="F214" t="n">
-        <v>46.6</v>
+        <v>48.04</v>
       </c>
       <c r="G214" t="n">
-        <v>47.06</v>
+        <v>50.4</v>
       </c>
       <c r="H214" t="n">
-        <v>-1.59</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>154.04</v>
+        <v>-415.48</v>
       </c>
       <c r="C215" t="n">
-        <v>4.88249477</v>
+        <v>4.88098377</v>
       </c>
       <c r="D215" t="n">
-        <v>46.68</v>
+        <v>49.44</v>
       </c>
       <c r="E215" t="n">
-        <v>46.76</v>
+        <v>50.15</v>
       </c>
       <c r="F215" t="n">
-        <v>44.56</v>
+        <v>48.88</v>
       </c>
       <c r="G215" t="n">
-        <v>45.86</v>
+        <v>49.32</v>
       </c>
       <c r="H215" t="n">
-        <v>-2.55</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>78.03</v>
+        <v>-394.96</v>
       </c>
       <c r="C216" t="n">
-        <v>4.89029777</v>
+        <v>4.84148777</v>
       </c>
       <c r="D216" t="n">
-        <v>46.56</v>
+        <v>49.08</v>
       </c>
       <c r="E216" t="n">
-        <v>48</v>
+        <v>49.08</v>
       </c>
       <c r="F216" t="n">
-        <v>46.2</v>
+        <v>47.2</v>
       </c>
       <c r="G216" t="n">
-        <v>46.38</v>
+        <v>47.62</v>
       </c>
       <c r="H216" t="n">
-        <v>1.13</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>401.67</v>
+        <v>-39.23</v>
       </c>
       <c r="C217" t="n">
-        <v>4.93046477</v>
+        <v>4.83756477</v>
       </c>
       <c r="D217" t="n">
-        <v>47.28</v>
+        <v>47.2</v>
       </c>
       <c r="E217" t="n">
-        <v>48.88</v>
+        <v>47.2</v>
       </c>
       <c r="F217" t="n">
-        <v>47.12</v>
+        <v>46.42</v>
       </c>
       <c r="G217" t="n">
-        <v>47.82</v>
+        <v>46.48</v>
       </c>
       <c r="H217" t="n">
-        <v>3.1</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>-79.33</v>
+        <v>219.67</v>
       </c>
       <c r="C218" t="n">
-        <v>4.92253177</v>
+        <v>4.85953177</v>
       </c>
       <c r="D218" t="n">
-        <v>48.1</v>
+        <v>45.74</v>
       </c>
       <c r="E218" t="n">
-        <v>50.45</v>
+        <v>46.44</v>
       </c>
       <c r="F218" t="n">
-        <v>48.04</v>
+        <v>45.38</v>
       </c>
       <c r="G218" t="n">
-        <v>50.4</v>
+        <v>46.34</v>
       </c>
       <c r="H218" t="n">
-        <v>5.4</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>-415.48</v>
+        <v>111.68</v>
       </c>
       <c r="C219" t="n">
-        <v>4.88098377</v>
+        <v>4.87069977</v>
       </c>
       <c r="D219" t="n">
-        <v>49.44</v>
+        <v>45.9</v>
       </c>
       <c r="E219" t="n">
-        <v>50.15</v>
+        <v>47.8</v>
       </c>
       <c r="F219" t="n">
-        <v>48.88</v>
+        <v>45.84</v>
       </c>
       <c r="G219" t="n">
-        <v>49.32</v>
+        <v>47.52</v>
       </c>
       <c r="H219" t="n">
-        <v>-2.14</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>-394.96</v>
+        <v>47.5</v>
       </c>
       <c r="C220" t="n">
-        <v>4.84148777</v>
+        <v>4.87544977</v>
       </c>
       <c r="D220" t="n">
-        <v>49.08</v>
+        <v>47.52</v>
       </c>
       <c r="E220" t="n">
-        <v>49.08</v>
+        <v>48.06</v>
       </c>
       <c r="F220" t="n">
-        <v>47.2</v>
+        <v>46.06</v>
       </c>
       <c r="G220" t="n">
-        <v>47.62</v>
+        <v>46.12</v>
       </c>
       <c r="H220" t="n">
-        <v>-3.45</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>-39.23</v>
+        <v>-30.32</v>
       </c>
       <c r="C221" t="n">
-        <v>4.83756477</v>
+        <v>4.87241777</v>
       </c>
       <c r="D221" t="n">
-        <v>47.2</v>
+        <v>46.92</v>
       </c>
       <c r="E221" t="n">
-        <v>47.2</v>
+        <v>47.42</v>
       </c>
       <c r="F221" t="n">
-        <v>46.42</v>
+        <v>45.94</v>
       </c>
       <c r="G221" t="n">
         <v>46.48</v>
       </c>
       <c r="H221" t="n">
-        <v>-2.39</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>219.67</v>
+        <v>15.46</v>
       </c>
       <c r="C222" t="n">
-        <v>4.85953177</v>
+        <v>4.87396377</v>
       </c>
       <c r="D222" t="n">
-        <v>45.74</v>
+        <v>46.9</v>
       </c>
       <c r="E222" t="n">
-        <v>46.44</v>
+        <v>47.5</v>
       </c>
       <c r="F222" t="n">
-        <v>45.38</v>
+        <v>44.94</v>
       </c>
       <c r="G222" t="n">
-        <v>46.34</v>
+        <v>46.88</v>
       </c>
       <c r="H222" t="n">
-        <v>-0.3</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>111.68</v>
+        <v>57.59</v>
       </c>
       <c r="C223" t="n">
-        <v>4.87069977</v>
+        <v>4.87972277</v>
       </c>
       <c r="D223" t="n">
-        <v>45.9</v>
+        <v>46.9</v>
       </c>
       <c r="E223" t="n">
-        <v>47.8</v>
+        <v>48.46</v>
       </c>
       <c r="F223" t="n">
-        <v>45.84</v>
+        <v>46.8</v>
       </c>
       <c r="G223" t="n">
-        <v>47.52</v>
+        <v>47.56</v>
       </c>
       <c r="H223" t="n">
-        <v>2.55</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>47.5</v>
+        <v>112.19</v>
       </c>
       <c r="C224" t="n">
-        <v>4.87544977</v>
+        <v>4.89094177</v>
       </c>
       <c r="D224" t="n">
-        <v>47.52</v>
+        <v>47.54</v>
       </c>
       <c r="E224" t="n">
-        <v>48.06</v>
+        <v>47.54</v>
       </c>
       <c r="F224" t="n">
-        <v>46.06</v>
+        <v>44.82</v>
       </c>
       <c r="G224" t="n">
-        <v>46.12</v>
+        <v>45.48</v>
       </c>
       <c r="H224" t="n">
-        <v>-2.95</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>-30.32</v>
+        <v>-42.06</v>
       </c>
       <c r="C225" t="n">
-        <v>4.87241777</v>
+        <v>4.88673577</v>
       </c>
       <c r="D225" t="n">
-        <v>46.92</v>
+        <v>45</v>
       </c>
       <c r="E225" t="n">
-        <v>47.42</v>
+        <v>45.8</v>
       </c>
       <c r="F225" t="n">
-        <v>45.94</v>
+        <v>44.68</v>
       </c>
       <c r="G225" t="n">
-        <v>46.48</v>
+        <v>45.08</v>
       </c>
       <c r="H225" t="n">
-        <v>0.78</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>15.46</v>
+        <v>201.66</v>
       </c>
       <c r="C226" t="n">
-        <v>4.87396377</v>
+        <v>4.90690177</v>
       </c>
       <c r="D226" t="n">
-        <v>46.9</v>
+        <v>45.72</v>
       </c>
       <c r="E226" t="n">
-        <v>47.5</v>
+        <v>46.54</v>
       </c>
       <c r="F226" t="n">
-        <v>44.94</v>
+        <v>45.34</v>
       </c>
       <c r="G226" t="n">
-        <v>46.88</v>
+        <v>46.24</v>
       </c>
       <c r="H226" t="n">
-        <v>0.86</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>57.59</v>
+        <v>138.5</v>
       </c>
       <c r="C227" t="n">
-        <v>4.87972277</v>
+        <v>4.92075177</v>
       </c>
       <c r="D227" t="n">
-        <v>46.9</v>
+        <v>45.48</v>
       </c>
       <c r="E227" t="n">
-        <v>48.46</v>
+        <v>47.3</v>
       </c>
       <c r="F227" t="n">
-        <v>46.8</v>
+        <v>45.48</v>
       </c>
       <c r="G227" t="n">
-        <v>47.56</v>
+        <v>46.76</v>
       </c>
       <c r="H227" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>112.19</v>
+        <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>4.89094177</v>
+        <v>4.92075177</v>
       </c>
       <c r="D228" t="n">
-        <v>47.54</v>
+        <v>46.76</v>
       </c>
       <c r="E228" t="n">
-        <v>47.54</v>
+        <v>46.76</v>
       </c>
       <c r="F228" t="n">
-        <v>44.82</v>
+        <v>44.9</v>
       </c>
       <c r="G228" t="n">
-        <v>45.48</v>
+        <v>45.24</v>
       </c>
       <c r="H228" t="n">
-        <v>-4.37</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>-42.06</v>
+        <v>-223.74</v>
       </c>
       <c r="C229" t="n">
-        <v>4.88673577</v>
+        <v>4.89837777</v>
       </c>
       <c r="D229" t="n">
-        <v>45</v>
+        <v>45.38</v>
       </c>
       <c r="E229" t="n">
-        <v>45.8</v>
+        <v>46.84</v>
       </c>
       <c r="F229" t="n">
-        <v>44.68</v>
+        <v>45.36</v>
       </c>
       <c r="G229" t="n">
-        <v>45.08</v>
+        <v>45.74</v>
       </c>
       <c r="H229" t="n">
-        <v>-0.88</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>201.66</v>
+        <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>4.90690177</v>
+        <v>4.89837777</v>
       </c>
       <c r="D230" t="n">
-        <v>45.72</v>
+        <v>45.86</v>
       </c>
       <c r="E230" t="n">
-        <v>46.54</v>
+        <v>45.86</v>
       </c>
       <c r="F230" t="n">
-        <v>45.34</v>
+        <v>44.3</v>
       </c>
       <c r="G230" t="n">
-        <v>46.24</v>
+        <v>44.54</v>
       </c>
       <c r="H230" t="n">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B231" t="n">
-        <v>138.5</v>
-      </c>
-      <c r="C231" t="n">
-        <v>4.92075177</v>
-      </c>
-      <c r="D231" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="E231" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="F231" t="n">
-        <v>45.48</v>
-      </c>
-      <c r="G231" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="H231" t="n">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
-      <c r="C232" t="n">
-        <v>4.92075177</v>
-      </c>
-      <c r="D232" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="E232" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="F232" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="G232" t="n">
-        <v>45.24</v>
-      </c>
-      <c r="H232" t="n">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B233" t="n">
-        <v>-223.74</v>
-      </c>
-      <c r="C233" t="n">
-        <v>4.89837777</v>
-      </c>
-      <c r="D233" t="n">
-        <v>45.38</v>
-      </c>
-      <c r="E233" t="n">
-        <v>46.84</v>
-      </c>
-      <c r="F233" t="n">
-        <v>45.36</v>
-      </c>
-      <c r="G233" t="n">
-        <v>45.74</v>
-      </c>
-      <c r="H233" t="n">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B234" t="n">
-        <v>0</v>
-      </c>
-      <c r="C234" t="n">
-        <v>4.89837777</v>
-      </c>
-      <c r="D234" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="E234" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="F234" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="G234" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="H234" t="n">
         <v>-2.62</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6880,6 +6880,34 @@
         <v>-2.62</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>-45.67</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4.89381077</v>
+      </c>
+      <c r="D231" t="n">
+        <v>44.26</v>
+      </c>
+      <c r="E231" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="F231" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="G231" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="H231" t="n">
+        <v>1.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H231"/>
+  <dimension ref="A1:H232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6908,6 +6908,34 @@
         <v>1.12</v>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
+      <c r="C232" t="n">
+        <v>4.89381077</v>
+      </c>
+      <c r="D232" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="E232" t="n">
+        <v>44.14</v>
+      </c>
+      <c r="F232" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="G232" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="H232" t="n">
+        <v>-5.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H232"/>
+  <dimension ref="A1:H233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6936,6 +6936,34 @@
         <v>-5.37</v>
       </c>
     </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>0</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4.89381077</v>
+      </c>
+      <c r="D233" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="E233" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="F233" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G233" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="H233" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H233"/>
+  <dimension ref="A1:H234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6964,6 +6964,34 @@
         <v>-0.52</v>
       </c>
     </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>0</v>
+      </c>
+      <c r="C234" t="n">
+        <v>4.89381077</v>
+      </c>
+      <c r="D234" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="E234" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="F234" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="G234" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H234"/>
+  <dimension ref="A1:H235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6992,6 +6992,34 @@
         <v>0.47</v>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
+      <c r="C235" t="n">
+        <v>4.89381077</v>
+      </c>
+      <c r="D235" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E235" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="F235" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G235" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H235" t="n">
+        <v>2.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H235"/>
+  <dimension ref="A1:H238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6911,7 +6911,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -6921,25 +6921,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D232" t="n">
-        <v>44.14</v>
+        <v>44.26</v>
       </c>
       <c r="E232" t="n">
-        <v>44.14</v>
+        <v>45.3</v>
       </c>
       <c r="F232" t="n">
-        <v>42.42</v>
+        <v>43.94</v>
       </c>
       <c r="G232" t="n">
-        <v>42.62</v>
+        <v>45.04</v>
       </c>
       <c r="H232" t="n">
-        <v>-5.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -6949,25 +6949,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D233" t="n">
-        <v>42.62</v>
+        <v>44.26</v>
       </c>
       <c r="E233" t="n">
-        <v>42.62</v>
+        <v>45.3</v>
       </c>
       <c r="F233" t="n">
-        <v>41.7</v>
+        <v>43.94</v>
       </c>
       <c r="G233" t="n">
-        <v>42.4</v>
+        <v>45.04</v>
       </c>
       <c r="H233" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -6977,25 +6977,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D234" t="n">
-        <v>42.5</v>
+        <v>44.14</v>
       </c>
       <c r="E234" t="n">
-        <v>43.12</v>
+        <v>44.14</v>
       </c>
       <c r="F234" t="n">
-        <v>42.34</v>
+        <v>42.42</v>
       </c>
       <c r="G234" t="n">
-        <v>42.6</v>
+        <v>42.62</v>
       </c>
       <c r="H234" t="n">
-        <v>0.47</v>
+        <v>-5.37</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -7005,19 +7005,103 @@
         <v>4.89381077</v>
       </c>
       <c r="D235" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="E235" t="n">
+        <v>42.62</v>
+      </c>
+      <c r="F235" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="G235" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="H235" t="n">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" t="n">
+        <v>4.89381077</v>
+      </c>
+      <c r="D236" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="E236" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="F236" t="n">
+        <v>42.34</v>
+      </c>
+      <c r="G236" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>4.89381077</v>
+      </c>
+      <c r="D237" t="n">
         <v>42.2</v>
       </c>
-      <c r="E235" t="n">
+      <c r="E237" t="n">
         <v>43.66</v>
       </c>
-      <c r="F235" t="n">
+      <c r="F237" t="n">
         <v>42.2</v>
       </c>
-      <c r="G235" t="n">
+      <c r="G237" t="n">
         <v>43.5</v>
       </c>
-      <c r="H235" t="n">
+      <c r="H237" t="n">
         <v>2.11</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4.89381077</v>
+      </c>
+      <c r="D238" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="E238" t="n">
+        <v>44.12</v>
+      </c>
+      <c r="F238" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="G238" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="H238" t="n">
+        <v>-1.1</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6911,7 +6911,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -6921,25 +6921,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D232" t="n">
-        <v>44.26</v>
+        <v>44.14</v>
       </c>
       <c r="E232" t="n">
-        <v>45.3</v>
+        <v>44.14</v>
       </c>
       <c r="F232" t="n">
-        <v>43.94</v>
+        <v>42.42</v>
       </c>
       <c r="G232" t="n">
-        <v>45.04</v>
+        <v>42.62</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>-5.37</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -6949,25 +6949,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D233" t="n">
-        <v>44.26</v>
+        <v>42.62</v>
       </c>
       <c r="E233" t="n">
-        <v>45.3</v>
+        <v>42.62</v>
       </c>
       <c r="F233" t="n">
-        <v>43.94</v>
+        <v>41.7</v>
       </c>
       <c r="G233" t="n">
-        <v>45.04</v>
+        <v>42.4</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -6977,25 +6977,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D234" t="n">
-        <v>44.14</v>
+        <v>42.5</v>
       </c>
       <c r="E234" t="n">
-        <v>44.14</v>
+        <v>43.12</v>
       </c>
       <c r="F234" t="n">
-        <v>42.42</v>
+        <v>42.34</v>
       </c>
       <c r="G234" t="n">
-        <v>42.62</v>
+        <v>42.6</v>
       </c>
       <c r="H234" t="n">
-        <v>-5.37</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -7005,102 +7005,46 @@
         <v>4.89381077</v>
       </c>
       <c r="D235" t="n">
-        <v>42.62</v>
+        <v>42.2</v>
       </c>
       <c r="E235" t="n">
-        <v>42.62</v>
+        <v>43.66</v>
       </c>
       <c r="F235" t="n">
-        <v>41.7</v>
+        <v>42.2</v>
       </c>
       <c r="G235" t="n">
-        <v>42.4</v>
+        <v>43.5</v>
       </c>
       <c r="H235" t="n">
-        <v>-0.52</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>53.3157</v>
       </c>
       <c r="C236" t="n">
-        <v>4.89381077</v>
+        <v>4.89914234</v>
       </c>
       <c r="D236" t="n">
-        <v>42.5</v>
+        <v>43.32</v>
       </c>
       <c r="E236" t="n">
-        <v>43.12</v>
+        <v>44.12</v>
       </c>
       <c r="F236" t="n">
-        <v>42.34</v>
+        <v>42.78</v>
       </c>
       <c r="G236" t="n">
-        <v>42.6</v>
+        <v>43.02</v>
       </c>
       <c r="H236" t="n">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B237" t="n">
-        <v>0</v>
-      </c>
-      <c r="C237" t="n">
-        <v>4.89381077</v>
-      </c>
-      <c r="D237" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="E237" t="n">
-        <v>43.66</v>
-      </c>
-      <c r="F237" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="G237" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="H237" t="n">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
-      <c r="C238" t="n">
-        <v>4.89381077</v>
-      </c>
-      <c r="D238" t="n">
-        <v>43.32</v>
-      </c>
-      <c r="E238" t="n">
-        <v>44.12</v>
-      </c>
-      <c r="F238" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="G238" t="n">
-        <v>43.02</v>
-      </c>
-      <c r="H238" t="n">
         <v>-1.1</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H236"/>
+  <dimension ref="A1:H237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7048,6 +7048,34 @@
         <v>-1.1</v>
       </c>
     </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" t="n">
+        <v>4.89914234</v>
+      </c>
+      <c r="D237" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="E237" t="n">
+        <v>45.04</v>
+      </c>
+      <c r="F237" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="G237" t="n">
+        <v>44.66</v>
+      </c>
+      <c r="H237" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7076,6 +7076,34 @@
         <v>3.81</v>
       </c>
     </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4.89914234</v>
+      </c>
+      <c r="D238" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="E238" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="F238" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="G238" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7098,10 +7098,10 @@
         <v>44.42</v>
       </c>
       <c r="G238" t="n">
-        <v>44.74</v>
+        <v>44.9</v>
       </c>
       <c r="H238" t="n">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0</v>
+        <v>53.68</v>
       </c>
       <c r="C238" t="n">
-        <v>4.89914234</v>
+        <v>4.90451034</v>
       </c>
       <c r="D238" t="n">
         <v>45.3</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H238"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7104,6 +7104,34 @@
         <v>0.54</v>
       </c>
     </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>0</v>
+      </c>
+      <c r="C239" t="n">
+        <v>4.90451034</v>
+      </c>
+      <c r="D239" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="E239" t="n">
+        <v>45.36</v>
+      </c>
+      <c r="F239" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="G239" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7126,10 +7126,10 @@
         <v>43.82</v>
       </c>
       <c r="G239" t="n">
-        <v>45.06</v>
+        <v>45.24</v>
       </c>
       <c r="H239" t="n">
-        <v>0.36</v>
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>47.98</v>
       </c>
       <c r="C239" t="n">
-        <v>4.90451034</v>
+        <v>4.90930834</v>
       </c>
       <c r="D239" t="n">
         <v>44.9</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H239"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7132,6 +7132,34 @@
         <v>0.76</v>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" t="n">
+        <v>4.90930834</v>
+      </c>
+      <c r="D240" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="E240" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F240" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="G240" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="H240" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7151,13 +7151,13 @@
         <v>46.1</v>
       </c>
       <c r="F240" t="n">
-        <v>45.06</v>
+        <v>45.12</v>
       </c>
       <c r="G240" t="n">
-        <v>45.06</v>
+        <v>45.3</v>
       </c>
       <c r="H240" t="n">
-        <v>-0.4</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7139,10 +7139,10 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>-23.39</v>
       </c>
       <c r="C240" t="n">
-        <v>4.90930834</v>
+        <v>4.90696934</v>
       </c>
       <c r="D240" t="n">
         <v>45.64</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7160,6 +7160,34 @@
         <v>0.13</v>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>4.90696934</v>
+      </c>
+      <c r="D241" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="E241" t="n">
+        <v>45</v>
+      </c>
+      <c r="F241" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="G241" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="H241" t="n">
+        <v>-2.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7160,34 +7160,6 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
-      <c r="C241" t="n">
-        <v>4.90696934</v>
-      </c>
-      <c r="D241" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="E241" t="n">
-        <v>45</v>
-      </c>
-      <c r="F241" t="n">
-        <v>44.04</v>
-      </c>
-      <c r="G241" t="n">
-        <v>44.24</v>
-      </c>
-      <c r="H241" t="n">
-        <v>-2.34</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7160,6 +7160,34 @@
         <v>0.13</v>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" t="n">
+        <v>4.90696934</v>
+      </c>
+      <c r="D241" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="E241" t="n">
+        <v>45</v>
+      </c>
+      <c r="F241" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="G241" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="H241" t="n">
+        <v>-1.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7167,10 +7167,10 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>-59.23</v>
       </c>
       <c r="C241" t="n">
-        <v>4.90696934</v>
+        <v>4.90104634</v>
       </c>
       <c r="D241" t="n">
         <v>44.54</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H241"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7188,6 +7188,34 @@
         <v>-1.9</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4.90104634</v>
+      </c>
+      <c r="D242" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="E242" t="n">
+        <v>45.66</v>
+      </c>
+      <c r="F242" t="n">
+        <v>44.36</v>
+      </c>
+      <c r="G242" t="n">
+        <v>44.68</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6911,7 +6911,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -6921,25 +6921,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D232" t="n">
-        <v>44.14</v>
+        <v>44.26</v>
       </c>
       <c r="E232" t="n">
-        <v>44.14</v>
+        <v>45.3</v>
       </c>
       <c r="F232" t="n">
-        <v>42.42</v>
+        <v>43.94</v>
       </c>
       <c r="G232" t="n">
-        <v>42.62</v>
+        <v>45.04</v>
       </c>
       <c r="H232" t="n">
-        <v>-5.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -6949,25 +6949,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D233" t="n">
-        <v>42.62</v>
+        <v>44.26</v>
       </c>
       <c r="E233" t="n">
-        <v>42.62</v>
+        <v>45.3</v>
       </c>
       <c r="F233" t="n">
-        <v>41.7</v>
+        <v>43.94</v>
       </c>
       <c r="G233" t="n">
-        <v>42.4</v>
+        <v>45.04</v>
       </c>
       <c r="H233" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -6977,25 +6977,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D234" t="n">
-        <v>42.5</v>
+        <v>44.14</v>
       </c>
       <c r="E234" t="n">
-        <v>43.12</v>
+        <v>44.14</v>
       </c>
       <c r="F234" t="n">
-        <v>42.34</v>
+        <v>42.42</v>
       </c>
       <c r="G234" t="n">
-        <v>42.6</v>
+        <v>42.62</v>
       </c>
       <c r="H234" t="n">
-        <v>0.47</v>
+        <v>-5.37</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -7005,215 +7005,271 @@
         <v>4.89381077</v>
       </c>
       <c r="D235" t="n">
-        <v>42.2</v>
+        <v>42.62</v>
       </c>
       <c r="E235" t="n">
-        <v>43.66</v>
+        <v>42.62</v>
       </c>
       <c r="F235" t="n">
-        <v>42.2</v>
+        <v>41.7</v>
       </c>
       <c r="G235" t="n">
-        <v>43.5</v>
+        <v>42.4</v>
       </c>
       <c r="H235" t="n">
-        <v>2.11</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>53.3157</v>
+        <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>4.89914234</v>
+        <v>4.89381077</v>
       </c>
       <c r="D236" t="n">
-        <v>43.32</v>
+        <v>42.5</v>
       </c>
       <c r="E236" t="n">
-        <v>44.12</v>
+        <v>43.12</v>
       </c>
       <c r="F236" t="n">
-        <v>42.78</v>
+        <v>42.34</v>
       </c>
       <c r="G236" t="n">
-        <v>43.02</v>
+        <v>42.6</v>
       </c>
       <c r="H236" t="n">
-        <v>-1.1</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>0</v>
       </c>
       <c r="C237" t="n">
-        <v>4.89914234</v>
+        <v>4.89381077</v>
       </c>
       <c r="D237" t="n">
-        <v>43.14</v>
+        <v>42.2</v>
       </c>
       <c r="E237" t="n">
-        <v>45.04</v>
+        <v>43.66</v>
       </c>
       <c r="F237" t="n">
-        <v>43.02</v>
+        <v>42.2</v>
       </c>
       <c r="G237" t="n">
-        <v>44.66</v>
+        <v>43.5</v>
       </c>
       <c r="H237" t="n">
-        <v>3.81</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>53.68</v>
+        <v>53.3157</v>
       </c>
       <c r="C238" t="n">
-        <v>4.90451034</v>
+        <v>4.89914234</v>
       </c>
       <c r="D238" t="n">
-        <v>45.3</v>
+        <v>43.32</v>
       </c>
       <c r="E238" t="n">
-        <v>45.62</v>
+        <v>44.12</v>
       </c>
       <c r="F238" t="n">
-        <v>44.42</v>
+        <v>42.78</v>
       </c>
       <c r="G238" t="n">
-        <v>44.9</v>
+        <v>43.02</v>
       </c>
       <c r="H238" t="n">
-        <v>0.54</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>47.98</v>
+        <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>4.90930834</v>
+        <v>4.89914234</v>
       </c>
       <c r="D239" t="n">
-        <v>44.9</v>
+        <v>43.14</v>
       </c>
       <c r="E239" t="n">
-        <v>45.36</v>
+        <v>45.04</v>
       </c>
       <c r="F239" t="n">
-        <v>43.82</v>
+        <v>43.02</v>
       </c>
       <c r="G239" t="n">
-        <v>45.24</v>
+        <v>44.66</v>
       </c>
       <c r="H239" t="n">
-        <v>0.76</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>-23.39</v>
+        <v>53.68</v>
       </c>
       <c r="C240" t="n">
-        <v>4.90696934</v>
+        <v>4.90451034</v>
       </c>
       <c r="D240" t="n">
-        <v>45.64</v>
+        <v>45.3</v>
       </c>
       <c r="E240" t="n">
-        <v>46.1</v>
+        <v>45.62</v>
       </c>
       <c r="F240" t="n">
-        <v>45.12</v>
+        <v>44.42</v>
       </c>
       <c r="G240" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="H240" t="n">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>-59.23</v>
+        <v>47.98</v>
       </c>
       <c r="C241" t="n">
-        <v>4.90104634</v>
+        <v>4.90930834</v>
       </c>
       <c r="D241" t="n">
-        <v>44.54</v>
+        <v>44.9</v>
       </c>
       <c r="E241" t="n">
-        <v>45</v>
+        <v>45.36</v>
       </c>
       <c r="F241" t="n">
-        <v>44.04</v>
+        <v>43.82</v>
       </c>
       <c r="G241" t="n">
-        <v>44.44</v>
+        <v>45.24</v>
       </c>
       <c r="H241" t="n">
-        <v>-1.9</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>-23.39</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4.90696934</v>
+      </c>
+      <c r="D242" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="E242" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F242" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="G242" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>-59.23</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4.90104634</v>
+      </c>
+      <c r="D243" t="n">
+        <v>44.54</v>
+      </c>
+      <c r="E243" t="n">
+        <v>45</v>
+      </c>
+      <c r="F243" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="G243" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="H243" t="n">
+        <v>-1.9</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="B242" t="n">
+      <c r="B244" t="n">
         <v>0</v>
       </c>
-      <c r="C242" t="n">
+      <c r="C244" t="n">
         <v>4.90104634</v>
       </c>
-      <c r="D242" t="n">
+      <c r="D244" t="n">
         <v>44.88</v>
       </c>
-      <c r="E242" t="n">
+      <c r="E244" t="n">
         <v>45.66</v>
       </c>
-      <c r="F242" t="n">
+      <c r="F244" t="n">
         <v>44.36</v>
       </c>
-      <c r="G242" t="n">
-        <v>44.68</v>
-      </c>
-      <c r="H242" t="n">
-        <v>0.54</v>
+      <c r="G244" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.72</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H244"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6911,7 +6911,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -6921,25 +6921,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D232" t="n">
-        <v>44.26</v>
+        <v>44.14</v>
       </c>
       <c r="E232" t="n">
-        <v>45.3</v>
+        <v>44.14</v>
       </c>
       <c r="F232" t="n">
-        <v>43.94</v>
+        <v>42.42</v>
       </c>
       <c r="G232" t="n">
-        <v>45.04</v>
+        <v>42.62</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>-5.37</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -6949,25 +6949,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D233" t="n">
-        <v>44.26</v>
+        <v>42.62</v>
       </c>
       <c r="E233" t="n">
-        <v>45.3</v>
+        <v>42.62</v>
       </c>
       <c r="F233" t="n">
-        <v>43.94</v>
+        <v>41.7</v>
       </c>
       <c r="G233" t="n">
-        <v>45.04</v>
+        <v>42.4</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -6977,25 +6977,25 @@
         <v>4.89381077</v>
       </c>
       <c r="D234" t="n">
-        <v>44.14</v>
+        <v>42.5</v>
       </c>
       <c r="E234" t="n">
-        <v>44.14</v>
+        <v>43.12</v>
       </c>
       <c r="F234" t="n">
-        <v>42.42</v>
+        <v>42.34</v>
       </c>
       <c r="G234" t="n">
-        <v>42.62</v>
+        <v>42.6</v>
       </c>
       <c r="H234" t="n">
-        <v>-5.37</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -7005,270 +7005,214 @@
         <v>4.89381077</v>
       </c>
       <c r="D235" t="n">
-        <v>42.62</v>
+        <v>42.2</v>
       </c>
       <c r="E235" t="n">
-        <v>42.62</v>
+        <v>43.66</v>
       </c>
       <c r="F235" t="n">
-        <v>41.7</v>
+        <v>42.2</v>
       </c>
       <c r="G235" t="n">
-        <v>42.4</v>
+        <v>43.5</v>
       </c>
       <c r="H235" t="n">
-        <v>-0.52</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>53.3157</v>
       </c>
       <c r="C236" t="n">
-        <v>4.89381077</v>
+        <v>4.89914234</v>
       </c>
       <c r="D236" t="n">
-        <v>42.5</v>
+        <v>43.32</v>
       </c>
       <c r="E236" t="n">
-        <v>43.12</v>
+        <v>44.12</v>
       </c>
       <c r="F236" t="n">
-        <v>42.34</v>
+        <v>42.78</v>
       </c>
       <c r="G236" t="n">
-        <v>42.6</v>
+        <v>43.02</v>
       </c>
       <c r="H236" t="n">
-        <v>0.47</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B237" t="n">
         <v>0</v>
       </c>
       <c r="C237" t="n">
-        <v>4.89381077</v>
+        <v>4.89914234</v>
       </c>
       <c r="D237" t="n">
-        <v>42.2</v>
+        <v>43.14</v>
       </c>
       <c r="E237" t="n">
-        <v>43.66</v>
+        <v>45.04</v>
       </c>
       <c r="F237" t="n">
-        <v>42.2</v>
+        <v>43.02</v>
       </c>
       <c r="G237" t="n">
-        <v>43.5</v>
+        <v>44.66</v>
       </c>
       <c r="H237" t="n">
-        <v>2.11</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>53.3157</v>
+        <v>53.68</v>
       </c>
       <c r="C238" t="n">
-        <v>4.89914234</v>
+        <v>4.90451034</v>
       </c>
       <c r="D238" t="n">
-        <v>43.32</v>
+        <v>45.3</v>
       </c>
       <c r="E238" t="n">
-        <v>44.12</v>
+        <v>45.62</v>
       </c>
       <c r="F238" t="n">
-        <v>42.78</v>
+        <v>44.42</v>
       </c>
       <c r="G238" t="n">
-        <v>43.02</v>
+        <v>44.9</v>
       </c>
       <c r="H238" t="n">
-        <v>-1.1</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0</v>
+        <v>47.98</v>
       </c>
       <c r="C239" t="n">
-        <v>4.89914234</v>
+        <v>4.90930834</v>
       </c>
       <c r="D239" t="n">
-        <v>43.14</v>
+        <v>44.9</v>
       </c>
       <c r="E239" t="n">
-        <v>45.04</v>
+        <v>45.36</v>
       </c>
       <c r="F239" t="n">
-        <v>43.02</v>
+        <v>43.82</v>
       </c>
       <c r="G239" t="n">
-        <v>44.66</v>
+        <v>45.24</v>
       </c>
       <c r="H239" t="n">
-        <v>3.81</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>53.68</v>
+        <v>-23.39</v>
       </c>
       <c r="C240" t="n">
-        <v>4.90451034</v>
+        <v>4.90696934</v>
       </c>
       <c r="D240" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="E240" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="F240" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="G240" t="n">
         <v>45.3</v>
       </c>
-      <c r="E240" t="n">
-        <v>45.62</v>
-      </c>
-      <c r="F240" t="n">
-        <v>44.42</v>
-      </c>
-      <c r="G240" t="n">
-        <v>44.9</v>
-      </c>
       <c r="H240" t="n">
-        <v>0.54</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>47.98</v>
+        <v>-59.23</v>
       </c>
       <c r="C241" t="n">
-        <v>4.90930834</v>
+        <v>4.90104634</v>
       </c>
       <c r="D241" t="n">
-        <v>44.9</v>
+        <v>44.54</v>
       </c>
       <c r="E241" t="n">
-        <v>45.36</v>
+        <v>45</v>
       </c>
       <c r="F241" t="n">
-        <v>43.82</v>
+        <v>44.04</v>
       </c>
       <c r="G241" t="n">
-        <v>45.24</v>
+        <v>44.44</v>
       </c>
       <c r="H241" t="n">
-        <v>0.76</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>-23.39</v>
+        <v>-88.19</v>
       </c>
       <c r="C242" t="n">
-        <v>4.90696934</v>
+        <v>4.89222734</v>
       </c>
       <c r="D242" t="n">
-        <v>45.64</v>
+        <v>44.88</v>
       </c>
       <c r="E242" t="n">
-        <v>46.1</v>
+        <v>45.66</v>
       </c>
       <c r="F242" t="n">
-        <v>45.12</v>
+        <v>44.36</v>
       </c>
       <c r="G242" t="n">
-        <v>45.3</v>
+        <v>44.76</v>
       </c>
       <c r="H242" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>-59.23</v>
-      </c>
-      <c r="C243" t="n">
-        <v>4.90104634</v>
-      </c>
-      <c r="D243" t="n">
-        <v>44.54</v>
-      </c>
-      <c r="E243" t="n">
-        <v>45</v>
-      </c>
-      <c r="F243" t="n">
-        <v>44.04</v>
-      </c>
-      <c r="G243" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="H243" t="n">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B244" t="n">
-        <v>0</v>
-      </c>
-      <c r="C244" t="n">
-        <v>4.90104634</v>
-      </c>
-      <c r="D244" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="E244" t="n">
-        <v>45.66</v>
-      </c>
-      <c r="F244" t="n">
-        <v>44.36</v>
-      </c>
-      <c r="G244" t="n">
-        <v>44.76</v>
-      </c>
-      <c r="H244" t="n">
         <v>0.72</v>
       </c>
     </row>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7216,6 +7216,34 @@
         <v>0.72</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4.89222734</v>
+      </c>
+      <c r="D243" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="E243" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="F243" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="G243" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7216,34 +7216,6 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B243" t="n">
-        <v>0</v>
-      </c>
-      <c r="C243" t="n">
-        <v>4.89222734</v>
-      </c>
-      <c r="D243" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="E243" t="n">
-        <v>45.98</v>
-      </c>
-      <c r="F243" t="n">
-        <v>44.28</v>
-      </c>
-      <c r="G243" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="H243" t="n">
-        <v>1.65</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H242"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7216,6 +7216,34 @@
         <v>0.72</v>
       </c>
     </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>0</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4.89222734</v>
+      </c>
+      <c r="D243" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="E243" t="n">
+        <v>45.98</v>
+      </c>
+      <c r="F243" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="G243" t="n">
+        <v>45.64</v>
+      </c>
+      <c r="H243" t="n">
+        <v>1.97</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7223,10 +7223,10 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>-25.39</v>
       </c>
       <c r="C243" t="n">
-        <v>4.89222734</v>
+        <v>4.88968834</v>
       </c>
       <c r="D243" t="n">
         <v>44.5</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7244,6 +7244,34 @@
         <v>1.97</v>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>0</v>
+      </c>
+      <c r="C244" t="n">
+        <v>4.88968834</v>
+      </c>
+      <c r="D244" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="E244" t="n">
+        <v>47.58</v>
+      </c>
+      <c r="F244" t="n">
+        <v>45.34</v>
+      </c>
+      <c r="G244" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7266,10 +7266,10 @@
         <v>45.34</v>
       </c>
       <c r="G244" t="n">
-        <v>45.74</v>
+        <v>45.82</v>
       </c>
       <c r="H244" t="n">
-        <v>0.22</v>
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>-66.3309</v>
       </c>
       <c r="C244" t="n">
-        <v>4.88968834</v>
+        <v>4.88305525</v>
       </c>
       <c r="D244" t="n">
         <v>46.98</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H244"/>
+  <dimension ref="A1:H245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7272,6 +7272,34 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>0</v>
+      </c>
+      <c r="C245" t="n">
+        <v>4.88305525</v>
+      </c>
+      <c r="D245" t="n">
+        <v>45.02</v>
+      </c>
+      <c r="E245" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="F245" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="G245" t="n">
+        <v>43.38</v>
+      </c>
+      <c r="H245" t="n">
+        <v>-5.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>33.86</v>
       </c>
       <c r="C245" t="n">
-        <v>4.88305525</v>
+        <v>4.88644125</v>
       </c>
       <c r="D245" t="n">
         <v>45.02</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H245"/>
+  <dimension ref="A1:H246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7300,6 +7300,34 @@
         <v>-5.33</v>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
+      <c r="C246" t="n">
+        <v>4.88644125</v>
+      </c>
+      <c r="D246" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="E246" t="n">
+        <v>46.04</v>
+      </c>
+      <c r="F246" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="G246" t="n">
+        <v>45.08</v>
+      </c>
+      <c r="H246" t="n">
+        <v>3.92</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>-2.23</v>
       </c>
       <c r="C246" t="n">
-        <v>4.88644125</v>
+        <v>4.88621825</v>
       </c>
       <c r="D246" t="n">
         <v>44.88</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H246"/>
+  <dimension ref="A1:H247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7328,6 +7328,34 @@
         <v>3.92</v>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
+      <c r="C247" t="n">
+        <v>4.88621825</v>
+      </c>
+      <c r="D247" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="E247" t="n">
+        <v>45.56</v>
+      </c>
+      <c r="F247" t="n">
+        <v>44.04</v>
+      </c>
+      <c r="G247" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="H247" t="n">
+        <v>-1.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7350,10 +7350,10 @@
         <v>44.04</v>
       </c>
       <c r="G247" t="n">
-        <v>44.6</v>
+        <v>44.46</v>
       </c>
       <c r="H247" t="n">
-        <v>-1.06</v>
+        <v>-1.38</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7335,10 +7335,10 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>124.78</v>
       </c>
       <c r="C247" t="n">
-        <v>4.88621825</v>
+        <v>4.89869625</v>
       </c>
       <c r="D247" t="n">
         <v>45.56</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H247"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7356,6 +7356,34 @@
         <v>-1.38</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" t="n">
+        <v>4.89869625</v>
+      </c>
+      <c r="D248" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="E248" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="F248" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="G248" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="H248" t="n">
+        <v>-2.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H248"/>
+  <dimension ref="A1:H247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7356,34 +7356,6 @@
         <v>-1.38</v>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
-      <c r="C248" t="n">
-        <v>4.89869625</v>
-      </c>
-      <c r="D248" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="E248" t="n">
-        <v>44.74</v>
-      </c>
-      <c r="F248" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="G248" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="H248" t="n">
-        <v>-2.61</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H247"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7356,6 +7356,34 @@
         <v>-1.38</v>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
+      <c r="C248" t="n">
+        <v>4.89869625</v>
+      </c>
+      <c r="D248" t="n">
+        <v>44.44</v>
+      </c>
+      <c r="E248" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="F248" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="G248" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="H248" t="n">
+        <v>-2.29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7363,10 +7363,10 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>-151.04</v>
       </c>
       <c r="C248" t="n">
-        <v>4.89869625</v>
+        <v>4.88359225</v>
       </c>
       <c r="D248" t="n">
         <v>44.44</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H248"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7384,6 +7384,34 @@
         <v>-2.29</v>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
+      <c r="C249" t="n">
+        <v>4.88359225</v>
+      </c>
+      <c r="D249" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="E249" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="F249" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="G249" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="H249" t="n">
+        <v>2.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7391,10 +7391,10 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0</v>
+        <v>27.02</v>
       </c>
       <c r="C249" t="n">
-        <v>4.88359225</v>
+        <v>4.88629425</v>
       </c>
       <c r="D249" t="n">
         <v>43.48</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7412,6 +7412,34 @@
         <v>2.76</v>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" t="n">
+        <v>4.88629425</v>
+      </c>
+      <c r="D250" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="E250" t="n">
+        <v>44.76</v>
+      </c>
+      <c r="F250" t="n">
+        <v>43.74</v>
+      </c>
+      <c r="G250" t="n">
+        <v>43.88</v>
+      </c>
+      <c r="H250" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7431,13 +7431,13 @@
         <v>44.76</v>
       </c>
       <c r="F250" t="n">
-        <v>43.74</v>
+        <v>43.5</v>
       </c>
       <c r="G250" t="n">
-        <v>43.88</v>
+        <v>43.54</v>
       </c>
       <c r="H250" t="n">
-        <v>-1.7</v>
+        <v>-2.46</v>
       </c>
     </row>
   </sheetData>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7419,10 +7419,10 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0</v>
+        <v>119.66</v>
       </c>
       <c r="C250" t="n">
-        <v>4.88629425</v>
+        <v>4.89826025</v>
       </c>
       <c r="D250" t="n">
         <v>44.76</v>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H250"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7440,6 +7440,34 @@
         <v>-2.46</v>
       </c>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" t="n">
+        <v>4.89826025</v>
+      </c>
+      <c r="D251" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="E251" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="F251" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="G251" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="H251" t="n">
+        <v>-1.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/liauto_southbound.xlsx
+++ b/liauto_southbound.xlsx
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0</v>
+        <v>-44.3</v>
       </c>
       <c r="C251" t="n">
-        <v>4.89826025</v>
+        <v>4.89383025</v>
       </c>
       <c r="D251" t="n">
         <v>43.6</v>
